--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ceaa8977d2236823/Documents/GitHub/451-DBF-Team01/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\Fall 2026\AAE 451\451-DBF-Team01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{D90AE71A-0B5B-4B86-868D-16070F90B040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27328F69-6F6C-4A88-B232-EE2B8B09F70C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC9010D4-B4DA-4D64-B885-B91E588D68F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="-23430" yWindow="3600" windowWidth="9255" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INPUTS" sheetId="1" r:id="rId1"/>
@@ -543,15 +543,9 @@
     <t>tc_wing</t>
   </si>
   <si>
-    <t>NACA 0012 max thickness</t>
-  </si>
-  <si>
     <t>xcm_hstab</t>
   </si>
   <si>
-    <t>NACA 0012 location of max thickness</t>
-  </si>
-  <si>
     <t>c_vstab</t>
   </si>
   <si>
@@ -664,6 +658,12 @@
   </si>
   <si>
     <t>Wing Root Height</t>
+  </si>
+  <si>
+    <t>NACA 0010 max thickness</t>
+  </si>
+  <si>
+    <t>NACA 0010 location of max thickness</t>
   </si>
 </sst>
 </file>
@@ -2572,19 +2572,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R132"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.7" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.65" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="34.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.6640625" style="1" customWidth="1"/>
-    <col min="7" max="19" width="8.6640625" style="1" customWidth="1"/>
-    <col min="20" max="16384" width="8.6640625" style="1"/>
+    <col min="1" max="1" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="34.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" style="1" customWidth="1"/>
+    <col min="7" max="19" width="8.7109375" style="1" customWidth="1"/>
+    <col min="20" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -2598,7 +2598,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F1" s="16" t="s">
         <v>147</v>
@@ -2618,7 +2618,7 @@
       <c r="Q1" s="3"/>
       <c r="R1" s="3"/>
     </row>
-    <row r="2" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -2650,7 +2650,7 @@
       <c r="Q2" s="3"/>
       <c r="R2" s="3"/>
     </row>
-    <row r="3" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
@@ -2680,7 +2680,7 @@
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
     </row>
-    <row r="4" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>14</v>
       </c>
@@ -2710,7 +2710,7 @@
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
     </row>
-    <row r="5" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>17</v>
       </c>
@@ -2742,7 +2742,7 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
     </row>
-    <row r="6" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>22</v>
       </c>
@@ -2774,9 +2774,9 @@
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
     </row>
-    <row r="7" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B7" s="13">
         <f>1.78*(1-0.045*B8^0.68)-0.64</f>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
@@ -2805,7 +2805,7 @@
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
     </row>
-    <row r="8" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>26</v>
       </c>
@@ -2838,9 +2838,9 @@
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
     </row>
-    <row r="9" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B9" s="14" cm="1">
         <f t="array" ref="B9">1/(PI()*B7*B8)</f>
@@ -2869,7 +2869,7 @@
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
     </row>
-    <row r="10" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>32</v>
       </c>
@@ -2899,7 +2899,7 @@
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
     </row>
-    <row r="11" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>35</v>
       </c>
@@ -2931,7 +2931,7 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
     </row>
-    <row r="12" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>39</v>
       </c>
@@ -2964,7 +2964,7 @@
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
     </row>
-    <row r="13" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>43</v>
       </c>
@@ -2997,12 +2997,12 @@
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
     </row>
-    <row r="14" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>47</v>
       </c>
       <c r="B14" s="14">
-        <v>2.7199999999999998E-2</v>
+        <v>2.8299999999999999E-2</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>18</v>
@@ -3011,7 +3011,7 @@
         <v>48</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>49</v>
@@ -3031,13 +3031,13 @@
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
     </row>
-    <row r="15" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>142</v>
       </c>
       <c r="B15" s="14" cm="1">
         <f t="array" ref="B15">B14+B9*B10^2</f>
-        <v>3.3874132425993971E-2</v>
+        <v>3.4974132425993974E-2</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>18</v>
@@ -3062,13 +3062,13 @@
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
     </row>
-    <row r="16" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>53</v>
       </c>
       <c r="B16" s="14" cm="1">
         <f t="array" ref="B16">B14+B9*B12^2</f>
-        <v>3.3874132425993971E-2</v>
+        <v>3.4974132425993974E-2</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>18</v>
@@ -3095,13 +3095,13 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
     </row>
-    <row r="17" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>56</v>
       </c>
       <c r="B17" s="14" cm="1">
         <f t="array" ref="B17">B16-B5*B12</f>
-        <v>1.8874132425993971E-2</v>
+        <v>1.9974132425993975E-2</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>18</v>
@@ -3126,13 +3126,13 @@
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
     </row>
-    <row r="18" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>59</v>
       </c>
       <c r="B18" s="13" cm="1">
         <f t="array" ref="B18">B10/B15</f>
-        <v>8.856315380339872</v>
+        <v>8.5777681729434327</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>18</v>
@@ -3157,7 +3157,7 @@
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
     </row>
-    <row r="19" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>62</v>
       </c>
@@ -3187,7 +3187,7 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
     </row>
-    <row r="20" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>65</v>
       </c>
@@ -3217,7 +3217,7 @@
       <c r="Q20" s="3"/>
       <c r="R20" s="3"/>
     </row>
-    <row r="21" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>67</v>
       </c>
@@ -3248,7 +3248,7 @@
       <c r="Q21" s="3"/>
       <c r="R21" s="3"/>
     </row>
-    <row r="22" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>69</v>
       </c>
@@ -3279,7 +3279,7 @@
       <c r="Q22" s="3"/>
       <c r="R22" s="3"/>
     </row>
-    <row r="23" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>72</v>
       </c>
@@ -3308,7 +3308,7 @@
       <c r="Q23" s="3"/>
       <c r="R23" s="3"/>
     </row>
-    <row r="24" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>74</v>
       </c>
@@ -3339,7 +3339,7 @@
       <c r="Q24" s="3"/>
       <c r="R24" s="3"/>
     </row>
-    <row r="25" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>77</v>
       </c>
@@ -3369,7 +3369,7 @@
       <c r="Q25" s="3"/>
       <c r="R25" s="3"/>
     </row>
-    <row r="26" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>80</v>
       </c>
@@ -3399,7 +3399,7 @@
       <c r="Q26" s="3"/>
       <c r="R26" s="3"/>
     </row>
-    <row r="27" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>83</v>
       </c>
@@ -3428,7 +3428,7 @@
       <c r="Q27" s="3"/>
       <c r="R27" s="3"/>
     </row>
-    <row r="28" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>86</v>
       </c>
@@ -3458,7 +3458,7 @@
       <c r="Q28" s="3"/>
       <c r="R28" s="3"/>
     </row>
-    <row r="29" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>89</v>
       </c>
@@ -3488,7 +3488,7 @@
       <c r="Q29" s="3"/>
       <c r="R29" s="3"/>
     </row>
-    <row r="30" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>92</v>
       </c>
@@ -3518,7 +3518,7 @@
       <c r="Q30" s="3"/>
       <c r="R30" s="3"/>
     </row>
-    <row r="31" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>94</v>
       </c>
@@ -3548,7 +3548,7 @@
       <c r="Q31" s="3"/>
       <c r="R31" s="3"/>
     </row>
-    <row r="32" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>97</v>
       </c>
@@ -3578,7 +3578,7 @@
       <c r="Q32" s="3"/>
       <c r="R32" s="3"/>
     </row>
-    <row r="33" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>100</v>
       </c>
@@ -3607,7 +3607,7 @@
       <c r="Q33" s="3"/>
       <c r="R33" s="3"/>
     </row>
-    <row r="34" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>102</v>
       </c>
@@ -3637,7 +3637,7 @@
       <c r="Q34" s="3"/>
       <c r="R34" s="3"/>
     </row>
-    <row r="35" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>105</v>
       </c>
@@ -3665,7 +3665,7 @@
       <c r="Q35" s="3"/>
       <c r="R35" s="3"/>
     </row>
-    <row r="36" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>108</v>
       </c>
@@ -3693,7 +3693,7 @@
       <c r="Q36" s="3"/>
       <c r="R36" s="3"/>
     </row>
-    <row r="37" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>111</v>
       </c>
@@ -3721,7 +3721,7 @@
       <c r="Q37" s="3"/>
       <c r="R37" s="3"/>
     </row>
-    <row r="38" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
         <v>113</v>
       </c>
@@ -3751,7 +3751,7 @@
       <c r="Q38" s="3"/>
       <c r="R38" s="3"/>
     </row>
-    <row r="39" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>117</v>
       </c>
@@ -3780,7 +3780,7 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
     </row>
-    <row r="40" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>120</v>
       </c>
@@ -3809,7 +3809,7 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
     </row>
-    <row r="41" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
         <v>143</v>
       </c>
@@ -3839,9 +3839,9 @@
       <c r="Q41" s="3"/>
       <c r="R41" s="3"/>
     </row>
-    <row r="42" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B42" s="10">
         <f>B40/(B54-B55)</f>
@@ -3866,7 +3866,7 @@
       <c r="Q42" s="3"/>
       <c r="R42" s="3"/>
     </row>
-    <row r="43" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>126</v>
       </c>
@@ -3879,7 +3879,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="7" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
@@ -3894,7 +3894,7 @@
       <c r="Q43" s="3"/>
       <c r="R43" s="3"/>
     </row>
-    <row r="44" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
         <v>128</v>
       </c>
@@ -3922,9 +3922,9 @@
       <c r="Q44" s="3"/>
       <c r="R44" s="3"/>
     </row>
-    <row r="45" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B45" s="6">
         <v>0.23</v>
@@ -3933,7 +3933,7 @@
         <v>18</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="3"/>
@@ -3950,7 +3950,7 @@
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
     </row>
-    <row r="46" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>131</v>
       </c>
@@ -3980,7 +3980,7 @@
       <c r="Q46" s="3"/>
       <c r="R46" s="3"/>
     </row>
-    <row r="47" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>134</v>
       </c>
@@ -4010,12 +4010,12 @@
       <c r="Q47" s="3"/>
       <c r="R47" s="3"/>
     </row>
-    <row r="48" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
         <v>159</v>
       </c>
       <c r="B48" s="6">
-        <v>0.12</v>
+        <v>0.19600000000000001</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>81</v>
@@ -4040,23 +4040,19 @@
       <c r="Q48" s="3"/>
       <c r="R48" s="3"/>
     </row>
-    <row r="49" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="B49" s="6">
-        <v>2.75</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>138</v>
-      </c>
+        <v>0.53900000000000003</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D49" s="2"/>
       <c r="E49" s="2"/>
-      <c r="F49" s="2" t="s">
-        <v>139</v>
-      </c>
+      <c r="F49" s="2"/>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
@@ -4070,20 +4066,24 @@
       <c r="Q49" s="3"/>
       <c r="R49" s="3"/>
     </row>
-    <row r="50" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="B50" s="6">
-        <f>B49*B48</f>
-        <v>0.32999999999999996</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="D50" s="2"/>
+        <v>165</v>
+      </c>
+      <c r="B50" s="22">
+        <f>B49/B48</f>
+        <v>2.75</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>138</v>
+      </c>
       <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
+      <c r="F50" s="2" t="s">
+        <v>139</v>
+      </c>
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
@@ -4097,7 +4097,7 @@
       <c r="Q50" s="3"/>
       <c r="R50" s="3"/>
     </row>
-    <row r="51" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
         <v>140</v>
       </c>
@@ -4111,7 +4111,7 @@
         <v>141</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F51" s="7"/>
       <c r="G51" s="3"/>
@@ -4127,19 +4127,19 @@
       <c r="Q51" s="3"/>
       <c r="R51" s="3"/>
     </row>
-    <row r="52" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="8" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B52" s="22">
-        <f>1/(PI()*B51*B49)</f>
+        <f>1/(PI()*B51*B50)</f>
         <v>0.17807546080212067</v>
       </c>
       <c r="C52" s="8" t="s">
         <v>18</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E52" s="8"/>
       <c r="F52" s="7"/>
@@ -4156,7 +4156,7 @@
       <c r="Q52" s="3"/>
       <c r="R52" s="3"/>
     </row>
-    <row r="53" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>144</v>
       </c>
@@ -4184,7 +4184,7 @@
       <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
     </row>
-    <row r="54" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="8" t="s">
         <v>148</v>
       </c>
@@ -4212,7 +4212,7 @@
       <c r="Q54" s="3"/>
       <c r="R54" s="3"/>
     </row>
-    <row r="55" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
         <v>150</v>
       </c>
@@ -4240,7 +4240,7 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
     </row>
-    <row r="56" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="8" t="s">
         <v>149</v>
       </c>
@@ -4268,12 +4268,12 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
     </row>
-    <row r="57" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
         <v>152</v>
       </c>
       <c r="B57" s="3">
-        <v>0.127</v>
+        <v>0.24299999999999999</v>
       </c>
       <c r="C57" s="8" t="s">
         <v>121</v>
@@ -4296,7 +4296,7 @@
       <c r="Q57" s="3"/>
       <c r="R57" s="3"/>
     </row>
-    <row r="58" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
         <v>161</v>
       </c>
@@ -4324,7 +4324,7 @@
       <c r="Q58" s="3"/>
       <c r="R58" s="3"/>
     </row>
-    <row r="59" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
         <v>156</v>
       </c>
@@ -4352,18 +4352,18 @@
       <c r="Q59" s="3"/>
       <c r="R59" s="3"/>
     </row>
-    <row r="60" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="8" t="s">
         <v>160</v>
       </c>
       <c r="B60" s="3">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="C60" s="8" t="s">
         <v>18</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>162</v>
+        <v>201</v>
       </c>
       <c r="E60" s="8"/>
       <c r="F60" s="3"/>
@@ -4380,9 +4380,9 @@
       <c r="Q60" s="3"/>
       <c r="R60" s="3"/>
     </row>
-    <row r="61" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B61" s="3">
         <v>0.3</v>
@@ -4391,7 +4391,7 @@
         <v>18</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>164</v>
+        <v>202</v>
       </c>
       <c r="E61" s="8"/>
       <c r="F61" s="3"/>
@@ -4408,12 +4408,12 @@
       <c r="Q61" s="3"/>
       <c r="R61" s="3"/>
     </row>
-    <row r="62" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="8" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B62" s="3">
-        <v>0.12</v>
+        <v>0.16200000000000001</v>
       </c>
       <c r="C62" s="8" t="s">
         <v>81</v>
@@ -4434,12 +4434,12 @@
       <c r="Q62" s="3"/>
       <c r="R62" s="3"/>
     </row>
-    <row r="63" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B63" s="3">
-        <v>0.2</v>
+        <v>0.24299999999999999</v>
       </c>
       <c r="C63" s="8" t="s">
         <v>81</v>
@@ -4460,13 +4460,13 @@
       <c r="Q63" s="3"/>
       <c r="R63" s="3"/>
     </row>
-    <row r="64" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B64" s="22">
         <f>B63/B62</f>
-        <v>1.6666666666666667</v>
+        <v>1.5</v>
       </c>
       <c r="C64" s="8" t="s">
         <v>18</v>
@@ -4487,18 +4487,18 @@
       <c r="Q64" s="3"/>
       <c r="R64" s="3"/>
     </row>
-    <row r="65" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B65" s="3">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="C65" s="8" t="s">
         <v>18</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>162</v>
+        <v>201</v>
       </c>
       <c r="E65" s="8"/>
       <c r="F65" s="3"/>
@@ -4515,9 +4515,9 @@
       <c r="Q65" s="3"/>
       <c r="R65" s="3"/>
     </row>
-    <row r="66" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="8" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B66" s="3">
         <v>0.3</v>
@@ -4526,7 +4526,7 @@
         <v>18</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>164</v>
+        <v>202</v>
       </c>
       <c r="E66" s="8"/>
       <c r="F66" s="3"/>
@@ -4543,9 +4543,9 @@
       <c r="Q66" s="3"/>
       <c r="R66" s="3"/>
     </row>
-    <row r="67" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B67" s="3">
         <v>0.05</v>
@@ -4569,9 +4569,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
     </row>
-    <row r="68" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="8" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B68" s="3">
         <v>1.4999999999999999E-2</v>
@@ -4595,9 +4595,9 @@
       <c r="Q68" s="3"/>
       <c r="R68" s="3"/>
     </row>
-    <row r="69" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B69" s="3">
         <v>0.155</v>
@@ -4621,9 +4621,9 @@
       <c r="Q69" s="3"/>
       <c r="R69" s="3"/>
     </row>
-    <row r="70" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B70" s="3">
         <v>1.6E-2</v>
@@ -4647,9 +4647,9 @@
       <c r="Q70" s="3"/>
       <c r="R70" s="3"/>
     </row>
-    <row r="71" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B71" s="3">
         <v>0.05</v>
@@ -4673,9 +4673,9 @@
       <c r="Q71" s="3"/>
       <c r="R71" s="3"/>
     </row>
-    <row r="72" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B72" s="3">
         <v>1.4999999999999999E-2</v>
@@ -4699,9 +4699,9 @@
       <c r="Q72" s="3"/>
       <c r="R72" s="3"/>
     </row>
-    <row r="73" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B73" s="3">
         <v>0.09</v>
@@ -4725,9 +4725,9 @@
       <c r="Q73" s="3"/>
       <c r="R73" s="3"/>
     </row>
-    <row r="74" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="8" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B74" s="3">
         <v>0.01</v>
@@ -4751,9 +4751,9 @@
       <c r="Q74" s="3"/>
       <c r="R74" s="3"/>
     </row>
-    <row r="75" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B75" s="3">
         <v>0.25</v>
@@ -4762,7 +4762,7 @@
         <v>18</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E75" s="8"/>
       <c r="F75" s="3"/>
@@ -4779,9 +4779,9 @@
       <c r="Q75" s="3"/>
       <c r="R75" s="3"/>
     </row>
-    <row r="76" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="8" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B76" s="3">
         <v>0.3</v>
@@ -4790,7 +4790,7 @@
         <v>18</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E76" s="8"/>
       <c r="F76" s="3"/>
@@ -4807,9 +4807,9 @@
       <c r="Q76" s="3"/>
       <c r="R76" s="3"/>
     </row>
-    <row r="77" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B77" s="3">
         <v>0.1</v>
@@ -4833,18 +4833,18 @@
       <c r="Q77" s="3"/>
       <c r="R77" s="3"/>
     </row>
-    <row r="78" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B78" s="3">
         <v>0.08</v>
       </c>
       <c r="C78" s="24" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
@@ -4861,9 +4861,9 @@
       <c r="Q78" s="3"/>
       <c r="R78" s="3"/>
     </row>
-    <row r="79" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B79" s="3">
         <v>0.1</v>
@@ -4872,7 +4872,7 @@
         <v>81</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
@@ -4889,9 +4889,9 @@
       <c r="Q79" s="3"/>
       <c r="R79" s="3"/>
     </row>
-    <row r="80" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B80" s="3">
         <v>0.04</v>
@@ -4900,7 +4900,7 @@
         <v>81</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
@@ -4917,7 +4917,7 @@
       <c r="Q80" s="3"/>
       <c r="R80" s="3"/>
     </row>
-    <row r="81" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
@@ -4937,7 +4937,7 @@
       <c r="Q81" s="3"/>
       <c r="R81" s="3"/>
     </row>
-    <row r="82" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
@@ -4957,7 +4957,7 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
     </row>
-    <row r="83" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
@@ -4977,7 +4977,7 @@
       <c r="Q83" s="3"/>
       <c r="R83" s="3"/>
     </row>
-    <row r="84" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
@@ -4997,7 +4997,7 @@
       <c r="Q84" s="3"/>
       <c r="R84" s="3"/>
     </row>
-    <row r="85" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
@@ -5017,7 +5017,7 @@
       <c r="Q85" s="3"/>
       <c r="R85" s="3"/>
     </row>
-    <row r="86" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
@@ -5037,7 +5037,7 @@
       <c r="Q86" s="3"/>
       <c r="R86" s="3"/>
     </row>
-    <row r="87" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
@@ -5057,7 +5057,7 @@
       <c r="Q87" s="3"/>
       <c r="R87" s="3"/>
     </row>
-    <row r="88" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
@@ -5077,7 +5077,7 @@
       <c r="Q88" s="3"/>
       <c r="R88" s="3"/>
     </row>
-    <row r="89" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
@@ -5097,7 +5097,7 @@
       <c r="Q89" s="3"/>
       <c r="R89" s="3"/>
     </row>
-    <row r="90" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
@@ -5117,7 +5117,7 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
     </row>
-    <row r="91" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
@@ -5137,7 +5137,7 @@
       <c r="Q91" s="3"/>
       <c r="R91" s="3"/>
     </row>
-    <row r="92" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
@@ -5157,7 +5157,7 @@
       <c r="Q92" s="3"/>
       <c r="R92" s="3"/>
     </row>
-    <row r="93" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
@@ -5177,7 +5177,7 @@
       <c r="Q93" s="3"/>
       <c r="R93" s="3"/>
     </row>
-    <row r="94" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
@@ -5197,7 +5197,7 @@
       <c r="Q94" s="3"/>
       <c r="R94" s="3"/>
     </row>
-    <row r="95" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
@@ -5217,7 +5217,7 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
     </row>
-    <row r="96" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
@@ -5237,7 +5237,7 @@
       <c r="Q96" s="3"/>
       <c r="R96" s="3"/>
     </row>
-    <row r="97" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
@@ -5257,7 +5257,7 @@
       <c r="Q97" s="3"/>
       <c r="R97" s="3"/>
     </row>
-    <row r="98" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
@@ -5277,7 +5277,7 @@
       <c r="Q98" s="3"/>
       <c r="R98" s="3"/>
     </row>
-    <row r="99" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
@@ -5297,7 +5297,7 @@
       <c r="Q99" s="3"/>
       <c r="R99" s="3"/>
     </row>
-    <row r="100" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
@@ -5317,7 +5317,7 @@
       <c r="Q100" s="3"/>
       <c r="R100" s="3"/>
     </row>
-    <row r="101" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
@@ -5337,7 +5337,7 @@
       <c r="Q101" s="3"/>
       <c r="R101" s="3"/>
     </row>
-    <row r="102" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
@@ -5357,7 +5357,7 @@
       <c r="Q102" s="3"/>
       <c r="R102" s="3"/>
     </row>
-    <row r="103" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
@@ -5377,7 +5377,7 @@
       <c r="Q103" s="3"/>
       <c r="R103" s="3"/>
     </row>
-    <row r="104" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
@@ -5397,7 +5397,7 @@
       <c r="Q104" s="3"/>
       <c r="R104" s="3"/>
     </row>
-    <row r="105" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
@@ -5417,7 +5417,7 @@
       <c r="Q105" s="3"/>
       <c r="R105" s="3"/>
     </row>
-    <row r="106" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="3"/>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
@@ -5437,7 +5437,7 @@
       <c r="Q106" s="3"/>
       <c r="R106" s="3"/>
     </row>
-    <row r="107" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
@@ -5457,7 +5457,7 @@
       <c r="Q107" s="3"/>
       <c r="R107" s="3"/>
     </row>
-    <row r="108" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
@@ -5477,7 +5477,7 @@
       <c r="Q108" s="3"/>
       <c r="R108" s="3"/>
     </row>
-    <row r="109" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
@@ -5497,7 +5497,7 @@
       <c r="Q109" s="3"/>
       <c r="R109" s="3"/>
     </row>
-    <row r="110" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="3"/>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
@@ -5517,7 +5517,7 @@
       <c r="Q110" s="3"/>
       <c r="R110" s="3"/>
     </row>
-    <row r="111" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
@@ -5537,7 +5537,7 @@
       <c r="Q111" s="3"/>
       <c r="R111" s="3"/>
     </row>
-    <row r="112" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
@@ -5557,7 +5557,7 @@
       <c r="Q112" s="3"/>
       <c r="R112" s="3"/>
     </row>
-    <row r="113" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
@@ -5577,7 +5577,7 @@
       <c r="Q113" s="3"/>
       <c r="R113" s="3"/>
     </row>
-    <row r="114" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
@@ -5597,7 +5597,7 @@
       <c r="Q114" s="3"/>
       <c r="R114" s="3"/>
     </row>
-    <row r="115" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="3"/>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
@@ -5617,7 +5617,7 @@
       <c r="Q115" s="3"/>
       <c r="R115" s="3"/>
     </row>
-    <row r="116" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="3"/>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
@@ -5637,7 +5637,7 @@
       <c r="Q116" s="3"/>
       <c r="R116" s="3"/>
     </row>
-    <row r="117" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="3"/>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
@@ -5657,7 +5657,7 @@
       <c r="Q117" s="3"/>
       <c r="R117" s="3"/>
     </row>
-    <row r="118" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="3"/>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
@@ -5677,7 +5677,7 @@
       <c r="Q118" s="3"/>
       <c r="R118" s="3"/>
     </row>
-    <row r="119" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="3"/>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
@@ -5697,7 +5697,7 @@
       <c r="Q119" s="3"/>
       <c r="R119" s="3"/>
     </row>
-    <row r="120" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="3"/>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
@@ -5717,7 +5717,7 @@
       <c r="Q120" s="3"/>
       <c r="R120" s="3"/>
     </row>
-    <row r="121" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="3"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
@@ -5737,7 +5737,7 @@
       <c r="Q121" s="3"/>
       <c r="R121" s="3"/>
     </row>
-    <row r="122" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="3"/>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
@@ -5757,7 +5757,7 @@
       <c r="Q122" s="3"/>
       <c r="R122" s="3"/>
     </row>
-    <row r="123" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="3"/>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
@@ -5777,7 +5777,7 @@
       <c r="Q123" s="3"/>
       <c r="R123" s="3"/>
     </row>
-    <row r="124" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="3"/>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
@@ -5797,7 +5797,7 @@
       <c r="Q124" s="3"/>
       <c r="R124" s="3"/>
     </row>
-    <row r="125" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="3"/>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
@@ -5817,7 +5817,7 @@
       <c r="Q125" s="3"/>
       <c r="R125" s="3"/>
     </row>
-    <row r="126" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="3"/>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
@@ -5837,7 +5837,7 @@
       <c r="Q126" s="3"/>
       <c r="R126" s="3"/>
     </row>
-    <row r="127" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="3"/>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
@@ -5857,7 +5857,7 @@
       <c r="Q127" s="3"/>
       <c r="R127" s="3"/>
     </row>
-    <row r="128" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="3"/>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
@@ -5877,7 +5877,7 @@
       <c r="Q128" s="3"/>
       <c r="R128" s="3"/>
     </row>
-    <row r="129" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="3"/>
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
@@ -5897,7 +5897,7 @@
       <c r="Q129" s="3"/>
       <c r="R129" s="3"/>
     </row>
-    <row r="130" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="3"/>
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
@@ -5917,7 +5917,7 @@
       <c r="Q130" s="3"/>
       <c r="R130" s="3"/>
     </row>
-    <row r="131" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="3"/>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
@@ -5937,7 +5937,7 @@
       <c r="Q131" s="3"/>
       <c r="R131" s="3"/>
     </row>
-    <row r="132" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="3"/>
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\Fall 2026\AAE 451\451-DBF-Team01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hudson/Documents/GitHub/451-DBF-Team01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC9010D4-B4DA-4D64-B885-B91E588D68F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD91AC9F-6BE5-2549-A407-92A499FD7404}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INPUTS" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="209">
   <si>
     <t>Parameter</t>
   </si>
@@ -664,6 +664,24 @@
   </si>
   <si>
     <t>NACA 0010 location of max thickness</t>
+  </si>
+  <si>
+    <t>Subclass</t>
+  </si>
+  <si>
+    <t>env</t>
+  </si>
+  <si>
+    <t>aero</t>
+  </si>
+  <si>
+    <t>geometry</t>
+  </si>
+  <si>
+    <t>performance</t>
+  </si>
+  <si>
+    <t>prop</t>
   </si>
 </sst>
 </file>
@@ -710,7 +728,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -735,51 +753,6 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right style="thin">
-        <color indexed="10"/>
-      </right>
-      <top style="thin">
-        <color indexed="10"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="11"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right style="thin">
-        <color indexed="11"/>
-      </right>
-      <top style="thin">
-        <color indexed="10"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="10"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="11"/>
-      </left>
-      <right style="thin">
-        <color indexed="11"/>
-      </right>
-      <top style="thin">
-        <color indexed="11"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="11"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color indexed="11"/>
       </left>
       <right style="thin">
@@ -794,9 +767,61 @@
       <diagonal/>
     </border>
     <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
+        <color indexed="10"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="10"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom style="thin">
         <color indexed="11"/>
-      </left>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="11"/>
+      </right>
+      <top style="thin">
+        <color indexed="11"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="11"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color indexed="10"/>
       </right>
@@ -809,9 +834,7 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="11"/>
-      </left>
+      <left/>
       <right style="thin">
         <color indexed="10"/>
       </right>
@@ -823,36 +846,57 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="10"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -942,13 +986,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>183515</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
+      <xdr:col>17</xdr:col>
       <xdr:colOff>39108</xdr:colOff>
       <xdr:row>37</xdr:row>
       <xdr:rowOff>62871</xdr:rowOff>
@@ -991,13 +1035,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>9151</xdr:colOff>
       <xdr:row>37</xdr:row>
       <xdr:rowOff>141220</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
+      <xdr:col>17</xdr:col>
       <xdr:colOff>43963</xdr:colOff>
       <xdr:row>53</xdr:row>
       <xdr:rowOff>67330</xdr:rowOff>
@@ -1046,7 +1090,7 @@
       <xdr:rowOff>97457</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>605269</xdr:colOff>
       <xdr:row>100</xdr:row>
       <xdr:rowOff>59358</xdr:rowOff>
@@ -1089,13 +1133,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>297995</xdr:colOff>
       <xdr:row>70</xdr:row>
       <xdr:rowOff>108868</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>153761</xdr:colOff>
       <xdr:row>90</xdr:row>
       <xdr:rowOff>775</xdr:rowOff>
@@ -1138,13 +1182,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>254451</xdr:colOff>
       <xdr:row>62</xdr:row>
       <xdr:rowOff>81649</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>475977</xdr:colOff>
       <xdr:row>68</xdr:row>
       <xdr:rowOff>60011</xdr:rowOff>
@@ -1193,7 +1237,7 @@
       <xdr:rowOff>43014</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>575716</xdr:colOff>
       <xdr:row>104</xdr:row>
       <xdr:rowOff>65005</xdr:rowOff>
@@ -1242,7 +1286,7 @@
       <xdr:rowOff>14660</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>1516674</xdr:colOff>
       <xdr:row>106</xdr:row>
       <xdr:rowOff>118773</xdr:rowOff>
@@ -1285,13 +1329,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
       <xdr:row>92</xdr:row>
       <xdr:rowOff>142880</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>244370</xdr:colOff>
       <xdr:row>113</xdr:row>
       <xdr:rowOff>53886</xdr:rowOff>
@@ -1340,7 +1384,7 @@
       <xdr:rowOff>109907</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>1281404</xdr:colOff>
       <xdr:row>122</xdr:row>
       <xdr:rowOff>79550</xdr:rowOff>
@@ -1389,7 +1433,7 @@
       <xdr:rowOff>52020</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>1305657</xdr:colOff>
       <xdr:row>139</xdr:row>
       <xdr:rowOff>59792</xdr:rowOff>
@@ -1432,13 +1476,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>58615</xdr:colOff>
       <xdr:row>132</xdr:row>
       <xdr:rowOff>130415</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
+      <xdr:col>17</xdr:col>
       <xdr:colOff>366931</xdr:colOff>
       <xdr:row>139</xdr:row>
       <xdr:rowOff>25826</xdr:rowOff>
@@ -1481,14 +1525,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>443594</xdr:colOff>
       <xdr:row>54</xdr:row>
       <xdr:rowOff>92527</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>249283</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>477883</xdr:colOff>
       <xdr:row>61</xdr:row>
       <xdr:rowOff>129905</xdr:rowOff>
     </xdr:to>
@@ -2571,42 +2615,46 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R132"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.65" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:S132"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="34.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.7109375" style="1" customWidth="1"/>
-    <col min="7" max="19" width="8.7109375" style="1" customWidth="1"/>
-    <col min="20" max="16384" width="8.7109375" style="1"/>
+    <col min="1" max="1" width="18.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5" style="32" customWidth="1"/>
+    <col min="3" max="3" width="9.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="34.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.6640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="40.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="20" width="8.6640625" style="1" customWidth="1"/>
+    <col min="21" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="29" t="s">
+        <v>203</v>
+      </c>
+      <c r="C1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="D1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="E1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="F1" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="G1" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="H1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
@@ -2617,28 +2665,31 @@
       <c r="P1" s="3"/>
       <c r="Q1" s="3"/>
       <c r="R1" s="3"/>
-    </row>
-    <row r="2" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="S1" s="3"/>
+    </row>
+    <row r="2" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="30" t="s">
+        <v>204</v>
+      </c>
+      <c r="C2" s="16">
         <v>1.2250000000000001</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="2"/>
+      <c r="G2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
@@ -2649,26 +2700,29 @@
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
       <c r="R2" s="3"/>
-    </row>
-    <row r="3" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="S2" s="3"/>
+    </row>
+    <row r="3" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="12">
+      <c r="B3" s="30" t="s">
+        <v>204</v>
+      </c>
+      <c r="C3" s="17">
         <v>1.7960000000000001E-5</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="2"/>
+      <c r="G3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="3"/>
+      <c r="H3" s="2"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
@@ -2679,25 +2733,28 @@
       <c r="P3" s="3"/>
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
-    </row>
-    <row r="4" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="S3" s="3"/>
+    </row>
+    <row r="4" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="30" t="s">
+        <v>204</v>
+      </c>
+      <c r="C4" s="16">
         <v>9.81</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="2"/>
+      <c r="G4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
@@ -2709,28 +2766,31 @@
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
-    </row>
-    <row r="5" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="S4" s="3"/>
+    </row>
+    <row r="5" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="30" t="s">
+        <v>204</v>
+      </c>
+      <c r="C5" s="16">
         <v>0.05</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="2"/>
+      <c r="G5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
@@ -2741,28 +2801,31 @@
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
-    </row>
-    <row r="6" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="S5" s="3"/>
+    </row>
+    <row r="6" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="30" t="s">
+        <v>204</v>
+      </c>
+      <c r="C6" s="16">
         <v>0.08</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="2"/>
+      <c r="G6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
@@ -2773,26 +2836,29 @@
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
-    </row>
-    <row r="7" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+      <c r="S6" s="3"/>
+    </row>
+    <row r="7" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="B7" s="13">
-        <f>1.78*(1-0.045*B8^0.68)-0.64</f>
+      <c r="B7" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="C7" s="18">
+        <f>1.78*(1-0.045*C8^0.68)-0.64</f>
         <v>0.91000572412664693</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="2"/>
+      <c r="G7" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
@@ -2804,29 +2870,32 @@
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
-    </row>
-    <row r="8" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="S7" s="3"/>
+    </row>
+    <row r="8" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="13">
-        <f>B54/B42</f>
+      <c r="B8" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="C8" s="18">
+        <f>C54/C42</f>
         <v>4.7168676768718001</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="2"/>
+      <c r="G8" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
@@ -2837,26 +2906,29 @@
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="B9" s="14" cm="1">
-        <f t="array" ref="B9">1/(PI()*B7*B8)</f>
+      <c r="B9" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="C9" s="19" cm="1">
+        <f t="array" ref="C9">1/(PI()*C7*C8)</f>
         <v>7.4157026955488606E-2</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="2"/>
+      <c r="G9" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
@@ -2868,25 +2940,28 @@
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="C10" s="16">
         <v>0.3</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="D10" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="2"/>
+      <c r="G10" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
@@ -2898,28 +2973,31 @@
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="C11" s="16">
         <v>1.43</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="D11" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="2"/>
+      <c r="G11" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="H11" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
@@ -2930,29 +3008,32 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="11" cm="1">
-        <f t="array" ref="B12">B10</f>
+      <c r="B12" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="C12" s="16" cm="1">
+        <f t="array" ref="C12">C10</f>
         <v>0.3</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="D12" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="2"/>
+      <c r="G12" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="H12" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
@@ -2963,29 +3044,32 @@
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="13" cm="1">
-        <f t="array" ref="B13">B11/B20^2</f>
+      <c r="B13" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="C13" s="18" cm="1">
+        <f t="array" ref="C13">C11/C20^2</f>
         <v>1.1818181818181817</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="D13" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="2"/>
+      <c r="G13" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="H13" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
@@ -2996,30 +3080,33 @@
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="B14" s="14">
+      <c r="B14" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="C14" s="19">
         <v>2.8299999999999999E-2</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="D14" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="F14" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="G14" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="H14" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
@@ -3030,26 +3117,29 @@
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="B15" s="14" cm="1">
-        <f t="array" ref="B15">B14+B9*B10^2</f>
+      <c r="B15" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="C15" s="19" cm="1">
+        <f t="array" ref="C15">C14+C9*C10^2</f>
         <v>3.4974132425993974E-2</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="D15" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="2"/>
+      <c r="G15" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="G15" s="3"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
@@ -3061,29 +3151,32 @@
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="B16" s="14" cm="1">
-        <f t="array" ref="B16">B14+B9*B12^2</f>
+      <c r="B16" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="C16" s="19" cm="1">
+        <f t="array" ref="C16">C14+C9*C12^2</f>
         <v>3.4974132425993974E-2</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="D16" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="2"/>
+      <c r="G16" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="H16" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
@@ -3094,26 +3187,29 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="B17" s="14" cm="1">
-        <f t="array" ref="B17">B16-B5*B12</f>
+      <c r="B17" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="C17" s="19" cm="1">
+        <f t="array" ref="C17">C16-C5*C12</f>
         <v>1.9974132425993975E-2</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="D17" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="2"/>
+      <c r="G17" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G17" s="3"/>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
@@ -3125,27 +3221,30 @@
       <c r="P17" s="3"/>
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="B18" s="13" cm="1">
-        <f t="array" ref="B18">B10/B15</f>
+      <c r="B18" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="C18" s="18" cm="1">
+        <f t="array" ref="C18">C10/C15</f>
         <v>8.5777681729434327</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="D18" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E18" s="2"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="2" t="s">
+      <c r="F18" s="2"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
@@ -3156,25 +3255,28 @@
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="B19" s="13">
+      <c r="B19" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="C19" s="18">
         <v>10.5</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="D19" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="2"/>
+      <c r="G19" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="G19" s="3"/>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
@@ -3186,25 +3288,28 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="B20" s="15">
+      <c r="B20" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="C20" s="20">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="D20" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="2"/>
+      <c r="G20" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G20" s="3"/>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
@@ -3216,26 +3321,29 @@
       <c r="P20" s="3"/>
       <c r="Q20" s="3"/>
       <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="B21" s="13" cm="1">
-        <f t="array" ref="B21">B20*B19</f>
+      <c r="B21" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="C21" s="18" cm="1">
+        <f t="array" ref="C21">C20*C19</f>
         <v>11.55</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="D21" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="E21" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2" t="s">
+      <c r="F21" s="2"/>
+      <c r="G21" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G21" s="3"/>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
@@ -3247,27 +3355,30 @@
       <c r="P21" s="3"/>
       <c r="Q21" s="3"/>
       <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="B22" s="13" cm="1">
-        <f t="array" ref="B22">SQRT(B19^2*B11/B10)</f>
+      <c r="B22" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="C22" s="18" cm="1">
+        <f t="array" ref="C22">SQRT(C19^2*C11/C10)</f>
         <v>22.924332051337942</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="D22" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="E22" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E22" s="2"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="2" t="s">
+      <c r="F22" s="2"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="H22" s="3"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
@@ -3278,23 +3389,26 @@
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
       <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="B23" s="13" cm="1">
-        <f t="array" ref="B23">SQRT(B26*B4*SQRT(B25^2-1))</f>
+      <c r="B23" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="C23" s="18" cm="1">
+        <f t="array" ref="C23">SQRT(C26*C4*SQRT(C25^2-1))</f>
         <v>14.810748414335091</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="D23" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E23" s="2"/>
-      <c r="F23" s="3"/>
+      <c r="F23" s="2"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
@@ -3307,26 +3421,29 @@
       <c r="P23" s="3"/>
       <c r="Q23" s="3"/>
       <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="B24" s="13" cm="1">
-        <f t="array" ref="B24">B19*SQRT(B25)</f>
+      <c r="B24" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="C24" s="18" cm="1">
+        <f t="array" ref="C24">C19*SQRT(C25)</f>
         <v>12.859821149611683</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="D24" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="E24" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2" t="s">
+      <c r="F24" s="2"/>
+      <c r="G24" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
@@ -3338,25 +3455,28 @@
       <c r="P24" s="3"/>
       <c r="Q24" s="3"/>
       <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="B25" s="11">
+      <c r="B25" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="C25" s="16">
         <v>1.5</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="D25" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="E25" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2" t="s">
+      <c r="F25" s="2"/>
+      <c r="G25" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="G25" s="3"/>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
@@ -3368,25 +3488,28 @@
       <c r="P25" s="3"/>
       <c r="Q25" s="3"/>
       <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="B26" s="11">
+      <c r="B26" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="C26" s="16">
         <v>20</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="D26" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="E26" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2" t="s">
+      <c r="F26" s="2"/>
+      <c r="G26" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="G26" s="3"/>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
@@ -3398,23 +3521,26 @@
       <c r="P26" s="3"/>
       <c r="Q26" s="3"/>
       <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="B27" s="13" cm="1">
-        <f t="array" ref="B27">DEGREES(ACOS(1/B25))</f>
+      <c r="B27" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="C27" s="18" cm="1">
+        <f t="array" ref="C27">DEGREES(ACOS(1/C25))</f>
         <v>48.189685104221404</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="D27" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="E27" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E27" s="2"/>
-      <c r="F27" s="3"/>
+      <c r="F27" s="2"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
@@ -3427,25 +3553,28 @@
       <c r="P27" s="3"/>
       <c r="Q27" s="3"/>
       <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="B28" s="11">
+      <c r="B28" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="C28" s="16">
         <v>0.75</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="D28" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="E28" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2" t="s">
+      <c r="F28" s="2"/>
+      <c r="G28" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="G28" s="3"/>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
@@ -3457,25 +3586,28 @@
       <c r="P28" s="3"/>
       <c r="Q28" s="3"/>
       <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="B29" s="11">
+      <c r="B29" s="30" t="s">
+        <v>208</v>
+      </c>
+      <c r="C29" s="16">
         <v>0.75</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="D29" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="E29" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2" t="s">
+      <c r="F29" s="2"/>
+      <c r="G29" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="G29" s="3"/>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
@@ -3487,25 +3619,28 @@
       <c r="P29" s="3"/>
       <c r="Q29" s="3"/>
       <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="B30" s="11">
+      <c r="B30" s="30" t="s">
+        <v>208</v>
+      </c>
+      <c r="C30" s="16">
         <v>0.45</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="D30" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="E30" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2" t="s">
+      <c r="F30" s="2"/>
+      <c r="G30" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="G30" s="3"/>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
@@ -3517,25 +3652,28 @@
       <c r="P30" s="3"/>
       <c r="Q30" s="3"/>
       <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="B31" s="11">
+      <c r="B31" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="C31" s="16">
         <v>30</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="D31" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="E31" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2" t="s">
+      <c r="F31" s="2"/>
+      <c r="G31" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="G31" s="3"/>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
@@ -3547,25 +3685,28 @@
       <c r="P31" s="3"/>
       <c r="Q31" s="3"/>
       <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="B32" s="11">
+      <c r="B32" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="C32" s="16">
         <v>100</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="D32" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="E32" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2" t="s">
+      <c r="F32" s="2"/>
+      <c r="G32" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
@@ -3577,23 +3718,26 @@
       <c r="P32" s="3"/>
       <c r="Q32" s="3"/>
       <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="B33" s="13" cm="1">
-        <f t="array" ref="B33">DEGREES(ATAN(30/100))</f>
+      <c r="B33" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="C33" s="18" cm="1">
+        <f t="array" ref="C33">DEGREES(ATAN(30/100))</f>
         <v>16.699244233993621</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="D33" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="E33" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="E33" s="2"/>
-      <c r="F33" s="3"/>
+      <c r="F33" s="2"/>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
@@ -3606,25 +3750,28 @@
       <c r="P33" s="3"/>
       <c r="Q33" s="3"/>
       <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="B34" s="13">
+      <c r="B34" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="C34" s="18">
         <v>25</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="D34" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="E34" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2" t="s">
+      <c r="F34" s="2"/>
+      <c r="G34" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
@@ -3636,22 +3783,25 @@
       <c r="P34" s="3"/>
       <c r="Q34" s="3"/>
       <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="B35" s="11">
+      <c r="B35" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="C35" s="16">
         <v>95</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="D35" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="E35" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="E35" s="2"/>
-      <c r="F35" s="3"/>
+      <c r="F35" s="2"/>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
@@ -3664,22 +3814,25 @@
       <c r="P35" s="3"/>
       <c r="Q35" s="3"/>
       <c r="R35" s="3"/>
-    </row>
-    <row r="36" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="36" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="B36" s="11">
+      <c r="B36" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="C36" s="16">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="D36" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="E36" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="E36" s="2"/>
-      <c r="F36" s="3"/>
+      <c r="F36" s="2"/>
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -3692,22 +3845,25 @@
       <c r="P36" s="3"/>
       <c r="Q36" s="3"/>
       <c r="R36" s="3"/>
-    </row>
-    <row r="37" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
+      <c r="S36" s="3"/>
+    </row>
+    <row r="37" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="B37" s="11">
+      <c r="B37" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="C37" s="16">
         <v>0.8</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="D37" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="E37" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="E37" s="2"/>
-      <c r="F37" s="3"/>
+      <c r="F37" s="2"/>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
@@ -3720,25 +3876,28 @@
       <c r="P37" s="3"/>
       <c r="Q37" s="3"/>
       <c r="R37" s="3"/>
-    </row>
-    <row r="38" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
+      <c r="S37" s="3"/>
+    </row>
+    <row r="38" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="B38" s="18">
+      <c r="B38" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="C38" s="21">
         <v>4.45</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="D38" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="E38" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2" t="s">
+      <c r="F38" s="2"/>
+      <c r="G38" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
@@ -3750,23 +3909,26 @@
       <c r="P38" s="3"/>
       <c r="Q38" s="3"/>
       <c r="R38" s="3"/>
-    </row>
-    <row r="39" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
+      <c r="S38" s="3"/>
+    </row>
+    <row r="39" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="B39" s="19" cm="1">
-        <f t="array" ref="B39">B4*B38</f>
+      <c r="B39" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="C39" s="22" cm="1">
+        <f t="array" ref="C39">C4*C38</f>
         <v>43.654500000000006</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="D39" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="E39" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="E39" s="2"/>
-      <c r="F39" s="3"/>
+      <c r="F39" s="2"/>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
@@ -3779,23 +3941,26 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="B40" s="20">
-        <f>B39/B35</f>
+      <c r="B40" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="C40" s="23">
+        <f>C39/C35</f>
         <v>0.459521052631579</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="D40" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="E40" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="E40" s="2"/>
-      <c r="F40" s="3"/>
+      <c r="F40" s="2"/>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
@@ -3808,25 +3973,28 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="7" t="s">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="B41" s="21">
+      <c r="B41" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="C41" s="24">
         <v>-0.08</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="D41" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="E41" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2" t="s">
+      <c r="F41" s="2"/>
+      <c r="G41" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="G41" s="3"/>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
@@ -3838,21 +4006,24 @@
       <c r="P41" s="3"/>
       <c r="Q41" s="3"/>
       <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="7" t="s">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="B42" s="10">
-        <f>B40/(B54-B55)</f>
+      <c r="B42" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="C42" s="25">
+        <f>C40/(C54-C55)</f>
         <v>0.31800764887998545</v>
       </c>
-      <c r="C42" s="3"/>
-      <c r="D42" s="2" t="s">
+      <c r="D42" s="3"/>
+      <c r="E42" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="E42" s="2"/>
-      <c r="F42" s="3"/>
+      <c r="F42" s="2"/>
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
@@ -3865,23 +4036,26 @@
       <c r="P42" s="3"/>
       <c r="Q42" s="3"/>
       <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="B43" s="6">
+      <c r="B43" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="C43" s="26">
         <v>0.25</v>
       </c>
-      <c r="C43" s="3"/>
-      <c r="D43" s="2" t="s">
+      <c r="D43" s="3"/>
+      <c r="E43" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="E43" s="2"/>
-      <c r="F43" s="7" t="s">
+      <c r="F43" s="2"/>
+      <c r="G43" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
       <c r="J43" s="3"/>
@@ -3893,22 +4067,25 @@
       <c r="P43" s="3"/>
       <c r="Q43" s="3"/>
       <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="7" t="s">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="B44" s="6">
+      <c r="B44" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="C44" s="26">
         <v>0.7</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="D44" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="E44" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="E44" s="2"/>
-      <c r="F44" s="3"/>
+      <c r="F44" s="2"/>
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
@@ -3921,22 +4098,25 @@
       <c r="P44" s="3"/>
       <c r="Q44" s="3"/>
       <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="7" t="s">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="12" t="s">
         <v>190</v>
       </c>
-      <c r="B45" s="6">
+      <c r="B45" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="C45" s="26">
         <v>0.23</v>
       </c>
-      <c r="C45" s="7" t="s">
+      <c r="D45" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D45" s="7" t="s">
+      <c r="E45" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="E45" s="2"/>
-      <c r="F45" s="3"/>
+      <c r="F45" s="2"/>
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
@@ -3949,25 +4129,28 @@
       <c r="P45" s="3"/>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="B46" s="6">
+      <c r="B46" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="C46" s="26">
         <v>0.3</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="D46" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="E46" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2" t="s">
+      <c r="F46" s="2"/>
+      <c r="G46" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="3"/>
@@ -3979,25 +4162,28 @@
       <c r="P46" s="3"/>
       <c r="Q46" s="3"/>
       <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="B47" s="6">
+      <c r="B47" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="C47" s="26">
         <v>0.43</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="D47" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="E47" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2" t="s">
+      <c r="F47" s="2"/>
+      <c r="G47" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="G47" s="3"/>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
       <c r="J47" s="3"/>
@@ -4009,25 +4195,28 @@
       <c r="P47" s="3"/>
       <c r="Q47" s="3"/>
       <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="7" t="s">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="B48" s="6">
+      <c r="B48" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="C48" s="26">
         <v>0.19600000000000001</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="D48" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D48" s="2" t="s">
+      <c r="E48" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2" t="s">
+      <c r="F48" s="2"/>
+      <c r="G48" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="G48" s="3"/>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
       <c r="J48" s="3"/>
@@ -4039,21 +4228,24 @@
       <c r="P48" s="3"/>
       <c r="Q48" s="3"/>
       <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="7" t="s">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="B49" s="6">
+      <c r="B49" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="C49" s="26">
         <v>0.53900000000000003</v>
       </c>
-      <c r="C49" s="7" t="s">
+      <c r="D49" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="D49" s="2"/>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
-      <c r="G49" s="3"/>
+      <c r="G49" s="2"/>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
       <c r="J49" s="3"/>
@@ -4065,26 +4257,29 @@
       <c r="P49" s="3"/>
       <c r="Q49" s="3"/>
       <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="7" t="s">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="B50" s="22">
-        <f>B49/B48</f>
+      <c r="B50" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="C50" s="27">
+        <f>C49/C48</f>
         <v>2.75</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="D50" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="E50" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2" t="s">
+      <c r="F50" s="2"/>
+      <c r="G50" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="G50" s="3"/>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
       <c r="J50" s="3"/>
@@ -4096,25 +4291,28 @@
       <c r="P50" s="3"/>
       <c r="Q50" s="3"/>
       <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="8" t="s">
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="B51" s="22">
+      <c r="B51" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="C51" s="27">
         <v>0.65</v>
       </c>
-      <c r="C51" s="8" t="s">
+      <c r="D51" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D51" s="8" t="s">
+      <c r="E51" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="E51" s="8" t="s">
+      <c r="F51" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="F51" s="7"/>
-      <c r="G51" s="3"/>
+      <c r="G51" s="5"/>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
       <c r="J51" s="3"/>
@@ -4126,24 +4324,27 @@
       <c r="P51" s="3"/>
       <c r="Q51" s="3"/>
       <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="8" t="s">
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="B52" s="22">
-        <f>1/(PI()*B51*B50)</f>
+      <c r="B52" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="C52" s="27">
+        <f>1/(PI()*C51*C50)</f>
         <v>0.17807546080212067</v>
       </c>
-      <c r="C52" s="8" t="s">
+      <c r="D52" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D52" s="8" t="s">
+      <c r="E52" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="E52" s="8"/>
-      <c r="F52" s="7"/>
-      <c r="G52" s="3"/>
+      <c r="F52" s="6"/>
+      <c r="G52" s="5"/>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
       <c r="J52" s="3"/>
@@ -4155,21 +4356,24 @@
       <c r="P52" s="3"/>
       <c r="Q52" s="3"/>
       <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="3" t="s">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="B53" s="3">
+      <c r="B53" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="C53" s="28">
         <v>0.15</v>
       </c>
-      <c r="C53" s="23" t="s">
+      <c r="D53" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D53" s="3" t="s">
+      <c r="E53" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="E53" s="3"/>
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
@@ -4183,21 +4387,24 @@
       <c r="P53" s="3"/>
       <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="8" t="s">
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="B54" s="3">
+      <c r="B54" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="C54" s="28">
         <v>1.5</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="D54" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D54" s="3" t="s">
+      <c r="E54" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="E54" s="3"/>
       <c r="F54" s="3"/>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
@@ -4211,22 +4418,25 @@
       <c r="P54" s="3"/>
       <c r="Q54" s="3"/>
       <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="8" t="s">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="B55" s="3">
+      <c r="B55" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="C55" s="28">
         <v>5.5E-2</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="D55" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D55" s="8" t="s">
+      <c r="E55" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="E55" s="8"/>
-      <c r="F55" s="3"/>
+      <c r="F55" s="6"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
@@ -4239,22 +4449,25 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="8" t="s">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="B56" s="3">
+      <c r="B56" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="C56" s="28">
         <v>1</v>
       </c>
-      <c r="C56" s="8" t="s">
+      <c r="D56" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="D56" s="8" t="s">
+      <c r="E56" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="E56" s="8"/>
-      <c r="F56" s="3"/>
+      <c r="F56" s="6"/>
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
@@ -4267,22 +4480,25 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="8" t="s">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="B57" s="3">
+      <c r="B57" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="C57" s="28">
         <v>0.24299999999999999</v>
       </c>
-      <c r="C57" s="8" t="s">
+      <c r="D57" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="D57" s="8" t="s">
+      <c r="E57" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="E57" s="8"/>
-      <c r="F57" s="3"/>
+      <c r="F57" s="6"/>
       <c r="G57" s="3"/>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
@@ -4295,22 +4511,25 @@
       <c r="P57" s="3"/>
       <c r="Q57" s="3"/>
       <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="8" t="s">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="B58" s="3">
+      <c r="B58" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="C58" s="28">
         <v>0.14000000000000001</v>
       </c>
-      <c r="C58" s="8" t="s">
+      <c r="D58" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D58" s="8" t="s">
+      <c r="E58" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="E58" s="8"/>
-      <c r="F58" s="3"/>
+      <c r="F58" s="6"/>
       <c r="G58" s="3"/>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
@@ -4323,22 +4542,25 @@
       <c r="P58" s="3"/>
       <c r="Q58" s="3"/>
       <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="8" t="s">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="B59" s="3">
+      <c r="B59" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="C59" s="28">
         <v>0.255</v>
       </c>
-      <c r="C59" s="8" t="s">
+      <c r="D59" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D59" s="8" t="s">
+      <c r="E59" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="E59" s="8"/>
-      <c r="F59" s="3"/>
+      <c r="F59" s="6"/>
       <c r="G59" s="3"/>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
@@ -4351,22 +4573,25 @@
       <c r="P59" s="3"/>
       <c r="Q59" s="3"/>
       <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="8" t="s">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="B60" s="3">
+      <c r="B60" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="C60" s="28">
         <v>0.1</v>
       </c>
-      <c r="C60" s="8" t="s">
+      <c r="D60" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D60" s="8" t="s">
+      <c r="E60" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="E60" s="8"/>
-      <c r="F60" s="3"/>
+      <c r="F60" s="6"/>
       <c r="G60" s="3"/>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
@@ -4379,22 +4604,25 @@
       <c r="P60" s="3"/>
       <c r="Q60" s="3"/>
       <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="8" t="s">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="B61" s="3">
+      <c r="B61" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="C61" s="28">
         <v>0.3</v>
       </c>
-      <c r="C61" s="8" t="s">
+      <c r="D61" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D61" s="8" t="s">
+      <c r="E61" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="E61" s="8"/>
-      <c r="F61" s="3"/>
+      <c r="F61" s="6"/>
       <c r="G61" s="3"/>
       <c r="H61" s="3"/>
       <c r="I61" s="3"/>
@@ -4407,18 +4635,21 @@
       <c r="P61" s="3"/>
       <c r="Q61" s="3"/>
       <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="8" t="s">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="B62" s="3">
+      <c r="B62" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="C62" s="28">
         <v>0.16200000000000001</v>
       </c>
-      <c r="C62" s="8" t="s">
+      <c r="D62" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="D62" s="3"/>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
       <c r="G62" s="3"/>
@@ -4433,18 +4664,21 @@
       <c r="P62" s="3"/>
       <c r="Q62" s="3"/>
       <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="8" t="s">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="B63" s="3">
+      <c r="B63" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="C63" s="28">
         <v>0.24299999999999999</v>
       </c>
-      <c r="C63" s="8" t="s">
+      <c r="D63" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="D63" s="3"/>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
       <c r="G63" s="3"/>
@@ -4459,19 +4693,22 @@
       <c r="P63" s="3"/>
       <c r="Q63" s="3"/>
       <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="8" t="s">
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="B64" s="22">
-        <f>B63/B62</f>
+      <c r="B64" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="C64" s="27">
+        <f>C63/C62</f>
         <v>1.5</v>
       </c>
-      <c r="C64" s="8" t="s">
+      <c r="D64" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D64" s="3"/>
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
       <c r="G64" s="3"/>
@@ -4486,22 +4723,25 @@
       <c r="P64" s="3"/>
       <c r="Q64" s="3"/>
       <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="8" t="s">
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="B65" s="3">
+      <c r="B65" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="C65" s="28">
         <v>0.1</v>
       </c>
-      <c r="C65" s="8" t="s">
+      <c r="D65" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D65" s="8" t="s">
+      <c r="E65" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="E65" s="8"/>
-      <c r="F65" s="3"/>
+      <c r="F65" s="6"/>
       <c r="G65" s="3"/>
       <c r="H65" s="3"/>
       <c r="I65" s="3"/>
@@ -4514,22 +4754,25 @@
       <c r="P65" s="3"/>
       <c r="Q65" s="3"/>
       <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="8" t="s">
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="B66" s="3">
+      <c r="B66" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="C66" s="28">
         <v>0.3</v>
       </c>
-      <c r="C66" s="8" t="s">
+      <c r="D66" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D66" s="8" t="s">
+      <c r="E66" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="E66" s="8"/>
-      <c r="F66" s="3"/>
+      <c r="F66" s="6"/>
       <c r="G66" s="3"/>
       <c r="H66" s="3"/>
       <c r="I66" s="3"/>
@@ -4542,18 +4785,21 @@
       <c r="P66" s="3"/>
       <c r="Q66" s="3"/>
       <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="8" t="s">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="B67" s="3">
+      <c r="B67" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="C67" s="28">
         <v>0.05</v>
       </c>
-      <c r="C67" s="8" t="s">
+      <c r="D67" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="D67" s="3"/>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
       <c r="G67" s="3"/>
@@ -4568,18 +4814,21 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="8" t="s">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="B68" s="3">
+      <c r="B68" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="C68" s="28">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="C68" s="8" t="s">
+      <c r="D68" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="D68" s="3"/>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" s="3"/>
@@ -4594,18 +4843,21 @@
       <c r="P68" s="3"/>
       <c r="Q68" s="3"/>
       <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="8" t="s">
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="13" t="s">
         <v>169</v>
       </c>
-      <c r="B69" s="3">
+      <c r="B69" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="C69" s="28">
         <v>0.155</v>
       </c>
-      <c r="C69" s="8" t="s">
+      <c r="D69" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="D69" s="3"/>
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
       <c r="G69" s="3"/>
@@ -4620,18 +4872,21 @@
       <c r="P69" s="3"/>
       <c r="Q69" s="3"/>
       <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="8" t="s">
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="B70" s="3">
+      <c r="B70" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="C70" s="28">
         <v>1.6E-2</v>
       </c>
-      <c r="C70" s="8" t="s">
+      <c r="D70" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="D70" s="3"/>
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
       <c r="G70" s="3"/>
@@ -4646,18 +4901,21 @@
       <c r="P70" s="3"/>
       <c r="Q70" s="3"/>
       <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="8" t="s">
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="13" t="s">
         <v>171</v>
       </c>
-      <c r="B71" s="3">
+      <c r="B71" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="C71" s="28">
         <v>0.05</v>
       </c>
-      <c r="C71" s="8" t="s">
+      <c r="D71" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="D71" s="3"/>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
       <c r="G71" s="3"/>
@@ -4672,18 +4930,21 @@
       <c r="P71" s="3"/>
       <c r="Q71" s="3"/>
       <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="8" t="s">
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="B72" s="3">
+      <c r="B72" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="C72" s="28">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="C72" s="8" t="s">
+      <c r="D72" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="D72" s="3"/>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
       <c r="G72" s="3"/>
@@ -4698,18 +4959,21 @@
       <c r="P72" s="3"/>
       <c r="Q72" s="3"/>
       <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="8" t="s">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="B73" s="3">
+      <c r="B73" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="C73" s="28">
         <v>0.09</v>
       </c>
-      <c r="C73" s="8" t="s">
+      <c r="D73" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="3"/>
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
       <c r="G73" s="3"/>
@@ -4724,18 +4988,21 @@
       <c r="P73" s="3"/>
       <c r="Q73" s="3"/>
       <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="8" t="s">
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="B74" s="3">
+      <c r="B74" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="C74" s="28">
         <v>0.01</v>
       </c>
-      <c r="C74" s="8" t="s">
+      <c r="D74" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="D74" s="3"/>
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
       <c r="G74" s="3"/>
@@ -4750,22 +5017,25 @@
       <c r="P74" s="3"/>
       <c r="Q74" s="3"/>
       <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="8" t="s">
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="B75" s="3">
+      <c r="B75" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="C75" s="28">
         <v>0.25</v>
       </c>
-      <c r="C75" s="8" t="s">
+      <c r="D75" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D75" s="8" t="s">
+      <c r="E75" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="E75" s="8"/>
-      <c r="F75" s="3"/>
+      <c r="F75" s="6"/>
       <c r="G75" s="3"/>
       <c r="H75" s="3"/>
       <c r="I75" s="3"/>
@@ -4778,22 +5048,25 @@
       <c r="P75" s="3"/>
       <c r="Q75" s="3"/>
       <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="8" t="s">
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="B76" s="3">
+      <c r="B76" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="C76" s="28">
         <v>0.3</v>
       </c>
-      <c r="C76" s="8" t="s">
+      <c r="D76" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D76" s="8" t="s">
+      <c r="E76" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="E76" s="8"/>
-      <c r="F76" s="3"/>
+      <c r="F76" s="6"/>
       <c r="G76" s="3"/>
       <c r="H76" s="3"/>
       <c r="I76" s="3"/>
@@ -4806,18 +5079,21 @@
       <c r="P76" s="3"/>
       <c r="Q76" s="3"/>
       <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="8" t="s">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="13" t="s">
         <v>193</v>
       </c>
-      <c r="B77" s="3">
+      <c r="B77" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="C77" s="28">
         <v>0.1</v>
       </c>
-      <c r="C77" s="8" t="s">
+      <c r="D77" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D77" s="3"/>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
       <c r="G77" s="3"/>
@@ -4832,21 +5108,24 @@
       <c r="P77" s="3"/>
       <c r="Q77" s="3"/>
       <c r="R77" s="3"/>
-    </row>
-    <row r="78" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="3" t="s">
+      <c r="S77" s="3"/>
+    </row>
+    <row r="78" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="B78" s="3">
+      <c r="B78" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="C78" s="28">
         <v>0.08</v>
       </c>
-      <c r="C78" s="24" t="s">
+      <c r="D78" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="D78" s="3" t="s">
+      <c r="E78" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="E78" s="3"/>
       <c r="F78" s="3"/>
       <c r="G78" s="3"/>
       <c r="H78" s="3"/>
@@ -4860,21 +5139,24 @@
       <c r="P78" s="3"/>
       <c r="Q78" s="3"/>
       <c r="R78" s="3"/>
-    </row>
-    <row r="79" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="3" t="s">
+      <c r="S78" s="3"/>
+    </row>
+    <row r="79" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="B79" s="3">
+      <c r="B79" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="C79" s="28">
         <v>0.1</v>
       </c>
-      <c r="C79" s="24" t="s">
+      <c r="D79" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="D79" s="3" t="s">
+      <c r="E79" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="E79" s="3"/>
       <c r="F79" s="3"/>
       <c r="G79" s="3"/>
       <c r="H79" s="3"/>
@@ -4888,21 +5170,24 @@
       <c r="P79" s="3"/>
       <c r="Q79" s="3"/>
       <c r="R79" s="3"/>
-    </row>
-    <row r="80" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="3" t="s">
+      <c r="S79" s="3"/>
+    </row>
+    <row r="80" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="B80" s="3">
+      <c r="B80" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="C80" s="28">
         <v>0.04</v>
       </c>
-      <c r="C80" s="24" t="s">
+      <c r="D80" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="D80" s="3" t="s">
+      <c r="E80" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="E80" s="3"/>
       <c r="F80" s="3"/>
       <c r="G80" s="3"/>
       <c r="H80" s="3"/>
@@ -4916,11 +5201,12 @@
       <c r="P80" s="3"/>
       <c r="Q80" s="3"/>
       <c r="R80" s="3"/>
-    </row>
-    <row r="81" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="3"/>
-      <c r="B81" s="3"/>
-      <c r="C81" s="3"/>
+      <c r="S80" s="3"/>
+    </row>
+    <row r="81" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="14"/>
+      <c r="B81" s="31"/>
+      <c r="C81" s="28"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
@@ -4936,11 +5222,12 @@
       <c r="P81" s="3"/>
       <c r="Q81" s="3"/>
       <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="3"/>
-      <c r="B82" s="3"/>
-      <c r="C82" s="3"/>
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="14"/>
+      <c r="B82" s="31"/>
+      <c r="C82" s="28"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
@@ -4956,11 +5243,12 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="3"/>
-      <c r="B83" s="3"/>
-      <c r="C83" s="3"/>
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="14"/>
+      <c r="B83" s="31"/>
+      <c r="C83" s="28"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
@@ -4976,11 +5264,12 @@
       <c r="P83" s="3"/>
       <c r="Q83" s="3"/>
       <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="3"/>
-      <c r="B84" s="3"/>
-      <c r="C84" s="3"/>
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="14"/>
+      <c r="B84" s="31"/>
+      <c r="C84" s="28"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
@@ -4996,11 +5285,12 @@
       <c r="P84" s="3"/>
       <c r="Q84" s="3"/>
       <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="3"/>
-      <c r="B85" s="3"/>
-      <c r="C85" s="3"/>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="14"/>
+      <c r="B85" s="31"/>
+      <c r="C85" s="28"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
@@ -5016,11 +5306,12 @@
       <c r="P85" s="3"/>
       <c r="Q85" s="3"/>
       <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="3"/>
-      <c r="B86" s="3"/>
-      <c r="C86" s="3"/>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="14"/>
+      <c r="B86" s="31"/>
+      <c r="C86" s="28"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
@@ -5036,11 +5327,12 @@
       <c r="P86" s="3"/>
       <c r="Q86" s="3"/>
       <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="3"/>
-      <c r="B87" s="3"/>
-      <c r="C87" s="3"/>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="14"/>
+      <c r="B87" s="31"/>
+      <c r="C87" s="28"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
@@ -5056,11 +5348,12 @@
       <c r="P87" s="3"/>
       <c r="Q87" s="3"/>
       <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="3"/>
-      <c r="B88" s="3"/>
-      <c r="C88" s="3"/>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="14"/>
+      <c r="B88" s="31"/>
+      <c r="C88" s="28"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
@@ -5076,11 +5369,12 @@
       <c r="P88" s="3"/>
       <c r="Q88" s="3"/>
       <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="3"/>
-      <c r="B89" s="3"/>
-      <c r="C89" s="3"/>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="14"/>
+      <c r="B89" s="31"/>
+      <c r="C89" s="28"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
@@ -5096,11 +5390,12 @@
       <c r="P89" s="3"/>
       <c r="Q89" s="3"/>
       <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="3"/>
-      <c r="B90" s="3"/>
-      <c r="C90" s="3"/>
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="14"/>
+      <c r="B90" s="31"/>
+      <c r="C90" s="28"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
@@ -5116,11 +5411,12 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="3"/>
-      <c r="B91" s="3"/>
-      <c r="C91" s="3"/>
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="14"/>
+      <c r="B91" s="31"/>
+      <c r="C91" s="28"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
@@ -5136,11 +5432,12 @@
       <c r="P91" s="3"/>
       <c r="Q91" s="3"/>
       <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="3"/>
-      <c r="B92" s="3"/>
-      <c r="C92" s="3"/>
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="14"/>
+      <c r="B92" s="31"/>
+      <c r="C92" s="28"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
@@ -5156,11 +5453,12 @@
       <c r="P92" s="3"/>
       <c r="Q92" s="3"/>
       <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="3"/>
-      <c r="B93" s="3"/>
-      <c r="C93" s="3"/>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="14"/>
+      <c r="B93" s="31"/>
+      <c r="C93" s="28"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
@@ -5176,11 +5474,12 @@
       <c r="P93" s="3"/>
       <c r="Q93" s="3"/>
       <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="3"/>
-      <c r="B94" s="3"/>
-      <c r="C94" s="3"/>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="14"/>
+      <c r="B94" s="31"/>
+      <c r="C94" s="28"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
@@ -5196,11 +5495,12 @@
       <c r="P94" s="3"/>
       <c r="Q94" s="3"/>
       <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="3"/>
-      <c r="B95" s="3"/>
-      <c r="C95" s="3"/>
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="14"/>
+      <c r="B95" s="31"/>
+      <c r="C95" s="28"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
@@ -5216,11 +5516,12 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="3"/>
-      <c r="B96" s="3"/>
-      <c r="C96" s="3"/>
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="14"/>
+      <c r="B96" s="31"/>
+      <c r="C96" s="28"/>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
@@ -5236,11 +5537,12 @@
       <c r="P96" s="3"/>
       <c r="Q96" s="3"/>
       <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="3"/>
-      <c r="B97" s="3"/>
-      <c r="C97" s="3"/>
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="14"/>
+      <c r="B97" s="31"/>
+      <c r="C97" s="28"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
@@ -5256,11 +5558,12 @@
       <c r="P97" s="3"/>
       <c r="Q97" s="3"/>
       <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="3"/>
-      <c r="B98" s="3"/>
-      <c r="C98" s="3"/>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="14"/>
+      <c r="B98" s="31"/>
+      <c r="C98" s="28"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
@@ -5276,11 +5579,12 @@
       <c r="P98" s="3"/>
       <c r="Q98" s="3"/>
       <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="3"/>
-      <c r="B99" s="3"/>
-      <c r="C99" s="3"/>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="14"/>
+      <c r="B99" s="31"/>
+      <c r="C99" s="28"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
@@ -5296,11 +5600,12 @@
       <c r="P99" s="3"/>
       <c r="Q99" s="3"/>
       <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="3"/>
-      <c r="B100" s="3"/>
-      <c r="C100" s="3"/>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="14"/>
+      <c r="B100" s="31"/>
+      <c r="C100" s="28"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
@@ -5316,11 +5621,12 @@
       <c r="P100" s="3"/>
       <c r="Q100" s="3"/>
       <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="3"/>
-      <c r="B101" s="3"/>
-      <c r="C101" s="3"/>
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="14"/>
+      <c r="B101" s="31"/>
+      <c r="C101" s="28"/>
       <c r="D101" s="3"/>
       <c r="E101" s="3"/>
       <c r="F101" s="3"/>
@@ -5336,11 +5642,12 @@
       <c r="P101" s="3"/>
       <c r="Q101" s="3"/>
       <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="3"/>
-      <c r="B102" s="3"/>
-      <c r="C102" s="3"/>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="14"/>
+      <c r="B102" s="31"/>
+      <c r="C102" s="28"/>
       <c r="D102" s="3"/>
       <c r="E102" s="3"/>
       <c r="F102" s="3"/>
@@ -5356,11 +5663,12 @@
       <c r="P102" s="3"/>
       <c r="Q102" s="3"/>
       <c r="R102" s="3"/>
-    </row>
-    <row r="103" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="3"/>
-      <c r="B103" s="3"/>
-      <c r="C103" s="3"/>
+      <c r="S102" s="3"/>
+    </row>
+    <row r="103" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A103" s="14"/>
+      <c r="B103" s="31"/>
+      <c r="C103" s="28"/>
       <c r="D103" s="3"/>
       <c r="E103" s="3"/>
       <c r="F103" s="3"/>
@@ -5376,11 +5684,12 @@
       <c r="P103" s="3"/>
       <c r="Q103" s="3"/>
       <c r="R103" s="3"/>
-    </row>
-    <row r="104" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="3"/>
-      <c r="B104" s="3"/>
-      <c r="C104" s="3"/>
+      <c r="S103" s="3"/>
+    </row>
+    <row r="104" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A104" s="14"/>
+      <c r="B104" s="31"/>
+      <c r="C104" s="28"/>
       <c r="D104" s="3"/>
       <c r="E104" s="3"/>
       <c r="F104" s="3"/>
@@ -5396,11 +5705,12 @@
       <c r="P104" s="3"/>
       <c r="Q104" s="3"/>
       <c r="R104" s="3"/>
-    </row>
-    <row r="105" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="3"/>
-      <c r="B105" s="3"/>
-      <c r="C105" s="3"/>
+      <c r="S104" s="3"/>
+    </row>
+    <row r="105" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A105" s="14"/>
+      <c r="B105" s="31"/>
+      <c r="C105" s="28"/>
       <c r="D105" s="3"/>
       <c r="E105" s="3"/>
       <c r="F105" s="3"/>
@@ -5416,11 +5726,12 @@
       <c r="P105" s="3"/>
       <c r="Q105" s="3"/>
       <c r="R105" s="3"/>
-    </row>
-    <row r="106" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="3"/>
-      <c r="B106" s="3"/>
-      <c r="C106" s="3"/>
+      <c r="S105" s="3"/>
+    </row>
+    <row r="106" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A106" s="14"/>
+      <c r="B106" s="31"/>
+      <c r="C106" s="28"/>
       <c r="D106" s="3"/>
       <c r="E106" s="3"/>
       <c r="F106" s="3"/>
@@ -5436,11 +5747,12 @@
       <c r="P106" s="3"/>
       <c r="Q106" s="3"/>
       <c r="R106" s="3"/>
-    </row>
-    <row r="107" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="3"/>
-      <c r="B107" s="3"/>
-      <c r="C107" s="3"/>
+      <c r="S106" s="3"/>
+    </row>
+    <row r="107" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A107" s="14"/>
+      <c r="B107" s="31"/>
+      <c r="C107" s="28"/>
       <c r="D107" s="3"/>
       <c r="E107" s="3"/>
       <c r="F107" s="3"/>
@@ -5456,11 +5768,12 @@
       <c r="P107" s="3"/>
       <c r="Q107" s="3"/>
       <c r="R107" s="3"/>
-    </row>
-    <row r="108" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="3"/>
-      <c r="B108" s="3"/>
-      <c r="C108" s="3"/>
+      <c r="S107" s="3"/>
+    </row>
+    <row r="108" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A108" s="14"/>
+      <c r="B108" s="31"/>
+      <c r="C108" s="28"/>
       <c r="D108" s="3"/>
       <c r="E108" s="3"/>
       <c r="F108" s="3"/>
@@ -5476,11 +5789,12 @@
       <c r="P108" s="3"/>
       <c r="Q108" s="3"/>
       <c r="R108" s="3"/>
-    </row>
-    <row r="109" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="3"/>
-      <c r="B109" s="3"/>
-      <c r="C109" s="3"/>
+      <c r="S108" s="3"/>
+    </row>
+    <row r="109" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A109" s="14"/>
+      <c r="B109" s="31"/>
+      <c r="C109" s="28"/>
       <c r="D109" s="3"/>
       <c r="E109" s="3"/>
       <c r="F109" s="3"/>
@@ -5496,11 +5810,12 @@
       <c r="P109" s="3"/>
       <c r="Q109" s="3"/>
       <c r="R109" s="3"/>
-    </row>
-    <row r="110" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="3"/>
-      <c r="B110" s="3"/>
-      <c r="C110" s="3"/>
+      <c r="S109" s="3"/>
+    </row>
+    <row r="110" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A110" s="14"/>
+      <c r="B110" s="31"/>
+      <c r="C110" s="28"/>
       <c r="D110" s="3"/>
       <c r="E110" s="3"/>
       <c r="F110" s="3"/>
@@ -5516,11 +5831,12 @@
       <c r="P110" s="3"/>
       <c r="Q110" s="3"/>
       <c r="R110" s="3"/>
-    </row>
-    <row r="111" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="3"/>
-      <c r="B111" s="3"/>
-      <c r="C111" s="3"/>
+      <c r="S110" s="3"/>
+    </row>
+    <row r="111" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A111" s="14"/>
+      <c r="B111" s="31"/>
+      <c r="C111" s="28"/>
       <c r="D111" s="3"/>
       <c r="E111" s="3"/>
       <c r="F111" s="3"/>
@@ -5536,11 +5852,12 @@
       <c r="P111" s="3"/>
       <c r="Q111" s="3"/>
       <c r="R111" s="3"/>
-    </row>
-    <row r="112" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="3"/>
-      <c r="B112" s="3"/>
-      <c r="C112" s="3"/>
+      <c r="S111" s="3"/>
+    </row>
+    <row r="112" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A112" s="14"/>
+      <c r="B112" s="31"/>
+      <c r="C112" s="28"/>
       <c r="D112" s="3"/>
       <c r="E112" s="3"/>
       <c r="F112" s="3"/>
@@ -5556,11 +5873,12 @@
       <c r="P112" s="3"/>
       <c r="Q112" s="3"/>
       <c r="R112" s="3"/>
-    </row>
-    <row r="113" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="3"/>
-      <c r="B113" s="3"/>
-      <c r="C113" s="3"/>
+      <c r="S112" s="3"/>
+    </row>
+    <row r="113" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A113" s="14"/>
+      <c r="B113" s="31"/>
+      <c r="C113" s="28"/>
       <c r="D113" s="3"/>
       <c r="E113" s="3"/>
       <c r="F113" s="3"/>
@@ -5576,11 +5894,12 @@
       <c r="P113" s="3"/>
       <c r="Q113" s="3"/>
       <c r="R113" s="3"/>
-    </row>
-    <row r="114" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="3"/>
-      <c r="B114" s="3"/>
-      <c r="C114" s="3"/>
+      <c r="S113" s="3"/>
+    </row>
+    <row r="114" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A114" s="14"/>
+      <c r="B114" s="31"/>
+      <c r="C114" s="28"/>
       <c r="D114" s="3"/>
       <c r="E114" s="3"/>
       <c r="F114" s="3"/>
@@ -5596,11 +5915,12 @@
       <c r="P114" s="3"/>
       <c r="Q114" s="3"/>
       <c r="R114" s="3"/>
-    </row>
-    <row r="115" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="3"/>
-      <c r="B115" s="3"/>
-      <c r="C115" s="3"/>
+      <c r="S114" s="3"/>
+    </row>
+    <row r="115" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A115" s="14"/>
+      <c r="B115" s="31"/>
+      <c r="C115" s="28"/>
       <c r="D115" s="3"/>
       <c r="E115" s="3"/>
       <c r="F115" s="3"/>
@@ -5616,11 +5936,12 @@
       <c r="P115" s="3"/>
       <c r="Q115" s="3"/>
       <c r="R115" s="3"/>
-    </row>
-    <row r="116" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="3"/>
-      <c r="B116" s="3"/>
-      <c r="C116" s="3"/>
+      <c r="S115" s="3"/>
+    </row>
+    <row r="116" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A116" s="14"/>
+      <c r="B116" s="31"/>
+      <c r="C116" s="28"/>
       <c r="D116" s="3"/>
       <c r="E116" s="3"/>
       <c r="F116" s="3"/>
@@ -5636,11 +5957,12 @@
       <c r="P116" s="3"/>
       <c r="Q116" s="3"/>
       <c r="R116" s="3"/>
-    </row>
-    <row r="117" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="3"/>
-      <c r="B117" s="3"/>
-      <c r="C117" s="3"/>
+      <c r="S116" s="3"/>
+    </row>
+    <row r="117" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A117" s="14"/>
+      <c r="B117" s="31"/>
+      <c r="C117" s="28"/>
       <c r="D117" s="3"/>
       <c r="E117" s="3"/>
       <c r="F117" s="3"/>
@@ -5656,11 +5978,12 @@
       <c r="P117" s="3"/>
       <c r="Q117" s="3"/>
       <c r="R117" s="3"/>
-    </row>
-    <row r="118" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="3"/>
-      <c r="B118" s="3"/>
-      <c r="C118" s="3"/>
+      <c r="S117" s="3"/>
+    </row>
+    <row r="118" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A118" s="14"/>
+      <c r="B118" s="31"/>
+      <c r="C118" s="28"/>
       <c r="D118" s="3"/>
       <c r="E118" s="3"/>
       <c r="F118" s="3"/>
@@ -5676,11 +5999,12 @@
       <c r="P118" s="3"/>
       <c r="Q118" s="3"/>
       <c r="R118" s="3"/>
-    </row>
-    <row r="119" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="3"/>
-      <c r="B119" s="3"/>
-      <c r="C119" s="3"/>
+      <c r="S118" s="3"/>
+    </row>
+    <row r="119" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A119" s="14"/>
+      <c r="B119" s="31"/>
+      <c r="C119" s="28"/>
       <c r="D119" s="3"/>
       <c r="E119" s="3"/>
       <c r="F119" s="3"/>
@@ -5696,11 +6020,12 @@
       <c r="P119" s="3"/>
       <c r="Q119" s="3"/>
       <c r="R119" s="3"/>
-    </row>
-    <row r="120" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="3"/>
-      <c r="B120" s="3"/>
-      <c r="C120" s="3"/>
+      <c r="S119" s="3"/>
+    </row>
+    <row r="120" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A120" s="14"/>
+      <c r="B120" s="31"/>
+      <c r="C120" s="28"/>
       <c r="D120" s="3"/>
       <c r="E120" s="3"/>
       <c r="F120" s="3"/>
@@ -5716,11 +6041,12 @@
       <c r="P120" s="3"/>
       <c r="Q120" s="3"/>
       <c r="R120" s="3"/>
-    </row>
-    <row r="121" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="3"/>
-      <c r="B121" s="3"/>
-      <c r="C121" s="3"/>
+      <c r="S120" s="3"/>
+    </row>
+    <row r="121" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A121" s="14"/>
+      <c r="B121" s="31"/>
+      <c r="C121" s="28"/>
       <c r="D121" s="3"/>
       <c r="E121" s="3"/>
       <c r="F121" s="3"/>
@@ -5736,11 +6062,12 @@
       <c r="P121" s="3"/>
       <c r="Q121" s="3"/>
       <c r="R121" s="3"/>
-    </row>
-    <row r="122" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="3"/>
-      <c r="B122" s="3"/>
-      <c r="C122" s="3"/>
+      <c r="S121" s="3"/>
+    </row>
+    <row r="122" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A122" s="14"/>
+      <c r="B122" s="31"/>
+      <c r="C122" s="28"/>
       <c r="D122" s="3"/>
       <c r="E122" s="3"/>
       <c r="F122" s="3"/>
@@ -5756,11 +6083,12 @@
       <c r="P122" s="3"/>
       <c r="Q122" s="3"/>
       <c r="R122" s="3"/>
-    </row>
-    <row r="123" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="3"/>
-      <c r="B123" s="3"/>
-      <c r="C123" s="3"/>
+      <c r="S122" s="3"/>
+    </row>
+    <row r="123" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A123" s="14"/>
+      <c r="B123" s="31"/>
+      <c r="C123" s="28"/>
       <c r="D123" s="3"/>
       <c r="E123" s="3"/>
       <c r="F123" s="3"/>
@@ -5776,11 +6104,12 @@
       <c r="P123" s="3"/>
       <c r="Q123" s="3"/>
       <c r="R123" s="3"/>
-    </row>
-    <row r="124" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="3"/>
-      <c r="B124" s="3"/>
-      <c r="C124" s="3"/>
+      <c r="S123" s="3"/>
+    </row>
+    <row r="124" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A124" s="14"/>
+      <c r="B124" s="31"/>
+      <c r="C124" s="28"/>
       <c r="D124" s="3"/>
       <c r="E124" s="3"/>
       <c r="F124" s="3"/>
@@ -5796,11 +6125,12 @@
       <c r="P124" s="3"/>
       <c r="Q124" s="3"/>
       <c r="R124" s="3"/>
-    </row>
-    <row r="125" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="3"/>
-      <c r="B125" s="3"/>
-      <c r="C125" s="3"/>
+      <c r="S124" s="3"/>
+    </row>
+    <row r="125" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A125" s="14"/>
+      <c r="B125" s="31"/>
+      <c r="C125" s="28"/>
       <c r="D125" s="3"/>
       <c r="E125" s="3"/>
       <c r="F125" s="3"/>
@@ -5816,11 +6146,12 @@
       <c r="P125" s="3"/>
       <c r="Q125" s="3"/>
       <c r="R125" s="3"/>
-    </row>
-    <row r="126" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="3"/>
-      <c r="B126" s="3"/>
-      <c r="C126" s="3"/>
+      <c r="S125" s="3"/>
+    </row>
+    <row r="126" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A126" s="14"/>
+      <c r="B126" s="31"/>
+      <c r="C126" s="28"/>
       <c r="D126" s="3"/>
       <c r="E126" s="3"/>
       <c r="F126" s="3"/>
@@ -5836,11 +6167,12 @@
       <c r="P126" s="3"/>
       <c r="Q126" s="3"/>
       <c r="R126" s="3"/>
-    </row>
-    <row r="127" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="3"/>
-      <c r="B127" s="3"/>
-      <c r="C127" s="3"/>
+      <c r="S126" s="3"/>
+    </row>
+    <row r="127" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A127" s="14"/>
+      <c r="B127" s="31"/>
+      <c r="C127" s="28"/>
       <c r="D127" s="3"/>
       <c r="E127" s="3"/>
       <c r="F127" s="3"/>
@@ -5856,11 +6188,12 @@
       <c r="P127" s="3"/>
       <c r="Q127" s="3"/>
       <c r="R127" s="3"/>
-    </row>
-    <row r="128" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="3"/>
-      <c r="B128" s="3"/>
-      <c r="C128" s="3"/>
+      <c r="S127" s="3"/>
+    </row>
+    <row r="128" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A128" s="14"/>
+      <c r="B128" s="31"/>
+      <c r="C128" s="28"/>
       <c r="D128" s="3"/>
       <c r="E128" s="3"/>
       <c r="F128" s="3"/>
@@ -5876,11 +6209,12 @@
       <c r="P128" s="3"/>
       <c r="Q128" s="3"/>
       <c r="R128" s="3"/>
-    </row>
-    <row r="129" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="3"/>
-      <c r="B129" s="3"/>
-      <c r="C129" s="3"/>
+      <c r="S128" s="3"/>
+    </row>
+    <row r="129" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A129" s="14"/>
+      <c r="B129" s="31"/>
+      <c r="C129" s="28"/>
       <c r="D129" s="3"/>
       <c r="E129" s="3"/>
       <c r="F129" s="3"/>
@@ -5896,11 +6230,12 @@
       <c r="P129" s="3"/>
       <c r="Q129" s="3"/>
       <c r="R129" s="3"/>
-    </row>
-    <row r="130" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="3"/>
-      <c r="B130" s="3"/>
-      <c r="C130" s="3"/>
+      <c r="S129" s="3"/>
+    </row>
+    <row r="130" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A130" s="14"/>
+      <c r="B130" s="31"/>
+      <c r="C130" s="28"/>
       <c r="D130" s="3"/>
       <c r="E130" s="3"/>
       <c r="F130" s="3"/>
@@ -5916,11 +6251,12 @@
       <c r="P130" s="3"/>
       <c r="Q130" s="3"/>
       <c r="R130" s="3"/>
-    </row>
-    <row r="131" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="3"/>
-      <c r="B131" s="3"/>
-      <c r="C131" s="3"/>
+      <c r="S130" s="3"/>
+    </row>
+    <row r="131" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A131" s="14"/>
+      <c r="B131" s="31"/>
+      <c r="C131" s="28"/>
       <c r="D131" s="3"/>
       <c r="E131" s="3"/>
       <c r="F131" s="3"/>
@@ -5936,11 +6272,12 @@
       <c r="P131" s="3"/>
       <c r="Q131" s="3"/>
       <c r="R131" s="3"/>
-    </row>
-    <row r="132" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="3"/>
-      <c r="B132" s="3"/>
-      <c r="C132" s="3"/>
+      <c r="S131" s="3"/>
+    </row>
+    <row r="132" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A132" s="14"/>
+      <c r="B132" s="31"/>
+      <c r="C132" s="28"/>
       <c r="D132" s="3"/>
       <c r="E132" s="3"/>
       <c r="F132" s="3"/>
@@ -5956,6 +6293,7 @@
       <c r="P132" s="3"/>
       <c r="Q132" s="3"/>
       <c r="R132" s="3"/>
+      <c r="S132" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hudson/Documents/GitHub/451-DBF-Team01/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\Fall 2026\AAE 451\451-DBF-Team01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD91AC9F-6BE5-2549-A407-92A499FD7404}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D321C07E-B7CE-43E4-8A83-32A447DA3053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INPUTS" sheetId="1" r:id="rId1"/>
@@ -2616,21 +2616,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S132"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.85" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5" style="32" customWidth="1"/>
-    <col min="3" max="3" width="9.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="34.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.6640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="40.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="20" width="8.6640625" style="1" customWidth="1"/>
-    <col min="21" max="16384" width="8.6640625" style="1"/>
+    <col min="1" max="1" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" style="32" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="34.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.7109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="40.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="20" width="8.7109375" style="1" customWidth="1"/>
+    <col min="21" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -2667,7 +2667,7 @@
       <c r="R1" s="3"/>
       <c r="S1" s="3"/>
     </row>
-    <row r="2" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>5</v>
       </c>
@@ -2702,7 +2702,7 @@
       <c r="R2" s="3"/>
       <c r="S2" s="3"/>
     </row>
-    <row r="3" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>10</v>
       </c>
@@ -2735,7 +2735,7 @@
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
     </row>
-    <row r="4" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
         <v>14</v>
       </c>
@@ -2768,7 +2768,7 @@
       <c r="R4" s="3"/>
       <c r="S4" s="3"/>
     </row>
-    <row r="5" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>17</v>
       </c>
@@ -2803,7 +2803,7 @@
       <c r="R5" s="3"/>
       <c r="S5" s="3"/>
     </row>
-    <row r="6" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>22</v>
       </c>
@@ -2838,7 +2838,7 @@
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
     </row>
-    <row r="7" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>179</v>
       </c>
@@ -2872,7 +2872,7 @@
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
     </row>
-    <row r="8" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>26</v>
       </c>
@@ -2908,7 +2908,7 @@
       <c r="R8" s="3"/>
       <c r="S8" s="3"/>
     </row>
-    <row r="9" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>184</v>
       </c>
@@ -2942,7 +2942,7 @@
       <c r="R9" s="3"/>
       <c r="S9" s="3"/>
     </row>
-    <row r="10" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>32</v>
       </c>
@@ -2975,7 +2975,7 @@
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
     </row>
-    <row r="11" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>35</v>
       </c>
@@ -3010,7 +3010,7 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
     </row>
-    <row r="12" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>39</v>
       </c>
@@ -3046,7 +3046,7 @@
       <c r="R12" s="3"/>
       <c r="S12" s="3"/>
     </row>
-    <row r="13" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>43</v>
       </c>
@@ -3082,7 +3082,7 @@
       <c r="R13" s="3"/>
       <c r="S13" s="3"/>
     </row>
-    <row r="14" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>47</v>
       </c>
@@ -3090,7 +3090,7 @@
         <v>205</v>
       </c>
       <c r="C14" s="19">
-        <v>2.8299999999999999E-2</v>
+        <v>3.15E-2</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>18</v>
@@ -3119,7 +3119,7 @@
       <c r="R14" s="3"/>
       <c r="S14" s="3"/>
     </row>
-    <row r="15" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
         <v>142</v>
       </c>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="C15" s="19" cm="1">
         <f t="array" ref="C15">C14+C9*C10^2</f>
-        <v>3.4974132425993974E-2</v>
+        <v>3.8174132425993976E-2</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>18</v>
@@ -3153,7 +3153,7 @@
       <c r="R15" s="3"/>
       <c r="S15" s="3"/>
     </row>
-    <row r="16" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>53</v>
       </c>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="C16" s="19" cm="1">
         <f t="array" ref="C16">C14+C9*C12^2</f>
-        <v>3.4974132425993974E-2</v>
+        <v>3.8174132425993976E-2</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>18</v>
@@ -3189,7 +3189,7 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
     </row>
-    <row r="17" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>56</v>
       </c>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="C17" s="19" cm="1">
         <f t="array" ref="C17">C16-C5*C12</f>
-        <v>1.9974132425993975E-2</v>
+        <v>2.3174132425993976E-2</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>18</v>
@@ -3223,7 +3223,7 @@
       <c r="R17" s="3"/>
       <c r="S17" s="3"/>
     </row>
-    <row r="18" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>59</v>
       </c>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="C18" s="18" cm="1">
         <f t="array" ref="C18">C10/C15</f>
-        <v>8.5777681729434327</v>
+        <v>7.8587247681815153</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>18</v>
@@ -3257,7 +3257,7 @@
       <c r="R18" s="3"/>
       <c r="S18" s="3"/>
     </row>
-    <row r="19" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>62</v>
       </c>
@@ -3290,7 +3290,7 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
     </row>
-    <row r="20" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>65</v>
       </c>
@@ -3323,7 +3323,7 @@
       <c r="R20" s="3"/>
       <c r="S20" s="3"/>
     </row>
-    <row r="21" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>67</v>
       </c>
@@ -3357,7 +3357,7 @@
       <c r="R21" s="3"/>
       <c r="S21" s="3"/>
     </row>
-    <row r="22" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
         <v>69</v>
       </c>
@@ -3391,7 +3391,7 @@
       <c r="R22" s="3"/>
       <c r="S22" s="3"/>
     </row>
-    <row r="23" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>72</v>
       </c>
@@ -3423,7 +3423,7 @@
       <c r="R23" s="3"/>
       <c r="S23" s="3"/>
     </row>
-    <row r="24" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>74</v>
       </c>
@@ -3457,7 +3457,7 @@
       <c r="R24" s="3"/>
       <c r="S24" s="3"/>
     </row>
-    <row r="25" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>77</v>
       </c>
@@ -3490,7 +3490,7 @@
       <c r="R25" s="3"/>
       <c r="S25" s="3"/>
     </row>
-    <row r="26" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>80</v>
       </c>
@@ -3523,7 +3523,7 @@
       <c r="R26" s="3"/>
       <c r="S26" s="3"/>
     </row>
-    <row r="27" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>83</v>
       </c>
@@ -3555,7 +3555,7 @@
       <c r="R27" s="3"/>
       <c r="S27" s="3"/>
     </row>
-    <row r="28" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>86</v>
       </c>
@@ -3588,7 +3588,7 @@
       <c r="R28" s="3"/>
       <c r="S28" s="3"/>
     </row>
-    <row r="29" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>89</v>
       </c>
@@ -3621,7 +3621,7 @@
       <c r="R29" s="3"/>
       <c r="S29" s="3"/>
     </row>
-    <row r="30" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>92</v>
       </c>
@@ -3654,7 +3654,7 @@
       <c r="R30" s="3"/>
       <c r="S30" s="3"/>
     </row>
-    <row r="31" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
         <v>94</v>
       </c>
@@ -3687,7 +3687,7 @@
       <c r="R31" s="3"/>
       <c r="S31" s="3"/>
     </row>
-    <row r="32" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
         <v>97</v>
       </c>
@@ -3720,7 +3720,7 @@
       <c r="R32" s="3"/>
       <c r="S32" s="3"/>
     </row>
-    <row r="33" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
         <v>100</v>
       </c>
@@ -3752,7 +3752,7 @@
       <c r="R33" s="3"/>
       <c r="S33" s="3"/>
     </row>
-    <row r="34" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
         <v>102</v>
       </c>
@@ -3785,7 +3785,7 @@
       <c r="R34" s="3"/>
       <c r="S34" s="3"/>
     </row>
-    <row r="35" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
         <v>105</v>
       </c>
@@ -3816,7 +3816,7 @@
       <c r="R35" s="3"/>
       <c r="S35" s="3"/>
     </row>
-    <row r="36" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>108</v>
       </c>
@@ -3847,7 +3847,7 @@
       <c r="R36" s="3"/>
       <c r="S36" s="3"/>
     </row>
-    <row r="37" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>111</v>
       </c>
@@ -3878,7 +3878,7 @@
       <c r="R37" s="3"/>
       <c r="S37" s="3"/>
     </row>
-    <row r="38" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
         <v>113</v>
       </c>
@@ -3911,7 +3911,7 @@
       <c r="R38" s="3"/>
       <c r="S38" s="3"/>
     </row>
-    <row r="39" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
         <v>117</v>
       </c>
@@ -3943,7 +3943,7 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
     </row>
-    <row r="40" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
         <v>120</v>
       </c>
@@ -3975,7 +3975,7 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
     </row>
-    <row r="41" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
         <v>143</v>
       </c>
@@ -4008,7 +4008,7 @@
       <c r="R41" s="3"/>
       <c r="S41" s="3"/>
     </row>
-    <row r="42" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
         <v>181</v>
       </c>
@@ -4038,7 +4038,7 @@
       <c r="R42" s="3"/>
       <c r="S42" s="3"/>
     </row>
-    <row r="43" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
         <v>126</v>
       </c>
@@ -4069,7 +4069,7 @@
       <c r="R43" s="3"/>
       <c r="S43" s="3"/>
     </row>
-    <row r="44" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
         <v>128</v>
       </c>
@@ -4100,7 +4100,7 @@
       <c r="R44" s="3"/>
       <c r="S44" s="3"/>
     </row>
-    <row r="45" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
         <v>190</v>
       </c>
@@ -4131,7 +4131,7 @@
       <c r="R45" s="3"/>
       <c r="S45" s="3"/>
     </row>
-    <row r="46" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
         <v>131</v>
       </c>
@@ -4164,7 +4164,7 @@
       <c r="R46" s="3"/>
       <c r="S46" s="3"/>
     </row>
-    <row r="47" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
         <v>134</v>
       </c>
@@ -4197,7 +4197,7 @@
       <c r="R47" s="3"/>
       <c r="S47" s="3"/>
     </row>
-    <row r="48" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="12" t="s">
         <v>159</v>
       </c>
@@ -4230,7 +4230,7 @@
       <c r="R48" s="3"/>
       <c r="S48" s="3"/>
     </row>
-    <row r="49" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
         <v>158</v>
       </c>
@@ -4259,7 +4259,7 @@
       <c r="R49" s="3"/>
       <c r="S49" s="3"/>
     </row>
-    <row r="50" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="12" t="s">
         <v>165</v>
       </c>
@@ -4293,7 +4293,7 @@
       <c r="R50" s="3"/>
       <c r="S50" s="3"/>
     </row>
-    <row r="51" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="13" t="s">
         <v>140</v>
       </c>
@@ -4326,7 +4326,7 @@
       <c r="R51" s="3"/>
       <c r="S51" s="3"/>
     </row>
-    <row r="52" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="13" t="s">
         <v>187</v>
       </c>
@@ -4358,7 +4358,7 @@
       <c r="R52" s="3"/>
       <c r="S52" s="3"/>
     </row>
-    <row r="53" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="14" t="s">
         <v>144</v>
       </c>
@@ -4389,7 +4389,7 @@
       <c r="R53" s="3"/>
       <c r="S53" s="3"/>
     </row>
-    <row r="54" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="13" t="s">
         <v>148</v>
       </c>
@@ -4420,7 +4420,7 @@
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
     </row>
-    <row r="55" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="13" t="s">
         <v>150</v>
       </c>
@@ -4451,7 +4451,7 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
     </row>
-    <row r="56" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="13" t="s">
         <v>149</v>
       </c>
@@ -4482,7 +4482,7 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
     </row>
-    <row r="57" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="13" t="s">
         <v>152</v>
       </c>
@@ -4513,7 +4513,7 @@
       <c r="R57" s="3"/>
       <c r="S57" s="3"/>
     </row>
-    <row r="58" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="13" t="s">
         <v>161</v>
       </c>
@@ -4544,7 +4544,7 @@
       <c r="R58" s="3"/>
       <c r="S58" s="3"/>
     </row>
-    <row r="59" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="13" t="s">
         <v>156</v>
       </c>
@@ -4575,7 +4575,7 @@
       <c r="R59" s="3"/>
       <c r="S59" s="3"/>
     </row>
-    <row r="60" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="13" t="s">
         <v>160</v>
       </c>
@@ -4606,7 +4606,7 @@
       <c r="R60" s="3"/>
       <c r="S60" s="3"/>
     </row>
-    <row r="61" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="13" t="s">
         <v>162</v>
       </c>
@@ -4637,7 +4637,7 @@
       <c r="R61" s="3"/>
       <c r="S61" s="3"/>
     </row>
-    <row r="62" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="13" t="s">
         <v>163</v>
       </c>
@@ -4666,7 +4666,7 @@
       <c r="R62" s="3"/>
       <c r="S62" s="3"/>
     </row>
-    <row r="63" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="13" t="s">
         <v>164</v>
       </c>
@@ -4695,7 +4695,7 @@
       <c r="R63" s="3"/>
       <c r="S63" s="3"/>
     </row>
-    <row r="64" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="13" t="s">
         <v>166</v>
       </c>
@@ -4725,7 +4725,7 @@
       <c r="R64" s="3"/>
       <c r="S64" s="3"/>
     </row>
-    <row r="65" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="13" t="s">
         <v>182</v>
       </c>
@@ -4756,7 +4756,7 @@
       <c r="R65" s="3"/>
       <c r="S65" s="3"/>
     </row>
-    <row r="66" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="13" t="s">
         <v>183</v>
       </c>
@@ -4787,7 +4787,7 @@
       <c r="R66" s="3"/>
       <c r="S66" s="3"/>
     </row>
-    <row r="67" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="13" t="s">
         <v>167</v>
       </c>
@@ -4816,7 +4816,7 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
     </row>
-    <row r="68" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="13" t="s">
         <v>168</v>
       </c>
@@ -4845,7 +4845,7 @@
       <c r="R68" s="3"/>
       <c r="S68" s="3"/>
     </row>
-    <row r="69" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="13" t="s">
         <v>169</v>
       </c>
@@ -4874,7 +4874,7 @@
       <c r="R69" s="3"/>
       <c r="S69" s="3"/>
     </row>
-    <row r="70" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="13" t="s">
         <v>170</v>
       </c>
@@ -4903,7 +4903,7 @@
       <c r="R70" s="3"/>
       <c r="S70" s="3"/>
     </row>
-    <row r="71" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="13" t="s">
         <v>171</v>
       </c>
@@ -4932,7 +4932,7 @@
       <c r="R71" s="3"/>
       <c r="S71" s="3"/>
     </row>
-    <row r="72" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="13" t="s">
         <v>172</v>
       </c>
@@ -4961,7 +4961,7 @@
       <c r="R72" s="3"/>
       <c r="S72" s="3"/>
     </row>
-    <row r="73" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="13" t="s">
         <v>173</v>
       </c>
@@ -4990,7 +4990,7 @@
       <c r="R73" s="3"/>
       <c r="S73" s="3"/>
     </row>
-    <row r="74" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="13" t="s">
         <v>174</v>
       </c>
@@ -5019,7 +5019,7 @@
       <c r="R74" s="3"/>
       <c r="S74" s="3"/>
     </row>
-    <row r="75" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="13" t="s">
         <v>175</v>
       </c>
@@ -5050,7 +5050,7 @@
       <c r="R75" s="3"/>
       <c r="S75" s="3"/>
     </row>
-    <row r="76" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="13" t="s">
         <v>177</v>
       </c>
@@ -5081,7 +5081,7 @@
       <c r="R76" s="3"/>
       <c r="S76" s="3"/>
     </row>
-    <row r="77" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="13" t="s">
         <v>193</v>
       </c>
@@ -5110,7 +5110,7 @@
       <c r="R77" s="3"/>
       <c r="S77" s="3"/>
     </row>
-    <row r="78" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="14" t="s">
         <v>194</v>
       </c>
@@ -5141,7 +5141,7 @@
       <c r="R78" s="3"/>
       <c r="S78" s="3"/>
     </row>
-    <row r="79" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="14" t="s">
         <v>197</v>
       </c>
@@ -5172,7 +5172,7 @@
       <c r="R79" s="3"/>
       <c r="S79" s="3"/>
     </row>
-    <row r="80" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="14" t="s">
         <v>198</v>
       </c>
@@ -5203,7 +5203,7 @@
       <c r="R80" s="3"/>
       <c r="S80" s="3"/>
     </row>
-    <row r="81" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="14"/>
       <c r="B81" s="31"/>
       <c r="C81" s="28"/>
@@ -5224,7 +5224,7 @@
       <c r="R81" s="3"/>
       <c r="S81" s="3"/>
     </row>
-    <row r="82" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="14"/>
       <c r="B82" s="31"/>
       <c r="C82" s="28"/>
@@ -5245,7 +5245,7 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
     </row>
-    <row r="83" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="14"/>
       <c r="B83" s="31"/>
       <c r="C83" s="28"/>
@@ -5266,7 +5266,7 @@
       <c r="R83" s="3"/>
       <c r="S83" s="3"/>
     </row>
-    <row r="84" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="14"/>
       <c r="B84" s="31"/>
       <c r="C84" s="28"/>
@@ -5287,7 +5287,7 @@
       <c r="R84" s="3"/>
       <c r="S84" s="3"/>
     </row>
-    <row r="85" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="14"/>
       <c r="B85" s="31"/>
       <c r="C85" s="28"/>
@@ -5308,7 +5308,7 @@
       <c r="R85" s="3"/>
       <c r="S85" s="3"/>
     </row>
-    <row r="86" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="14"/>
       <c r="B86" s="31"/>
       <c r="C86" s="28"/>
@@ -5329,7 +5329,7 @@
       <c r="R86" s="3"/>
       <c r="S86" s="3"/>
     </row>
-    <row r="87" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="14"/>
       <c r="B87" s="31"/>
       <c r="C87" s="28"/>
@@ -5350,7 +5350,7 @@
       <c r="R87" s="3"/>
       <c r="S87" s="3"/>
     </row>
-    <row r="88" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="14"/>
       <c r="B88" s="31"/>
       <c r="C88" s="28"/>
@@ -5371,7 +5371,7 @@
       <c r="R88" s="3"/>
       <c r="S88" s="3"/>
     </row>
-    <row r="89" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="14"/>
       <c r="B89" s="31"/>
       <c r="C89" s="28"/>
@@ -5392,7 +5392,7 @@
       <c r="R89" s="3"/>
       <c r="S89" s="3"/>
     </row>
-    <row r="90" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="14"/>
       <c r="B90" s="31"/>
       <c r="C90" s="28"/>
@@ -5413,7 +5413,7 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
     </row>
-    <row r="91" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="14"/>
       <c r="B91" s="31"/>
       <c r="C91" s="28"/>
@@ -5434,7 +5434,7 @@
       <c r="R91" s="3"/>
       <c r="S91" s="3"/>
     </row>
-    <row r="92" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="14"/>
       <c r="B92" s="31"/>
       <c r="C92" s="28"/>
@@ -5455,7 +5455,7 @@
       <c r="R92" s="3"/>
       <c r="S92" s="3"/>
     </row>
-    <row r="93" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="14"/>
       <c r="B93" s="31"/>
       <c r="C93" s="28"/>
@@ -5476,7 +5476,7 @@
       <c r="R93" s="3"/>
       <c r="S93" s="3"/>
     </row>
-    <row r="94" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="14"/>
       <c r="B94" s="31"/>
       <c r="C94" s="28"/>
@@ -5497,7 +5497,7 @@
       <c r="R94" s="3"/>
       <c r="S94" s="3"/>
     </row>
-    <row r="95" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="14"/>
       <c r="B95" s="31"/>
       <c r="C95" s="28"/>
@@ -5518,7 +5518,7 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
     </row>
-    <row r="96" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="14"/>
       <c r="B96" s="31"/>
       <c r="C96" s="28"/>
@@ -5539,7 +5539,7 @@
       <c r="R96" s="3"/>
       <c r="S96" s="3"/>
     </row>
-    <row r="97" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="14"/>
       <c r="B97" s="31"/>
       <c r="C97" s="28"/>
@@ -5560,7 +5560,7 @@
       <c r="R97" s="3"/>
       <c r="S97" s="3"/>
     </row>
-    <row r="98" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="14"/>
       <c r="B98" s="31"/>
       <c r="C98" s="28"/>
@@ -5581,7 +5581,7 @@
       <c r="R98" s="3"/>
       <c r="S98" s="3"/>
     </row>
-    <row r="99" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="14"/>
       <c r="B99" s="31"/>
       <c r="C99" s="28"/>
@@ -5602,7 +5602,7 @@
       <c r="R99" s="3"/>
       <c r="S99" s="3"/>
     </row>
-    <row r="100" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="14"/>
       <c r="B100" s="31"/>
       <c r="C100" s="28"/>
@@ -5623,7 +5623,7 @@
       <c r="R100" s="3"/>
       <c r="S100" s="3"/>
     </row>
-    <row r="101" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="14"/>
       <c r="B101" s="31"/>
       <c r="C101" s="28"/>
@@ -5644,7 +5644,7 @@
       <c r="R101" s="3"/>
       <c r="S101" s="3"/>
     </row>
-    <row r="102" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="14"/>
       <c r="B102" s="31"/>
       <c r="C102" s="28"/>
@@ -5665,7 +5665,7 @@
       <c r="R102" s="3"/>
       <c r="S102" s="3"/>
     </row>
-    <row r="103" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="14"/>
       <c r="B103" s="31"/>
       <c r="C103" s="28"/>
@@ -5686,7 +5686,7 @@
       <c r="R103" s="3"/>
       <c r="S103" s="3"/>
     </row>
-    <row r="104" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="14"/>
       <c r="B104" s="31"/>
       <c r="C104" s="28"/>
@@ -5707,7 +5707,7 @@
       <c r="R104" s="3"/>
       <c r="S104" s="3"/>
     </row>
-    <row r="105" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="14"/>
       <c r="B105" s="31"/>
       <c r="C105" s="28"/>
@@ -5728,7 +5728,7 @@
       <c r="R105" s="3"/>
       <c r="S105" s="3"/>
     </row>
-    <row r="106" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="14"/>
       <c r="B106" s="31"/>
       <c r="C106" s="28"/>
@@ -5749,7 +5749,7 @@
       <c r="R106" s="3"/>
       <c r="S106" s="3"/>
     </row>
-    <row r="107" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="14"/>
       <c r="B107" s="31"/>
       <c r="C107" s="28"/>
@@ -5770,7 +5770,7 @@
       <c r="R107" s="3"/>
       <c r="S107" s="3"/>
     </row>
-    <row r="108" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="14"/>
       <c r="B108" s="31"/>
       <c r="C108" s="28"/>
@@ -5791,7 +5791,7 @@
       <c r="R108" s="3"/>
       <c r="S108" s="3"/>
     </row>
-    <row r="109" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="14"/>
       <c r="B109" s="31"/>
       <c r="C109" s="28"/>
@@ -5812,7 +5812,7 @@
       <c r="R109" s="3"/>
       <c r="S109" s="3"/>
     </row>
-    <row r="110" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="14"/>
       <c r="B110" s="31"/>
       <c r="C110" s="28"/>
@@ -5833,7 +5833,7 @@
       <c r="R110" s="3"/>
       <c r="S110" s="3"/>
     </row>
-    <row r="111" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="14"/>
       <c r="B111" s="31"/>
       <c r="C111" s="28"/>
@@ -5854,7 +5854,7 @@
       <c r="R111" s="3"/>
       <c r="S111" s="3"/>
     </row>
-    <row r="112" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="14"/>
       <c r="B112" s="31"/>
       <c r="C112" s="28"/>
@@ -5875,7 +5875,7 @@
       <c r="R112" s="3"/>
       <c r="S112" s="3"/>
     </row>
-    <row r="113" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="14"/>
       <c r="B113" s="31"/>
       <c r="C113" s="28"/>
@@ -5896,7 +5896,7 @@
       <c r="R113" s="3"/>
       <c r="S113" s="3"/>
     </row>
-    <row r="114" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="14"/>
       <c r="B114" s="31"/>
       <c r="C114" s="28"/>
@@ -5917,7 +5917,7 @@
       <c r="R114" s="3"/>
       <c r="S114" s="3"/>
     </row>
-    <row r="115" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="14"/>
       <c r="B115" s="31"/>
       <c r="C115" s="28"/>
@@ -5938,7 +5938,7 @@
       <c r="R115" s="3"/>
       <c r="S115" s="3"/>
     </row>
-    <row r="116" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="14"/>
       <c r="B116" s="31"/>
       <c r="C116" s="28"/>
@@ -5959,7 +5959,7 @@
       <c r="R116" s="3"/>
       <c r="S116" s="3"/>
     </row>
-    <row r="117" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="14"/>
       <c r="B117" s="31"/>
       <c r="C117" s="28"/>
@@ -5980,7 +5980,7 @@
       <c r="R117" s="3"/>
       <c r="S117" s="3"/>
     </row>
-    <row r="118" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="14"/>
       <c r="B118" s="31"/>
       <c r="C118" s="28"/>
@@ -6001,7 +6001,7 @@
       <c r="R118" s="3"/>
       <c r="S118" s="3"/>
     </row>
-    <row r="119" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="14"/>
       <c r="B119" s="31"/>
       <c r="C119" s="28"/>
@@ -6022,7 +6022,7 @@
       <c r="R119" s="3"/>
       <c r="S119" s="3"/>
     </row>
-    <row r="120" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="14"/>
       <c r="B120" s="31"/>
       <c r="C120" s="28"/>
@@ -6043,7 +6043,7 @@
       <c r="R120" s="3"/>
       <c r="S120" s="3"/>
     </row>
-    <row r="121" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="14"/>
       <c r="B121" s="31"/>
       <c r="C121" s="28"/>
@@ -6064,7 +6064,7 @@
       <c r="R121" s="3"/>
       <c r="S121" s="3"/>
     </row>
-    <row r="122" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="14"/>
       <c r="B122" s="31"/>
       <c r="C122" s="28"/>
@@ -6085,7 +6085,7 @@
       <c r="R122" s="3"/>
       <c r="S122" s="3"/>
     </row>
-    <row r="123" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="14"/>
       <c r="B123" s="31"/>
       <c r="C123" s="28"/>
@@ -6106,7 +6106,7 @@
       <c r="R123" s="3"/>
       <c r="S123" s="3"/>
     </row>
-    <row r="124" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="14"/>
       <c r="B124" s="31"/>
       <c r="C124" s="28"/>
@@ -6127,7 +6127,7 @@
       <c r="R124" s="3"/>
       <c r="S124" s="3"/>
     </row>
-    <row r="125" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="14"/>
       <c r="B125" s="31"/>
       <c r="C125" s="28"/>
@@ -6148,7 +6148,7 @@
       <c r="R125" s="3"/>
       <c r="S125" s="3"/>
     </row>
-    <row r="126" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="14"/>
       <c r="B126" s="31"/>
       <c r="C126" s="28"/>
@@ -6169,7 +6169,7 @@
       <c r="R126" s="3"/>
       <c r="S126" s="3"/>
     </row>
-    <row r="127" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="14"/>
       <c r="B127" s="31"/>
       <c r="C127" s="28"/>
@@ -6190,7 +6190,7 @@
       <c r="R127" s="3"/>
       <c r="S127" s="3"/>
     </row>
-    <row r="128" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="14"/>
       <c r="B128" s="31"/>
       <c r="C128" s="28"/>
@@ -6211,7 +6211,7 @@
       <c r="R128" s="3"/>
       <c r="S128" s="3"/>
     </row>
-    <row r="129" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="14"/>
       <c r="B129" s="31"/>
       <c r="C129" s="28"/>
@@ -6232,7 +6232,7 @@
       <c r="R129" s="3"/>
       <c r="S129" s="3"/>
     </row>
-    <row r="130" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="14"/>
       <c r="B130" s="31"/>
       <c r="C130" s="28"/>
@@ -6253,7 +6253,7 @@
       <c r="R130" s="3"/>
       <c r="S130" s="3"/>
     </row>
-    <row r="131" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="14"/>
       <c r="B131" s="31"/>
       <c r="C131" s="28"/>
@@ -6274,7 +6274,7 @@
       <c r="R131" s="3"/>
       <c r="S131" s="3"/>
     </row>
-    <row r="132" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="14"/>
       <c r="B132" s="31"/>
       <c r="C132" s="28"/>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\Fall 2026\AAE 451\451-DBF-Team01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D321C07E-B7CE-43E4-8A83-32A447DA3053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8FE2283-5D42-44E7-810A-D88494F7A345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="INPUTS" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -55,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="210">
   <si>
     <t>Parameter</t>
   </si>
@@ -201,9 +202,6 @@
     <t>CD_0</t>
   </si>
   <si>
-    <t>Zero lift CD</t>
-  </si>
-  <si>
     <t>Sadraey, table 4.12</t>
   </si>
   <si>
@@ -682,6 +680,12 @@
   </si>
   <si>
     <t>prop</t>
+  </si>
+  <si>
+    <t>Recalc with V_C, MTOW</t>
+  </si>
+  <si>
+    <t>Parasitic drag</t>
   </si>
 </sst>
 </file>
@@ -863,7 +867,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -897,6 +901,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2623,7 +2628,7 @@
     <col min="3" max="3" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.7109375" style="1" customWidth="1"/>
     <col min="5" max="5" width="34.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="25.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="40.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="20" width="8.7109375" style="1" customWidth="1"/>
@@ -2635,7 +2640,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="29" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C1" s="15" t="s">
         <v>1</v>
@@ -2647,10 +2652,10 @@
         <v>3</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H1" s="7" t="s">
         <v>4</v>
@@ -2672,7 +2677,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="30" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C2" s="16">
         <v>1.2250000000000001</v>
@@ -2707,7 +2712,7 @@
         <v>10</v>
       </c>
       <c r="B3" s="30" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C3" s="17">
         <v>1.7960000000000001E-5</v>
@@ -2740,7 +2745,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C4" s="16">
         <v>9.81</v>
@@ -2773,7 +2778,7 @@
         <v>17</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C5" s="16">
         <v>0.05</v>
@@ -2808,7 +2813,7 @@
         <v>22</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C6" s="16">
         <v>0.08</v>
@@ -2840,14 +2845,14 @@
     </row>
     <row r="7" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C7" s="18">
         <f>1.78*(1-0.045*C8^0.68)-0.64</f>
-        <v>0.91000572412664693</v>
+        <v>0.90801296185572322</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>18</v>
@@ -2857,7 +2862,7 @@
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
@@ -2877,11 +2882,11 @@
         <v>26</v>
       </c>
       <c r="B8" s="30" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C8" s="18">
         <f>C54/C42</f>
-        <v>4.7168676768718001</v>
+        <v>4.777091231498102</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>18</v>
@@ -2910,14 +2915,14 @@
     </row>
     <row r="9" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C9" s="19" cm="1">
         <f t="array" ref="C9">1/(PI()*C7*C8)</f>
-        <v>7.4157026955488606E-2</v>
+        <v>7.3382844793574334E-2</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>18</v>
@@ -2947,10 +2952,11 @@
         <v>32</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="C10" s="16">
-        <v>0.3</v>
+        <v>204</v>
+      </c>
+      <c r="C10" s="19">
+        <f>C39/(0.5*C2*C22^2*C40)</f>
+        <v>0.29319856487018242</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>18</v>
@@ -2958,7 +2964,9 @@
       <c r="E10" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="2"/>
+      <c r="F10" s="2" t="s">
+        <v>208</v>
+      </c>
       <c r="G10" s="2" t="s">
         <v>34</v>
       </c>
@@ -2980,9 +2988,9 @@
         <v>35</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="C11" s="16">
+        <v>204</v>
+      </c>
+      <c r="C11" s="19">
         <v>1.43</v>
       </c>
       <c r="D11" s="4" t="s">
@@ -3015,11 +3023,11 @@
         <v>39</v>
       </c>
       <c r="B12" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="C12" s="16" cm="1">
+        <v>204</v>
+      </c>
+      <c r="C12" s="18" cm="1">
         <f t="array" ref="C12">C10</f>
-        <v>0.3</v>
+        <v>0.29319856487018242</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>18</v>
@@ -3051,7 +3059,7 @@
         <v>43</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C13" s="18" cm="1">
         <f t="array" ref="C13">C11/C20^2</f>
@@ -3087,25 +3095,25 @@
         <v>47</v>
       </c>
       <c r="B14" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="C14" s="19">
-        <v>3.15E-2</v>
+        <v>204</v>
+      </c>
+      <c r="C14" s="33">
+        <v>3.1699999999999999E-2</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F14" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="G14" s="2" t="s">
+      <c r="H14" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
@@ -3121,24 +3129,24 @@
     </row>
     <row r="15" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B15" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="C15" s="19" cm="1">
+        <v>204</v>
+      </c>
+      <c r="C15" s="33" cm="1">
         <f t="array" ref="C15">C14+C9*C10^2</f>
-        <v>3.8174132425993976E-2</v>
+        <v>3.8008385491482263E-2</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
@@ -3155,24 +3163,24 @@
     </row>
     <row r="16" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B16" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="C16" s="19" cm="1">
+        <v>204</v>
+      </c>
+      <c r="C16" s="33" cm="1">
         <f t="array" ref="C16">C14+C9*C12^2</f>
-        <v>3.8174132425993976E-2</v>
+        <v>3.8008385491482263E-2</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>42</v>
@@ -3191,24 +3199,24 @@
     </row>
     <row r="17" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B17" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="C17" s="19" cm="1">
+        <v>204</v>
+      </c>
+      <c r="C17" s="33" cm="1">
         <f t="array" ref="C17">C16-C5*C12</f>
-        <v>2.3174132425993976E-2</v>
+        <v>2.3348457247973142E-2</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
@@ -3225,25 +3233,25 @@
     </row>
     <row r="18" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B18" s="30" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C18" s="18" cm="1">
         <f t="array" ref="C18">C10/C15</f>
-        <v>7.8587247681815153</v>
+        <v>7.7140494414288829</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="3"/>
       <c r="H18" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
@@ -3259,10 +3267,10 @@
     </row>
     <row r="19" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B19" s="30" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C19" s="18">
         <v>10.5</v>
@@ -3271,11 +3279,11 @@
         <v>15</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
@@ -3292,10 +3300,10 @@
     </row>
     <row r="20" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B20" s="30" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C20" s="20">
         <v>1.1000000000000001</v>
@@ -3304,7 +3312,7 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2" t="s">
@@ -3325,10 +3333,10 @@
     </row>
     <row r="21" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B21" s="30" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C21" s="18" cm="1">
         <f t="array" ref="C21">C20*C19</f>
@@ -3338,7 +3346,7 @@
         <v>15</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2" t="s">
@@ -3359,25 +3367,24 @@
     </row>
     <row r="22" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B22" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="C22" s="18" cm="1">
-        <f t="array" ref="C22">SQRT(C19^2*C11/C10)</f>
-        <v>22.924332051337942</v>
+        <v>206</v>
+      </c>
+      <c r="C22" s="18">
+        <v>23</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="3"/>
       <c r="H22" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
@@ -3393,10 +3400,10 @@
     </row>
     <row r="23" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B23" s="30" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C23" s="18" cm="1">
         <f t="array" ref="C23">SQRT(C26*C4*SQRT(C25^2-1))</f>
@@ -3406,7 +3413,7 @@
         <v>15</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="3"/>
@@ -3425,10 +3432,10 @@
     </row>
     <row r="24" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B24" s="30" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C24" s="18" cm="1">
         <f t="array" ref="C24">C19*SQRT(C25)</f>
@@ -3438,11 +3445,11 @@
         <v>15</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
@@ -3459,10 +3466,10 @@
     </row>
     <row r="25" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B25" s="30" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C25" s="16">
         <v>1.5</v>
@@ -3471,11 +3478,11 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
@@ -3492,23 +3499,23 @@
     </row>
     <row r="26" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B26" s="30" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C26" s="16">
         <v>20</v>
       </c>
       <c r="D26" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>82</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
@@ -3525,20 +3532,20 @@
     </row>
     <row r="27" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B27" s="30" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C27" s="18" cm="1">
         <f t="array" ref="C27">DEGREES(ACOS(1/C25))</f>
         <v>48.189685104221404</v>
       </c>
       <c r="D27" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="3"/>
@@ -3557,10 +3564,10 @@
     </row>
     <row r="28" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B28" s="30" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C28" s="16">
         <v>0.75</v>
@@ -3569,11 +3576,11 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
@@ -3590,10 +3597,10 @@
     </row>
     <row r="29" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B29" s="30" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C29" s="16">
         <v>0.75</v>
@@ -3602,11 +3609,11 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
@@ -3623,10 +3630,10 @@
     </row>
     <row r="30" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B30" s="30" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C30" s="16">
         <v>0.45</v>
@@ -3635,11 +3642,11 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
@@ -3656,23 +3663,23 @@
     </row>
     <row r="31" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B31" s="30" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C31" s="16">
         <v>30</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
@@ -3689,23 +3696,23 @@
     </row>
     <row r="32" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B32" s="30" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C32" s="16">
         <v>100</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
@@ -3722,20 +3729,20 @@
     </row>
     <row r="33" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B33" s="30" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C33" s="18" cm="1">
         <f t="array" ref="C33">DEGREES(ATAN(30/100))</f>
         <v>16.699244233993621</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="3"/>
@@ -3754,23 +3761,23 @@
     </row>
     <row r="34" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B34" s="30" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C34" s="18">
         <v>25</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
@@ -3787,19 +3794,19 @@
     </row>
     <row r="35" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B35" s="30" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C35" s="16">
         <v>95</v>
       </c>
       <c r="D35" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="3"/>
@@ -3818,19 +3825,19 @@
     </row>
     <row r="36" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B36" s="30" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C36" s="16">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="D36" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E36" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>110</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="3"/>
@@ -3849,10 +3856,10 @@
     </row>
     <row r="37" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B37" s="30" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C37" s="16">
         <v>0.8</v>
@@ -3861,7 +3868,7 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="3"/>
@@ -3880,23 +3887,23 @@
     </row>
     <row r="38" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="B38" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="C38" s="21">
+        <v>4.3939000000000004</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B38" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="C38" s="21">
-        <v>4.45</v>
-      </c>
-      <c r="D38" s="2" t="s">
+      <c r="E38" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>115</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
@@ -3913,20 +3920,20 @@
     </row>
     <row r="39" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B39" s="30" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C39" s="22" cm="1">
         <f t="array" ref="C39">C4*C38</f>
-        <v>43.654500000000006</v>
+        <v>43.104159000000003</v>
       </c>
       <c r="D39" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E39" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>119</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="3"/>
@@ -3945,20 +3952,20 @@
     </row>
     <row r="40" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B40" s="30" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C40" s="23">
         <f>C39/C35</f>
-        <v>0.459521052631579</v>
+        <v>0.45372798947368426</v>
       </c>
       <c r="D40" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E40" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>122</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="3"/>
@@ -3977,10 +3984,10 @@
     </row>
     <row r="41" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B41" s="30" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C41" s="24">
         <v>-0.08</v>
@@ -3989,11 +3996,11 @@
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
@@ -4010,18 +4017,18 @@
     </row>
     <row r="42" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B42" s="30" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C42" s="25">
         <f>C40/(C54-C55)</f>
-        <v>0.31800764887998545</v>
+        <v>0.31399860863230744</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="3"/>
@@ -4040,21 +4047,21 @@
     </row>
     <row r="43" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B43" s="30" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C43" s="26">
         <v>0.25</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
@@ -4071,19 +4078,19 @@
     </row>
     <row r="44" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B44" s="30" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C44" s="26">
         <v>0.7</v>
       </c>
       <c r="D44" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>130</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="3"/>
@@ -4102,10 +4109,10 @@
     </row>
     <row r="45" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B45" s="30" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C45" s="26">
         <v>0.23</v>
@@ -4114,7 +4121,7 @@
         <v>18</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="3"/>
@@ -4133,10 +4140,10 @@
     </row>
     <row r="46" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B46" s="30" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C46" s="26">
         <v>0.3</v>
@@ -4145,11 +4152,11 @@
         <v>18</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F46" s="2"/>
       <c r="G46" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
@@ -4166,10 +4173,10 @@
     </row>
     <row r="47" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B47" s="30" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C47" s="26">
         <v>0.43</v>
@@ -4178,11 +4185,11 @@
         <v>18</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F47" s="2"/>
       <c r="G47" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
@@ -4199,23 +4206,23 @@
     </row>
     <row r="48" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B48" s="30" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C48" s="26">
         <v>0.19600000000000001</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
@@ -4232,16 +4239,16 @@
     </row>
     <row r="49" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B49" s="30" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C49" s="26">
         <v>0.53900000000000003</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
@@ -4261,10 +4268,10 @@
     </row>
     <row r="50" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="12" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B50" s="30" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C50" s="27">
         <f>C49/C48</f>
@@ -4274,11 +4281,11 @@
         <v>18</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
@@ -4295,10 +4302,10 @@
     </row>
     <row r="51" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="13" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B51" s="30" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C51" s="27">
         <v>0.65</v>
@@ -4307,10 +4314,10 @@
         <v>18</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G51" s="5"/>
       <c r="H51" s="3"/>
@@ -4328,10 +4335,10 @@
     </row>
     <row r="52" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B52" s="30" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C52" s="27">
         <f>1/(PI()*C51*C50)</f>
@@ -4341,7 +4348,7 @@
         <v>18</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F52" s="6"/>
       <c r="G52" s="5"/>
@@ -4360,10 +4367,10 @@
     </row>
     <row r="53" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B53" s="30" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C53" s="28">
         <v>0.15</v>
@@ -4372,7 +4379,7 @@
         <v>18</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
@@ -4391,19 +4398,19 @@
     </row>
     <row r="54" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B54" s="30" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C54" s="28">
         <v>1.5</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3"/>
@@ -4422,19 +4429,19 @@
     </row>
     <row r="55" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B55" s="30" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C55" s="28">
         <v>5.5E-2</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F55" s="6"/>
       <c r="G55" s="3"/>
@@ -4453,19 +4460,19 @@
     </row>
     <row r="56" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="13" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B56" s="30" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C56" s="28">
         <v>1</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F56" s="6"/>
       <c r="G56" s="3"/>
@@ -4484,19 +4491,19 @@
     </row>
     <row r="57" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="13" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B57" s="30" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C57" s="28">
         <v>0.24299999999999999</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F57" s="6"/>
       <c r="G57" s="3"/>
@@ -4515,10 +4522,10 @@
     </row>
     <row r="58" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B58" s="30" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C58" s="28">
         <v>0.14000000000000001</v>
@@ -4527,7 +4534,7 @@
         <v>18</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F58" s="6"/>
       <c r="G58" s="3"/>
@@ -4546,10 +4553,10 @@
     </row>
     <row r="59" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B59" s="30" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C59" s="28">
         <v>0.255</v>
@@ -4558,7 +4565,7 @@
         <v>18</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F59" s="6"/>
       <c r="G59" s="3"/>
@@ -4577,10 +4584,10 @@
     </row>
     <row r="60" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B60" s="30" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C60" s="28">
         <v>0.1</v>
@@ -4589,7 +4596,7 @@
         <v>18</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F60" s="6"/>
       <c r="G60" s="3"/>
@@ -4608,10 +4615,10 @@
     </row>
     <row r="61" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="13" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B61" s="30" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C61" s="28">
         <v>0.3</v>
@@ -4620,7 +4627,7 @@
         <v>18</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F61" s="6"/>
       <c r="G61" s="3"/>
@@ -4639,16 +4646,16 @@
     </row>
     <row r="62" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="13" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B62" s="30" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C62" s="28">
         <v>0.16200000000000001</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
@@ -4668,16 +4675,16 @@
     </row>
     <row r="63" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B63" s="30" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C63" s="28">
         <v>0.24299999999999999</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
@@ -4697,10 +4704,10 @@
     </row>
     <row r="64" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B64" s="30" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C64" s="27">
         <f>C63/C62</f>
@@ -4727,10 +4734,10 @@
     </row>
     <row r="65" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B65" s="30" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C65" s="28">
         <v>0.1</v>
@@ -4739,7 +4746,7 @@
         <v>18</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F65" s="6"/>
       <c r="G65" s="3"/>
@@ -4758,10 +4765,10 @@
     </row>
     <row r="66" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="13" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B66" s="30" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C66" s="28">
         <v>0.3</v>
@@ -4770,7 +4777,7 @@
         <v>18</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F66" s="6"/>
       <c r="G66" s="3"/>
@@ -4789,16 +4796,16 @@
     </row>
     <row r="67" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B67" s="30" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C67" s="28">
         <v>0.05</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
@@ -4818,16 +4825,16 @@
     </row>
     <row r="68" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B68" s="30" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C68" s="28">
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
@@ -4847,16 +4854,16 @@
     </row>
     <row r="69" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="13" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B69" s="30" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C69" s="28">
         <v>0.155</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
@@ -4876,16 +4883,16 @@
     </row>
     <row r="70" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="13" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B70" s="30" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C70" s="28">
         <v>1.6E-2</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
@@ -4905,16 +4912,16 @@
     </row>
     <row r="71" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="13" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B71" s="30" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C71" s="28">
         <v>0.05</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
@@ -4934,16 +4941,16 @@
     </row>
     <row r="72" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="13" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B72" s="30" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C72" s="28">
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
@@ -4963,16 +4970,16 @@
     </row>
     <row r="73" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B73" s="30" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C73" s="28">
         <v>0.09</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
@@ -4992,16 +4999,16 @@
     </row>
     <row r="74" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B74" s="30" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C74" s="28">
         <v>0.01</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
@@ -5021,10 +5028,10 @@
     </row>
     <row r="75" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B75" s="30" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C75" s="28">
         <v>0.25</v>
@@ -5033,7 +5040,7 @@
         <v>18</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F75" s="6"/>
       <c r="G75" s="3"/>
@@ -5052,10 +5059,10 @@
     </row>
     <row r="76" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B76" s="30" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C76" s="28">
         <v>0.3</v>
@@ -5064,7 +5071,7 @@
         <v>18</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F76" s="6"/>
       <c r="G76" s="3"/>
@@ -5083,10 +5090,10 @@
     </row>
     <row r="77" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B77" s="30" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C77" s="28">
         <v>0.1</v>
@@ -5112,19 +5119,19 @@
     </row>
     <row r="78" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="14" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B78" s="30" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C78" s="28">
         <v>0.08</v>
       </c>
       <c r="D78" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="E78" s="3" t="s">
         <v>195</v>
-      </c>
-      <c r="E78" s="3" t="s">
-        <v>196</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3"/>
@@ -5143,19 +5150,19 @@
     </row>
     <row r="79" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="14" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B79" s="30" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C79" s="28">
         <v>0.1</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3"/>
@@ -5174,19 +5181,19 @@
     </row>
     <row r="80" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="14" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B80" s="30" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C80" s="28">
         <v>0.04</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3"/>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -16,7 +16,6 @@
     <sheet name="INPUTS" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\Fall 2026\AAE 451\451-DBF-Team01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ceaa8977d2236823/Documents/GitHub/451-DBF-Team01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8FE2283-5D42-44E7-810A-D88494F7A345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="77" documentId="13_ncr:1_{B8FE2283-5D42-44E7-810A-D88494F7A345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFC54096-9E1B-46ED-AC3C-8C70B6949F5A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5136" yWindow="1980" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INPUTS" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="234">
   <si>
     <t>Parameter</t>
   </si>
@@ -685,6 +685,78 @@
   </si>
   <si>
     <t>Parasitic drag</t>
+  </si>
+  <si>
+    <t>CM_0_Wing</t>
+  </si>
+  <si>
+    <t>CM of Wing at 0 AoA</t>
+  </si>
+  <si>
+    <t>Airfoil_Alpha_Stall</t>
+  </si>
+  <si>
+    <t>kappa</t>
+  </si>
+  <si>
+    <t>AR_v</t>
+  </si>
+  <si>
+    <t>Vertical Tail Aspect Ratio</t>
+  </si>
+  <si>
+    <t>E_r</t>
+  </si>
+  <si>
+    <t>Rudder Chord Fraction</t>
+  </si>
+  <si>
+    <t>delta_r_limit</t>
+  </si>
+  <si>
+    <t>Max Rudder Deflection</t>
+  </si>
+  <si>
+    <t>crosswind_ratio</t>
+  </si>
+  <si>
+    <t>Cross Wind Ratio</t>
+  </si>
+  <si>
+    <t>roll_rate_target_dps</t>
+  </si>
+  <si>
+    <t>deg/s</t>
+  </si>
+  <si>
+    <t>Roll Rate Target</t>
+  </si>
+  <si>
+    <t>E_a</t>
+  </si>
+  <si>
+    <t>Aileron Chord Fraction</t>
+  </si>
+  <si>
+    <t>y1_frac</t>
+  </si>
+  <si>
+    <t>y2_frac</t>
+  </si>
+  <si>
+    <t>Aileron Span Fractions of the Semi Span</t>
+  </si>
+  <si>
+    <t>delta_a_limit</t>
+  </si>
+  <si>
+    <t>Max Aileron Deflection</t>
+  </si>
+  <si>
+    <t>Gamma_dihedral_deg</t>
+  </si>
+  <si>
+    <t>Dihedral Initialization</t>
   </si>
 </sst>
 </file>
@@ -731,7 +803,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -862,11 +934,46 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="10"/>
+      </left>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="10"/>
+      </left>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="10"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -901,6 +1008,14 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1089,15 +1204,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>142142</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>97457</xdr:rowOff>
+      <xdr:colOff>179294</xdr:colOff>
+      <xdr:row>120</xdr:row>
+      <xdr:rowOff>167247</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>605269</xdr:colOff>
-      <xdr:row>100</xdr:row>
-      <xdr:rowOff>59358</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1096331</xdr:colOff>
+      <xdr:row>132</xdr:row>
+      <xdr:rowOff>166935</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1120,8 +1235,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="142142" y="14937407"/>
-          <a:ext cx="5206577" cy="3038476"/>
+          <a:off x="179294" y="21682541"/>
+          <a:ext cx="4718072" cy="2151218"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1236,15 +1351,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>175846</xdr:colOff>
-      <xdr:row>96</xdr:row>
-      <xdr:rowOff>43014</xdr:rowOff>
+      <xdr:colOff>212997</xdr:colOff>
+      <xdr:row>128</xdr:row>
+      <xdr:rowOff>150591</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>575716</xdr:colOff>
-      <xdr:row>104</xdr:row>
-      <xdr:rowOff>65005</xdr:rowOff>
+      <xdr:colOff>612867</xdr:colOff>
+      <xdr:row>136</xdr:row>
+      <xdr:rowOff>172582</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1267,8 +1382,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="175846" y="17261283"/>
-          <a:ext cx="4920582" cy="1487376"/>
+          <a:off x="212997" y="23100238"/>
+          <a:ext cx="8073658" cy="1456344"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1285,15 +1400,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>278424</xdr:colOff>
-      <xdr:row>104</xdr:row>
-      <xdr:rowOff>14660</xdr:rowOff>
+      <xdr:colOff>296354</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>23624</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>1516674</xdr:colOff>
-      <xdr:row>106</xdr:row>
-      <xdr:rowOff>118773</xdr:rowOff>
+      <xdr:colOff>1534604</xdr:colOff>
+      <xdr:row>119</xdr:row>
+      <xdr:rowOff>127737</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1316,8 +1431,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="278424" y="18698314"/>
-          <a:ext cx="5758962" cy="470459"/>
+          <a:off x="296354" y="21001036"/>
+          <a:ext cx="8912038" cy="462701"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1383,15 +1498,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>498231</xdr:colOff>
-      <xdr:row>106</xdr:row>
-      <xdr:rowOff>109907</xdr:rowOff>
+      <xdr:colOff>535382</xdr:colOff>
+      <xdr:row>139</xdr:row>
+      <xdr:rowOff>38190</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>1281404</xdr:colOff>
-      <xdr:row>122</xdr:row>
-      <xdr:rowOff>79550</xdr:rowOff>
+      <xdr:colOff>1318555</xdr:colOff>
+      <xdr:row>155</xdr:row>
+      <xdr:rowOff>7833</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1414,8 +1529,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="498231" y="19159907"/>
-          <a:ext cx="5062096" cy="2900412"/>
+          <a:off x="535382" y="24960072"/>
+          <a:ext cx="8456961" cy="2838349"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1432,15 +1547,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>685067</xdr:colOff>
-      <xdr:row>124</xdr:row>
-      <xdr:rowOff>52020</xdr:rowOff>
+      <xdr:colOff>722218</xdr:colOff>
+      <xdr:row>156</xdr:row>
+      <xdr:rowOff>159598</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>1305657</xdr:colOff>
-      <xdr:row>139</xdr:row>
-      <xdr:rowOff>59792</xdr:rowOff>
+      <xdr:colOff>1342808</xdr:colOff>
+      <xdr:row>171</xdr:row>
+      <xdr:rowOff>167369</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1463,8 +1578,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685067" y="22399135"/>
-          <a:ext cx="4899513" cy="2755369"/>
+          <a:off x="722218" y="28129480"/>
+          <a:ext cx="8294378" cy="2697183"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2620,21 +2735,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S132"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.85" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.85" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" style="32" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="34.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.7109375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="40.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="20" width="8.7109375" style="1" customWidth="1"/>
-    <col min="21" max="16384" width="8.7109375" style="1"/>
+    <col min="1" max="1" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.44140625" style="32" customWidth="1"/>
+    <col min="3" max="3" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="34.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.6640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="40.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="20" width="8.6640625" style="1" customWidth="1"/>
+    <col min="21" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -2671,7 +2786,7 @@
       <c r="R1" s="3"/>
       <c r="S1" s="3"/>
     </row>
-    <row r="2" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
         <v>5</v>
       </c>
@@ -2706,7 +2821,7 @@
       <c r="R2" s="3"/>
       <c r="S2" s="3"/>
     </row>
-    <row r="3" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>10</v>
       </c>
@@ -2739,7 +2854,7 @@
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
     </row>
-    <row r="4" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
         <v>14</v>
       </c>
@@ -2772,7 +2887,7 @@
       <c r="R4" s="3"/>
       <c r="S4" s="3"/>
     </row>
-    <row r="5" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>17</v>
       </c>
@@ -2807,7 +2922,7 @@
       <c r="R5" s="3"/>
       <c r="S5" s="3"/>
     </row>
-    <row r="6" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>22</v>
       </c>
@@ -2842,7 +2957,7 @@
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
     </row>
-    <row r="7" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
         <v>178</v>
       </c>
@@ -2876,7 +2991,7 @@
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
     </row>
-    <row r="8" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>26</v>
       </c>
@@ -2912,7 +3027,7 @@
       <c r="R8" s="3"/>
       <c r="S8" s="3"/>
     </row>
-    <row r="9" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
         <v>183</v>
       </c>
@@ -2946,7 +3061,7 @@
       <c r="R9" s="3"/>
       <c r="S9" s="3"/>
     </row>
-    <row r="10" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>32</v>
       </c>
@@ -2982,7 +3097,7 @@
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
     </row>
-    <row r="11" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>35</v>
       </c>
@@ -3017,7 +3132,7 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
     </row>
-    <row r="12" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>39</v>
       </c>
@@ -3053,7 +3168,7 @@
       <c r="R12" s="3"/>
       <c r="S12" s="3"/>
     </row>
-    <row r="13" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>43</v>
       </c>
@@ -3089,7 +3204,7 @@
       <c r="R13" s="3"/>
       <c r="S13" s="3"/>
     </row>
-    <row r="14" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>47</v>
       </c>
@@ -3126,7 +3241,7 @@
       <c r="R14" s="3"/>
       <c r="S14" s="3"/>
     </row>
-    <row r="15" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
         <v>141</v>
       </c>
@@ -3160,7 +3275,7 @@
       <c r="R15" s="3"/>
       <c r="S15" s="3"/>
     </row>
-    <row r="16" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
         <v>52</v>
       </c>
@@ -3196,7 +3311,7 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
     </row>
-    <row r="17" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>55</v>
       </c>
@@ -3230,7 +3345,7 @@
       <c r="R17" s="3"/>
       <c r="S17" s="3"/>
     </row>
-    <row r="18" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>58</v>
       </c>
@@ -3264,7 +3379,7 @@
       <c r="R18" s="3"/>
       <c r="S18" s="3"/>
     </row>
-    <row r="19" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>61</v>
       </c>
@@ -3297,7 +3412,7 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
     </row>
-    <row r="20" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>64</v>
       </c>
@@ -3330,7 +3445,7 @@
       <c r="R20" s="3"/>
       <c r="S20" s="3"/>
     </row>
-    <row r="21" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>66</v>
       </c>
@@ -3364,7 +3479,7 @@
       <c r="R21" s="3"/>
       <c r="S21" s="3"/>
     </row>
-    <row r="22" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
         <v>68</v>
       </c>
@@ -3397,7 +3512,7 @@
       <c r="R22" s="3"/>
       <c r="S22" s="3"/>
     </row>
-    <row r="23" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>71</v>
       </c>
@@ -3429,7 +3544,7 @@
       <c r="R23" s="3"/>
       <c r="S23" s="3"/>
     </row>
-    <row r="24" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
         <v>73</v>
       </c>
@@ -3463,7 +3578,7 @@
       <c r="R24" s="3"/>
       <c r="S24" s="3"/>
     </row>
-    <row r="25" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>76</v>
       </c>
@@ -3496,7 +3611,7 @@
       <c r="R25" s="3"/>
       <c r="S25" s="3"/>
     </row>
-    <row r="26" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
         <v>79</v>
       </c>
@@ -3529,7 +3644,7 @@
       <c r="R26" s="3"/>
       <c r="S26" s="3"/>
     </row>
-    <row r="27" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>82</v>
       </c>
@@ -3561,7 +3676,7 @@
       <c r="R27" s="3"/>
       <c r="S27" s="3"/>
     </row>
-    <row r="28" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="s">
         <v>85</v>
       </c>
@@ -3594,7 +3709,7 @@
       <c r="R28" s="3"/>
       <c r="S28" s="3"/>
     </row>
-    <row r="29" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
         <v>88</v>
       </c>
@@ -3627,7 +3742,7 @@
       <c r="R29" s="3"/>
       <c r="S29" s="3"/>
     </row>
-    <row r="30" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
         <v>91</v>
       </c>
@@ -3660,7 +3775,7 @@
       <c r="R30" s="3"/>
       <c r="S30" s="3"/>
     </row>
-    <row r="31" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
         <v>93</v>
       </c>
@@ -3693,7 +3808,7 @@
       <c r="R31" s="3"/>
       <c r="S31" s="3"/>
     </row>
-    <row r="32" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
         <v>96</v>
       </c>
@@ -3726,7 +3841,7 @@
       <c r="R32" s="3"/>
       <c r="S32" s="3"/>
     </row>
-    <row r="33" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="s">
         <v>99</v>
       </c>
@@ -3758,7 +3873,7 @@
       <c r="R33" s="3"/>
       <c r="S33" s="3"/>
     </row>
-    <row r="34" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
         <v>101</v>
       </c>
@@ -3791,7 +3906,7 @@
       <c r="R34" s="3"/>
       <c r="S34" s="3"/>
     </row>
-    <row r="35" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="11" t="s">
         <v>104</v>
       </c>
@@ -3822,7 +3937,7 @@
       <c r="R35" s="3"/>
       <c r="S35" s="3"/>
     </row>
-    <row r="36" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="11" t="s">
         <v>107</v>
       </c>
@@ -3853,7 +3968,7 @@
       <c r="R36" s="3"/>
       <c r="S36" s="3"/>
     </row>
-    <row r="37" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="11" t="s">
         <v>110</v>
       </c>
@@ -3884,7 +3999,7 @@
       <c r="R37" s="3"/>
       <c r="S37" s="3"/>
     </row>
-    <row r="38" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="s">
         <v>112</v>
       </c>
@@ -3917,7 +4032,7 @@
       <c r="R38" s="3"/>
       <c r="S38" s="3"/>
     </row>
-    <row r="39" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="11" t="s">
         <v>116</v>
       </c>
@@ -3949,7 +4064,7 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
     </row>
-    <row r="40" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="11" t="s">
         <v>119</v>
       </c>
@@ -3981,7 +4096,7 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
     </row>
-    <row r="41" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="12" t="s">
         <v>142</v>
       </c>
@@ -4014,7 +4129,7 @@
       <c r="R41" s="3"/>
       <c r="S41" s="3"/>
     </row>
-    <row r="42" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="12" t="s">
         <v>180</v>
       </c>
@@ -4044,7 +4159,7 @@
       <c r="R42" s="3"/>
       <c r="S42" s="3"/>
     </row>
-    <row r="43" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="11" t="s">
         <v>125</v>
       </c>
@@ -4075,7 +4190,7 @@
       <c r="R43" s="3"/>
       <c r="S43" s="3"/>
     </row>
-    <row r="44" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="12" t="s">
         <v>127</v>
       </c>
@@ -4106,7 +4221,7 @@
       <c r="R44" s="3"/>
       <c r="S44" s="3"/>
     </row>
-    <row r="45" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="12" t="s">
         <v>189</v>
       </c>
@@ -4137,7 +4252,7 @@
       <c r="R45" s="3"/>
       <c r="S45" s="3"/>
     </row>
-    <row r="46" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="11" t="s">
         <v>130</v>
       </c>
@@ -4170,7 +4285,7 @@
       <c r="R46" s="3"/>
       <c r="S46" s="3"/>
     </row>
-    <row r="47" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="11" t="s">
         <v>133</v>
       </c>
@@ -4203,7 +4318,7 @@
       <c r="R47" s="3"/>
       <c r="S47" s="3"/>
     </row>
-    <row r="48" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="12" t="s">
         <v>158</v>
       </c>
@@ -4236,7 +4351,7 @@
       <c r="R48" s="3"/>
       <c r="S48" s="3"/>
     </row>
-    <row r="49" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="12" t="s">
         <v>157</v>
       </c>
@@ -4265,7 +4380,7 @@
       <c r="R49" s="3"/>
       <c r="S49" s="3"/>
     </row>
-    <row r="50" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="12" t="s">
         <v>164</v>
       </c>
@@ -4299,7 +4414,7 @@
       <c r="R50" s="3"/>
       <c r="S50" s="3"/>
     </row>
-    <row r="51" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="13" t="s">
         <v>139</v>
       </c>
@@ -4332,7 +4447,7 @@
       <c r="R51" s="3"/>
       <c r="S51" s="3"/>
     </row>
-    <row r="52" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="13" t="s">
         <v>186</v>
       </c>
@@ -4364,7 +4479,7 @@
       <c r="R52" s="3"/>
       <c r="S52" s="3"/>
     </row>
-    <row r="53" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="14" t="s">
         <v>143</v>
       </c>
@@ -4395,7 +4510,7 @@
       <c r="R53" s="3"/>
       <c r="S53" s="3"/>
     </row>
-    <row r="54" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="13" t="s">
         <v>147</v>
       </c>
@@ -4426,7 +4541,7 @@
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
     </row>
-    <row r="55" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="13" t="s">
         <v>149</v>
       </c>
@@ -4457,7 +4572,7 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
     </row>
-    <row r="56" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="13" t="s">
         <v>148</v>
       </c>
@@ -4488,7 +4603,7 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
     </row>
-    <row r="57" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="13" t="s">
         <v>151</v>
       </c>
@@ -4519,7 +4634,7 @@
       <c r="R57" s="3"/>
       <c r="S57" s="3"/>
     </row>
-    <row r="58" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="13" t="s">
         <v>160</v>
       </c>
@@ -4550,7 +4665,7 @@
       <c r="R58" s="3"/>
       <c r="S58" s="3"/>
     </row>
-    <row r="59" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="13" t="s">
         <v>155</v>
       </c>
@@ -4581,7 +4696,7 @@
       <c r="R59" s="3"/>
       <c r="S59" s="3"/>
     </row>
-    <row r="60" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="13" t="s">
         <v>159</v>
       </c>
@@ -4612,7 +4727,7 @@
       <c r="R60" s="3"/>
       <c r="S60" s="3"/>
     </row>
-    <row r="61" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="13" t="s">
         <v>161</v>
       </c>
@@ -4643,7 +4758,7 @@
       <c r="R61" s="3"/>
       <c r="S61" s="3"/>
     </row>
-    <row r="62" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="13" t="s">
         <v>162</v>
       </c>
@@ -4672,7 +4787,7 @@
       <c r="R62" s="3"/>
       <c r="S62" s="3"/>
     </row>
-    <row r="63" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="13" t="s">
         <v>163</v>
       </c>
@@ -4701,7 +4816,7 @@
       <c r="R63" s="3"/>
       <c r="S63" s="3"/>
     </row>
-    <row r="64" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="13" t="s">
         <v>165</v>
       </c>
@@ -4731,7 +4846,7 @@
       <c r="R64" s="3"/>
       <c r="S64" s="3"/>
     </row>
-    <row r="65" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="13" t="s">
         <v>181</v>
       </c>
@@ -4762,7 +4877,7 @@
       <c r="R65" s="3"/>
       <c r="S65" s="3"/>
     </row>
-    <row r="66" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="13" t="s">
         <v>182</v>
       </c>
@@ -4793,7 +4908,7 @@
       <c r="R66" s="3"/>
       <c r="S66" s="3"/>
     </row>
-    <row r="67" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="13" t="s">
         <v>166</v>
       </c>
@@ -4822,7 +4937,7 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
     </row>
-    <row r="68" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="13" t="s">
         <v>167</v>
       </c>
@@ -4851,7 +4966,7 @@
       <c r="R68" s="3"/>
       <c r="S68" s="3"/>
     </row>
-    <row r="69" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="13" t="s">
         <v>168</v>
       </c>
@@ -4880,7 +4995,7 @@
       <c r="R69" s="3"/>
       <c r="S69" s="3"/>
     </row>
-    <row r="70" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="13" t="s">
         <v>169</v>
       </c>
@@ -4909,7 +5024,7 @@
       <c r="R70" s="3"/>
       <c r="S70" s="3"/>
     </row>
-    <row r="71" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="13" t="s">
         <v>170</v>
       </c>
@@ -4938,7 +5053,7 @@
       <c r="R71" s="3"/>
       <c r="S71" s="3"/>
     </row>
-    <row r="72" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="13" t="s">
         <v>171</v>
       </c>
@@ -4967,7 +5082,7 @@
       <c r="R72" s="3"/>
       <c r="S72" s="3"/>
     </row>
-    <row r="73" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="13" t="s">
         <v>172</v>
       </c>
@@ -4996,7 +5111,7 @@
       <c r="R73" s="3"/>
       <c r="S73" s="3"/>
     </row>
-    <row r="74" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="13" t="s">
         <v>173</v>
       </c>
@@ -5025,7 +5140,7 @@
       <c r="R74" s="3"/>
       <c r="S74" s="3"/>
     </row>
-    <row r="75" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="13" t="s">
         <v>174</v>
       </c>
@@ -5056,7 +5171,7 @@
       <c r="R75" s="3"/>
       <c r="S75" s="3"/>
     </row>
-    <row r="76" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="13" t="s">
         <v>176</v>
       </c>
@@ -5087,7 +5202,7 @@
       <c r="R76" s="3"/>
       <c r="S76" s="3"/>
     </row>
-    <row r="77" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="13" t="s">
         <v>192</v>
       </c>
@@ -5116,7 +5231,7 @@
       <c r="R77" s="3"/>
       <c r="S77" s="3"/>
     </row>
-    <row r="78" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="14" t="s">
         <v>193</v>
       </c>
@@ -5147,7 +5262,7 @@
       <c r="R78" s="3"/>
       <c r="S78" s="3"/>
     </row>
-    <row r="79" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="14" t="s">
         <v>196</v>
       </c>
@@ -5178,7 +5293,7 @@
       <c r="R79" s="3"/>
       <c r="S79" s="3"/>
     </row>
-    <row r="80" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="14" t="s">
         <v>197</v>
       </c>
@@ -5209,12 +5324,22 @@
       <c r="R80" s="3"/>
       <c r="S80" s="3"/>
     </row>
-    <row r="81" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="14"/>
-      <c r="B81" s="31"/>
-      <c r="C81" s="28"/>
-      <c r="D81" s="3"/>
-      <c r="E81" s="3"/>
+    <row r="81" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="B81" s="31" t="s">
+        <v>204</v>
+      </c>
+      <c r="C81" s="28">
+        <v>-0.08</v>
+      </c>
+      <c r="D81" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3"/>
       <c r="H81" s="3"/>
@@ -5230,11 +5355,19 @@
       <c r="R81" s="3"/>
       <c r="S81" s="3"/>
     </row>
-    <row r="82" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="14"/>
-      <c r="B82" s="31"/>
-      <c r="C82" s="28"/>
-      <c r="D82" s="3"/>
+    <row r="82" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="B82" s="31" t="s">
+        <v>204</v>
+      </c>
+      <c r="C82" s="28">
+        <v>15.8</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>83</v>
+      </c>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
       <c r="G82" s="3"/>
@@ -5251,11 +5384,19 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
     </row>
-    <row r="83" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="14"/>
-      <c r="B83" s="31"/>
-      <c r="C83" s="28"/>
-      <c r="D83" s="3"/>
+    <row r="83" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="B83" s="31" t="s">
+        <v>205</v>
+      </c>
+      <c r="C83" s="28">
+        <v>2</v>
+      </c>
+      <c r="D83" s="9" t="s">
+        <v>194</v>
+      </c>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
       <c r="G83" s="3"/>
@@ -5272,12 +5413,22 @@
       <c r="R83" s="3"/>
       <c r="S83" s="3"/>
     </row>
-    <row r="84" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="14"/>
-      <c r="B84" s="31"/>
-      <c r="C84" s="28"/>
-      <c r="D84" s="3"/>
-      <c r="E84" s="3"/>
+    <row r="84" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="B84" s="31" t="s">
+        <v>205</v>
+      </c>
+      <c r="C84" s="28">
+        <v>1.5</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>215</v>
+      </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3"/>
       <c r="H84" s="3"/>
@@ -5293,12 +5444,22 @@
       <c r="R84" s="3"/>
       <c r="S84" s="3"/>
     </row>
-    <row r="85" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="14"/>
-      <c r="B85" s="31"/>
-      <c r="C85" s="28"/>
-      <c r="D85" s="3"/>
-      <c r="E85" s="3"/>
+    <row r="85" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="B85" s="31" t="s">
+        <v>205</v>
+      </c>
+      <c r="C85" s="28">
+        <v>0.3</v>
+      </c>
+      <c r="D85" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>217</v>
+      </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3"/>
       <c r="H85" s="3"/>
@@ -5314,12 +5475,22 @@
       <c r="R85" s="3"/>
       <c r="S85" s="3"/>
     </row>
-    <row r="86" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="14"/>
-      <c r="B86" s="31"/>
-      <c r="C86" s="28"/>
-      <c r="D86" s="3"/>
-      <c r="E86" s="3"/>
+    <row r="86" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="B86" s="31" t="s">
+        <v>205</v>
+      </c>
+      <c r="C86" s="28">
+        <v>20</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>219</v>
+      </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3"/>
       <c r="H86" s="3"/>
@@ -5335,12 +5506,22 @@
       <c r="R86" s="3"/>
       <c r="S86" s="3"/>
     </row>
-    <row r="87" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="14"/>
-      <c r="B87" s="31"/>
-      <c r="C87" s="28"/>
-      <c r="D87" s="3"/>
-      <c r="E87" s="3"/>
+    <row r="87" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="B87" s="31" t="s">
+        <v>204</v>
+      </c>
+      <c r="C87" s="28">
+        <v>0.2</v>
+      </c>
+      <c r="D87" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>221</v>
+      </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3"/>
       <c r="H87" s="3"/>
@@ -5356,12 +5537,22 @@
       <c r="R87" s="3"/>
       <c r="S87" s="3"/>
     </row>
-    <row r="88" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="14"/>
-      <c r="B88" s="31"/>
-      <c r="C88" s="28"/>
-      <c r="D88" s="3"/>
-      <c r="E88" s="3"/>
+    <row r="88" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="B88" s="32" t="s">
+        <v>204</v>
+      </c>
+      <c r="C88" s="31">
+        <v>120</v>
+      </c>
+      <c r="D88" s="28" t="s">
+        <v>223</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>224</v>
+      </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3"/>
       <c r="H88" s="3"/>
@@ -5377,12 +5568,22 @@
       <c r="R88" s="3"/>
       <c r="S88" s="3"/>
     </row>
-    <row r="89" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="14"/>
-      <c r="B89" s="31"/>
-      <c r="C89" s="28"/>
-      <c r="D89" s="3"/>
-      <c r="E89" s="3"/>
+    <row r="89" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="B89" s="34" t="s">
+        <v>205</v>
+      </c>
+      <c r="C89" s="28">
+        <v>0.25</v>
+      </c>
+      <c r="D89" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="E89" s="6" t="s">
+        <v>226</v>
+      </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3"/>
       <c r="H89" s="3"/>
@@ -5398,12 +5599,22 @@
       <c r="R89" s="3"/>
       <c r="S89" s="3"/>
     </row>
-    <row r="90" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="14"/>
-      <c r="B90" s="31"/>
-      <c r="C90" s="28"/>
-      <c r="D90" s="3"/>
-      <c r="E90" s="3"/>
+    <row r="90" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="B90" s="34" t="s">
+        <v>205</v>
+      </c>
+      <c r="C90" s="28">
+        <v>0.7</v>
+      </c>
+      <c r="D90" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="E90" s="36" t="s">
+        <v>229</v>
+      </c>
       <c r="F90" s="3"/>
       <c r="G90" s="3"/>
       <c r="H90" s="3"/>
@@ -5419,12 +5630,20 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
     </row>
-    <row r="91" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="14"/>
-      <c r="B91" s="31"/>
-      <c r="C91" s="28"/>
-      <c r="D91" s="3"/>
-      <c r="E91" s="3"/>
+    <row r="91" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="B91" s="34" t="s">
+        <v>205</v>
+      </c>
+      <c r="C91" s="28">
+        <v>1</v>
+      </c>
+      <c r="D91" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="E91" s="37"/>
       <c r="F91" s="3"/>
       <c r="G91" s="3"/>
       <c r="H91" s="3"/>
@@ -5440,12 +5659,22 @@
       <c r="R91" s="3"/>
       <c r="S91" s="3"/>
     </row>
-    <row r="92" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="14"/>
-      <c r="B92" s="31"/>
-      <c r="C92" s="28"/>
-      <c r="D92" s="3"/>
-      <c r="E92" s="3"/>
+    <row r="92" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="14" t="s">
+        <v>230</v>
+      </c>
+      <c r="B92" s="31" t="s">
+        <v>205</v>
+      </c>
+      <c r="C92" s="28">
+        <v>15</v>
+      </c>
+      <c r="D92" s="35" t="s">
+        <v>83</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>231</v>
+      </c>
       <c r="F92" s="3"/>
       <c r="G92" s="3"/>
       <c r="H92" s="3"/>
@@ -5461,12 +5690,22 @@
       <c r="R92" s="3"/>
       <c r="S92" s="3"/>
     </row>
-    <row r="93" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="14"/>
-      <c r="B93" s="31"/>
-      <c r="C93" s="28"/>
-      <c r="D93" s="3"/>
-      <c r="E93" s="3"/>
+    <row r="93" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="B93" s="31" t="s">
+        <v>205</v>
+      </c>
+      <c r="C93" s="28">
+        <v>4</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>233</v>
+      </c>
       <c r="F93" s="3"/>
       <c r="G93" s="3"/>
       <c r="H93" s="3"/>
@@ -5482,7 +5721,7 @@
       <c r="R93" s="3"/>
       <c r="S93" s="3"/>
     </row>
-    <row r="94" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="14"/>
       <c r="B94" s="31"/>
       <c r="C94" s="28"/>
@@ -5503,7 +5742,7 @@
       <c r="R94" s="3"/>
       <c r="S94" s="3"/>
     </row>
-    <row r="95" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="14"/>
       <c r="B95" s="31"/>
       <c r="C95" s="28"/>
@@ -5524,7 +5763,7 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
     </row>
-    <row r="96" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="14"/>
       <c r="B96" s="31"/>
       <c r="C96" s="28"/>
@@ -5545,7 +5784,7 @@
       <c r="R96" s="3"/>
       <c r="S96" s="3"/>
     </row>
-    <row r="97" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="14"/>
       <c r="B97" s="31"/>
       <c r="C97" s="28"/>
@@ -5566,7 +5805,7 @@
       <c r="R97" s="3"/>
       <c r="S97" s="3"/>
     </row>
-    <row r="98" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="14"/>
       <c r="B98" s="31"/>
       <c r="C98" s="28"/>
@@ -5587,7 +5826,7 @@
       <c r="R98" s="3"/>
       <c r="S98" s="3"/>
     </row>
-    <row r="99" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="14"/>
       <c r="B99" s="31"/>
       <c r="C99" s="28"/>
@@ -5608,7 +5847,7 @@
       <c r="R99" s="3"/>
       <c r="S99" s="3"/>
     </row>
-    <row r="100" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="14"/>
       <c r="B100" s="31"/>
       <c r="C100" s="28"/>
@@ -5629,7 +5868,7 @@
       <c r="R100" s="3"/>
       <c r="S100" s="3"/>
     </row>
-    <row r="101" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="14"/>
       <c r="B101" s="31"/>
       <c r="C101" s="28"/>
@@ -5650,7 +5889,7 @@
       <c r="R101" s="3"/>
       <c r="S101" s="3"/>
     </row>
-    <row r="102" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="14"/>
       <c r="B102" s="31"/>
       <c r="C102" s="28"/>
@@ -5671,7 +5910,7 @@
       <c r="R102" s="3"/>
       <c r="S102" s="3"/>
     </row>
-    <row r="103" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="14"/>
       <c r="B103" s="31"/>
       <c r="C103" s="28"/>
@@ -5692,7 +5931,7 @@
       <c r="R103" s="3"/>
       <c r="S103" s="3"/>
     </row>
-    <row r="104" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="14"/>
       <c r="B104" s="31"/>
       <c r="C104" s="28"/>
@@ -5713,7 +5952,7 @@
       <c r="R104" s="3"/>
       <c r="S104" s="3"/>
     </row>
-    <row r="105" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="14"/>
       <c r="B105" s="31"/>
       <c r="C105" s="28"/>
@@ -5734,7 +5973,7 @@
       <c r="R105" s="3"/>
       <c r="S105" s="3"/>
     </row>
-    <row r="106" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="14"/>
       <c r="B106" s="31"/>
       <c r="C106" s="28"/>
@@ -5755,7 +5994,7 @@
       <c r="R106" s="3"/>
       <c r="S106" s="3"/>
     </row>
-    <row r="107" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="14"/>
       <c r="B107" s="31"/>
       <c r="C107" s="28"/>
@@ -5776,7 +6015,7 @@
       <c r="R107" s="3"/>
       <c r="S107" s="3"/>
     </row>
-    <row r="108" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="14"/>
       <c r="B108" s="31"/>
       <c r="C108" s="28"/>
@@ -5797,7 +6036,7 @@
       <c r="R108" s="3"/>
       <c r="S108" s="3"/>
     </row>
-    <row r="109" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="14"/>
       <c r="B109" s="31"/>
       <c r="C109" s="28"/>
@@ -5818,7 +6057,7 @@
       <c r="R109" s="3"/>
       <c r="S109" s="3"/>
     </row>
-    <row r="110" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="14"/>
       <c r="B110" s="31"/>
       <c r="C110" s="28"/>
@@ -5839,7 +6078,7 @@
       <c r="R110" s="3"/>
       <c r="S110" s="3"/>
     </row>
-    <row r="111" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="14"/>
       <c r="B111" s="31"/>
       <c r="C111" s="28"/>
@@ -5860,7 +6099,7 @@
       <c r="R111" s="3"/>
       <c r="S111" s="3"/>
     </row>
-    <row r="112" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="14"/>
       <c r="B112" s="31"/>
       <c r="C112" s="28"/>
@@ -5881,7 +6120,7 @@
       <c r="R112" s="3"/>
       <c r="S112" s="3"/>
     </row>
-    <row r="113" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="14"/>
       <c r="B113" s="31"/>
       <c r="C113" s="28"/>
@@ -5902,7 +6141,7 @@
       <c r="R113" s="3"/>
       <c r="S113" s="3"/>
     </row>
-    <row r="114" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="14"/>
       <c r="B114" s="31"/>
       <c r="C114" s="28"/>
@@ -5923,7 +6162,7 @@
       <c r="R114" s="3"/>
       <c r="S114" s="3"/>
     </row>
-    <row r="115" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="14"/>
       <c r="B115" s="31"/>
       <c r="C115" s="28"/>
@@ -5944,7 +6183,7 @@
       <c r="R115" s="3"/>
       <c r="S115" s="3"/>
     </row>
-    <row r="116" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="14"/>
       <c r="B116" s="31"/>
       <c r="C116" s="28"/>
@@ -5965,7 +6204,7 @@
       <c r="R116" s="3"/>
       <c r="S116" s="3"/>
     </row>
-    <row r="117" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="14"/>
       <c r="B117" s="31"/>
       <c r="C117" s="28"/>
@@ -5986,7 +6225,7 @@
       <c r="R117" s="3"/>
       <c r="S117" s="3"/>
     </row>
-    <row r="118" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="14"/>
       <c r="B118" s="31"/>
       <c r="C118" s="28"/>
@@ -6007,7 +6246,7 @@
       <c r="R118" s="3"/>
       <c r="S118" s="3"/>
     </row>
-    <row r="119" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="14"/>
       <c r="B119" s="31"/>
       <c r="C119" s="28"/>
@@ -6028,7 +6267,7 @@
       <c r="R119" s="3"/>
       <c r="S119" s="3"/>
     </row>
-    <row r="120" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="14"/>
       <c r="B120" s="31"/>
       <c r="C120" s="28"/>
@@ -6049,7 +6288,7 @@
       <c r="R120" s="3"/>
       <c r="S120" s="3"/>
     </row>
-    <row r="121" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="14"/>
       <c r="B121" s="31"/>
       <c r="C121" s="28"/>
@@ -6070,7 +6309,7 @@
       <c r="R121" s="3"/>
       <c r="S121" s="3"/>
     </row>
-    <row r="122" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="14"/>
       <c r="B122" s="31"/>
       <c r="C122" s="28"/>
@@ -6091,7 +6330,7 @@
       <c r="R122" s="3"/>
       <c r="S122" s="3"/>
     </row>
-    <row r="123" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="14"/>
       <c r="B123" s="31"/>
       <c r="C123" s="28"/>
@@ -6112,7 +6351,7 @@
       <c r="R123" s="3"/>
       <c r="S123" s="3"/>
     </row>
-    <row r="124" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="14"/>
       <c r="B124" s="31"/>
       <c r="C124" s="28"/>
@@ -6133,7 +6372,7 @@
       <c r="R124" s="3"/>
       <c r="S124" s="3"/>
     </row>
-    <row r="125" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="14"/>
       <c r="B125" s="31"/>
       <c r="C125" s="28"/>
@@ -6154,7 +6393,7 @@
       <c r="R125" s="3"/>
       <c r="S125" s="3"/>
     </row>
-    <row r="126" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="14"/>
       <c r="B126" s="31"/>
       <c r="C126" s="28"/>
@@ -6175,7 +6414,7 @@
       <c r="R126" s="3"/>
       <c r="S126" s="3"/>
     </row>
-    <row r="127" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="14"/>
       <c r="B127" s="31"/>
       <c r="C127" s="28"/>
@@ -6196,7 +6435,7 @@
       <c r="R127" s="3"/>
       <c r="S127" s="3"/>
     </row>
-    <row r="128" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="14"/>
       <c r="B128" s="31"/>
       <c r="C128" s="28"/>
@@ -6217,7 +6456,7 @@
       <c r="R128" s="3"/>
       <c r="S128" s="3"/>
     </row>
-    <row r="129" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="14"/>
       <c r="B129" s="31"/>
       <c r="C129" s="28"/>
@@ -6238,7 +6477,7 @@
       <c r="R129" s="3"/>
       <c r="S129" s="3"/>
     </row>
-    <row r="130" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="14"/>
       <c r="B130" s="31"/>
       <c r="C130" s="28"/>
@@ -6259,7 +6498,7 @@
       <c r="R130" s="3"/>
       <c r="S130" s="3"/>
     </row>
-    <row r="131" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="14"/>
       <c r="B131" s="31"/>
       <c r="C131" s="28"/>
@@ -6280,7 +6519,7 @@
       <c r="R131" s="3"/>
       <c r="S131" s="3"/>
     </row>
-    <row r="132" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="14"/>
       <c r="B132" s="31"/>
       <c r="C132" s="28"/>
@@ -6302,6 +6541,9 @@
       <c r="S132" s="3"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E90:E91"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <headerFooter>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ceaa8977d2236823/Documents/GitHub/451-DBF-Team01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="13_ncr:1_{B8FE2283-5D42-44E7-810A-D88494F7A345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFC54096-9E1B-46ED-AC3C-8C70B6949F5A}"/>
+  <xr:revisionPtr revIDLastSave="680" documentId="13_ncr:1_{B8FE2283-5D42-44E7-810A-D88494F7A345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84498A4A-773D-4D3E-A0D0-B0F5F1A8960B}"/>
   <bookViews>
-    <workbookView xWindow="5136" yWindow="1980" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-14505" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INPUTS" sheetId="1" r:id="rId1"/>
+    <sheet name="Hinge Moments" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -55,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="275">
   <si>
     <t>Parameter</t>
   </si>
@@ -757,6 +758,129 @@
   </si>
   <si>
     <t>Dihedral Initialization</t>
+  </si>
+  <si>
+    <t>PARAMETER</t>
+  </si>
+  <si>
+    <t>AILERON</t>
+  </si>
+  <si>
+    <t>ELEVATOR</t>
+  </si>
+  <si>
+    <t>RUDDER</t>
+  </si>
+  <si>
+    <t>Reference (root) chord, c  (m)</t>
+  </si>
+  <si>
+    <t>Control-surface chord fraction, Ef = cf/c</t>
+  </si>
+  <si>
+    <t>Control-surface chord, cf = Ef*c  (m)</t>
+  </si>
+  <si>
+    <t>Control-surface span, bf  (m)</t>
+  </si>
+  <si>
+    <t>Max deflection, delta_max  (deg)</t>
+  </si>
+  <si>
+    <t>Local AoA assumed for this case, alpha  (deg)</t>
+  </si>
+  <si>
+    <t>Design airspeed for this case, V  (m/s)</t>
+  </si>
+  <si>
+    <t>Air density, rho  (kg/m^3)</t>
+  </si>
+  <si>
+    <t>Extra servo safety margin factor  (x)</t>
+  </si>
+  <si>
+    <t>THIN-AIRFOIL DERIVATION</t>
+  </si>
+  <si>
+    <t>theta_f = ACOS(2*Ef-1)  (rad)</t>
+  </si>
+  <si>
+    <t>X = pi - theta_f</t>
+  </si>
+  <si>
+    <t>Ch_alpha  (floating tendency, per rad)</t>
+  </si>
+  <si>
+    <t>Ch_delta  (restoring tendency, per rad)</t>
+  </si>
+  <si>
+    <t>RESULTING HINGE MOMENT (worst case: alpha &amp; delta_max together)</t>
+  </si>
+  <si>
+    <t>alpha (rad)</t>
+  </si>
+  <si>
+    <t>delta_max (rad)</t>
+  </si>
+  <si>
+    <t>Ch = Ch_alpha*alpha + Ch_delta*delta_max</t>
+  </si>
+  <si>
+    <t>Dynamic pressure, q = 0.5*rho*V^2  (Pa)</t>
+  </si>
+  <si>
+    <t>Control-surface area, Sf = cf*bf  (m^2)</t>
+  </si>
+  <si>
+    <t>Hinge moment, H = Ch*q*Sf*cf  (N*m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ... with safety margin, |H|*margin  (N*m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ... in servo units  (oz-in)</t>
+  </si>
+  <si>
+    <t>COMPARE TO XFLR5 (paste your sweep results here)</t>
+  </si>
+  <si>
+    <t>XFLR5 Ch at same alpha, delta_max</t>
+  </si>
+  <si>
+    <t>Ratio: thin-airfoil / XFLR5</t>
+  </si>
+  <si>
+    <t>Ch_alpha, Ch_delta from closed-form thin-airfoil (Glauert) flap theory, verified</t>
+  </si>
+  <si>
+    <t>against an independent numerical vortex-panel solution to 4 sig. figs.</t>
+  </si>
+  <si>
+    <t>Yellow cells are NOT linked to INPUTS -- check/edit them:</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Elevator delta_max is not in INPUTS; 25 deg placeholder used, please confirm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - alpha assumption per surface defaults to 0 deg (pure control deflection case);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   raise it for combined maneuver cases (e.g. elevator at high AoA).</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - V_design defaults to V_C (cruise); consider a higher design/dive speed if known.</t>
+  </si>
+  <si>
+    <t>Theory is inviscid/2-D and typically over-predicts real hinge moment ~2x --</t>
+  </si>
+  <si>
+    <t>conservative (safe) for servo torque sizing, but state that factor in the report.</t>
+  </si>
+  <si>
+    <t>Control-Surface Hinge Moments - Thin-Airfoil (Glauert) Theory</t>
+  </si>
+  <si>
+    <t>Geometry linked live from the INPUTS sheet. Inviscid 2-D theory typically over-predicts the real hinge moment by ~2x - conservative for servo sizing.</t>
   </si>
 </sst>
 </file>
@@ -769,7 +893,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -788,8 +912,29 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF1F3C78"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF808080"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -800,6 +945,24 @@
       <patternFill patternType="solid">
         <fgColor indexed="9"/>
         <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF784E1F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAEFE2"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -973,7 +1136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -1016,6 +1179,19 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6551,4 +6727,470 @@
   </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1ADFA23C-5193-4068-BEB5-E93369C6617F}">
+  <dimension ref="A1:F30"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="48.109375" customWidth="1"/>
+    <col min="2" max="4" width="15.77734375" customWidth="1"/>
+    <col min="5" max="5" width="3.77734375" customWidth="1"/>
+    <col min="6" max="6" width="46.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+      <c r="A1" s="39" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="40" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="41" t="s">
+        <v>234</v>
+      </c>
+      <c r="B4" s="41" t="s">
+        <v>235</v>
+      </c>
+      <c r="C4" s="41" t="s">
+        <v>236</v>
+      </c>
+      <c r="D4" s="41" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>238</v>
+      </c>
+      <c r="B5" s="42">
+        <f>INPUTS!C42</f>
+        <v>0.31399860863230744</v>
+      </c>
+      <c r="C5" s="42">
+        <f>INPUTS!C48</f>
+        <v>0.19600000000000001</v>
+      </c>
+      <c r="D5" s="42">
+        <f>INPUTS!C62</f>
+        <v>0.16200000000000001</v>
+      </c>
+      <c r="F5" s="40" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>239</v>
+      </c>
+      <c r="B6" s="43">
+        <f>INPUTS!C89</f>
+        <v>0.25</v>
+      </c>
+      <c r="C6" s="43">
+        <f>INPUTS!C46</f>
+        <v>0.3</v>
+      </c>
+      <c r="D6" s="43">
+        <f>INPUTS!C85</f>
+        <v>0.3</v>
+      </c>
+      <c r="F6" s="40" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>240</v>
+      </c>
+      <c r="B7" s="42">
+        <f>B6*B5</f>
+        <v>7.849965215807686E-2</v>
+      </c>
+      <c r="C7" s="42">
+        <f>C6*C5</f>
+        <v>5.8799999999999998E-2</v>
+      </c>
+      <c r="D7" s="42">
+        <f>D6*D5</f>
+        <v>4.8599999999999997E-2</v>
+      </c>
+      <c r="F7" s="40" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>241</v>
+      </c>
+      <c r="B8" s="42">
+        <f>(INPUTS!C91-INPUTS!C90)*INPUTS!C54/2</f>
+        <v>0.22500000000000003</v>
+      </c>
+      <c r="C8" s="42">
+        <f>INPUTS!C49</f>
+        <v>0.53900000000000003</v>
+      </c>
+      <c r="D8" s="42">
+        <f>INPUTS!C63</f>
+        <v>0.24299999999999999</v>
+      </c>
+      <c r="F8" s="40" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>242</v>
+      </c>
+      <c r="B9" s="44">
+        <f>INPUTS!C92</f>
+        <v>15</v>
+      </c>
+      <c r="C9" s="49">
+        <v>20</v>
+      </c>
+      <c r="D9" s="44">
+        <f>INPUTS!C86</f>
+        <v>20</v>
+      </c>
+      <c r="F9" s="40" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>243</v>
+      </c>
+      <c r="B10" s="49">
+        <v>0</v>
+      </c>
+      <c r="C10" s="49">
+        <v>1</v>
+      </c>
+      <c r="D10" s="49">
+        <v>0</v>
+      </c>
+      <c r="F10" s="40" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>244</v>
+      </c>
+      <c r="B11" s="47">
+        <f>INPUTS!C22</f>
+        <v>23</v>
+      </c>
+      <c r="C11" s="47">
+        <f>INPUTS!C22</f>
+        <v>23</v>
+      </c>
+      <c r="D11" s="47">
+        <f>INPUTS!C22</f>
+        <v>23</v>
+      </c>
+      <c r="F11" s="40" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>245</v>
+      </c>
+      <c r="B12" s="42">
+        <f>INPUTS!C2</f>
+        <v>1.2250000000000001</v>
+      </c>
+      <c r="C12" s="42">
+        <f>INPUTS!C2</f>
+        <v>1.2250000000000001</v>
+      </c>
+      <c r="D12" s="42">
+        <f>INPUTS!C2</f>
+        <v>1.2250000000000001</v>
+      </c>
+      <c r="F12" s="40" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>246</v>
+      </c>
+      <c r="B13" s="49">
+        <v>1</v>
+      </c>
+      <c r="C13" s="49">
+        <v>1</v>
+      </c>
+      <c r="D13" s="49">
+        <v>1</v>
+      </c>
+      <c r="F13" s="40" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="41" t="s">
+        <v>247</v>
+      </c>
+      <c r="B14" s="41"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="41"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>248</v>
+      </c>
+      <c r="B15" s="43">
+        <f>ACOS(2*B6-1)</f>
+        <v>2.0943951023931957</v>
+      </c>
+      <c r="C15" s="43">
+        <f>ACOS(2*C6-1)</f>
+        <v>1.9823131728623846</v>
+      </c>
+      <c r="D15" s="43">
+        <f>ACOS(2*D6-1)</f>
+        <v>1.9823131728623846</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>249</v>
+      </c>
+      <c r="B16" s="43">
+        <f>PI()-B15</f>
+        <v>1.0471975511965974</v>
+      </c>
+      <c r="C16" s="43">
+        <f>PI()-C15</f>
+        <v>1.1592794807274085</v>
+      </c>
+      <c r="D16" s="43">
+        <f>PI()-D15</f>
+        <v>1.1592794807274085</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>250</v>
+      </c>
+      <c r="B17" s="48">
+        <f>-(B16*(COS(B15)-0.5)+SIN(B15)*(1-COS(B15)/2))/B6^2</f>
+        <v>-0.56534725654320894</v>
+      </c>
+      <c r="C17" s="48">
+        <f>-(C16*(COS(C15)-0.5)+SIN(C15)*(1-COS(C15)/2))/C6^2</f>
+        <v>-0.62740704594148844</v>
+      </c>
+      <c r="D17" s="48">
+        <f>-(D16*(COS(D15)-0.5)+SIN(D15)*(1-COS(D15)/2))/D6^2</f>
+        <v>-0.62740704594148844</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>251</v>
+      </c>
+      <c r="B18" s="48">
+        <f>-(B16^2*(COS(B15)-0.5)+B16*SIN(B15)+SIN(B15)^2/2)/(PI()*B6^2)</f>
+        <v>-0.94360786423789478</v>
+      </c>
+      <c r="C18" s="48">
+        <f>-(C16^2*(COS(C15)-0.5)+C16*SIN(C15)+SIN(C15)^2/2)/(PI()*C6^2)</f>
+        <v>-0.96540266006846076</v>
+      </c>
+      <c r="D18" s="48">
+        <f>-(D16^2*(COS(D15)-0.5)+D16*SIN(D15)+SIN(D15)^2/2)/(PI()*D6^2)</f>
+        <v>-0.96540266006846076</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="41" t="s">
+        <v>252</v>
+      </c>
+      <c r="B19" s="41"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="41"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>253</v>
+      </c>
+      <c r="B20" s="43">
+        <f>RADIANS(B10)</f>
+        <v>0</v>
+      </c>
+      <c r="C20" s="43">
+        <f>RADIANS(C10)</f>
+        <v>1.7453292519943295E-2</v>
+      </c>
+      <c r="D20" s="43">
+        <f>RADIANS(D10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>254</v>
+      </c>
+      <c r="B21" s="43">
+        <f>RADIANS(B9)</f>
+        <v>0.26179938779914941</v>
+      </c>
+      <c r="C21" s="43">
+        <f>RADIANS(C9)</f>
+        <v>0.3490658503988659</v>
+      </c>
+      <c r="D21" s="43">
+        <f>RADIANS(D9)</f>
+        <v>0.3490658503988659</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>255</v>
+      </c>
+      <c r="B22" s="48">
+        <f>B17*B20+B18*B21</f>
+        <v>-0.24703596117994375</v>
+      </c>
+      <c r="C22" s="48">
+        <f>C17*C20+C18*C21</f>
+        <v>-0.34793941921601479</v>
+      </c>
+      <c r="D22" s="48">
+        <f>D17*D20+D18*D21</f>
+        <v>-0.33698910051412451</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>256</v>
+      </c>
+      <c r="B23" s="42">
+        <f>0.5*B12*B11^2</f>
+        <v>324.01250000000005</v>
+      </c>
+      <c r="C23" s="42">
+        <f>0.5*C12*C11^2</f>
+        <v>324.01250000000005</v>
+      </c>
+      <c r="D23" s="42">
+        <f>0.5*D12*D11^2</f>
+        <v>324.01250000000005</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>257</v>
+      </c>
+      <c r="B24" s="42">
+        <f>B7*B8</f>
+        <v>1.7662421735567296E-2</v>
+      </c>
+      <c r="C24" s="42">
+        <f>C7*C8</f>
+        <v>3.1693199999999998E-2</v>
+      </c>
+      <c r="D24" s="42">
+        <f>D7*D8</f>
+        <v>1.1809799999999999E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="38" t="s">
+        <v>258</v>
+      </c>
+      <c r="B25" s="50">
+        <f>B22*B23*B24*B7</f>
+        <v>-0.11097877488188827</v>
+      </c>
+      <c r="C25" s="50">
+        <f>C22*C23*C24*C7</f>
+        <v>-0.21009166195271597</v>
+      </c>
+      <c r="D25" s="50">
+        <f>D22*D23*D24*D7</f>
+        <v>-6.2669529124880732E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>259</v>
+      </c>
+      <c r="B26" s="43">
+        <f>ABS(B25)*B13</f>
+        <v>0.11097877488188827</v>
+      </c>
+      <c r="C26" s="43">
+        <f>ABS(C25)*C13</f>
+        <v>0.21009166195271597</v>
+      </c>
+      <c r="D26" s="43">
+        <f>ABS(D25)*D13</f>
+        <v>6.2669529124880732E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="38" t="s">
+        <v>260</v>
+      </c>
+      <c r="B27" s="45">
+        <f>B26*141.612</f>
+        <v>15.715926268573961</v>
+      </c>
+      <c r="C27" s="45">
+        <f>C26*141.612</f>
+        <v>29.751500432448015</v>
+      </c>
+      <c r="D27" s="45">
+        <f>D26*141.612</f>
+        <v>8.8747573584326105</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="41" t="s">
+        <v>261</v>
+      </c>
+      <c r="B28" s="41"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="41"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>262</v>
+      </c>
+      <c r="B29" s="46"/>
+      <c r="C29" s="46"/>
+      <c r="D29" s="46"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>263</v>
+      </c>
+      <c r="B30" s="43" t="str">
+        <f>IF(B29="","",B22/B29)</f>
+        <v/>
+      </c>
+      <c r="C30" s="43" t="str">
+        <f>IF(C29="","",C22/C29)</f>
+        <v/>
+      </c>
+      <c r="D30" s="43" t="str">
+        <f>IF(D29="","",D22/D29)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ceaa8977d2236823/Documents/GitHub/451-DBF-Team01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="680" documentId="13_ncr:1_{B8FE2283-5D42-44E7-810A-D88494F7A345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84498A4A-773D-4D3E-A0D0-B0F5F1A8960B}"/>
+  <xr:revisionPtr revIDLastSave="817" documentId="13_ncr:1_{B8FE2283-5D42-44E7-810A-D88494F7A345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{525D52DE-856C-46D2-9A63-82D2CBB510BE}"/>
   <bookViews>
-    <workbookView xWindow="-14505" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INPUTS" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="276">
   <si>
     <t>Parameter</t>
   </si>
@@ -881,6 +881,9 @@
   </si>
   <si>
     <t>Geometry linked live from the INPUTS sheet. Inviscid 2-D theory typically over-predicts the real hinge moment by ~2x - conservative for servo sizing.</t>
+  </si>
+  <si>
+    <t>Vertical Stabilizer Chord</t>
   </si>
 </sst>
 </file>
@@ -1173,12 +1176,6 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1192,6 +1189,12 @@
     <xf numFmtId="167" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="166" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="167" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4942,12 +4945,14 @@
         <v>205</v>
       </c>
       <c r="C62" s="28">
-        <v>0.16200000000000001</v>
+        <v>0.19600000000000001</v>
       </c>
       <c r="D62" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="E62" s="3"/>
+      <c r="E62" s="3" t="s">
+        <v>275</v>
+      </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3"/>
       <c r="H62" s="3"/>
@@ -5001,7 +5006,7 @@
       </c>
       <c r="C64" s="27">
         <f>C63/C62</f>
-        <v>1.5</v>
+        <v>1.2397959183673468</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>18</v>
@@ -5597,7 +5602,7 @@
         <v>205</v>
       </c>
       <c r="C84" s="28">
-        <v>1.5</v>
+        <v>1.07</v>
       </c>
       <c r="D84" s="9" t="s">
         <v>194</v>
@@ -5788,7 +5793,7 @@
       <c r="D90" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="E90" s="36" t="s">
+      <c r="E90" s="49" t="s">
         <v>229</v>
       </c>
       <c r="F90" s="3"/>
@@ -5819,7 +5824,7 @@
       <c r="D91" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="E91" s="37"/>
+      <c r="E91" s="50"/>
       <c r="F91" s="3"/>
       <c r="G91" s="3"/>
       <c r="H91" s="3"/>
@@ -6741,26 +6746,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="37" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="38" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="39" t="s">
         <v>234</v>
       </c>
-      <c r="B4" s="41" t="s">
+      <c r="B4" s="39" t="s">
         <v>235</v>
       </c>
-      <c r="C4" s="41" t="s">
+      <c r="C4" s="39" t="s">
         <v>236</v>
       </c>
-      <c r="D4" s="41" t="s">
+      <c r="D4" s="39" t="s">
         <v>237</v>
       </c>
     </row>
@@ -6768,19 +6773,19 @@
       <c r="A5" t="s">
         <v>238</v>
       </c>
-      <c r="B5" s="42">
+      <c r="B5" s="40">
         <f>INPUTS!C42</f>
         <v>0.31399860863230744</v>
       </c>
-      <c r="C5" s="42">
+      <c r="C5" s="40">
         <f>INPUTS!C48</f>
         <v>0.19600000000000001</v>
       </c>
-      <c r="D5" s="42">
+      <c r="D5" s="40">
         <f>INPUTS!C62</f>
-        <v>0.16200000000000001</v>
-      </c>
-      <c r="F5" s="40" t="s">
+        <v>0.19600000000000001</v>
+      </c>
+      <c r="F5" s="38" t="s">
         <v>264</v>
       </c>
     </row>
@@ -6788,19 +6793,19 @@
       <c r="A6" t="s">
         <v>239</v>
       </c>
-      <c r="B6" s="43">
+      <c r="B6" s="41">
         <f>INPUTS!C89</f>
         <v>0.25</v>
       </c>
-      <c r="C6" s="43">
+      <c r="C6" s="41">
         <f>INPUTS!C46</f>
         <v>0.3</v>
       </c>
-      <c r="D6" s="43">
+      <c r="D6" s="41">
         <f>INPUTS!C85</f>
         <v>0.3</v>
       </c>
-      <c r="F6" s="40" t="s">
+      <c r="F6" s="38" t="s">
         <v>265</v>
       </c>
     </row>
@@ -6808,19 +6813,19 @@
       <c r="A7" t="s">
         <v>240</v>
       </c>
-      <c r="B7" s="42">
+      <c r="B7" s="40">
         <f>B6*B5</f>
         <v>7.849965215807686E-2</v>
       </c>
-      <c r="C7" s="42">
+      <c r="C7" s="40">
         <f>C6*C5</f>
         <v>5.8799999999999998E-2</v>
       </c>
-      <c r="D7" s="42">
+      <c r="D7" s="40">
         <f>D6*D5</f>
-        <v>4.8599999999999997E-2</v>
-      </c>
-      <c r="F7" s="40" t="s">
+        <v>5.8799999999999998E-2</v>
+      </c>
+      <c r="F7" s="38" t="s">
         <v>266</v>
       </c>
     </row>
@@ -6828,19 +6833,19 @@
       <c r="A8" t="s">
         <v>241</v>
       </c>
-      <c r="B8" s="42">
+      <c r="B8" s="40">
         <f>(INPUTS!C91-INPUTS!C90)*INPUTS!C54/2</f>
         <v>0.22500000000000003</v>
       </c>
-      <c r="C8" s="42">
+      <c r="C8" s="40">
         <f>INPUTS!C49</f>
         <v>0.53900000000000003</v>
       </c>
-      <c r="D8" s="42">
+      <c r="D8" s="40">
         <f>INPUTS!C63</f>
         <v>0.24299999999999999</v>
       </c>
-      <c r="F8" s="40" t="s">
+      <c r="F8" s="38" t="s">
         <v>267</v>
       </c>
     </row>
@@ -6848,18 +6853,18 @@
       <c r="A9" t="s">
         <v>242</v>
       </c>
-      <c r="B9" s="44">
+      <c r="B9" s="42">
         <f>INPUTS!C92</f>
         <v>15</v>
       </c>
-      <c r="C9" s="49">
+      <c r="C9" s="47">
         <v>20</v>
       </c>
-      <c r="D9" s="44">
+      <c r="D9" s="42">
         <f>INPUTS!C86</f>
         <v>20</v>
       </c>
-      <c r="F9" s="40" t="s">
+      <c r="F9" s="38" t="s">
         <v>268</v>
       </c>
     </row>
@@ -6867,16 +6872,16 @@
       <c r="A10" t="s">
         <v>243</v>
       </c>
-      <c r="B10" s="49">
+      <c r="B10" s="47">
         <v>0</v>
       </c>
-      <c r="C10" s="49">
+      <c r="C10" s="47">
         <v>1</v>
       </c>
-      <c r="D10" s="49">
+      <c r="D10" s="47">
         <v>0</v>
       </c>
-      <c r="F10" s="40" t="s">
+      <c r="F10" s="38" t="s">
         <v>269</v>
       </c>
     </row>
@@ -6884,19 +6889,19 @@
       <c r="A11" t="s">
         <v>244</v>
       </c>
-      <c r="B11" s="47">
+      <c r="B11" s="45">
         <f>INPUTS!C22</f>
         <v>23</v>
       </c>
-      <c r="C11" s="47">
+      <c r="C11" s="45">
         <f>INPUTS!C22</f>
         <v>23</v>
       </c>
-      <c r="D11" s="47">
+      <c r="D11" s="45">
         <f>INPUTS!C22</f>
         <v>23</v>
       </c>
-      <c r="F11" s="40" t="s">
+      <c r="F11" s="38" t="s">
         <v>270</v>
       </c>
     </row>
@@ -6904,19 +6909,19 @@
       <c r="A12" t="s">
         <v>245</v>
       </c>
-      <c r="B12" s="42">
+      <c r="B12" s="40">
         <f>INPUTS!C2</f>
         <v>1.2250000000000001</v>
       </c>
-      <c r="C12" s="42">
+      <c r="C12" s="40">
         <f>INPUTS!C2</f>
         <v>1.2250000000000001</v>
       </c>
-      <c r="D12" s="42">
+      <c r="D12" s="40">
         <f>INPUTS!C2</f>
         <v>1.2250000000000001</v>
       </c>
-      <c r="F12" s="40" t="s">
+      <c r="F12" s="38" t="s">
         <v>271</v>
       </c>
     </row>
@@ -6924,40 +6929,40 @@
       <c r="A13" t="s">
         <v>246</v>
       </c>
-      <c r="B13" s="49">
+      <c r="B13" s="47">
         <v>1</v>
       </c>
-      <c r="C13" s="49">
+      <c r="C13" s="47">
         <v>1</v>
       </c>
-      <c r="D13" s="49">
+      <c r="D13" s="47">
         <v>1</v>
       </c>
-      <c r="F13" s="40" t="s">
+      <c r="F13" s="38" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="41" t="s">
+      <c r="A14" s="39" t="s">
         <v>247</v>
       </c>
-      <c r="B14" s="41"/>
-      <c r="C14" s="41"/>
-      <c r="D14" s="41"/>
+      <c r="B14" s="39"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>248</v>
       </c>
-      <c r="B15" s="43">
+      <c r="B15" s="41">
         <f>ACOS(2*B6-1)</f>
         <v>2.0943951023931957</v>
       </c>
-      <c r="C15" s="43">
+      <c r="C15" s="41">
         <f>ACOS(2*C6-1)</f>
         <v>1.9823131728623846</v>
       </c>
-      <c r="D15" s="43">
+      <c r="D15" s="41">
         <f>ACOS(2*D6-1)</f>
         <v>1.9823131728623846</v>
       </c>
@@ -6966,15 +6971,15 @@
       <c r="A16" t="s">
         <v>249</v>
       </c>
-      <c r="B16" s="43">
+      <c r="B16" s="41">
         <f>PI()-B15</f>
         <v>1.0471975511965974</v>
       </c>
-      <c r="C16" s="43">
+      <c r="C16" s="41">
         <f>PI()-C15</f>
         <v>1.1592794807274085</v>
       </c>
-      <c r="D16" s="43">
+      <c r="D16" s="41">
         <f>PI()-D15</f>
         <v>1.1592794807274085</v>
       </c>
@@ -6983,15 +6988,15 @@
       <c r="A17" t="s">
         <v>250</v>
       </c>
-      <c r="B17" s="48">
+      <c r="B17" s="46">
         <f>-(B16*(COS(B15)-0.5)+SIN(B15)*(1-COS(B15)/2))/B6^2</f>
         <v>-0.56534725654320894</v>
       </c>
-      <c r="C17" s="48">
+      <c r="C17" s="46">
         <f>-(C16*(COS(C15)-0.5)+SIN(C15)*(1-COS(C15)/2))/C6^2</f>
         <v>-0.62740704594148844</v>
       </c>
-      <c r="D17" s="48">
+      <c r="D17" s="46">
         <f>-(D16*(COS(D15)-0.5)+SIN(D15)*(1-COS(D15)/2))/D6^2</f>
         <v>-0.62740704594148844</v>
       </c>
@@ -7000,40 +7005,40 @@
       <c r="A18" t="s">
         <v>251</v>
       </c>
-      <c r="B18" s="48">
+      <c r="B18" s="46">
         <f>-(B16^2*(COS(B15)-0.5)+B16*SIN(B15)+SIN(B15)^2/2)/(PI()*B6^2)</f>
         <v>-0.94360786423789478</v>
       </c>
-      <c r="C18" s="48">
+      <c r="C18" s="46">
         <f>-(C16^2*(COS(C15)-0.5)+C16*SIN(C15)+SIN(C15)^2/2)/(PI()*C6^2)</f>
         <v>-0.96540266006846076</v>
       </c>
-      <c r="D18" s="48">
+      <c r="D18" s="46">
         <f>-(D16^2*(COS(D15)-0.5)+D16*SIN(D15)+SIN(D15)^2/2)/(PI()*D6^2)</f>
         <v>-0.96540266006846076</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="41" t="s">
+      <c r="A19" s="39" t="s">
         <v>252</v>
       </c>
-      <c r="B19" s="41"/>
-      <c r="C19" s="41"/>
-      <c r="D19" s="41"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>253</v>
       </c>
-      <c r="B20" s="43">
+      <c r="B20" s="41">
         <f>RADIANS(B10)</f>
         <v>0</v>
       </c>
-      <c r="C20" s="43">
+      <c r="C20" s="41">
         <f>RADIANS(C10)</f>
         <v>1.7453292519943295E-2</v>
       </c>
-      <c r="D20" s="43">
+      <c r="D20" s="41">
         <f>RADIANS(D10)</f>
         <v>0</v>
       </c>
@@ -7042,15 +7047,15 @@
       <c r="A21" t="s">
         <v>254</v>
       </c>
-      <c r="B21" s="43">
+      <c r="B21" s="41">
         <f>RADIANS(B9)</f>
         <v>0.26179938779914941</v>
       </c>
-      <c r="C21" s="43">
+      <c r="C21" s="41">
         <f>RADIANS(C9)</f>
         <v>0.3490658503988659</v>
       </c>
-      <c r="D21" s="43">
+      <c r="D21" s="41">
         <f>RADIANS(D9)</f>
         <v>0.3490658503988659</v>
       </c>
@@ -7059,15 +7064,15 @@
       <c r="A22" t="s">
         <v>255</v>
       </c>
-      <c r="B22" s="48">
+      <c r="B22" s="46">
         <f>B17*B20+B18*B21</f>
         <v>-0.24703596117994375</v>
       </c>
-      <c r="C22" s="48">
+      <c r="C22" s="46">
         <f>C17*C20+C18*C21</f>
         <v>-0.34793941921601479</v>
       </c>
-      <c r="D22" s="48">
+      <c r="D22" s="46">
         <f>D17*D20+D18*D21</f>
         <v>-0.33698910051412451</v>
       </c>
@@ -7076,15 +7081,15 @@
       <c r="A23" t="s">
         <v>256</v>
       </c>
-      <c r="B23" s="42">
+      <c r="B23" s="40">
         <f>0.5*B12*B11^2</f>
         <v>324.01250000000005</v>
       </c>
-      <c r="C23" s="42">
+      <c r="C23" s="40">
         <f>0.5*C12*C11^2</f>
         <v>324.01250000000005</v>
       </c>
-      <c r="D23" s="42">
+      <c r="D23" s="40">
         <f>0.5*D12*D11^2</f>
         <v>324.01250000000005</v>
       </c>
@@ -7093,99 +7098,99 @@
       <c r="A24" t="s">
         <v>257</v>
       </c>
-      <c r="B24" s="42">
+      <c r="B24" s="40">
         <f>B7*B8</f>
         <v>1.7662421735567296E-2</v>
       </c>
-      <c r="C24" s="42">
+      <c r="C24" s="40">
         <f>C7*C8</f>
         <v>3.1693199999999998E-2</v>
       </c>
-      <c r="D24" s="42">
+      <c r="D24" s="40">
         <f>D7*D8</f>
-        <v>1.1809799999999999E-2</v>
+        <v>1.42884E-2</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="38" t="s">
+      <c r="A25" s="36" t="s">
         <v>258</v>
       </c>
-      <c r="B25" s="50">
+      <c r="B25" s="48">
         <f>B22*B23*B24*B7</f>
         <v>-0.11097877488188827</v>
       </c>
-      <c r="C25" s="50">
+      <c r="C25" s="48">
         <f>C22*C23*C24*C7</f>
         <v>-0.21009166195271597</v>
       </c>
-      <c r="D25" s="50">
+      <c r="D25" s="48">
         <f>D22*D23*D24*D7</f>
-        <v>-6.2669529124880732E-2</v>
+        <v>-9.1735735057972057E-2</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>259</v>
       </c>
-      <c r="B26" s="43">
+      <c r="B26" s="41">
         <f>ABS(B25)*B13</f>
         <v>0.11097877488188827</v>
       </c>
-      <c r="C26" s="43">
+      <c r="C26" s="41">
         <f>ABS(C25)*C13</f>
         <v>0.21009166195271597</v>
       </c>
-      <c r="D26" s="43">
+      <c r="D26" s="41">
         <f>ABS(D25)*D13</f>
-        <v>6.2669529124880732E-2</v>
+        <v>9.1735735057972057E-2</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="38" t="s">
+      <c r="A27" s="36" t="s">
         <v>260</v>
       </c>
-      <c r="B27" s="45">
+      <c r="B27" s="43">
         <f>B26*141.612</f>
         <v>15.715926268573961</v>
       </c>
-      <c r="C27" s="45">
+      <c r="C27" s="43">
         <f>C26*141.612</f>
         <v>29.751500432448015</v>
       </c>
-      <c r="D27" s="45">
+      <c r="D27" s="43">
         <f>D26*141.612</f>
-        <v>8.8747573584326105</v>
+        <v>12.990880913029539</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="41" t="s">
+      <c r="A28" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="B28" s="41"/>
-      <c r="C28" s="41"/>
-      <c r="D28" s="41"/>
+      <c r="B28" s="39"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="39"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>262</v>
       </c>
-      <c r="B29" s="46"/>
-      <c r="C29" s="46"/>
-      <c r="D29" s="46"/>
+      <c r="B29" s="44"/>
+      <c r="C29" s="44"/>
+      <c r="D29" s="44"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>263</v>
       </c>
-      <c r="B30" s="43" t="str">
+      <c r="B30" s="41" t="str">
         <f>IF(B29="","",B22/B29)</f>
         <v/>
       </c>
-      <c r="C30" s="43" t="str">
+      <c r="C30" s="41" t="str">
         <f>IF(C29="","",C22/C29)</f>
         <v/>
       </c>
-      <c r="D30" s="43" t="str">
+      <c r="D30" s="41" t="str">
         <f>IF(D29="","",D22/D29)</f>
         <v/>
       </c>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ceaa8977d2236823/Documents/GitHub/451-DBF-Team01/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hudson/Documents/GitHub/451-DBF-Team01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="817" documentId="13_ncr:1_{B8FE2283-5D42-44E7-810A-D88494F7A345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{525D52DE-856C-46D2-9A63-82D2CBB510BE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BBFBC34-ECD8-FA4D-9907-981460FE349E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="23260" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INPUTS" sheetId="1" r:id="rId1"/>
@@ -2914,13 +2914,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S132"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.85" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.44140625" style="32" customWidth="1"/>
-    <col min="3" max="3" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5" style="32" customWidth="1"/>
+    <col min="3" max="3" width="9.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="34.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="25.6640625" style="1" customWidth="1"/>
     <col min="8" max="8" width="40.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -2928,7 +2928,7 @@
     <col min="21" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -2965,7 +2965,7 @@
       <c r="R1" s="3"/>
       <c r="S1" s="3"/>
     </row>
-    <row r="2" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="11" t="s">
         <v>5</v>
       </c>
@@ -3000,7 +3000,7 @@
       <c r="R2" s="3"/>
       <c r="S2" s="3"/>
     </row>
-    <row r="3" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
         <v>10</v>
       </c>
@@ -3033,7 +3033,7 @@
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
     </row>
-    <row r="4" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="11" t="s">
         <v>14</v>
       </c>
@@ -3066,7 +3066,7 @@
       <c r="R4" s="3"/>
       <c r="S4" s="3"/>
     </row>
-    <row r="5" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="11" t="s">
         <v>17</v>
       </c>
@@ -3101,7 +3101,7 @@
       <c r="R5" s="3"/>
       <c r="S5" s="3"/>
     </row>
-    <row r="6" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
         <v>22</v>
       </c>
@@ -3136,7 +3136,7 @@
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
     </row>
-    <row r="7" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
         <v>178</v>
       </c>
@@ -3170,7 +3170,7 @@
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
     </row>
-    <row r="8" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
         <v>26</v>
       </c>
@@ -3206,7 +3206,7 @@
       <c r="R8" s="3"/>
       <c r="S8" s="3"/>
     </row>
-    <row r="9" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
         <v>183</v>
       </c>
@@ -3240,7 +3240,7 @@
       <c r="R9" s="3"/>
       <c r="S9" s="3"/>
     </row>
-    <row r="10" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
         <v>32</v>
       </c>
@@ -3276,7 +3276,7 @@
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
     </row>
-    <row r="11" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
         <v>35</v>
       </c>
@@ -3311,7 +3311,7 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
     </row>
-    <row r="12" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
         <v>39</v>
       </c>
@@ -3347,7 +3347,7 @@
       <c r="R12" s="3"/>
       <c r="S12" s="3"/>
     </row>
-    <row r="13" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
         <v>43</v>
       </c>
@@ -3383,7 +3383,7 @@
       <c r="R13" s="3"/>
       <c r="S13" s="3"/>
     </row>
-    <row r="14" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
         <v>47</v>
       </c>
@@ -3420,7 +3420,7 @@
       <c r="R14" s="3"/>
       <c r="S14" s="3"/>
     </row>
-    <row r="15" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>141</v>
       </c>
@@ -3454,7 +3454,7 @@
       <c r="R15" s="3"/>
       <c r="S15" s="3"/>
     </row>
-    <row r="16" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
         <v>52</v>
       </c>
@@ -3490,7 +3490,7 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
     </row>
-    <row r="17" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="11" t="s">
         <v>55</v>
       </c>
@@ -3524,7 +3524,7 @@
       <c r="R17" s="3"/>
       <c r="S17" s="3"/>
     </row>
-    <row r="18" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="11" t="s">
         <v>58</v>
       </c>
@@ -3558,7 +3558,7 @@
       <c r="R18" s="3"/>
       <c r="S18" s="3"/>
     </row>
-    <row r="19" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="11" t="s">
         <v>61</v>
       </c>
@@ -3591,7 +3591,7 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
     </row>
-    <row r="20" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="11" t="s">
         <v>64</v>
       </c>
@@ -3624,7 +3624,7 @@
       <c r="R20" s="3"/>
       <c r="S20" s="3"/>
     </row>
-    <row r="21" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
         <v>66</v>
       </c>
@@ -3658,7 +3658,7 @@
       <c r="R21" s="3"/>
       <c r="S21" s="3"/>
     </row>
-    <row r="22" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="11" t="s">
         <v>68</v>
       </c>
@@ -3691,7 +3691,7 @@
       <c r="R22" s="3"/>
       <c r="S22" s="3"/>
     </row>
-    <row r="23" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="11" t="s">
         <v>71</v>
       </c>
@@ -3723,7 +3723,7 @@
       <c r="R23" s="3"/>
       <c r="S23" s="3"/>
     </row>
-    <row r="24" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="11" t="s">
         <v>73</v>
       </c>
@@ -3757,7 +3757,7 @@
       <c r="R24" s="3"/>
       <c r="S24" s="3"/>
     </row>
-    <row r="25" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="11" t="s">
         <v>76</v>
       </c>
@@ -3790,7 +3790,7 @@
       <c r="R25" s="3"/>
       <c r="S25" s="3"/>
     </row>
-    <row r="26" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="11" t="s">
         <v>79</v>
       </c>
@@ -3823,7 +3823,7 @@
       <c r="R26" s="3"/>
       <c r="S26" s="3"/>
     </row>
-    <row r="27" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="11" t="s">
         <v>82</v>
       </c>
@@ -3855,7 +3855,7 @@
       <c r="R27" s="3"/>
       <c r="S27" s="3"/>
     </row>
-    <row r="28" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="11" t="s">
         <v>85</v>
       </c>
@@ -3888,7 +3888,7 @@
       <c r="R28" s="3"/>
       <c r="S28" s="3"/>
     </row>
-    <row r="29" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="11" t="s">
         <v>88</v>
       </c>
@@ -3921,7 +3921,7 @@
       <c r="R29" s="3"/>
       <c r="S29" s="3"/>
     </row>
-    <row r="30" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="11" t="s">
         <v>91</v>
       </c>
@@ -3954,7 +3954,7 @@
       <c r="R30" s="3"/>
       <c r="S30" s="3"/>
     </row>
-    <row r="31" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="11" t="s">
         <v>93</v>
       </c>
@@ -3987,7 +3987,7 @@
       <c r="R31" s="3"/>
       <c r="S31" s="3"/>
     </row>
-    <row r="32" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="11" t="s">
         <v>96</v>
       </c>
@@ -4020,7 +4020,7 @@
       <c r="R32" s="3"/>
       <c r="S32" s="3"/>
     </row>
-    <row r="33" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="11" t="s">
         <v>99</v>
       </c>
@@ -4052,7 +4052,7 @@
       <c r="R33" s="3"/>
       <c r="S33" s="3"/>
     </row>
-    <row r="34" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="11" t="s">
         <v>101</v>
       </c>
@@ -4085,7 +4085,7 @@
       <c r="R34" s="3"/>
       <c r="S34" s="3"/>
     </row>
-    <row r="35" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="11" t="s">
         <v>104</v>
       </c>
@@ -4116,7 +4116,7 @@
       <c r="R35" s="3"/>
       <c r="S35" s="3"/>
     </row>
-    <row r="36" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="11" t="s">
         <v>107</v>
       </c>
@@ -4147,7 +4147,7 @@
       <c r="R36" s="3"/>
       <c r="S36" s="3"/>
     </row>
-    <row r="37" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="11" t="s">
         <v>110</v>
       </c>
@@ -4178,7 +4178,7 @@
       <c r="R37" s="3"/>
       <c r="S37" s="3"/>
     </row>
-    <row r="38" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="11" t="s">
         <v>112</v>
       </c>
@@ -4211,7 +4211,7 @@
       <c r="R38" s="3"/>
       <c r="S38" s="3"/>
     </row>
-    <row r="39" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="11" t="s">
         <v>116</v>
       </c>
@@ -4243,7 +4243,7 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
     </row>
-    <row r="40" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="11" t="s">
         <v>119</v>
       </c>
@@ -4275,7 +4275,7 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
     </row>
-    <row r="41" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="12" t="s">
         <v>142</v>
       </c>
@@ -4308,7 +4308,7 @@
       <c r="R41" s="3"/>
       <c r="S41" s="3"/>
     </row>
-    <row r="42" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="12" t="s">
         <v>180</v>
       </c>
@@ -4338,7 +4338,7 @@
       <c r="R42" s="3"/>
       <c r="S42" s="3"/>
     </row>
-    <row r="43" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="11" t="s">
         <v>125</v>
       </c>
@@ -4369,7 +4369,7 @@
       <c r="R43" s="3"/>
       <c r="S43" s="3"/>
     </row>
-    <row r="44" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="12" t="s">
         <v>127</v>
       </c>
@@ -4377,7 +4377,7 @@
         <v>205</v>
       </c>
       <c r="C44" s="26">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>128</v>
@@ -4400,7 +4400,7 @@
       <c r="R44" s="3"/>
       <c r="S44" s="3"/>
     </row>
-    <row r="45" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="12" t="s">
         <v>189</v>
       </c>
@@ -4408,7 +4408,7 @@
         <v>205</v>
       </c>
       <c r="C45" s="26">
-        <v>0.23</v>
+        <v>0.21299999999999999</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>18</v>
@@ -4431,7 +4431,7 @@
       <c r="R45" s="3"/>
       <c r="S45" s="3"/>
     </row>
-    <row r="46" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="11" t="s">
         <v>130</v>
       </c>
@@ -4464,7 +4464,7 @@
       <c r="R46" s="3"/>
       <c r="S46" s="3"/>
     </row>
-    <row r="47" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="11" t="s">
         <v>133</v>
       </c>
@@ -4497,7 +4497,7 @@
       <c r="R47" s="3"/>
       <c r="S47" s="3"/>
     </row>
-    <row r="48" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="12" t="s">
         <v>158</v>
       </c>
@@ -4530,7 +4530,7 @@
       <c r="R48" s="3"/>
       <c r="S48" s="3"/>
     </row>
-    <row r="49" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="12" t="s">
         <v>157</v>
       </c>
@@ -4538,7 +4538,7 @@
         <v>205</v>
       </c>
       <c r="C49" s="26">
-        <v>0.53900000000000003</v>
+        <v>0.5</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>80</v>
@@ -4559,7 +4559,7 @@
       <c r="R49" s="3"/>
       <c r="S49" s="3"/>
     </row>
-    <row r="50" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="12" t="s">
         <v>164</v>
       </c>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="C50" s="27">
         <f>C49/C48</f>
-        <v>2.75</v>
+        <v>2.5510204081632653</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>18</v>
@@ -4593,7 +4593,7 @@
       <c r="R50" s="3"/>
       <c r="S50" s="3"/>
     </row>
-    <row r="51" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="13" t="s">
         <v>139</v>
       </c>
@@ -4626,7 +4626,7 @@
       <c r="R51" s="3"/>
       <c r="S51" s="3"/>
     </row>
-    <row r="52" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="13" t="s">
         <v>186</v>
       </c>
@@ -4635,7 +4635,7 @@
       </c>
       <c r="C52" s="27">
         <f>1/(PI()*C51*C50)</f>
-        <v>0.17807546080212067</v>
+        <v>0.19196534674468607</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>18</v>
@@ -4658,7 +4658,7 @@
       <c r="R52" s="3"/>
       <c r="S52" s="3"/>
     </row>
-    <row r="53" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="14" t="s">
         <v>143</v>
       </c>
@@ -4689,7 +4689,7 @@
       <c r="R53" s="3"/>
       <c r="S53" s="3"/>
     </row>
-    <row r="54" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="13" t="s">
         <v>147</v>
       </c>
@@ -4720,7 +4720,7 @@
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
     </row>
-    <row r="55" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="13" t="s">
         <v>149</v>
       </c>
@@ -4751,7 +4751,7 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
     </row>
-    <row r="56" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="13" t="s">
         <v>148</v>
       </c>
@@ -4782,7 +4782,7 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
     </row>
-    <row r="57" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="13" t="s">
         <v>151</v>
       </c>
@@ -4813,7 +4813,7 @@
       <c r="R57" s="3"/>
       <c r="S57" s="3"/>
     </row>
-    <row r="58" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="13" t="s">
         <v>160</v>
       </c>
@@ -4844,7 +4844,7 @@
       <c r="R58" s="3"/>
       <c r="S58" s="3"/>
     </row>
-    <row r="59" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="13" t="s">
         <v>155</v>
       </c>
@@ -4875,7 +4875,7 @@
       <c r="R59" s="3"/>
       <c r="S59" s="3"/>
     </row>
-    <row r="60" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="13" t="s">
         <v>159</v>
       </c>
@@ -4906,7 +4906,7 @@
       <c r="R60" s="3"/>
       <c r="S60" s="3"/>
     </row>
-    <row r="61" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="13" t="s">
         <v>161</v>
       </c>
@@ -4937,7 +4937,7 @@
       <c r="R61" s="3"/>
       <c r="S61" s="3"/>
     </row>
-    <row r="62" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="13" t="s">
         <v>162</v>
       </c>
@@ -4968,7 +4968,7 @@
       <c r="R62" s="3"/>
       <c r="S62" s="3"/>
     </row>
-    <row r="63" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="13" t="s">
         <v>163</v>
       </c>
@@ -4976,7 +4976,7 @@
         <v>205</v>
       </c>
       <c r="C63" s="28">
-        <v>0.24299999999999999</v>
+        <v>0.21</v>
       </c>
       <c r="D63" s="6" t="s">
         <v>80</v>
@@ -4997,7 +4997,7 @@
       <c r="R63" s="3"/>
       <c r="S63" s="3"/>
     </row>
-    <row r="64" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="13" t="s">
         <v>165</v>
       </c>
@@ -5006,7 +5006,7 @@
       </c>
       <c r="C64" s="27">
         <f>C63/C62</f>
-        <v>1.2397959183673468</v>
+        <v>1.0714285714285714</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>18</v>
@@ -5027,7 +5027,7 @@
       <c r="R64" s="3"/>
       <c r="S64" s="3"/>
     </row>
-    <row r="65" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="13" t="s">
         <v>181</v>
       </c>
@@ -5058,7 +5058,7 @@
       <c r="R65" s="3"/>
       <c r="S65" s="3"/>
     </row>
-    <row r="66" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="13" t="s">
         <v>182</v>
       </c>
@@ -5089,7 +5089,7 @@
       <c r="R66" s="3"/>
       <c r="S66" s="3"/>
     </row>
-    <row r="67" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="13" t="s">
         <v>166</v>
       </c>
@@ -5118,7 +5118,7 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
     </row>
-    <row r="68" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="13" t="s">
         <v>167</v>
       </c>
@@ -5147,7 +5147,7 @@
       <c r="R68" s="3"/>
       <c r="S68" s="3"/>
     </row>
-    <row r="69" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="13" t="s">
         <v>168</v>
       </c>
@@ -5176,7 +5176,7 @@
       <c r="R69" s="3"/>
       <c r="S69" s="3"/>
     </row>
-    <row r="70" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="13" t="s">
         <v>169</v>
       </c>
@@ -5205,7 +5205,7 @@
       <c r="R70" s="3"/>
       <c r="S70" s="3"/>
     </row>
-    <row r="71" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="13" t="s">
         <v>170</v>
       </c>
@@ -5234,7 +5234,7 @@
       <c r="R71" s="3"/>
       <c r="S71" s="3"/>
     </row>
-    <row r="72" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="13" t="s">
         <v>171</v>
       </c>
@@ -5263,7 +5263,7 @@
       <c r="R72" s="3"/>
       <c r="S72" s="3"/>
     </row>
-    <row r="73" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="13" t="s">
         <v>172</v>
       </c>
@@ -5292,7 +5292,7 @@
       <c r="R73" s="3"/>
       <c r="S73" s="3"/>
     </row>
-    <row r="74" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="13" t="s">
         <v>173</v>
       </c>
@@ -5321,7 +5321,7 @@
       <c r="R74" s="3"/>
       <c r="S74" s="3"/>
     </row>
-    <row r="75" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="13" t="s">
         <v>174</v>
       </c>
@@ -5352,7 +5352,7 @@
       <c r="R75" s="3"/>
       <c r="S75" s="3"/>
     </row>
-    <row r="76" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="13" t="s">
         <v>176</v>
       </c>
@@ -5383,7 +5383,7 @@
       <c r="R76" s="3"/>
       <c r="S76" s="3"/>
     </row>
-    <row r="77" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="13" t="s">
         <v>192</v>
       </c>
@@ -5412,7 +5412,7 @@
       <c r="R77" s="3"/>
       <c r="S77" s="3"/>
     </row>
-    <row r="78" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="14" t="s">
         <v>193</v>
       </c>
@@ -5443,7 +5443,7 @@
       <c r="R78" s="3"/>
       <c r="S78" s="3"/>
     </row>
-    <row r="79" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="14" t="s">
         <v>196</v>
       </c>
@@ -5474,7 +5474,7 @@
       <c r="R79" s="3"/>
       <c r="S79" s="3"/>
     </row>
-    <row r="80" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="14" t="s">
         <v>197</v>
       </c>
@@ -5505,7 +5505,7 @@
       <c r="R80" s="3"/>
       <c r="S80" s="3"/>
     </row>
-    <row r="81" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="14" t="s">
         <v>210</v>
       </c>
@@ -5536,7 +5536,7 @@
       <c r="R81" s="3"/>
       <c r="S81" s="3"/>
     </row>
-    <row r="82" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="14" t="s">
         <v>212</v>
       </c>
@@ -5565,7 +5565,7 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
     </row>
-    <row r="83" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="14" t="s">
         <v>213</v>
       </c>
@@ -5594,7 +5594,7 @@
       <c r="R83" s="3"/>
       <c r="S83" s="3"/>
     </row>
-    <row r="84" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="14" t="s">
         <v>214</v>
       </c>
@@ -5625,7 +5625,7 @@
       <c r="R84" s="3"/>
       <c r="S84" s="3"/>
     </row>
-    <row r="85" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="14" t="s">
         <v>216</v>
       </c>
@@ -5656,7 +5656,7 @@
       <c r="R85" s="3"/>
       <c r="S85" s="3"/>
     </row>
-    <row r="86" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="14" t="s">
         <v>218</v>
       </c>
@@ -5687,7 +5687,7 @@
       <c r="R86" s="3"/>
       <c r="S86" s="3"/>
     </row>
-    <row r="87" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="14" t="s">
         <v>220</v>
       </c>
@@ -5718,7 +5718,7 @@
       <c r="R87" s="3"/>
       <c r="S87" s="3"/>
     </row>
-    <row r="88" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="14" t="s">
         <v>222</v>
       </c>
@@ -5749,7 +5749,7 @@
       <c r="R88" s="3"/>
       <c r="S88" s="3"/>
     </row>
-    <row r="89" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="13" t="s">
         <v>225</v>
       </c>
@@ -5780,7 +5780,7 @@
       <c r="R89" s="3"/>
       <c r="S89" s="3"/>
     </row>
-    <row r="90" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="13" t="s">
         <v>227</v>
       </c>
@@ -5811,7 +5811,7 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
     </row>
-    <row r="91" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="13" t="s">
         <v>228</v>
       </c>
@@ -5840,7 +5840,7 @@
       <c r="R91" s="3"/>
       <c r="S91" s="3"/>
     </row>
-    <row r="92" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="14" t="s">
         <v>230</v>
       </c>
@@ -5871,7 +5871,7 @@
       <c r="R92" s="3"/>
       <c r="S92" s="3"/>
     </row>
-    <row r="93" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="14" t="s">
         <v>232</v>
       </c>
@@ -5879,7 +5879,7 @@
         <v>205</v>
       </c>
       <c r="C93" s="28">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>83</v>
@@ -5902,7 +5902,7 @@
       <c r="R93" s="3"/>
       <c r="S93" s="3"/>
     </row>
-    <row r="94" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="14"/>
       <c r="B94" s="31"/>
       <c r="C94" s="28"/>
@@ -5923,7 +5923,7 @@
       <c r="R94" s="3"/>
       <c r="S94" s="3"/>
     </row>
-    <row r="95" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="14"/>
       <c r="B95" s="31"/>
       <c r="C95" s="28"/>
@@ -5944,7 +5944,7 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
     </row>
-    <row r="96" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="14"/>
       <c r="B96" s="31"/>
       <c r="C96" s="28"/>
@@ -5965,7 +5965,7 @@
       <c r="R96" s="3"/>
       <c r="S96" s="3"/>
     </row>
-    <row r="97" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="14"/>
       <c r="B97" s="31"/>
       <c r="C97" s="28"/>
@@ -5986,7 +5986,7 @@
       <c r="R97" s="3"/>
       <c r="S97" s="3"/>
     </row>
-    <row r="98" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="14"/>
       <c r="B98" s="31"/>
       <c r="C98" s="28"/>
@@ -6007,7 +6007,7 @@
       <c r="R98" s="3"/>
       <c r="S98" s="3"/>
     </row>
-    <row r="99" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="14"/>
       <c r="B99" s="31"/>
       <c r="C99" s="28"/>
@@ -6028,7 +6028,7 @@
       <c r="R99" s="3"/>
       <c r="S99" s="3"/>
     </row>
-    <row r="100" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="14"/>
       <c r="B100" s="31"/>
       <c r="C100" s="28"/>
@@ -6049,7 +6049,7 @@
       <c r="R100" s="3"/>
       <c r="S100" s="3"/>
     </row>
-    <row r="101" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="14"/>
       <c r="B101" s="31"/>
       <c r="C101" s="28"/>
@@ -6070,7 +6070,7 @@
       <c r="R101" s="3"/>
       <c r="S101" s="3"/>
     </row>
-    <row r="102" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="14"/>
       <c r="B102" s="31"/>
       <c r="C102" s="28"/>
@@ -6091,7 +6091,7 @@
       <c r="R102" s="3"/>
       <c r="S102" s="3"/>
     </row>
-    <row r="103" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="14"/>
       <c r="B103" s="31"/>
       <c r="C103" s="28"/>
@@ -6112,7 +6112,7 @@
       <c r="R103" s="3"/>
       <c r="S103" s="3"/>
     </row>
-    <row r="104" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="14"/>
       <c r="B104" s="31"/>
       <c r="C104" s="28"/>
@@ -6133,7 +6133,7 @@
       <c r="R104" s="3"/>
       <c r="S104" s="3"/>
     </row>
-    <row r="105" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="14"/>
       <c r="B105" s="31"/>
       <c r="C105" s="28"/>
@@ -6154,7 +6154,7 @@
       <c r="R105" s="3"/>
       <c r="S105" s="3"/>
     </row>
-    <row r="106" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="14"/>
       <c r="B106" s="31"/>
       <c r="C106" s="28"/>
@@ -6175,7 +6175,7 @@
       <c r="R106" s="3"/>
       <c r="S106" s="3"/>
     </row>
-    <row r="107" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="14"/>
       <c r="B107" s="31"/>
       <c r="C107" s="28"/>
@@ -6196,7 +6196,7 @@
       <c r="R107" s="3"/>
       <c r="S107" s="3"/>
     </row>
-    <row r="108" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="14"/>
       <c r="B108" s="31"/>
       <c r="C108" s="28"/>
@@ -6217,7 +6217,7 @@
       <c r="R108" s="3"/>
       <c r="S108" s="3"/>
     </row>
-    <row r="109" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="14"/>
       <c r="B109" s="31"/>
       <c r="C109" s="28"/>
@@ -6238,7 +6238,7 @@
       <c r="R109" s="3"/>
       <c r="S109" s="3"/>
     </row>
-    <row r="110" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="14"/>
       <c r="B110" s="31"/>
       <c r="C110" s="28"/>
@@ -6259,7 +6259,7 @@
       <c r="R110" s="3"/>
       <c r="S110" s="3"/>
     </row>
-    <row r="111" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="14"/>
       <c r="B111" s="31"/>
       <c r="C111" s="28"/>
@@ -6280,7 +6280,7 @@
       <c r="R111" s="3"/>
       <c r="S111" s="3"/>
     </row>
-    <row r="112" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="14"/>
       <c r="B112" s="31"/>
       <c r="C112" s="28"/>
@@ -6301,7 +6301,7 @@
       <c r="R112" s="3"/>
       <c r="S112" s="3"/>
     </row>
-    <row r="113" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="14"/>
       <c r="B113" s="31"/>
       <c r="C113" s="28"/>
@@ -6322,7 +6322,7 @@
       <c r="R113" s="3"/>
       <c r="S113" s="3"/>
     </row>
-    <row r="114" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="14"/>
       <c r="B114" s="31"/>
       <c r="C114" s="28"/>
@@ -6343,7 +6343,7 @@
       <c r="R114" s="3"/>
       <c r="S114" s="3"/>
     </row>
-    <row r="115" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="14"/>
       <c r="B115" s="31"/>
       <c r="C115" s="28"/>
@@ -6364,7 +6364,7 @@
       <c r="R115" s="3"/>
       <c r="S115" s="3"/>
     </row>
-    <row r="116" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="14"/>
       <c r="B116" s="31"/>
       <c r="C116" s="28"/>
@@ -6385,7 +6385,7 @@
       <c r="R116" s="3"/>
       <c r="S116" s="3"/>
     </row>
-    <row r="117" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="14"/>
       <c r="B117" s="31"/>
       <c r="C117" s="28"/>
@@ -6406,7 +6406,7 @@
       <c r="R117" s="3"/>
       <c r="S117" s="3"/>
     </row>
-    <row r="118" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="14"/>
       <c r="B118" s="31"/>
       <c r="C118" s="28"/>
@@ -6427,7 +6427,7 @@
       <c r="R118" s="3"/>
       <c r="S118" s="3"/>
     </row>
-    <row r="119" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="14"/>
       <c r="B119" s="31"/>
       <c r="C119" s="28"/>
@@ -6448,7 +6448,7 @@
       <c r="R119" s="3"/>
       <c r="S119" s="3"/>
     </row>
-    <row r="120" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="14"/>
       <c r="B120" s="31"/>
       <c r="C120" s="28"/>
@@ -6469,7 +6469,7 @@
       <c r="R120" s="3"/>
       <c r="S120" s="3"/>
     </row>
-    <row r="121" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="14"/>
       <c r="B121" s="31"/>
       <c r="C121" s="28"/>
@@ -6490,7 +6490,7 @@
       <c r="R121" s="3"/>
       <c r="S121" s="3"/>
     </row>
-    <row r="122" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="14"/>
       <c r="B122" s="31"/>
       <c r="C122" s="28"/>
@@ -6511,7 +6511,7 @@
       <c r="R122" s="3"/>
       <c r="S122" s="3"/>
     </row>
-    <row r="123" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="14"/>
       <c r="B123" s="31"/>
       <c r="C123" s="28"/>
@@ -6532,7 +6532,7 @@
       <c r="R123" s="3"/>
       <c r="S123" s="3"/>
     </row>
-    <row r="124" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="14"/>
       <c r="B124" s="31"/>
       <c r="C124" s="28"/>
@@ -6553,7 +6553,7 @@
       <c r="R124" s="3"/>
       <c r="S124" s="3"/>
     </row>
-    <row r="125" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="14"/>
       <c r="B125" s="31"/>
       <c r="C125" s="28"/>
@@ -6574,7 +6574,7 @@
       <c r="R125" s="3"/>
       <c r="S125" s="3"/>
     </row>
-    <row r="126" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="14"/>
       <c r="B126" s="31"/>
       <c r="C126" s="28"/>
@@ -6595,7 +6595,7 @@
       <c r="R126" s="3"/>
       <c r="S126" s="3"/>
     </row>
-    <row r="127" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="14"/>
       <c r="B127" s="31"/>
       <c r="C127" s="28"/>
@@ -6616,7 +6616,7 @@
       <c r="R127" s="3"/>
       <c r="S127" s="3"/>
     </row>
-    <row r="128" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="14"/>
       <c r="B128" s="31"/>
       <c r="C128" s="28"/>
@@ -6637,7 +6637,7 @@
       <c r="R128" s="3"/>
       <c r="S128" s="3"/>
     </row>
-    <row r="129" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="14"/>
       <c r="B129" s="31"/>
       <c r="C129" s="28"/>
@@ -6658,7 +6658,7 @@
       <c r="R129" s="3"/>
       <c r="S129" s="3"/>
     </row>
-    <row r="130" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="14"/>
       <c r="B130" s="31"/>
       <c r="C130" s="28"/>
@@ -6679,7 +6679,7 @@
       <c r="R130" s="3"/>
       <c r="S130" s="3"/>
     </row>
-    <row r="131" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="14"/>
       <c r="B131" s="31"/>
       <c r="C131" s="28"/>
@@ -6700,7 +6700,7 @@
       <c r="R131" s="3"/>
       <c r="S131" s="3"/>
     </row>
-    <row r="132" spans="1:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:19" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="14"/>
       <c r="B132" s="31"/>
       <c r="C132" s="28"/>
@@ -6737,25 +6737,25 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1ADFA23C-5193-4068-BEB5-E93369C6617F}">
   <dimension ref="A1:F30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="48.109375" customWidth="1"/>
-    <col min="2" max="4" width="15.77734375" customWidth="1"/>
-    <col min="5" max="5" width="3.77734375" customWidth="1"/>
-    <col min="6" max="6" width="46.77734375" customWidth="1"/>
+    <col min="1" max="1" width="48.1640625" customWidth="1"/>
+    <col min="2" max="4" width="15.83203125" customWidth="1"/>
+    <col min="5" max="5" width="3.83203125" customWidth="1"/>
+    <col min="6" max="6" width="46.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="19" x14ac:dyDescent="0.25">
       <c r="A1" s="37" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="38" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="39" t="s">
         <v>234</v>
       </c>
@@ -6769,7 +6769,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>238</v>
       </c>
@@ -6789,7 +6789,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>239</v>
       </c>
@@ -6809,7 +6809,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>240</v>
       </c>
@@ -6829,7 +6829,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>241</v>
       </c>
@@ -6839,17 +6839,17 @@
       </c>
       <c r="C8" s="40">
         <f>INPUTS!C49</f>
-        <v>0.53900000000000003</v>
+        <v>0.5</v>
       </c>
       <c r="D8" s="40">
         <f>INPUTS!C63</f>
-        <v>0.24299999999999999</v>
+        <v>0.21</v>
       </c>
       <c r="F8" s="38" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>242</v>
       </c>
@@ -6868,7 +6868,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>243</v>
       </c>
@@ -6885,7 +6885,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>244</v>
       </c>
@@ -6905,7 +6905,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>245</v>
       </c>
@@ -6925,7 +6925,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>246</v>
       </c>
@@ -6942,7 +6942,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="39" t="s">
         <v>247</v>
       </c>
@@ -6950,7 +6950,7 @@
       <c r="C14" s="39"/>
       <c r="D14" s="39"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>248</v>
       </c>
@@ -6967,7 +6967,7 @@
         <v>1.9823131728623846</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>249</v>
       </c>
@@ -6984,7 +6984,7 @@
         <v>1.1592794807274085</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>250</v>
       </c>
@@ -7001,7 +7001,7 @@
         <v>-0.62740704594148844</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>251</v>
       </c>
@@ -7018,7 +7018,7 @@
         <v>-0.96540266006846076</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="39" t="s">
         <v>252</v>
       </c>
@@ -7026,7 +7026,7 @@
       <c r="C19" s="39"/>
       <c r="D19" s="39"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>253</v>
       </c>
@@ -7043,7 +7043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>254</v>
       </c>
@@ -7060,7 +7060,7 @@
         <v>0.3490658503988659</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>255</v>
       </c>
@@ -7077,7 +7077,7 @@
         <v>-0.33698910051412451</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>256</v>
       </c>
@@ -7094,7 +7094,7 @@
         <v>324.01250000000005</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>257</v>
       </c>
@@ -7104,14 +7104,14 @@
       </c>
       <c r="C24" s="40">
         <f>C7*C8</f>
-        <v>3.1693199999999998E-2</v>
+        <v>2.9399999999999999E-2</v>
       </c>
       <c r="D24" s="40">
         <f>D7*D8</f>
-        <v>1.42884E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1.2348E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="36" t="s">
         <v>258</v>
       </c>
@@ -7121,14 +7121,14 @@
       </c>
       <c r="C25" s="48">
         <f>C22*C23*C24*C7</f>
-        <v>-0.21009166195271597</v>
+        <v>-0.19489022444593321</v>
       </c>
       <c r="D25" s="48">
         <f>D22*D23*D24*D7</f>
-        <v>-9.1735735057972057E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+        <v>-7.9277795729111644E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>259</v>
       </c>
@@ -7138,14 +7138,14 @@
       </c>
       <c r="C26" s="41">
         <f>ABS(C25)*C13</f>
-        <v>0.21009166195271597</v>
+        <v>0.19489022444593321</v>
       </c>
       <c r="D26" s="41">
         <f>ABS(D25)*D13</f>
-        <v>9.1735735057972057E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+        <v>7.9277795729111644E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="36" t="s">
         <v>260</v>
       </c>
@@ -7155,14 +7155,14 @@
       </c>
       <c r="C27" s="43">
         <f>C26*141.612</f>
-        <v>29.751500432448015</v>
+        <v>27.598794464237493</v>
       </c>
       <c r="D27" s="43">
         <f>D26*141.612</f>
-        <v>12.990880913029539</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+        <v>11.226687208790958</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="39" t="s">
         <v>261</v>
       </c>
@@ -7170,7 +7170,7 @@
       <c r="C28" s="39"/>
       <c r="D28" s="39"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>262</v>
       </c>
@@ -7178,7 +7178,7 @@
       <c r="C29" s="44"/>
       <c r="D29" s="44"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>263</v>
       </c>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\Fall 2026\AAE 451\451-DBF-Team01-LOCAL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\Fall 2026\AAE 451\451-DBF-Team01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F94A2213-8547-44B7-99B9-1EDD61418227}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6264661C-07D5-4B6E-9648-D59E06C92932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -608,9 +608,6 @@
     <t>V</t>
   </si>
   <si>
-    <t>Battery voltage (3S)</t>
-  </si>
-  <si>
     <t>prop_file</t>
   </si>
   <si>
@@ -654,6 +651,9 @@
   </si>
   <si>
     <t>CM_0_Wing</t>
+  </si>
+  <si>
+    <t>Battery voltage (4S)</t>
   </si>
 </sst>
 </file>
@@ -1141,7 +1141,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B9" t="s">
         <v>7</v>
@@ -1201,7 +1201,7 @@
         <v>8</v>
       </c>
       <c r="E12" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -2119,12 +2119,12 @@
         <v>59</v>
       </c>
       <c r="E66" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B67" t="s">
         <v>136</v>
@@ -2136,7 +2136,7 @@
         <v>59</v>
       </c>
       <c r="E67" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
@@ -2198,7 +2198,7 @@
         <v>136</v>
       </c>
       <c r="C71">
-        <v>200.73</v>
+        <v>200</v>
       </c>
       <c r="D71" t="s">
         <v>59</v>
@@ -2300,7 +2300,7 @@
         <v>136</v>
       </c>
       <c r="C77">
-        <v>4.3939000000000004</v>
+        <v>6</v>
       </c>
       <c r="D77" t="s">
         <v>163</v>
@@ -2459,29 +2459,29 @@
         <v>190</v>
       </c>
       <c r="E86" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B87" t="s">
         <v>170</v>
       </c>
       <c r="C87" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D87" t="s">
         <v>8</v>
       </c>
       <c r="E87" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B88" t="s">
         <v>170</v>
@@ -2490,15 +2490,15 @@
         <v>527000</v>
       </c>
       <c r="D88" t="s">
+        <v>194</v>
+      </c>
+      <c r="E88" t="s">
         <v>195</v>
-      </c>
-      <c r="E88" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B89" t="s">
         <v>170</v>
@@ -2510,12 +2510,12 @@
         <v>8</v>
       </c>
       <c r="E89" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B90" t="s">
         <v>170</v>
@@ -2527,7 +2527,7 @@
         <v>8</v>
       </c>
       <c r="E90" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\Fall 2026\AAE 451\451-DBF-Team01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6264661C-07D5-4B6E-9648-D59E06C92932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60007970-5A4F-400B-B565-6CA8D1228FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1467,7 +1467,7 @@
         <v>56</v>
       </c>
       <c r="C28">
-        <v>0.24299999999999999</v>
+        <v>0.433</v>
       </c>
       <c r="D28" t="s">
         <v>66</v>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\Fall 2026\AAE 451\451-DBF-Team01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ceaa8977d2236823/Documents/GitHub/451-DBF-Team01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60007970-5A4F-400B-B565-6CA8D1228FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="81" documentId="13_ncr:1_{60007970-5A4F-400B-B565-6CA8D1228FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D0CB0C3-AA3F-455A-B1AE-807F3BF48BD3}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="-26790" yWindow="2955" windowWidth="21600" windowHeight="11235" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hinge Moments" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="263">
   <si>
     <t>Parameter</t>
   </si>
@@ -654,13 +655,186 @@
   </si>
   <si>
     <t>Battery voltage (4S)</t>
+  </si>
+  <si>
+    <t>Control-Surface Hinge Moments - Thin-Airfoil (Glauert) Theory</t>
+  </si>
+  <si>
+    <t>PARAMETER</t>
+  </si>
+  <si>
+    <t>AILERON</t>
+  </si>
+  <si>
+    <t>ELEVATOR</t>
+  </si>
+  <si>
+    <t>RUDDER</t>
+  </si>
+  <si>
+    <t>Reference (root) chord, c  (m)</t>
+  </si>
+  <si>
+    <t>Ch_alpha, Ch_delta from closed-form thin-airfoil (Glauert) flap theory, verified</t>
+  </si>
+  <si>
+    <t>Control-surface chord fraction, Ef = cf/c</t>
+  </si>
+  <si>
+    <t>against an independent numerical vortex-panel solution to 4 sig. figs.</t>
+  </si>
+  <si>
+    <t>Control-surface chord, cf = Ef*c  (m)</t>
+  </si>
+  <si>
+    <t>Control-surface span, bf  (m)</t>
+  </si>
+  <si>
+    <t>Max deflection, delta_max  (deg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - alpha assumption per surface defaults to 0 deg (pure control deflection case);</t>
+  </si>
+  <si>
+    <t>Local AoA assumed for this case, alpha  (deg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   raise it for combined maneuver cases (e.g. elevator at high AoA).</t>
+  </si>
+  <si>
+    <t>Design airspeed for this case, V  (m/s)</t>
+  </si>
+  <si>
+    <t>Air density, rho  (kg/m^3)</t>
+  </si>
+  <si>
+    <t>Theory is inviscid/2-D and typically over-predicts real hinge moment ~2x --</t>
+  </si>
+  <si>
+    <t>Extra servo safety margin factor  (x)</t>
+  </si>
+  <si>
+    <t>conservative (safe) for servo torque sizing, but state that factor in the report.</t>
+  </si>
+  <si>
+    <t>THIN-AIRFOIL DERIVATION</t>
+  </si>
+  <si>
+    <t>theta_f = ACOS(2*Ef-1)  (rad)</t>
+  </si>
+  <si>
+    <t>X = pi - theta_f</t>
+  </si>
+  <si>
+    <t>Ch_alpha  (floating tendency, per rad)</t>
+  </si>
+  <si>
+    <t>Ch_delta  (restoring tendency, per rad)</t>
+  </si>
+  <si>
+    <t>RESULTING HINGE MOMENT (worst case: alpha &amp; delta_max together)</t>
+  </si>
+  <si>
+    <t>alpha (rad)</t>
+  </si>
+  <si>
+    <t>delta_max (rad)</t>
+  </si>
+  <si>
+    <t>Ch = Ch_alpha*alpha + Ch_delta*delta_max</t>
+  </si>
+  <si>
+    <t>Dynamic pressure, q = 0.5*rho*V^2  (Pa)</t>
+  </si>
+  <si>
+    <t>Control-surface area, Sf = cf*bf  (m^2)</t>
+  </si>
+  <si>
+    <t>Hinge moment, H = Ch*q*Sf*cf  (N*m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ... with safety margin, |H|*margin  (N*m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ... in servo units  (oz-in)</t>
+  </si>
+  <si>
+    <t>COMPARE TO XFLR5 (paste your sweep results here)</t>
+  </si>
+  <si>
+    <t>XFLR5 Ch at same alpha, delta_max</t>
+  </si>
+  <si>
+    <t>Ratio: thin-airfoil / XFLR5</t>
+  </si>
+  <si>
+    <t>Geometry linked live from the Sheet1 tab. Inviscid 2-D theory typically over-predicts the real hinge moment by ~2x - conservative for servo sizing.</t>
+  </si>
+  <si>
+    <t>Yellow cells are NOT linked to Sheet1 -- check/edit them:</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - c_hstab, c_vstab, span_hstab, span_vstab, and V_C (cruise speed) are not defined in Sheet1; literal values carried over from the old sheet -- verify/update manually.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - V_design defaults to V_C (cruise, not in Sheet1); consider a higher design/dive speed if known.</t>
+  </si>
+  <si>
+    <t>linkage_ratio_aileron</t>
+  </si>
+  <si>
+    <t>controls</t>
+  </si>
+  <si>
+    <t>Aileron servo-arm / control-horn mechanical advantage</t>
+  </si>
+  <si>
+    <t>linkage_ratio_elevator</t>
+  </si>
+  <si>
+    <t>Elevator servo-arm / control-horn mechanical advantage</t>
+  </si>
+  <si>
+    <t>linkage_ratio_rudder</t>
+  </si>
+  <si>
+    <t>Rudder servo-arm / control-horn mechanical advantage</t>
+  </si>
+  <si>
+    <t>linkage_efficiency</t>
+  </si>
+  <si>
+    <t>Pushrod/linkage mechanical efficiency (friction losses); applies to all three surfaces</t>
+  </si>
+  <si>
+    <t>Linkage ratio, servo arm / control horn (mechanical advantage)</t>
+  </si>
+  <si>
+    <t>Linkage efficiency, eta_linkage (friction losses)</t>
+  </si>
+  <si>
+    <t>Servo torque scales by (linkage ratio / efficiency): a longer servo arm vs. horn cuts required torque;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   friction losses in the linkage mean the servo must output more torque than the ideal case.</t>
+  </si>
+  <si>
+    <t>V_servo_rail</t>
+  </si>
+  <si>
+    <t>Servo rail (BEC output) voltage used to evaluate torque at the actual operating voltage</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -668,13 +842,76 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF1F3C78"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF808080"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF784E1F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAEFE2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -686,14 +923,33 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="6" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="5" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{230A598C-34F2-42DB-8399-2F181824D933}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -709,8 +965,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:F90" totalsRowShown="0">
-  <autoFilter ref="A1:F90" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:F95" totalsRowShown="0">
+  <autoFilter ref="A1:F95" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E43">
     <sortCondition ref="B1:B101"/>
   </sortState>
@@ -989,18 +1245,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F90"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F95"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" customWidth="1"/>
     <col min="5" max="5" width="44" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1020,7 +1276,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1037,7 +1293,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1054,7 +1310,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1071,7 +1327,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -1088,7 +1344,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -1105,7 +1361,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -1122,7 +1378,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -1139,7 +1395,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>205</v>
       </c>
@@ -1153,7 +1409,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -1170,7 +1426,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1187,7 +1443,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -1204,7 +1460,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -1221,7 +1477,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -1238,7 +1494,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -1255,7 +1511,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>35</v>
       </c>
@@ -1272,7 +1528,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>37</v>
       </c>
@@ -1289,7 +1545,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>39</v>
       </c>
@@ -1306,7 +1562,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>41</v>
       </c>
@@ -1323,7 +1579,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>45</v>
       </c>
@@ -1340,7 +1596,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -1357,7 +1613,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -1374,7 +1630,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -1391,7 +1647,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -1408,7 +1664,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>58</v>
       </c>
@@ -1425,7 +1681,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>61</v>
       </c>
@@ -1442,7 +1698,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>63</v>
       </c>
@@ -1459,7 +1715,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>65</v>
       </c>
@@ -1476,7 +1732,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -1493,7 +1749,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -1510,7 +1766,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>72</v>
       </c>
@@ -1527,7 +1783,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>74</v>
       </c>
@@ -1544,7 +1800,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>76</v>
       </c>
@@ -1561,7 +1817,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>78</v>
       </c>
@@ -1578,7 +1834,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>80</v>
       </c>
@@ -1595,7 +1851,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>82</v>
       </c>
@@ -1612,7 +1868,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>84</v>
       </c>
@@ -1629,7 +1885,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>86</v>
       </c>
@@ -1646,7 +1902,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>88</v>
       </c>
@@ -1663,7 +1919,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>90</v>
       </c>
@@ -1680,7 +1936,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>92</v>
       </c>
@@ -1697,7 +1953,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>94</v>
       </c>
@@ -1714,7 +1970,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>96</v>
       </c>
@@ -1731,7 +1987,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>98</v>
       </c>
@@ -1748,7 +2004,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>100</v>
       </c>
@@ -1765,7 +2021,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>103</v>
       </c>
@@ -1782,7 +2038,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>105</v>
       </c>
@@ -1799,7 +2055,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>107</v>
       </c>
@@ -1816,7 +2072,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>109</v>
       </c>
@@ -1833,7 +2089,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>111</v>
       </c>
@@ -1850,7 +2106,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>113</v>
       </c>
@@ -1867,7 +2123,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>115</v>
       </c>
@@ -1884,7 +2140,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>117</v>
       </c>
@@ -1901,7 +2157,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>119</v>
       </c>
@@ -1909,7 +2165,7 @@
         <v>56</v>
       </c>
       <c r="C54">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D54" t="s">
         <v>23</v>
@@ -1918,7 +2174,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>121</v>
       </c>
@@ -1935,7 +2191,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>123</v>
       </c>
@@ -1943,7 +2199,7 @@
         <v>56</v>
       </c>
       <c r="C56">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D56" t="s">
         <v>23</v>
@@ -1952,7 +2208,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>125</v>
       </c>
@@ -1969,7 +2225,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>127</v>
       </c>
@@ -1986,7 +2242,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>129</v>
       </c>
@@ -2003,7 +2259,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>131</v>
       </c>
@@ -2020,7 +2276,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>133</v>
       </c>
@@ -2037,7 +2293,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>135</v>
       </c>
@@ -2054,7 +2310,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>139</v>
       </c>
@@ -2071,7 +2327,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>141</v>
       </c>
@@ -2088,7 +2344,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>143</v>
       </c>
@@ -2105,7 +2361,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>145</v>
       </c>
@@ -2122,7 +2378,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>201</v>
       </c>
@@ -2139,7 +2395,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>146</v>
       </c>
@@ -2156,7 +2412,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>148</v>
       </c>
@@ -2173,7 +2429,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>150</v>
       </c>
@@ -2190,7 +2446,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>152</v>
       </c>
@@ -2207,7 +2463,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>154</v>
       </c>
@@ -2224,7 +2480,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>157</v>
       </c>
@@ -2241,7 +2497,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>160</v>
       </c>
@@ -2258,7 +2514,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>162</v>
       </c>
@@ -2275,7 +2531,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>165</v>
       </c>
@@ -2292,7 +2548,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>167</v>
       </c>
@@ -2309,7 +2565,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>169</v>
       </c>
@@ -2326,7 +2582,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>172</v>
       </c>
@@ -2343,7 +2599,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>174</v>
       </c>
@@ -2360,7 +2616,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>176</v>
       </c>
@@ -2377,7 +2633,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>178</v>
       </c>
@@ -2394,7 +2650,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>180</v>
       </c>
@@ -2411,7 +2667,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>183</v>
       </c>
@@ -2428,7 +2684,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>186</v>
       </c>
@@ -2445,7 +2701,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>189</v>
       </c>
@@ -2462,7 +2718,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>191</v>
       </c>
@@ -2479,7 +2735,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>193</v>
       </c>
@@ -2496,7 +2752,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>196</v>
       </c>
@@ -2513,7 +2769,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>198</v>
       </c>
@@ -2528,6 +2784,91 @@
       </c>
       <c r="E90" t="s">
         <v>199</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>248</v>
+      </c>
+      <c r="B91" t="s">
+        <v>249</v>
+      </c>
+      <c r="C91">
+        <v>1</v>
+      </c>
+      <c r="D91" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>251</v>
+      </c>
+      <c r="B92" t="s">
+        <v>249</v>
+      </c>
+      <c r="C92">
+        <v>1.2</v>
+      </c>
+      <c r="D92" t="s">
+        <v>8</v>
+      </c>
+      <c r="E92" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>253</v>
+      </c>
+      <c r="B93" t="s">
+        <v>249</v>
+      </c>
+      <c r="C93">
+        <v>1</v>
+      </c>
+      <c r="D93" t="s">
+        <v>8</v>
+      </c>
+      <c r="E93" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>255</v>
+      </c>
+      <c r="B94" t="s">
+        <v>249</v>
+      </c>
+      <c r="C94">
+        <v>0.85</v>
+      </c>
+      <c r="D94" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>261</v>
+      </c>
+      <c r="B95" t="s">
+        <v>249</v>
+      </c>
+      <c r="C95">
+        <v>6</v>
+      </c>
+      <c r="D95" t="s">
+        <v>190</v>
+      </c>
+      <c r="E95" t="s">
+        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -2536,4 +2877,505 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{118BE621-EF6B-4648-868E-9937B9C5B685}">
+  <dimension ref="A1:F32"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="48.109375" style="2" customWidth="1"/>
+    <col min="2" max="4" width="15.77734375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="3.77734375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="46.77734375" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B5" s="5">
+        <f>(Sheet1!C19*Sheet1!C77/Sheet1!C72)/(Sheet1!C25-Sheet1!C26)</f>
+        <v>0.42877435804042974</v>
+      </c>
+      <c r="C5" s="15">
+        <v>0.19600000000000001</v>
+      </c>
+      <c r="D5" s="15">
+        <v>0.19600000000000001</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B6" s="6">
+        <f>Sheet1!C57</f>
+        <v>0.25</v>
+      </c>
+      <c r="C6" s="6">
+        <f>Sheet1!C53</f>
+        <v>0.3</v>
+      </c>
+      <c r="D6" s="6">
+        <f>Sheet1!C55</f>
+        <v>0.3</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B7" s="5">
+        <f>B6*B5</f>
+        <v>0.10719358951010743</v>
+      </c>
+      <c r="C7" s="5">
+        <f>C6*C5</f>
+        <v>5.8799999999999998E-2</v>
+      </c>
+      <c r="D7" s="5">
+        <f>D6*D5</f>
+        <v>5.8799999999999998E-2</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B8" s="5">
+        <f>(Sheet1!C59-Sheet1!C58)*Sheet1!C25/2</f>
+        <v>0.22500000000000003</v>
+      </c>
+      <c r="C8" s="15">
+        <v>0.53900000000000003</v>
+      </c>
+      <c r="D8" s="15">
+        <v>0.24299999999999999</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B9" s="7">
+        <f>Sheet1!C60</f>
+        <v>15</v>
+      </c>
+      <c r="C9" s="16">
+        <f>Sheet1!C54</f>
+        <v>30</v>
+      </c>
+      <c r="D9" s="7">
+        <f>Sheet1!C56</f>
+        <v>30</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B10" s="8">
+        <v>0</v>
+      </c>
+      <c r="C10" s="8">
+        <v>1</v>
+      </c>
+      <c r="D10" s="8">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B11" s="9">
+        <v>23</v>
+      </c>
+      <c r="C11" s="9">
+        <v>23</v>
+      </c>
+      <c r="D11" s="9">
+        <v>23</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B12" s="5">
+        <f>Sheet1!C20</f>
+        <v>1.2250000000000001</v>
+      </c>
+      <c r="C12" s="5">
+        <f>Sheet1!C20</f>
+        <v>1.2250000000000001</v>
+      </c>
+      <c r="D12" s="5">
+        <f>Sheet1!C20</f>
+        <v>1.2250000000000001</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B13" s="8">
+        <v>1</v>
+      </c>
+      <c r="C13" s="8">
+        <v>1</v>
+      </c>
+      <c r="D13" s="8">
+        <v>1</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B14" s="17">
+        <f>Sheet1!C91</f>
+        <v>1</v>
+      </c>
+      <c r="C14" s="17">
+        <f>Sheet1!C92</f>
+        <v>1.2</v>
+      </c>
+      <c r="D14" s="17">
+        <f>Sheet1!C93</f>
+        <v>1</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B15" s="17">
+        <f>Sheet1!C94</f>
+        <v>0.85</v>
+      </c>
+      <c r="C15" s="17">
+        <f>Sheet1!C94</f>
+        <v>0.85</v>
+      </c>
+      <c r="D15" s="17">
+        <f>Sheet1!C94</f>
+        <v>0.85</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B17" s="6">
+        <f>ACOS(2*B6-1)</f>
+        <v>2.0943951023931957</v>
+      </c>
+      <c r="C17" s="6">
+        <f>ACOS(2*C6-1)</f>
+        <v>1.9823131728623846</v>
+      </c>
+      <c r="D17" s="6">
+        <f>ACOS(2*D6-1)</f>
+        <v>1.9823131728623846</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B18" s="6">
+        <f>PI()-B17</f>
+        <v>1.0471975511965974</v>
+      </c>
+      <c r="C18" s="6">
+        <f>PI()-C17</f>
+        <v>1.1592794807274085</v>
+      </c>
+      <c r="D18" s="6">
+        <f>PI()-D17</f>
+        <v>1.1592794807274085</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B19" s="10">
+        <f>-(B18*(COS(B17)-0.5)+SIN(B17)*(1-COS(B17)/2))/B6^2</f>
+        <v>-0.56534725654320894</v>
+      </c>
+      <c r="C19" s="10">
+        <f>-(C18*(COS(C17)-0.5)+SIN(C17)*(1-COS(C17)/2))/C6^2</f>
+        <v>-0.62740704594148844</v>
+      </c>
+      <c r="D19" s="10">
+        <f>-(D18*(COS(D17)-0.5)+SIN(D17)*(1-COS(D17)/2))/D6^2</f>
+        <v>-0.62740704594148844</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B20" s="10">
+        <f>-(B18^2*(COS(B17)-0.5)+B18*SIN(B17)+SIN(B17)^2/2)/(PI()*B6^2)</f>
+        <v>-0.94360786423789478</v>
+      </c>
+      <c r="C20" s="10">
+        <f>-(C18^2*(COS(C17)-0.5)+C18*SIN(C17)+SIN(C17)^2/2)/(PI()*C6^2)</f>
+        <v>-0.96540266006846076</v>
+      </c>
+      <c r="D20" s="10">
+        <f>-(D18^2*(COS(D17)-0.5)+D18*SIN(D17)+SIN(D17)^2/2)/(PI()*D6^2)</f>
+        <v>-0.96540266006846076</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B22" s="6">
+        <f>RADIANS(B10)</f>
+        <v>0</v>
+      </c>
+      <c r="C22" s="6">
+        <f>RADIANS(C10)</f>
+        <v>1.7453292519943295E-2</v>
+      </c>
+      <c r="D22" s="6">
+        <f>RADIANS(D10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B23" s="6">
+        <f>RADIANS(B9)</f>
+        <v>0.26179938779914941</v>
+      </c>
+      <c r="C23" s="6">
+        <f>RADIANS(C9)</f>
+        <v>0.52359877559829882</v>
+      </c>
+      <c r="D23" s="6">
+        <f>RADIANS(D9)</f>
+        <v>0.52359877559829882</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B24" s="10">
+        <f>B19*B22+B20*B23</f>
+        <v>-0.24703596117994375</v>
+      </c>
+      <c r="C24" s="10">
+        <f>C19*C22+C20*C23</f>
+        <v>-0.51643396947307707</v>
+      </c>
+      <c r="D24" s="10">
+        <f>D19*D22+D20*D23</f>
+        <v>-0.50548365077118673</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B25" s="5">
+        <f>0.5*B12*B11^2</f>
+        <v>324.01250000000005</v>
+      </c>
+      <c r="C25" s="5">
+        <f>0.5*C12*C11^2</f>
+        <v>324.01250000000005</v>
+      </c>
+      <c r="D25" s="5">
+        <f>0.5*D12*D11^2</f>
+        <v>324.01250000000005</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B26" s="5">
+        <f>B7*B8</f>
+        <v>2.4118557639774177E-2</v>
+      </c>
+      <c r="C26" s="5">
+        <f>C7*C8</f>
+        <v>3.1693199999999998E-2</v>
+      </c>
+      <c r="D26" s="5">
+        <f>D7*D8</f>
+        <v>1.42884E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="B27" s="12">
+        <f>B24*B25*B26*B7</f>
+        <v>-0.2069388778157791</v>
+      </c>
+      <c r="C27" s="12">
+        <f>C24*C25*C26*C7</f>
+        <v>-0.31183149980507596</v>
+      </c>
+      <c r="D27" s="12">
+        <f>D24*D25*D26*D7</f>
+        <v>-0.13760360258695806</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B28" s="6">
+        <f>ABS(B27)*B13</f>
+        <v>0.2069388778157791</v>
+      </c>
+      <c r="C28" s="6">
+        <f>ABS(C27)*C13</f>
+        <v>0.31183149980507596</v>
+      </c>
+      <c r="D28" s="6">
+        <f>ABS(D27)*D13</f>
+        <v>0.13760360258695806</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="B29" s="13">
+        <f>B28*B14/B15*141.612</f>
+        <v>34.476503959115426</v>
+      </c>
+      <c r="C29" s="13">
+        <f>C28*C14/C15*141.612</f>
+        <v>62.342233906441997</v>
+      </c>
+      <c r="D29" s="13">
+        <f>D28*D14/D15*141.612</f>
+        <v>22.925083964169769</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B31" s="14"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B32" s="6" t="str">
+        <f>IF(B31="","",B24/B31)</f>
+        <v/>
+      </c>
+      <c r="C32" s="6" t="str">
+        <f>IF(C31="","",C24/C31)</f>
+        <v/>
+      </c>
+      <c r="D32" s="6" t="str">
+        <f>IF(D31="","",D24/D31)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ceaa8977d2236823/Documents/GitHub/451-DBF-Team01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="81" documentId="13_ncr:1_{60007970-5A4F-400B-B565-6CA8D1228FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D0CB0C3-AA3F-455A-B1AE-807F3BF48BD3}"/>
+  <xr:revisionPtr revIDLastSave="83" documentId="13_ncr:1_{60007970-5A4F-400B-B565-6CA8D1228FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24AC53F3-43CB-4F1E-92F8-F5B6D7266914}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="-26790" yWindow="2955" windowWidth="21600" windowHeight="11235" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -822,7 +822,7 @@
     <t>V_servo_rail</t>
   </si>
   <si>
-    <t>Servo rail (BEC output) voltage used to evaluate torque at the actual operating voltage</t>
+    <t>Servo rail (BEC output) voltage used to evaluate torque at the actual operating voltage -- matches the MG90S stall-torque rating quoted at 5.5V</t>
   </si>
 </sst>
 </file>
@@ -2862,7 +2862,7 @@
         <v>249</v>
       </c>
       <c r="C95">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="D95" t="s">
         <v>190</v>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ceaa8977d2236823/Documents/GitHub/451-DBF-Team01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="83" documentId="13_ncr:1_{60007970-5A4F-400B-B565-6CA8D1228FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24AC53F3-43CB-4F1E-92F8-F5B6D7266914}"/>
+  <xr:revisionPtr revIDLastSave="89" documentId="13_ncr:1_{60007970-5A4F-400B-B565-6CA8D1228FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2829B90-CE97-4288-87DE-2A6BB9766E4A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="265">
   <si>
     <t>Parameter</t>
   </si>
@@ -823,6 +823,12 @@
   </si>
   <si>
     <t>Servo rail (BEC output) voltage used to evaluate torque at the actual operating voltage -- matches the MG90S stall-torque rating quoted at 5.5V</t>
+  </si>
+  <si>
+    <t>CL_max_neg</t>
+  </si>
+  <si>
+    <t>Negative (inverted-flight) max lift coefficient -- ASSUMPTION, not measured; refine with an XFLR5 negative-alpha sweep</t>
   </si>
 </sst>
 </file>
@@ -965,8 +971,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:F95" totalsRowShown="0">
-  <autoFilter ref="A1:F95" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:F96" totalsRowShown="0">
+  <autoFilter ref="A1:F96" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E43">
     <sortCondition ref="B1:B101"/>
   </sortState>
@@ -1245,7 +1251,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F95"/>
+  <dimension ref="A1:F96"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.44140625" bestFit="1" customWidth="1"/>
@@ -2869,6 +2875,23 @@
       </c>
       <c r="E95" t="s">
         <v>262</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>263</v>
+      </c>
+      <c r="B96" t="s">
+        <v>7</v>
+      </c>
+      <c r="C96">
+        <v>-0.8</v>
+      </c>
+      <c r="D96" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" t="s">
+        <v>264</v>
       </c>
     </row>
   </sheetData>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ceaa8977d2236823/Documents/GitHub/451-DBF-Team01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="89" documentId="13_ncr:1_{60007970-5A4F-400B-B565-6CA8D1228FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2829B90-CE97-4288-87DE-2A6BB9766E4A}"/>
+  <xr:revisionPtr revIDLastSave="129" documentId="13_ncr:1_{60007970-5A4F-400B-B565-6CA8D1228FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{927E2BE3-773B-4076-9F96-1EE500C81D59}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="283">
   <si>
     <t>Parameter</t>
   </si>
@@ -829,6 +829,60 @@
   </si>
   <si>
     <t>Negative (inverted-flight) max lift coefficient -- ASSUMPTION, not measured; refine with an XFLR5 negative-alpha sweep</t>
+  </si>
+  <si>
+    <t>x_spar</t>
+  </si>
+  <si>
+    <t>structures</t>
+  </si>
+  <si>
+    <t>Wing spar/shear-center location, fraction of chord aft of LE -- ASSUMPTION, set once the spar is chosen; sign of (x_spar-x_ac) decides whether Cm_ac adds to or opposes the lift-offset torque</t>
+  </si>
+  <si>
+    <t>eta_h</t>
+  </si>
+  <si>
+    <t>Horizontal tail dynamic-pressure ratio q_tail/q_freestream -- ASSUMPTION (high-wing/clear tail), refine from wake/downwash data</t>
+  </si>
+  <si>
+    <t>eta_v</t>
+  </si>
+  <si>
+    <t>Vertical tail (fin) dynamic-pressure ratio -- ASSUMPTION, refine from wake/downwash data</t>
+  </si>
+  <si>
+    <t>CL_max_tail</t>
+  </si>
+  <si>
+    <t>Max lift coefficient of the tail's symmetric section (NACA 0010) -- ASSUMPTION, refine with an XFLR5 sweep</t>
+  </si>
+  <si>
+    <t>D_fus_tail</t>
+  </si>
+  <si>
+    <t>Fuselage/tailboom depth at the fin root -- ASSUMPTION, measure once the boom is sized</t>
+  </si>
+  <si>
+    <t>x_LE_wing</t>
+  </si>
+  <si>
+    <t>Fuselage station of the wing's MAC leading edge, from the nose -- ASSUMPTION/PLACEHOLDER, set from your actual layout</t>
+  </si>
+  <si>
+    <t>sink_rate</t>
+  </si>
+  <si>
+    <t>Design sink rate for the landing load factor derivation -- ASSUMPTION, state your source</t>
+  </si>
+  <si>
+    <t>gear_stiffness</t>
+  </si>
+  <si>
+    <t>N/m</t>
+  </si>
+  <si>
+    <t>Main landing gear vertical stiffness (both legs) -- PLACEHOLDER, replace once gear is selected/tested</t>
   </si>
 </sst>
 </file>
@@ -971,8 +1025,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:F96" totalsRowShown="0">
-  <autoFilter ref="A1:F96" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:F104" totalsRowShown="0">
+  <autoFilter ref="A1:F104" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E43">
     <sortCondition ref="B1:B101"/>
   </sortState>
@@ -1251,7 +1305,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F96"/>
+  <dimension ref="A1:F104"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.44140625" bestFit="1" customWidth="1"/>
@@ -2892,6 +2946,142 @@
       </c>
       <c r="E96" t="s">
         <v>264</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>265</v>
+      </c>
+      <c r="B97" t="s">
+        <v>266</v>
+      </c>
+      <c r="C97">
+        <v>0.3</v>
+      </c>
+      <c r="D97" t="s">
+        <v>8</v>
+      </c>
+      <c r="E97" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>268</v>
+      </c>
+      <c r="B98" t="s">
+        <v>266</v>
+      </c>
+      <c r="C98">
+        <v>1</v>
+      </c>
+      <c r="D98" t="s">
+        <v>8</v>
+      </c>
+      <c r="E98" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>270</v>
+      </c>
+      <c r="B99" t="s">
+        <v>266</v>
+      </c>
+      <c r="C99">
+        <v>1</v>
+      </c>
+      <c r="D99" t="s">
+        <v>8</v>
+      </c>
+      <c r="E99" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>272</v>
+      </c>
+      <c r="B100" t="s">
+        <v>266</v>
+      </c>
+      <c r="C100">
+        <v>1</v>
+      </c>
+      <c r="D100" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>274</v>
+      </c>
+      <c r="B101" t="s">
+        <v>266</v>
+      </c>
+      <c r="C101">
+        <v>0.03</v>
+      </c>
+      <c r="D101" t="s">
+        <v>59</v>
+      </c>
+      <c r="E101" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>276</v>
+      </c>
+      <c r="B102" t="s">
+        <v>266</v>
+      </c>
+      <c r="C102">
+        <v>0.3</v>
+      </c>
+      <c r="D102" t="s">
+        <v>59</v>
+      </c>
+      <c r="E102" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>278</v>
+      </c>
+      <c r="B103" t="s">
+        <v>266</v>
+      </c>
+      <c r="C103">
+        <v>0.5</v>
+      </c>
+      <c r="D103" t="s">
+        <v>137</v>
+      </c>
+      <c r="E103" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>280</v>
+      </c>
+      <c r="B104" t="s">
+        <v>266</v>
+      </c>
+      <c r="C104">
+        <v>5000</v>
+      </c>
+      <c r="D104" t="s">
+        <v>281</v>
+      </c>
+      <c r="E104" t="s">
+        <v>282</v>
       </c>
     </row>
   </sheetData>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ceaa8977d2236823/Documents/GitHub/451-DBF-Team01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="129" documentId="13_ncr:1_{60007970-5A4F-400B-B565-6CA8D1228FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{927E2BE3-773B-4076-9F96-1EE500C81D59}"/>
+  <xr:revisionPtr revIDLastSave="216" documentId="13_ncr:1_{60007970-5A4F-400B-B565-6CA8D1228FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{184DB1EF-0713-4BEA-BBDD-63D93BF77A7B}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="9960" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Hinge Moments" sheetId="2" r:id="rId2"/>
+    <sheet name="MassBudget" sheetId="3" r:id="rId2"/>
+    <sheet name="Hinge Moments" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="312">
   <si>
     <t>Parameter</t>
   </si>
@@ -883,6 +884,93 @@
   </si>
   <si>
     <t>Main landing gear vertical stiffness (both legs) -- PLACEHOLDER, replace once gear is selected/tested</t>
+  </si>
+  <si>
+    <t>Component</t>
+  </si>
+  <si>
+    <t>Mass_g</t>
+  </si>
+  <si>
+    <t>Station_m</t>
+  </si>
+  <si>
+    <t>Propeller+spinner</t>
+  </si>
+  <si>
+    <t>PLACEHOLDER</t>
+  </si>
+  <si>
+    <t>Motor</t>
+  </si>
+  <si>
+    <t>Motor mount/firewall</t>
+  </si>
+  <si>
+    <t>ESC</t>
+  </si>
+  <si>
+    <t>Nose gear</t>
+  </si>
+  <si>
+    <t>Battery</t>
+  </si>
+  <si>
+    <t>PLACEHOLDER (sized from W_e_frac/W_pay split)</t>
+  </si>
+  <si>
+    <t>Flight controller/avionics</t>
+  </si>
+  <si>
+    <t>Wiring + connectors</t>
+  </si>
+  <si>
+    <t>Misc electronics</t>
+  </si>
+  <si>
+    <t>PLACEHOLDER filler</t>
+  </si>
+  <si>
+    <t>Servo, aileron 1</t>
+  </si>
+  <si>
+    <t>REAL -- MG90S spec, A7</t>
+  </si>
+  <si>
+    <t>Servo, aileron 2</t>
+  </si>
+  <si>
+    <t>Payload cube</t>
+  </si>
+  <si>
+    <t>REAL -- Sheet1 W_pay</t>
+  </si>
+  <si>
+    <t>Wing (spar+foam)</t>
+  </si>
+  <si>
+    <t>PLACEHOLDER, station ~ x_ac</t>
+  </si>
+  <si>
+    <t>Main gear (pair)</t>
+  </si>
+  <si>
+    <t>Fuselage (keel+shell)</t>
+  </si>
+  <si>
+    <t>Servo, elevator</t>
+  </si>
+  <si>
+    <t>Servo, rudder</t>
+  </si>
+  <si>
+    <t>H-tail (spar+foam)</t>
+  </si>
+  <si>
+    <t>PLACEHOLDER, station ~ x_t</t>
+  </si>
+  <si>
+    <t>V-tail (spar+foam)</t>
   </si>
 </sst>
 </file>
@@ -894,7 +982,7 @@
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -940,6 +1028,14 @@
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -987,7 +1083,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -1006,6 +1102,7 @@
     <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="166" fontId="5" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="5" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3093,6 +3190,300 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFCC8514-E0AF-4C67-BF86-8649FC702924}">
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="26.77734375" customWidth="1"/>
+    <col min="4" max="4" width="40.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="18" t="s">
+        <v>283</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>284</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>285</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B2">
+        <v>40</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>288</v>
+      </c>
+      <c r="B3">
+        <v>180</v>
+      </c>
+      <c r="C3">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>289</v>
+      </c>
+      <c r="B4">
+        <v>35</v>
+      </c>
+      <c r="C4">
+        <v>5.5E-2</v>
+      </c>
+      <c r="D4" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>290</v>
+      </c>
+      <c r="B5">
+        <v>50</v>
+      </c>
+      <c r="C5">
+        <v>0.09</v>
+      </c>
+      <c r="D5" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>291</v>
+      </c>
+      <c r="B6">
+        <v>70</v>
+      </c>
+      <c r="C6">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="D6" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>292</v>
+      </c>
+      <c r="B7">
+        <v>680</v>
+      </c>
+      <c r="C7">
+        <v>0.12</v>
+      </c>
+      <c r="D7" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>294</v>
+      </c>
+      <c r="B8">
+        <v>90</v>
+      </c>
+      <c r="C8">
+        <v>0.23</v>
+      </c>
+      <c r="D8" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>295</v>
+      </c>
+      <c r="B9">
+        <v>100</v>
+      </c>
+      <c r="C9">
+        <v>0.3</v>
+      </c>
+      <c r="D9" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>296</v>
+      </c>
+      <c r="B10">
+        <v>400</v>
+      </c>
+      <c r="C10">
+        <v>0.32</v>
+      </c>
+      <c r="D10" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>298</v>
+      </c>
+      <c r="B11">
+        <v>13.4</v>
+      </c>
+      <c r="C11">
+        <v>0.4</v>
+      </c>
+      <c r="D11" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>300</v>
+      </c>
+      <c r="B12">
+        <v>13.4</v>
+      </c>
+      <c r="C12">
+        <v>0.4</v>
+      </c>
+      <c r="D12" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>301</v>
+      </c>
+      <c r="B13">
+        <v>520</v>
+      </c>
+      <c r="C13">
+        <v>0.4</v>
+      </c>
+      <c r="D13" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>303</v>
+      </c>
+      <c r="B14">
+        <v>1400</v>
+      </c>
+      <c r="C14">
+        <v>0.40699999999999997</v>
+      </c>
+      <c r="D14" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>305</v>
+      </c>
+      <c r="B15">
+        <v>220</v>
+      </c>
+      <c r="C15">
+        <v>0.43</v>
+      </c>
+      <c r="D15" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>306</v>
+      </c>
+      <c r="B16">
+        <v>1900</v>
+      </c>
+      <c r="C16">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="D16" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>307</v>
+      </c>
+      <c r="B17">
+        <v>13.4</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>308</v>
+      </c>
+      <c r="B18">
+        <v>13.4</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>309</v>
+      </c>
+      <c r="B19">
+        <v>120</v>
+      </c>
+      <c r="C19">
+        <v>1.05</v>
+      </c>
+      <c r="D19" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>311</v>
+      </c>
+      <c r="B20">
+        <v>80</v>
+      </c>
+      <c r="C20">
+        <v>1.05</v>
+      </c>
+      <c r="D20" t="s">
+        <v>310</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{118BE621-EF6B-4648-868E-9937B9C5B685}">
   <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ceaa8977d2236823/Documents/GitHub/451-DBF-Team01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="216" documentId="13_ncr:1_{60007970-5A4F-400B-B565-6CA8D1228FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{184DB1EF-0713-4BEA-BBDD-63D93BF77A7B}"/>
+  <xr:revisionPtr revIDLastSave="273" documentId="13_ncr:1_{60007970-5A4F-400B-B565-6CA8D1228FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2540A57B-32A3-4A49-866F-5AA261EF41B3}"/>
   <bookViews>
-    <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="9960" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="306">
   <si>
     <t>Parameter</t>
   </si>
@@ -898,9 +898,6 @@
     <t>Propeller+spinner</t>
   </si>
   <si>
-    <t>PLACEHOLDER</t>
-  </si>
-  <si>
     <t>Motor</t>
   </si>
   <si>
@@ -916,9 +913,6 @@
     <t>Battery</t>
   </si>
   <si>
-    <t>PLACEHOLDER (sized from W_e_frac/W_pay split)</t>
-  </si>
-  <si>
     <t>Flight controller/avionics</t>
   </si>
   <si>
@@ -928,30 +922,18 @@
     <t>Misc electronics</t>
   </si>
   <si>
-    <t>PLACEHOLDER filler</t>
-  </si>
-  <si>
     <t>Servo, aileron 1</t>
   </si>
   <si>
-    <t>REAL -- MG90S spec, A7</t>
-  </si>
-  <si>
     <t>Servo, aileron 2</t>
   </si>
   <si>
     <t>Payload cube</t>
   </si>
   <si>
-    <t>REAL -- Sheet1 W_pay</t>
-  </si>
-  <si>
     <t>Wing (spar+foam)</t>
   </si>
   <si>
-    <t>PLACEHOLDER, station ~ x_ac</t>
-  </si>
-  <si>
     <t>Main gear (pair)</t>
   </si>
   <si>
@@ -967,10 +949,10 @@
     <t>H-tail (spar+foam)</t>
   </si>
   <si>
-    <t>PLACEHOLDER, station ~ x_t</t>
-  </si>
-  <si>
     <t>V-tail (spar+foam)</t>
+  </si>
+  <si>
+    <t>PLACEHOLDER, rescaled to match iterated MTOM</t>
   </si>
 </sst>
 </file>
@@ -1038,7 +1020,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1069,6 +1051,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1083,7 +1071,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -1103,6 +1091,16 @@
     <xf numFmtId="166" fontId="5" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="5" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3049,10 +3047,10 @@
       <c r="A97" t="s">
         <v>265</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" s="19" t="s">
         <v>266</v>
       </c>
-      <c r="C97">
+      <c r="C97" s="19">
         <v>0.3</v>
       </c>
       <c r="D97" t="s">
@@ -3066,10 +3064,10 @@
       <c r="A98" t="s">
         <v>268</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" s="19" t="s">
         <v>266</v>
       </c>
-      <c r="C98">
+      <c r="C98" s="19">
         <v>1</v>
       </c>
       <c r="D98" t="s">
@@ -3083,10 +3081,10 @@
       <c r="A99" t="s">
         <v>270</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" s="19" t="s">
         <v>266</v>
       </c>
-      <c r="C99">
+      <c r="C99" s="19">
         <v>1</v>
       </c>
       <c r="D99" t="s">
@@ -3100,10 +3098,10 @@
       <c r="A100" t="s">
         <v>272</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" s="19" t="s">
         <v>266</v>
       </c>
-      <c r="C100">
+      <c r="C100" s="19">
         <v>1</v>
       </c>
       <c r="D100" t="s">
@@ -3117,10 +3115,10 @@
       <c r="A101" t="s">
         <v>274</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" s="19" t="s">
         <v>266</v>
       </c>
-      <c r="C101">
+      <c r="C101" s="19">
         <v>0.03</v>
       </c>
       <c r="D101" t="s">
@@ -3134,10 +3132,10 @@
       <c r="A102" t="s">
         <v>276</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" s="19" t="s">
         <v>266</v>
       </c>
-      <c r="C102">
+      <c r="C102" s="19">
         <v>0.3</v>
       </c>
       <c r="D102" t="s">
@@ -3151,10 +3149,10 @@
       <c r="A103" t="s">
         <v>278</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" s="19" t="s">
         <v>266</v>
       </c>
-      <c r="C103">
+      <c r="C103" s="19">
         <v>0.5</v>
       </c>
       <c r="D103" t="s">
@@ -3168,10 +3166,10 @@
       <c r="A104" t="s">
         <v>280</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" s="19" t="s">
         <v>266</v>
       </c>
-      <c r="C104">
+      <c r="C104" s="19">
         <v>5000</v>
       </c>
       <c r="D104" t="s">
@@ -3194,21 +3192,21 @@
   <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.77734375" customWidth="1"/>
-    <col min="4" max="4" width="40.77734375" customWidth="1"/>
+    <col min="1" max="1" width="32.5546875" customWidth="1"/>
+    <col min="2" max="3" width="32.5546875" style="21" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>283</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="20" t="s">
         <v>284</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="20" t="s">
         <v>285</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -3216,266 +3214,251 @@
       <c r="A2" t="s">
         <v>286</v>
       </c>
-      <c r="B2">
-        <v>40</v>
-      </c>
-      <c r="C2">
+      <c r="B2" s="22">
+        <v>25.9</v>
+      </c>
+      <c r="C2" s="22">
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>288</v>
-      </c>
-      <c r="B3">
-        <v>180</v>
-      </c>
-      <c r="C3">
+        <v>287</v>
+      </c>
+      <c r="B3" s="22">
+        <v>116.7</v>
+      </c>
+      <c r="C3" s="22">
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="D3" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>289</v>
-      </c>
-      <c r="B4">
-        <v>35</v>
-      </c>
-      <c r="C4">
+        <v>288</v>
+      </c>
+      <c r="B4" s="22">
+        <v>22.7</v>
+      </c>
+      <c r="C4" s="22">
         <v>5.5E-2</v>
       </c>
       <c r="D4" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>290</v>
-      </c>
-      <c r="B5">
-        <v>50</v>
-      </c>
-      <c r="C5">
+        <v>289</v>
+      </c>
+      <c r="B5" s="22">
+        <v>32.4</v>
+      </c>
+      <c r="C5" s="22">
         <v>0.09</v>
       </c>
       <c r="D5" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>291</v>
-      </c>
-      <c r="B6">
-        <v>70</v>
-      </c>
-      <c r="C6">
+        <v>290</v>
+      </c>
+      <c r="B6" s="22">
+        <v>45.4</v>
+      </c>
+      <c r="C6" s="22">
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="D6" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>292</v>
-      </c>
-      <c r="B7">
-        <v>680</v>
-      </c>
-      <c r="C7">
+        <v>291</v>
+      </c>
+      <c r="B7" s="22">
+        <v>440.8</v>
+      </c>
+      <c r="C7" s="22">
         <v>0.12</v>
       </c>
       <c r="D7" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>294</v>
-      </c>
-      <c r="B8">
-        <v>90</v>
-      </c>
-      <c r="C8">
+        <v>292</v>
+      </c>
+      <c r="B8" s="22">
+        <v>58.3</v>
+      </c>
+      <c r="C8" s="22">
         <v>0.23</v>
       </c>
       <c r="D8" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>295</v>
-      </c>
-      <c r="B9">
-        <v>100</v>
-      </c>
-      <c r="C9">
+        <v>293</v>
+      </c>
+      <c r="B9" s="22">
+        <v>64.8</v>
+      </c>
+      <c r="C9" s="22">
         <v>0.3</v>
       </c>
       <c r="D9" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>296</v>
-      </c>
-      <c r="B10">
-        <v>400</v>
-      </c>
-      <c r="C10">
+        <v>294</v>
+      </c>
+      <c r="B10" s="22">
+        <v>259.3</v>
+      </c>
+      <c r="C10" s="22">
         <v>0.32</v>
       </c>
       <c r="D10" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>298</v>
-      </c>
-      <c r="B11">
+        <v>295</v>
+      </c>
+      <c r="B11" s="22">
         <v>13.4</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="22">
         <v>0.4</v>
-      </c>
-      <c r="D11" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>300</v>
-      </c>
-      <c r="B12">
+        <v>296</v>
+      </c>
+      <c r="B12" s="22">
         <v>13.4</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="22">
         <v>0.4</v>
-      </c>
-      <c r="D12" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>301</v>
-      </c>
-      <c r="B13">
+        <v>297</v>
+      </c>
+      <c r="B13" s="21">
         <v>520</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="22">
         <v>0.4</v>
-      </c>
-      <c r="D13" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>303</v>
-      </c>
-      <c r="B14">
-        <v>1400</v>
-      </c>
-      <c r="C14">
+        <v>298</v>
+      </c>
+      <c r="B14" s="22">
+        <v>907.6</v>
+      </c>
+      <c r="C14" s="22">
         <v>0.40699999999999997</v>
       </c>
       <c r="D14" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>299</v>
+      </c>
+      <c r="B15" s="22">
+        <v>142.6</v>
+      </c>
+      <c r="C15" s="22">
+        <v>0.43</v>
+      </c>
+      <c r="D15" t="s">
         <v>305</v>
-      </c>
-      <c r="B15">
-        <v>220</v>
-      </c>
-      <c r="C15">
-        <v>0.43</v>
-      </c>
-      <c r="D15" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>306</v>
-      </c>
-      <c r="B16">
-        <v>1900</v>
-      </c>
-      <c r="C16">
+        <v>300</v>
+      </c>
+      <c r="B16" s="22">
+        <v>1231.8</v>
+      </c>
+      <c r="C16" s="22">
         <v>0.55000000000000004</v>
       </c>
       <c r="D16" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>307</v>
-      </c>
-      <c r="B17">
+        <v>301</v>
+      </c>
+      <c r="B17" s="22">
         <v>13.4</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="22">
         <v>1</v>
-      </c>
-      <c r="D17" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>308</v>
-      </c>
-      <c r="B18">
+        <v>302</v>
+      </c>
+      <c r="B18" s="22">
         <v>13.4</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="22">
         <v>1</v>
-      </c>
-      <c r="D18" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>309</v>
-      </c>
-      <c r="B19">
-        <v>120</v>
-      </c>
-      <c r="C19">
+        <v>303</v>
+      </c>
+      <c r="B19" s="22">
+        <v>77.8</v>
+      </c>
+      <c r="C19" s="22">
         <v>1.05</v>
       </c>
       <c r="D19" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>311</v>
-      </c>
-      <c r="B20">
-        <v>80</v>
-      </c>
-      <c r="C20">
+        <v>304</v>
+      </c>
+      <c r="B20" s="22">
+        <v>51.9</v>
+      </c>
+      <c r="C20" s="22">
         <v>1.05</v>
       </c>
       <c r="D20" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
     </row>
   </sheetData>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ceaa8977d2236823/Documents/GitHub/451-DBF-Team01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="273" documentId="13_ncr:1_{60007970-5A4F-400B-B565-6CA8D1228FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2540A57B-32A3-4A49-866F-5AA261EF41B3}"/>
+  <xr:revisionPtr revIDLastSave="340" documentId="13_ncr:1_{60007970-5A4F-400B-B565-6CA8D1228FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17327AF0-D2A2-401A-AFA4-5BA44D815C39}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="306">
   <si>
     <t>Parameter</t>
   </si>
@@ -892,9 +892,6 @@
     <t>Mass_g</t>
   </si>
   <si>
-    <t>Station_m</t>
-  </si>
-  <si>
     <t>Propeller+spinner</t>
   </si>
   <si>
@@ -946,13 +943,16 @@
     <t>Servo, rudder</t>
   </si>
   <si>
-    <t>H-tail (spar+foam)</t>
-  </si>
-  <si>
     <t>V-tail (spar+foam)</t>
   </si>
   <si>
-    <t>PLACEHOLDER, rescaled to match iterated MTOM</t>
+    <t>Height_m</t>
+  </si>
+  <si>
+    <t>Horizontal tail (spar+foam)</t>
+  </si>
+  <si>
+    <t>X_m</t>
   </si>
 </sst>
 </file>
@@ -1407,8 +1407,8 @@
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="10.6640625" customWidth="1"/>
-    <col min="5" max="5" width="44" customWidth="1"/>
-    <col min="6" max="6" width="60" customWidth="1"/>
+    <col min="5" max="5" width="168.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -3194,6 +3194,7 @@
   <cols>
     <col min="1" max="1" width="32.5546875" customWidth="1"/>
     <col min="2" max="3" width="32.5546875" style="21" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" style="21" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -3204,15 +3205,15 @@
         <v>284</v>
       </c>
       <c r="C1" s="20" t="s">
-        <v>285</v>
-      </c>
-      <c r="D1" t="s">
-        <v>5</v>
+        <v>305</v>
+      </c>
+      <c r="D1" s="21" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B2" s="22">
         <v>25.9</v>
@@ -3220,13 +3221,13 @@
       <c r="C2" s="22">
         <v>0</v>
       </c>
-      <c r="D2" t="s">
-        <v>305</v>
+      <c r="D2" s="22">
+        <v>2.8000000000000001E-2</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B3" s="22">
         <v>116.7</v>
@@ -3234,13 +3235,13 @@
       <c r="C3" s="22">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="D3" t="s">
-        <v>305</v>
+      <c r="D3" s="22">
+        <v>2.8000000000000001E-2</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B4" s="22">
         <v>22.7</v>
@@ -3248,13 +3249,13 @@
       <c r="C4" s="22">
         <v>5.5E-2</v>
       </c>
-      <c r="D4" t="s">
-        <v>305</v>
+      <c r="D4" s="22">
+        <v>2.8000000000000001E-2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B5" s="22">
         <v>32.4</v>
@@ -3262,13 +3263,13 @@
       <c r="C5" s="22">
         <v>0.09</v>
       </c>
-      <c r="D5" t="s">
-        <v>305</v>
+      <c r="D5" s="22">
+        <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B6" s="22">
         <v>45.4</v>
@@ -3276,13 +3277,13 @@
       <c r="C6" s="22">
         <v>9.5000000000000001E-2</v>
       </c>
-      <c r="D6" t="s">
-        <v>305</v>
+      <c r="D6" s="22">
+        <v>-4.4999999999999998E-2</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B7" s="22">
         <v>440.8</v>
@@ -3290,13 +3291,13 @@
       <c r="C7" s="22">
         <v>0.12</v>
       </c>
-      <c r="D7" t="s">
-        <v>305</v>
+      <c r="D7" s="22">
+        <v>1.4999999999999999E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B8" s="22">
         <v>58.3</v>
@@ -3304,13 +3305,13 @@
       <c r="C8" s="22">
         <v>0.23</v>
       </c>
-      <c r="D8" t="s">
-        <v>305</v>
+      <c r="D8" s="22">
+        <v>2.8000000000000001E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B9" s="22">
         <v>64.8</v>
@@ -3318,13 +3319,13 @@
       <c r="C9" s="22">
         <v>0.3</v>
       </c>
-      <c r="D9" t="s">
-        <v>305</v>
+      <c r="D9" s="22">
+        <v>2.8000000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B10" s="22">
         <v>259.3</v>
@@ -3332,13 +3333,13 @@
       <c r="C10" s="22">
         <v>0.32</v>
       </c>
-      <c r="D10" t="s">
-        <v>305</v>
+      <c r="D10" s="22">
+        <v>2.8000000000000001E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B11" s="22">
         <v>13.4</v>
@@ -3346,10 +3347,13 @@
       <c r="C11" s="22">
         <v>0.4</v>
       </c>
+      <c r="D11" s="22">
+        <v>5.5E-2</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B12" s="22">
         <v>13.4</v>
@@ -3357,10 +3361,13 @@
       <c r="C12" s="22">
         <v>0.4</v>
       </c>
+      <c r="D12" s="22">
+        <v>5.5E-2</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B13" s="21">
         <v>520</v>
@@ -3368,10 +3375,13 @@
       <c r="C13" s="22">
         <v>0.4</v>
       </c>
+      <c r="D13" s="22">
+        <v>2.8000000000000001E-2</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B14" s="22">
         <v>907.6</v>
@@ -3379,13 +3389,13 @@
       <c r="C14" s="22">
         <v>0.40699999999999997</v>
       </c>
-      <c r="D14" t="s">
-        <v>305</v>
+      <c r="D14" s="22">
+        <v>5.5E-2</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B15" s="22">
         <v>142.6</v>
@@ -3393,13 +3403,13 @@
       <c r="C15" s="22">
         <v>0.43</v>
       </c>
-      <c r="D15" t="s">
-        <v>305</v>
+      <c r="D15" s="22">
+        <v>-7.8E-2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B16" s="22">
         <v>1231.8</v>
@@ -3407,13 +3417,13 @@
       <c r="C16" s="22">
         <v>0.55000000000000004</v>
       </c>
-      <c r="D16" t="s">
-        <v>305</v>
+      <c r="D16" s="22">
+        <v>2.8000000000000001E-2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B17" s="22">
         <v>13.4</v>
@@ -3421,10 +3431,13 @@
       <c r="C17" s="22">
         <v>1</v>
       </c>
+      <c r="D17" s="22">
+        <v>1.4999999999999999E-2</v>
+      </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B18" s="22">
         <v>13.4</v>
@@ -3432,10 +3445,13 @@
       <c r="C18" s="22">
         <v>1</v>
       </c>
+      <c r="D18" s="22">
+        <v>1.4999999999999999E-2</v>
+      </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B19" s="22">
         <v>77.8</v>
@@ -3443,13 +3459,13 @@
       <c r="C19" s="22">
         <v>1.05</v>
       </c>
-      <c r="D19" t="s">
-        <v>305</v>
+      <c r="D19" s="22">
+        <v>1.4999999999999999E-2</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B20" s="22">
         <v>51.9</v>
@@ -3457,8 +3473,8 @@
       <c r="C20" s="22">
         <v>1.05</v>
       </c>
-      <c r="D20" t="s">
-        <v>305</v>
+      <c r="D20" s="22">
+        <v>0.15</v>
       </c>
     </row>
   </sheetData>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ceaa8977d2236823/Documents/GitHub/451-DBF-Team01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="340" documentId="13_ncr:1_{60007970-5A4F-400B-B565-6CA8D1228FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17327AF0-D2A2-401A-AFA4-5BA44D815C39}"/>
+  <xr:revisionPtr revIDLastSave="352" documentId="13_ncr:1_{60007970-5A4F-400B-B565-6CA8D1228FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FE1296C-A7BA-4ACA-AB64-C16541545B99}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -829,63 +829,36 @@
     <t>CL_max_neg</t>
   </si>
   <si>
-    <t>Negative (inverted-flight) max lift coefficient -- ASSUMPTION, not measured; refine with an XFLR5 negative-alpha sweep</t>
-  </si>
-  <si>
     <t>x_spar</t>
   </si>
   <si>
     <t>structures</t>
   </si>
   <si>
-    <t>Wing spar/shear-center location, fraction of chord aft of LE -- ASSUMPTION, set once the spar is chosen; sign of (x_spar-x_ac) decides whether Cm_ac adds to or opposes the lift-offset torque</t>
-  </si>
-  <si>
     <t>eta_h</t>
   </si>
   <si>
-    <t>Horizontal tail dynamic-pressure ratio q_tail/q_freestream -- ASSUMPTION (high-wing/clear tail), refine from wake/downwash data</t>
-  </si>
-  <si>
     <t>eta_v</t>
   </si>
   <si>
-    <t>Vertical tail (fin) dynamic-pressure ratio -- ASSUMPTION, refine from wake/downwash data</t>
-  </si>
-  <si>
     <t>CL_max_tail</t>
   </si>
   <si>
-    <t>Max lift coefficient of the tail's symmetric section (NACA 0010) -- ASSUMPTION, refine with an XFLR5 sweep</t>
-  </si>
-  <si>
     <t>D_fus_tail</t>
   </si>
   <si>
-    <t>Fuselage/tailboom depth at the fin root -- ASSUMPTION, measure once the boom is sized</t>
-  </si>
-  <si>
     <t>x_LE_wing</t>
   </si>
   <si>
-    <t>Fuselage station of the wing's MAC leading edge, from the nose -- ASSUMPTION/PLACEHOLDER, set from your actual layout</t>
-  </si>
-  <si>
     <t>sink_rate</t>
   </si>
   <si>
-    <t>Design sink rate for the landing load factor derivation -- ASSUMPTION, state your source</t>
-  </si>
-  <si>
     <t>gear_stiffness</t>
   </si>
   <si>
     <t>N/m</t>
   </si>
   <si>
-    <t>Main landing gear vertical stiffness (both legs) -- PLACEHOLDER, replace once gear is selected/tested</t>
-  </si>
-  <si>
     <t>Component</t>
   </si>
   <si>
@@ -946,13 +919,40 @@
     <t>V-tail (spar+foam)</t>
   </si>
   <si>
-    <t>Height_m</t>
-  </si>
-  <si>
     <t>Horizontal tail (spar+foam)</t>
   </si>
   <si>
     <t>X_m</t>
+  </si>
+  <si>
+    <t>Negative (inverted-flight) max lift coefficient</t>
+  </si>
+  <si>
+    <t>Wing spar/shear-center location, fraction of chord aft of LE</t>
+  </si>
+  <si>
+    <t>Horizontal tail dynamic-pressure ratio q_tail/q_freestream</t>
+  </si>
+  <si>
+    <t>Vertical tail (fin) dynamic-pressure ratio</t>
+  </si>
+  <si>
+    <t>Max lift coefficient of the tail's symmetric section (NACA 0010)</t>
+  </si>
+  <si>
+    <t>Fuselage/tailboom depth at the fin root</t>
+  </si>
+  <si>
+    <t>Fuselage station of the wing's MAC leading edge, from the nose</t>
+  </si>
+  <si>
+    <t>Design sink rate for the landing load factor derivation</t>
+  </si>
+  <si>
+    <t>Main landing gear vertical stiffness (both legs)</t>
+  </si>
+  <si>
+    <t>Z_m</t>
   </si>
 </sst>
 </file>
@@ -3030,25 +3030,25 @@
       <c r="A96" t="s">
         <v>263</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="C96">
+      <c r="C96" s="19">
         <v>-0.8</v>
       </c>
       <c r="D96" t="s">
         <v>8</v>
       </c>
       <c r="E96" t="s">
-        <v>264</v>
+        <v>296</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
+        <v>264</v>
+      </c>
+      <c r="B97" s="19" t="s">
         <v>265</v>
-      </c>
-      <c r="B97" s="19" t="s">
-        <v>266</v>
       </c>
       <c r="C97" s="19">
         <v>0.3</v>
@@ -3057,15 +3057,15 @@
         <v>8</v>
       </c>
       <c r="E97" t="s">
-        <v>267</v>
+        <v>297</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B98" s="19" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C98" s="19">
         <v>1</v>
@@ -3074,15 +3074,15 @@
         <v>8</v>
       </c>
       <c r="E98" t="s">
-        <v>269</v>
+        <v>298</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B99" s="19" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C99" s="19">
         <v>1</v>
@@ -3091,15 +3091,15 @@
         <v>8</v>
       </c>
       <c r="E99" t="s">
-        <v>271</v>
+        <v>299</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B100" s="19" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C100" s="19">
         <v>1</v>
@@ -3108,15 +3108,15 @@
         <v>8</v>
       </c>
       <c r="E100" t="s">
-        <v>273</v>
+        <v>300</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="B101" s="19" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C101" s="19">
         <v>0.03</v>
@@ -3125,15 +3125,15 @@
         <v>59</v>
       </c>
       <c r="E101" t="s">
-        <v>275</v>
+        <v>301</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="B102" s="19" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C102" s="19">
         <v>0.3</v>
@@ -3142,15 +3142,15 @@
         <v>59</v>
       </c>
       <c r="E102" t="s">
-        <v>277</v>
+        <v>302</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="B103" s="19" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C103" s="19">
         <v>0.5</v>
@@ -3159,24 +3159,24 @@
         <v>137</v>
       </c>
       <c r="E103" t="s">
-        <v>279</v>
+        <v>303</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="B104" s="19" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C104" s="19">
         <v>5000</v>
       </c>
       <c r="D104" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="E104" t="s">
-        <v>282</v>
+        <v>304</v>
       </c>
     </row>
   </sheetData>
@@ -3199,21 +3199,21 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="C1" s="20" t="s">
+        <v>295</v>
+      </c>
+      <c r="D1" s="20" t="s">
         <v>305</v>
-      </c>
-      <c r="D1" s="21" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="B2" s="22">
         <v>25.9</v>
@@ -3227,7 +3227,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="B3" s="22">
         <v>116.7</v>
@@ -3241,7 +3241,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="B4" s="22">
         <v>22.7</v>
@@ -3255,7 +3255,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="B5" s="22">
         <v>32.4</v>
@@ -3269,7 +3269,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="B6" s="22">
         <v>45.4</v>
@@ -3283,7 +3283,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="B7" s="22">
         <v>440.8</v>
@@ -3297,7 +3297,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="B8" s="22">
         <v>58.3</v>
@@ -3311,7 +3311,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="B9" s="22">
         <v>64.8</v>
@@ -3325,7 +3325,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="B10" s="22">
         <v>259.3</v>
@@ -3339,7 +3339,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="B11" s="22">
         <v>13.4</v>
@@ -3353,7 +3353,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="B12" s="22">
         <v>13.4</v>
@@ -3367,7 +3367,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="B13" s="21">
         <v>520</v>
@@ -3381,7 +3381,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="B14" s="22">
         <v>907.6</v>
@@ -3395,7 +3395,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="B15" s="22">
         <v>142.6</v>
@@ -3409,7 +3409,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="B16" s="22">
         <v>1231.8</v>
@@ -3423,7 +3423,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="B17" s="22">
         <v>13.4</v>
@@ -3437,7 +3437,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="B18" s="22">
         <v>13.4</v>
@@ -3451,7 +3451,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="B19" s="22">
         <v>77.8</v>
@@ -3465,7 +3465,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="B20" s="22">
         <v>51.9</v>
@@ -3479,6 +3479,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ceaa8977d2236823/Documents/GitHub/451-DBF-Team01/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hudson/Documents/GitHub/451-DBF-Team01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="340" documentId="13_ncr:1_{60007970-5A4F-400B-B565-6CA8D1228FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17327AF0-D2A2-401A-AFA4-5BA44D815C39}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B07C9115-910C-EA49-AF5C-D506317D2282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -976,6 +976,7 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1401,17 +1402,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F104"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="10.6640625" customWidth="1"/>
-    <col min="5" max="5" width="168.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="168.1640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1431,7 +1432,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1448,7 +1449,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1465,7 +1466,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1482,7 +1483,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -1499,7 +1500,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -1516,7 +1517,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -1533,7 +1534,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -1550,7 +1551,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>205</v>
       </c>
@@ -1564,7 +1565,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -1581,7 +1582,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1598,7 +1599,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -1615,7 +1616,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -1632,7 +1633,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -1649,7 +1650,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -1666,7 +1667,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>35</v>
       </c>
@@ -1683,7 +1684,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>37</v>
       </c>
@@ -1700,7 +1701,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>39</v>
       </c>
@@ -1717,7 +1718,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>41</v>
       </c>
@@ -1734,7 +1735,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>45</v>
       </c>
@@ -1751,7 +1752,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -1768,7 +1769,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -1785,7 +1786,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -1802,7 +1803,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -1819,7 +1820,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>58</v>
       </c>
@@ -1836,7 +1837,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>61</v>
       </c>
@@ -1853,7 +1854,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>63</v>
       </c>
@@ -1870,7 +1871,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>65</v>
       </c>
@@ -1887,7 +1888,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -1904,7 +1905,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -1921,7 +1922,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>72</v>
       </c>
@@ -1938,7 +1939,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>74</v>
       </c>
@@ -1955,7 +1956,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>76</v>
       </c>
@@ -1972,7 +1973,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>78</v>
       </c>
@@ -1989,7 +1990,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>80</v>
       </c>
@@ -2006,7 +2007,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>82</v>
       </c>
@@ -2023,7 +2024,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>84</v>
       </c>
@@ -2040,7 +2041,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>86</v>
       </c>
@@ -2057,7 +2058,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>88</v>
       </c>
@@ -2074,7 +2075,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>90</v>
       </c>
@@ -2091,7 +2092,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>92</v>
       </c>
@@ -2108,7 +2109,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>94</v>
       </c>
@@ -2125,7 +2126,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>96</v>
       </c>
@@ -2142,7 +2143,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>98</v>
       </c>
@@ -2159,7 +2160,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>100</v>
       </c>
@@ -2176,7 +2177,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>103</v>
       </c>
@@ -2193,7 +2194,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>105</v>
       </c>
@@ -2210,7 +2211,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>107</v>
       </c>
@@ -2227,7 +2228,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>109</v>
       </c>
@@ -2244,7 +2245,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>111</v>
       </c>
@@ -2252,7 +2253,7 @@
         <v>56</v>
       </c>
       <c r="C50">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="D50" t="s">
         <v>8</v>
@@ -2261,7 +2262,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>113</v>
       </c>
@@ -2278,7 +2279,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>115</v>
       </c>
@@ -2295,7 +2296,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>117</v>
       </c>
@@ -2312,7 +2313,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>119</v>
       </c>
@@ -2329,7 +2330,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>121</v>
       </c>
@@ -2346,7 +2347,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>123</v>
       </c>
@@ -2363,7 +2364,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>125</v>
       </c>
@@ -2380,7 +2381,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>127</v>
       </c>
@@ -2397,7 +2398,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>129</v>
       </c>
@@ -2414,7 +2415,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>131</v>
       </c>
@@ -2431,7 +2432,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>133</v>
       </c>
@@ -2448,7 +2449,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>135</v>
       </c>
@@ -2465,7 +2466,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>139</v>
       </c>
@@ -2482,7 +2483,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>141</v>
       </c>
@@ -2499,7 +2500,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>143</v>
       </c>
@@ -2516,7 +2517,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>145</v>
       </c>
@@ -2533,7 +2534,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>201</v>
       </c>
@@ -2550,7 +2551,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>146</v>
       </c>
@@ -2567,7 +2568,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>148</v>
       </c>
@@ -2584,7 +2585,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>150</v>
       </c>
@@ -2601,7 +2602,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>152</v>
       </c>
@@ -2618,7 +2619,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>154</v>
       </c>
@@ -2635,7 +2636,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>157</v>
       </c>
@@ -2652,7 +2653,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>160</v>
       </c>
@@ -2669,7 +2670,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>162</v>
       </c>
@@ -2686,7 +2687,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>165</v>
       </c>
@@ -2703,7 +2704,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>167</v>
       </c>
@@ -2720,7 +2721,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>169</v>
       </c>
@@ -2737,7 +2738,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>172</v>
       </c>
@@ -2754,7 +2755,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>174</v>
       </c>
@@ -2771,7 +2772,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>176</v>
       </c>
@@ -2788,7 +2789,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>178</v>
       </c>
@@ -2805,7 +2806,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>180</v>
       </c>
@@ -2822,7 +2823,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>183</v>
       </c>
@@ -2839,7 +2840,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>186</v>
       </c>
@@ -2856,7 +2857,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>189</v>
       </c>
@@ -2873,7 +2874,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>191</v>
       </c>
@@ -2890,7 +2891,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>193</v>
       </c>
@@ -2907,7 +2908,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>196</v>
       </c>
@@ -2924,7 +2925,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>198</v>
       </c>
@@ -2941,7 +2942,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>248</v>
       </c>
@@ -2958,7 +2959,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>251</v>
       </c>
@@ -2975,7 +2976,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>253</v>
       </c>
@@ -2992,7 +2993,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>255</v>
       </c>
@@ -3009,7 +3010,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>261</v>
       </c>
@@ -3026,7 +3027,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>263</v>
       </c>
@@ -3043,7 +3044,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>265</v>
       </c>
@@ -3060,7 +3061,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>268</v>
       </c>
@@ -3077,7 +3078,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>270</v>
       </c>
@@ -3094,7 +3095,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>272</v>
       </c>
@@ -3111,7 +3112,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>274</v>
       </c>
@@ -3128,7 +3129,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>276</v>
       </c>
@@ -3145,7 +3146,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>278</v>
       </c>
@@ -3162,7 +3163,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>280</v>
       </c>
@@ -3190,14 +3191,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFCC8514-E0AF-4C67-BF86-8649FC702924}">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32.5546875" customWidth="1"/>
-    <col min="2" max="3" width="32.5546875" style="21" customWidth="1"/>
+    <col min="1" max="1" width="32.5" customWidth="1"/>
+    <col min="2" max="3" width="32.5" style="21" customWidth="1"/>
     <col min="4" max="4" width="13.33203125" style="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="18" t="s">
         <v>283</v>
       </c>
@@ -3211,7 +3212,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>285</v>
       </c>
@@ -3225,7 +3226,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>286</v>
       </c>
@@ -3239,7 +3240,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>287</v>
       </c>
@@ -3253,7 +3254,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>288</v>
       </c>
@@ -3267,7 +3268,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>289</v>
       </c>
@@ -3281,7 +3282,7 @@
         <v>-4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>290</v>
       </c>
@@ -3295,7 +3296,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>291</v>
       </c>
@@ -3309,7 +3310,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>292</v>
       </c>
@@ -3323,7 +3324,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>293</v>
       </c>
@@ -3337,7 +3338,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>294</v>
       </c>
@@ -3351,7 +3352,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>295</v>
       </c>
@@ -3365,7 +3366,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>296</v>
       </c>
@@ -3379,7 +3380,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>297</v>
       </c>
@@ -3393,7 +3394,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>298</v>
       </c>
@@ -3407,7 +3408,7 @@
         <v>-7.8E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>299</v>
       </c>
@@ -3421,7 +3422,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>300</v>
       </c>
@@ -3435,7 +3436,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>301</v>
       </c>
@@ -3449,7 +3450,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>304</v>
       </c>
@@ -3463,7 +3464,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>302</v>
       </c>
@@ -3485,26 +3486,26 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{118BE621-EF6B-4648-868E-9937B9C5B685}">
   <dimension ref="A1:F32"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="48.109375" style="2" customWidth="1"/>
-    <col min="2" max="4" width="15.77734375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="3.77734375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="46.77734375" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="8.88671875" style="2"/>
+    <col min="1" max="1" width="48.1640625" style="2" customWidth="1"/>
+    <col min="2" max="4" width="15.83203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="3.83203125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="46.83203125" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>208</v>
       </c>
@@ -3518,7 +3519,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>212</v>
       </c>
@@ -3536,7 +3537,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>214</v>
       </c>
@@ -3556,7 +3557,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>216</v>
       </c>
@@ -3576,7 +3577,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>217</v>
       </c>
@@ -3594,7 +3595,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>218</v>
       </c>
@@ -3614,7 +3615,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>220</v>
       </c>
@@ -3631,7 +3632,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>222</v>
       </c>
@@ -3648,7 +3649,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>223</v>
       </c>
@@ -3668,7 +3669,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>225</v>
       </c>
@@ -3685,7 +3686,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>257</v>
       </c>
@@ -3705,7 +3706,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>258</v>
       </c>
@@ -3725,7 +3726,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>227</v>
       </c>
@@ -3733,7 +3734,7 @@
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>228</v>
       </c>
@@ -3750,7 +3751,7 @@
         <v>1.9823131728623846</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>229</v>
       </c>
@@ -3767,7 +3768,7 @@
         <v>1.1592794807274085</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>230</v>
       </c>
@@ -3784,7 +3785,7 @@
         <v>-0.62740704594148844</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>231</v>
       </c>
@@ -3801,7 +3802,7 @@
         <v>-0.96540266006846076</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>232</v>
       </c>
@@ -3809,7 +3810,7 @@
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>233</v>
       </c>
@@ -3826,7 +3827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>234</v>
       </c>
@@ -3843,7 +3844,7 @@
         <v>0.52359877559829882</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>235</v>
       </c>
@@ -3860,7 +3861,7 @@
         <v>-0.50548365077118673</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>236</v>
       </c>
@@ -3877,7 +3878,7 @@
         <v>324.01250000000005</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>237</v>
       </c>
@@ -3894,7 +3895,7 @@
         <v>1.42884E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="11" t="s">
         <v>238</v>
       </c>
@@ -3911,7 +3912,7 @@
         <v>-0.13760360258695806</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>239</v>
       </c>
@@ -3928,7 +3929,7 @@
         <v>0.13760360258695806</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="11" t="s">
         <v>240</v>
       </c>
@@ -3945,7 +3946,7 @@
         <v>22.925083964169769</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>241</v>
       </c>
@@ -3953,7 +3954,7 @@
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>242</v>
       </c>
@@ -3961,7 +3962,7 @@
       <c r="C31" s="14"/>
       <c r="D31" s="14"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>243</v>
       </c>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hudson/Documents/GitHub/451-DBF-Team01/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ceaa8977d2236823/Documents/GitHub/451-DBF-Team01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B07C9115-910C-EA49-AF5C-D506317D2282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{B07C9115-910C-EA49-AF5C-D506317D2282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D11A2D1-C561-487D-B23C-12F18838913A}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -829,63 +829,36 @@
     <t>CL_max_neg</t>
   </si>
   <si>
-    <t>Negative (inverted-flight) max lift coefficient -- ASSUMPTION, not measured; refine with an XFLR5 negative-alpha sweep</t>
-  </si>
-  <si>
     <t>x_spar</t>
   </si>
   <si>
     <t>structures</t>
   </si>
   <si>
-    <t>Wing spar/shear-center location, fraction of chord aft of LE -- ASSUMPTION, set once the spar is chosen; sign of (x_spar-x_ac) decides whether Cm_ac adds to or opposes the lift-offset torque</t>
-  </si>
-  <si>
     <t>eta_h</t>
   </si>
   <si>
-    <t>Horizontal tail dynamic-pressure ratio q_tail/q_freestream -- ASSUMPTION (high-wing/clear tail), refine from wake/downwash data</t>
-  </si>
-  <si>
     <t>eta_v</t>
   </si>
   <si>
-    <t>Vertical tail (fin) dynamic-pressure ratio -- ASSUMPTION, refine from wake/downwash data</t>
-  </si>
-  <si>
     <t>CL_max_tail</t>
   </si>
   <si>
-    <t>Max lift coefficient of the tail's symmetric section (NACA 0010) -- ASSUMPTION, refine with an XFLR5 sweep</t>
-  </si>
-  <si>
     <t>D_fus_tail</t>
   </si>
   <si>
-    <t>Fuselage/tailboom depth at the fin root -- ASSUMPTION, measure once the boom is sized</t>
-  </si>
-  <si>
     <t>x_LE_wing</t>
   </si>
   <si>
-    <t>Fuselage station of the wing's MAC leading edge, from the nose -- ASSUMPTION/PLACEHOLDER, set from your actual layout</t>
-  </si>
-  <si>
     <t>sink_rate</t>
   </si>
   <si>
-    <t>Design sink rate for the landing load factor derivation -- ASSUMPTION, state your source</t>
-  </si>
-  <si>
     <t>gear_stiffness</t>
   </si>
   <si>
     <t>N/m</t>
   </si>
   <si>
-    <t>Main landing gear vertical stiffness (both legs) -- PLACEHOLDER, replace once gear is selected/tested</t>
-  </si>
-  <si>
     <t>Component</t>
   </si>
   <si>
@@ -953,6 +926,33 @@
   </si>
   <si>
     <t>X_m</t>
+  </si>
+  <si>
+    <t>Negative (inverted-flight) max lift coefficient</t>
+  </si>
+  <si>
+    <t>Wing spar/shear-center location, fraction of chord aft of LE</t>
+  </si>
+  <si>
+    <t>Horizontal tail dynamic-pressure ratio q_tail/q_freestream</t>
+  </si>
+  <si>
+    <t>Vertical tail (fin) dynamic-pressure ratio</t>
+  </si>
+  <si>
+    <t>Max lift coefficient of the tail's symmetric section (NACA 0010)</t>
+  </si>
+  <si>
+    <t>Fuselage/tailboom depth at the fin root</t>
+  </si>
+  <si>
+    <t>Fuselage station of the wing's MAC leading edge, from the nose</t>
+  </si>
+  <si>
+    <t>Design sink rate for the landing load factor derivation</t>
+  </si>
+  <si>
+    <t>Main landing gear vertical stiffness (both legs)</t>
   </si>
 </sst>
 </file>
@@ -1072,7 +1072,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -1102,6 +1102,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1402,17 +1403,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F104"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="10.6640625" customWidth="1"/>
-    <col min="5" max="5" width="168.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="168.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1432,7 +1433,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1449,7 +1450,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1466,7 +1467,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1483,7 +1484,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -1500,7 +1501,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -1517,7 +1518,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -1534,7 +1535,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -1551,7 +1552,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>205</v>
       </c>
@@ -1565,7 +1566,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -1582,7 +1583,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1599,7 +1600,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -1616,7 +1617,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -1633,7 +1634,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -1650,7 +1651,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -1667,7 +1668,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>35</v>
       </c>
@@ -1684,7 +1685,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>37</v>
       </c>
@@ -1701,7 +1702,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>39</v>
       </c>
@@ -1718,7 +1719,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>41</v>
       </c>
@@ -1735,7 +1736,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>45</v>
       </c>
@@ -1752,7 +1753,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -1769,7 +1770,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -1786,7 +1787,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -1803,7 +1804,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -1820,7 +1821,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>58</v>
       </c>
@@ -1837,7 +1838,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>61</v>
       </c>
@@ -1854,7 +1855,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>63</v>
       </c>
@@ -1871,7 +1872,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>65</v>
       </c>
@@ -1888,7 +1889,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -1905,7 +1906,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -1922,7 +1923,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>72</v>
       </c>
@@ -1939,7 +1940,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>74</v>
       </c>
@@ -1956,7 +1957,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>76</v>
       </c>
@@ -1973,7 +1974,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>78</v>
       </c>
@@ -1990,7 +1991,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>80</v>
       </c>
@@ -2007,7 +2008,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>82</v>
       </c>
@@ -2024,7 +2025,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>84</v>
       </c>
@@ -2041,7 +2042,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>86</v>
       </c>
@@ -2058,7 +2059,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>88</v>
       </c>
@@ -2075,7 +2076,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>90</v>
       </c>
@@ -2092,7 +2093,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>92</v>
       </c>
@@ -2109,7 +2110,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>94</v>
       </c>
@@ -2126,7 +2127,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>96</v>
       </c>
@@ -2143,7 +2144,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>98</v>
       </c>
@@ -2160,7 +2161,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>100</v>
       </c>
@@ -2177,7 +2178,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>103</v>
       </c>
@@ -2194,7 +2195,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>105</v>
       </c>
@@ -2211,7 +2212,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>107</v>
       </c>
@@ -2228,7 +2229,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>109</v>
       </c>
@@ -2236,7 +2237,7 @@
         <v>56</v>
       </c>
       <c r="C49">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="D49" t="s">
         <v>59</v>
@@ -2245,7 +2246,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>111</v>
       </c>
@@ -2262,7 +2263,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>113</v>
       </c>
@@ -2279,7 +2280,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>115</v>
       </c>
@@ -2296,7 +2297,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>117</v>
       </c>
@@ -2313,7 +2314,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>119</v>
       </c>
@@ -2330,7 +2331,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>121</v>
       </c>
@@ -2347,7 +2348,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>123</v>
       </c>
@@ -2364,7 +2365,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>125</v>
       </c>
@@ -2381,7 +2382,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>127</v>
       </c>
@@ -2398,7 +2399,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>129</v>
       </c>
@@ -2415,7 +2416,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>131</v>
       </c>
@@ -2432,7 +2433,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>133</v>
       </c>
@@ -2449,7 +2450,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>135</v>
       </c>
@@ -2466,7 +2467,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>139</v>
       </c>
@@ -2483,7 +2484,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>141</v>
       </c>
@@ -2500,7 +2501,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>143</v>
       </c>
@@ -2517,7 +2518,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>145</v>
       </c>
@@ -2534,7 +2535,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>201</v>
       </c>
@@ -2551,7 +2552,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>146</v>
       </c>
@@ -2568,7 +2569,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>148</v>
       </c>
@@ -2585,7 +2586,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>150</v>
       </c>
@@ -2602,7 +2603,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>152</v>
       </c>
@@ -2619,7 +2620,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>154</v>
       </c>
@@ -2636,7 +2637,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>157</v>
       </c>
@@ -2653,7 +2654,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>160</v>
       </c>
@@ -2670,7 +2671,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>162</v>
       </c>
@@ -2687,7 +2688,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>165</v>
       </c>
@@ -2704,7 +2705,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>167</v>
       </c>
@@ -2721,7 +2722,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>169</v>
       </c>
@@ -2738,7 +2739,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>172</v>
       </c>
@@ -2755,7 +2756,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>174</v>
       </c>
@@ -2772,7 +2773,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>176</v>
       </c>
@@ -2789,7 +2790,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>178</v>
       </c>
@@ -2806,7 +2807,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>180</v>
       </c>
@@ -2823,7 +2824,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>183</v>
       </c>
@@ -2840,7 +2841,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>186</v>
       </c>
@@ -2857,7 +2858,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>189</v>
       </c>
@@ -2874,7 +2875,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>191</v>
       </c>
@@ -2891,7 +2892,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>193</v>
       </c>
@@ -2908,7 +2909,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>196</v>
       </c>
@@ -2925,7 +2926,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>198</v>
       </c>
@@ -2942,7 +2943,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>248</v>
       </c>
@@ -2959,7 +2960,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>251</v>
       </c>
@@ -2976,7 +2977,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>253</v>
       </c>
@@ -2993,7 +2994,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>255</v>
       </c>
@@ -3010,7 +3011,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>261</v>
       </c>
@@ -3027,29 +3028,29 @@
         <v>262</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>263</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="C96">
+      <c r="C96" s="19">
         <v>-0.8</v>
       </c>
       <c r="D96" t="s">
         <v>8</v>
       </c>
       <c r="E96" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A97" t="s">
+      <c r="B97" s="19" t="s">
         <v>265</v>
-      </c>
-      <c r="B97" s="19" t="s">
-        <v>266</v>
       </c>
       <c r="C97" s="19">
         <v>0.3</v>
@@ -3058,15 +3059,15 @@
         <v>8</v>
       </c>
       <c r="E97" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B98" s="19" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C98" s="19">
         <v>1</v>
@@ -3075,15 +3076,15 @@
         <v>8</v>
       </c>
       <c r="E98" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B99" s="19" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C99" s="19">
         <v>1</v>
@@ -3092,15 +3093,15 @@
         <v>8</v>
       </c>
       <c r="E99" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B100" s="19" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C100" s="19">
         <v>1</v>
@@ -3109,15 +3110,15 @@
         <v>8</v>
       </c>
       <c r="E100" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="B101" s="19" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C101" s="19">
         <v>0.03</v>
@@ -3126,15 +3127,15 @@
         <v>59</v>
       </c>
       <c r="E101" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="B102" s="19" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C102" s="19">
         <v>0.3</v>
@@ -3143,41 +3144,41 @@
         <v>59</v>
       </c>
       <c r="E102" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>278</v>
-      </c>
-      <c r="B103" s="19" t="s">
-        <v>266</v>
-      </c>
-      <c r="C103" s="19">
-        <v>0.5</v>
+        <v>271</v>
+      </c>
+      <c r="B103" s="23" t="s">
+        <v>265</v>
+      </c>
+      <c r="C103" s="23">
+        <v>1</v>
       </c>
       <c r="D103" t="s">
         <v>137</v>
       </c>
       <c r="E103" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="B104" s="19" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C104" s="19">
         <v>5000</v>
       </c>
       <c r="D104" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="E104" t="s">
-        <v>282</v>
+        <v>305</v>
       </c>
     </row>
   </sheetData>
@@ -3191,30 +3192,30 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFCC8514-E0AF-4C67-BF86-8649FC702924}">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32.5" customWidth="1"/>
-    <col min="2" max="3" width="32.5" style="21" customWidth="1"/>
+    <col min="1" max="1" width="32.44140625" customWidth="1"/>
+    <col min="2" max="3" width="32.44140625" style="21" customWidth="1"/>
     <col min="4" max="4" width="13.33203125" style="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="C1" s="20" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="D1" s="21" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="B2" s="22">
         <v>25.9</v>
@@ -3226,9 +3227,9 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="B3" s="22">
         <v>116.7</v>
@@ -3240,9 +3241,9 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="B4" s="22">
         <v>22.7</v>
@@ -3254,9 +3255,9 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="B5" s="22">
         <v>32.4</v>
@@ -3268,9 +3269,9 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="B6" s="22">
         <v>45.4</v>
@@ -3282,9 +3283,9 @@
         <v>-4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="B7" s="22">
         <v>440.8</v>
@@ -3296,9 +3297,9 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="B8" s="22">
         <v>58.3</v>
@@ -3310,9 +3311,9 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="B9" s="22">
         <v>64.8</v>
@@ -3324,9 +3325,9 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="B10" s="22">
         <v>259.3</v>
@@ -3338,9 +3339,9 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="B11" s="22">
         <v>13.4</v>
@@ -3352,9 +3353,9 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="B12" s="22">
         <v>13.4</v>
@@ -3366,9 +3367,9 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="B13" s="21">
         <v>520</v>
@@ -3380,9 +3381,9 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="B14" s="22">
         <v>907.6</v>
@@ -3394,9 +3395,9 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="B15" s="22">
         <v>142.6</v>
@@ -3408,9 +3409,9 @@
         <v>-7.8E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="B16" s="22">
         <v>1231.8</v>
@@ -3422,9 +3423,9 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="B17" s="22">
         <v>13.4</v>
@@ -3436,9 +3437,9 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="B18" s="22">
         <v>13.4</v>
@@ -3450,9 +3451,9 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="B19" s="22">
         <v>77.8</v>
@@ -3464,9 +3465,9 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="B20" s="22">
         <v>51.9</v>
@@ -3486,26 +3487,26 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{118BE621-EF6B-4648-868E-9937B9C5B685}">
   <dimension ref="A1:F32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="48.1640625" style="2" customWidth="1"/>
-    <col min="2" max="4" width="15.83203125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="3.83203125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="46.83203125" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="8.83203125" style="2"/>
+    <col min="1" max="1" width="48.109375" style="2" customWidth="1"/>
+    <col min="2" max="4" width="15.77734375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="3.77734375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="46.77734375" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="8.77734375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>208</v>
       </c>
@@ -3519,7 +3520,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>212</v>
       </c>
@@ -3537,7 +3538,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>214</v>
       </c>
@@ -3557,7 +3558,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>216</v>
       </c>
@@ -3577,7 +3578,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>217</v>
       </c>
@@ -3595,7 +3596,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>218</v>
       </c>
@@ -3615,7 +3616,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>220</v>
       </c>
@@ -3632,7 +3633,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>222</v>
       </c>
@@ -3649,7 +3650,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>223</v>
       </c>
@@ -3669,7 +3670,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>225</v>
       </c>
@@ -3686,7 +3687,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>257</v>
       </c>
@@ -3706,7 +3707,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>258</v>
       </c>
@@ -3726,7 +3727,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>227</v>
       </c>
@@ -3734,7 +3735,7 @@
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>228</v>
       </c>
@@ -3751,7 +3752,7 @@
         <v>1.9823131728623846</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>229</v>
       </c>
@@ -3768,7 +3769,7 @@
         <v>1.1592794807274085</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>230</v>
       </c>
@@ -3785,7 +3786,7 @@
         <v>-0.62740704594148844</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>231</v>
       </c>
@@ -3802,7 +3803,7 @@
         <v>-0.96540266006846076</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>232</v>
       </c>
@@ -3810,7 +3811,7 @@
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>233</v>
       </c>
@@ -3827,7 +3828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>234</v>
       </c>
@@ -3844,7 +3845,7 @@
         <v>0.52359877559829882</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>235</v>
       </c>
@@ -3861,7 +3862,7 @@
         <v>-0.50548365077118673</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>236</v>
       </c>
@@ -3878,7 +3879,7 @@
         <v>324.01250000000005</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>237</v>
       </c>
@@ -3895,7 +3896,7 @@
         <v>1.42884E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>238</v>
       </c>
@@ -3912,7 +3913,7 @@
         <v>-0.13760360258695806</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>239</v>
       </c>
@@ -3929,7 +3930,7 @@
         <v>0.13760360258695806</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
         <v>240</v>
       </c>
@@ -3946,7 +3947,7 @@
         <v>22.925083964169769</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>241</v>
       </c>
@@ -3954,7 +3955,7 @@
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>242</v>
       </c>
@@ -3962,7 +3963,7 @@
       <c r="C31" s="14"/>
       <c r="D31" s="14"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>243</v>
       </c>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ceaa8977d2236823/Documents/GitHub/451-DBF-Team01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{B07C9115-910C-EA49-AF5C-D506317D2282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D11A2D1-C561-487D-B23C-12F18838913A}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{B07C9115-910C-EA49-AF5C-D506317D2282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8579DF5C-F9C9-4F36-B3BC-D608D5288F2A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3032,11 +3032,11 @@
       <c r="A96" t="s">
         <v>263</v>
       </c>
-      <c r="B96" s="19" t="s">
+      <c r="B96" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="C96" s="19">
-        <v>-0.8</v>
+      <c r="C96" s="23">
+        <v>-0.66</v>
       </c>
       <c r="D96" t="s">
         <v>8</v>
@@ -3100,10 +3100,10 @@
       <c r="A100" t="s">
         <v>268</v>
       </c>
-      <c r="B100" s="19" t="s">
+      <c r="B100" s="23" t="s">
         <v>265</v>
       </c>
-      <c r="C100" s="19">
+      <c r="C100" s="23">
         <v>1</v>
       </c>
       <c r="D100" t="s">

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ceaa8977d2236823/Documents/GitHub/451-DBF-Team01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{B07C9115-910C-EA49-AF5C-D506317D2282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8579DF5C-F9C9-4F36-B3BC-D608D5288F2A}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{B07C9115-910C-EA49-AF5C-D506317D2282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D89576C-7277-47AF-85BF-248977ED0433}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -919,9 +919,6 @@
     <t>V-tail (spar+foam)</t>
   </si>
   <si>
-    <t>Height_m</t>
-  </si>
-  <si>
     <t>Horizontal tail (spar+foam)</t>
   </si>
   <si>
@@ -953,6 +950,9 @@
   </si>
   <si>
     <t>Main landing gear vertical stiffness (both legs)</t>
+  </si>
+  <si>
+    <t>Z_m</t>
   </si>
 </sst>
 </file>
@@ -3042,7 +3042,7 @@
         <v>8</v>
       </c>
       <c r="E96" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
@@ -3059,7 +3059,7 @@
         <v>8</v>
       </c>
       <c r="E97" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
@@ -3076,7 +3076,7 @@
         <v>8</v>
       </c>
       <c r="E98" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
@@ -3093,7 +3093,7 @@
         <v>8</v>
       </c>
       <c r="E99" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
@@ -3110,7 +3110,7 @@
         <v>8</v>
       </c>
       <c r="E100" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
@@ -3127,7 +3127,7 @@
         <v>59</v>
       </c>
       <c r="E101" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
@@ -3144,7 +3144,7 @@
         <v>59</v>
       </c>
       <c r="E102" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
@@ -3161,7 +3161,7 @@
         <v>137</v>
       </c>
       <c r="E103" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
@@ -3178,7 +3178,7 @@
         <v>273</v>
       </c>
       <c r="E104" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
   </sheetData>
@@ -3207,10 +3207,10 @@
         <v>275</v>
       </c>
       <c r="C1" s="20" t="s">
-        <v>296</v>
-      </c>
-      <c r="D1" s="21" t="s">
-        <v>294</v>
+        <v>295</v>
+      </c>
+      <c r="D1" s="20" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -3453,7 +3453,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B19" s="22">
         <v>77.8</v>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ceaa8977d2236823/Documents/GitHub/451-DBF-Team01/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hudson/Documents/GitHub/451-DBF-Team01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{B07C9115-910C-EA49-AF5C-D506317D2282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D89576C-7277-47AF-85BF-248977ED0433}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FDDA133-6212-434F-87AA-F220BBD3158A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="23260" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1072,7 +1072,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -1102,7 +1102,6 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1403,17 +1402,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F104"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="10.6640625" customWidth="1"/>
-    <col min="5" max="5" width="168.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="168.1640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1433,7 +1432,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1450,7 +1449,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1467,7 +1466,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1484,7 +1483,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -1501,7 +1500,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -1518,7 +1517,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -1535,7 +1534,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -1552,7 +1551,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>205</v>
       </c>
@@ -1566,7 +1565,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -1583,7 +1582,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1600,7 +1599,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -1617,7 +1616,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -1634,7 +1633,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -1651,7 +1650,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -1668,7 +1667,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>35</v>
       </c>
@@ -1685,7 +1684,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>37</v>
       </c>
@@ -1702,7 +1701,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>39</v>
       </c>
@@ -1719,7 +1718,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>41</v>
       </c>
@@ -1736,7 +1735,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>45</v>
       </c>
@@ -1753,7 +1752,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -1770,7 +1769,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -1787,7 +1786,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -1804,7 +1803,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -1821,7 +1820,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>58</v>
       </c>
@@ -1838,7 +1837,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>61</v>
       </c>
@@ -1855,7 +1854,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>63</v>
       </c>
@@ -1872,7 +1871,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>65</v>
       </c>
@@ -1889,7 +1888,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -1906,7 +1905,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -1923,7 +1922,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>72</v>
       </c>
@@ -1940,7 +1939,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>74</v>
       </c>
@@ -1957,7 +1956,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>76</v>
       </c>
@@ -1965,7 +1964,7 @@
         <v>56</v>
       </c>
       <c r="C33">
-        <v>2.5499999999999998</v>
+        <v>2.5</v>
       </c>
       <c r="D33" t="s">
         <v>8</v>
@@ -1974,7 +1973,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>78</v>
       </c>
@@ -1991,7 +1990,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>80</v>
       </c>
@@ -2008,7 +2007,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>82</v>
       </c>
@@ -2025,7 +2024,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>84</v>
       </c>
@@ -2042,7 +2041,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>86</v>
       </c>
@@ -2059,7 +2058,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>88</v>
       </c>
@@ -2076,7 +2075,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>90</v>
       </c>
@@ -2093,7 +2092,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>92</v>
       </c>
@@ -2110,7 +2109,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>94</v>
       </c>
@@ -2127,7 +2126,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>96</v>
       </c>
@@ -2144,7 +2143,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>98</v>
       </c>
@@ -2161,7 +2160,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>100</v>
       </c>
@@ -2178,7 +2177,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>103</v>
       </c>
@@ -2195,7 +2194,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>105</v>
       </c>
@@ -2212,7 +2211,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>107</v>
       </c>
@@ -2229,7 +2228,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>109</v>
       </c>
@@ -2246,7 +2245,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>111</v>
       </c>
@@ -2263,7 +2262,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>113</v>
       </c>
@@ -2280,7 +2279,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>115</v>
       </c>
@@ -2297,7 +2296,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>117</v>
       </c>
@@ -2314,7 +2313,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>119</v>
       </c>
@@ -2331,7 +2330,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>121</v>
       </c>
@@ -2348,7 +2347,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>123</v>
       </c>
@@ -2365,7 +2364,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>125</v>
       </c>
@@ -2382,7 +2381,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>127</v>
       </c>
@@ -2399,7 +2398,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>129</v>
       </c>
@@ -2416,7 +2415,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>131</v>
       </c>
@@ -2433,7 +2432,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>133</v>
       </c>
@@ -2441,7 +2440,7 @@
         <v>56</v>
       </c>
       <c r="C61">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D61" t="s">
         <v>23</v>
@@ -2450,7 +2449,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>135</v>
       </c>
@@ -2458,7 +2457,7 @@
         <v>136</v>
       </c>
       <c r="C62">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="D62" t="s">
         <v>137</v>
@@ -2467,7 +2466,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>139</v>
       </c>
@@ -2484,7 +2483,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>141</v>
       </c>
@@ -2501,7 +2500,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>143</v>
       </c>
@@ -2518,7 +2517,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>145</v>
       </c>
@@ -2535,7 +2534,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>201</v>
       </c>
@@ -2552,7 +2551,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>146</v>
       </c>
@@ -2569,7 +2568,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>148</v>
       </c>
@@ -2586,7 +2585,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>150</v>
       </c>
@@ -2603,7 +2602,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>152</v>
       </c>
@@ -2620,7 +2619,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>154</v>
       </c>
@@ -2637,7 +2636,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>157</v>
       </c>
@@ -2654,7 +2653,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>160</v>
       </c>
@@ -2671,7 +2670,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>162</v>
       </c>
@@ -2688,7 +2687,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>165</v>
       </c>
@@ -2705,7 +2704,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>167</v>
       </c>
@@ -2722,7 +2721,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>169</v>
       </c>
@@ -2739,7 +2738,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>172</v>
       </c>
@@ -2756,7 +2755,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>174</v>
       </c>
@@ -2773,7 +2772,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>176</v>
       </c>
@@ -2790,7 +2789,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>178</v>
       </c>
@@ -2807,7 +2806,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>180</v>
       </c>
@@ -2824,7 +2823,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>183</v>
       </c>
@@ -2841,7 +2840,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>186</v>
       </c>
@@ -2858,7 +2857,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>189</v>
       </c>
@@ -2875,7 +2874,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>191</v>
       </c>
@@ -2892,7 +2891,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>193</v>
       </c>
@@ -2909,7 +2908,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>196</v>
       </c>
@@ -2926,7 +2925,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>198</v>
       </c>
@@ -2943,7 +2942,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>248</v>
       </c>
@@ -2960,7 +2959,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>251</v>
       </c>
@@ -2977,7 +2976,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>253</v>
       </c>
@@ -2994,7 +2993,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>255</v>
       </c>
@@ -3011,7 +3010,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>261</v>
       </c>
@@ -3028,14 +3027,14 @@
         <v>262</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>263</v>
       </c>
-      <c r="B96" s="23" t="s">
+      <c r="B96" t="s">
         <v>7</v>
       </c>
-      <c r="C96" s="23">
+      <c r="C96">
         <v>-0.66</v>
       </c>
       <c r="D96" t="s">
@@ -3045,7 +3044,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>264</v>
       </c>
@@ -3062,7 +3061,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>266</v>
       </c>
@@ -3079,7 +3078,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>267</v>
       </c>
@@ -3096,14 +3095,14 @@
         <v>299</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>268</v>
       </c>
-      <c r="B100" s="23" t="s">
+      <c r="B100" t="s">
         <v>265</v>
       </c>
-      <c r="C100" s="23">
+      <c r="C100">
         <v>1</v>
       </c>
       <c r="D100" t="s">
@@ -3113,7 +3112,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>269</v>
       </c>
@@ -3130,7 +3129,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>270</v>
       </c>
@@ -3147,14 +3146,14 @@
         <v>302</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>271</v>
       </c>
-      <c r="B103" s="23" t="s">
+      <c r="B103" t="s">
         <v>265</v>
       </c>
-      <c r="C103" s="23">
+      <c r="C103">
         <v>1</v>
       </c>
       <c r="D103" t="s">
@@ -3164,7 +3163,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>272</v>
       </c>
@@ -3192,14 +3191,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFCC8514-E0AF-4C67-BF86-8649FC702924}">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32.44140625" customWidth="1"/>
-    <col min="2" max="3" width="32.44140625" style="21" customWidth="1"/>
+    <col min="1" max="1" width="32.5" customWidth="1"/>
+    <col min="2" max="3" width="32.5" style="21" customWidth="1"/>
     <col min="4" max="4" width="13.33203125" style="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="18" t="s">
         <v>274</v>
       </c>
@@ -3213,7 +3212,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>276</v>
       </c>
@@ -3227,7 +3226,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>277</v>
       </c>
@@ -3241,7 +3240,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>278</v>
       </c>
@@ -3255,7 +3254,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>279</v>
       </c>
@@ -3269,7 +3268,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>280</v>
       </c>
@@ -3283,7 +3282,7 @@
         <v>-4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>281</v>
       </c>
@@ -3297,7 +3296,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>282</v>
       </c>
@@ -3311,7 +3310,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>283</v>
       </c>
@@ -3325,7 +3324,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>284</v>
       </c>
@@ -3339,7 +3338,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>285</v>
       </c>
@@ -3353,7 +3352,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>286</v>
       </c>
@@ -3367,7 +3366,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>287</v>
       </c>
@@ -3381,7 +3380,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>288</v>
       </c>
@@ -3395,7 +3394,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>289</v>
       </c>
@@ -3409,7 +3408,7 @@
         <v>-7.8E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>290</v>
       </c>
@@ -3423,7 +3422,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>291</v>
       </c>
@@ -3437,7 +3436,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>292</v>
       </c>
@@ -3451,7 +3450,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>294</v>
       </c>
@@ -3465,7 +3464,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>293</v>
       </c>
@@ -3487,26 +3486,26 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{118BE621-EF6B-4648-868E-9937B9C5B685}">
   <dimension ref="A1:F32"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="48.109375" style="2" customWidth="1"/>
-    <col min="2" max="4" width="15.77734375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="3.77734375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="46.77734375" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="8.77734375" style="2"/>
+    <col min="1" max="1" width="48.1640625" style="2" customWidth="1"/>
+    <col min="2" max="4" width="15.83203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="3.83203125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="46.83203125" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>208</v>
       </c>
@@ -3520,7 +3519,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>212</v>
       </c>
@@ -3538,7 +3537,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>214</v>
       </c>
@@ -3558,7 +3557,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>216</v>
       </c>
@@ -3578,7 +3577,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>217</v>
       </c>
@@ -3596,7 +3595,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>218</v>
       </c>
@@ -3616,7 +3615,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>220</v>
       </c>
@@ -3633,7 +3632,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>222</v>
       </c>
@@ -3650,7 +3649,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>223</v>
       </c>
@@ -3670,7 +3669,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>225</v>
       </c>
@@ -3687,7 +3686,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>257</v>
       </c>
@@ -3707,7 +3706,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>258</v>
       </c>
@@ -3727,7 +3726,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>227</v>
       </c>
@@ -3735,7 +3734,7 @@
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>228</v>
       </c>
@@ -3752,7 +3751,7 @@
         <v>1.9823131728623846</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>229</v>
       </c>
@@ -3769,7 +3768,7 @@
         <v>1.1592794807274085</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>230</v>
       </c>
@@ -3786,7 +3785,7 @@
         <v>-0.62740704594148844</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>231</v>
       </c>
@@ -3803,7 +3802,7 @@
         <v>-0.96540266006846076</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>232</v>
       </c>
@@ -3811,7 +3810,7 @@
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>233</v>
       </c>
@@ -3828,7 +3827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>234</v>
       </c>
@@ -3845,7 +3844,7 @@
         <v>0.52359877559829882</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>235</v>
       </c>
@@ -3862,7 +3861,7 @@
         <v>-0.50548365077118673</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>236</v>
       </c>
@@ -3879,7 +3878,7 @@
         <v>324.01250000000005</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>237</v>
       </c>
@@ -3896,7 +3895,7 @@
         <v>1.42884E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="11" t="s">
         <v>238</v>
       </c>
@@ -3913,7 +3912,7 @@
         <v>-0.13760360258695806</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>239</v>
       </c>
@@ -3930,7 +3929,7 @@
         <v>0.13760360258695806</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="11" t="s">
         <v>240</v>
       </c>
@@ -3947,7 +3946,7 @@
         <v>22.925083964169769</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>241</v>
       </c>
@@ -3955,7 +3954,7 @@
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>242</v>
       </c>
@@ -3963,7 +3962,7 @@
       <c r="C31" s="14"/>
       <c r="D31" s="14"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>243</v>
       </c>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hudson/Documents/GitHub/451-DBF-Team01/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ceaa8977d2236823/Documents/GitHub/451-DBF-Team01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FDDA133-6212-434F-87AA-F220BBD3158A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{9FDDA133-6212-434F-87AA-F220BBD3158A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32653BCF-470F-4421-8409-A4ADE2E956AE}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="23260" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="308">
   <si>
     <t>Parameter</t>
   </si>
@@ -877,9 +877,6 @@
     <t>ESC</t>
   </si>
   <si>
-    <t>Nose gear</t>
-  </si>
-  <si>
     <t>Battery</t>
   </si>
   <si>
@@ -953,6 +950,15 @@
   </si>
   <si>
     <t>Z_m</t>
+  </si>
+  <si>
+    <t>Tail wheel</t>
+  </si>
+  <si>
+    <t>gear_track</t>
+  </si>
+  <si>
+    <t>Lateral distance between the two main wheels (track), ASSUMPTION -- needed for the overturn-angle check, not previously modelled (~20% of wingspan)</t>
   </si>
 </sst>
 </file>
@@ -1121,8 +1127,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:F104" totalsRowShown="0">
-  <autoFilter ref="A1:F104" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:F105" totalsRowShown="0">
+  <autoFilter ref="A1:F105" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E43">
     <sortCondition ref="B1:B101"/>
   </sortState>
@@ -1401,18 +1407,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F104"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F105"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="10.6640625" customWidth="1"/>
-    <col min="5" max="5" width="168.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="168.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1432,7 +1438,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1449,7 +1455,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1466,7 +1472,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1483,7 +1489,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -1500,7 +1506,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -1517,7 +1523,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -1534,7 +1540,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -1551,7 +1557,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>205</v>
       </c>
@@ -1565,7 +1571,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -1582,7 +1588,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1599,7 +1605,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -1616,7 +1622,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -1633,7 +1639,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -1650,7 +1656,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -1667,7 +1673,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>35</v>
       </c>
@@ -1684,7 +1690,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>37</v>
       </c>
@@ -1701,7 +1707,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>39</v>
       </c>
@@ -1718,7 +1724,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>41</v>
       </c>
@@ -1735,7 +1741,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>45</v>
       </c>
@@ -1752,7 +1758,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -1769,7 +1775,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -1786,7 +1792,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -1803,7 +1809,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -1820,7 +1826,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>58</v>
       </c>
@@ -1837,7 +1843,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>61</v>
       </c>
@@ -1854,7 +1860,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>63</v>
       </c>
@@ -1871,7 +1877,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>65</v>
       </c>
@@ -1888,7 +1894,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -1905,7 +1911,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -1922,7 +1928,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>72</v>
       </c>
@@ -1939,7 +1945,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>74</v>
       </c>
@@ -1956,7 +1962,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>76</v>
       </c>
@@ -1973,7 +1979,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>78</v>
       </c>
@@ -1990,7 +1996,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>80</v>
       </c>
@@ -2007,7 +2013,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>82</v>
       </c>
@@ -2024,7 +2030,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>84</v>
       </c>
@@ -2041,7 +2047,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>86</v>
       </c>
@@ -2058,7 +2064,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>88</v>
       </c>
@@ -2075,7 +2081,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>90</v>
       </c>
@@ -2092,7 +2098,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>92</v>
       </c>
@@ -2109,7 +2115,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>94</v>
       </c>
@@ -2126,7 +2132,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>96</v>
       </c>
@@ -2143,7 +2149,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>98</v>
       </c>
@@ -2160,7 +2166,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>100</v>
       </c>
@@ -2177,7 +2183,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>103</v>
       </c>
@@ -2194,7 +2200,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>105</v>
       </c>
@@ -2211,7 +2217,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>107</v>
       </c>
@@ -2228,7 +2234,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>109</v>
       </c>
@@ -2245,7 +2251,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>111</v>
       </c>
@@ -2262,7 +2268,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>113</v>
       </c>
@@ -2279,7 +2285,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>115</v>
       </c>
@@ -2296,7 +2302,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>117</v>
       </c>
@@ -2313,7 +2319,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>119</v>
       </c>
@@ -2330,7 +2336,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>121</v>
       </c>
@@ -2347,7 +2353,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>123</v>
       </c>
@@ -2364,7 +2370,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>125</v>
       </c>
@@ -2381,7 +2387,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>127</v>
       </c>
@@ -2398,7 +2404,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>129</v>
       </c>
@@ -2415,7 +2421,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>131</v>
       </c>
@@ -2432,7 +2438,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>133</v>
       </c>
@@ -2449,7 +2455,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>135</v>
       </c>
@@ -2466,7 +2472,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>139</v>
       </c>
@@ -2483,7 +2489,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>141</v>
       </c>
@@ -2500,7 +2506,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>143</v>
       </c>
@@ -2517,7 +2523,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>145</v>
       </c>
@@ -2534,7 +2540,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>201</v>
       </c>
@@ -2551,7 +2557,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>146</v>
       </c>
@@ -2568,7 +2574,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>148</v>
       </c>
@@ -2585,7 +2591,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>150</v>
       </c>
@@ -2602,7 +2608,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>152</v>
       </c>
@@ -2619,7 +2625,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>154</v>
       </c>
@@ -2636,7 +2642,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>157</v>
       </c>
@@ -2653,7 +2659,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>160</v>
       </c>
@@ -2670,7 +2676,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>162</v>
       </c>
@@ -2687,7 +2693,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>165</v>
       </c>
@@ -2704,7 +2710,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>167</v>
       </c>
@@ -2721,7 +2727,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>169</v>
       </c>
@@ -2738,7 +2744,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>172</v>
       </c>
@@ -2755,7 +2761,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>174</v>
       </c>
@@ -2772,7 +2778,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>176</v>
       </c>
@@ -2789,7 +2795,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>178</v>
       </c>
@@ -2806,7 +2812,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>180</v>
       </c>
@@ -2823,7 +2829,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>183</v>
       </c>
@@ -2840,7 +2846,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>186</v>
       </c>
@@ -2857,7 +2863,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>189</v>
       </c>
@@ -2874,7 +2880,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>191</v>
       </c>
@@ -2891,7 +2897,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>193</v>
       </c>
@@ -2908,7 +2914,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>196</v>
       </c>
@@ -2925,7 +2931,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>198</v>
       </c>
@@ -2942,7 +2948,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>248</v>
       </c>
@@ -2959,7 +2965,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>251</v>
       </c>
@@ -2976,7 +2982,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>253</v>
       </c>
@@ -2993,7 +2999,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>255</v>
       </c>
@@ -3010,7 +3016,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>261</v>
       </c>
@@ -3027,7 +3033,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>263</v>
       </c>
@@ -3041,10 +3047,10 @@
         <v>8</v>
       </c>
       <c r="E96" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>264</v>
       </c>
@@ -3058,10 +3064,10 @@
         <v>8</v>
       </c>
       <c r="E97" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>266</v>
       </c>
@@ -3075,10 +3081,10 @@
         <v>8</v>
       </c>
       <c r="E98" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>267</v>
       </c>
@@ -3092,10 +3098,10 @@
         <v>8</v>
       </c>
       <c r="E99" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>268</v>
       </c>
@@ -3109,10 +3115,10 @@
         <v>8</v>
       </c>
       <c r="E100" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>269</v>
       </c>
@@ -3126,10 +3132,10 @@
         <v>59</v>
       </c>
       <c r="E101" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>270</v>
       </c>
@@ -3143,10 +3149,10 @@
         <v>59</v>
       </c>
       <c r="E102" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>271</v>
       </c>
@@ -3160,10 +3166,10 @@
         <v>137</v>
       </c>
       <c r="E103" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>272</v>
       </c>
@@ -3177,7 +3183,24 @@
         <v>273</v>
       </c>
       <c r="E104" t="s">
-        <v>304</v>
+        <v>303</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>306</v>
+      </c>
+      <c r="B105" t="s">
+        <v>265</v>
+      </c>
+      <c r="C105">
+        <v>0.3</v>
+      </c>
+      <c r="D105" t="s">
+        <v>59</v>
+      </c>
+      <c r="E105" t="s">
+        <v>307</v>
       </c>
     </row>
   </sheetData>
@@ -3191,14 +3214,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFCC8514-E0AF-4C67-BF86-8649FC702924}">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32.5" customWidth="1"/>
-    <col min="2" max="3" width="32.5" style="21" customWidth="1"/>
+    <col min="1" max="1" width="32.44140625" customWidth="1"/>
+    <col min="2" max="3" width="32.44140625" style="21" customWidth="1"/>
     <col min="4" max="4" width="13.33203125" style="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>274</v>
       </c>
@@ -3206,13 +3229,13 @@
         <v>275</v>
       </c>
       <c r="C1" s="20" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D1" s="20" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>276</v>
       </c>
@@ -3226,7 +3249,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>277</v>
       </c>
@@ -3240,7 +3263,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>278</v>
       </c>
@@ -3254,7 +3277,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>279</v>
       </c>
@@ -3268,23 +3291,23 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="B6" s="22">
         <v>45.4</v>
       </c>
       <c r="C6" s="22">
-        <v>9.5000000000000001E-2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="D6" s="22">
         <v>-4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B7" s="22">
         <v>440.8</v>
@@ -3296,9 +3319,9 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B8" s="22">
         <v>58.3</v>
@@ -3310,9 +3333,9 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B9" s="22">
         <v>64.8</v>
@@ -3324,9 +3347,9 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B10" s="22">
         <v>259.3</v>
@@ -3338,9 +3361,9 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B11" s="22">
         <v>13.4</v>
@@ -3352,9 +3375,9 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B12" s="22">
         <v>13.4</v>
@@ -3366,9 +3389,9 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B13" s="21">
         <v>520</v>
@@ -3380,9 +3403,9 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B14" s="22">
         <v>907.6</v>
@@ -3394,23 +3417,23 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B15" s="22">
         <v>142.6</v>
       </c>
       <c r="C15" s="22">
-        <v>0.43</v>
+        <v>0.35199999999999998</v>
       </c>
       <c r="D15" s="22">
         <v>-7.8E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B16" s="22">
         <v>1231.8</v>
@@ -3422,9 +3445,9 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B17" s="22">
         <v>13.4</v>
@@ -3436,9 +3459,9 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B18" s="22">
         <v>13.4</v>
@@ -3450,9 +3473,9 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B19" s="22">
         <v>77.8</v>
@@ -3464,9 +3487,9 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B20" s="22">
         <v>51.9</v>
@@ -3486,26 +3509,26 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{118BE621-EF6B-4648-868E-9937B9C5B685}">
   <dimension ref="A1:F32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="48.1640625" style="2" customWidth="1"/>
-    <col min="2" max="4" width="15.83203125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="3.83203125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="46.83203125" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="8.83203125" style="2"/>
+    <col min="1" max="1" width="48.109375" style="2" customWidth="1"/>
+    <col min="2" max="4" width="15.77734375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="3.77734375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="46.77734375" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="8.77734375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>208</v>
       </c>
@@ -3519,7 +3542,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>212</v>
       </c>
@@ -3537,7 +3560,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>214</v>
       </c>
@@ -3557,7 +3580,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>216</v>
       </c>
@@ -3577,7 +3600,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>217</v>
       </c>
@@ -3595,7 +3618,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>218</v>
       </c>
@@ -3615,7 +3638,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>220</v>
       </c>
@@ -3632,7 +3655,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>222</v>
       </c>
@@ -3649,7 +3672,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>223</v>
       </c>
@@ -3669,7 +3692,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>225</v>
       </c>
@@ -3686,7 +3709,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>257</v>
       </c>
@@ -3706,7 +3729,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>258</v>
       </c>
@@ -3726,7 +3749,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>227</v>
       </c>
@@ -3734,7 +3757,7 @@
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>228</v>
       </c>
@@ -3751,7 +3774,7 @@
         <v>1.9823131728623846</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>229</v>
       </c>
@@ -3768,7 +3791,7 @@
         <v>1.1592794807274085</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>230</v>
       </c>
@@ -3785,7 +3808,7 @@
         <v>-0.62740704594148844</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>231</v>
       </c>
@@ -3802,7 +3825,7 @@
         <v>-0.96540266006846076</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>232</v>
       </c>
@@ -3810,7 +3833,7 @@
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>233</v>
       </c>
@@ -3827,7 +3850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>234</v>
       </c>
@@ -3844,7 +3867,7 @@
         <v>0.52359877559829882</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>235</v>
       </c>
@@ -3861,7 +3884,7 @@
         <v>-0.50548365077118673</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>236</v>
       </c>
@@ -3878,7 +3901,7 @@
         <v>324.01250000000005</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>237</v>
       </c>
@@ -3895,7 +3918,7 @@
         <v>1.42884E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>238</v>
       </c>
@@ -3912,7 +3935,7 @@
         <v>-0.13760360258695806</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>239</v>
       </c>
@@ -3929,7 +3952,7 @@
         <v>0.13760360258695806</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
         <v>240</v>
       </c>
@@ -3946,7 +3969,7 @@
         <v>22.925083964169769</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>241</v>
       </c>
@@ -3954,7 +3977,7 @@
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>242</v>
       </c>
@@ -3962,7 +3985,7 @@
       <c r="C31" s="14"/>
       <c r="D31" s="14"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>243</v>
       </c>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ceaa8977d2236823/Documents/GitHub/451-DBF-Team01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{9FDDA133-6212-434F-87AA-F220BBD3158A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32653BCF-470F-4421-8409-A4ADE2E956AE}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{9FDDA133-6212-434F-87AA-F220BBD3158A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD4435D9-C2E4-4946-9CA7-4F3448C44E4A}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3190,10 +3190,10 @@
       <c r="A105" t="s">
         <v>306</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105" s="19" t="s">
         <v>265</v>
       </c>
-      <c r="C105">
+      <c r="C105" s="19">
         <v>0.3</v>
       </c>
       <c r="D105" t="s">

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ceaa8977d2236823/Documents/GitHub/451-DBF-Team01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{9FDDA133-6212-434F-87AA-F220BBD3158A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD4435D9-C2E4-4946-9CA7-4F3448C44E4A}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{9FDDA133-6212-434F-87AA-F220BBD3158A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{115E58BF-A98E-4EC5-BA33-1FCC68D912FF}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1078,7 +1078,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -1108,6 +1108,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3071,10 +3072,10 @@
       <c r="A98" t="s">
         <v>266</v>
       </c>
-      <c r="B98" s="19" t="s">
+      <c r="B98" s="23" t="s">
         <v>265</v>
       </c>
-      <c r="C98" s="19">
+      <c r="C98" s="23">
         <v>1</v>
       </c>
       <c r="D98" t="s">
@@ -3088,10 +3089,10 @@
       <c r="A99" t="s">
         <v>267</v>
       </c>
-      <c r="B99" s="19" t="s">
+      <c r="B99" s="23" t="s">
         <v>265</v>
       </c>
-      <c r="C99" s="19">
+      <c r="C99" s="23">
         <v>1</v>
       </c>
       <c r="D99" t="s">

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ceaa8977d2236823/Documents/GitHub/451-DBF-Team01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{9FDDA133-6212-434F-87AA-F220BBD3158A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{115E58BF-A98E-4EC5-BA33-1FCC68D912FF}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{9FDDA133-6212-434F-87AA-F220BBD3158A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56026FD7-4C03-4317-AA4C-B44D1D6BB7CC}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1078,7 +1078,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -1108,7 +1108,6 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3072,10 +3071,10 @@
       <c r="A98" t="s">
         <v>266</v>
       </c>
-      <c r="B98" s="23" t="s">
+      <c r="B98" t="s">
         <v>265</v>
       </c>
-      <c r="C98" s="23">
+      <c r="C98">
         <v>1</v>
       </c>
       <c r="D98" t="s">
@@ -3089,10 +3088,10 @@
       <c r="A99" t="s">
         <v>267</v>
       </c>
-      <c r="B99" s="23" t="s">
+      <c r="B99" t="s">
         <v>265</v>
       </c>
-      <c r="C99" s="23">
+      <c r="C99">
         <v>1</v>
       </c>
       <c r="D99" t="s">
@@ -3178,7 +3177,7 @@
         <v>265</v>
       </c>
       <c r="C104" s="19">
-        <v>5000</v>
+        <v>35000</v>
       </c>
       <c r="D104" t="s">
         <v>273</v>
@@ -3195,7 +3194,7 @@
         <v>265</v>
       </c>
       <c r="C105" s="19">
-        <v>0.3</v>
+        <v>0.22</v>
       </c>
       <c r="D105" t="s">
         <v>59</v>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ceaa8977d2236823/Documents/GitHub/451-DBF-Team01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{9FDDA133-6212-434F-87AA-F220BBD3158A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56026FD7-4C03-4317-AA4C-B44D1D6BB7CC}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{9FDDA133-6212-434F-87AA-F220BBD3158A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB3CF111-DA9F-46C3-878A-B159FDEAE657}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="311">
   <si>
     <t>Parameter</t>
   </si>
@@ -959,6 +959,15 @@
   </si>
   <si>
     <t>Lateral distance between the two main wheels (track), ASSUMPTION -- needed for the overturn-angle check, not previously modelled (~20% of wingspan)</t>
+  </si>
+  <si>
+    <t>P_limit_RFP</t>
+  </si>
+  <si>
+    <t>P_motor_rated</t>
+  </si>
+  <si>
+    <t>I_motor_limit</t>
   </si>
 </sst>
 </file>
@@ -1127,8 +1136,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:F105" totalsRowShown="0">
-  <autoFilter ref="A1:F105" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:F108" totalsRowShown="0">
+  <autoFilter ref="A1:F108" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E43">
     <sortCondition ref="B1:B101"/>
   </sortState>
@@ -1407,7 +1416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F105"/>
+  <dimension ref="A1:F108"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.77734375" bestFit="1" customWidth="1"/>
@@ -3201,6 +3210,39 @@
       </c>
       <c r="E105" t="s">
         <v>307</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>308</v>
+      </c>
+      <c r="B106" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="C106" s="19">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>309</v>
+      </c>
+      <c r="B107" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="C107" s="19">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>310</v>
+      </c>
+      <c r="B108" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="C108" s="19">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ceaa8977d2236823/Documents/GitHub/451-DBF-Team01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{9FDDA133-6212-434F-87AA-F220BBD3158A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB3CF111-DA9F-46C3-878A-B159FDEAE657}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="13_ncr:1_{9FDDA133-6212-434F-87AA-F220BBD3158A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF26CAC9-B2FA-48F2-8B06-ABA26ACC337F}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="314">
   <si>
     <t>Parameter</t>
   </si>
@@ -968,6 +968,15 @@
   </si>
   <si>
     <t>I_motor_limit</t>
+  </si>
+  <si>
+    <t>V_S_landing_limit</t>
+  </si>
+  <si>
+    <t>Maximum acceptable stall/touchdown speed for a safe landing on the RFP's grass/dirt surface (R5)</t>
+  </si>
+  <si>
+    <t>ASSUMPTION / placeholder -- invented by Claude per team request (A9 D8 needs a landing-speed limit to check stall speed against payload; none existed in any prior assignment). About 25% above the baseline self-consistent V_S (~10.4 m/s). Team should replace with a real value, e.g. derived from an acceptable touchdown sink rate/energy on unimproved ground, or a pilot-comfort limit.</t>
   </si>
 </sst>
 </file>
@@ -1136,8 +1145,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:F108" totalsRowShown="0">
-  <autoFilter ref="A1:F108" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:F109" totalsRowShown="0">
+  <autoFilter ref="A1:F109" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E43">
     <sortCondition ref="B1:B101"/>
   </sortState>
@@ -1416,7 +1425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F108"/>
+  <dimension ref="A1:F109"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.77734375" bestFit="1" customWidth="1"/>
@@ -3059,7 +3068,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>264</v>
       </c>
@@ -3076,7 +3085,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>266</v>
       </c>
@@ -3093,7 +3102,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>267</v>
       </c>
@@ -3110,7 +3119,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>268</v>
       </c>
@@ -3127,7 +3136,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>269</v>
       </c>
@@ -3144,7 +3153,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>270</v>
       </c>
@@ -3161,7 +3170,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>271</v>
       </c>
@@ -3178,7 +3187,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>272</v>
       </c>
@@ -3195,7 +3204,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>306</v>
       </c>
@@ -3212,7 +3221,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>308</v>
       </c>
@@ -3223,7 +3232,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>309</v>
       </c>
@@ -3234,7 +3243,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>310</v>
       </c>
@@ -3243,6 +3252,26 @@
       </c>
       <c r="C108" s="19">
         <v>50</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>311</v>
+      </c>
+      <c r="B109" t="s">
+        <v>136</v>
+      </c>
+      <c r="C109">
+        <v>13</v>
+      </c>
+      <c r="D109" t="s">
+        <v>137</v>
+      </c>
+      <c r="E109" t="s">
+        <v>312</v>
+      </c>
+      <c r="F109" t="s">
+        <v>313</v>
       </c>
     </row>
   </sheetData>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ceaa8977d2236823/Documents/GitHub/451-DBF-Team01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="13_ncr:1_{9FDDA133-6212-434F-87AA-F220BBD3158A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF26CAC9-B2FA-48F2-8B06-ABA26ACC337F}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="13_ncr:1_{9FDDA133-6212-434F-87AA-F220BBD3158A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABE914F6-7534-42EF-BB9C-503D58A6C7C8}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3258,10 +3258,10 @@
       <c r="A109" t="s">
         <v>311</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B109" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="C109">
+      <c r="C109" s="19">
         <v>13</v>
       </c>
       <c r="D109" t="s">

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ceaa8977d2236823/Documents/GitHub/451-DBF-Team01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="13_ncr:1_{9FDDA133-6212-434F-87AA-F220BBD3158A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABE914F6-7534-42EF-BB9C-503D58A6C7C8}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="13_ncr:1_{9FDDA133-6212-434F-87AA-F220BBD3158A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88D9FE6F-D10D-47C8-99A2-956B2A25DC86}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="315">
   <si>
     <t>Parameter</t>
   </si>
@@ -973,10 +973,13 @@
     <t>V_S_landing_limit</t>
   </si>
   <si>
-    <t>Maximum acceptable stall/touchdown speed for a safe landing on the RFP's grass/dirt surface (R5)</t>
-  </si>
-  <si>
     <t>ASSUMPTION / placeholder -- invented by Claude per team request (A9 D8 needs a landing-speed limit to check stall speed against payload; none existed in any prior assignment). About 25% above the baseline self-consistent V_S (~10.4 m/s). Team should replace with a real value, e.g. derived from an acceptable touchdown sink rate/energy on unimproved ground, or a pilot-comfort limit.</t>
+  </si>
+  <si>
+    <t>A9 Assumption</t>
+  </si>
+  <si>
+    <t>A9 Assumption - Maximum acceptable stall/touchdown speed for a safe landing on the RFP's grass/dirt surface (R5)</t>
   </si>
 </sst>
 </file>
@@ -1045,7 +1048,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1082,6 +1085,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1096,7 +1105,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -1126,6 +1135,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3231,6 +3241,9 @@
       <c r="C106" s="19">
         <v>600</v>
       </c>
+      <c r="E106" s="23" t="s">
+        <v>313</v>
+      </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
@@ -3242,6 +3255,9 @@
       <c r="C107" s="19">
         <v>700</v>
       </c>
+      <c r="E107" s="23" t="s">
+        <v>313</v>
+      </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
@@ -3253,6 +3269,9 @@
       <c r="C108" s="19">
         <v>50</v>
       </c>
+      <c r="E108" s="23" t="s">
+        <v>313</v>
+      </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
@@ -3267,11 +3286,11 @@
       <c r="D109" t="s">
         <v>137</v>
       </c>
-      <c r="E109" t="s">
+      <c r="E109" s="23" t="s">
+        <v>314</v>
+      </c>
+      <c r="F109" t="s">
         <v>312</v>
-      </c>
-      <c r="F109" t="s">
-        <v>313</v>
       </c>
     </row>
   </sheetData>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ceaa8977d2236823/Documents/GitHub/451-DBF-Team01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="13_ncr:1_{9FDDA133-6212-434F-87AA-F220BBD3158A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88D9FE6F-D10D-47C8-99A2-956B2A25DC86}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="13_ncr:1_{9FDDA133-6212-434F-87AA-F220BBD3158A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F77D405F-C3BA-4031-973F-22D491FD56CF}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2814,7 +2814,7 @@
         <v>170</v>
       </c>
       <c r="C81">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="D81" t="s">
         <v>8</v>
@@ -3099,10 +3099,10 @@
       <c r="A98" t="s">
         <v>266</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" s="19" t="s">
         <v>265</v>
       </c>
-      <c r="C98">
+      <c r="C98" s="19">
         <v>1</v>
       </c>
       <c r="D98" t="s">
@@ -3116,10 +3116,10 @@
       <c r="A99" t="s">
         <v>267</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" s="19" t="s">
         <v>265</v>
       </c>
-      <c r="C99">
+      <c r="C99" s="19">
         <v>1</v>
       </c>
       <c r="D99" t="s">
@@ -3235,11 +3235,11 @@
       <c r="A106" t="s">
         <v>308</v>
       </c>
-      <c r="B106" s="19" t="s">
+      <c r="B106" t="s">
         <v>136</v>
       </c>
-      <c r="C106" s="19">
-        <v>600</v>
+      <c r="C106">
+        <v>1000</v>
       </c>
       <c r="E106" s="23" t="s">
         <v>313</v>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ceaa8977d2236823/Documents/GitHub/451-DBF-Team01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="52" documentId="13_ncr:1_{9FDDA133-6212-434F-87AA-F220BBD3158A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F77D405F-C3BA-4031-973F-22D491FD56CF}"/>
+  <xr:revisionPtr revIDLastSave="77" documentId="13_ncr:1_{9FDDA133-6212-434F-87AA-F220BBD3158A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18732B82-4D2B-430B-801A-DF61420F094F}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="316">
   <si>
     <t>Parameter</t>
   </si>
@@ -946,9 +946,6 @@
     <t>Design sink rate for the landing load factor derivation</t>
   </si>
   <si>
-    <t>Main landing gear vertical stiffness (both legs)</t>
-  </si>
-  <si>
     <t>Z_m</t>
   </si>
   <si>
@@ -973,13 +970,19 @@
     <t>V_S_landing_limit</t>
   </si>
   <si>
-    <t>ASSUMPTION / placeholder -- invented by Claude per team request (A9 D8 needs a landing-speed limit to check stall speed against payload; none existed in any prior assignment). About 25% above the baseline self-consistent V_S (~10.4 m/s). Team should replace with a real value, e.g. derived from an acceptable touchdown sink rate/energy on unimproved ground, or a pilot-comfort limit.</t>
-  </si>
-  <si>
     <t>A9 Assumption</t>
   </si>
   <si>
-    <t>A9 Assumption - Maximum acceptable stall/touchdown speed for a safe landing on the RFP's grass/dirt surface (R5)</t>
+    <t>W</t>
+  </si>
+  <si>
+    <t>RFP Max Power Requirement</t>
+  </si>
+  <si>
+    <t>Main landing gear vertical stiffness (both legs), value makes load factor ~ n = 10</t>
+  </si>
+  <si>
+    <t>COMPUTED each run by MaxPayloadSweep.m = 1.25x the baseline self-consistent stall speed; In line with other aircraft of this size.</t>
   </si>
 </sst>
 </file>
@@ -1087,7 +1090,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.79995117038483843"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1125,7 +1128,6 @@
     <xf numFmtId="166" fontId="5" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="5" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1136,12 +1138,25 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{230A598C-34F2-42DB-8399-2F181824D933}"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1162,9 +1177,9 @@
   </sortState>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Parameter"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Subclass"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Value"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Units"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Subclass" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Value" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Units" dataDxfId="0"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Description"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Notes"/>
   </tableColumns>
@@ -1439,24 +1454,24 @@
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="2" max="2" width="15.109375" style="20" customWidth="1"/>
+    <col min="3" max="3" width="13.77734375" style="20" customWidth="1"/>
+    <col min="4" max="4" width="16.88671875" style="20" customWidth="1"/>
     <col min="5" max="5" width="168.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="142.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="20" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
@@ -1470,13 +1485,13 @@
       <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="20">
         <v>0.25</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E2" t="s">
@@ -1487,13 +1502,13 @@
       <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="20">
         <v>0.3</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
@@ -1504,13 +1519,13 @@
       <c r="A4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="20">
         <v>0.1</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E4" t="s">
@@ -1521,13 +1536,13 @@
       <c r="A5" t="s">
         <v>14</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="20">
         <v>1.43</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E5" t="s">
@@ -1538,13 +1553,13 @@
       <c r="A6" t="s">
         <v>16</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="20">
         <v>0.3</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E6" t="s">
@@ -1555,13 +1570,13 @@
       <c r="A7" t="s">
         <v>18</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="20">
         <v>0.43</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E7" t="s">
@@ -1572,13 +1587,13 @@
       <c r="A8" t="s">
         <v>20</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="20">
         <v>-0.08</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E8" t="s">
@@ -1589,13 +1604,13 @@
       <c r="A9" t="s">
         <v>205</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="20">
         <v>-0.08</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="20" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1603,13 +1618,13 @@
       <c r="A10" t="s">
         <v>22</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="20">
         <v>15.8</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="20" t="s">
         <v>23</v>
       </c>
       <c r="E10" t="s">
@@ -1620,13 +1635,13 @@
       <c r="A11" t="s">
         <v>25</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="20">
         <v>0.65</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E11" t="s">
@@ -1637,13 +1652,13 @@
       <c r="A12" t="s">
         <v>27</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="20">
         <v>0.33</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E12" t="s">
@@ -1654,13 +1669,13 @@
       <c r="A13" t="s">
         <v>28</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="20">
         <v>120</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="20" t="s">
         <v>29</v>
       </c>
       <c r="E13" t="s">
@@ -1671,13 +1686,13 @@
       <c r="A14" t="s">
         <v>31</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="20">
         <v>0.1</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E14" t="s">
@@ -1688,13 +1703,13 @@
       <c r="A15" t="s">
         <v>33</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="20">
         <v>1</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E15" t="s">
@@ -1705,13 +1720,13 @@
       <c r="A16" t="s">
         <v>35</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="20">
         <v>1.05</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E16" t="s">
@@ -1722,13 +1737,13 @@
       <c r="A17" t="s">
         <v>37</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="20">
         <v>1.05</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E17" t="s">
@@ -1739,13 +1754,13 @@
       <c r="A18" t="s">
         <v>39</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="20">
         <v>1.02</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E18" t="s">
@@ -1756,13 +1771,13 @@
       <c r="A19" t="s">
         <v>41</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="20">
         <v>9.81</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="20" t="s">
         <v>43</v>
       </c>
       <c r="E19" t="s">
@@ -1773,13 +1788,13 @@
       <c r="A20" t="s">
         <v>45</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="20">
         <v>1.2250000000000001</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="20" t="s">
         <v>46</v>
       </c>
       <c r="E20" t="s">
@@ -1790,13 +1805,13 @@
       <c r="A21" t="s">
         <v>48</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="20">
         <v>1.7960000000000001E-5</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="20" t="s">
         <v>49</v>
       </c>
       <c r="E21" t="s">
@@ -1807,13 +1822,13 @@
       <c r="A22" t="s">
         <v>51</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="20">
         <v>0.05</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E22" t="s">
@@ -1824,13 +1839,13 @@
       <c r="A23" t="s">
         <v>53</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="20">
         <v>0.08</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E23" t="s">
@@ -1841,13 +1856,13 @@
       <c r="A24" t="s">
         <v>55</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="20">
         <v>0.15</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E24" t="s">
@@ -1858,13 +1873,13 @@
       <c r="A25" t="s">
         <v>58</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="20">
         <v>1.5</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="20" t="s">
         <v>59</v>
       </c>
       <c r="E25" t="s">
@@ -1875,13 +1890,13 @@
       <c r="A26" t="s">
         <v>61</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="20">
         <v>5.5E-2</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="20" t="s">
         <v>59</v>
       </c>
       <c r="E26" t="s">
@@ -1892,13 +1907,13 @@
       <c r="A27" t="s">
         <v>63</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="20">
         <v>1</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="20" t="s">
         <v>59</v>
       </c>
       <c r="E27" t="s">
@@ -1909,13 +1924,13 @@
       <c r="A28" t="s">
         <v>65</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="20">
         <v>0.433</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="20" t="s">
         <v>66</v>
       </c>
       <c r="E28" t="s">
@@ -1926,13 +1941,13 @@
       <c r="A29" t="s">
         <v>68</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="20">
         <v>0.14000000000000001</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E29" t="s">
@@ -1943,13 +1958,13 @@
       <c r="A30" t="s">
         <v>70</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="20">
         <v>0.255</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E30" t="s">
@@ -1960,13 +1975,13 @@
       <c r="A31" t="s">
         <v>72</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="20">
         <v>0.1</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E31" t="s">
@@ -1977,13 +1992,13 @@
       <c r="A32" t="s">
         <v>74</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="20">
         <v>0.3</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E32" t="s">
@@ -1994,13 +2009,13 @@
       <c r="A33" t="s">
         <v>76</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="20">
         <v>2.5</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D33" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E33" t="s">
@@ -2011,13 +2026,13 @@
       <c r="A34" t="s">
         <v>78</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="20">
         <v>1.07</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E34" t="s">
@@ -2028,13 +2043,13 @@
       <c r="A35" t="s">
         <v>80</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="20">
         <v>0.1</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D35" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E35" t="s">
@@ -2045,13 +2060,13 @@
       <c r="A36" t="s">
         <v>82</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C36">
+      <c r="C36" s="20">
         <v>0.3</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D36" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E36" t="s">
@@ -2062,13 +2077,13 @@
       <c r="A37" t="s">
         <v>84</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C37">
+      <c r="C37" s="20">
         <v>0.05</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D37" s="20" t="s">
         <v>59</v>
       </c>
       <c r="E37" t="s">
@@ -2079,13 +2094,13 @@
       <c r="A38" t="s">
         <v>86</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C38">
+      <c r="C38" s="20">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D38" s="20" t="s">
         <v>59</v>
       </c>
       <c r="E38" t="s">
@@ -2096,13 +2111,13 @@
       <c r="A39" t="s">
         <v>88</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C39">
+      <c r="C39" s="20">
         <v>0.155</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D39" s="20" t="s">
         <v>59</v>
       </c>
       <c r="E39" t="s">
@@ -2113,13 +2128,13 @@
       <c r="A40" t="s">
         <v>90</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C40">
+      <c r="C40" s="20">
         <v>1.6E-2</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D40" s="20" t="s">
         <v>59</v>
       </c>
       <c r="E40" t="s">
@@ -2130,13 +2145,13 @@
       <c r="A41" t="s">
         <v>92</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C41">
+      <c r="C41" s="20">
         <v>0.05</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D41" s="20" t="s">
         <v>59</v>
       </c>
       <c r="E41" t="s">
@@ -2147,13 +2162,13 @@
       <c r="A42" t="s">
         <v>94</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C42">
+      <c r="C42" s="20">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D42" s="20" t="s">
         <v>59</v>
       </c>
       <c r="E42" t="s">
@@ -2164,13 +2179,13 @@
       <c r="A43" t="s">
         <v>96</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C43">
+      <c r="C43" s="20">
         <v>0.09</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D43" s="20" t="s">
         <v>59</v>
       </c>
       <c r="E43" t="s">
@@ -2181,13 +2196,13 @@
       <c r="A44" t="s">
         <v>98</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C44">
+      <c r="C44" s="20">
         <v>0.01</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D44" s="20" t="s">
         <v>59</v>
       </c>
       <c r="E44" t="s">
@@ -2198,13 +2213,13 @@
       <c r="A45" t="s">
         <v>100</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C45">
+      <c r="C45" s="20">
         <v>0.08</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D45" s="20" t="s">
         <v>101</v>
       </c>
       <c r="E45" t="s">
@@ -2215,13 +2230,13 @@
       <c r="A46" t="s">
         <v>103</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C46">
+      <c r="C46" s="20">
         <v>0.1</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D46" s="20" t="s">
         <v>59</v>
       </c>
       <c r="E46" t="s">
@@ -2232,13 +2247,13 @@
       <c r="A47" t="s">
         <v>105</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C47">
+      <c r="C47" s="20">
         <v>0.04</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D47" s="20" t="s">
         <v>59</v>
       </c>
       <c r="E47" t="s">
@@ -2249,13 +2264,13 @@
       <c r="A48" t="s">
         <v>107</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C48">
+      <c r="C48" s="20">
         <v>0.25</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D48" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E48" t="s">
@@ -2266,13 +2281,13 @@
       <c r="A49" t="s">
         <v>109</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C49">
+      <c r="C49" s="20">
         <v>0.8</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D49" s="20" t="s">
         <v>59</v>
       </c>
       <c r="E49" t="s">
@@ -2283,13 +2298,13 @@
       <c r="A50" t="s">
         <v>111</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C50">
+      <c r="C50" s="20">
         <v>0.17</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D50" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E50" t="s">
@@ -2300,13 +2315,13 @@
       <c r="A51" t="s">
         <v>113</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C51">
+      <c r="C51" s="20">
         <v>2</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D51" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E51" t="s">
@@ -2317,13 +2332,13 @@
       <c r="A52" t="s">
         <v>115</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C52">
+      <c r="C52" s="20">
         <v>1</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D52" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E52" t="s">
@@ -2334,13 +2349,13 @@
       <c r="A53" t="s">
         <v>117</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C53">
+      <c r="C53" s="20">
         <v>0.3</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D53" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E53" t="s">
@@ -2351,13 +2366,13 @@
       <c r="A54" t="s">
         <v>119</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C54">
+      <c r="C54" s="20">
         <v>30</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D54" s="20" t="s">
         <v>23</v>
       </c>
       <c r="E54" t="s">
@@ -2368,13 +2383,13 @@
       <c r="A55" t="s">
         <v>121</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C55">
+      <c r="C55" s="20">
         <v>0.3</v>
       </c>
-      <c r="D55" t="s">
+      <c r="D55" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E55" t="s">
@@ -2385,13 +2400,13 @@
       <c r="A56" t="s">
         <v>123</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C56">
+      <c r="C56" s="20">
         <v>30</v>
       </c>
-      <c r="D56" t="s">
+      <c r="D56" s="20" t="s">
         <v>23</v>
       </c>
       <c r="E56" t="s">
@@ -2402,13 +2417,13 @@
       <c r="A57" t="s">
         <v>125</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C57">
+      <c r="C57" s="20">
         <v>0.25</v>
       </c>
-      <c r="D57" t="s">
+      <c r="D57" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E57" t="s">
@@ -2419,13 +2434,13 @@
       <c r="A58" t="s">
         <v>127</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C58">
+      <c r="C58" s="20">
         <v>0.7</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D58" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E58" t="s">
@@ -2436,13 +2451,13 @@
       <c r="A59" t="s">
         <v>129</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C59">
+      <c r="C59" s="20">
         <v>1</v>
       </c>
-      <c r="D59" t="s">
+      <c r="D59" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E59" t="s">
@@ -2453,13 +2468,13 @@
       <c r="A60" t="s">
         <v>131</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C60">
+      <c r="C60" s="20">
         <v>15</v>
       </c>
-      <c r="D60" t="s">
+      <c r="D60" s="20" t="s">
         <v>23</v>
       </c>
       <c r="E60" t="s">
@@ -2470,13 +2485,13 @@
       <c r="A61" t="s">
         <v>133</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C61">
+      <c r="C61" s="20">
         <v>5</v>
       </c>
-      <c r="D61" t="s">
+      <c r="D61" s="20" t="s">
         <v>23</v>
       </c>
       <c r="E61" t="s">
@@ -2487,13 +2502,13 @@
       <c r="A62" t="s">
         <v>135</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="C62">
+      <c r="C62" s="20">
         <v>10</v>
       </c>
-      <c r="D62" t="s">
+      <c r="D62" s="20" t="s">
         <v>137</v>
       </c>
       <c r="E62" t="s">
@@ -2504,13 +2519,13 @@
       <c r="A63" t="s">
         <v>139</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="C63">
+      <c r="C63" s="20">
         <v>1.1000000000000001</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D63" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E63" t="s">
@@ -2521,13 +2536,13 @@
       <c r="A64" t="s">
         <v>141</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="C64">
+      <c r="C64" s="20">
         <v>0.75</v>
       </c>
-      <c r="D64" t="s">
+      <c r="D64" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E64" t="s">
@@ -2538,13 +2553,13 @@
       <c r="A65" t="s">
         <v>143</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="C65">
+      <c r="C65" s="20">
         <v>1.5</v>
       </c>
-      <c r="D65" t="s">
+      <c r="D65" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E65" t="s">
@@ -2555,13 +2570,13 @@
       <c r="A66" t="s">
         <v>145</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="C66">
+      <c r="C66" s="20">
         <v>20</v>
       </c>
-      <c r="D66" t="s">
+      <c r="D66" s="20" t="s">
         <v>59</v>
       </c>
       <c r="E66" t="s">
@@ -2572,13 +2587,13 @@
       <c r="A67" t="s">
         <v>201</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="C67">
+      <c r="C67" s="20">
         <v>50</v>
       </c>
-      <c r="D67" t="s">
+      <c r="D67" s="20" t="s">
         <v>59</v>
       </c>
       <c r="E67" t="s">
@@ -2589,13 +2604,13 @@
       <c r="A68" t="s">
         <v>146</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="C68">
+      <c r="C68" s="20">
         <v>30</v>
       </c>
-      <c r="D68" t="s">
+      <c r="D68" s="20" t="s">
         <v>59</v>
       </c>
       <c r="E68" t="s">
@@ -2606,13 +2621,13 @@
       <c r="A69" t="s">
         <v>148</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="C69">
+      <c r="C69" s="20">
         <v>100</v>
       </c>
-      <c r="D69" t="s">
+      <c r="D69" s="20" t="s">
         <v>59</v>
       </c>
       <c r="E69" t="s">
@@ -2623,13 +2638,13 @@
       <c r="A70" t="s">
         <v>150</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="C70">
+      <c r="C70" s="20">
         <v>25</v>
       </c>
-      <c r="D70" t="s">
+      <c r="D70" s="20" t="s">
         <v>59</v>
       </c>
       <c r="E70" t="s">
@@ -2640,13 +2655,13 @@
       <c r="A71" t="s">
         <v>152</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="C71">
+      <c r="C71" s="20">
         <v>200</v>
       </c>
-      <c r="D71" t="s">
+      <c r="D71" s="20" t="s">
         <v>59</v>
       </c>
       <c r="E71" t="s">
@@ -2657,13 +2672,13 @@
       <c r="A72" t="s">
         <v>154</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="C72">
+      <c r="C72" s="20">
         <v>95</v>
       </c>
-      <c r="D72" t="s">
+      <c r="D72" s="20" t="s">
         <v>155</v>
       </c>
       <c r="E72" t="s">
@@ -2674,13 +2689,13 @@
       <c r="A73" t="s">
         <v>157</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="C73">
+      <c r="C73" s="20">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="D73" t="s">
+      <c r="D73" s="20" t="s">
         <v>158</v>
       </c>
       <c r="E73" t="s">
@@ -2691,13 +2706,13 @@
       <c r="A74" t="s">
         <v>160</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="C74">
+      <c r="C74" s="20">
         <v>0.8</v>
       </c>
-      <c r="D74" t="s">
+      <c r="D74" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E74" t="s">
@@ -2708,13 +2723,13 @@
       <c r="A75" t="s">
         <v>162</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="C75">
+      <c r="C75" s="20">
         <v>0.52</v>
       </c>
-      <c r="D75" t="s">
+      <c r="D75" s="20" t="s">
         <v>163</v>
       </c>
       <c r="E75" t="s">
@@ -2725,13 +2740,13 @@
       <c r="A76" t="s">
         <v>165</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="C76">
+      <c r="C76" s="20">
         <v>10</v>
       </c>
-      <c r="D76" t="s">
+      <c r="D76" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E76" t="s">
@@ -2742,13 +2757,13 @@
       <c r="A77" t="s">
         <v>167</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="C77">
+      <c r="C77" s="20">
         <v>6</v>
       </c>
-      <c r="D77" t="s">
+      <c r="D77" s="20" t="s">
         <v>163</v>
       </c>
       <c r="E77" t="s">
@@ -2759,13 +2774,13 @@
       <c r="A78" t="s">
         <v>169</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="C78">
+      <c r="C78" s="20">
         <v>0.75</v>
       </c>
-      <c r="D78" t="s">
+      <c r="D78" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E78" t="s">
@@ -2776,13 +2791,13 @@
       <c r="A79" t="s">
         <v>172</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="C79">
+      <c r="C79" s="20">
         <v>0.45</v>
       </c>
-      <c r="D79" t="s">
+      <c r="D79" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E79" t="s">
@@ -2793,13 +2808,13 @@
       <c r="A80" t="s">
         <v>174</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="C80">
+      <c r="C80" s="20">
         <v>1</v>
       </c>
-      <c r="D80" t="s">
+      <c r="D80" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E80" t="s">
@@ -2810,13 +2825,13 @@
       <c r="A81" t="s">
         <v>176</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="C81">
+      <c r="C81" s="20">
         <v>0.75</v>
       </c>
-      <c r="D81" t="s">
+      <c r="D81" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E81" t="s">
@@ -2827,13 +2842,13 @@
       <c r="A82" t="s">
         <v>178</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="C82">
+      <c r="C82" s="20">
         <v>0.95</v>
       </c>
-      <c r="D82" t="s">
+      <c r="D82" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E82" t="s">
@@ -2844,13 +2859,13 @@
       <c r="A83" t="s">
         <v>180</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="C83">
+      <c r="C83" s="20">
         <v>950</v>
       </c>
-      <c r="D83" t="s">
+      <c r="D83" s="20" t="s">
         <v>181</v>
       </c>
       <c r="E83" t="s">
@@ -2861,13 +2876,13 @@
       <c r="A84" t="s">
         <v>183</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="C84">
+      <c r="C84" s="20">
         <v>1.39</v>
       </c>
-      <c r="D84" t="s">
+      <c r="D84" s="20" t="s">
         <v>184</v>
       </c>
       <c r="E84" t="s">
@@ -2878,13 +2893,13 @@
       <c r="A85" t="s">
         <v>186</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="C85">
+      <c r="C85" s="20">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="D85" t="s">
+      <c r="D85" s="20" t="s">
         <v>187</v>
       </c>
       <c r="E85" t="s">
@@ -2895,13 +2910,13 @@
       <c r="A86" t="s">
         <v>189</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="C86">
+      <c r="C86" s="20">
         <v>14.8</v>
       </c>
-      <c r="D86" t="s">
+      <c r="D86" s="20" t="s">
         <v>190</v>
       </c>
       <c r="E86" t="s">
@@ -2912,13 +2927,13 @@
       <c r="A87" t="s">
         <v>191</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C87" s="20" t="s">
         <v>204</v>
       </c>
-      <c r="D87" t="s">
+      <c r="D87" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E87" t="s">
@@ -2929,13 +2944,13 @@
       <c r="A88" t="s">
         <v>193</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="C88">
+      <c r="C88" s="20">
         <v>527000</v>
       </c>
-      <c r="D88" t="s">
+      <c r="D88" s="20" t="s">
         <v>194</v>
       </c>
       <c r="E88" t="s">
@@ -2946,13 +2961,13 @@
       <c r="A89" t="s">
         <v>196</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="C89">
+      <c r="C89" s="20">
         <v>0.8</v>
       </c>
-      <c r="D89" t="s">
+      <c r="D89" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E89" t="s">
@@ -2963,13 +2978,13 @@
       <c r="A90" t="s">
         <v>198</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="C90">
+      <c r="C90" s="20">
         <v>0.7</v>
       </c>
-      <c r="D90" t="s">
+      <c r="D90" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E90" t="s">
@@ -2980,13 +2995,13 @@
       <c r="A91" t="s">
         <v>248</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" s="20" t="s">
         <v>249</v>
       </c>
-      <c r="C91">
+      <c r="C91" s="20">
         <v>1</v>
       </c>
-      <c r="D91" t="s">
+      <c r="D91" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E91" t="s">
@@ -2997,13 +3012,13 @@
       <c r="A92" t="s">
         <v>251</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" s="20" t="s">
         <v>249</v>
       </c>
-      <c r="C92">
+      <c r="C92" s="20">
         <v>1.2</v>
       </c>
-      <c r="D92" t="s">
+      <c r="D92" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E92" t="s">
@@ -3014,13 +3029,13 @@
       <c r="A93" t="s">
         <v>253</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" s="20" t="s">
         <v>249</v>
       </c>
-      <c r="C93">
+      <c r="C93" s="20">
         <v>1</v>
       </c>
-      <c r="D93" t="s">
+      <c r="D93" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E93" t="s">
@@ -3031,13 +3046,13 @@
       <c r="A94" t="s">
         <v>255</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" s="20" t="s">
         <v>249</v>
       </c>
-      <c r="C94">
+      <c r="C94" s="20">
         <v>0.85</v>
       </c>
-      <c r="D94" t="s">
+      <c r="D94" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E94" t="s">
@@ -3048,13 +3063,13 @@
       <c r="A95" t="s">
         <v>261</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95" s="20" t="s">
         <v>249</v>
       </c>
-      <c r="C95">
+      <c r="C95" s="20">
         <v>5.5</v>
       </c>
-      <c r="D95" t="s">
+      <c r="D95" s="20" t="s">
         <v>190</v>
       </c>
       <c r="E95" t="s">
@@ -3065,232 +3080,238 @@
       <c r="A96" t="s">
         <v>263</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C96">
+      <c r="C96" s="20">
         <v>-0.66</v>
       </c>
-      <c r="D96" t="s">
+      <c r="D96" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E96" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>264</v>
       </c>
-      <c r="B97" s="19" t="s">
+      <c r="B97" s="21" t="s">
         <v>265</v>
       </c>
-      <c r="C97" s="19">
+      <c r="C97" s="21">
         <v>0.3</v>
       </c>
-      <c r="D97" t="s">
+      <c r="D97" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E97" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>266</v>
       </c>
-      <c r="B98" s="19" t="s">
+      <c r="B98" s="21" t="s">
         <v>265</v>
       </c>
-      <c r="C98" s="19">
+      <c r="C98" s="21">
         <v>1</v>
       </c>
-      <c r="D98" t="s">
+      <c r="D98" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E98" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>267</v>
       </c>
-      <c r="B99" s="19" t="s">
+      <c r="B99" s="21" t="s">
         <v>265</v>
       </c>
-      <c r="C99" s="19">
+      <c r="C99" s="21">
         <v>1</v>
       </c>
-      <c r="D99" t="s">
+      <c r="D99" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E99" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>268</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" s="20" t="s">
         <v>265</v>
       </c>
-      <c r="C100">
+      <c r="C100" s="20">
         <v>1</v>
       </c>
-      <c r="D100" t="s">
+      <c r="D100" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E100" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>269</v>
       </c>
-      <c r="B101" s="19" t="s">
+      <c r="B101" s="21" t="s">
         <v>265</v>
       </c>
-      <c r="C101" s="19">
+      <c r="C101" s="21">
         <v>0.03</v>
       </c>
-      <c r="D101" t="s">
+      <c r="D101" s="20" t="s">
         <v>59</v>
       </c>
       <c r="E101" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>270</v>
       </c>
-      <c r="B102" s="19" t="s">
+      <c r="B102" s="21" t="s">
         <v>265</v>
       </c>
-      <c r="C102" s="19">
+      <c r="C102" s="21">
         <v>0.3</v>
       </c>
-      <c r="D102" t="s">
+      <c r="D102" s="20" t="s">
         <v>59</v>
       </c>
       <c r="E102" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>271</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" s="20" t="s">
         <v>265</v>
       </c>
-      <c r="C103">
+      <c r="C103" s="20">
         <v>1</v>
       </c>
-      <c r="D103" t="s">
+      <c r="D103" s="20" t="s">
         <v>137</v>
       </c>
       <c r="E103" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>272</v>
       </c>
-      <c r="B104" s="19" t="s">
+      <c r="B104" s="21" t="s">
         <v>265</v>
       </c>
-      <c r="C104" s="19">
+      <c r="C104" s="21">
         <v>35000</v>
       </c>
-      <c r="D104" t="s">
+      <c r="D104" s="20" t="s">
         <v>273</v>
       </c>
       <c r="E104" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
+        <v>305</v>
+      </c>
+      <c r="B105" s="21" t="s">
+        <v>265</v>
+      </c>
+      <c r="C105" s="21">
+        <v>0.22</v>
+      </c>
+      <c r="D105" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="E105" t="s">
         <v>306</v>
       </c>
-      <c r="B105" s="19" t="s">
-        <v>265</v>
-      </c>
-      <c r="C105" s="19">
-        <v>0.22</v>
-      </c>
-      <c r="D105" t="s">
-        <v>59</v>
-      </c>
-      <c r="E105" t="s">
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
+      <c r="B106" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="C106" s="20">
+        <v>1000</v>
+      </c>
+      <c r="D106" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="E106" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
         <v>308</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B107" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="C107" s="21">
+        <v>700</v>
+      </c>
+      <c r="D107" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="E107" s="22" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>309</v>
+      </c>
+      <c r="B108" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="C108" s="21">
+        <v>50</v>
+      </c>
+      <c r="D108" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="E108" s="22" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>310</v>
+      </c>
+      <c r="B109" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="C106">
-        <v>1000</v>
-      </c>
-      <c r="E106" s="23" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
-        <v>309</v>
-      </c>
-      <c r="B107" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="C107" s="19">
-        <v>700</v>
-      </c>
-      <c r="E107" s="23" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
-        <v>310</v>
-      </c>
-      <c r="B108" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="C108" s="19">
-        <v>50</v>
-      </c>
-      <c r="E108" s="23" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
-        <v>311</v>
-      </c>
-      <c r="B109" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="C109" s="19">
-        <v>13</v>
-      </c>
-      <c r="D109" t="s">
+      <c r="C109" s="23">
+        <v>11.941543440928031</v>
+      </c>
+      <c r="D109" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="E109" s="23" t="s">
-        <v>314</v>
-      </c>
-      <c r="F109" t="s">
-        <v>312</v>
+      <c r="E109" t="s">
+        <v>315</v>
       </c>
     </row>
   </sheetData>
@@ -3307,35 +3328,35 @@
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.44140625" customWidth="1"/>
-    <col min="2" max="3" width="32.44140625" style="21" customWidth="1"/>
-    <col min="4" max="4" width="13.33203125" style="21" customWidth="1"/>
+    <col min="2" max="3" width="32.44140625" style="20" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" style="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>274</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="19" t="s">
         <v>294</v>
       </c>
-      <c r="D1" s="20" t="s">
-        <v>304</v>
+      <c r="D1" s="19" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>276</v>
       </c>
-      <c r="B2" s="22">
+      <c r="B2" s="21">
         <v>25.9</v>
       </c>
-      <c r="C2" s="22">
+      <c r="C2" s="21">
         <v>0</v>
       </c>
-      <c r="D2" s="22">
+      <c r="D2" s="21">
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
@@ -3343,13 +3364,13 @@
       <c r="A3" t="s">
         <v>277</v>
       </c>
-      <c r="B3" s="22">
+      <c r="B3" s="21">
         <v>116.7</v>
       </c>
-      <c r="C3" s="22">
+      <c r="C3" s="21">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="D3" s="22">
+      <c r="D3" s="21">
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
@@ -3357,13 +3378,13 @@
       <c r="A4" t="s">
         <v>278</v>
       </c>
-      <c r="B4" s="22">
+      <c r="B4" s="21">
         <v>22.7</v>
       </c>
-      <c r="C4" s="22">
+      <c r="C4" s="21">
         <v>5.5E-2</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="21">
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
@@ -3371,27 +3392,27 @@
       <c r="A5" t="s">
         <v>279</v>
       </c>
-      <c r="B5" s="22">
+      <c r="B5" s="21">
         <v>32.4</v>
       </c>
-      <c r="C5" s="22">
+      <c r="C5" s="21">
         <v>0.09</v>
       </c>
-      <c r="D5" s="22">
+      <c r="D5" s="21">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>305</v>
-      </c>
-      <c r="B6" s="22">
+        <v>304</v>
+      </c>
+      <c r="B6" s="21">
         <v>45.4</v>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="21">
         <v>1.1000000000000001</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="21">
         <v>-4.4999999999999998E-2</v>
       </c>
     </row>
@@ -3399,13 +3420,13 @@
       <c r="A7" t="s">
         <v>280</v>
       </c>
-      <c r="B7" s="22">
+      <c r="B7" s="21">
         <v>440.8</v>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="21">
         <v>0.12</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="21">
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
@@ -3413,13 +3434,13 @@
       <c r="A8" t="s">
         <v>281</v>
       </c>
-      <c r="B8" s="22">
+      <c r="B8" s="21">
         <v>58.3</v>
       </c>
-      <c r="C8" s="22">
+      <c r="C8" s="21">
         <v>0.23</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="21">
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
@@ -3427,13 +3448,13 @@
       <c r="A9" t="s">
         <v>282</v>
       </c>
-      <c r="B9" s="22">
+      <c r="B9" s="21">
         <v>64.8</v>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="21">
         <v>0.3</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="21">
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
@@ -3441,13 +3462,13 @@
       <c r="A10" t="s">
         <v>283</v>
       </c>
-      <c r="B10" s="22">
+      <c r="B10" s="21">
         <v>259.3</v>
       </c>
-      <c r="C10" s="22">
+      <c r="C10" s="21">
         <v>0.32</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="21">
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
@@ -3455,13 +3476,13 @@
       <c r="A11" t="s">
         <v>284</v>
       </c>
-      <c r="B11" s="22">
+      <c r="B11" s="21">
         <v>13.4</v>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="21">
         <v>0.4</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="21">
         <v>5.5E-2</v>
       </c>
     </row>
@@ -3469,13 +3490,13 @@
       <c r="A12" t="s">
         <v>285</v>
       </c>
-      <c r="B12" s="22">
+      <c r="B12" s="21">
         <v>13.4</v>
       </c>
-      <c r="C12" s="22">
+      <c r="C12" s="21">
         <v>0.4</v>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="21">
         <v>5.5E-2</v>
       </c>
     </row>
@@ -3483,13 +3504,13 @@
       <c r="A13" t="s">
         <v>286</v>
       </c>
-      <c r="B13" s="21">
+      <c r="B13" s="20">
         <v>520</v>
       </c>
-      <c r="C13" s="22">
+      <c r="C13" s="21">
         <v>0.4</v>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="21">
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
@@ -3497,13 +3518,13 @@
       <c r="A14" t="s">
         <v>287</v>
       </c>
-      <c r="B14" s="22">
+      <c r="B14" s="21">
         <v>907.6</v>
       </c>
-      <c r="C14" s="22">
+      <c r="C14" s="21">
         <v>0.40699999999999997</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="21">
         <v>5.5E-2</v>
       </c>
     </row>
@@ -3511,13 +3532,13 @@
       <c r="A15" t="s">
         <v>288</v>
       </c>
-      <c r="B15" s="22">
+      <c r="B15" s="21">
         <v>142.6</v>
       </c>
-      <c r="C15" s="22">
+      <c r="C15" s="21">
         <v>0.35199999999999998</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="21">
         <v>-7.8E-2</v>
       </c>
     </row>
@@ -3525,13 +3546,13 @@
       <c r="A16" t="s">
         <v>289</v>
       </c>
-      <c r="B16" s="22">
+      <c r="B16" s="21">
         <v>1231.8</v>
       </c>
-      <c r="C16" s="22">
+      <c r="C16" s="21">
         <v>0.55000000000000004</v>
       </c>
-      <c r="D16" s="22">
+      <c r="D16" s="21">
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
@@ -3539,13 +3560,13 @@
       <c r="A17" t="s">
         <v>290</v>
       </c>
-      <c r="B17" s="22">
+      <c r="B17" s="21">
         <v>13.4</v>
       </c>
-      <c r="C17" s="22">
+      <c r="C17" s="21">
         <v>1</v>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="21">
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
@@ -3553,13 +3574,13 @@
       <c r="A18" t="s">
         <v>291</v>
       </c>
-      <c r="B18" s="22">
+      <c r="B18" s="21">
         <v>13.4</v>
       </c>
-      <c r="C18" s="22">
+      <c r="C18" s="21">
         <v>1</v>
       </c>
-      <c r="D18" s="22">
+      <c r="D18" s="21">
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
@@ -3567,13 +3588,13 @@
       <c r="A19" t="s">
         <v>293</v>
       </c>
-      <c r="B19" s="22">
+      <c r="B19" s="21">
         <v>77.8</v>
       </c>
-      <c r="C19" s="22">
+      <c r="C19" s="21">
         <v>1.05</v>
       </c>
-      <c r="D19" s="22">
+      <c r="D19" s="21">
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
@@ -3581,13 +3602,13 @@
       <c r="A20" t="s">
         <v>292</v>
       </c>
-      <c r="B20" s="22">
+      <c r="B20" s="21">
         <v>51.9</v>
       </c>
-      <c r="C20" s="22">
+      <c r="C20" s="21">
         <v>1.05</v>
       </c>
-      <c r="D20" s="22">
+      <c r="D20" s="21">
         <v>0.15</v>
       </c>
     </row>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ceaa8977d2236823/Documents/GitHub/451-DBF-Team01/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\Fall 2026\AAE 451\451-DBF-Team01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="13_ncr:1_{9FDDA133-6212-434F-87AA-F220BBD3158A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18732B82-4D2B-430B-801A-DF61420F094F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{914314AF-C084-405E-9BA6-7E6E9B0AA2AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1108,7 +1108,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -1138,9 +1138,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1171,7 +1168,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:F109" totalsRowShown="0">
-  <autoFilter ref="A1:F109" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <autoFilter ref="A1:F109" xr:uid="{00000000-0009-0000-0100-000001000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="prop"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E43">
     <sortCondition ref="B1:B101"/>
   </sortState>
@@ -1451,17 +1454,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F109"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.109375" style="20" customWidth="1"/>
-    <col min="3" max="3" width="13.77734375" style="20" customWidth="1"/>
-    <col min="4" max="4" width="16.88671875" style="20" customWidth="1"/>
-    <col min="5" max="5" width="168.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="142.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" style="20" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" style="20" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" style="20" customWidth="1"/>
+    <col min="5" max="5" width="168.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="142.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1481,7 +1484,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1498,7 +1501,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1515,7 +1518,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1532,7 +1535,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -1549,7 +1552,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -1566,7 +1569,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -1583,7 +1586,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -1600,7 +1603,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>205</v>
       </c>
@@ -1614,7 +1617,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -1631,7 +1634,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1648,7 +1651,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -1665,7 +1668,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -1682,7 +1685,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -1699,7 +1702,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -1716,7 +1719,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>35</v>
       </c>
@@ -1733,7 +1736,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>37</v>
       </c>
@@ -1750,7 +1753,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>39</v>
       </c>
@@ -1767,7 +1770,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>41</v>
       </c>
@@ -1784,7 +1787,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>45</v>
       </c>
@@ -1801,7 +1804,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -1818,7 +1821,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -1835,7 +1838,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -1852,7 +1855,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -1869,7 +1872,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>58</v>
       </c>
@@ -1886,7 +1889,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>61</v>
       </c>
@@ -1903,7 +1906,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>63</v>
       </c>
@@ -1920,7 +1923,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>65</v>
       </c>
@@ -1937,7 +1940,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -1954,7 +1957,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -1971,7 +1974,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>72</v>
       </c>
@@ -1988,7 +1991,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>74</v>
       </c>
@@ -2005,7 +2008,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>76</v>
       </c>
@@ -2022,7 +2025,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>78</v>
       </c>
@@ -2039,7 +2042,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>80</v>
       </c>
@@ -2056,7 +2059,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>82</v>
       </c>
@@ -2073,7 +2076,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>84</v>
       </c>
@@ -2090,7 +2093,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>86</v>
       </c>
@@ -2107,7 +2110,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>88</v>
       </c>
@@ -2124,7 +2127,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>90</v>
       </c>
@@ -2141,7 +2144,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>92</v>
       </c>
@@ -2158,7 +2161,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>94</v>
       </c>
@@ -2175,7 +2178,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>96</v>
       </c>
@@ -2192,7 +2195,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>98</v>
       </c>
@@ -2209,7 +2212,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>100</v>
       </c>
@@ -2226,7 +2229,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>103</v>
       </c>
@@ -2243,7 +2246,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>105</v>
       </c>
@@ -2260,7 +2263,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>107</v>
       </c>
@@ -2277,7 +2280,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>109</v>
       </c>
@@ -2294,7 +2297,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>111</v>
       </c>
@@ -2311,7 +2314,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>113</v>
       </c>
@@ -2328,7 +2331,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>115</v>
       </c>
@@ -2345,7 +2348,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>117</v>
       </c>
@@ -2362,7 +2365,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>119</v>
       </c>
@@ -2379,7 +2382,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>121</v>
       </c>
@@ -2396,7 +2399,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>123</v>
       </c>
@@ -2413,7 +2416,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>125</v>
       </c>
@@ -2430,7 +2433,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>127</v>
       </c>
@@ -2447,7 +2450,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>129</v>
       </c>
@@ -2464,7 +2467,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>131</v>
       </c>
@@ -2481,7 +2484,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>133</v>
       </c>
@@ -2498,7 +2501,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>135</v>
       </c>
@@ -2515,7 +2518,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>139</v>
       </c>
@@ -2532,7 +2535,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>141</v>
       </c>
@@ -2549,7 +2552,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>143</v>
       </c>
@@ -2566,7 +2569,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>145</v>
       </c>
@@ -2583,7 +2586,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>201</v>
       </c>
@@ -2600,7 +2603,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>146</v>
       </c>
@@ -2617,7 +2620,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>148</v>
       </c>
@@ -2634,7 +2637,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>150</v>
       </c>
@@ -2651,7 +2654,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>152</v>
       </c>
@@ -2668,7 +2671,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>154</v>
       </c>
@@ -2685,7 +2688,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>157</v>
       </c>
@@ -2702,7 +2705,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>160</v>
       </c>
@@ -2719,7 +2722,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>162</v>
       </c>
@@ -2736,7 +2739,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>165</v>
       </c>
@@ -2753,7 +2756,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>167</v>
       </c>
@@ -2770,7 +2773,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>169</v>
       </c>
@@ -2787,7 +2790,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>172</v>
       </c>
@@ -2804,7 +2807,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>174</v>
       </c>
@@ -2821,7 +2824,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>176</v>
       </c>
@@ -2838,7 +2841,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>178</v>
       </c>
@@ -2855,7 +2858,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>180</v>
       </c>
@@ -2863,7 +2866,7 @@
         <v>170</v>
       </c>
       <c r="C83" s="20">
-        <v>950</v>
+        <v>980</v>
       </c>
       <c r="D83" s="20" t="s">
         <v>181</v>
@@ -2872,7 +2875,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>183</v>
       </c>
@@ -2880,7 +2883,7 @@
         <v>170</v>
       </c>
       <c r="C84" s="20">
-        <v>1.39</v>
+        <v>1.84</v>
       </c>
       <c r="D84" s="20" t="s">
         <v>184</v>
@@ -2889,7 +2892,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>186</v>
       </c>
@@ -2897,7 +2900,7 @@
         <v>170</v>
       </c>
       <c r="C85" s="20">
-        <v>2.9000000000000001E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="D85" s="20" t="s">
         <v>187</v>
@@ -2906,7 +2909,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>189</v>
       </c>
@@ -2923,7 +2926,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>191</v>
       </c>
@@ -2940,7 +2943,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>193</v>
       </c>
@@ -2957,7 +2960,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>196</v>
       </c>
@@ -2974,7 +2977,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>198</v>
       </c>
@@ -2991,7 +2994,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>248</v>
       </c>
@@ -3008,7 +3011,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>251</v>
       </c>
@@ -3025,7 +3028,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>253</v>
       </c>
@@ -3042,7 +3045,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>255</v>
       </c>
@@ -3059,7 +3062,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>261</v>
       </c>
@@ -3076,7 +3079,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>263</v>
       </c>
@@ -3093,7 +3096,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>264</v>
       </c>
@@ -3110,7 +3113,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>266</v>
       </c>
@@ -3127,7 +3130,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>267</v>
       </c>
@@ -3144,7 +3147,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>268</v>
       </c>
@@ -3161,7 +3164,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>269</v>
       </c>
@@ -3178,7 +3181,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>270</v>
       </c>
@@ -3195,7 +3198,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>271</v>
       </c>
@@ -3212,7 +3215,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>272</v>
       </c>
@@ -3229,7 +3232,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>305</v>
       </c>
@@ -3246,7 +3249,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>307</v>
       </c>
@@ -3263,7 +3266,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>308</v>
       </c>
@@ -3280,7 +3283,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>309</v>
       </c>
@@ -3297,14 +3300,14 @@
         <v>311</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>310</v>
       </c>
-      <c r="B109" s="23" t="s">
+      <c r="B109" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="C109" s="23">
+      <c r="C109" s="20">
         <v>11.941543440928031</v>
       </c>
       <c r="D109" s="20" t="s">
@@ -3325,14 +3328,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFCC8514-E0AF-4C67-BF86-8649FC702924}">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.44140625" customWidth="1"/>
-    <col min="2" max="3" width="32.44140625" style="20" customWidth="1"/>
-    <col min="4" max="4" width="13.33203125" style="20" customWidth="1"/>
+    <col min="1" max="1" width="32.42578125" customWidth="1"/>
+    <col min="2" max="3" width="32.42578125" style="20" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" style="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>274</v>
       </c>
@@ -3346,7 +3349,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>276</v>
       </c>
@@ -3360,7 +3363,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>277</v>
       </c>
@@ -3374,7 +3377,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>278</v>
       </c>
@@ -3388,7 +3391,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>279</v>
       </c>
@@ -3402,7 +3405,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>304</v>
       </c>
@@ -3416,7 +3419,7 @@
         <v>-4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>280</v>
       </c>
@@ -3430,7 +3433,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>281</v>
       </c>
@@ -3444,7 +3447,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>282</v>
       </c>
@@ -3458,7 +3461,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>283</v>
       </c>
@@ -3472,7 +3475,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>284</v>
       </c>
@@ -3486,7 +3489,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>285</v>
       </c>
@@ -3500,7 +3503,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>286</v>
       </c>
@@ -3514,7 +3517,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>287</v>
       </c>
@@ -3528,7 +3531,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>288</v>
       </c>
@@ -3542,7 +3545,7 @@
         <v>-7.8E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>289</v>
       </c>
@@ -3556,7 +3559,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>290</v>
       </c>
@@ -3570,7 +3573,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>291</v>
       </c>
@@ -3584,7 +3587,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>293</v>
       </c>
@@ -3598,7 +3601,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>292</v>
       </c>
@@ -3620,26 +3623,26 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{118BE621-EF6B-4648-868E-9937B9C5B685}">
   <dimension ref="A1:F32"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="48.109375" style="2" customWidth="1"/>
-    <col min="2" max="4" width="15.77734375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="3.77734375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="46.77734375" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="8.77734375" style="2"/>
+    <col min="1" max="1" width="48.140625" style="2" customWidth="1"/>
+    <col min="2" max="4" width="15.7109375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="3.7109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="46.7109375" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="8.7109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>208</v>
       </c>
@@ -3653,7 +3656,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>212</v>
       </c>
@@ -3671,7 +3674,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>214</v>
       </c>
@@ -3691,7 +3694,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>216</v>
       </c>
@@ -3711,7 +3714,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>217</v>
       </c>
@@ -3729,7 +3732,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>218</v>
       </c>
@@ -3749,7 +3752,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>220</v>
       </c>
@@ -3766,7 +3769,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>222</v>
       </c>
@@ -3783,7 +3786,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>223</v>
       </c>
@@ -3803,7 +3806,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>225</v>
       </c>
@@ -3820,7 +3823,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>257</v>
       </c>
@@ -3840,7 +3843,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>258</v>
       </c>
@@ -3860,7 +3863,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>227</v>
       </c>
@@ -3868,7 +3871,7 @@
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>228</v>
       </c>
@@ -3885,7 +3888,7 @@
         <v>1.9823131728623846</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>229</v>
       </c>
@@ -3902,7 +3905,7 @@
         <v>1.1592794807274085</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>230</v>
       </c>
@@ -3919,7 +3922,7 @@
         <v>-0.62740704594148844</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>231</v>
       </c>
@@ -3936,7 +3939,7 @@
         <v>-0.96540266006846076</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>232</v>
       </c>
@@ -3944,7 +3947,7 @@
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>233</v>
       </c>
@@ -3961,7 +3964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>234</v>
       </c>
@@ -3978,7 +3981,7 @@
         <v>0.52359877559829882</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>235</v>
       </c>
@@ -3995,7 +3998,7 @@
         <v>-0.50548365077118673</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>236</v>
       </c>
@@ -4012,7 +4015,7 @@
         <v>324.01250000000005</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>237</v>
       </c>
@@ -4029,7 +4032,7 @@
         <v>1.42884E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>238</v>
       </c>
@@ -4046,7 +4049,7 @@
         <v>-0.13760360258695806</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>239</v>
       </c>
@@ -4063,7 +4066,7 @@
         <v>0.13760360258695806</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>240</v>
       </c>
@@ -4080,7 +4083,7 @@
         <v>22.925083964169769</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>241</v>
       </c>
@@ -4088,7 +4091,7 @@
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>242</v>
       </c>
@@ -4096,7 +4099,7 @@
       <c r="C31" s="14"/>
       <c r="D31" s="14"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>243</v>
       </c>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,16 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\Fall 2026\AAE 451\451-DBF-Team01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{914314AF-C084-405E-9BA6-7E6E9B0AA2AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37DAE441-3691-47BB-B387-517F08F01369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="MassBudget" sheetId="3" r:id="rId2"/>
-    <sheet name="Hinge Moments" sheetId="2" r:id="rId3"/>
+    <sheet name="Inputs" sheetId="1" r:id="rId1"/>
+    <sheet name="Outputs" sheetId="4" r:id="rId2"/>
+    <sheet name="MassBudget" sheetId="3" r:id="rId3"/>
+    <sheet name="Hinge Moments" sheetId="2" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="true"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1386" uniqueCount="523">
   <si>
     <t>Parameter</t>
   </si>
@@ -983,18 +985,639 @@
   </si>
   <si>
     <t>COMPUTED each run by MaxPayloadSweep.m = 1.25x the baseline self-consistent stall speed; In line with other aircraft of this size.</t>
+  </si>
+  <si>
+    <t>CL_TO</t>
+  </si>
+  <si>
+    <t>CL_R</t>
+  </si>
+  <si>
+    <t>e_wing</t>
+  </si>
+  <si>
+    <t>K_wing</t>
+  </si>
+  <si>
+    <t>K_hstab</t>
+  </si>
+  <si>
+    <t>CD_0</t>
+  </si>
+  <si>
+    <t>CD_C</t>
+  </si>
+  <si>
+    <t>CD_TO</t>
+  </si>
+  <si>
+    <t>CD_G</t>
+  </si>
+  <si>
+    <t>L_D_C</t>
+  </si>
+  <si>
+    <t>L_D_max</t>
+  </si>
+  <si>
+    <t>S_wing</t>
+  </si>
+  <si>
+    <t>c_wing</t>
+  </si>
+  <si>
+    <t>AR</t>
+  </si>
+  <si>
+    <t>S_hstab</t>
+  </si>
+  <si>
+    <t>span_hstab</t>
+  </si>
+  <si>
+    <t>c_hstab</t>
+  </si>
+  <si>
+    <t>V_H</t>
+  </si>
+  <si>
+    <t>S_v</t>
+  </si>
+  <si>
+    <t>S_fin</t>
+  </si>
+  <si>
+    <t>span_vstab</t>
+  </si>
+  <si>
+    <t>c_vstab</t>
+  </si>
+  <si>
+    <t>V_C</t>
+  </si>
+  <si>
+    <t>V_TO</t>
+  </si>
+  <si>
+    <t>V_M</t>
+  </si>
+  <si>
+    <t>V_S_M</t>
+  </si>
+  <si>
+    <t>bank_angle</t>
+  </si>
+  <si>
+    <t>gamma</t>
+  </si>
+  <si>
+    <t>MTOW</t>
+  </si>
+  <si>
+    <t>totBatteryMass_kg</t>
+  </si>
+  <si>
+    <t>totBatteryEnergy_J</t>
+  </si>
+  <si>
+    <t>usableBatteryEnergy_J</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Takeoff CL before rotation, no flaps, same as cruise</t>
+  </si>
+  <si>
+    <t>Rotation CL</t>
+  </si>
+  <si>
+    <t>Oswald efficiency, Sadraey eqn 5.27a</t>
+  </si>
+  <si>
+    <t>Induced drag factor</t>
+  </si>
+  <si>
+    <t>H-stab induced drag factor</t>
+  </si>
+  <si>
+    <t>Cruise CD</t>
+  </si>
+  <si>
+    <t>Takeoff CD</t>
+  </si>
+  <si>
+    <t>Ground roll CD, Sadraey eqn 4.67a</t>
+  </si>
+  <si>
+    <t>L/D at cruise</t>
+  </si>
+  <si>
+    <t>Max L/D of parabolic polar</t>
+  </si>
+  <si>
+    <t>Wing area from design wing loading</t>
+  </si>
+  <si>
+    <t>Wing chord, area excludes fuselage section</t>
+  </si>
+  <si>
+    <t>Wing aspect ratio</t>
+  </si>
+  <si>
+    <t>H-stab area from area ratio</t>
+  </si>
+  <si>
+    <t>H-stab span</t>
+  </si>
+  <si>
+    <t>H-stab chord</t>
+  </si>
+  <si>
+    <t>Horizontal tail volume coefficient</t>
+  </si>
+  <si>
+    <t>Total fin area from volume coefficient, fin arm = l_t</t>
+  </si>
+  <si>
+    <t>Area per fin</t>
+  </si>
+  <si>
+    <t>Fin span</t>
+  </si>
+  <si>
+    <t>Fin chord</t>
+  </si>
+  <si>
+    <t>Cruise speed from design CL_C</t>
+  </si>
+  <si>
+    <t>Takeoff speed</t>
+  </si>
+  <si>
+    <t>Maneuver speed for turn radius R_M</t>
+  </si>
+  <si>
+    <t>Stall speed at load factor n</t>
+  </si>
+  <si>
+    <t>Bank angle at load factor n</t>
+  </si>
+  <si>
+    <t>Climb angle</t>
+  </si>
+  <si>
+    <t>Takeoff weight</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Calculated</t>
+  </si>
+  <si>
+    <t>Overwritten input (Sheet1 value: 6)</t>
+  </si>
+  <si>
+    <t>Written by writeOutputs.m on 2026-10-06 13:51</t>
+  </si>
+  <si>
+    <t>Written by writeOutputs.m on 2026-10-06 13:54</t>
+  </si>
+  <si>
+    <t>COMPUTED each run by MaxPayloadSweep.m = 1.25x the baseline self-consistent stall speed -- not read back in as an input, edit LANDING_SPEED_RATIO in that script instead.</t>
+  </si>
+  <si>
+    <t>CL_Alpha_Tail</t>
+  </si>
+  <si>
+    <t>CL_Alpha_Wing</t>
+  </si>
+  <si>
+    <t>de_da</t>
+  </si>
+  <si>
+    <t>CL_Alpha</t>
+  </si>
+  <si>
+    <t>CM_0</t>
+  </si>
+  <si>
+    <t>tau_e</t>
+  </si>
+  <si>
+    <t>tau_a</t>
+  </si>
+  <si>
+    <t>CL_Alpha_VT</t>
+  </si>
+  <si>
+    <t>tau_r</t>
+  </si>
+  <si>
+    <t>Cn_beta_VT</t>
+  </si>
+  <si>
+    <t>x_cg_fwd</t>
+  </si>
+  <si>
+    <t>x_cg_aft</t>
+  </si>
+  <si>
+    <t>x_n</t>
+  </si>
+  <si>
+    <t>x_cg_design</t>
+  </si>
+  <si>
+    <t>V_max_level</t>
+  </si>
+  <si>
+    <t>T_static_design</t>
+  </si>
+  <si>
+    <t>n_limit_pos</t>
+  </si>
+  <si>
+    <t>n_limit_neg</t>
+  </si>
+  <si>
+    <t>n_ult_pos</t>
+  </si>
+  <si>
+    <t>n_ult_neg</t>
+  </si>
+  <si>
+    <t>V_A</t>
+  </si>
+  <si>
+    <t>V_NO</t>
+  </si>
+  <si>
+    <t>V_NE</t>
+  </si>
+  <si>
+    <t>V_D</t>
+  </si>
+  <si>
+    <t>V_tailUp</t>
+  </si>
+  <si>
+    <t>groundRoll_x</t>
+  </si>
+  <si>
+    <t>groundRoll_t</t>
+  </si>
+  <si>
+    <t>groundRoll_V_LO</t>
+  </si>
+  <si>
+    <t>groundRoll_ok</t>
+  </si>
+  <si>
+    <t>ROC_max</t>
+  </si>
+  <si>
+    <t>V_ROC_max</t>
+  </si>
+  <si>
+    <t>t_climb</t>
+  </si>
+  <si>
+    <t>V_max_level_A8</t>
+  </si>
+  <si>
+    <t>V_endurance</t>
+  </si>
+  <si>
+    <t>V_range</t>
+  </si>
+  <si>
+    <t>endurance_min</t>
+  </si>
+  <si>
+    <t>range_km</t>
+  </si>
+  <si>
+    <t>n_turn</t>
+  </si>
+  <si>
+    <t>bank_turn_deg</t>
+  </si>
+  <si>
+    <t>turn_ok</t>
+  </si>
+  <si>
+    <t>mission_t</t>
+  </si>
+  <si>
+    <t>mission_E</t>
+  </si>
+  <si>
+    <t>mission_ok_energy</t>
+  </si>
+  <si>
+    <t>mission_ok_power</t>
+  </si>
+  <si>
+    <t>mission_laps_possible</t>
+  </si>
+  <si>
+    <t>mission_E_left</t>
+  </si>
+  <si>
+    <t>mission_battery_mass_left_kg</t>
+  </si>
+  <si>
+    <t>W_pay_max</t>
+  </si>
+  <si>
+    <t>model.CD_trim_fn</t>
+  </si>
+  <si>
+    <t>model.CL_minDrag</t>
+  </si>
+  <si>
+    <t>model.CD_trim_is_parabolic_at_zero</t>
+  </si>
+  <si>
+    <t>model.D_prop</t>
+  </si>
+  <si>
+    <t>model.R_prop</t>
+  </si>
+  <si>
+    <t>model.RPM_lim</t>
+  </si>
+  <si>
+    <t>model.V_grid</t>
+  </si>
+  <si>
+    <t>model.throttle_grid</t>
+  </si>
+  <si>
+    <t>model.T_avail_fn</t>
+  </si>
+  <si>
+    <t>model.Pelec_avail_fn</t>
+  </si>
+  <si>
+    <t>model.I_avail_fn</t>
+  </si>
+  <si>
+    <t>model.throttle_cap_fn</t>
+  </si>
+  <si>
+    <t>model.RPM_avail_fn</t>
+  </si>
+  <si>
+    <t>model.T_grid_fn</t>
+  </si>
+  <si>
+    <t>model.Pelec_grid_fn</t>
+  </si>
+  <si>
+    <t>model.I_grid_fn</t>
+  </si>
+  <si>
+    <t>model.find_throttle_for_thrust</t>
+  </si>
+  <si>
+    <t>model.P_cap</t>
+  </si>
+  <si>
+    <t>model.I_cap</t>
+  </si>
+  <si>
+    <t>model.throttle_bound</t>
+  </si>
+  <si>
+    <t>model.Ct_corr_fn</t>
+  </si>
+  <si>
+    <t>model.labCal.RPM</t>
+  </si>
+  <si>
+    <t>model.labCal.Ct_meas</t>
+  </si>
+  <si>
+    <t>model.labCal.Ct_apc</t>
+  </si>
+  <si>
+    <t>model.labCal.Ct_pctDiff</t>
+  </si>
+  <si>
+    <t>model.labCal.Cp_meas</t>
+  </si>
+  <si>
+    <t>model.labCal.Cp_apc</t>
+  </si>
+  <si>
+    <t>model.labCal.Cp_pctDiff</t>
+  </si>
+  <si>
+    <t>wing_M_driving</t>
+  </si>
+  <si>
+    <t>wing_M_driving_location</t>
+  </si>
+  <si>
+    <t>wing_governing_case</t>
+  </si>
+  <si>
+    <t>wing_V_driving</t>
+  </si>
+  <si>
+    <t>wing_V_driving_location</t>
+  </si>
+  <si>
+    <t>wing_T_driving</t>
+  </si>
+  <si>
+    <t>wing_T_driving_location</t>
+  </si>
+  <si>
+    <t>horizontal_tail_M_root</t>
+  </si>
+  <si>
+    <t>horizontal_tail_T_root</t>
+  </si>
+  <si>
+    <t>fin_M_root</t>
+  </si>
+  <si>
+    <t>tailcone_T</t>
+  </si>
+  <si>
+    <t>tailcone_Ml</t>
+  </si>
+  <si>
+    <t>fuselage_M_envelope_max</t>
+  </si>
+  <si>
+    <t>fuselage_M_envelope_station</t>
+  </si>
+  <si>
+    <t>fuselage_governing_case</t>
+  </si>
+  <si>
+    <t>fuselage_V_envelope_max</t>
+  </si>
+  <si>
+    <t>fuselage_V_envelope_station</t>
+  </si>
+  <si>
+    <t>fuselage_governing_case_V</t>
+  </si>
+  <si>
+    <t>landing_n_L</t>
+  </si>
+  <si>
+    <t>landing_F_main</t>
+  </si>
+  <si>
+    <t>landing_F_tailwheel</t>
+  </si>
+  <si>
+    <t>x_cg_abs</t>
+  </si>
+  <si>
+    <t>mass_table_MTOM</t>
+  </si>
+  <si>
+    <t>mass_table_MTOW</t>
+  </si>
+  <si>
+    <t>alpha_tf_deg</t>
+  </si>
+  <si>
+    <t>prop_clearance_tailUp</t>
+  </si>
+  <si>
+    <t>overturn_phi_deg</t>
+  </si>
+  <si>
+    <t>lastControlSurfaces.Elevator.E</t>
+  </si>
+  <si>
+    <t>lastControlSurfaces.Elevator.delta_flare_deg</t>
+  </si>
+  <si>
+    <t>lastControlSurfaces.Elevator.margin_deg</t>
+  </si>
+  <si>
+    <t>lastControlSurfaces.Aileron.E_a</t>
+  </si>
+  <si>
+    <t>lastControlSurfaces.Aileron.y1_frac</t>
+  </si>
+  <si>
+    <t>lastControlSurfaces.Aileron.y2_frac</t>
+  </si>
+  <si>
+    <t>lastControlSurfaces.Aileron.pb_2V</t>
+  </si>
+  <si>
+    <t>lastControlSurfaces.Aileron.roll_rate_dps</t>
+  </si>
+  <si>
+    <t>lastControlSurfaces.Rudder.S_v</t>
+  </si>
+  <si>
+    <t>lastControlSurfaces.Rudder.AR_v</t>
+  </si>
+  <si>
+    <t>lastControlSurfaces.Rudder.E_r</t>
+  </si>
+  <si>
+    <t>lastControlSurfaces.Rudder.delta_r_deg</t>
+  </si>
+  <si>
+    <t>lastControlSurfaces.Rudder.margin_deg</t>
+  </si>
+  <si>
+    <t>lastDerivatives.CL_Alpha</t>
+  </si>
+  <si>
+    <t>lastDerivatives.x_n</t>
+  </si>
+  <si>
+    <t>lastDerivatives.SM</t>
+  </si>
+  <si>
+    <t>lastDerivatives.CM_Alpha</t>
+  </si>
+  <si>
+    <t>lastDerivatives.Cn_beta</t>
+  </si>
+  <si>
+    <t>lastDerivatives.Gamma_deg</t>
+  </si>
+  <si>
+    <t>lastDerivatives.Cl_beta</t>
+  </si>
+  <si>
+    <t>stability</t>
+  </si>
+  <si>
+    <t>@(CL)local_CD_trim(CL,params)</t>
+  </si>
+  <si>
+    <t>[1x81 double] min 0, max 40</t>
+  </si>
+  <si>
+    <t>[19x1 double] min 0.1, max 1</t>
+  </si>
+  <si>
+    <t>[1x1 griddedInterpolant]</t>
+  </si>
+  <si>
+    <t>@(V,T_req)local_findThrottleForThrust(V,T_req,throttle_grid,T_grid_fn)</t>
+  </si>
+  <si>
+    <t>[1x81 logical]</t>
+  </si>
+  <si>
+    <t>[5186.73 7068.46 9016.72 11006.5]</t>
+  </si>
+  <si>
+    <t>[0.0921493 0.0960023 0.103712 0.108459]</t>
+  </si>
+  <si>
+    <t>[0.120956 0.121521 0.122105 0.122803]</t>
+  </si>
+  <si>
+    <t>[-23.8159 -20.9991 -15.0632 -11.6807]</t>
+  </si>
+  <si>
+    <t>[0.0523414 0.0494839 0.0510573 0.0535032]</t>
+  </si>
+  <si>
+    <t>[0.0514693 0.0504726 0.0498983 0.0498]</t>
+  </si>
+  <si>
+    <t>[1.69451 -1.95884 2.32259 7.43611]</t>
+  </si>
+  <si>
+    <t>rolling maneuver (down-going wing)</t>
+  </si>
+  <si>
+    <t>hard landing</t>
+  </si>
+  <si>
+    <t>Written by writeOutputs.m on 2026-10-06 13:56</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1090,12 +1713,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79995117038483843"/>
+        <fgColor theme="5" tint="0.79995117038484"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1103,55 +1726,57 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="true"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="5" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="6" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="5" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="5" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="true"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="true" applyFill="true"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="true"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="true"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="true"/>
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="0" xfId="1" applyNumberFormat="true" applyFont="true" applyFill="true"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="1" applyNumberFormat="true" applyFont="true" applyFill="true"/>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="0" xfId="1" applyNumberFormat="true" applyFont="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="true"/>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="0" xfId="1" applyNumberFormat="true" applyFont="true" applyFill="true"/>
+    <xf numFmtId="2" fontId="6" fillId="4" borderId="0" xfId="1" applyNumberFormat="true" applyFont="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="1" applyFont="true" applyFill="true"/>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="1" applyNumberFormat="true" applyFill="true"/>
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="0" xfId="1" applyNumberFormat="true" applyFont="true" applyFill="true"/>
+    <xf numFmtId="2" fontId="5" fillId="5" borderId="0" xfId="1" applyNumberFormat="true" applyFont="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal 2" xfId="1"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" justifyLastLine="false" shrinkToFit="false" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" justifyLastLine="false" shrinkToFit="false" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" justifyLastLine="false" shrinkToFit="false" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1167,31 +1792,40 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:F109" totalsRowShown="0">
-  <autoFilter ref="A1:F109" xr:uid="{00000000-0009-0000-0100-000001000000}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="prop"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E43">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" id="1" name="Table1" displayName="Table1" ref="A1:F109" totalsRowShown="false">
+  <autoFilter ref="A1:F109"/>
+  <sortState ref="A2:E43">
     <sortCondition ref="B1:B101"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Parameter"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Subclass" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Value" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Units" dataDxfId="0"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Description"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Notes"/>
+    <tableColumn id="1" name="Parameter"/>
+    <tableColumn id="2" name="Subclass" dataDxfId="2"/>
+    <tableColumn id="3" name="Value" dataDxfId="1"/>
+    <tableColumn id="4" name="Units" dataDxfId="0"/>
+    <tableColumn id="5" name="Description"/>
+    <tableColumn id="6" name="Notes"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium15" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" id="2" name="Table2" displayName="Table2" ref="A1:F34" totalsRowShown="false">
+  <autoFilter ref="A1:F34"/>
+  <tableColumns count="6">
+    <tableColumn id="1" name="Parameter"/>
+    <tableColumn id="2" name="Subclass"/>
+    <tableColumn id="3" name="Value"/>
+    <tableColumn id="4" name="Units"/>
+    <tableColumn id="5" name="Description"/>
+    <tableColumn id="6" name="Source"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium15" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1308,7 +1942,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -1332,9 +1966,9 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -1358,7 +1992,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -1393,7 +2027,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="false">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -1411,7 +2045,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -1436,7 +2070,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -1452,19 +2086,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F109"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.140625" style="20" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" style="20" customWidth="1"/>
-    <col min="4" max="4" width="16.85546875" style="20" customWidth="1"/>
-    <col min="5" max="5" width="168.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="142.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" bestFit="true" customWidth="true"/>
+    <col min="2" max="2" width="15.140625" style="20" customWidth="true"/>
+    <col min="3" max="3" width="13.7109375" style="20" customWidth="true"/>
+    <col min="4" max="4" width="16.85546875" style="20" customWidth="true"/>
+    <col min="5" max="5" width="168.140625" bestFit="true" customWidth="true"/>
+    <col min="6" max="6" width="142.42578125" bestFit="true" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1484,7 +2118,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1501,7 +2135,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1518,7 +2152,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1535,7 +2169,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -1552,7 +2186,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -1569,7 +2203,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -1586,7 +2220,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -1603,7 +2237,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>205</v>
       </c>
@@ -1617,7 +2251,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -1634,7 +2268,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1651,7 +2285,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -1668,7 +2302,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -1685,7 +2319,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -1702,7 +2336,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -1719,7 +2353,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>35</v>
       </c>
@@ -1736,7 +2370,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>37</v>
       </c>
@@ -1753,7 +2387,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="18" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>39</v>
       </c>
@@ -1770,7 +2404,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="19" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>41</v>
       </c>
@@ -1787,7 +2421,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="20" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>45</v>
       </c>
@@ -1804,7 +2438,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="21" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -1821,7 +2455,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="22" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -1838,7 +2472,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="23" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -1855,7 +2489,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="24" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -1872,7 +2506,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="25" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>58</v>
       </c>
@@ -1889,7 +2523,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="26" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>61</v>
       </c>
@@ -1906,7 +2540,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="27" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>63</v>
       </c>
@@ -1923,7 +2557,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="28" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>65</v>
       </c>
@@ -1940,7 +2574,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="29" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -1957,7 +2591,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="30" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -1974,7 +2608,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="31" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>72</v>
       </c>
@@ -1991,7 +2625,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="32" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>74</v>
       </c>
@@ -2008,7 +2642,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="33" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>76</v>
       </c>
@@ -2025,7 +2659,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="34" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>78</v>
       </c>
@@ -2042,7 +2676,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="35" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>80</v>
       </c>
@@ -2059,7 +2693,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="36" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>82</v>
       </c>
@@ -2076,7 +2710,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="37" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>84</v>
       </c>
@@ -2093,7 +2727,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="38" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>86</v>
       </c>
@@ -2110,7 +2744,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="39" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>88</v>
       </c>
@@ -2127,7 +2761,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="40" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>90</v>
       </c>
@@ -2144,7 +2778,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="41" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>92</v>
       </c>
@@ -2161,7 +2795,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="42" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>94</v>
       </c>
@@ -2178,7 +2812,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="43" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>96</v>
       </c>
@@ -2195,7 +2829,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="44" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>98</v>
       </c>
@@ -2212,7 +2846,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="45" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>100</v>
       </c>
@@ -2229,7 +2863,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="46" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>103</v>
       </c>
@@ -2246,7 +2880,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="47" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>105</v>
       </c>
@@ -2263,7 +2897,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="48" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>107</v>
       </c>
@@ -2280,7 +2914,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="49" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>109</v>
       </c>
@@ -2297,7 +2931,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="50" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>111</v>
       </c>
@@ -2314,7 +2948,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="51" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>113</v>
       </c>
@@ -2331,7 +2965,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="52" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>115</v>
       </c>
@@ -2348,7 +2982,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="53" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>117</v>
       </c>
@@ -2365,7 +2999,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="54" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>119</v>
       </c>
@@ -2382,7 +3016,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="55" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>121</v>
       </c>
@@ -2399,7 +3033,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="56" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>123</v>
       </c>
@@ -2416,7 +3050,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="57" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>125</v>
       </c>
@@ -2433,7 +3067,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="58" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>127</v>
       </c>
@@ -2450,7 +3084,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="59" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>129</v>
       </c>
@@ -2467,7 +3101,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="60" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>131</v>
       </c>
@@ -2484,7 +3118,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="61" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>133</v>
       </c>
@@ -2501,7 +3135,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="62" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>135</v>
       </c>
@@ -2518,7 +3152,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="63" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>139</v>
       </c>
@@ -2535,7 +3169,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="64" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>141</v>
       </c>
@@ -2552,7 +3186,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="65" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>143</v>
       </c>
@@ -2569,7 +3203,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="66" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>145</v>
       </c>
@@ -2586,7 +3220,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="67" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>201</v>
       </c>
@@ -2603,7 +3237,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="68" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>146</v>
       </c>
@@ -2620,7 +3254,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="69" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>148</v>
       </c>
@@ -2637,7 +3271,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="70" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>150</v>
       </c>
@@ -2654,7 +3288,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="71" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>152</v>
       </c>
@@ -2671,7 +3305,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="72" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>154</v>
       </c>
@@ -2688,7 +3322,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="73" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>157</v>
       </c>
@@ -2705,7 +3339,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="74" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>160</v>
       </c>
@@ -2722,7 +3356,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="75" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>162</v>
       </c>
@@ -2739,7 +3373,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="76" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>165</v>
       </c>
@@ -2756,7 +3390,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="77" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>167</v>
       </c>
@@ -2773,7 +3407,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="78" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>169</v>
       </c>
@@ -2790,7 +3424,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="79" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>172</v>
       </c>
@@ -2807,7 +3441,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="80" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>174</v>
       </c>
@@ -2824,7 +3458,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="81" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>176</v>
       </c>
@@ -2841,7 +3475,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="82" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>178</v>
       </c>
@@ -2858,7 +3492,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="83" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>180</v>
       </c>
@@ -2875,7 +3509,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="84" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>183</v>
       </c>
@@ -2892,7 +3526,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="85" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>186</v>
       </c>
@@ -2909,7 +3543,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="86" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>189</v>
       </c>
@@ -2926,7 +3560,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="87" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>191</v>
       </c>
@@ -2943,7 +3577,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="88" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>193</v>
       </c>
@@ -2960,7 +3594,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="89" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>196</v>
       </c>
@@ -2977,7 +3611,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="90" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>198</v>
       </c>
@@ -2994,7 +3628,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="91" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>248</v>
       </c>
@@ -3011,7 +3645,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="92" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>251</v>
       </c>
@@ -3028,7 +3662,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="93" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>253</v>
       </c>
@@ -3045,7 +3679,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="94" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>255</v>
       </c>
@@ -3062,7 +3696,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="95" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>261</v>
       </c>
@@ -3079,7 +3713,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="96" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>263</v>
       </c>
@@ -3096,7 +3730,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="97" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>264</v>
       </c>
@@ -3113,7 +3747,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="98" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>266</v>
       </c>
@@ -3130,7 +3764,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="99" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>267</v>
       </c>
@@ -3147,7 +3781,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="100" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>268</v>
       </c>
@@ -3164,7 +3798,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="101" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>269</v>
       </c>
@@ -3181,7 +3815,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="102" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>270</v>
       </c>
@@ -3198,7 +3832,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="103" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>271</v>
       </c>
@@ -3215,7 +3849,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="104" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>272</v>
       </c>
@@ -3232,7 +3866,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="105" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>305</v>
       </c>
@@ -3249,7 +3883,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="106" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>307</v>
       </c>
@@ -3266,7 +3900,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="107" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>308</v>
       </c>
@@ -3283,7 +3917,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="108" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>309</v>
       </c>
@@ -3300,7 +3934,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="109" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>310</v>
       </c>
@@ -3326,16 +3960,2983 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFCC8514-E0AF-4C67-BF86-8649FC702924}">
-  <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:H157"/>
+  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.42578125" customWidth="1"/>
-    <col min="2" max="3" width="32.42578125" style="20" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" style="20" customWidth="1"/>
+    <col min="1" max="1" width="40.7109375" customWidth="true"/>
+    <col min="2" max="2" width="12.5703125" customWidth="true"/>
+    <col min="3" max="3" width="64.5703125" customWidth="true"/>
+    <col min="4" max="4" width="5.7109375" customWidth="true"/>
+    <col min="5" max="5" width="46" customWidth="true"/>
+    <col min="6" max="6" width="32.42578125" customWidth="true"/>
+    <col min="8" max="8" width="42.7109375" customWidth="true"/>
+    <col min="7" max="7" width="9.140625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G1" s="0"/>
+      <c r="H1" s="0" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="s">
+        <v>316</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="0">
+        <v>0.29999999999999999</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>349</v>
+      </c>
+      <c r="F2" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G2" s="0"/>
+      <c r="H2" s="0"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="s">
+        <v>317</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="0">
+        <v>1.1818181818181817</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>350</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G3" s="0"/>
+      <c r="H3" s="0"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="s">
+        <v>318</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="0">
+        <v>0.92201380973471758</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>351</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G4" s="0"/>
+      <c r="H4" s="0"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="s">
+        <v>319</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="0">
+        <v>0.07919652663705147</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>352</v>
+      </c>
+      <c r="F5" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G5" s="0"/>
+      <c r="H5" s="0"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="s">
+        <v>320</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="0">
+        <v>0.19588300688233271</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>353</v>
+      </c>
+      <c r="F6" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G6" s="0"/>
+      <c r="H6" s="0"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="s">
+        <v>321</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="0">
+        <v>0.029817638776781716</v>
+      </c>
+      <c r="D7" s="0"/>
+      <c r="E7" s="0"/>
+      <c r="F7" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G7" s="0"/>
+      <c r="H7" s="0"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="s">
+        <v>322</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="0">
+        <v>0.036945326174116347</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="0" t="s">
+        <v>354</v>
+      </c>
+      <c r="F8" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G8" s="0"/>
+      <c r="H8" s="0"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="s">
+        <v>323</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="0">
+        <v>0.036945326174116347</v>
+      </c>
+      <c r="D9" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="0" t="s">
+        <v>355</v>
+      </c>
+      <c r="F9" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G9" s="0"/>
+      <c r="H9" s="0"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="s">
+        <v>324</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="0">
+        <v>0.021945326174116347</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="F10" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G10" s="0"/>
+      <c r="H10" s="0"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="s">
+        <v>325</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="0">
+        <v>8.120106954426566</v>
+      </c>
+      <c r="D11" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="0" t="s">
+        <v>357</v>
+      </c>
+      <c r="F11" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G11" s="0"/>
+      <c r="H11" s="0"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="s">
+        <v>326</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="0">
+        <v>10.289169276665902</v>
+      </c>
+      <c r="D12" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="0" t="s">
+        <v>358</v>
+      </c>
+      <c r="F12" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G12" s="0"/>
+      <c r="H12" s="0"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="s">
+        <v>383</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="0">
+        <v>3.0198549799930445</v>
+      </c>
+      <c r="D13" s="0"/>
+      <c r="E13" s="0"/>
+      <c r="F13" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G13" s="0"/>
+      <c r="H13" s="0"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="s">
+        <v>384</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="0">
+        <v>4.0327458299223453</v>
+      </c>
+      <c r="D14" s="0"/>
+      <c r="E14" s="0"/>
+      <c r="F14" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G14" s="0"/>
+      <c r="H14" s="0"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="s">
+        <v>385</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="0">
+        <v>0.58894455001488533</v>
+      </c>
+      <c r="D15" s="0"/>
+      <c r="E15" s="0"/>
+      <c r="F15" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G15" s="0"/>
+      <c r="H15" s="0"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="s">
+        <v>386</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="0">
+        <v>5.2740736776131758</v>
+      </c>
+      <c r="D16" s="0"/>
+      <c r="E16" s="0"/>
+      <c r="F16" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G16" s="0"/>
+      <c r="H16" s="0"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="s">
+        <v>387</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="0">
+        <v>-0.094788465253600393</v>
+      </c>
+      <c r="D17" s="0"/>
+      <c r="E17" s="0"/>
+      <c r="F17" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G17" s="0"/>
+      <c r="H17" s="0"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="s">
+        <v>388</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="0">
+        <v>0.66074594914354523</v>
+      </c>
+      <c r="D18" s="0"/>
+      <c r="E18" s="0"/>
+      <c r="F18" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G18" s="0"/>
+      <c r="H18" s="0"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="s">
+        <v>389</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="0">
+        <v>0.60899778104422941</v>
+      </c>
+      <c r="D19" s="0"/>
+      <c r="E19" s="0"/>
+      <c r="F19" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G19" s="0"/>
+      <c r="H19" s="0"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="s">
+        <v>390</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="0">
+        <v>1.5753270213496304</v>
+      </c>
+      <c r="D20" s="0"/>
+      <c r="E20" s="0"/>
+      <c r="F20" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G20" s="0"/>
+      <c r="H20" s="0"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="s">
+        <v>391</v>
+      </c>
+      <c r="B21" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="0">
+        <v>0.66074594914354523</v>
+      </c>
+      <c r="D21" s="0"/>
+      <c r="E21" s="0"/>
+      <c r="F21" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G21" s="0"/>
+      <c r="H21" s="0"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="s">
+        <v>392</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="0">
+        <v>0.12602616170797043</v>
+      </c>
+      <c r="D22" s="0"/>
+      <c r="E22" s="0"/>
+      <c r="F22" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G22" s="0"/>
+      <c r="H22" s="0"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="s">
+        <v>327</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23" s="0">
+        <v>0.49722452282391244</v>
+      </c>
+      <c r="D23" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="E23" s="0" t="s">
+        <v>359</v>
+      </c>
+      <c r="F23" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G23" s="0"/>
+      <c r="H23" s="0"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="s">
+        <v>328</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="0">
+        <v>0.34410001579509508</v>
+      </c>
+      <c r="D24" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="E24" s="0" t="s">
+        <v>360</v>
+      </c>
+      <c r="F24" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G24" s="0"/>
+      <c r="H24" s="0"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="s">
+        <v>329</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C25" s="0">
+        <v>4.3591977074863637</v>
+      </c>
+      <c r="D25" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="0" t="s">
+        <v>361</v>
+      </c>
+      <c r="F25" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G25" s="0"/>
+      <c r="H25" s="0"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>330</v>
+      </c>
+      <c r="B26" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" s="0">
+        <v>0.084528168880065119</v>
+      </c>
+      <c r="D26" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="E26" s="0" t="s">
+        <v>362</v>
+      </c>
+      <c r="F26" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G26" s="0"/>
+      <c r="H26" s="0"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>331</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27" s="0">
+        <v>0.45969601064199239</v>
+      </c>
+      <c r="D27" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="E27" s="0" t="s">
+        <v>363</v>
+      </c>
+      <c r="F27" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G27" s="0"/>
+      <c r="H27" s="0"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>332</v>
+      </c>
+      <c r="B28" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28" s="0">
+        <v>0.18387840425679697</v>
+      </c>
+      <c r="D28" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="E28" s="0" t="s">
+        <v>364</v>
+      </c>
+      <c r="F28" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G28" s="0"/>
+      <c r="H28" s="0"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="s">
+        <v>333</v>
+      </c>
+      <c r="B29" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29" s="0">
+        <v>0.39523392547876368</v>
+      </c>
+      <c r="D29" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="0" t="s">
+        <v>365</v>
+      </c>
+      <c r="F29" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G29" s="0"/>
+      <c r="H29" s="0"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="s">
+        <v>334</v>
+      </c>
+      <c r="B30" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30" s="0">
+        <v>0.074583678423586861</v>
+      </c>
+      <c r="D30" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="E30" s="0" t="s">
+        <v>366</v>
+      </c>
+      <c r="F30" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G30" s="0"/>
+      <c r="H30" s="0"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="s">
+        <v>335</v>
+      </c>
+      <c r="B31" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C31" s="0">
+        <v>0.074583678423586861</v>
+      </c>
+      <c r="D31" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="E31" s="0" t="s">
+        <v>367</v>
+      </c>
+      <c r="F31" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G31" s="0"/>
+      <c r="H31" s="0"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="s">
+        <v>336</v>
+      </c>
+      <c r="B32" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32" s="0">
+        <v>0.28249696620183012</v>
+      </c>
+      <c r="D32" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="E32" s="0" t="s">
+        <v>368</v>
+      </c>
+      <c r="F32" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G32" s="0"/>
+      <c r="H32" s="0"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="s">
+        <v>337</v>
+      </c>
+      <c r="B33" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C33" s="0">
+        <v>0.26401585626339263</v>
+      </c>
+      <c r="D33" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="E33" s="0" t="s">
+        <v>369</v>
+      </c>
+      <c r="F33" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G33" s="0"/>
+      <c r="H33" s="0"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="s">
+        <v>393</v>
+      </c>
+      <c r="B34" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C34" s="0">
+        <v>0.018046437163813135</v>
+      </c>
+      <c r="D34" s="0"/>
+      <c r="E34" s="0"/>
+      <c r="F34" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G34" s="0"/>
+      <c r="H34" s="0"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="s">
+        <v>394</v>
+      </c>
+      <c r="B35" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C35" s="0">
+        <v>0.23885083680507355</v>
+      </c>
+      <c r="D35" s="0"/>
+      <c r="E35" s="0"/>
+      <c r="F35" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G35" s="0"/>
+      <c r="H35" s="0"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="s">
+        <v>395</v>
+      </c>
+      <c r="B36" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C36" s="0">
+        <v>0.3656082203404642</v>
+      </c>
+      <c r="D36" s="0"/>
+      <c r="E36" s="0"/>
+      <c r="F36" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G36" s="0"/>
+      <c r="H36" s="0"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="s">
+        <v>396</v>
+      </c>
+      <c r="B37" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C37" s="0">
+        <v>0.2156082203404642</v>
+      </c>
+      <c r="D37" s="0"/>
+      <c r="E37" s="0"/>
+      <c r="F37" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G37" s="0"/>
+      <c r="H37" s="0"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="s">
+        <v>167</v>
+      </c>
+      <c r="B38" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C38" s="0">
+        <v>4.0516000000000005</v>
+      </c>
+      <c r="D38" s="0"/>
+      <c r="E38" s="0"/>
+      <c r="F38" s="0" t="s">
+        <v>379</v>
+      </c>
+      <c r="G38" s="0"/>
+      <c r="H38" s="0"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="s">
+        <v>338</v>
+      </c>
+      <c r="B39" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C39" s="0">
+        <v>22.737783592977756</v>
+      </c>
+      <c r="D39" s="0" t="s">
+        <v>137</v>
+      </c>
+      <c r="E39" s="0" t="s">
+        <v>370</v>
+      </c>
+      <c r="F39" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G39" s="0"/>
+      <c r="H39" s="0"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="s">
+        <v>339</v>
+      </c>
+      <c r="B40" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C40" s="0">
+        <v>11</v>
+      </c>
+      <c r="D40" s="0" t="s">
+        <v>137</v>
+      </c>
+      <c r="E40" s="0" t="s">
+        <v>371</v>
+      </c>
+      <c r="F40" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G40" s="0"/>
+      <c r="H40" s="0"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="0" t="s">
+        <v>340</v>
+      </c>
+      <c r="B41" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C41" s="0">
+        <v>14.810748414335091</v>
+      </c>
+      <c r="D41" s="0" t="s">
+        <v>137</v>
+      </c>
+      <c r="E41" s="0" t="s">
+        <v>372</v>
+      </c>
+      <c r="F41" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G41" s="0"/>
+      <c r="H41" s="0"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="0" t="s">
+        <v>341</v>
+      </c>
+      <c r="B42" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C42" s="0">
+        <v>12.24744871391589</v>
+      </c>
+      <c r="D42" s="0" t="s">
+        <v>137</v>
+      </c>
+      <c r="E42" s="0" t="s">
+        <v>373</v>
+      </c>
+      <c r="F42" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G42" s="0"/>
+      <c r="H42" s="0"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="0" t="s">
+        <v>342</v>
+      </c>
+      <c r="B43" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C43" s="0">
+        <v>48.189685104221404</v>
+      </c>
+      <c r="D43" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="E43" s="0" t="s">
+        <v>374</v>
+      </c>
+      <c r="F43" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G43" s="0"/>
+      <c r="H43" s="0"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="0" t="s">
+        <v>343</v>
+      </c>
+      <c r="B44" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C44" s="0">
+        <v>16.699244233993625</v>
+      </c>
+      <c r="D44" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="E44" s="0" t="s">
+        <v>375</v>
+      </c>
+      <c r="F44" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G44" s="0"/>
+      <c r="H44" s="0"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="0" t="s">
+        <v>344</v>
+      </c>
+      <c r="B45" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C45" s="0">
+        <v>39.746196000000005</v>
+      </c>
+      <c r="D45" s="0" t="s">
+        <v>348</v>
+      </c>
+      <c r="E45" s="0" t="s">
+        <v>376</v>
+      </c>
+      <c r="F45" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G45" s="0"/>
+      <c r="H45" s="0"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="0" t="s">
+        <v>345</v>
+      </c>
+      <c r="B46" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C46" s="0">
+        <v>0.44283295832701008</v>
+      </c>
+      <c r="D46" s="0"/>
+      <c r="E46" s="0"/>
+      <c r="F46" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G46" s="0"/>
+      <c r="H46" s="0"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="0" t="s">
+        <v>346</v>
+      </c>
+      <c r="B47" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C47" s="0">
+        <v>233372.96903833433</v>
+      </c>
+      <c r="D47" s="0"/>
+      <c r="E47" s="0"/>
+      <c r="F47" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G47" s="0"/>
+      <c r="H47" s="0"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="0" t="s">
+        <v>347</v>
+      </c>
+      <c r="B48" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C48" s="0">
+        <v>130688.86266146721</v>
+      </c>
+      <c r="D48" s="0"/>
+      <c r="E48" s="0"/>
+      <c r="F48" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G48" s="0"/>
+      <c r="H48" s="0"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="0" t="s">
+        <v>397</v>
+      </c>
+      <c r="B49" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C49" s="0">
+        <v>34.144135350668904</v>
+      </c>
+      <c r="D49" s="0"/>
+      <c r="E49" s="0"/>
+      <c r="F49" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G49" s="0"/>
+      <c r="H49" s="0"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="0" t="s">
+        <v>398</v>
+      </c>
+      <c r="B50" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C50" s="0">
+        <v>15.480365443172449</v>
+      </c>
+      <c r="D50" s="0"/>
+      <c r="E50" s="0"/>
+      <c r="F50" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G50" s="0"/>
+      <c r="H50" s="0"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="0" t="s">
+        <v>399</v>
+      </c>
+      <c r="B51" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C51" s="0">
+        <v>3.7999999999999998</v>
+      </c>
+      <c r="D51" s="0"/>
+      <c r="E51" s="0"/>
+      <c r="F51" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G51" s="0"/>
+      <c r="H51" s="0"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="0" t="s">
+        <v>400</v>
+      </c>
+      <c r="B52" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C52" s="0">
+        <v>-1.52</v>
+      </c>
+      <c r="D52" s="0"/>
+      <c r="E52" s="0"/>
+      <c r="F52" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G52" s="0"/>
+      <c r="H52" s="0"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="0" t="s">
+        <v>401</v>
+      </c>
+      <c r="B53" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C53" s="0">
+        <v>5.6999999999999993</v>
+      </c>
+      <c r="D53" s="0"/>
+      <c r="E53" s="0"/>
+      <c r="F53" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G53" s="0"/>
+      <c r="H53" s="0"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="0" t="s">
+        <v>402</v>
+      </c>
+      <c r="B54" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C54" s="0">
+        <v>-2.2800000000000002</v>
+      </c>
+      <c r="D54" s="0"/>
+      <c r="E54" s="0"/>
+      <c r="F54" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G54" s="0"/>
+      <c r="H54" s="0"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="0" t="s">
+        <v>403</v>
+      </c>
+      <c r="B55" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C55" s="0">
+        <v>18.622682892532463</v>
+      </c>
+      <c r="D55" s="0"/>
+      <c r="E55" s="0"/>
+      <c r="F55" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G55" s="0"/>
+      <c r="H55" s="0"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="0" t="s">
+        <v>404</v>
+      </c>
+      <c r="B56" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C56" s="0">
+        <v>27.131986877647702</v>
+      </c>
+      <c r="D56" s="0"/>
+      <c r="E56" s="0"/>
+      <c r="F56" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G56" s="0"/>
+      <c r="H56" s="0"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="0" t="s">
+        <v>405</v>
+      </c>
+      <c r="B57" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C57" s="0">
+        <v>25.580006542099976</v>
+      </c>
+      <c r="D57" s="0"/>
+      <c r="E57" s="0"/>
+      <c r="F57" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G57" s="0"/>
+      <c r="H57" s="0"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="0" t="s">
+        <v>406</v>
+      </c>
+      <c r="B58" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C58" s="0">
+        <v>28.422229491222197</v>
+      </c>
+      <c r="D58" s="0"/>
+      <c r="E58" s="0"/>
+      <c r="F58" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G58" s="0"/>
+      <c r="H58" s="0"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="0" t="s">
+        <v>407</v>
+      </c>
+      <c r="B59" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C59" s="0">
+        <v>6.3586494759793881</v>
+      </c>
+      <c r="D59" s="0"/>
+      <c r="E59" s="0"/>
+      <c r="F59" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G59" s="0"/>
+      <c r="H59" s="0"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="0" t="s">
+        <v>408</v>
+      </c>
+      <c r="B60" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C60" s="0">
+        <v>12.884684205822825</v>
+      </c>
+      <c r="D60" s="0"/>
+      <c r="E60" s="0"/>
+      <c r="F60" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G60" s="0"/>
+      <c r="H60" s="0"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="0" t="s">
+        <v>409</v>
+      </c>
+      <c r="B61" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C61" s="0">
+        <v>2.2299999999999964</v>
+      </c>
+      <c r="D61" s="0"/>
+      <c r="E61" s="0"/>
+      <c r="F61" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G61" s="0"/>
+      <c r="H61" s="0"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="0" t="s">
+        <v>410</v>
+      </c>
+      <c r="B62" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C62" s="0">
+        <v>11.011406321896699</v>
+      </c>
+      <c r="D62" s="0"/>
+      <c r="E62" s="0"/>
+      <c r="F62" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G62" s="0"/>
+      <c r="H62" s="0"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="0" t="s">
+        <v>411</v>
+      </c>
+      <c r="B63" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C63" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="D63" s="0"/>
+      <c r="E63" s="0"/>
+      <c r="F63" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G63" s="0"/>
+      <c r="H63" s="0"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="0" t="s">
+        <v>412</v>
+      </c>
+      <c r="B64" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C64" s="0">
+        <v>5.6667672012645314</v>
+      </c>
+      <c r="D64" s="0"/>
+      <c r="E64" s="0"/>
+      <c r="F64" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G64" s="0"/>
+      <c r="H64" s="0"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="0" t="s">
+        <v>413</v>
+      </c>
+      <c r="B65" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C65" s="0">
+        <v>19.023298859748962</v>
+      </c>
+      <c r="D65" s="0"/>
+      <c r="E65" s="0"/>
+      <c r="F65" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G65" s="0"/>
+      <c r="H65" s="0"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="0" t="s">
+        <v>414</v>
+      </c>
+      <c r="B66" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C66" s="0">
+        <v>5.2940237236683272</v>
+      </c>
+      <c r="D66" s="0"/>
+      <c r="E66" s="0"/>
+      <c r="F66" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G66" s="0"/>
+      <c r="H66" s="0"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="0" t="s">
+        <v>415</v>
+      </c>
+      <c r="B67" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C67" s="0">
+        <v>22.608098531363336</v>
+      </c>
+      <c r="D67" s="0"/>
+      <c r="E67" s="0"/>
+      <c r="F67" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G67" s="0"/>
+      <c r="H67" s="0"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="0" t="s">
+        <v>416</v>
+      </c>
+      <c r="B68" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C68" s="0">
+        <v>12.709922788411269</v>
+      </c>
+      <c r="D68" s="0"/>
+      <c r="E68" s="0"/>
+      <c r="F68" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G68" s="0"/>
+      <c r="H68" s="0"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="0" t="s">
+        <v>417</v>
+      </c>
+      <c r="B69" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C69" s="0">
+        <v>16.27392540932771</v>
+      </c>
+      <c r="D69" s="0"/>
+      <c r="E69" s="0"/>
+      <c r="F69" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G69" s="0"/>
+      <c r="H69" s="0"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="0" t="s">
+        <v>418</v>
+      </c>
+      <c r="B70" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C70" s="0">
+        <v>15.956485750905872</v>
+      </c>
+      <c r="D70" s="0"/>
+      <c r="E70" s="0"/>
+      <c r="F70" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G70" s="0"/>
+      <c r="H70" s="0"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="B71" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C71" s="0">
+        <v>13.695854805920606</v>
+      </c>
+      <c r="D71" s="0"/>
+      <c r="E71" s="0"/>
+      <c r="F71" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G71" s="0"/>
+      <c r="H71" s="0"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="0" t="s">
+        <v>420</v>
+      </c>
+      <c r="B72" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C72" s="0">
+        <v>1.0954451150103324</v>
+      </c>
+      <c r="D72" s="0"/>
+      <c r="E72" s="0"/>
+      <c r="F72" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G72" s="0"/>
+      <c r="H72" s="0"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="0" t="s">
+        <v>421</v>
+      </c>
+      <c r="B73" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C73" s="0">
+        <v>24.094842552110709</v>
+      </c>
+      <c r="D73" s="0"/>
+      <c r="E73" s="0"/>
+      <c r="F73" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G73" s="0"/>
+      <c r="H73" s="0"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="0" t="s">
+        <v>422</v>
+      </c>
+      <c r="B74" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C74" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="D74" s="0"/>
+      <c r="E74" s="0"/>
+      <c r="F74" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G74" s="0"/>
+      <c r="H74" s="0"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="0" t="s">
+        <v>423</v>
+      </c>
+      <c r="B75" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C75" s="0">
+        <v>156.52835771396133</v>
+      </c>
+      <c r="D75" s="0"/>
+      <c r="E75" s="0"/>
+      <c r="F75" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G75" s="0"/>
+      <c r="H75" s="0"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="0" t="s">
+        <v>424</v>
+      </c>
+      <c r="B76" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C76" s="0">
+        <v>44593.916314433394</v>
+      </c>
+      <c r="D76" s="0"/>
+      <c r="E76" s="0"/>
+      <c r="F76" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G76" s="0"/>
+      <c r="H76" s="0"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="0" t="s">
+        <v>425</v>
+      </c>
+      <c r="B77" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C77" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="D77" s="0"/>
+      <c r="E77" s="0"/>
+      <c r="F77" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G77" s="0"/>
+      <c r="H77" s="0"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="0" t="s">
+        <v>426</v>
+      </c>
+      <c r="B78" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C78" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="D78" s="0"/>
+      <c r="E78" s="0"/>
+      <c r="F78" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G78" s="0"/>
+      <c r="H78" s="0"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="0" t="s">
+        <v>427</v>
+      </c>
+      <c r="B79" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C79" s="0">
+        <v>13</v>
+      </c>
+      <c r="D79" s="0"/>
+      <c r="E79" s="0"/>
+      <c r="F79" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G79" s="0"/>
+      <c r="H79" s="0"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="0" t="s">
+        <v>428</v>
+      </c>
+      <c r="B80" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C80" s="0">
+        <v>86094.946347033809</v>
+      </c>
+      <c r="D80" s="0"/>
+      <c r="E80" s="0"/>
+      <c r="F80" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G80" s="0"/>
+      <c r="H80" s="0"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="0" t="s">
+        <v>429</v>
+      </c>
+      <c r="B81" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C81" s="0">
+        <v>0.16336801963384023</v>
+      </c>
+      <c r="D81" s="0"/>
+      <c r="E81" s="0"/>
+      <c r="F81" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G81" s="0"/>
+      <c r="H81" s="0"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="0" t="s">
+        <v>430</v>
+      </c>
+      <c r="B82" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C82" s="0">
+        <v>2.185902626124927</v>
+      </c>
+      <c r="D82" s="0"/>
+      <c r="E82" s="0"/>
+      <c r="F82" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G82" s="0"/>
+      <c r="H82" s="0"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="0" t="s">
+        <v>431</v>
+      </c>
+      <c r="B83" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C83" s="0" t="s">
+        <v>507</v>
+      </c>
+      <c r="D83" s="0"/>
+      <c r="E83" s="0"/>
+      <c r="F83" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G83" s="0"/>
+      <c r="H83" s="0"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="0" t="s">
+        <v>432</v>
+      </c>
+      <c r="B84" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C84" s="0">
+        <v>-0.040973254512723323</v>
+      </c>
+      <c r="D84" s="0"/>
+      <c r="E84" s="0"/>
+      <c r="F84" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G84" s="0"/>
+      <c r="H84" s="0"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="0" t="s">
+        <v>433</v>
+      </c>
+      <c r="B85" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C85" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="D85" s="0"/>
+      <c r="E85" s="0"/>
+      <c r="F85" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G85" s="0"/>
+      <c r="H85" s="0"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="0" t="s">
+        <v>434</v>
+      </c>
+      <c r="B86" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C86" s="0">
+        <v>0.254</v>
+      </c>
+      <c r="D86" s="0"/>
+      <c r="E86" s="0"/>
+      <c r="F86" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G86" s="0"/>
+      <c r="H86" s="0"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="0" t="s">
+        <v>435</v>
+      </c>
+      <c r="B87" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C87" s="0">
+        <v>0.127</v>
+      </c>
+      <c r="D87" s="0"/>
+      <c r="E87" s="0"/>
+      <c r="F87" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G87" s="0"/>
+      <c r="H87" s="0"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="B88" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C88" s="0">
+        <v>14500</v>
+      </c>
+      <c r="D88" s="0"/>
+      <c r="E88" s="0"/>
+      <c r="F88" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G88" s="0"/>
+      <c r="H88" s="0"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="0" t="s">
+        <v>437</v>
+      </c>
+      <c r="B89" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C89" s="0" t="s">
+        <v>508</v>
+      </c>
+      <c r="D89" s="0"/>
+      <c r="E89" s="0"/>
+      <c r="F89" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G89" s="0"/>
+      <c r="H89" s="0"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="0" t="s">
+        <v>438</v>
+      </c>
+      <c r="B90" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C90" s="0" t="s">
+        <v>509</v>
+      </c>
+      <c r="D90" s="0"/>
+      <c r="E90" s="0"/>
+      <c r="F90" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G90" s="0"/>
+      <c r="H90" s="0"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="B91" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C91" s="0" t="s">
+        <v>510</v>
+      </c>
+      <c r="D91" s="0"/>
+      <c r="E91" s="0"/>
+      <c r="F91" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G91" s="0"/>
+      <c r="H91" s="0"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="0" t="s">
+        <v>440</v>
+      </c>
+      <c r="B92" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C92" s="0" t="s">
+        <v>510</v>
+      </c>
+      <c r="D92" s="0"/>
+      <c r="E92" s="0"/>
+      <c r="F92" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G92" s="0"/>
+      <c r="H92" s="0"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="0" t="s">
+        <v>441</v>
+      </c>
+      <c r="B93" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C93" s="0" t="s">
+        <v>510</v>
+      </c>
+      <c r="D93" s="0"/>
+      <c r="E93" s="0"/>
+      <c r="F93" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G93" s="0"/>
+      <c r="H93" s="0"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="0" t="s">
+        <v>442</v>
+      </c>
+      <c r="B94" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C94" s="0" t="s">
+        <v>510</v>
+      </c>
+      <c r="D94" s="0"/>
+      <c r="E94" s="0"/>
+      <c r="F94" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G94" s="0"/>
+      <c r="H94" s="0"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="0" t="s">
+        <v>443</v>
+      </c>
+      <c r="B95" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C95" s="0" t="s">
+        <v>510</v>
+      </c>
+      <c r="D95" s="0"/>
+      <c r="E95" s="0"/>
+      <c r="F95" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G95" s="0"/>
+      <c r="H95" s="0"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="0" t="s">
+        <v>444</v>
+      </c>
+      <c r="B96" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C96" s="0" t="s">
+        <v>510</v>
+      </c>
+      <c r="D96" s="0"/>
+      <c r="E96" s="0"/>
+      <c r="F96" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G96" s="0"/>
+      <c r="H96" s="0"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="0" t="s">
+        <v>445</v>
+      </c>
+      <c r="B97" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C97" s="0" t="s">
+        <v>510</v>
+      </c>
+      <c r="D97" s="0"/>
+      <c r="E97" s="0"/>
+      <c r="F97" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G97" s="0"/>
+      <c r="H97" s="0"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="0" t="s">
+        <v>446</v>
+      </c>
+      <c r="B98" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C98" s="0" t="s">
+        <v>510</v>
+      </c>
+      <c r="D98" s="0"/>
+      <c r="E98" s="0"/>
+      <c r="F98" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G98" s="0"/>
+      <c r="H98" s="0"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="0" t="s">
+        <v>447</v>
+      </c>
+      <c r="B99" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C99" s="0" t="s">
+        <v>511</v>
+      </c>
+      <c r="D99" s="0"/>
+      <c r="E99" s="0"/>
+      <c r="F99" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G99" s="0"/>
+      <c r="H99" s="0"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="0" t="s">
+        <v>448</v>
+      </c>
+      <c r="B100" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C100" s="0">
+        <v>700</v>
+      </c>
+      <c r="D100" s="0"/>
+      <c r="E100" s="0"/>
+      <c r="F100" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G100" s="0"/>
+      <c r="H100" s="0"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="0" t="s">
+        <v>449</v>
+      </c>
+      <c r="B101" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C101" s="0">
+        <v>50</v>
+      </c>
+      <c r="D101" s="0"/>
+      <c r="E101" s="0"/>
+      <c r="F101" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G101" s="0"/>
+      <c r="H101" s="0"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="0" t="s">
+        <v>450</v>
+      </c>
+      <c r="B102" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C102" s="0" t="s">
+        <v>512</v>
+      </c>
+      <c r="D102" s="0"/>
+      <c r="E102" s="0"/>
+      <c r="F102" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G102" s="0"/>
+      <c r="H102" s="0"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="0" t="s">
+        <v>451</v>
+      </c>
+      <c r="B103" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C103" s="0" t="s">
+        <v>510</v>
+      </c>
+      <c r="D103" s="0"/>
+      <c r="E103" s="0"/>
+      <c r="F103" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G103" s="0"/>
+      <c r="H103" s="0"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="0" t="s">
+        <v>452</v>
+      </c>
+      <c r="B104" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C104" s="0" t="s">
+        <v>513</v>
+      </c>
+      <c r="D104" s="0"/>
+      <c r="E104" s="0"/>
+      <c r="F104" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G104" s="0"/>
+      <c r="H104" s="0"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="0" t="s">
+        <v>453</v>
+      </c>
+      <c r="B105" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C105" s="0" t="s">
+        <v>514</v>
+      </c>
+      <c r="D105" s="0"/>
+      <c r="E105" s="0"/>
+      <c r="F105" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G105" s="0"/>
+      <c r="H105" s="0"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="0" t="s">
+        <v>454</v>
+      </c>
+      <c r="B106" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C106" s="0" t="s">
+        <v>515</v>
+      </c>
+      <c r="D106" s="0"/>
+      <c r="E106" s="0"/>
+      <c r="F106" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G106" s="0"/>
+      <c r="H106" s="0"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="0" t="s">
+        <v>455</v>
+      </c>
+      <c r="B107" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C107" s="0" t="s">
+        <v>516</v>
+      </c>
+      <c r="D107" s="0"/>
+      <c r="E107" s="0"/>
+      <c r="F107" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G107" s="0"/>
+      <c r="H107" s="0"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="0" t="s">
+        <v>456</v>
+      </c>
+      <c r="B108" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C108" s="0" t="s">
+        <v>517</v>
+      </c>
+      <c r="D108" s="0"/>
+      <c r="E108" s="0"/>
+      <c r="F108" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G108" s="0"/>
+      <c r="H108" s="0"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="0" t="s">
+        <v>457</v>
+      </c>
+      <c r="B109" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C109" s="0" t="s">
+        <v>518</v>
+      </c>
+      <c r="D109" s="0"/>
+      <c r="E109" s="0"/>
+      <c r="F109" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G109" s="0"/>
+      <c r="H109" s="0"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="0" t="s">
+        <v>458</v>
+      </c>
+      <c r="B110" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C110" s="0" t="s">
+        <v>519</v>
+      </c>
+      <c r="D110" s="0"/>
+      <c r="E110" s="0"/>
+      <c r="F110" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G110" s="0"/>
+      <c r="H110" s="0"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="0" t="s">
+        <v>459</v>
+      </c>
+      <c r="B111" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C111" s="0">
+        <v>32.946133306980855</v>
+      </c>
+      <c r="D111" s="0"/>
+      <c r="E111" s="0"/>
+      <c r="F111" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G111" s="0"/>
+      <c r="H111" s="0"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="0" t="s">
+        <v>460</v>
+      </c>
+      <c r="B112" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C112" s="0">
+        <v>0</v>
+      </c>
+      <c r="D112" s="0"/>
+      <c r="E112" s="0"/>
+      <c r="F112" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G112" s="0"/>
+      <c r="H112" s="0"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="0" t="s">
+        <v>461</v>
+      </c>
+      <c r="B113" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C113" s="0" t="s">
+        <v>520</v>
+      </c>
+      <c r="D113" s="0"/>
+      <c r="E113" s="0"/>
+      <c r="F113" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G113" s="0"/>
+      <c r="H113" s="0"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="0" t="s">
+        <v>462</v>
+      </c>
+      <c r="B114" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C114" s="0">
+        <v>86.068285472894019</v>
+      </c>
+      <c r="D114" s="0"/>
+      <c r="E114" s="0"/>
+      <c r="F114" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G114" s="0"/>
+      <c r="H114" s="0"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="0" t="s">
+        <v>463</v>
+      </c>
+      <c r="B115" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C115" s="0">
+        <v>0</v>
+      </c>
+      <c r="D115" s="0"/>
+      <c r="E115" s="0"/>
+      <c r="F115" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G115" s="0"/>
+      <c r="H115" s="0"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="0" t="s">
+        <v>464</v>
+      </c>
+      <c r="B116" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C116" s="0">
+        <v>-1.8275795392708134</v>
+      </c>
+      <c r="D116" s="0"/>
+      <c r="E116" s="0"/>
+      <c r="F116" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G116" s="0"/>
+      <c r="H116" s="0"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="0" t="s">
+        <v>465</v>
+      </c>
+      <c r="B117" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C117" s="0">
+        <v>0</v>
+      </c>
+      <c r="D117" s="0"/>
+      <c r="E117" s="0"/>
+      <c r="F117" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G117" s="0"/>
+      <c r="H117" s="0"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="0" t="s">
+        <v>466</v>
+      </c>
+      <c r="B118" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C118" s="0">
+        <v>1.7526473681977495</v>
+      </c>
+      <c r="D118" s="0"/>
+      <c r="E118" s="0"/>
+      <c r="F118" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G118" s="0"/>
+      <c r="H118" s="0"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="0" t="s">
+        <v>467</v>
+      </c>
+      <c r="B119" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C119" s="0">
+        <v>0.15168253041257554</v>
+      </c>
+      <c r="D119" s="0"/>
+      <c r="E119" s="0"/>
+      <c r="F119" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G119" s="0"/>
+      <c r="H119" s="0"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="0" t="s">
+        <v>468</v>
+      </c>
+      <c r="B120" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C120" s="0">
+        <v>2.4110213483593652</v>
+      </c>
+      <c r="D120" s="0"/>
+      <c r="E120" s="0"/>
+      <c r="F120" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G120" s="0"/>
+      <c r="H120" s="0"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="0" t="s">
+        <v>469</v>
+      </c>
+      <c r="B121" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C121" s="0">
+        <v>2.7131092758196531</v>
+      </c>
+      <c r="D121" s="0"/>
+      <c r="E121" s="0"/>
+      <c r="F121" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G121" s="0"/>
+      <c r="H121" s="0"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="0" t="s">
+        <v>470</v>
+      </c>
+      <c r="B122" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C122" s="0">
+        <v>16.090147165877724</v>
+      </c>
+      <c r="D122" s="0"/>
+      <c r="E122" s="0"/>
+      <c r="F122" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G122" s="0"/>
+      <c r="H122" s="0"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="0" t="s">
+        <v>471</v>
+      </c>
+      <c r="B123" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C123" s="0">
+        <v>16.925292122478595</v>
+      </c>
+      <c r="D123" s="0"/>
+      <c r="E123" s="0"/>
+      <c r="F123" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G123" s="0"/>
+      <c r="H123" s="0"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="0" t="s">
+        <v>472</v>
+      </c>
+      <c r="B124" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C124" s="0">
+        <v>0.35178486510320511</v>
+      </c>
+      <c r="D124" s="0"/>
+      <c r="E124" s="0"/>
+      <c r="F124" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G124" s="0"/>
+      <c r="H124" s="0"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="0" t="s">
+        <v>473</v>
+      </c>
+      <c r="B125" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C125" s="0" t="s">
+        <v>521</v>
+      </c>
+      <c r="D125" s="0"/>
+      <c r="E125" s="0"/>
+      <c r="F125" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G125" s="0"/>
+      <c r="H125" s="0"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="0" t="s">
+        <v>474</v>
+      </c>
+      <c r="B126" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C126" s="0">
+        <v>233.69773788009346</v>
+      </c>
+      <c r="D126" s="0"/>
+      <c r="E126" s="0"/>
+      <c r="F126" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G126" s="0"/>
+      <c r="H126" s="0"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="0" t="s">
+        <v>475</v>
+      </c>
+      <c r="B127" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C127" s="0">
+        <v>0.35242563899228196</v>
+      </c>
+      <c r="D127" s="0"/>
+      <c r="E127" s="0"/>
+      <c r="F127" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G127" s="0"/>
+      <c r="H127" s="0"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="0" t="s">
+        <v>476</v>
+      </c>
+      <c r="B128" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C128" s="0" t="s">
+        <v>521</v>
+      </c>
+      <c r="D128" s="0"/>
+      <c r="E128" s="0"/>
+      <c r="F128" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G128" s="0"/>
+      <c r="H128" s="0"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="0" t="s">
+        <v>477</v>
+      </c>
+      <c r="B129" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C129" s="0">
+        <v>9.4744003772526408</v>
+      </c>
+      <c r="D129" s="0"/>
+      <c r="E129" s="0"/>
+      <c r="F129" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G129" s="0"/>
+      <c r="H129" s="0"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="0" t="s">
+        <v>478</v>
+      </c>
+      <c r="B130" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C130" s="0">
+        <v>341.83792795003058</v>
+      </c>
+      <c r="D130" s="0"/>
+      <c r="E130" s="0"/>
+      <c r="F130" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G130" s="0"/>
+      <c r="H130" s="0"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="0" t="s">
+        <v>479</v>
+      </c>
+      <c r="B131" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C131" s="0">
+        <v>34.733446426726843</v>
+      </c>
+      <c r="D131" s="0"/>
+      <c r="E131" s="0"/>
+      <c r="F131" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G131" s="0"/>
+      <c r="H131" s="0"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="0" t="s">
+        <v>480</v>
+      </c>
+      <c r="B132" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C132" s="0">
+        <v>0.42099254615460552</v>
+      </c>
+      <c r="D132" s="0"/>
+      <c r="E132" s="0"/>
+      <c r="F132" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G132" s="0"/>
+      <c r="H132" s="0"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="0" t="s">
+        <v>481</v>
+      </c>
+      <c r="B133" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C133" s="0">
+        <v>4.0516000000000005</v>
+      </c>
+      <c r="D133" s="0"/>
+      <c r="E133" s="0"/>
+      <c r="F133" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G133" s="0"/>
+      <c r="H133" s="0"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="0" t="s">
+        <v>482</v>
+      </c>
+      <c r="B134" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C134" s="0">
+        <v>39.746196000000005</v>
+      </c>
+      <c r="D134" s="0"/>
+      <c r="E134" s="0"/>
+      <c r="F134" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G134" s="0"/>
+      <c r="H134" s="0"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="0" t="s">
+        <v>483</v>
+      </c>
+      <c r="B135" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C135" s="0">
+        <v>18.230437113682747</v>
+      </c>
+      <c r="D135" s="0"/>
+      <c r="E135" s="0"/>
+      <c r="F135" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G135" s="0"/>
+      <c r="H135" s="0"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="0" t="s">
+        <v>484</v>
+      </c>
+      <c r="B136" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C136" s="0">
+        <v>0.080999999999999989</v>
+      </c>
+      <c r="D136" s="0"/>
+      <c r="E136" s="0"/>
+      <c r="F136" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G136" s="0"/>
+      <c r="H136" s="0"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="0" t="s">
+        <v>485</v>
+      </c>
+      <c r="B137" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C137" s="0">
+        <v>64.749890848167752</v>
+      </c>
+      <c r="D137" s="0"/>
+      <c r="E137" s="0"/>
+      <c r="F137" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G137" s="0"/>
+      <c r="H137" s="0"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="0" t="s">
+        <v>486</v>
+      </c>
+      <c r="B138" s="0" t="s">
+        <v>506</v>
+      </c>
+      <c r="C138" s="0">
+        <v>0.29999999999999999</v>
+      </c>
+      <c r="D138" s="0"/>
+      <c r="E138" s="0"/>
+      <c r="F138" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G138" s="0"/>
+      <c r="H138" s="0"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="0" t="s">
+        <v>487</v>
+      </c>
+      <c r="B139" s="0" t="s">
+        <v>506</v>
+      </c>
+      <c r="C139" s="0">
+        <v>26.360381758366742</v>
+      </c>
+      <c r="D139" s="0"/>
+      <c r="E139" s="0"/>
+      <c r="F139" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G139" s="0"/>
+      <c r="H139" s="0"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="0" t="s">
+        <v>488</v>
+      </c>
+      <c r="B140" s="0" t="s">
+        <v>506</v>
+      </c>
+      <c r="C140" s="0">
+        <v>3.6396182416332579</v>
+      </c>
+      <c r="D140" s="0"/>
+      <c r="E140" s="0"/>
+      <c r="F140" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G140" s="0"/>
+      <c r="H140" s="0"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="0" t="s">
+        <v>489</v>
+      </c>
+      <c r="B141" s="0" t="s">
+        <v>506</v>
+      </c>
+      <c r="C141" s="0">
+        <v>0.25</v>
+      </c>
+      <c r="D141" s="0"/>
+      <c r="E141" s="0"/>
+      <c r="F141" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G141" s="0"/>
+      <c r="H141" s="0"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="0" t="s">
+        <v>490</v>
+      </c>
+      <c r="B142" s="0" t="s">
+        <v>506</v>
+      </c>
+      <c r="C142" s="0">
+        <v>0.69999999999999996</v>
+      </c>
+      <c r="D142" s="0"/>
+      <c r="E142" s="0"/>
+      <c r="F142" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G142" s="0"/>
+      <c r="H142" s="0"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="0" t="s">
+        <v>491</v>
+      </c>
+      <c r="B143" s="0" t="s">
+        <v>506</v>
+      </c>
+      <c r="C143" s="0">
+        <v>1</v>
+      </c>
+      <c r="D143" s="0"/>
+      <c r="E143" s="0"/>
+      <c r="F143" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G143" s="0"/>
+      <c r="H143" s="0"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="0" t="s">
+        <v>492</v>
+      </c>
+      <c r="B144" s="0" t="s">
+        <v>506</v>
+      </c>
+      <c r="C144" s="0">
+        <v>0.12048857500544551</v>
+      </c>
+      <c r="D144" s="0"/>
+      <c r="E144" s="0"/>
+      <c r="F144" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G144" s="0"/>
+      <c r="H144" s="0"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="0" t="s">
+        <v>493</v>
+      </c>
+      <c r="B145" s="0" t="s">
+        <v>506</v>
+      </c>
+      <c r="C145" s="0">
+        <v>119.66043834086311</v>
+      </c>
+      <c r="D145" s="0"/>
+      <c r="E145" s="0"/>
+      <c r="F145" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G145" s="0"/>
+      <c r="H145" s="0"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="0" t="s">
+        <v>494</v>
+      </c>
+      <c r="B146" s="0" t="s">
+        <v>506</v>
+      </c>
+      <c r="C146" s="0">
+        <v>0.074583678423586861</v>
+      </c>
+      <c r="D146" s="0"/>
+      <c r="E146" s="0"/>
+      <c r="F146" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G146" s="0"/>
+      <c r="H146" s="0"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="0" t="s">
+        <v>495</v>
+      </c>
+      <c r="B147" s="0" t="s">
+        <v>506</v>
+      </c>
+      <c r="C147" s="0">
+        <v>1.0700000000000001</v>
+      </c>
+      <c r="D147" s="0"/>
+      <c r="E147" s="0"/>
+      <c r="F147" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G147" s="0"/>
+      <c r="H147" s="0"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="0" t="s">
+        <v>496</v>
+      </c>
+      <c r="B148" s="0" t="s">
+        <v>506</v>
+      </c>
+      <c r="C148" s="0">
+        <v>0.29999999999999999</v>
+      </c>
+      <c r="D148" s="0"/>
+      <c r="E148" s="0"/>
+      <c r="F148" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G148" s="0"/>
+      <c r="H148" s="0"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="0" t="s">
+        <v>497</v>
+      </c>
+      <c r="B149" s="0" t="s">
+        <v>506</v>
+      </c>
+      <c r="C149" s="0">
+        <v>29.162154556467332</v>
+      </c>
+      <c r="D149" s="0"/>
+      <c r="E149" s="0"/>
+      <c r="F149" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G149" s="0"/>
+      <c r="H149" s="0"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="0" t="s">
+        <v>498</v>
+      </c>
+      <c r="B150" s="0" t="s">
+        <v>506</v>
+      </c>
+      <c r="C150" s="0">
+        <v>0.83784544353266455</v>
+      </c>
+      <c r="D150" s="0"/>
+      <c r="E150" s="0"/>
+      <c r="F150" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G150" s="0"/>
+      <c r="H150" s="0"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="0" t="s">
+        <v>499</v>
+      </c>
+      <c r="B151" s="0" t="s">
+        <v>506</v>
+      </c>
+      <c r="C151" s="0">
+        <v>5.2740736776131758</v>
+      </c>
+      <c r="D151" s="0"/>
+      <c r="E151" s="0"/>
+      <c r="F151" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G151" s="0"/>
+      <c r="H151" s="0"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="0" t="s">
+        <v>500</v>
+      </c>
+      <c r="B152" s="0" t="s">
+        <v>506</v>
+      </c>
+      <c r="C152" s="0">
+        <v>0.3656082203404642</v>
+      </c>
+      <c r="D152" s="0"/>
+      <c r="E152" s="0"/>
+      <c r="F152" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G152" s="0"/>
+      <c r="H152" s="0"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="0" t="s">
+        <v>501</v>
+      </c>
+      <c r="B153" s="0" t="s">
+        <v>506</v>
+      </c>
+      <c r="C153" s="0">
+        <v>0.14999999999999999</v>
+      </c>
+      <c r="D153" s="0"/>
+      <c r="E153" s="0"/>
+      <c r="F153" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G153" s="0"/>
+      <c r="H153" s="0"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="0" t="s">
+        <v>502</v>
+      </c>
+      <c r="B154" s="0" t="s">
+        <v>506</v>
+      </c>
+      <c r="C154" s="0">
+        <v>-0.79111105164197637</v>
+      </c>
+      <c r="D154" s="0"/>
+      <c r="E154" s="0"/>
+      <c r="F154" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G154" s="0"/>
+      <c r="H154" s="0"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="0" t="s">
+        <v>503</v>
+      </c>
+      <c r="B155" s="0" t="s">
+        <v>506</v>
+      </c>
+      <c r="C155" s="0">
+        <v>0.12602616170797043</v>
+      </c>
+      <c r="D155" s="0"/>
+      <c r="E155" s="0"/>
+      <c r="F155" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G155" s="0"/>
+      <c r="H155" s="0"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="0" t="s">
+        <v>504</v>
+      </c>
+      <c r="B156" s="0" t="s">
+        <v>506</v>
+      </c>
+      <c r="C156" s="0">
+        <v>5</v>
+      </c>
+      <c r="D156" s="0"/>
+      <c r="E156" s="0"/>
+      <c r="F156" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G156" s="0"/>
+      <c r="H156" s="0"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="0" t="s">
+        <v>505</v>
+      </c>
+      <c r="B157" s="0" t="s">
+        <v>506</v>
+      </c>
+      <c r="C157" s="0">
+        <v>-0.18486997339978403</v>
+      </c>
+      <c r="D157" s="0"/>
+      <c r="E157" s="0"/>
+      <c r="F157" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G157" s="0"/>
+      <c r="H157" s="0"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFCC8514-E0AF-4C67-BF86-8649FC702924}">
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="32.42578125" customWidth="true"/>
+    <col min="2" max="3" width="32.42578125" style="20" customWidth="true"/>
+    <col min="4" max="4" width="13.28515625" style="20" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>274</v>
       </c>
@@ -3349,7 +6950,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>276</v>
       </c>
@@ -3363,7 +6964,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>277</v>
       </c>
@@ -3377,7 +6978,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>278</v>
       </c>
@@ -3391,7 +6992,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>279</v>
       </c>
@@ -3405,7 +7006,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>304</v>
       </c>
@@ -3419,7 +7020,7 @@
         <v>-4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>280</v>
       </c>
@@ -3433,7 +7034,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>281</v>
       </c>
@@ -3447,7 +7048,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>282</v>
       </c>
@@ -3461,7 +7062,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>283</v>
       </c>
@@ -3475,7 +7076,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>284</v>
       </c>
@@ -3489,7 +7090,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>285</v>
       </c>
@@ -3503,7 +7104,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>286</v>
       </c>
@@ -3517,7 +7118,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>287</v>
       </c>
@@ -3531,7 +7132,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>288</v>
       </c>
@@ -3545,7 +7146,7 @@
         <v>-7.8E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>289</v>
       </c>
@@ -3559,7 +7160,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>290</v>
       </c>
@@ -3573,7 +7174,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="18" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>291</v>
       </c>
@@ -3587,7 +7188,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="19" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>293</v>
       </c>
@@ -3601,7 +7202,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="20" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>292</v>
       </c>
@@ -3620,29 +7221,29 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{118BE621-EF6B-4648-868E-9937B9C5B685}">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{118BE621-EF6B-4648-868E-9937B9C5B685}">
   <dimension ref="A1:F32"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="48.140625" style="2" customWidth="1"/>
-    <col min="2" max="4" width="15.7109375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="3.7109375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="46.7109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="48.140625" style="2" customWidth="true"/>
+    <col min="2" max="4" width="15.7109375" style="2" customWidth="true"/>
+    <col min="5" max="5" width="3.7109375" style="2" customWidth="true"/>
+    <col min="6" max="6" width="46.7109375" style="2" customWidth="true"/>
     <col min="7" max="16384" width="8.7109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>208</v>
       </c>
@@ -3656,12 +7257,12 @@
         <v>211</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>212</v>
       </c>
       <c r="B5" s="5">
-        <f>(Sheet1!C19*Sheet1!C77/Sheet1!C72)/(Sheet1!C25-Sheet1!C26)</f>
+        <f>(Inputs!C19*Inputs!C77/Inputs!C72)/(Inputs!C25-Inputs!C26)</f>
         <v>0.42877435804042974</v>
       </c>
       <c r="C5" s="15">
@@ -3674,27 +7275,27 @@
         <v>213</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>214</v>
       </c>
       <c r="B6" s="6">
-        <f>Sheet1!C57</f>
+        <f>Inputs!C57</f>
         <v>0.25</v>
       </c>
       <c r="C6" s="6">
-        <f>Sheet1!C53</f>
+        <f>Inputs!C53</f>
         <v>0.3</v>
       </c>
       <c r="D6" s="6">
-        <f>Sheet1!C55</f>
+        <f>Inputs!C55</f>
         <v>0.3</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>216</v>
       </c>
@@ -3714,12 +7315,12 @@
         <v>245</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>217</v>
       </c>
       <c r="B8" s="5">
-        <f>(Sheet1!C59-Sheet1!C58)*Sheet1!C25/2</f>
+        <f>(Inputs!C59-Inputs!C58)*Inputs!C25/2</f>
         <v>0.22500000000000003</v>
       </c>
       <c r="C8" s="15">
@@ -3732,27 +7333,27 @@
         <v>246</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>218</v>
       </c>
       <c r="B9" s="7">
-        <f>Sheet1!C60</f>
+        <f>Inputs!C60</f>
         <v>15</v>
       </c>
       <c r="C9" s="16">
-        <f>Sheet1!C54</f>
+        <f>Inputs!C54</f>
         <v>30</v>
       </c>
       <c r="D9" s="7">
-        <f>Sheet1!C56</f>
+        <f>Inputs!C56</f>
         <v>30</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>220</v>
       </c>
@@ -3769,7 +7370,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>222</v>
       </c>
@@ -3786,27 +7387,27 @@
         <v>247</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>223</v>
       </c>
       <c r="B12" s="5">
-        <f>Sheet1!C20</f>
+        <f>Inputs!C20</f>
         <v>1.2250000000000001</v>
       </c>
       <c r="C12" s="5">
-        <f>Sheet1!C20</f>
+        <f>Inputs!C20</f>
         <v>1.2250000000000001</v>
       </c>
       <c r="D12" s="5">
-        <f>Sheet1!C20</f>
+        <f>Inputs!C20</f>
         <v>1.2250000000000001</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>225</v>
       </c>
@@ -3823,47 +7424,47 @@
         <v>226</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>257</v>
       </c>
       <c r="B14" s="17">
-        <f>Sheet1!C91</f>
+        <f>Inputs!C91</f>
         <v>1</v>
       </c>
       <c r="C14" s="17">
-        <f>Sheet1!C92</f>
+        <f>Inputs!C92</f>
         <v>1.2</v>
       </c>
       <c r="D14" s="17">
-        <f>Sheet1!C93</f>
+        <f>Inputs!C93</f>
         <v>1</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>258</v>
       </c>
       <c r="B15" s="17">
-        <f>Sheet1!C94</f>
+        <f>Inputs!C94</f>
         <v>0.85</v>
       </c>
       <c r="C15" s="17">
-        <f>Sheet1!C94</f>
+        <f>Inputs!C94</f>
         <v>0.85</v>
       </c>
       <c r="D15" s="17">
-        <f>Sheet1!C94</f>
+        <f>Inputs!C94</f>
         <v>0.85</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>227</v>
       </c>
@@ -3871,7 +7472,7 @@
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="17" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>228</v>
       </c>
@@ -3888,7 +7489,7 @@
         <v>1.9823131728623846</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="18" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>229</v>
       </c>
@@ -3905,7 +7506,7 @@
         <v>1.1592794807274085</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="19" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>230</v>
       </c>
@@ -3922,7 +7523,7 @@
         <v>-0.62740704594148844</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="20" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>231</v>
       </c>
@@ -3939,7 +7540,7 @@
         <v>-0.96540266006846076</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="21" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>232</v>
       </c>
@@ -3947,7 +7548,7 @@
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="22" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>233</v>
       </c>
@@ -3964,7 +7565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="23" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>234</v>
       </c>
@@ -3981,7 +7582,7 @@
         <v>0.52359877559829882</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="24" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>235</v>
       </c>
@@ -3998,7 +7599,7 @@
         <v>-0.50548365077118673</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="25" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>236</v>
       </c>
@@ -4015,7 +7616,7 @@
         <v>324.01250000000005</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="26" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>237</v>
       </c>
@@ -4032,7 +7633,7 @@
         <v>1.42884E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="27" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>238</v>
       </c>
@@ -4049,7 +7650,7 @@
         <v>-0.13760360258695806</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="28" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>239</v>
       </c>
@@ -4066,7 +7667,7 @@
         <v>0.13760360258695806</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="29" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>240</v>
       </c>
@@ -4083,7 +7684,7 @@
         <v>22.925083964169769</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="30" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>241</v>
       </c>
@@ -4091,7 +7692,7 @@
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="31" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>242</v>
       </c>
@@ -4099,7 +7700,7 @@
       <c r="C31" s="14"/>
       <c r="D31" s="14"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="32" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>243</v>
       </c>
@@ -4119,4 +7720,25 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="C109:F109"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="3" max="3" width="11.7109375" customWidth="true"/>
+    <col min="6" max="6" width="153.85546875" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="109">
+      <c r="C109" s="0">
+        <v>11.941543440928031</v>
+      </c>
+      <c r="F109" s="0" t="s">
+        <v>382</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1386" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1387" uniqueCount="523">
   <si>
     <t>Parameter</t>
   </si>
@@ -7727,13 +7727,13 @@
   <dimension ref="C109:F109"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="11.7109375" customWidth="true"/>
-    <col min="6" max="6" width="153.85546875" customWidth="true"/>
+    <col min="3" max="3" width="11.5546875" customWidth="true"/>
+    <col min="6" max="6" width="142.44140625" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="109">
       <c r="C109" s="0">
-        <v>11.941543440928031</v>
+        <v>12.250154543435004</v>
       </c>
       <c r="F109" s="0" t="s">
         <v>382</v>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\Fall 2026\AAE 451\451-DBF-Team01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ceaa8977d2236823/Documents/GitHub/451-DBF-Team01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37DAE441-3691-47BB-B387-517F08F01369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{37DAE441-3691-47BB-B387-517F08F01369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2836BEBE-EF50-4D84-AD56-610C67D58106}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs" sheetId="1" r:id="rId1"/>
     <sheet name="Outputs" sheetId="4" r:id="rId2"/>
     <sheet name="MassBudget" sheetId="3" r:id="rId3"/>
     <sheet name="Hinge Moments" sheetId="2" r:id="rId4"/>
-    <sheet name="Sheet1" sheetId="5" r:id="rId8"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="true"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1387" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1062" uniqueCount="521">
   <si>
     <t>Parameter</t>
   </si>
@@ -1177,12 +1177,6 @@
   </si>
   <si>
     <t>Overwritten input (Sheet1 value: 6)</t>
-  </si>
-  <si>
-    <t>Written by writeOutputs.m on 2026-10-06 13:51</t>
-  </si>
-  <si>
-    <t>Written by writeOutputs.m on 2026-10-06 13:54</t>
   </si>
   <si>
     <t>COMPUTED each run by MaxPayloadSweep.m = 1.25x the baseline self-consistent stall speed -- not read back in as an input, edit LANDING_SPEED_RATIO in that script instead.</t>
@@ -1611,13 +1605,13 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1674,7 +1668,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1713,12 +1707,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79995117038484"/>
+        <fgColor theme="5" tint="0.79995117038483843"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1726,57 +1726,56 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border/>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="true"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="true"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="true" applyFill="true"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="true"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="true"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="true"/>
-    <xf numFmtId="166" fontId="5" fillId="3" borderId="0" xfId="1" applyNumberFormat="true" applyFont="true" applyFill="true"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="1" applyNumberFormat="true" applyFont="true" applyFill="true"/>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="0" xfId="1" applyNumberFormat="true" applyFont="true" applyFill="true"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="true"/>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="0" xfId="1" applyNumberFormat="true" applyFont="true" applyFill="true"/>
-    <xf numFmtId="2" fontId="6" fillId="4" borderId="0" xfId="1" applyNumberFormat="true" applyFont="true" applyFill="true"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="1" applyFont="true" applyFill="true"/>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="1" applyNumberFormat="true" applyFill="true"/>
-    <xf numFmtId="166" fontId="5" fillId="5" borderId="0" xfId="1" applyNumberFormat="true" applyFont="true" applyFill="true"/>
-    <xf numFmtId="2" fontId="5" fillId="5" borderId="0" xfId="1" applyNumberFormat="true" applyFont="true" applyFill="true"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="6" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="5" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" justifyLastLine="false" shrinkToFit="false" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" justifyLastLine="false" shrinkToFit="false" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" justifyLastLine="false" shrinkToFit="false" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1792,40 +1791,40 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" id="1" name="Table1" displayName="Table1" ref="A1:F109" totalsRowShown="false">
-  <autoFilter ref="A1:F109"/>
-  <sortState ref="A2:E43">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:F109" totalsRowShown="0">
+  <autoFilter ref="A1:F109" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E43">
     <sortCondition ref="B1:B101"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" name="Parameter"/>
-    <tableColumn id="2" name="Subclass" dataDxfId="2"/>
-    <tableColumn id="3" name="Value" dataDxfId="1"/>
-    <tableColumn id="4" name="Units" dataDxfId="0"/>
-    <tableColumn id="5" name="Description"/>
-    <tableColumn id="6" name="Notes"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Parameter"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Subclass" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Value" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Units" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Description"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Notes"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium15" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
+  <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" id="2" name="Table2" displayName="Table2" ref="A1:F34" totalsRowShown="false">
-  <autoFilter ref="A1:F34"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="A1:F34" totalsRowShown="0">
+  <autoFilter ref="A1:F34" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="Parameter"/>
-    <tableColumn id="2" name="Subclass"/>
-    <tableColumn id="3" name="Value"/>
-    <tableColumn id="4" name="Units"/>
-    <tableColumn id="5" name="Description"/>
-    <tableColumn id="6" name="Source"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Parameter"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Subclass"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Value"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Units"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Description"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Source"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium15" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
+  <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1942,7 +1941,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="true">
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -1966,9 +1965,9 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="false"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="true">
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -1992,7 +1991,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="false"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -2027,7 +2026,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="false">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -2045,7 +2044,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="true">
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -2070,7 +2069,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="false"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -2086,19 +2085,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F109"/>
-  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" bestFit="true" customWidth="true"/>
-    <col min="2" max="2" width="15.140625" style="20" customWidth="true"/>
-    <col min="3" max="3" width="13.7109375" style="20" customWidth="true"/>
-    <col min="4" max="4" width="16.85546875" style="20" customWidth="true"/>
-    <col min="5" max="5" width="168.140625" bestFit="true" customWidth="true"/>
-    <col min="6" max="6" width="142.42578125" bestFit="true" customWidth="true"/>
+    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.109375" style="20" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" style="20" customWidth="1"/>
+    <col min="4" max="4" width="16.88671875" style="20" customWidth="1"/>
+    <col min="5" max="5" width="168.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="142.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2118,7 +2117,7 @@
         <v>5</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -2135,7 +2134,7 @@
         <v>9</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -2152,7 +2151,7 @@
         <v>11</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -2169,7 +2168,7 @@
         <v>13</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -2186,7 +2185,7 @@
         <v>15</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -2203,7 +2202,7 @@
         <v>17</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -2220,7 +2219,7 @@
         <v>19</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -2237,7 +2236,7 @@
         <v>21</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>205</v>
       </c>
@@ -2251,7 +2250,7 @@
         <v>8</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -2268,7 +2267,7 @@
         <v>24</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -2285,7 +2284,7 @@
         <v>26</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -2302,7 +2301,7 @@
         <v>203</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -2319,7 +2318,7 @@
         <v>30</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -2336,7 +2335,7 @@
         <v>32</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -2353,7 +2352,7 @@
         <v>34</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>35</v>
       </c>
@@ -2370,7 +2369,7 @@
         <v>36</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>37</v>
       </c>
@@ -2387,7 +2386,7 @@
         <v>38</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>39</v>
       </c>
@@ -2404,7 +2403,7 @@
         <v>40</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="19" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>41</v>
       </c>
@@ -2421,7 +2420,7 @@
         <v>44</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>45</v>
       </c>
@@ -2438,7 +2437,7 @@
         <v>47</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="21" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -2455,7 +2454,7 @@
         <v>50</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="22" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -2472,7 +2471,7 @@
         <v>52</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="23" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -2489,7 +2488,7 @@
         <v>54</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="24" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -2506,7 +2505,7 @@
         <v>57</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>58</v>
       </c>
@@ -2523,7 +2522,7 @@
         <v>60</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="26" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>61</v>
       </c>
@@ -2540,7 +2539,7 @@
         <v>62</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="27" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>63</v>
       </c>
@@ -2557,7 +2556,7 @@
         <v>64</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="28" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>65</v>
       </c>
@@ -2574,7 +2573,7 @@
         <v>67</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="29" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -2591,7 +2590,7 @@
         <v>69</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -2608,7 +2607,7 @@
         <v>71</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="31" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>72</v>
       </c>
@@ -2625,7 +2624,7 @@
         <v>73</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="32" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>74</v>
       </c>
@@ -2642,7 +2641,7 @@
         <v>75</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="33" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>76</v>
       </c>
@@ -2659,7 +2658,7 @@
         <v>77</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="34" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>78</v>
       </c>
@@ -2676,7 +2675,7 @@
         <v>79</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="35" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>80</v>
       </c>
@@ -2693,7 +2692,7 @@
         <v>81</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="36" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>82</v>
       </c>
@@ -2710,7 +2709,7 @@
         <v>83</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="37" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>84</v>
       </c>
@@ -2727,7 +2726,7 @@
         <v>85</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="38" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>86</v>
       </c>
@@ -2744,7 +2743,7 @@
         <v>87</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="39" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>88</v>
       </c>
@@ -2761,7 +2760,7 @@
         <v>89</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="40" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>90</v>
       </c>
@@ -2778,7 +2777,7 @@
         <v>91</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="41" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>92</v>
       </c>
@@ -2795,7 +2794,7 @@
         <v>93</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="42" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>94</v>
       </c>
@@ -2812,7 +2811,7 @@
         <v>95</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="43" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>96</v>
       </c>
@@ -2829,7 +2828,7 @@
         <v>97</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="44" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>98</v>
       </c>
@@ -2846,7 +2845,7 @@
         <v>99</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="45" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>100</v>
       </c>
@@ -2863,7 +2862,7 @@
         <v>102</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="46" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>103</v>
       </c>
@@ -2880,7 +2879,7 @@
         <v>104</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="47" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>105</v>
       </c>
@@ -2897,7 +2896,7 @@
         <v>106</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="48" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>107</v>
       </c>
@@ -2914,7 +2913,7 @@
         <v>108</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="49" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>109</v>
       </c>
@@ -2931,7 +2930,7 @@
         <v>110</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="50" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>111</v>
       </c>
@@ -2948,7 +2947,7 @@
         <v>112</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="51" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>113</v>
       </c>
@@ -2965,7 +2964,7 @@
         <v>114</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="52" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>115</v>
       </c>
@@ -2982,7 +2981,7 @@
         <v>116</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="53" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>117</v>
       </c>
@@ -2999,7 +2998,7 @@
         <v>118</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="54" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>119</v>
       </c>
@@ -3016,7 +3015,7 @@
         <v>120</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="55" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>121</v>
       </c>
@@ -3033,7 +3032,7 @@
         <v>122</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="56" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>123</v>
       </c>
@@ -3050,7 +3049,7 @@
         <v>124</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="57" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>125</v>
       </c>
@@ -3067,7 +3066,7 @@
         <v>126</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="58" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>127</v>
       </c>
@@ -3084,7 +3083,7 @@
         <v>128</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="59" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>129</v>
       </c>
@@ -3101,7 +3100,7 @@
         <v>130</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="60" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>131</v>
       </c>
@@ -3118,7 +3117,7 @@
         <v>132</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="61" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>133</v>
       </c>
@@ -3135,7 +3134,7 @@
         <v>134</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="62" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>135</v>
       </c>
@@ -3152,7 +3151,7 @@
         <v>138</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="63" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>139</v>
       </c>
@@ -3169,7 +3168,7 @@
         <v>140</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="64" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>141</v>
       </c>
@@ -3186,7 +3185,7 @@
         <v>142</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="65" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>143</v>
       </c>
@@ -3203,7 +3202,7 @@
         <v>144</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="66" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>145</v>
       </c>
@@ -3220,7 +3219,7 @@
         <v>200</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="67" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>201</v>
       </c>
@@ -3237,7 +3236,7 @@
         <v>202</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="68" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>146</v>
       </c>
@@ -3254,7 +3253,7 @@
         <v>147</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="69" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>148</v>
       </c>
@@ -3271,7 +3270,7 @@
         <v>149</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="70" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>150</v>
       </c>
@@ -3288,7 +3287,7 @@
         <v>151</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="71" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>152</v>
       </c>
@@ -3305,7 +3304,7 @@
         <v>153</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="72" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>154</v>
       </c>
@@ -3322,7 +3321,7 @@
         <v>156</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="73" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>157</v>
       </c>
@@ -3339,7 +3338,7 @@
         <v>159</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="74" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>160</v>
       </c>
@@ -3356,7 +3355,7 @@
         <v>161</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>162</v>
       </c>
@@ -3373,7 +3372,7 @@
         <v>164</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="76" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>165</v>
       </c>
@@ -3390,7 +3389,7 @@
         <v>166</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="77" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>167</v>
       </c>
@@ -3407,7 +3406,7 @@
         <v>168</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="78" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>169</v>
       </c>
@@ -3424,7 +3423,7 @@
         <v>171</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="79" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>172</v>
       </c>
@@ -3441,7 +3440,7 @@
         <v>173</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="80" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>174</v>
       </c>
@@ -3458,7 +3457,7 @@
         <v>175</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="81" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>176</v>
       </c>
@@ -3475,7 +3474,7 @@
         <v>177</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="82" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>178</v>
       </c>
@@ -3492,7 +3491,7 @@
         <v>179</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="83" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>180</v>
       </c>
@@ -3509,7 +3508,7 @@
         <v>182</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="84" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>183</v>
       </c>
@@ -3526,7 +3525,7 @@
         <v>185</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="85" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>186</v>
       </c>
@@ -3543,7 +3542,7 @@
         <v>188</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="86" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>189</v>
       </c>
@@ -3560,7 +3559,7 @@
         <v>206</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="87" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>191</v>
       </c>
@@ -3577,7 +3576,7 @@
         <v>192</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="88" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>193</v>
       </c>
@@ -3594,7 +3593,7 @@
         <v>195</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="89" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>196</v>
       </c>
@@ -3611,7 +3610,7 @@
         <v>197</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="90" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>198</v>
       </c>
@@ -3628,7 +3627,7 @@
         <v>199</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="91" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>248</v>
       </c>
@@ -3645,7 +3644,7 @@
         <v>250</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="92" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>251</v>
       </c>
@@ -3662,7 +3661,7 @@
         <v>252</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="93" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>253</v>
       </c>
@@ -3679,7 +3678,7 @@
         <v>254</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="94" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>255</v>
       </c>
@@ -3696,7 +3695,7 @@
         <v>256</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="95" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>261</v>
       </c>
@@ -3713,7 +3712,7 @@
         <v>262</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="96" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>263</v>
       </c>
@@ -3730,7 +3729,7 @@
         <v>295</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="97" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>264</v>
       </c>
@@ -3747,7 +3746,7 @@
         <v>296</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="98" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>266</v>
       </c>
@@ -3764,7 +3763,7 @@
         <v>297</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="99" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>267</v>
       </c>
@@ -3781,7 +3780,7 @@
         <v>298</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="100" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>268</v>
       </c>
@@ -3798,7 +3797,7 @@
         <v>299</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="101" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>269</v>
       </c>
@@ -3815,7 +3814,7 @@
         <v>300</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="102" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>270</v>
       </c>
@@ -3832,7 +3831,7 @@
         <v>301</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="103" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>271</v>
       </c>
@@ -3849,7 +3848,7 @@
         <v>302</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="104" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>272</v>
       </c>
@@ -3866,7 +3865,7 @@
         <v>314</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="105" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>305</v>
       </c>
@@ -3883,7 +3882,7 @@
         <v>306</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="106" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>307</v>
       </c>
@@ -3900,7 +3899,7 @@
         <v>313</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="107" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>308</v>
       </c>
@@ -3917,7 +3916,7 @@
         <v>311</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="108" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>309</v>
       </c>
@@ -3934,7 +3933,7 @@
         <v>311</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="109" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>310</v>
       </c>
@@ -3960,2963 +3959,2394 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H157"/>
-  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="40.7109375" customWidth="true"/>
-    <col min="2" max="2" width="12.5703125" customWidth="true"/>
-    <col min="3" max="3" width="64.5703125" customWidth="true"/>
-    <col min="4" max="4" width="5.7109375" customWidth="true"/>
-    <col min="5" max="5" width="46" customWidth="true"/>
-    <col min="6" max="6" width="32.42578125" customWidth="true"/>
-    <col min="8" max="8" width="42.7109375" customWidth="true"/>
-    <col min="7" max="7" width="9.140625"/>
+    <col min="1" max="1" width="40.6640625" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" customWidth="1"/>
+    <col min="3" max="3" width="64.5546875" customWidth="1"/>
+    <col min="4" max="4" width="5.6640625" customWidth="1"/>
+    <col min="5" max="5" width="46" customWidth="1"/>
+    <col min="6" max="6" width="32.44140625" customWidth="1"/>
+    <col min="7" max="7" width="9.109375"/>
+    <col min="8" max="8" width="42.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" t="s">
         <v>377</v>
       </c>
-      <c r="G1" s="0"/>
-      <c r="H1" s="0" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="0" t="s">
+      <c r="H1" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>316</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="0">
-        <v>0.29999999999999999</v>
-      </c>
-      <c r="D2" s="0" t="s">
+      <c r="C2">
+        <v>0.3</v>
+      </c>
+      <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" t="s">
         <v>349</v>
       </c>
-      <c r="F2" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G2" s="0"/>
-      <c r="H2" s="0"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="0" t="s">
+      <c r="F2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>317</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="0">
+      <c r="C3">
         <v>1.1818181818181817</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" t="s">
         <v>350</v>
       </c>
-      <c r="F3" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G3" s="0"/>
-      <c r="H3" s="0"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="0" t="s">
+      <c r="F3" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>318</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="0">
+      <c r="C4">
         <v>0.92201380973471758</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" t="s">
         <v>351</v>
       </c>
-      <c r="F4" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G4" s="0"/>
-      <c r="H4" s="0"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="0" t="s">
+      <c r="F4" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>319</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="0">
-        <v>0.07919652663705147</v>
-      </c>
-      <c r="D5" s="0" t="s">
+      <c r="C5">
+        <v>7.919652663705147E-2</v>
+      </c>
+      <c r="D5" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" t="s">
         <v>352</v>
       </c>
-      <c r="F5" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G5" s="0"/>
-      <c r="H5" s="0"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="0" t="s">
+      <c r="F5" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>320</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="0">
+      <c r="C6">
         <v>0.19588300688233271</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" t="s">
         <v>353</v>
       </c>
-      <c r="F6" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G6" s="0"/>
-      <c r="H6" s="0"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="0" t="s">
+      <c r="F6" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>321</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="0">
-        <v>0.029817638776781716</v>
-      </c>
-      <c r="D7" s="0"/>
-      <c r="E7" s="0"/>
-      <c r="F7" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G7" s="0"/>
-      <c r="H7" s="0"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="0" t="s">
+      <c r="C7">
+        <v>2.9817638776781716E-2</v>
+      </c>
+      <c r="F7" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>322</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="0">
-        <v>0.036945326174116347</v>
-      </c>
-      <c r="D8" s="0" t="s">
+      <c r="C8">
+        <v>3.6945326174116347E-2</v>
+      </c>
+      <c r="D8" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="E8" t="s">
         <v>354</v>
       </c>
-      <c r="F8" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G8" s="0"/>
-      <c r="H8" s="0"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="0" t="s">
+      <c r="F8" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>323</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="0">
-        <v>0.036945326174116347</v>
-      </c>
-      <c r="D9" s="0" t="s">
+      <c r="C9">
+        <v>3.6945326174116347E-2</v>
+      </c>
+      <c r="D9" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="0" t="s">
+      <c r="E9" t="s">
         <v>355</v>
       </c>
-      <c r="F9" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G9" s="0"/>
-      <c r="H9" s="0"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="0" t="s">
+      <c r="F9" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>324</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="0">
-        <v>0.021945326174116347</v>
-      </c>
-      <c r="D10" s="0" t="s">
+      <c r="C10">
+        <v>2.1945326174116347E-2</v>
+      </c>
+      <c r="D10" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="0" t="s">
+      <c r="E10" t="s">
         <v>356</v>
       </c>
-      <c r="F10" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G10" s="0"/>
-      <c r="H10" s="0"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="0" t="s">
+      <c r="F10" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>325</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="0">
+      <c r="C11">
         <v>8.120106954426566</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="0" t="s">
+      <c r="E11" t="s">
         <v>357</v>
       </c>
-      <c r="F11" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G11" s="0"/>
-      <c r="H11" s="0"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="0" t="s">
+      <c r="F11" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>326</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="0">
+      <c r="C12">
         <v>10.289169276665902</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="0" t="s">
+      <c r="E12" t="s">
         <v>358</v>
       </c>
-      <c r="F12" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G12" s="0"/>
-      <c r="H12" s="0"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="0" t="s">
+      <c r="F12" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>381</v>
+      </c>
+      <c r="B13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13">
+        <v>3.0198549799930445</v>
+      </c>
+      <c r="F13" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>382</v>
+      </c>
+      <c r="B14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14">
+        <v>4.0327458299223453</v>
+      </c>
+      <c r="F14" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>383</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B15" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="0">
-        <v>3.0198549799930445</v>
-      </c>
-      <c r="D13" s="0"/>
-      <c r="E13" s="0"/>
-      <c r="F13" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G13" s="0"/>
-      <c r="H13" s="0"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="0" t="s">
+      <c r="C15">
+        <v>0.58894455001488533</v>
+      </c>
+      <c r="F15" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>384</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B16" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="0">
-        <v>4.0327458299223453</v>
-      </c>
-      <c r="D14" s="0"/>
-      <c r="E14" s="0"/>
-      <c r="F14" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G14" s="0"/>
-      <c r="H14" s="0"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="0" t="s">
+      <c r="C16">
+        <v>5.2740736776131758</v>
+      </c>
+      <c r="F16" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>385</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B17" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="0">
-        <v>0.58894455001488533</v>
-      </c>
-      <c r="D15" s="0"/>
-      <c r="E15" s="0"/>
-      <c r="F15" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G15" s="0"/>
-      <c r="H15" s="0"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="0" t="s">
+      <c r="C17">
+        <v>-9.4788465253600393E-2</v>
+      </c>
+      <c r="F17" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>386</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B18" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="0">
+      <c r="C18">
+        <v>0.66074594914354523</v>
+      </c>
+      <c r="F18" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>387</v>
+      </c>
+      <c r="B19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19">
+        <v>0.60899778104422941</v>
+      </c>
+      <c r="F19" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>388</v>
+      </c>
+      <c r="B20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20">
+        <v>1.5753270213496304</v>
+      </c>
+      <c r="F20" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>389</v>
+      </c>
+      <c r="B21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21">
+        <v>0.66074594914354523</v>
+      </c>
+      <c r="F21" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>390</v>
+      </c>
+      <c r="B22" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22">
+        <v>0.12602616170797043</v>
+      </c>
+      <c r="F22" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>327</v>
+      </c>
+      <c r="B23" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23">
+        <v>0.49722452282391244</v>
+      </c>
+      <c r="D23" t="s">
+        <v>66</v>
+      </c>
+      <c r="E23" t="s">
+        <v>359</v>
+      </c>
+      <c r="F23" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>328</v>
+      </c>
+      <c r="B24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24">
+        <v>0.34410001579509508</v>
+      </c>
+      <c r="D24" t="s">
+        <v>59</v>
+      </c>
+      <c r="E24" t="s">
+        <v>360</v>
+      </c>
+      <c r="F24" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>329</v>
+      </c>
+      <c r="B25" t="s">
+        <v>56</v>
+      </c>
+      <c r="C25">
+        <v>4.3591977074863637</v>
+      </c>
+      <c r="D25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" t="s">
+        <v>361</v>
+      </c>
+      <c r="F25" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>330</v>
+      </c>
+      <c r="B26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26">
+        <v>8.4528168880065119E-2</v>
+      </c>
+      <c r="D26" t="s">
+        <v>66</v>
+      </c>
+      <c r="E26" t="s">
+        <v>362</v>
+      </c>
+      <c r="F26" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>331</v>
+      </c>
+      <c r="B27" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27">
+        <v>0.45969601064199239</v>
+      </c>
+      <c r="D27" t="s">
+        <v>59</v>
+      </c>
+      <c r="E27" t="s">
+        <v>363</v>
+      </c>
+      <c r="F27" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>332</v>
+      </c>
+      <c r="B28" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28">
+        <v>0.18387840425679697</v>
+      </c>
+      <c r="D28" t="s">
+        <v>59</v>
+      </c>
+      <c r="E28" t="s">
+        <v>364</v>
+      </c>
+      <c r="F28" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>333</v>
+      </c>
+      <c r="B29" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29">
+        <v>0.39523392547876368</v>
+      </c>
+      <c r="D29" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" t="s">
+        <v>365</v>
+      </c>
+      <c r="F29" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>334</v>
+      </c>
+      <c r="B30" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30">
+        <v>7.4583678423586861E-2</v>
+      </c>
+      <c r="D30" t="s">
+        <v>66</v>
+      </c>
+      <c r="E30" t="s">
+        <v>366</v>
+      </c>
+      <c r="F30" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>335</v>
+      </c>
+      <c r="B31" t="s">
+        <v>56</v>
+      </c>
+      <c r="C31">
+        <v>7.4583678423586861E-2</v>
+      </c>
+      <c r="D31" t="s">
+        <v>66</v>
+      </c>
+      <c r="E31" t="s">
+        <v>367</v>
+      </c>
+      <c r="F31" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>336</v>
+      </c>
+      <c r="B32" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32">
+        <v>0.28249696620183012</v>
+      </c>
+      <c r="D32" t="s">
+        <v>59</v>
+      </c>
+      <c r="E32" t="s">
+        <v>368</v>
+      </c>
+      <c r="F32" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>337</v>
+      </c>
+      <c r="B33" t="s">
+        <v>56</v>
+      </c>
+      <c r="C33">
+        <v>0.26401585626339263</v>
+      </c>
+      <c r="D33" t="s">
+        <v>59</v>
+      </c>
+      <c r="E33" t="s">
+        <v>369</v>
+      </c>
+      <c r="F33" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>391</v>
+      </c>
+      <c r="B34" t="s">
+        <v>56</v>
+      </c>
+      <c r="C34">
+        <v>1.8046437163813135E-2</v>
+      </c>
+      <c r="F34" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>392</v>
+      </c>
+      <c r="B35" t="s">
+        <v>56</v>
+      </c>
+      <c r="C35">
+        <v>0.23885083680507355</v>
+      </c>
+      <c r="F35" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>393</v>
+      </c>
+      <c r="B36" t="s">
+        <v>56</v>
+      </c>
+      <c r="C36">
+        <v>0.3656082203404642</v>
+      </c>
+      <c r="F36" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>394</v>
+      </c>
+      <c r="B37" t="s">
+        <v>56</v>
+      </c>
+      <c r="C37">
+        <v>0.2156082203404642</v>
+      </c>
+      <c r="F37" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>167</v>
+      </c>
+      <c r="B38" t="s">
+        <v>136</v>
+      </c>
+      <c r="C38">
+        <v>4.0516000000000005</v>
+      </c>
+      <c r="F38" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>338</v>
+      </c>
+      <c r="B39" t="s">
+        <v>136</v>
+      </c>
+      <c r="C39">
+        <v>22.737783592977756</v>
+      </c>
+      <c r="D39" t="s">
+        <v>137</v>
+      </c>
+      <c r="E39" t="s">
+        <v>370</v>
+      </c>
+      <c r="F39" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>339</v>
+      </c>
+      <c r="B40" t="s">
+        <v>136</v>
+      </c>
+      <c r="C40">
+        <v>11</v>
+      </c>
+      <c r="D40" t="s">
+        <v>137</v>
+      </c>
+      <c r="E40" t="s">
+        <v>371</v>
+      </c>
+      <c r="F40" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>340</v>
+      </c>
+      <c r="B41" t="s">
+        <v>136</v>
+      </c>
+      <c r="C41">
+        <v>14.810748414335091</v>
+      </c>
+      <c r="D41" t="s">
+        <v>137</v>
+      </c>
+      <c r="E41" t="s">
+        <v>372</v>
+      </c>
+      <c r="F41" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>341</v>
+      </c>
+      <c r="B42" t="s">
+        <v>136</v>
+      </c>
+      <c r="C42">
+        <v>12.24744871391589</v>
+      </c>
+      <c r="D42" t="s">
+        <v>137</v>
+      </c>
+      <c r="E42" t="s">
+        <v>373</v>
+      </c>
+      <c r="F42" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>342</v>
+      </c>
+      <c r="B43" t="s">
+        <v>136</v>
+      </c>
+      <c r="C43">
+        <v>48.189685104221404</v>
+      </c>
+      <c r="D43" t="s">
+        <v>23</v>
+      </c>
+      <c r="E43" t="s">
+        <v>374</v>
+      </c>
+      <c r="F43" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>343</v>
+      </c>
+      <c r="B44" t="s">
+        <v>136</v>
+      </c>
+      <c r="C44">
+        <v>16.699244233993625</v>
+      </c>
+      <c r="D44" t="s">
+        <v>23</v>
+      </c>
+      <c r="E44" t="s">
+        <v>375</v>
+      </c>
+      <c r="F44" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>344</v>
+      </c>
+      <c r="B45" t="s">
+        <v>136</v>
+      </c>
+      <c r="C45">
+        <v>39.746196000000005</v>
+      </c>
+      <c r="D45" t="s">
+        <v>348</v>
+      </c>
+      <c r="E45" t="s">
+        <v>376</v>
+      </c>
+      <c r="F45" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>345</v>
+      </c>
+      <c r="B46" t="s">
+        <v>136</v>
+      </c>
+      <c r="C46">
+        <v>0.44283295832701008</v>
+      </c>
+      <c r="F46" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>346</v>
+      </c>
+      <c r="B47" t="s">
+        <v>136</v>
+      </c>
+      <c r="C47">
+        <v>233372.96903833433</v>
+      </c>
+      <c r="F47" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>347</v>
+      </c>
+      <c r="B48" t="s">
+        <v>136</v>
+      </c>
+      <c r="C48">
+        <v>130688.86266146721</v>
+      </c>
+      <c r="F48" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>395</v>
+      </c>
+      <c r="B49" t="s">
+        <v>136</v>
+      </c>
+      <c r="C49">
+        <v>34.144135350668904</v>
+      </c>
+      <c r="F49" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>396</v>
+      </c>
+      <c r="B50" t="s">
+        <v>136</v>
+      </c>
+      <c r="C50">
+        <v>15.480365443172449</v>
+      </c>
+      <c r="F50" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>397</v>
+      </c>
+      <c r="B51" t="s">
+        <v>136</v>
+      </c>
+      <c r="C51">
+        <v>3.8</v>
+      </c>
+      <c r="F51" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>398</v>
+      </c>
+      <c r="B52" t="s">
+        <v>136</v>
+      </c>
+      <c r="C52">
+        <v>-1.52</v>
+      </c>
+      <c r="F52" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>399</v>
+      </c>
+      <c r="B53" t="s">
+        <v>136</v>
+      </c>
+      <c r="C53">
+        <v>5.6999999999999993</v>
+      </c>
+      <c r="F53" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>400</v>
+      </c>
+      <c r="B54" t="s">
+        <v>136</v>
+      </c>
+      <c r="C54">
+        <v>-2.2800000000000002</v>
+      </c>
+      <c r="F54" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>401</v>
+      </c>
+      <c r="B55" t="s">
+        <v>136</v>
+      </c>
+      <c r="C55">
+        <v>18.622682892532463</v>
+      </c>
+      <c r="F55" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>402</v>
+      </c>
+      <c r="B56" t="s">
+        <v>136</v>
+      </c>
+      <c r="C56">
+        <v>27.131986877647702</v>
+      </c>
+      <c r="F56" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>403</v>
+      </c>
+      <c r="B57" t="s">
+        <v>136</v>
+      </c>
+      <c r="C57">
+        <v>25.580006542099976</v>
+      </c>
+      <c r="F57" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>404</v>
+      </c>
+      <c r="B58" t="s">
+        <v>136</v>
+      </c>
+      <c r="C58">
+        <v>28.422229491222197</v>
+      </c>
+      <c r="F58" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>405</v>
+      </c>
+      <c r="B59" t="s">
+        <v>136</v>
+      </c>
+      <c r="C59">
+        <v>6.3586494759793881</v>
+      </c>
+      <c r="F59" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>406</v>
+      </c>
+      <c r="B60" t="s">
+        <v>136</v>
+      </c>
+      <c r="C60">
+        <v>12.884684205822825</v>
+      </c>
+      <c r="F60" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>407</v>
+      </c>
+      <c r="B61" t="s">
+        <v>136</v>
+      </c>
+      <c r="C61">
+        <v>2.2299999999999964</v>
+      </c>
+      <c r="F61" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>408</v>
+      </c>
+      <c r="B62" t="s">
+        <v>136</v>
+      </c>
+      <c r="C62">
+        <v>11.011406321896699</v>
+      </c>
+      <c r="F62" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>409</v>
+      </c>
+      <c r="B63" t="s">
+        <v>136</v>
+      </c>
+      <c r="C63" t="b">
+        <v>1</v>
+      </c>
+      <c r="F63" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>410</v>
+      </c>
+      <c r="B64" t="s">
+        <v>136</v>
+      </c>
+      <c r="C64">
+        <v>5.6667672012645314</v>
+      </c>
+      <c r="F64" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>411</v>
+      </c>
+      <c r="B65" t="s">
+        <v>136</v>
+      </c>
+      <c r="C65">
+        <v>19.023298859748962</v>
+      </c>
+      <c r="F65" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>412</v>
+      </c>
+      <c r="B66" t="s">
+        <v>136</v>
+      </c>
+      <c r="C66">
+        <v>5.2940237236683272</v>
+      </c>
+      <c r="F66" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>413</v>
+      </c>
+      <c r="B67" t="s">
+        <v>136</v>
+      </c>
+      <c r="C67">
+        <v>22.608098531363336</v>
+      </c>
+      <c r="F67" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>414</v>
+      </c>
+      <c r="B68" t="s">
+        <v>136</v>
+      </c>
+      <c r="C68">
+        <v>12.709922788411269</v>
+      </c>
+      <c r="F68" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>415</v>
+      </c>
+      <c r="B69" t="s">
+        <v>136</v>
+      </c>
+      <c r="C69">
+        <v>16.27392540932771</v>
+      </c>
+      <c r="F69" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>416</v>
+      </c>
+      <c r="B70" t="s">
+        <v>136</v>
+      </c>
+      <c r="C70">
+        <v>15.956485750905872</v>
+      </c>
+      <c r="F70" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>417</v>
+      </c>
+      <c r="B71" t="s">
+        <v>136</v>
+      </c>
+      <c r="C71">
+        <v>13.695854805920606</v>
+      </c>
+      <c r="F71" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>418</v>
+      </c>
+      <c r="B72" t="s">
+        <v>136</v>
+      </c>
+      <c r="C72">
+        <v>1.0954451150103324</v>
+      </c>
+      <c r="F72" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>419</v>
+      </c>
+      <c r="B73" t="s">
+        <v>136</v>
+      </c>
+      <c r="C73">
+        <v>24.094842552110709</v>
+      </c>
+      <c r="F73" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>420</v>
+      </c>
+      <c r="B74" t="s">
+        <v>136</v>
+      </c>
+      <c r="C74" t="b">
+        <v>1</v>
+      </c>
+      <c r="F74" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>421</v>
+      </c>
+      <c r="B75" t="s">
+        <v>136</v>
+      </c>
+      <c r="C75">
+        <v>156.52835771396133</v>
+      </c>
+      <c r="F75" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>422</v>
+      </c>
+      <c r="B76" t="s">
+        <v>136</v>
+      </c>
+      <c r="C76">
+        <v>44593.916314433394</v>
+      </c>
+      <c r="F76" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>423</v>
+      </c>
+      <c r="B77" t="s">
+        <v>136</v>
+      </c>
+      <c r="C77" t="b">
+        <v>1</v>
+      </c>
+      <c r="F77" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>424</v>
+      </c>
+      <c r="B78" t="s">
+        <v>136</v>
+      </c>
+      <c r="C78" t="b">
+        <v>1</v>
+      </c>
+      <c r="F78" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>425</v>
+      </c>
+      <c r="B79" t="s">
+        <v>136</v>
+      </c>
+      <c r="C79">
+        <v>13</v>
+      </c>
+      <c r="F79" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>426</v>
+      </c>
+      <c r="B80" t="s">
+        <v>136</v>
+      </c>
+      <c r="C80">
+        <v>86094.946347033809</v>
+      </c>
+      <c r="F80" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>427</v>
+      </c>
+      <c r="B81" t="s">
+        <v>136</v>
+      </c>
+      <c r="C81">
+        <v>0.16336801963384023</v>
+      </c>
+      <c r="F81" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>428</v>
+      </c>
+      <c r="B82" t="s">
+        <v>136</v>
+      </c>
+      <c r="C82">
+        <v>2.185902626124927</v>
+      </c>
+      <c r="F82" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>429</v>
+      </c>
+      <c r="B83" t="s">
+        <v>170</v>
+      </c>
+      <c r="C83" t="s">
+        <v>505</v>
+      </c>
+      <c r="F83" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>430</v>
+      </c>
+      <c r="B84" t="s">
+        <v>170</v>
+      </c>
+      <c r="C84">
+        <v>-4.0973254512723323E-2</v>
+      </c>
+      <c r="F84" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>431</v>
+      </c>
+      <c r="B85" t="s">
+        <v>170</v>
+      </c>
+      <c r="C85" t="b">
+        <v>0</v>
+      </c>
+      <c r="F85" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>432</v>
+      </c>
+      <c r="B86" t="s">
+        <v>170</v>
+      </c>
+      <c r="C86">
+        <v>0.254</v>
+      </c>
+      <c r="F86" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>433</v>
+      </c>
+      <c r="B87" t="s">
+        <v>170</v>
+      </c>
+      <c r="C87">
+        <v>0.127</v>
+      </c>
+      <c r="F87" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>434</v>
+      </c>
+      <c r="B88" t="s">
+        <v>170</v>
+      </c>
+      <c r="C88">
+        <v>14500</v>
+      </c>
+      <c r="F88" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>435</v>
+      </c>
+      <c r="B89" t="s">
+        <v>170</v>
+      </c>
+      <c r="C89" t="s">
+        <v>506</v>
+      </c>
+      <c r="F89" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>436</v>
+      </c>
+      <c r="B90" t="s">
+        <v>170</v>
+      </c>
+      <c r="C90" t="s">
+        <v>507</v>
+      </c>
+      <c r="F90" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>437</v>
+      </c>
+      <c r="B91" t="s">
+        <v>170</v>
+      </c>
+      <c r="C91" t="s">
+        <v>508</v>
+      </c>
+      <c r="F91" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>438</v>
+      </c>
+      <c r="B92" t="s">
+        <v>170</v>
+      </c>
+      <c r="C92" t="s">
+        <v>508</v>
+      </c>
+      <c r="F92" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>439</v>
+      </c>
+      <c r="B93" t="s">
+        <v>170</v>
+      </c>
+      <c r="C93" t="s">
+        <v>508</v>
+      </c>
+      <c r="F93" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>440</v>
+      </c>
+      <c r="B94" t="s">
+        <v>170</v>
+      </c>
+      <c r="C94" t="s">
+        <v>508</v>
+      </c>
+      <c r="F94" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>441</v>
+      </c>
+      <c r="B95" t="s">
+        <v>170</v>
+      </c>
+      <c r="C95" t="s">
+        <v>508</v>
+      </c>
+      <c r="F95" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>442</v>
+      </c>
+      <c r="B96" t="s">
+        <v>170</v>
+      </c>
+      <c r="C96" t="s">
+        <v>508</v>
+      </c>
+      <c r="F96" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>443</v>
+      </c>
+      <c r="B97" t="s">
+        <v>170</v>
+      </c>
+      <c r="C97" t="s">
+        <v>508</v>
+      </c>
+      <c r="F97" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>444</v>
+      </c>
+      <c r="B98" t="s">
+        <v>170</v>
+      </c>
+      <c r="C98" t="s">
+        <v>508</v>
+      </c>
+      <c r="F98" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>445</v>
+      </c>
+      <c r="B99" t="s">
+        <v>170</v>
+      </c>
+      <c r="C99" t="s">
+        <v>509</v>
+      </c>
+      <c r="F99" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>446</v>
+      </c>
+      <c r="B100" t="s">
+        <v>170</v>
+      </c>
+      <c r="C100">
+        <v>700</v>
+      </c>
+      <c r="F100" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>447</v>
+      </c>
+      <c r="B101" t="s">
+        <v>170</v>
+      </c>
+      <c r="C101">
+        <v>50</v>
+      </c>
+      <c r="F101" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>448</v>
+      </c>
+      <c r="B102" t="s">
+        <v>170</v>
+      </c>
+      <c r="C102" t="s">
+        <v>510</v>
+      </c>
+      <c r="F102" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>449</v>
+      </c>
+      <c r="B103" t="s">
+        <v>170</v>
+      </c>
+      <c r="C103" t="s">
+        <v>508</v>
+      </c>
+      <c r="F103" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>450</v>
+      </c>
+      <c r="B104" t="s">
+        <v>170</v>
+      </c>
+      <c r="C104" t="s">
+        <v>511</v>
+      </c>
+      <c r="F104" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>451</v>
+      </c>
+      <c r="B105" t="s">
+        <v>170</v>
+      </c>
+      <c r="C105" t="s">
+        <v>512</v>
+      </c>
+      <c r="F105" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>452</v>
+      </c>
+      <c r="B106" t="s">
+        <v>170</v>
+      </c>
+      <c r="C106" t="s">
+        <v>513</v>
+      </c>
+      <c r="F106" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>453</v>
+      </c>
+      <c r="B107" t="s">
+        <v>170</v>
+      </c>
+      <c r="C107" t="s">
+        <v>514</v>
+      </c>
+      <c r="F107" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>454</v>
+      </c>
+      <c r="B108" t="s">
+        <v>170</v>
+      </c>
+      <c r="C108" t="s">
+        <v>515</v>
+      </c>
+      <c r="F108" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>455</v>
+      </c>
+      <c r="B109" t="s">
+        <v>170</v>
+      </c>
+      <c r="C109" t="s">
+        <v>516</v>
+      </c>
+      <c r="F109" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>456</v>
+      </c>
+      <c r="B110" t="s">
+        <v>170</v>
+      </c>
+      <c r="C110" t="s">
+        <v>517</v>
+      </c>
+      <c r="F110" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>457</v>
+      </c>
+      <c r="B111" t="s">
+        <v>265</v>
+      </c>
+      <c r="C111">
+        <v>32.946133306980855</v>
+      </c>
+      <c r="F111" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>458</v>
+      </c>
+      <c r="B112" t="s">
+        <v>265</v>
+      </c>
+      <c r="C112">
+        <v>0</v>
+      </c>
+      <c r="F112" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>459</v>
+      </c>
+      <c r="B113" t="s">
+        <v>265</v>
+      </c>
+      <c r="C113" t="s">
+        <v>518</v>
+      </c>
+      <c r="F113" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>460</v>
+      </c>
+      <c r="B114" t="s">
+        <v>265</v>
+      </c>
+      <c r="C114">
+        <v>86.068285472894019</v>
+      </c>
+      <c r="F114" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>461</v>
+      </c>
+      <c r="B115" t="s">
+        <v>265</v>
+      </c>
+      <c r="C115">
+        <v>0</v>
+      </c>
+      <c r="F115" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>462</v>
+      </c>
+      <c r="B116" t="s">
+        <v>265</v>
+      </c>
+      <c r="C116">
+        <v>-1.8275795392708134</v>
+      </c>
+      <c r="F116" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>463</v>
+      </c>
+      <c r="B117" t="s">
+        <v>265</v>
+      </c>
+      <c r="C117">
+        <v>0</v>
+      </c>
+      <c r="F117" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>464</v>
+      </c>
+      <c r="B118" t="s">
+        <v>265</v>
+      </c>
+      <c r="C118">
+        <v>1.7526473681977495</v>
+      </c>
+      <c r="F118" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>465</v>
+      </c>
+      <c r="B119" t="s">
+        <v>265</v>
+      </c>
+      <c r="C119">
+        <v>0.15168253041257554</v>
+      </c>
+      <c r="F119" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>466</v>
+      </c>
+      <c r="B120" t="s">
+        <v>265</v>
+      </c>
+      <c r="C120">
+        <v>2.4110213483593652</v>
+      </c>
+      <c r="F120" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>467</v>
+      </c>
+      <c r="B121" t="s">
+        <v>265</v>
+      </c>
+      <c r="C121">
+        <v>2.7131092758196531</v>
+      </c>
+      <c r="F121" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>468</v>
+      </c>
+      <c r="B122" t="s">
+        <v>265</v>
+      </c>
+      <c r="C122">
+        <v>16.090147165877724</v>
+      </c>
+      <c r="F122" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>469</v>
+      </c>
+      <c r="B123" t="s">
+        <v>265</v>
+      </c>
+      <c r="C123">
+        <v>16.925292122478595</v>
+      </c>
+      <c r="F123" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>470</v>
+      </c>
+      <c r="B124" t="s">
+        <v>265</v>
+      </c>
+      <c r="C124">
+        <v>0.35178486510320511</v>
+      </c>
+      <c r="F124" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>471</v>
+      </c>
+      <c r="B125" t="s">
+        <v>265</v>
+      </c>
+      <c r="C125" t="s">
+        <v>519</v>
+      </c>
+      <c r="F125" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>472</v>
+      </c>
+      <c r="B126" t="s">
+        <v>265</v>
+      </c>
+      <c r="C126">
+        <v>233.69773788009346</v>
+      </c>
+      <c r="F126" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>473</v>
+      </c>
+      <c r="B127" t="s">
+        <v>265</v>
+      </c>
+      <c r="C127">
+        <v>0.35242563899228196</v>
+      </c>
+      <c r="F127" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>474</v>
+      </c>
+      <c r="B128" t="s">
+        <v>265</v>
+      </c>
+      <c r="C128" t="s">
+        <v>519</v>
+      </c>
+      <c r="F128" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>475</v>
+      </c>
+      <c r="B129" t="s">
+        <v>265</v>
+      </c>
+      <c r="C129">
+        <v>9.4744003772526408</v>
+      </c>
+      <c r="F129" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>476</v>
+      </c>
+      <c r="B130" t="s">
+        <v>265</v>
+      </c>
+      <c r="C130">
+        <v>341.83792795003058</v>
+      </c>
+      <c r="F130" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>477</v>
+      </c>
+      <c r="B131" t="s">
+        <v>265</v>
+      </c>
+      <c r="C131">
+        <v>34.733446426726843</v>
+      </c>
+      <c r="F131" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>478</v>
+      </c>
+      <c r="B132" t="s">
+        <v>265</v>
+      </c>
+      <c r="C132">
+        <v>0.42099254615460552</v>
+      </c>
+      <c r="F132" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>479</v>
+      </c>
+      <c r="B133" t="s">
+        <v>265</v>
+      </c>
+      <c r="C133">
+        <v>4.0516000000000005</v>
+      </c>
+      <c r="F133" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>480</v>
+      </c>
+      <c r="B134" t="s">
+        <v>265</v>
+      </c>
+      <c r="C134">
+        <v>39.746196000000005</v>
+      </c>
+      <c r="F134" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>481</v>
+      </c>
+      <c r="B135" t="s">
+        <v>265</v>
+      </c>
+      <c r="C135">
+        <v>18.230437113682747</v>
+      </c>
+      <c r="F135" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>482</v>
+      </c>
+      <c r="B136" t="s">
+        <v>265</v>
+      </c>
+      <c r="C136">
+        <v>8.0999999999999989E-2</v>
+      </c>
+      <c r="F136" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>483</v>
+      </c>
+      <c r="B137" t="s">
+        <v>265</v>
+      </c>
+      <c r="C137">
+        <v>64.749890848167752</v>
+      </c>
+      <c r="F137" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>484</v>
+      </c>
+      <c r="B138" t="s">
+        <v>504</v>
+      </c>
+      <c r="C138">
+        <v>0.3</v>
+      </c>
+      <c r="F138" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>485</v>
+      </c>
+      <c r="B139" t="s">
+        <v>504</v>
+      </c>
+      <c r="C139">
+        <v>26.360381758366742</v>
+      </c>
+      <c r="F139" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>486</v>
+      </c>
+      <c r="B140" t="s">
+        <v>504</v>
+      </c>
+      <c r="C140">
+        <v>3.6396182416332579</v>
+      </c>
+      <c r="F140" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>487</v>
+      </c>
+      <c r="B141" t="s">
+        <v>504</v>
+      </c>
+      <c r="C141">
+        <v>0.25</v>
+      </c>
+      <c r="F141" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>488</v>
+      </c>
+      <c r="B142" t="s">
+        <v>504</v>
+      </c>
+      <c r="C142">
+        <v>0.7</v>
+      </c>
+      <c r="F142" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>489</v>
+      </c>
+      <c r="B143" t="s">
+        <v>504</v>
+      </c>
+      <c r="C143">
+        <v>1</v>
+      </c>
+      <c r="F143" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>490</v>
+      </c>
+      <c r="B144" t="s">
+        <v>504</v>
+      </c>
+      <c r="C144">
+        <v>0.12048857500544551</v>
+      </c>
+      <c r="F144" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>491</v>
+      </c>
+      <c r="B145" t="s">
+        <v>504</v>
+      </c>
+      <c r="C145">
+        <v>119.66043834086311</v>
+      </c>
+      <c r="F145" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>492</v>
+      </c>
+      <c r="B146" t="s">
+        <v>504</v>
+      </c>
+      <c r="C146">
+        <v>7.4583678423586861E-2</v>
+      </c>
+      <c r="F146" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>493</v>
+      </c>
+      <c r="B147" t="s">
+        <v>504</v>
+      </c>
+      <c r="C147">
+        <v>1.07</v>
+      </c>
+      <c r="F147" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>494</v>
+      </c>
+      <c r="B148" t="s">
+        <v>504</v>
+      </c>
+      <c r="C148">
+        <v>0.3</v>
+      </c>
+      <c r="F148" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>495</v>
+      </c>
+      <c r="B149" t="s">
+        <v>504</v>
+      </c>
+      <c r="C149">
+        <v>29.162154556467332</v>
+      </c>
+      <c r="F149" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>496</v>
+      </c>
+      <c r="B150" t="s">
+        <v>504</v>
+      </c>
+      <c r="C150">
+        <v>0.83784544353266455</v>
+      </c>
+      <c r="F150" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>497</v>
+      </c>
+      <c r="B151" t="s">
+        <v>504</v>
+      </c>
+      <c r="C151">
         <v>5.2740736776131758</v>
       </c>
-      <c r="D16" s="0"/>
-      <c r="E16" s="0"/>
-      <c r="F16" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G16" s="0"/>
-      <c r="H16" s="0"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="0" t="s">
-        <v>387</v>
-      </c>
-      <c r="B17" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="0">
-        <v>-0.094788465253600393</v>
-      </c>
-      <c r="D17" s="0"/>
-      <c r="E17" s="0"/>
-      <c r="F17" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G17" s="0"/>
-      <c r="H17" s="0"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="0" t="s">
-        <v>388</v>
-      </c>
-      <c r="B18" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="0">
-        <v>0.66074594914354523</v>
-      </c>
-      <c r="D18" s="0"/>
-      <c r="E18" s="0"/>
-      <c r="F18" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G18" s="0"/>
-      <c r="H18" s="0"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="0" t="s">
-        <v>389</v>
-      </c>
-      <c r="B19" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="0">
-        <v>0.60899778104422941</v>
-      </c>
-      <c r="D19" s="0"/>
-      <c r="E19" s="0"/>
-      <c r="F19" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G19" s="0"/>
-      <c r="H19" s="0"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="0" t="s">
-        <v>390</v>
-      </c>
-      <c r="B20" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="0">
-        <v>1.5753270213496304</v>
-      </c>
-      <c r="D20" s="0"/>
-      <c r="E20" s="0"/>
-      <c r="F20" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G20" s="0"/>
-      <c r="H20" s="0"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="0" t="s">
-        <v>391</v>
-      </c>
-      <c r="B21" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="0">
-        <v>0.66074594914354523</v>
-      </c>
-      <c r="D21" s="0"/>
-      <c r="E21" s="0"/>
-      <c r="F21" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G21" s="0"/>
-      <c r="H21" s="0"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="0" t="s">
-        <v>392</v>
-      </c>
-      <c r="B22" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="0">
+      <c r="F151" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>498</v>
+      </c>
+      <c r="B152" t="s">
+        <v>504</v>
+      </c>
+      <c r="C152">
+        <v>0.3656082203404642</v>
+      </c>
+      <c r="F152" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>499</v>
+      </c>
+      <c r="B153" t="s">
+        <v>504</v>
+      </c>
+      <c r="C153">
+        <v>0.15</v>
+      </c>
+      <c r="F153" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>500</v>
+      </c>
+      <c r="B154" t="s">
+        <v>504</v>
+      </c>
+      <c r="C154">
+        <v>-0.79111105164197637</v>
+      </c>
+      <c r="F154" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>501</v>
+      </c>
+      <c r="B155" t="s">
+        <v>504</v>
+      </c>
+      <c r="C155">
         <v>0.12602616170797043</v>
       </c>
-      <c r="D22" s="0"/>
-      <c r="E22" s="0"/>
-      <c r="F22" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G22" s="0"/>
-      <c r="H22" s="0"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="0" t="s">
-        <v>327</v>
-      </c>
-      <c r="B23" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C23" s="0">
-        <v>0.49722452282391244</v>
-      </c>
-      <c r="D23" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="E23" s="0" t="s">
-        <v>359</v>
-      </c>
-      <c r="F23" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G23" s="0"/>
-      <c r="H23" s="0"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="0" t="s">
-        <v>328</v>
-      </c>
-      <c r="B24" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C24" s="0">
-        <v>0.34410001579509508</v>
-      </c>
-      <c r="D24" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="E24" s="0" t="s">
-        <v>360</v>
-      </c>
-      <c r="F24" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G24" s="0"/>
-      <c r="H24" s="0"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="0" t="s">
-        <v>329</v>
-      </c>
-      <c r="B25" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C25" s="0">
-        <v>4.3591977074863637</v>
-      </c>
-      <c r="D25" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="0" t="s">
-        <v>361</v>
-      </c>
-      <c r="F25" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G25" s="0"/>
-      <c r="H25" s="0"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="0" t="s">
-        <v>330</v>
-      </c>
-      <c r="B26" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C26" s="0">
-        <v>0.084528168880065119</v>
-      </c>
-      <c r="D26" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="E26" s="0" t="s">
-        <v>362</v>
-      </c>
-      <c r="F26" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G26" s="0"/>
-      <c r="H26" s="0"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="0" t="s">
-        <v>331</v>
-      </c>
-      <c r="B27" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C27" s="0">
-        <v>0.45969601064199239</v>
-      </c>
-      <c r="D27" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="E27" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="F27" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G27" s="0"/>
-      <c r="H27" s="0"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="0" t="s">
-        <v>332</v>
-      </c>
-      <c r="B28" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C28" s="0">
-        <v>0.18387840425679697</v>
-      </c>
-      <c r="D28" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="E28" s="0" t="s">
-        <v>364</v>
-      </c>
-      <c r="F28" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G28" s="0"/>
-      <c r="H28" s="0"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="0" t="s">
-        <v>333</v>
-      </c>
-      <c r="B29" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C29" s="0">
-        <v>0.39523392547876368</v>
-      </c>
-      <c r="D29" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="0" t="s">
-        <v>365</v>
-      </c>
-      <c r="F29" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G29" s="0"/>
-      <c r="H29" s="0"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="0" t="s">
-        <v>334</v>
-      </c>
-      <c r="B30" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C30" s="0">
-        <v>0.074583678423586861</v>
-      </c>
-      <c r="D30" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="E30" s="0" t="s">
-        <v>366</v>
-      </c>
-      <c r="F30" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G30" s="0"/>
-      <c r="H30" s="0"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="0" t="s">
-        <v>335</v>
-      </c>
-      <c r="B31" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C31" s="0">
-        <v>0.074583678423586861</v>
-      </c>
-      <c r="D31" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="E31" s="0" t="s">
-        <v>367</v>
-      </c>
-      <c r="F31" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G31" s="0"/>
-      <c r="H31" s="0"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="0" t="s">
-        <v>336</v>
-      </c>
-      <c r="B32" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C32" s="0">
-        <v>0.28249696620183012</v>
-      </c>
-      <c r="D32" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="E32" s="0" t="s">
-        <v>368</v>
-      </c>
-      <c r="F32" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G32" s="0"/>
-      <c r="H32" s="0"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="0" t="s">
-        <v>337</v>
-      </c>
-      <c r="B33" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C33" s="0">
-        <v>0.26401585626339263</v>
-      </c>
-      <c r="D33" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="E33" s="0" t="s">
-        <v>369</v>
-      </c>
-      <c r="F33" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G33" s="0"/>
-      <c r="H33" s="0"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="0" t="s">
-        <v>393</v>
-      </c>
-      <c r="B34" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C34" s="0">
-        <v>0.018046437163813135</v>
-      </c>
-      <c r="D34" s="0"/>
-      <c r="E34" s="0"/>
-      <c r="F34" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G34" s="0"/>
-      <c r="H34" s="0"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="0" t="s">
-        <v>394</v>
-      </c>
-      <c r="B35" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C35" s="0">
-        <v>0.23885083680507355</v>
-      </c>
-      <c r="D35" s="0"/>
-      <c r="E35" s="0"/>
-      <c r="F35" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G35" s="0"/>
-      <c r="H35" s="0"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="0" t="s">
-        <v>395</v>
-      </c>
-      <c r="B36" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C36" s="0">
-        <v>0.3656082203404642</v>
-      </c>
-      <c r="D36" s="0"/>
-      <c r="E36" s="0"/>
-      <c r="F36" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G36" s="0"/>
-      <c r="H36" s="0"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="0" t="s">
-        <v>396</v>
-      </c>
-      <c r="B37" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C37" s="0">
-        <v>0.2156082203404642</v>
-      </c>
-      <c r="D37" s="0"/>
-      <c r="E37" s="0"/>
-      <c r="F37" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G37" s="0"/>
-      <c r="H37" s="0"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="0" t="s">
-        <v>167</v>
-      </c>
-      <c r="B38" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C38" s="0">
-        <v>4.0516000000000005</v>
-      </c>
-      <c r="D38" s="0"/>
-      <c r="E38" s="0"/>
-      <c r="F38" s="0" t="s">
-        <v>379</v>
-      </c>
-      <c r="G38" s="0"/>
-      <c r="H38" s="0"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="0" t="s">
-        <v>338</v>
-      </c>
-      <c r="B39" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C39" s="0">
-        <v>22.737783592977756</v>
-      </c>
-      <c r="D39" s="0" t="s">
-        <v>137</v>
-      </c>
-      <c r="E39" s="0" t="s">
-        <v>370</v>
-      </c>
-      <c r="F39" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G39" s="0"/>
-      <c r="H39" s="0"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="0" t="s">
-        <v>339</v>
-      </c>
-      <c r="B40" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C40" s="0">
-        <v>11</v>
-      </c>
-      <c r="D40" s="0" t="s">
-        <v>137</v>
-      </c>
-      <c r="E40" s="0" t="s">
-        <v>371</v>
-      </c>
-      <c r="F40" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G40" s="0"/>
-      <c r="H40" s="0"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="0" t="s">
-        <v>340</v>
-      </c>
-      <c r="B41" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C41" s="0">
-        <v>14.810748414335091</v>
-      </c>
-      <c r="D41" s="0" t="s">
-        <v>137</v>
-      </c>
-      <c r="E41" s="0" t="s">
-        <v>372</v>
-      </c>
-      <c r="F41" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G41" s="0"/>
-      <c r="H41" s="0"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="0" t="s">
-        <v>341</v>
-      </c>
-      <c r="B42" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C42" s="0">
-        <v>12.24744871391589</v>
-      </c>
-      <c r="D42" s="0" t="s">
-        <v>137</v>
-      </c>
-      <c r="E42" s="0" t="s">
-        <v>373</v>
-      </c>
-      <c r="F42" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G42" s="0"/>
-      <c r="H42" s="0"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="0" t="s">
-        <v>342</v>
-      </c>
-      <c r="B43" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C43" s="0">
-        <v>48.189685104221404</v>
-      </c>
-      <c r="D43" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="E43" s="0" t="s">
-        <v>374</v>
-      </c>
-      <c r="F43" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G43" s="0"/>
-      <c r="H43" s="0"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="0" t="s">
-        <v>343</v>
-      </c>
-      <c r="B44" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C44" s="0">
-        <v>16.699244233993625</v>
-      </c>
-      <c r="D44" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="E44" s="0" t="s">
-        <v>375</v>
-      </c>
-      <c r="F44" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G44" s="0"/>
-      <c r="H44" s="0"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="0" t="s">
-        <v>344</v>
-      </c>
-      <c r="B45" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C45" s="0">
-        <v>39.746196000000005</v>
-      </c>
-      <c r="D45" s="0" t="s">
-        <v>348</v>
-      </c>
-      <c r="E45" s="0" t="s">
-        <v>376</v>
-      </c>
-      <c r="F45" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G45" s="0"/>
-      <c r="H45" s="0"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="0" t="s">
-        <v>345</v>
-      </c>
-      <c r="B46" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C46" s="0">
-        <v>0.44283295832701008</v>
-      </c>
-      <c r="D46" s="0"/>
-      <c r="E46" s="0"/>
-      <c r="F46" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G46" s="0"/>
-      <c r="H46" s="0"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="0" t="s">
-        <v>346</v>
-      </c>
-      <c r="B47" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C47" s="0">
-        <v>233372.96903833433</v>
-      </c>
-      <c r="D47" s="0"/>
-      <c r="E47" s="0"/>
-      <c r="F47" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G47" s="0"/>
-      <c r="H47" s="0"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="0" t="s">
-        <v>347</v>
-      </c>
-      <c r="B48" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C48" s="0">
-        <v>130688.86266146721</v>
-      </c>
-      <c r="D48" s="0"/>
-      <c r="E48" s="0"/>
-      <c r="F48" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G48" s="0"/>
-      <c r="H48" s="0"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="0" t="s">
-        <v>397</v>
-      </c>
-      <c r="B49" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C49" s="0">
-        <v>34.144135350668904</v>
-      </c>
-      <c r="D49" s="0"/>
-      <c r="E49" s="0"/>
-      <c r="F49" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G49" s="0"/>
-      <c r="H49" s="0"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="0" t="s">
-        <v>398</v>
-      </c>
-      <c r="B50" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C50" s="0">
-        <v>15.480365443172449</v>
-      </c>
-      <c r="D50" s="0"/>
-      <c r="E50" s="0"/>
-      <c r="F50" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G50" s="0"/>
-      <c r="H50" s="0"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="0" t="s">
-        <v>399</v>
-      </c>
-      <c r="B51" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C51" s="0">
-        <v>3.7999999999999998</v>
-      </c>
-      <c r="D51" s="0"/>
-      <c r="E51" s="0"/>
-      <c r="F51" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G51" s="0"/>
-      <c r="H51" s="0"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="0" t="s">
-        <v>400</v>
-      </c>
-      <c r="B52" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C52" s="0">
-        <v>-1.52</v>
-      </c>
-      <c r="D52" s="0"/>
-      <c r="E52" s="0"/>
-      <c r="F52" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G52" s="0"/>
-      <c r="H52" s="0"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="0" t="s">
-        <v>401</v>
-      </c>
-      <c r="B53" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C53" s="0">
-        <v>5.6999999999999993</v>
-      </c>
-      <c r="D53" s="0"/>
-      <c r="E53" s="0"/>
-      <c r="F53" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G53" s="0"/>
-      <c r="H53" s="0"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="0" t="s">
-        <v>402</v>
-      </c>
-      <c r="B54" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C54" s="0">
-        <v>-2.2800000000000002</v>
-      </c>
-      <c r="D54" s="0"/>
-      <c r="E54" s="0"/>
-      <c r="F54" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G54" s="0"/>
-      <c r="H54" s="0"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="0" t="s">
-        <v>403</v>
-      </c>
-      <c r="B55" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C55" s="0">
-        <v>18.622682892532463</v>
-      </c>
-      <c r="D55" s="0"/>
-      <c r="E55" s="0"/>
-      <c r="F55" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G55" s="0"/>
-      <c r="H55" s="0"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="0" t="s">
-        <v>404</v>
-      </c>
-      <c r="B56" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C56" s="0">
-        <v>27.131986877647702</v>
-      </c>
-      <c r="D56" s="0"/>
-      <c r="E56" s="0"/>
-      <c r="F56" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G56" s="0"/>
-      <c r="H56" s="0"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="0" t="s">
-        <v>405</v>
-      </c>
-      <c r="B57" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C57" s="0">
-        <v>25.580006542099976</v>
-      </c>
-      <c r="D57" s="0"/>
-      <c r="E57" s="0"/>
-      <c r="F57" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G57" s="0"/>
-      <c r="H57" s="0"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="0" t="s">
-        <v>406</v>
-      </c>
-      <c r="B58" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C58" s="0">
-        <v>28.422229491222197</v>
-      </c>
-      <c r="D58" s="0"/>
-      <c r="E58" s="0"/>
-      <c r="F58" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G58" s="0"/>
-      <c r="H58" s="0"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="0" t="s">
-        <v>407</v>
-      </c>
-      <c r="B59" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C59" s="0">
-        <v>6.3586494759793881</v>
-      </c>
-      <c r="D59" s="0"/>
-      <c r="E59" s="0"/>
-      <c r="F59" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G59" s="0"/>
-      <c r="H59" s="0"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="0" t="s">
-        <v>408</v>
-      </c>
-      <c r="B60" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C60" s="0">
-        <v>12.884684205822825</v>
-      </c>
-      <c r="D60" s="0"/>
-      <c r="E60" s="0"/>
-      <c r="F60" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G60" s="0"/>
-      <c r="H60" s="0"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="0" t="s">
-        <v>409</v>
-      </c>
-      <c r="B61" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C61" s="0">
-        <v>2.2299999999999964</v>
-      </c>
-      <c r="D61" s="0"/>
-      <c r="E61" s="0"/>
-      <c r="F61" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G61" s="0"/>
-      <c r="H61" s="0"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="0" t="s">
-        <v>410</v>
-      </c>
-      <c r="B62" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C62" s="0">
-        <v>11.011406321896699</v>
-      </c>
-      <c r="D62" s="0"/>
-      <c r="E62" s="0"/>
-      <c r="F62" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G62" s="0"/>
-      <c r="H62" s="0"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="0" t="s">
-        <v>411</v>
-      </c>
-      <c r="B63" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C63" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="D63" s="0"/>
-      <c r="E63" s="0"/>
-      <c r="F63" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G63" s="0"/>
-      <c r="H63" s="0"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="0" t="s">
-        <v>412</v>
-      </c>
-      <c r="B64" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C64" s="0">
-        <v>5.6667672012645314</v>
-      </c>
-      <c r="D64" s="0"/>
-      <c r="E64" s="0"/>
-      <c r="F64" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G64" s="0"/>
-      <c r="H64" s="0"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="0" t="s">
-        <v>413</v>
-      </c>
-      <c r="B65" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C65" s="0">
-        <v>19.023298859748962</v>
-      </c>
-      <c r="D65" s="0"/>
-      <c r="E65" s="0"/>
-      <c r="F65" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G65" s="0"/>
-      <c r="H65" s="0"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="0" t="s">
-        <v>414</v>
-      </c>
-      <c r="B66" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C66" s="0">
-        <v>5.2940237236683272</v>
-      </c>
-      <c r="D66" s="0"/>
-      <c r="E66" s="0"/>
-      <c r="F66" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G66" s="0"/>
-      <c r="H66" s="0"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="0" t="s">
-        <v>415</v>
-      </c>
-      <c r="B67" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C67" s="0">
-        <v>22.608098531363336</v>
-      </c>
-      <c r="D67" s="0"/>
-      <c r="E67" s="0"/>
-      <c r="F67" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G67" s="0"/>
-      <c r="H67" s="0"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="0" t="s">
-        <v>416</v>
-      </c>
-      <c r="B68" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C68" s="0">
-        <v>12.709922788411269</v>
-      </c>
-      <c r="D68" s="0"/>
-      <c r="E68" s="0"/>
-      <c r="F68" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G68" s="0"/>
-      <c r="H68" s="0"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="0" t="s">
-        <v>417</v>
-      </c>
-      <c r="B69" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C69" s="0">
-        <v>16.27392540932771</v>
-      </c>
-      <c r="D69" s="0"/>
-      <c r="E69" s="0"/>
-      <c r="F69" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G69" s="0"/>
-      <c r="H69" s="0"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="0" t="s">
-        <v>418</v>
-      </c>
-      <c r="B70" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C70" s="0">
-        <v>15.956485750905872</v>
-      </c>
-      <c r="D70" s="0"/>
-      <c r="E70" s="0"/>
-      <c r="F70" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G70" s="0"/>
-      <c r="H70" s="0"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="0" t="s">
-        <v>419</v>
-      </c>
-      <c r="B71" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C71" s="0">
-        <v>13.695854805920606</v>
-      </c>
-      <c r="D71" s="0"/>
-      <c r="E71" s="0"/>
-      <c r="F71" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G71" s="0"/>
-      <c r="H71" s="0"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="0" t="s">
-        <v>420</v>
-      </c>
-      <c r="B72" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C72" s="0">
-        <v>1.0954451150103324</v>
-      </c>
-      <c r="D72" s="0"/>
-      <c r="E72" s="0"/>
-      <c r="F72" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G72" s="0"/>
-      <c r="H72" s="0"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="0" t="s">
-        <v>421</v>
-      </c>
-      <c r="B73" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C73" s="0">
-        <v>24.094842552110709</v>
-      </c>
-      <c r="D73" s="0"/>
-      <c r="E73" s="0"/>
-      <c r="F73" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G73" s="0"/>
-      <c r="H73" s="0"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="0" t="s">
-        <v>422</v>
-      </c>
-      <c r="B74" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C74" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="D74" s="0"/>
-      <c r="E74" s="0"/>
-      <c r="F74" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G74" s="0"/>
-      <c r="H74" s="0"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="0" t="s">
-        <v>423</v>
-      </c>
-      <c r="B75" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C75" s="0">
-        <v>156.52835771396133</v>
-      </c>
-      <c r="D75" s="0"/>
-      <c r="E75" s="0"/>
-      <c r="F75" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G75" s="0"/>
-      <c r="H75" s="0"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="0" t="s">
-        <v>424</v>
-      </c>
-      <c r="B76" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C76" s="0">
-        <v>44593.916314433394</v>
-      </c>
-      <c r="D76" s="0"/>
-      <c r="E76" s="0"/>
-      <c r="F76" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G76" s="0"/>
-      <c r="H76" s="0"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="0" t="s">
-        <v>425</v>
-      </c>
-      <c r="B77" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C77" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="D77" s="0"/>
-      <c r="E77" s="0"/>
-      <c r="F77" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G77" s="0"/>
-      <c r="H77" s="0"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="0" t="s">
-        <v>426</v>
-      </c>
-      <c r="B78" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C78" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="D78" s="0"/>
-      <c r="E78" s="0"/>
-      <c r="F78" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G78" s="0"/>
-      <c r="H78" s="0"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="0" t="s">
-        <v>427</v>
-      </c>
-      <c r="B79" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C79" s="0">
-        <v>13</v>
-      </c>
-      <c r="D79" s="0"/>
-      <c r="E79" s="0"/>
-      <c r="F79" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G79" s="0"/>
-      <c r="H79" s="0"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="0" t="s">
-        <v>428</v>
-      </c>
-      <c r="B80" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C80" s="0">
-        <v>86094.946347033809</v>
-      </c>
-      <c r="D80" s="0"/>
-      <c r="E80" s="0"/>
-      <c r="F80" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G80" s="0"/>
-      <c r="H80" s="0"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="0" t="s">
-        <v>429</v>
-      </c>
-      <c r="B81" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C81" s="0">
-        <v>0.16336801963384023</v>
-      </c>
-      <c r="D81" s="0"/>
-      <c r="E81" s="0"/>
-      <c r="F81" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G81" s="0"/>
-      <c r="H81" s="0"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="0" t="s">
-        <v>430</v>
-      </c>
-      <c r="B82" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C82" s="0">
-        <v>2.185902626124927</v>
-      </c>
-      <c r="D82" s="0"/>
-      <c r="E82" s="0"/>
-      <c r="F82" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G82" s="0"/>
-      <c r="H82" s="0"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="0" t="s">
-        <v>431</v>
-      </c>
-      <c r="B83" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C83" s="0" t="s">
-        <v>507</v>
-      </c>
-      <c r="D83" s="0"/>
-      <c r="E83" s="0"/>
-      <c r="F83" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G83" s="0"/>
-      <c r="H83" s="0"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="0" t="s">
-        <v>432</v>
-      </c>
-      <c r="B84" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C84" s="0">
-        <v>-0.040973254512723323</v>
-      </c>
-      <c r="D84" s="0"/>
-      <c r="E84" s="0"/>
-      <c r="F84" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G84" s="0"/>
-      <c r="H84" s="0"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="0" t="s">
-        <v>433</v>
-      </c>
-      <c r="B85" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C85" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="D85" s="0"/>
-      <c r="E85" s="0"/>
-      <c r="F85" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G85" s="0"/>
-      <c r="H85" s="0"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="0" t="s">
-        <v>434</v>
-      </c>
-      <c r="B86" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C86" s="0">
-        <v>0.254</v>
-      </c>
-      <c r="D86" s="0"/>
-      <c r="E86" s="0"/>
-      <c r="F86" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G86" s="0"/>
-      <c r="H86" s="0"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="0" t="s">
-        <v>435</v>
-      </c>
-      <c r="B87" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C87" s="0">
-        <v>0.127</v>
-      </c>
-      <c r="D87" s="0"/>
-      <c r="E87" s="0"/>
-      <c r="F87" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G87" s="0"/>
-      <c r="H87" s="0"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="0" t="s">
-        <v>436</v>
-      </c>
-      <c r="B88" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C88" s="0">
-        <v>14500</v>
-      </c>
-      <c r="D88" s="0"/>
-      <c r="E88" s="0"/>
-      <c r="F88" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G88" s="0"/>
-      <c r="H88" s="0"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="0" t="s">
-        <v>437</v>
-      </c>
-      <c r="B89" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C89" s="0" t="s">
-        <v>508</v>
-      </c>
-      <c r="D89" s="0"/>
-      <c r="E89" s="0"/>
-      <c r="F89" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G89" s="0"/>
-      <c r="H89" s="0"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="0" t="s">
-        <v>438</v>
-      </c>
-      <c r="B90" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C90" s="0" t="s">
-        <v>509</v>
-      </c>
-      <c r="D90" s="0"/>
-      <c r="E90" s="0"/>
-      <c r="F90" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G90" s="0"/>
-      <c r="H90" s="0"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="0" t="s">
-        <v>439</v>
-      </c>
-      <c r="B91" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C91" s="0" t="s">
-        <v>510</v>
-      </c>
-      <c r="D91" s="0"/>
-      <c r="E91" s="0"/>
-      <c r="F91" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G91" s="0"/>
-      <c r="H91" s="0"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="0" t="s">
-        <v>440</v>
-      </c>
-      <c r="B92" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C92" s="0" t="s">
-        <v>510</v>
-      </c>
-      <c r="D92" s="0"/>
-      <c r="E92" s="0"/>
-      <c r="F92" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G92" s="0"/>
-      <c r="H92" s="0"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="0" t="s">
-        <v>441</v>
-      </c>
-      <c r="B93" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C93" s="0" t="s">
-        <v>510</v>
-      </c>
-      <c r="D93" s="0"/>
-      <c r="E93" s="0"/>
-      <c r="F93" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G93" s="0"/>
-      <c r="H93" s="0"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="0" t="s">
-        <v>442</v>
-      </c>
-      <c r="B94" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C94" s="0" t="s">
-        <v>510</v>
-      </c>
-      <c r="D94" s="0"/>
-      <c r="E94" s="0"/>
-      <c r="F94" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G94" s="0"/>
-      <c r="H94" s="0"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="0" t="s">
-        <v>443</v>
-      </c>
-      <c r="B95" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C95" s="0" t="s">
-        <v>510</v>
-      </c>
-      <c r="D95" s="0"/>
-      <c r="E95" s="0"/>
-      <c r="F95" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G95" s="0"/>
-      <c r="H95" s="0"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="0" t="s">
-        <v>444</v>
-      </c>
-      <c r="B96" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C96" s="0" t="s">
-        <v>510</v>
-      </c>
-      <c r="D96" s="0"/>
-      <c r="E96" s="0"/>
-      <c r="F96" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G96" s="0"/>
-      <c r="H96" s="0"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="0" t="s">
-        <v>445</v>
-      </c>
-      <c r="B97" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C97" s="0" t="s">
-        <v>510</v>
-      </c>
-      <c r="D97" s="0"/>
-      <c r="E97" s="0"/>
-      <c r="F97" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G97" s="0"/>
-      <c r="H97" s="0"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="0" t="s">
-        <v>446</v>
-      </c>
-      <c r="B98" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C98" s="0" t="s">
-        <v>510</v>
-      </c>
-      <c r="D98" s="0"/>
-      <c r="E98" s="0"/>
-      <c r="F98" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G98" s="0"/>
-      <c r="H98" s="0"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="0" t="s">
-        <v>447</v>
-      </c>
-      <c r="B99" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C99" s="0" t="s">
-        <v>511</v>
-      </c>
-      <c r="D99" s="0"/>
-      <c r="E99" s="0"/>
-      <c r="F99" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G99" s="0"/>
-      <c r="H99" s="0"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="0" t="s">
-        <v>448</v>
-      </c>
-      <c r="B100" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C100" s="0">
-        <v>700</v>
-      </c>
-      <c r="D100" s="0"/>
-      <c r="E100" s="0"/>
-      <c r="F100" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G100" s="0"/>
-      <c r="H100" s="0"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="0" t="s">
-        <v>449</v>
-      </c>
-      <c r="B101" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C101" s="0">
-        <v>50</v>
-      </c>
-      <c r="D101" s="0"/>
-      <c r="E101" s="0"/>
-      <c r="F101" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G101" s="0"/>
-      <c r="H101" s="0"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="0" t="s">
-        <v>450</v>
-      </c>
-      <c r="B102" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C102" s="0" t="s">
-        <v>512</v>
-      </c>
-      <c r="D102" s="0"/>
-      <c r="E102" s="0"/>
-      <c r="F102" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G102" s="0"/>
-      <c r="H102" s="0"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="0" t="s">
-        <v>451</v>
-      </c>
-      <c r="B103" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C103" s="0" t="s">
-        <v>510</v>
-      </c>
-      <c r="D103" s="0"/>
-      <c r="E103" s="0"/>
-      <c r="F103" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G103" s="0"/>
-      <c r="H103" s="0"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="0" t="s">
-        <v>452</v>
-      </c>
-      <c r="B104" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C104" s="0" t="s">
-        <v>513</v>
-      </c>
-      <c r="D104" s="0"/>
-      <c r="E104" s="0"/>
-      <c r="F104" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G104" s="0"/>
-      <c r="H104" s="0"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="0" t="s">
-        <v>453</v>
-      </c>
-      <c r="B105" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C105" s="0" t="s">
-        <v>514</v>
-      </c>
-      <c r="D105" s="0"/>
-      <c r="E105" s="0"/>
-      <c r="F105" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G105" s="0"/>
-      <c r="H105" s="0"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="0" t="s">
-        <v>454</v>
-      </c>
-      <c r="B106" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C106" s="0" t="s">
-        <v>515</v>
-      </c>
-      <c r="D106" s="0"/>
-      <c r="E106" s="0"/>
-      <c r="F106" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G106" s="0"/>
-      <c r="H106" s="0"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="0" t="s">
-        <v>455</v>
-      </c>
-      <c r="B107" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C107" s="0" t="s">
-        <v>516</v>
-      </c>
-      <c r="D107" s="0"/>
-      <c r="E107" s="0"/>
-      <c r="F107" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G107" s="0"/>
-      <c r="H107" s="0"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="0" t="s">
-        <v>456</v>
-      </c>
-      <c r="B108" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C108" s="0" t="s">
-        <v>517</v>
-      </c>
-      <c r="D108" s="0"/>
-      <c r="E108" s="0"/>
-      <c r="F108" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G108" s="0"/>
-      <c r="H108" s="0"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="0" t="s">
-        <v>457</v>
-      </c>
-      <c r="B109" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C109" s="0" t="s">
-        <v>518</v>
-      </c>
-      <c r="D109" s="0"/>
-      <c r="E109" s="0"/>
-      <c r="F109" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G109" s="0"/>
-      <c r="H109" s="0"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="0" t="s">
-        <v>458</v>
-      </c>
-      <c r="B110" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C110" s="0" t="s">
-        <v>519</v>
-      </c>
-      <c r="D110" s="0"/>
-      <c r="E110" s="0"/>
-      <c r="F110" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G110" s="0"/>
-      <c r="H110" s="0"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="0" t="s">
-        <v>459</v>
-      </c>
-      <c r="B111" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C111" s="0">
-        <v>32.946133306980855</v>
-      </c>
-      <c r="D111" s="0"/>
-      <c r="E111" s="0"/>
-      <c r="F111" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G111" s="0"/>
-      <c r="H111" s="0"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="0" t="s">
-        <v>460</v>
-      </c>
-      <c r="B112" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C112" s="0">
-        <v>0</v>
-      </c>
-      <c r="D112" s="0"/>
-      <c r="E112" s="0"/>
-      <c r="F112" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G112" s="0"/>
-      <c r="H112" s="0"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="0" t="s">
-        <v>461</v>
-      </c>
-      <c r="B113" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C113" s="0" t="s">
-        <v>520</v>
-      </c>
-      <c r="D113" s="0"/>
-      <c r="E113" s="0"/>
-      <c r="F113" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G113" s="0"/>
-      <c r="H113" s="0"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="0" t="s">
-        <v>462</v>
-      </c>
-      <c r="B114" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C114" s="0">
-        <v>86.068285472894019</v>
-      </c>
-      <c r="D114" s="0"/>
-      <c r="E114" s="0"/>
-      <c r="F114" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G114" s="0"/>
-      <c r="H114" s="0"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="0" t="s">
-        <v>463</v>
-      </c>
-      <c r="B115" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C115" s="0">
-        <v>0</v>
-      </c>
-      <c r="D115" s="0"/>
-      <c r="E115" s="0"/>
-      <c r="F115" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G115" s="0"/>
-      <c r="H115" s="0"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="0" t="s">
-        <v>464</v>
-      </c>
-      <c r="B116" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C116" s="0">
-        <v>-1.8275795392708134</v>
-      </c>
-      <c r="D116" s="0"/>
-      <c r="E116" s="0"/>
-      <c r="F116" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G116" s="0"/>
-      <c r="H116" s="0"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="0" t="s">
-        <v>465</v>
-      </c>
-      <c r="B117" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C117" s="0">
-        <v>0</v>
-      </c>
-      <c r="D117" s="0"/>
-      <c r="E117" s="0"/>
-      <c r="F117" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G117" s="0"/>
-      <c r="H117" s="0"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="0" t="s">
-        <v>466</v>
-      </c>
-      <c r="B118" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C118" s="0">
-        <v>1.7526473681977495</v>
-      </c>
-      <c r="D118" s="0"/>
-      <c r="E118" s="0"/>
-      <c r="F118" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G118" s="0"/>
-      <c r="H118" s="0"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="0" t="s">
-        <v>467</v>
-      </c>
-      <c r="B119" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C119" s="0">
-        <v>0.15168253041257554</v>
-      </c>
-      <c r="D119" s="0"/>
-      <c r="E119" s="0"/>
-      <c r="F119" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G119" s="0"/>
-      <c r="H119" s="0"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="0" t="s">
-        <v>468</v>
-      </c>
-      <c r="B120" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C120" s="0">
-        <v>2.4110213483593652</v>
-      </c>
-      <c r="D120" s="0"/>
-      <c r="E120" s="0"/>
-      <c r="F120" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G120" s="0"/>
-      <c r="H120" s="0"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="0" t="s">
-        <v>469</v>
-      </c>
-      <c r="B121" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C121" s="0">
-        <v>2.7131092758196531</v>
-      </c>
-      <c r="D121" s="0"/>
-      <c r="E121" s="0"/>
-      <c r="F121" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G121" s="0"/>
-      <c r="H121" s="0"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="0" t="s">
-        <v>470</v>
-      </c>
-      <c r="B122" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C122" s="0">
-        <v>16.090147165877724</v>
-      </c>
-      <c r="D122" s="0"/>
-      <c r="E122" s="0"/>
-      <c r="F122" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G122" s="0"/>
-      <c r="H122" s="0"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="0" t="s">
-        <v>471</v>
-      </c>
-      <c r="B123" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C123" s="0">
-        <v>16.925292122478595</v>
-      </c>
-      <c r="D123" s="0"/>
-      <c r="E123" s="0"/>
-      <c r="F123" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G123" s="0"/>
-      <c r="H123" s="0"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="0" t="s">
-        <v>472</v>
-      </c>
-      <c r="B124" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C124" s="0">
-        <v>0.35178486510320511</v>
-      </c>
-      <c r="D124" s="0"/>
-      <c r="E124" s="0"/>
-      <c r="F124" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G124" s="0"/>
-      <c r="H124" s="0"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="0" t="s">
-        <v>473</v>
-      </c>
-      <c r="B125" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C125" s="0" t="s">
-        <v>521</v>
-      </c>
-      <c r="D125" s="0"/>
-      <c r="E125" s="0"/>
-      <c r="F125" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G125" s="0"/>
-      <c r="H125" s="0"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="0" t="s">
-        <v>474</v>
-      </c>
-      <c r="B126" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C126" s="0">
-        <v>233.69773788009346</v>
-      </c>
-      <c r="D126" s="0"/>
-      <c r="E126" s="0"/>
-      <c r="F126" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G126" s="0"/>
-      <c r="H126" s="0"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="0" t="s">
-        <v>475</v>
-      </c>
-      <c r="B127" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C127" s="0">
-        <v>0.35242563899228196</v>
-      </c>
-      <c r="D127" s="0"/>
-      <c r="E127" s="0"/>
-      <c r="F127" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G127" s="0"/>
-      <c r="H127" s="0"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="0" t="s">
-        <v>476</v>
-      </c>
-      <c r="B128" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C128" s="0" t="s">
-        <v>521</v>
-      </c>
-      <c r="D128" s="0"/>
-      <c r="E128" s="0"/>
-      <c r="F128" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G128" s="0"/>
-      <c r="H128" s="0"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="0" t="s">
-        <v>477</v>
-      </c>
-      <c r="B129" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C129" s="0">
-        <v>9.4744003772526408</v>
-      </c>
-      <c r="D129" s="0"/>
-      <c r="E129" s="0"/>
-      <c r="F129" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G129" s="0"/>
-      <c r="H129" s="0"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="0" t="s">
-        <v>478</v>
-      </c>
-      <c r="B130" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C130" s="0">
-        <v>341.83792795003058</v>
-      </c>
-      <c r="D130" s="0"/>
-      <c r="E130" s="0"/>
-      <c r="F130" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G130" s="0"/>
-      <c r="H130" s="0"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="0" t="s">
-        <v>479</v>
-      </c>
-      <c r="B131" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C131" s="0">
-        <v>34.733446426726843</v>
-      </c>
-      <c r="D131" s="0"/>
-      <c r="E131" s="0"/>
-      <c r="F131" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G131" s="0"/>
-      <c r="H131" s="0"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="0" t="s">
-        <v>480</v>
-      </c>
-      <c r="B132" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C132" s="0">
-        <v>0.42099254615460552</v>
-      </c>
-      <c r="D132" s="0"/>
-      <c r="E132" s="0"/>
-      <c r="F132" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G132" s="0"/>
-      <c r="H132" s="0"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="0" t="s">
-        <v>481</v>
-      </c>
-      <c r="B133" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C133" s="0">
-        <v>4.0516000000000005</v>
-      </c>
-      <c r="D133" s="0"/>
-      <c r="E133" s="0"/>
-      <c r="F133" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G133" s="0"/>
-      <c r="H133" s="0"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="0" t="s">
-        <v>482</v>
-      </c>
-      <c r="B134" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C134" s="0">
-        <v>39.746196000000005</v>
-      </c>
-      <c r="D134" s="0"/>
-      <c r="E134" s="0"/>
-      <c r="F134" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G134" s="0"/>
-      <c r="H134" s="0"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="0" t="s">
-        <v>483</v>
-      </c>
-      <c r="B135" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C135" s="0">
-        <v>18.230437113682747</v>
-      </c>
-      <c r="D135" s="0"/>
-      <c r="E135" s="0"/>
-      <c r="F135" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G135" s="0"/>
-      <c r="H135" s="0"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="0" t="s">
-        <v>484</v>
-      </c>
-      <c r="B136" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C136" s="0">
-        <v>0.080999999999999989</v>
-      </c>
-      <c r="D136" s="0"/>
-      <c r="E136" s="0"/>
-      <c r="F136" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G136" s="0"/>
-      <c r="H136" s="0"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="0" t="s">
-        <v>485</v>
-      </c>
-      <c r="B137" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C137" s="0">
-        <v>64.749890848167752</v>
-      </c>
-      <c r="D137" s="0"/>
-      <c r="E137" s="0"/>
-      <c r="F137" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G137" s="0"/>
-      <c r="H137" s="0"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="0" t="s">
-        <v>486</v>
-      </c>
-      <c r="B138" s="0" t="s">
-        <v>506</v>
-      </c>
-      <c r="C138" s="0">
-        <v>0.29999999999999999</v>
-      </c>
-      <c r="D138" s="0"/>
-      <c r="E138" s="0"/>
-      <c r="F138" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G138" s="0"/>
-      <c r="H138" s="0"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="0" t="s">
-        <v>487</v>
-      </c>
-      <c r="B139" s="0" t="s">
-        <v>506</v>
-      </c>
-      <c r="C139" s="0">
-        <v>26.360381758366742</v>
-      </c>
-      <c r="D139" s="0"/>
-      <c r="E139" s="0"/>
-      <c r="F139" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G139" s="0"/>
-      <c r="H139" s="0"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="0" t="s">
-        <v>488</v>
-      </c>
-      <c r="B140" s="0" t="s">
-        <v>506</v>
-      </c>
-      <c r="C140" s="0">
-        <v>3.6396182416332579</v>
-      </c>
-      <c r="D140" s="0"/>
-      <c r="E140" s="0"/>
-      <c r="F140" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G140" s="0"/>
-      <c r="H140" s="0"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="0" t="s">
-        <v>489</v>
-      </c>
-      <c r="B141" s="0" t="s">
-        <v>506</v>
-      </c>
-      <c r="C141" s="0">
-        <v>0.25</v>
-      </c>
-      <c r="D141" s="0"/>
-      <c r="E141" s="0"/>
-      <c r="F141" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G141" s="0"/>
-      <c r="H141" s="0"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="0" t="s">
-        <v>490</v>
-      </c>
-      <c r="B142" s="0" t="s">
-        <v>506</v>
-      </c>
-      <c r="C142" s="0">
-        <v>0.69999999999999996</v>
-      </c>
-      <c r="D142" s="0"/>
-      <c r="E142" s="0"/>
-      <c r="F142" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G142" s="0"/>
-      <c r="H142" s="0"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="0" t="s">
-        <v>491</v>
-      </c>
-      <c r="B143" s="0" t="s">
-        <v>506</v>
-      </c>
-      <c r="C143" s="0">
-        <v>1</v>
-      </c>
-      <c r="D143" s="0"/>
-      <c r="E143" s="0"/>
-      <c r="F143" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G143" s="0"/>
-      <c r="H143" s="0"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="0" t="s">
-        <v>492</v>
-      </c>
-      <c r="B144" s="0" t="s">
-        <v>506</v>
-      </c>
-      <c r="C144" s="0">
-        <v>0.12048857500544551</v>
-      </c>
-      <c r="D144" s="0"/>
-      <c r="E144" s="0"/>
-      <c r="F144" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G144" s="0"/>
-      <c r="H144" s="0"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="0" t="s">
-        <v>493</v>
-      </c>
-      <c r="B145" s="0" t="s">
-        <v>506</v>
-      </c>
-      <c r="C145" s="0">
-        <v>119.66043834086311</v>
-      </c>
-      <c r="D145" s="0"/>
-      <c r="E145" s="0"/>
-      <c r="F145" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G145" s="0"/>
-      <c r="H145" s="0"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="0" t="s">
-        <v>494</v>
-      </c>
-      <c r="B146" s="0" t="s">
-        <v>506</v>
-      </c>
-      <c r="C146" s="0">
-        <v>0.074583678423586861</v>
-      </c>
-      <c r="D146" s="0"/>
-      <c r="E146" s="0"/>
-      <c r="F146" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G146" s="0"/>
-      <c r="H146" s="0"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="0" t="s">
-        <v>495</v>
-      </c>
-      <c r="B147" s="0" t="s">
-        <v>506</v>
-      </c>
-      <c r="C147" s="0">
-        <v>1.0700000000000001</v>
-      </c>
-      <c r="D147" s="0"/>
-      <c r="E147" s="0"/>
-      <c r="F147" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G147" s="0"/>
-      <c r="H147" s="0"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="0" t="s">
-        <v>496</v>
-      </c>
-      <c r="B148" s="0" t="s">
-        <v>506</v>
-      </c>
-      <c r="C148" s="0">
-        <v>0.29999999999999999</v>
-      </c>
-      <c r="D148" s="0"/>
-      <c r="E148" s="0"/>
-      <c r="F148" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G148" s="0"/>
-      <c r="H148" s="0"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="0" t="s">
-        <v>497</v>
-      </c>
-      <c r="B149" s="0" t="s">
-        <v>506</v>
-      </c>
-      <c r="C149" s="0">
-        <v>29.162154556467332</v>
-      </c>
-      <c r="D149" s="0"/>
-      <c r="E149" s="0"/>
-      <c r="F149" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G149" s="0"/>
-      <c r="H149" s="0"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="0" t="s">
-        <v>498</v>
-      </c>
-      <c r="B150" s="0" t="s">
-        <v>506</v>
-      </c>
-      <c r="C150" s="0">
-        <v>0.83784544353266455</v>
-      </c>
-      <c r="D150" s="0"/>
-      <c r="E150" s="0"/>
-      <c r="F150" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G150" s="0"/>
-      <c r="H150" s="0"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="0" t="s">
-        <v>499</v>
-      </c>
-      <c r="B151" s="0" t="s">
-        <v>506</v>
-      </c>
-      <c r="C151" s="0">
-        <v>5.2740736776131758</v>
-      </c>
-      <c r="D151" s="0"/>
-      <c r="E151" s="0"/>
-      <c r="F151" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G151" s="0"/>
-      <c r="H151" s="0"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="0" t="s">
-        <v>500</v>
-      </c>
-      <c r="B152" s="0" t="s">
-        <v>506</v>
-      </c>
-      <c r="C152" s="0">
-        <v>0.3656082203404642</v>
-      </c>
-      <c r="D152" s="0"/>
-      <c r="E152" s="0"/>
-      <c r="F152" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G152" s="0"/>
-      <c r="H152" s="0"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="0" t="s">
-        <v>501</v>
-      </c>
-      <c r="B153" s="0" t="s">
-        <v>506</v>
-      </c>
-      <c r="C153" s="0">
-        <v>0.14999999999999999</v>
-      </c>
-      <c r="D153" s="0"/>
-      <c r="E153" s="0"/>
-      <c r="F153" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G153" s="0"/>
-      <c r="H153" s="0"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="0" t="s">
+      <c r="F155" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
         <v>502</v>
       </c>
-      <c r="B154" s="0" t="s">
-        <v>506</v>
-      </c>
-      <c r="C154" s="0">
-        <v>-0.79111105164197637</v>
-      </c>
-      <c r="D154" s="0"/>
-      <c r="E154" s="0"/>
-      <c r="F154" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G154" s="0"/>
-      <c r="H154" s="0"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="0" t="s">
+      <c r="B156" t="s">
+        <v>504</v>
+      </c>
+      <c r="C156">
+        <v>5</v>
+      </c>
+      <c r="F156" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
         <v>503</v>
       </c>
-      <c r="B155" s="0" t="s">
-        <v>506</v>
-      </c>
-      <c r="C155" s="0">
-        <v>0.12602616170797043</v>
-      </c>
-      <c r="D155" s="0"/>
-      <c r="E155" s="0"/>
-      <c r="F155" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G155" s="0"/>
-      <c r="H155" s="0"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="0" t="s">
+      <c r="B157" t="s">
         <v>504</v>
       </c>
-      <c r="B156" s="0" t="s">
-        <v>506</v>
-      </c>
-      <c r="C156" s="0">
-        <v>5</v>
-      </c>
-      <c r="D156" s="0"/>
-      <c r="E156" s="0"/>
-      <c r="F156" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G156" s="0"/>
-      <c r="H156" s="0"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="0" t="s">
-        <v>505</v>
-      </c>
-      <c r="B157" s="0" t="s">
-        <v>506</v>
-      </c>
-      <c r="C157" s="0">
+      <c r="C157">
         <v>-0.18486997339978403</v>
       </c>
-      <c r="D157" s="0"/>
-      <c r="E157" s="0"/>
-      <c r="F157" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G157" s="0"/>
-      <c r="H157" s="0"/>
+      <c r="F157" t="s">
+        <v>378</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6927,16 +6357,16 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFCC8514-E0AF-4C67-BF86-8649FC702924}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFCC8514-E0AF-4C67-BF86-8649FC702924}">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32.42578125" customWidth="true"/>
-    <col min="2" max="3" width="32.42578125" style="20" customWidth="true"/>
-    <col min="4" max="4" width="13.28515625" style="20" customWidth="true"/>
+    <col min="1" max="1" width="32.44140625" customWidth="1"/>
+    <col min="2" max="3" width="32.44140625" style="20" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" style="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>274</v>
       </c>
@@ -6950,7 +6380,7 @@
         <v>303</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>276</v>
       </c>
@@ -6964,8 +6394,8 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="23" t="s">
         <v>277</v>
       </c>
       <c r="B3" s="21">
@@ -6978,7 +6408,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>278</v>
       </c>
@@ -6992,7 +6422,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>279</v>
       </c>
@@ -7006,8 +6436,8 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="23" t="s">
         <v>304</v>
       </c>
       <c r="B6" s="21">
@@ -7020,7 +6450,7 @@
         <v>-4.4999999999999998E-2</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>280</v>
       </c>
@@ -7034,7 +6464,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>281</v>
       </c>
@@ -7048,7 +6478,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>282</v>
       </c>
@@ -7062,7 +6492,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>283</v>
       </c>
@@ -7076,7 +6506,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>284</v>
       </c>
@@ -7090,7 +6520,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>285</v>
       </c>
@@ -7104,7 +6534,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>286</v>
       </c>
@@ -7118,7 +6548,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>287</v>
       </c>
@@ -7132,8 +6562,8 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="23" t="s">
         <v>288</v>
       </c>
       <c r="B15" s="21">
@@ -7146,7 +6576,7 @@
         <v>-7.8E-2</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>289</v>
       </c>
@@ -7160,7 +6590,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>290</v>
       </c>
@@ -7174,7 +6604,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>291</v>
       </c>
@@ -7188,7 +6618,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="19" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>293</v>
       </c>
@@ -7202,7 +6632,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>292</v>
       </c>
@@ -7222,28 +6652,28 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{118BE621-EF6B-4648-868E-9937B9C5B685}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{118BE621-EF6B-4648-868E-9937B9C5B685}">
   <dimension ref="A1:F32"/>
-  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="48.140625" style="2" customWidth="true"/>
-    <col min="2" max="4" width="15.7109375" style="2" customWidth="true"/>
-    <col min="5" max="5" width="3.7109375" style="2" customWidth="true"/>
-    <col min="6" max="6" width="46.7109375" style="2" customWidth="true"/>
-    <col min="7" max="16384" width="8.7109375" style="2"/>
+    <col min="1" max="1" width="48.109375" style="2" customWidth="1"/>
+    <col min="2" max="4" width="15.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="3.6640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="46.6640625" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="8.6640625" style="2"/>
   </cols>
   <sheetData>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>207</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>244</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>208</v>
       </c>
@@ -7257,7 +6687,7 @@
         <v>211</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>212</v>
       </c>
@@ -7275,7 +6705,7 @@
         <v>213</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>214</v>
       </c>
@@ -7295,7 +6725,7 @@
         <v>215</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>216</v>
       </c>
@@ -7315,7 +6745,7 @@
         <v>245</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>217</v>
       </c>
@@ -7333,7 +6763,7 @@
         <v>246</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>218</v>
       </c>
@@ -7353,7 +6783,7 @@
         <v>219</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>220</v>
       </c>
@@ -7370,7 +6800,7 @@
         <v>221</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>222</v>
       </c>
@@ -7387,7 +6817,7 @@
         <v>247</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>223</v>
       </c>
@@ -7407,7 +6837,7 @@
         <v>224</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>225</v>
       </c>
@@ -7424,7 +6854,7 @@
         <v>226</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>257</v>
       </c>
@@ -7444,7 +6874,7 @@
         <v>259</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>258</v>
       </c>
@@ -7464,7 +6894,7 @@
         <v>260</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>227</v>
       </c>
@@ -7472,7 +6902,7 @@
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>228</v>
       </c>
@@ -7489,7 +6919,7 @@
         <v>1.9823131728623846</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>229</v>
       </c>
@@ -7506,7 +6936,7 @@
         <v>1.1592794807274085</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="19" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>230</v>
       </c>
@@ -7523,7 +6953,7 @@
         <v>-0.62740704594148844</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>231</v>
       </c>
@@ -7540,7 +6970,7 @@
         <v>-0.96540266006846076</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="21" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>232</v>
       </c>
@@ -7548,7 +6978,7 @@
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="22" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>233</v>
       </c>
@@ -7565,7 +6995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="23" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>234</v>
       </c>
@@ -7582,7 +7012,7 @@
         <v>0.52359877559829882</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="24" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>235</v>
       </c>
@@ -7599,7 +7029,7 @@
         <v>-0.50548365077118673</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>236</v>
       </c>
@@ -7616,7 +7046,7 @@
         <v>324.01250000000005</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="26" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>237</v>
       </c>
@@ -7633,7 +7063,7 @@
         <v>1.42884E-2</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="27" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>238</v>
       </c>
@@ -7650,7 +7080,7 @@
         <v>-0.13760360258695806</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="28" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>239</v>
       </c>
@@ -7667,7 +7097,7 @@
         <v>0.13760360258695806</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="29" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
         <v>240</v>
       </c>
@@ -7684,7 +7114,7 @@
         <v>22.925083964169769</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>241</v>
       </c>
@@ -7692,7 +7122,7 @@
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="31" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>242</v>
       </c>
@@ -7700,7 +7130,7 @@
       <c r="C31" s="14"/>
       <c r="D31" s="14"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="32" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>243</v>
       </c>
@@ -7723,22 +7153,23 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="C109:F109"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="11.5546875" customWidth="true"/>
-    <col min="6" max="6" width="142.44140625" customWidth="true"/>
+    <col min="3" max="3" width="11.5546875" customWidth="1"/>
+    <col min="6" max="6" width="142.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="109">
-      <c r="C109" s="0">
+    <row r="109" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C109">
         <v>12.250154543435004</v>
       </c>
-      <c r="F109" s="0" t="s">
-        <v>382</v>
+      <c r="F109" t="s">
+        <v>380</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ceaa8977d2236823/Documents/GitHub/451-DBF-Team01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{37DAE441-3691-47BB-B387-517F08F01369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2836BEBE-EF50-4D84-AD56-610C67D58106}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{37DAE441-3691-47BB-B387-517F08F01369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84407836-4197-495E-8968-99AA3ACC1078}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Hinge Moments" sheetId="2" r:id="rId4"/>
     <sheet name="Sheet1" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="true"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1062" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2192" uniqueCount="526">
   <si>
     <t>Parameter</t>
   </si>
@@ -972,9 +972,6 @@
     <t>V_S_landing_limit</t>
   </si>
   <si>
-    <t>A9 Assumption</t>
-  </si>
-  <si>
     <t>W</t>
   </si>
   <si>
@@ -1600,18 +1597,36 @@
   </si>
   <si>
     <t>Written by writeOutputs.m on 2026-10-06 13:56</t>
+  </si>
+  <si>
+    <t>Motor Spec per Jackson</t>
+  </si>
+  <si>
+    <t>CL_ground_attitude</t>
+  </si>
+  <si>
+    <t>x_climb</t>
+  </si>
+  <si>
+    <t>mission_P_peak</t>
+  </si>
+  <si>
+    <t>Written by writeOutputs.m on 2026-10-06 17:23</t>
+  </si>
+  <si>
+    <t>Written by writeOutputs.m on 2026-10-06 17:29</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1668,7 +1683,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1707,18 +1722,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79995117038483843"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1726,56 +1735,57 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="true"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="5" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="6" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="5" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="5" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="true"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="true" applyFill="true"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="true"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="true"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="true"/>
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="0" xfId="1" applyNumberFormat="true" applyFont="true" applyFill="true"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="1" applyNumberFormat="true" applyFont="true" applyFill="true"/>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="0" xfId="1" applyNumberFormat="true" applyFont="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="true"/>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="0" xfId="1" applyNumberFormat="true" applyFont="true" applyFill="true"/>
+    <xf numFmtId="2" fontId="6" fillId="4" borderId="0" xfId="1" applyNumberFormat="true" applyFont="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="1" applyFont="true" applyFill="true"/>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="1" applyNumberFormat="true" applyFill="true"/>
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="0" xfId="1" applyNumberFormat="true" applyFont="true" applyFill="true"/>
+    <xf numFmtId="2" fontId="5" fillId="5" borderId="0" xfId="1" applyNumberFormat="true" applyFont="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal 2" xfId="1"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" justifyLastLine="false" shrinkToFit="false" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" justifyLastLine="false" shrinkToFit="false" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" justifyLastLine="false" shrinkToFit="false" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1791,40 +1801,40 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:F109" totalsRowShown="0">
-  <autoFilter ref="A1:F109" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E43">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" id="1" name="Table1" displayName="Table1" ref="A1:F109" totalsRowShown="false">
+  <autoFilter ref="A1:F109"/>
+  <sortState ref="A2:E43">
     <sortCondition ref="B1:B101"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Parameter"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Subclass" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Value" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Units" dataDxfId="0"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Description"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Notes"/>
+    <tableColumn id="1" name="Parameter"/>
+    <tableColumn id="2" name="Subclass" dataDxfId="2"/>
+    <tableColumn id="3" name="Value" dataDxfId="1"/>
+    <tableColumn id="4" name="Units" dataDxfId="0"/>
+    <tableColumn id="5" name="Description"/>
+    <tableColumn id="6" name="Notes"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium15" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="A1:F34" totalsRowShown="0">
-  <autoFilter ref="A1:F34" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" id="2" name="Table2" displayName="Table2" ref="A1:F34" totalsRowShown="false">
+  <autoFilter ref="A1:F34"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Parameter"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Subclass"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Value"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Units"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Description"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Source"/>
+    <tableColumn id="1" name="Parameter"/>
+    <tableColumn id="2" name="Subclass"/>
+    <tableColumn id="3" name="Value"/>
+    <tableColumn id="4" name="Units"/>
+    <tableColumn id="5" name="Description"/>
+    <tableColumn id="6" name="Source"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium15" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1941,7 +1951,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -1965,9 +1975,9 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -1991,7 +2001,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -2026,7 +2036,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="false">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -2044,7 +2054,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -2069,7 +2079,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -3862,7 +3872,7 @@
         <v>273</v>
       </c>
       <c r="E104" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
@@ -3893,44 +3903,44 @@
         <v>1000</v>
       </c>
       <c r="D106" s="20" t="s">
+        <v>311</v>
+      </c>
+      <c r="E106" t="s">
         <v>312</v>
-      </c>
-      <c r="E106" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>308</v>
       </c>
-      <c r="B107" s="21" t="s">
+      <c r="B107" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="C107" s="21">
-        <v>700</v>
+      <c r="C107" s="20">
+        <v>890</v>
       </c>
       <c r="D107" s="20" t="s">
-        <v>312</v>
-      </c>
-      <c r="E107" s="22" t="s">
         <v>311</v>
+      </c>
+      <c r="E107" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>309</v>
       </c>
-      <c r="B108" s="21" t="s">
+      <c r="B108" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="C108" s="21">
-        <v>50</v>
+      <c r="C108" s="20">
+        <v>60</v>
       </c>
       <c r="D108" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="E108" s="22" t="s">
-        <v>311</v>
+      <c r="E108" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
@@ -3947,7 +3957,7 @@
         <v>137</v>
       </c>
       <c r="E109" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -3959,2394 +3969,3017 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:H157"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:H160"/>
+  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="40.6640625" customWidth="1"/>
-    <col min="2" max="2" width="12.5546875" customWidth="1"/>
-    <col min="3" max="3" width="64.5546875" customWidth="1"/>
-    <col min="4" max="4" width="5.6640625" customWidth="1"/>
-    <col min="5" max="5" width="46" customWidth="1"/>
-    <col min="6" max="6" width="32.44140625" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="true"/>
+    <col min="2" max="2" width="11.5546875" customWidth="true"/>
+    <col min="3" max="3" width="58.5546875" customWidth="true"/>
+    <col min="4" max="4" width="5.21875" customWidth="true"/>
+    <col min="5" max="5" width="42.77734375" customWidth="true"/>
+    <col min="6" max="6" width="29.21875" customWidth="true"/>
     <col min="7" max="7" width="9.109375"/>
-    <col min="8" max="8" width="42.6640625" customWidth="1"/>
+    <col min="8" max="8" width="40.109375" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>377</v>
-      </c>
-      <c r="H1" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="F1" s="0" t="s">
+        <v>376</v>
+      </c>
+      <c r="G1" s="0"/>
+      <c r="H1" s="0" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="0">
+        <v>0.29999999999999999</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>348</v>
+      </c>
+      <c r="F2" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G2" s="0"/>
+      <c r="H2" s="0"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="s">
         <v>316</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="C2">
-        <v>0.3</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="C3" s="0">
+        <v>1.1818181818181817</v>
+      </c>
+      <c r="D3" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E3" s="0" t="s">
         <v>349</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F3" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G3" s="0"/>
+      <c r="H3" s="0"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="s">
+        <v>317</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="0">
+        <v>0.92201380973471758</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>350</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G4" s="0"/>
+      <c r="H4" s="0"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="s">
+        <v>318</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="0">
+        <v>0.07919652663705147</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>351</v>
+      </c>
+      <c r="F5" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G5" s="0"/>
+      <c r="H5" s="0"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="s">
+        <v>319</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="0">
+        <v>0.19588300688233271</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>352</v>
+      </c>
+      <c r="F6" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G6" s="0"/>
+      <c r="H6" s="0"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="s">
+        <v>320</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="0">
+        <v>0.029817638776781716</v>
+      </c>
+      <c r="D7" s="0"/>
+      <c r="E7" s="0"/>
+      <c r="F7" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G7" s="0"/>
+      <c r="H7" s="0"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="s">
+        <v>321</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="0">
+        <v>0.036945326174116347</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="0" t="s">
+        <v>353</v>
+      </c>
+      <c r="F8" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G8" s="0"/>
+      <c r="H8" s="0"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="s">
+        <v>322</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="0">
+        <v>0.036945326174116347</v>
+      </c>
+      <c r="D9" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="0" t="s">
+        <v>354</v>
+      </c>
+      <c r="F9" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G9" s="0"/>
+      <c r="H9" s="0"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="s">
+        <v>323</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="0">
+        <v>0.021945326174116348</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="0" t="s">
+        <v>355</v>
+      </c>
+      <c r="F10" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G10" s="0"/>
+      <c r="H10" s="0"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="s">
+        <v>324</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="0">
+        <v>8.1201069544265661</v>
+      </c>
+      <c r="D11" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="F11" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G11" s="0"/>
+      <c r="H11" s="0"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="s">
+        <v>325</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="0">
+        <v>10.289169276665902</v>
+      </c>
+      <c r="D12" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="0" t="s">
+        <v>357</v>
+      </c>
+      <c r="F12" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G12" s="0"/>
+      <c r="H12" s="0"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="s">
+        <v>380</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="0">
+        <v>3.0198549799930445</v>
+      </c>
+      <c r="D13" s="0"/>
+      <c r="E13" s="0"/>
+      <c r="F13" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G13" s="0"/>
+      <c r="H13" s="0"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="s">
+        <v>381</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="0">
+        <v>4.0327458299223453</v>
+      </c>
+      <c r="D14" s="0"/>
+      <c r="E14" s="0"/>
+      <c r="F14" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G14" s="0"/>
+      <c r="H14" s="0"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="s">
+        <v>382</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="0">
+        <v>0.58894455001488533</v>
+      </c>
+      <c r="D15" s="0"/>
+      <c r="E15" s="0"/>
+      <c r="F15" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G15" s="0"/>
+      <c r="H15" s="0"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="s">
+        <v>383</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="0">
+        <v>5.2740736776131758</v>
+      </c>
+      <c r="D16" s="0"/>
+      <c r="E16" s="0"/>
+      <c r="F16" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G16" s="0"/>
+      <c r="H16" s="0"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="s">
+        <v>384</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="0">
+        <v>-0.094788465253600393</v>
+      </c>
+      <c r="D17" s="0"/>
+      <c r="E17" s="0"/>
+      <c r="F17" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G17" s="0"/>
+      <c r="H17" s="0"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="s">
+        <v>385</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="0">
+        <v>0.66074594914354523</v>
+      </c>
+      <c r="D18" s="0"/>
+      <c r="E18" s="0"/>
+      <c r="F18" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G18" s="0"/>
+      <c r="H18" s="0"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="s">
+        <v>386</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="0">
+        <v>0.60899778104422941</v>
+      </c>
+      <c r="D19" s="0"/>
+      <c r="E19" s="0"/>
+      <c r="F19" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G19" s="0"/>
+      <c r="H19" s="0"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="s">
+        <v>387</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="0">
+        <v>1.5753270213496304</v>
+      </c>
+      <c r="D20" s="0"/>
+      <c r="E20" s="0"/>
+      <c r="F20" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G20" s="0"/>
+      <c r="H20" s="0"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="s">
+        <v>388</v>
+      </c>
+      <c r="B21" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="0">
+        <v>0.66074594914354523</v>
+      </c>
+      <c r="D21" s="0"/>
+      <c r="E21" s="0"/>
+      <c r="F21" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G21" s="0"/>
+      <c r="H21" s="0"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="s">
+        <v>389</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="0">
+        <v>0.12602616170797043</v>
+      </c>
+      <c r="D22" s="0"/>
+      <c r="E22" s="0"/>
+      <c r="F22" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G22" s="0"/>
+      <c r="H22" s="0"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="s">
+        <v>521</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="0">
+        <v>0.8871601270722228</v>
+      </c>
+      <c r="D23" s="0"/>
+      <c r="E23" s="0"/>
+      <c r="F23" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G23" s="0"/>
+      <c r="H23" s="0"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="s">
+        <v>326</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="0">
+        <v>0.49722452282391244</v>
+      </c>
+      <c r="D24" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="E24" s="0" t="s">
+        <v>358</v>
+      </c>
+      <c r="F24" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G24" s="0"/>
+      <c r="H24" s="0"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="s">
+        <v>327</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C25" s="0">
+        <v>0.34410001579509508</v>
+      </c>
+      <c r="D25" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="E25" s="0" t="s">
+        <v>359</v>
+      </c>
+      <c r="F25" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G25" s="0"/>
+      <c r="H25" s="0"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>328</v>
+      </c>
+      <c r="B26" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" s="0">
+        <v>4.3591977074863637</v>
+      </c>
+      <c r="D26" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="0" t="s">
+        <v>360</v>
+      </c>
+      <c r="F26" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G26" s="0"/>
+      <c r="H26" s="0"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>329</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27" s="0">
+        <v>0.084528168880065119</v>
+      </c>
+      <c r="D27" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="E27" s="0" t="s">
+        <v>361</v>
+      </c>
+      <c r="F27" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G27" s="0"/>
+      <c r="H27" s="0"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>330</v>
+      </c>
+      <c r="B28" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28" s="0">
+        <v>0.45969601064199239</v>
+      </c>
+      <c r="D28" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="E28" s="0" t="s">
+        <v>362</v>
+      </c>
+      <c r="F28" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G28" s="0"/>
+      <c r="H28" s="0"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="s">
+        <v>331</v>
+      </c>
+      <c r="B29" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29" s="0">
+        <v>0.18387840425679697</v>
+      </c>
+      <c r="D29" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="E29" s="0" t="s">
+        <v>363</v>
+      </c>
+      <c r="F29" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G29" s="0"/>
+      <c r="H29" s="0"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="s">
+        <v>332</v>
+      </c>
+      <c r="B30" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30" s="0">
+        <v>0.39523392547876368</v>
+      </c>
+      <c r="D30" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="0" t="s">
+        <v>364</v>
+      </c>
+      <c r="F30" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G30" s="0"/>
+      <c r="H30" s="0"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="s">
+        <v>333</v>
+      </c>
+      <c r="B31" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C31" s="0">
+        <v>0.074583678423586861</v>
+      </c>
+      <c r="D31" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="E31" s="0" t="s">
+        <v>365</v>
+      </c>
+      <c r="F31" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G31" s="0"/>
+      <c r="H31" s="0"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="s">
+        <v>334</v>
+      </c>
+      <c r="B32" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32" s="0">
+        <v>0.074583678423586861</v>
+      </c>
+      <c r="D32" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="E32" s="0" t="s">
+        <v>366</v>
+      </c>
+      <c r="F32" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G32" s="0"/>
+      <c r="H32" s="0"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="s">
+        <v>335</v>
+      </c>
+      <c r="B33" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C33" s="0">
+        <v>0.28249696620183012</v>
+      </c>
+      <c r="D33" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="E33" s="0" t="s">
+        <v>367</v>
+      </c>
+      <c r="F33" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G33" s="0"/>
+      <c r="H33" s="0"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="s">
+        <v>336</v>
+      </c>
+      <c r="B34" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C34" s="0">
+        <v>0.26401585626339264</v>
+      </c>
+      <c r="D34" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="E34" s="0" t="s">
+        <v>368</v>
+      </c>
+      <c r="F34" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G34" s="0"/>
+      <c r="H34" s="0"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="s">
+        <v>390</v>
+      </c>
+      <c r="B35" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C35" s="0">
+        <v>0.018046437163813135</v>
+      </c>
+      <c r="D35" s="0"/>
+      <c r="E35" s="0"/>
+      <c r="F35" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G35" s="0"/>
+      <c r="H35" s="0"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="s">
+        <v>391</v>
+      </c>
+      <c r="B36" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C36" s="0">
+        <v>0.23885083680507355</v>
+      </c>
+      <c r="D36" s="0"/>
+      <c r="E36" s="0"/>
+      <c r="F36" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G36" s="0"/>
+      <c r="H36" s="0"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="s">
+        <v>392</v>
+      </c>
+      <c r="B37" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C37" s="0">
+        <v>0.3656082203404642</v>
+      </c>
+      <c r="D37" s="0"/>
+      <c r="E37" s="0"/>
+      <c r="F37" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G37" s="0"/>
+      <c r="H37" s="0"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="s">
+        <v>393</v>
+      </c>
+      <c r="B38" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C38" s="0">
+        <v>0.2156082203404642</v>
+      </c>
+      <c r="D38" s="0"/>
+      <c r="E38" s="0"/>
+      <c r="F38" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G38" s="0"/>
+      <c r="H38" s="0"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="s">
+        <v>167</v>
+      </c>
+      <c r="B39" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C39" s="0">
+        <v>4.0516000000000005</v>
+      </c>
+      <c r="D39" s="0"/>
+      <c r="E39" s="0"/>
+      <c r="F39" s="0" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>317</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>1.1818181818181817</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" t="s">
-        <v>350</v>
-      </c>
-      <c r="F3" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>318</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>0.92201380973471758</v>
-      </c>
-      <c r="D4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" t="s">
-        <v>351</v>
-      </c>
-      <c r="F4" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>319</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5">
-        <v>7.919652663705147E-2</v>
-      </c>
-      <c r="D5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" t="s">
-        <v>352</v>
-      </c>
-      <c r="F5" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>320</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6">
-        <v>0.19588300688233271</v>
-      </c>
-      <c r="D6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" t="s">
-        <v>353</v>
-      </c>
-      <c r="F6" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>321</v>
-      </c>
-      <c r="B7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7">
-        <v>2.9817638776781716E-2</v>
-      </c>
-      <c r="F7" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>322</v>
-      </c>
-      <c r="B8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8">
-        <v>3.6945326174116347E-2</v>
-      </c>
-      <c r="D8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" t="s">
-        <v>354</v>
-      </c>
-      <c r="F8" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>323</v>
-      </c>
-      <c r="B9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9">
-        <v>3.6945326174116347E-2</v>
-      </c>
-      <c r="D9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" t="s">
-        <v>355</v>
-      </c>
-      <c r="F9" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>324</v>
-      </c>
-      <c r="B10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10">
-        <v>2.1945326174116347E-2</v>
-      </c>
-      <c r="D10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" t="s">
-        <v>356</v>
-      </c>
-      <c r="F10" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>325</v>
-      </c>
-      <c r="B11" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11">
-        <v>8.120106954426566</v>
-      </c>
-      <c r="D11" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" t="s">
-        <v>357</v>
-      </c>
-      <c r="F11" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>326</v>
-      </c>
-      <c r="B12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12">
-        <v>10.289169276665902</v>
-      </c>
-      <c r="D12" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" t="s">
-        <v>358</v>
-      </c>
-      <c r="F12" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>381</v>
-      </c>
-      <c r="B13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13">
-        <v>3.0198549799930445</v>
-      </c>
-      <c r="F13" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>382</v>
-      </c>
-      <c r="B14" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14">
-        <v>4.0327458299223453</v>
-      </c>
-      <c r="F14" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>383</v>
-      </c>
-      <c r="B15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15">
-        <v>0.58894455001488533</v>
-      </c>
-      <c r="F15" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>384</v>
-      </c>
-      <c r="B16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16">
+      <c r="G39" s="0"/>
+      <c r="H39" s="0"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="s">
+        <v>337</v>
+      </c>
+      <c r="B40" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C40" s="0">
+        <v>22.737783592977756</v>
+      </c>
+      <c r="D40" s="0" t="s">
+        <v>137</v>
+      </c>
+      <c r="E40" s="0" t="s">
+        <v>369</v>
+      </c>
+      <c r="F40" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G40" s="0"/>
+      <c r="H40" s="0"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="0" t="s">
+        <v>338</v>
+      </c>
+      <c r="B41" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C41" s="0">
+        <v>11</v>
+      </c>
+      <c r="D41" s="0" t="s">
+        <v>137</v>
+      </c>
+      <c r="E41" s="0" t="s">
+        <v>370</v>
+      </c>
+      <c r="F41" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G41" s="0"/>
+      <c r="H41" s="0"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="0" t="s">
+        <v>339</v>
+      </c>
+      <c r="B42" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C42" s="0">
+        <v>14.810748414335091</v>
+      </c>
+      <c r="D42" s="0" t="s">
+        <v>137</v>
+      </c>
+      <c r="E42" s="0" t="s">
+        <v>371</v>
+      </c>
+      <c r="F42" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G42" s="0"/>
+      <c r="H42" s="0"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="0" t="s">
+        <v>340</v>
+      </c>
+      <c r="B43" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C43" s="0">
+        <v>12.24744871391589</v>
+      </c>
+      <c r="D43" s="0" t="s">
+        <v>137</v>
+      </c>
+      <c r="E43" s="0" t="s">
+        <v>372</v>
+      </c>
+      <c r="F43" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G43" s="0"/>
+      <c r="H43" s="0"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="0" t="s">
+        <v>341</v>
+      </c>
+      <c r="B44" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C44" s="0">
+        <v>48.189685104221404</v>
+      </c>
+      <c r="D44" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="E44" s="0" t="s">
+        <v>373</v>
+      </c>
+      <c r="F44" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G44" s="0"/>
+      <c r="H44" s="0"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="0" t="s">
+        <v>342</v>
+      </c>
+      <c r="B45" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C45" s="0">
+        <v>16.699244233993625</v>
+      </c>
+      <c r="D45" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="E45" s="0" t="s">
+        <v>374</v>
+      </c>
+      <c r="F45" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G45" s="0"/>
+      <c r="H45" s="0"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="0" t="s">
+        <v>343</v>
+      </c>
+      <c r="B46" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C46" s="0">
+        <v>39.746196000000005</v>
+      </c>
+      <c r="D46" s="0" t="s">
+        <v>347</v>
+      </c>
+      <c r="E46" s="0" t="s">
+        <v>375</v>
+      </c>
+      <c r="F46" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G46" s="0"/>
+      <c r="H46" s="0"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="0" t="s">
+        <v>344</v>
+      </c>
+      <c r="B47" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C47" s="0">
+        <v>0.44283295832701009</v>
+      </c>
+      <c r="D47" s="0"/>
+      <c r="E47" s="0"/>
+      <c r="F47" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G47" s="0"/>
+      <c r="H47" s="0"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="0" t="s">
+        <v>345</v>
+      </c>
+      <c r="B48" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C48" s="0">
+        <v>233372.96903833433</v>
+      </c>
+      <c r="D48" s="0"/>
+      <c r="E48" s="0"/>
+      <c r="F48" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G48" s="0"/>
+      <c r="H48" s="0"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="0" t="s">
+        <v>346</v>
+      </c>
+      <c r="B49" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C49" s="0">
+        <v>130688.86266146721</v>
+      </c>
+      <c r="D49" s="0"/>
+      <c r="E49" s="0"/>
+      <c r="F49" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G49" s="0"/>
+      <c r="H49" s="0"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="0" t="s">
+        <v>394</v>
+      </c>
+      <c r="B50" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C50" s="0">
+        <v>34.194077618408031</v>
+      </c>
+      <c r="D50" s="0"/>
+      <c r="E50" s="0"/>
+      <c r="F50" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G50" s="0"/>
+      <c r="H50" s="0"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="0" t="s">
+        <v>395</v>
+      </c>
+      <c r="B51" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C51" s="0">
+        <v>15.480365443172449</v>
+      </c>
+      <c r="D51" s="0"/>
+      <c r="E51" s="0"/>
+      <c r="F51" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G51" s="0"/>
+      <c r="H51" s="0"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="0" t="s">
+        <v>396</v>
+      </c>
+      <c r="B52" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C52" s="0">
+        <v>3.7999999999999998</v>
+      </c>
+      <c r="D52" s="0"/>
+      <c r="E52" s="0"/>
+      <c r="F52" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G52" s="0"/>
+      <c r="H52" s="0"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="0" t="s">
+        <v>397</v>
+      </c>
+      <c r="B53" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C53" s="0">
+        <v>-1.52</v>
+      </c>
+      <c r="D53" s="0"/>
+      <c r="E53" s="0"/>
+      <c r="F53" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G53" s="0"/>
+      <c r="H53" s="0"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="0" t="s">
+        <v>398</v>
+      </c>
+      <c r="B54" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C54" s="0">
+        <v>5.6999999999999993</v>
+      </c>
+      <c r="D54" s="0"/>
+      <c r="E54" s="0"/>
+      <c r="F54" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G54" s="0"/>
+      <c r="H54" s="0"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="0" t="s">
+        <v>399</v>
+      </c>
+      <c r="B55" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C55" s="0">
+        <v>-2.2800000000000003</v>
+      </c>
+      <c r="D55" s="0"/>
+      <c r="E55" s="0"/>
+      <c r="F55" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G55" s="0"/>
+      <c r="H55" s="0"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="0" t="s">
+        <v>400</v>
+      </c>
+      <c r="B56" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C56" s="0">
+        <v>18.622682892532463</v>
+      </c>
+      <c r="D56" s="0"/>
+      <c r="E56" s="0"/>
+      <c r="F56" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G56" s="0"/>
+      <c r="H56" s="0"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="0" t="s">
+        <v>401</v>
+      </c>
+      <c r="B57" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C57" s="0">
+        <v>27.131986877647702</v>
+      </c>
+      <c r="D57" s="0"/>
+      <c r="E57" s="0"/>
+      <c r="F57" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G57" s="0"/>
+      <c r="H57" s="0"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="0" t="s">
+        <v>402</v>
+      </c>
+      <c r="B58" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C58" s="0">
+        <v>25.580006542099977</v>
+      </c>
+      <c r="D58" s="0"/>
+      <c r="E58" s="0"/>
+      <c r="F58" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G58" s="0"/>
+      <c r="H58" s="0"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="0" t="s">
+        <v>403</v>
+      </c>
+      <c r="B59" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C59" s="0">
+        <v>28.422229491222197</v>
+      </c>
+      <c r="D59" s="0"/>
+      <c r="E59" s="0"/>
+      <c r="F59" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G59" s="0"/>
+      <c r="H59" s="0"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="0" t="s">
+        <v>404</v>
+      </c>
+      <c r="B60" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C60" s="0">
+        <v>6.3586494759793881</v>
+      </c>
+      <c r="D60" s="0"/>
+      <c r="E60" s="0"/>
+      <c r="F60" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G60" s="0"/>
+      <c r="H60" s="0"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="0" t="s">
+        <v>405</v>
+      </c>
+      <c r="B61" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C61" s="0">
+        <v>11.113261724726186</v>
+      </c>
+      <c r="D61" s="0"/>
+      <c r="E61" s="0"/>
+      <c r="F61" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G61" s="0"/>
+      <c r="H61" s="0"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="0" t="s">
+        <v>406</v>
+      </c>
+      <c r="B62" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C62" s="0">
+        <v>1.9300000000000015</v>
+      </c>
+      <c r="D62" s="0"/>
+      <c r="E62" s="0"/>
+      <c r="F62" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G62" s="0"/>
+      <c r="H62" s="0"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="0" t="s">
+        <v>407</v>
+      </c>
+      <c r="B63" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C63" s="0">
+        <v>11.008581406383897</v>
+      </c>
+      <c r="D63" s="0"/>
+      <c r="E63" s="0"/>
+      <c r="F63" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G63" s="0"/>
+      <c r="H63" s="0"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="0" t="s">
+        <v>408</v>
+      </c>
+      <c r="B64" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C64" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="D64" s="0"/>
+      <c r="E64" s="0"/>
+      <c r="F64" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G64" s="0"/>
+      <c r="H64" s="0"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="0" t="s">
+        <v>409</v>
+      </c>
+      <c r="B65" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C65" s="0">
+        <v>7.4507370536077033</v>
+      </c>
+      <c r="D65" s="0"/>
+      <c r="E65" s="0"/>
+      <c r="F65" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G65" s="0"/>
+      <c r="H65" s="0"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="0" t="s">
+        <v>410</v>
+      </c>
+      <c r="B66" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C66" s="0">
+        <v>20.550728554427437</v>
+      </c>
+      <c r="D66" s="0"/>
+      <c r="E66" s="0"/>
+      <c r="F66" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G66" s="0"/>
+      <c r="H66" s="0"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="0" t="s">
+        <v>411</v>
+      </c>
+      <c r="B67" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C67" s="0">
+        <v>4.0264472875839541</v>
+      </c>
+      <c r="D67" s="0"/>
+      <c r="E67" s="0"/>
+      <c r="F67" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G67" s="0"/>
+      <c r="H67" s="0"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="0" t="s">
+        <v>522</v>
+      </c>
+      <c r="B68" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C68" s="0">
+        <v>77.116605805538328</v>
+      </c>
+      <c r="D68" s="0"/>
+      <c r="E68" s="0"/>
+      <c r="F68" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G68" s="0"/>
+      <c r="H68" s="0"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="0" t="s">
+        <v>412</v>
+      </c>
+      <c r="B69" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C69" s="0">
+        <v>22.608098531363336</v>
+      </c>
+      <c r="D69" s="0"/>
+      <c r="E69" s="0"/>
+      <c r="F69" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G69" s="0"/>
+      <c r="H69" s="0"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="0" t="s">
+        <v>413</v>
+      </c>
+      <c r="B70" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C70" s="0">
+        <v>12.709922788411269</v>
+      </c>
+      <c r="D70" s="0"/>
+      <c r="E70" s="0"/>
+      <c r="F70" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G70" s="0"/>
+      <c r="H70" s="0"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="0" t="s">
+        <v>414</v>
+      </c>
+      <c r="B71" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C71" s="0">
+        <v>16.27392540932771</v>
+      </c>
+      <c r="D71" s="0"/>
+      <c r="E71" s="0"/>
+      <c r="F71" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G71" s="0"/>
+      <c r="H71" s="0"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="0" t="s">
+        <v>415</v>
+      </c>
+      <c r="B72" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C72" s="0">
+        <v>15.956485750905872</v>
+      </c>
+      <c r="D72" s="0"/>
+      <c r="E72" s="0"/>
+      <c r="F72" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G72" s="0"/>
+      <c r="H72" s="0"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="0" t="s">
+        <v>416</v>
+      </c>
+      <c r="B73" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C73" s="0">
+        <v>13.695854805920606</v>
+      </c>
+      <c r="D73" s="0"/>
+      <c r="E73" s="0"/>
+      <c r="F73" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G73" s="0"/>
+      <c r="H73" s="0"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="0" t="s">
+        <v>417</v>
+      </c>
+      <c r="B74" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C74" s="0">
+        <v>1.0954451150103324</v>
+      </c>
+      <c r="D74" s="0"/>
+      <c r="E74" s="0"/>
+      <c r="F74" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G74" s="0"/>
+      <c r="H74" s="0"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="0" t="s">
+        <v>418</v>
+      </c>
+      <c r="B75" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C75" s="0">
+        <v>24.094842552110709</v>
+      </c>
+      <c r="D75" s="0"/>
+      <c r="E75" s="0"/>
+      <c r="F75" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G75" s="0"/>
+      <c r="H75" s="0"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="B76" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C76" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="D76" s="0"/>
+      <c r="E76" s="0"/>
+      <c r="F76" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G76" s="0"/>
+      <c r="H76" s="0"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="0" t="s">
+        <v>420</v>
+      </c>
+      <c r="B77" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C77" s="0">
+        <v>150.69320484179264</v>
+      </c>
+      <c r="D77" s="0"/>
+      <c r="E77" s="0"/>
+      <c r="F77" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G77" s="0"/>
+      <c r="H77" s="0"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="0" t="s">
+        <v>421</v>
+      </c>
+      <c r="B78" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C78" s="0">
+        <v>46195.337793815328</v>
+      </c>
+      <c r="D78" s="0"/>
+      <c r="E78" s="0"/>
+      <c r="F78" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G78" s="0"/>
+      <c r="H78" s="0"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="0" t="s">
+        <v>422</v>
+      </c>
+      <c r="B79" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C79" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="D79" s="0"/>
+      <c r="E79" s="0"/>
+      <c r="F79" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G79" s="0"/>
+      <c r="H79" s="0"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="0" t="s">
+        <v>423</v>
+      </c>
+      <c r="B80" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C80" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="D80" s="0"/>
+      <c r="E80" s="0"/>
+      <c r="F80" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G80" s="0"/>
+      <c r="H80" s="0"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="0" t="s">
+        <v>523</v>
+      </c>
+      <c r="B81" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C81" s="0">
+        <v>890</v>
+      </c>
+      <c r="D81" s="0"/>
+      <c r="E81" s="0"/>
+      <c r="F81" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G81" s="0"/>
+      <c r="H81" s="0"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="0" t="s">
+        <v>424</v>
+      </c>
+      <c r="B82" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C82" s="0">
+        <v>13</v>
+      </c>
+      <c r="D82" s="0"/>
+      <c r="E82" s="0"/>
+      <c r="F82" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G82" s="0"/>
+      <c r="H82" s="0"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="0" t="s">
+        <v>425</v>
+      </c>
+      <c r="B83" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C83" s="0">
+        <v>84493.524867651882</v>
+      </c>
+      <c r="D83" s="0"/>
+      <c r="E83" s="0"/>
+      <c r="F83" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G83" s="0"/>
+      <c r="H83" s="0"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="0" t="s">
+        <v>426</v>
+      </c>
+      <c r="B84" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C84" s="0">
+        <v>0.16032926919858043</v>
+      </c>
+      <c r="D84" s="0"/>
+      <c r="E84" s="0"/>
+      <c r="F84" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G84" s="0"/>
+      <c r="H84" s="0"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="0" t="s">
+        <v>427</v>
+      </c>
+      <c r="B85" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C85" s="0">
+        <v>2.4683999999999995</v>
+      </c>
+      <c r="D85" s="0"/>
+      <c r="E85" s="0"/>
+      <c r="F85" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G85" s="0"/>
+      <c r="H85" s="0"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="0" t="s">
+        <v>428</v>
+      </c>
+      <c r="B86" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C86" s="0" t="s">
+        <v>504</v>
+      </c>
+      <c r="D86" s="0"/>
+      <c r="E86" s="0"/>
+      <c r="F86" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G86" s="0"/>
+      <c r="H86" s="0"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="0" t="s">
+        <v>429</v>
+      </c>
+      <c r="B87" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C87" s="0">
+        <v>-0.040973254512723323</v>
+      </c>
+      <c r="D87" s="0"/>
+      <c r="E87" s="0"/>
+      <c r="F87" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G87" s="0"/>
+      <c r="H87" s="0"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="0" t="s">
+        <v>430</v>
+      </c>
+      <c r="B88" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C88" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="D88" s="0"/>
+      <c r="E88" s="0"/>
+      <c r="F88" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G88" s="0"/>
+      <c r="H88" s="0"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="0" t="s">
+        <v>431</v>
+      </c>
+      <c r="B89" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C89" s="0">
+        <v>0.254</v>
+      </c>
+      <c r="D89" s="0"/>
+      <c r="E89" s="0"/>
+      <c r="F89" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G89" s="0"/>
+      <c r="H89" s="0"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="0" t="s">
+        <v>432</v>
+      </c>
+      <c r="B90" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C90" s="0">
+        <v>0.127</v>
+      </c>
+      <c r="D90" s="0"/>
+      <c r="E90" s="0"/>
+      <c r="F90" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G90" s="0"/>
+      <c r="H90" s="0"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="0" t="s">
+        <v>433</v>
+      </c>
+      <c r="B91" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C91" s="0">
+        <v>14500</v>
+      </c>
+      <c r="D91" s="0"/>
+      <c r="E91" s="0"/>
+      <c r="F91" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G91" s="0"/>
+      <c r="H91" s="0"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="0" t="s">
+        <v>434</v>
+      </c>
+      <c r="B92" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C92" s="0" t="s">
+        <v>505</v>
+      </c>
+      <c r="D92" s="0"/>
+      <c r="E92" s="0"/>
+      <c r="F92" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G92" s="0"/>
+      <c r="H92" s="0"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="0" t="s">
+        <v>435</v>
+      </c>
+      <c r="B93" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C93" s="0" t="s">
+        <v>506</v>
+      </c>
+      <c r="D93" s="0"/>
+      <c r="E93" s="0"/>
+      <c r="F93" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G93" s="0"/>
+      <c r="H93" s="0"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="B94" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C94" s="0" t="s">
+        <v>507</v>
+      </c>
+      <c r="D94" s="0"/>
+      <c r="E94" s="0"/>
+      <c r="F94" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G94" s="0"/>
+      <c r="H94" s="0"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="0" t="s">
+        <v>437</v>
+      </c>
+      <c r="B95" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C95" s="0" t="s">
+        <v>507</v>
+      </c>
+      <c r="D95" s="0"/>
+      <c r="E95" s="0"/>
+      <c r="F95" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G95" s="0"/>
+      <c r="H95" s="0"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="0" t="s">
+        <v>438</v>
+      </c>
+      <c r="B96" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C96" s="0" t="s">
+        <v>507</v>
+      </c>
+      <c r="D96" s="0"/>
+      <c r="E96" s="0"/>
+      <c r="F96" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G96" s="0"/>
+      <c r="H96" s="0"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="B97" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C97" s="0" t="s">
+        <v>507</v>
+      </c>
+      <c r="D97" s="0"/>
+      <c r="E97" s="0"/>
+      <c r="F97" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G97" s="0"/>
+      <c r="H97" s="0"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="0" t="s">
+        <v>440</v>
+      </c>
+      <c r="B98" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C98" s="0" t="s">
+        <v>507</v>
+      </c>
+      <c r="D98" s="0"/>
+      <c r="E98" s="0"/>
+      <c r="F98" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G98" s="0"/>
+      <c r="H98" s="0"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="0" t="s">
+        <v>441</v>
+      </c>
+      <c r="B99" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C99" s="0" t="s">
+        <v>507</v>
+      </c>
+      <c r="D99" s="0"/>
+      <c r="E99" s="0"/>
+      <c r="F99" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G99" s="0"/>
+      <c r="H99" s="0"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="0" t="s">
+        <v>442</v>
+      </c>
+      <c r="B100" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C100" s="0" t="s">
+        <v>507</v>
+      </c>
+      <c r="D100" s="0"/>
+      <c r="E100" s="0"/>
+      <c r="F100" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G100" s="0"/>
+      <c r="H100" s="0"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="0" t="s">
+        <v>443</v>
+      </c>
+      <c r="B101" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C101" s="0" t="s">
+        <v>507</v>
+      </c>
+      <c r="D101" s="0"/>
+      <c r="E101" s="0"/>
+      <c r="F101" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G101" s="0"/>
+      <c r="H101" s="0"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="0" t="s">
+        <v>444</v>
+      </c>
+      <c r="B102" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C102" s="0" t="s">
+        <v>508</v>
+      </c>
+      <c r="D102" s="0"/>
+      <c r="E102" s="0"/>
+      <c r="F102" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G102" s="0"/>
+      <c r="H102" s="0"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="0" t="s">
+        <v>445</v>
+      </c>
+      <c r="B103" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C103" s="0">
+        <v>890</v>
+      </c>
+      <c r="D103" s="0"/>
+      <c r="E103" s="0"/>
+      <c r="F103" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G103" s="0"/>
+      <c r="H103" s="0"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="0" t="s">
+        <v>446</v>
+      </c>
+      <c r="B104" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C104" s="0">
+        <v>60</v>
+      </c>
+      <c r="D104" s="0"/>
+      <c r="E104" s="0"/>
+      <c r="F104" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G104" s="0"/>
+      <c r="H104" s="0"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="0" t="s">
+        <v>447</v>
+      </c>
+      <c r="B105" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C105" s="0" t="s">
+        <v>509</v>
+      </c>
+      <c r="D105" s="0"/>
+      <c r="E105" s="0"/>
+      <c r="F105" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G105" s="0"/>
+      <c r="H105" s="0"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="0" t="s">
+        <v>448</v>
+      </c>
+      <c r="B106" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C106" s="0" t="s">
+        <v>507</v>
+      </c>
+      <c r="D106" s="0"/>
+      <c r="E106" s="0"/>
+      <c r="F106" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G106" s="0"/>
+      <c r="H106" s="0"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="0" t="s">
+        <v>449</v>
+      </c>
+      <c r="B107" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C107" s="0" t="s">
+        <v>510</v>
+      </c>
+      <c r="D107" s="0"/>
+      <c r="E107" s="0"/>
+      <c r="F107" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G107" s="0"/>
+      <c r="H107" s="0"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="0" t="s">
+        <v>450</v>
+      </c>
+      <c r="B108" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C108" s="0" t="s">
+        <v>511</v>
+      </c>
+      <c r="D108" s="0"/>
+      <c r="E108" s="0"/>
+      <c r="F108" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G108" s="0"/>
+      <c r="H108" s="0"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="0" t="s">
+        <v>451</v>
+      </c>
+      <c r="B109" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C109" s="0" t="s">
+        <v>512</v>
+      </c>
+      <c r="D109" s="0"/>
+      <c r="E109" s="0"/>
+      <c r="F109" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G109" s="0"/>
+      <c r="H109" s="0"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="0" t="s">
+        <v>452</v>
+      </c>
+      <c r="B110" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C110" s="0" t="s">
+        <v>513</v>
+      </c>
+      <c r="D110" s="0"/>
+      <c r="E110" s="0"/>
+      <c r="F110" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G110" s="0"/>
+      <c r="H110" s="0"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="0" t="s">
+        <v>453</v>
+      </c>
+      <c r="B111" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C111" s="0" t="s">
+        <v>514</v>
+      </c>
+      <c r="D111" s="0"/>
+      <c r="E111" s="0"/>
+      <c r="F111" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G111" s="0"/>
+      <c r="H111" s="0"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="0" t="s">
+        <v>454</v>
+      </c>
+      <c r="B112" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C112" s="0" t="s">
+        <v>515</v>
+      </c>
+      <c r="D112" s="0"/>
+      <c r="E112" s="0"/>
+      <c r="F112" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G112" s="0"/>
+      <c r="H112" s="0"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="0" t="s">
+        <v>455</v>
+      </c>
+      <c r="B113" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C113" s="0" t="s">
+        <v>516</v>
+      </c>
+      <c r="D113" s="0"/>
+      <c r="E113" s="0"/>
+      <c r="F113" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G113" s="0"/>
+      <c r="H113" s="0"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="0" t="s">
+        <v>456</v>
+      </c>
+      <c r="B114" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C114" s="0">
+        <v>32.946133306980855</v>
+      </c>
+      <c r="D114" s="0"/>
+      <c r="E114" s="0"/>
+      <c r="F114" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G114" s="0"/>
+      <c r="H114" s="0"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="0" t="s">
+        <v>457</v>
+      </c>
+      <c r="B115" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C115" s="0">
+        <v>0</v>
+      </c>
+      <c r="D115" s="0"/>
+      <c r="E115" s="0"/>
+      <c r="F115" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G115" s="0"/>
+      <c r="H115" s="0"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="0" t="s">
+        <v>458</v>
+      </c>
+      <c r="B116" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C116" s="0" t="s">
+        <v>517</v>
+      </c>
+      <c r="D116" s="0"/>
+      <c r="E116" s="0"/>
+      <c r="F116" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G116" s="0"/>
+      <c r="H116" s="0"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="0" t="s">
+        <v>459</v>
+      </c>
+      <c r="B117" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C117" s="0">
+        <v>86.068285472894019</v>
+      </c>
+      <c r="D117" s="0"/>
+      <c r="E117" s="0"/>
+      <c r="F117" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G117" s="0"/>
+      <c r="H117" s="0"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="0" t="s">
+        <v>460</v>
+      </c>
+      <c r="B118" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C118" s="0">
+        <v>0</v>
+      </c>
+      <c r="D118" s="0"/>
+      <c r="E118" s="0"/>
+      <c r="F118" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G118" s="0"/>
+      <c r="H118" s="0"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="0" t="s">
+        <v>461</v>
+      </c>
+      <c r="B119" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C119" s="0">
+        <v>-1.8275795392708134</v>
+      </c>
+      <c r="D119" s="0"/>
+      <c r="E119" s="0"/>
+      <c r="F119" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G119" s="0"/>
+      <c r="H119" s="0"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="0" t="s">
+        <v>462</v>
+      </c>
+      <c r="B120" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C120" s="0">
+        <v>0</v>
+      </c>
+      <c r="D120" s="0"/>
+      <c r="E120" s="0"/>
+      <c r="F120" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G120" s="0"/>
+      <c r="H120" s="0"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="0" t="s">
+        <v>463</v>
+      </c>
+      <c r="B121" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C121" s="0">
+        <v>1.7526473681977495</v>
+      </c>
+      <c r="D121" s="0"/>
+      <c r="E121" s="0"/>
+      <c r="F121" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G121" s="0"/>
+      <c r="H121" s="0"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="0" t="s">
+        <v>464</v>
+      </c>
+      <c r="B122" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C122" s="0">
+        <v>0.15168253041257554</v>
+      </c>
+      <c r="D122" s="0"/>
+      <c r="E122" s="0"/>
+      <c r="F122" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G122" s="0"/>
+      <c r="H122" s="0"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="0" t="s">
+        <v>465</v>
+      </c>
+      <c r="B123" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C123" s="0">
+        <v>2.4110213483593652</v>
+      </c>
+      <c r="D123" s="0"/>
+      <c r="E123" s="0"/>
+      <c r="F123" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G123" s="0"/>
+      <c r="H123" s="0"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="0" t="s">
+        <v>466</v>
+      </c>
+      <c r="B124" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C124" s="0">
+        <v>2.7131092758196531</v>
+      </c>
+      <c r="D124" s="0"/>
+      <c r="E124" s="0"/>
+      <c r="F124" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G124" s="0"/>
+      <c r="H124" s="0"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="0" t="s">
+        <v>467</v>
+      </c>
+      <c r="B125" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C125" s="0">
+        <v>16.090147165877724</v>
+      </c>
+      <c r="D125" s="0"/>
+      <c r="E125" s="0"/>
+      <c r="F125" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G125" s="0"/>
+      <c r="H125" s="0"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="0" t="s">
+        <v>468</v>
+      </c>
+      <c r="B126" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C126" s="0">
+        <v>16.925292122478595</v>
+      </c>
+      <c r="D126" s="0"/>
+      <c r="E126" s="0"/>
+      <c r="F126" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G126" s="0"/>
+      <c r="H126" s="0"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="0" t="s">
+        <v>469</v>
+      </c>
+      <c r="B127" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C127" s="0">
+        <v>0.35178486510320511</v>
+      </c>
+      <c r="D127" s="0"/>
+      <c r="E127" s="0"/>
+      <c r="F127" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G127" s="0"/>
+      <c r="H127" s="0"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="0" t="s">
+        <v>470</v>
+      </c>
+      <c r="B128" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C128" s="0" t="s">
+        <v>518</v>
+      </c>
+      <c r="D128" s="0"/>
+      <c r="E128" s="0"/>
+      <c r="F128" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G128" s="0"/>
+      <c r="H128" s="0"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="0" t="s">
+        <v>471</v>
+      </c>
+      <c r="B129" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C129" s="0">
+        <v>233.69773788009346</v>
+      </c>
+      <c r="D129" s="0"/>
+      <c r="E129" s="0"/>
+      <c r="F129" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G129" s="0"/>
+      <c r="H129" s="0"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="0" t="s">
+        <v>472</v>
+      </c>
+      <c r="B130" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C130" s="0">
+        <v>0.35242563899228197</v>
+      </c>
+      <c r="D130" s="0"/>
+      <c r="E130" s="0"/>
+      <c r="F130" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G130" s="0"/>
+      <c r="H130" s="0"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="0" t="s">
+        <v>473</v>
+      </c>
+      <c r="B131" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C131" s="0" t="s">
+        <v>518</v>
+      </c>
+      <c r="D131" s="0"/>
+      <c r="E131" s="0"/>
+      <c r="F131" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G131" s="0"/>
+      <c r="H131" s="0"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="0" t="s">
+        <v>474</v>
+      </c>
+      <c r="B132" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C132" s="0">
+        <v>9.4744003772526408</v>
+      </c>
+      <c r="D132" s="0"/>
+      <c r="E132" s="0"/>
+      <c r="F132" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G132" s="0"/>
+      <c r="H132" s="0"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="0" t="s">
+        <v>475</v>
+      </c>
+      <c r="B133" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C133" s="0">
+        <v>341.83792795003058</v>
+      </c>
+      <c r="D133" s="0"/>
+      <c r="E133" s="0"/>
+      <c r="F133" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G133" s="0"/>
+      <c r="H133" s="0"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="0" t="s">
+        <v>476</v>
+      </c>
+      <c r="B134" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C134" s="0">
+        <v>34.733446426726843</v>
+      </c>
+      <c r="D134" s="0"/>
+      <c r="E134" s="0"/>
+      <c r="F134" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G134" s="0"/>
+      <c r="H134" s="0"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="0" t="s">
+        <v>477</v>
+      </c>
+      <c r="B135" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C135" s="0">
+        <v>0.42099254615460552</v>
+      </c>
+      <c r="D135" s="0"/>
+      <c r="E135" s="0"/>
+      <c r="F135" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G135" s="0"/>
+      <c r="H135" s="0"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="0" t="s">
+        <v>478</v>
+      </c>
+      <c r="B136" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C136" s="0">
+        <v>4.0516000000000005</v>
+      </c>
+      <c r="D136" s="0"/>
+      <c r="E136" s="0"/>
+      <c r="F136" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G136" s="0"/>
+      <c r="H136" s="0"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="0" t="s">
+        <v>479</v>
+      </c>
+      <c r="B137" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C137" s="0">
+        <v>39.746196000000005</v>
+      </c>
+      <c r="D137" s="0"/>
+      <c r="E137" s="0"/>
+      <c r="F137" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G137" s="0"/>
+      <c r="H137" s="0"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="0" t="s">
+        <v>480</v>
+      </c>
+      <c r="B138" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C138" s="0">
+        <v>18.230437113682747</v>
+      </c>
+      <c r="D138" s="0"/>
+      <c r="E138" s="0"/>
+      <c r="F138" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G138" s="0"/>
+      <c r="H138" s="0"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="0" t="s">
+        <v>481</v>
+      </c>
+      <c r="B139" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C139" s="0">
+        <v>0.080999999999999989</v>
+      </c>
+      <c r="D139" s="0"/>
+      <c r="E139" s="0"/>
+      <c r="F139" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G139" s="0"/>
+      <c r="H139" s="0"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="0" t="s">
+        <v>482</v>
+      </c>
+      <c r="B140" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C140" s="0">
+        <v>64.749890848167752</v>
+      </c>
+      <c r="D140" s="0"/>
+      <c r="E140" s="0"/>
+      <c r="F140" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G140" s="0"/>
+      <c r="H140" s="0"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="0" t="s">
+        <v>483</v>
+      </c>
+      <c r="B141" s="0" t="s">
+        <v>503</v>
+      </c>
+      <c r="C141" s="0">
+        <v>0.29999999999999999</v>
+      </c>
+      <c r="D141" s="0"/>
+      <c r="E141" s="0"/>
+      <c r="F141" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G141" s="0"/>
+      <c r="H141" s="0"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="0" t="s">
+        <v>484</v>
+      </c>
+      <c r="B142" s="0" t="s">
+        <v>503</v>
+      </c>
+      <c r="C142" s="0">
+        <v>26.360381758366742</v>
+      </c>
+      <c r="D142" s="0"/>
+      <c r="E142" s="0"/>
+      <c r="F142" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G142" s="0"/>
+      <c r="H142" s="0"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="0" t="s">
+        <v>485</v>
+      </c>
+      <c r="B143" s="0" t="s">
+        <v>503</v>
+      </c>
+      <c r="C143" s="0">
+        <v>3.6396182416332579</v>
+      </c>
+      <c r="D143" s="0"/>
+      <c r="E143" s="0"/>
+      <c r="F143" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G143" s="0"/>
+      <c r="H143" s="0"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="0" t="s">
+        <v>486</v>
+      </c>
+      <c r="B144" s="0" t="s">
+        <v>503</v>
+      </c>
+      <c r="C144" s="0">
+        <v>0.25</v>
+      </c>
+      <c r="D144" s="0"/>
+      <c r="E144" s="0"/>
+      <c r="F144" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G144" s="0"/>
+      <c r="H144" s="0"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="0" t="s">
+        <v>487</v>
+      </c>
+      <c r="B145" s="0" t="s">
+        <v>503</v>
+      </c>
+      <c r="C145" s="0">
+        <v>0.69999999999999996</v>
+      </c>
+      <c r="D145" s="0"/>
+      <c r="E145" s="0"/>
+      <c r="F145" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G145" s="0"/>
+      <c r="H145" s="0"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="0" t="s">
+        <v>488</v>
+      </c>
+      <c r="B146" s="0" t="s">
+        <v>503</v>
+      </c>
+      <c r="C146" s="0">
+        <v>1</v>
+      </c>
+      <c r="D146" s="0"/>
+      <c r="E146" s="0"/>
+      <c r="F146" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G146" s="0"/>
+      <c r="H146" s="0"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="0" t="s">
+        <v>489</v>
+      </c>
+      <c r="B147" s="0" t="s">
+        <v>503</v>
+      </c>
+      <c r="C147" s="0">
+        <v>0.12048857500544551</v>
+      </c>
+      <c r="D147" s="0"/>
+      <c r="E147" s="0"/>
+      <c r="F147" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G147" s="0"/>
+      <c r="H147" s="0"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="0" t="s">
+        <v>490</v>
+      </c>
+      <c r="B148" s="0" t="s">
+        <v>503</v>
+      </c>
+      <c r="C148" s="0">
+        <v>119.66043834086311</v>
+      </c>
+      <c r="D148" s="0"/>
+      <c r="E148" s="0"/>
+      <c r="F148" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G148" s="0"/>
+      <c r="H148" s="0"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="0" t="s">
+        <v>491</v>
+      </c>
+      <c r="B149" s="0" t="s">
+        <v>503</v>
+      </c>
+      <c r="C149" s="0">
+        <v>0.074583678423586861</v>
+      </c>
+      <c r="D149" s="0"/>
+      <c r="E149" s="0"/>
+      <c r="F149" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G149" s="0"/>
+      <c r="H149" s="0"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="0" t="s">
+        <v>492</v>
+      </c>
+      <c r="B150" s="0" t="s">
+        <v>503</v>
+      </c>
+      <c r="C150" s="0">
+        <v>1.0700000000000001</v>
+      </c>
+      <c r="D150" s="0"/>
+      <c r="E150" s="0"/>
+      <c r="F150" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G150" s="0"/>
+      <c r="H150" s="0"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="0" t="s">
+        <v>493</v>
+      </c>
+      <c r="B151" s="0" t="s">
+        <v>503</v>
+      </c>
+      <c r="C151" s="0">
+        <v>0.29999999999999999</v>
+      </c>
+      <c r="D151" s="0"/>
+      <c r="E151" s="0"/>
+      <c r="F151" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G151" s="0"/>
+      <c r="H151" s="0"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="0" t="s">
+        <v>494</v>
+      </c>
+      <c r="B152" s="0" t="s">
+        <v>503</v>
+      </c>
+      <c r="C152" s="0">
+        <v>29.162154556467332</v>
+      </c>
+      <c r="D152" s="0"/>
+      <c r="E152" s="0"/>
+      <c r="F152" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G152" s="0"/>
+      <c r="H152" s="0"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="0" t="s">
+        <v>495</v>
+      </c>
+      <c r="B153" s="0" t="s">
+        <v>503</v>
+      </c>
+      <c r="C153" s="0">
+        <v>0.83784544353266455</v>
+      </c>
+      <c r="D153" s="0"/>
+      <c r="E153" s="0"/>
+      <c r="F153" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G153" s="0"/>
+      <c r="H153" s="0"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="0" t="s">
+        <v>496</v>
+      </c>
+      <c r="B154" s="0" t="s">
+        <v>503</v>
+      </c>
+      <c r="C154" s="0">
         <v>5.2740736776131758</v>
       </c>
-      <c r="F16" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>385</v>
-      </c>
-      <c r="B17" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17">
-        <v>-9.4788465253600393E-2</v>
-      </c>
-      <c r="F17" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>386</v>
-      </c>
-      <c r="B18" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18">
-        <v>0.66074594914354523</v>
-      </c>
-      <c r="F18" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>387</v>
-      </c>
-      <c r="B19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19">
-        <v>0.60899778104422941</v>
-      </c>
-      <c r="F19" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>388</v>
-      </c>
-      <c r="B20" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20">
-        <v>1.5753270213496304</v>
-      </c>
-      <c r="F20" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>389</v>
-      </c>
-      <c r="B21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21">
-        <v>0.66074594914354523</v>
-      </c>
-      <c r="F21" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>390</v>
-      </c>
-      <c r="B22" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22">
+      <c r="D154" s="0"/>
+      <c r="E154" s="0"/>
+      <c r="F154" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G154" s="0"/>
+      <c r="H154" s="0"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="0" t="s">
+        <v>497</v>
+      </c>
+      <c r="B155" s="0" t="s">
+        <v>503</v>
+      </c>
+      <c r="C155" s="0">
+        <v>0.3656082203404642</v>
+      </c>
+      <c r="D155" s="0"/>
+      <c r="E155" s="0"/>
+      <c r="F155" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G155" s="0"/>
+      <c r="H155" s="0"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="0" t="s">
+        <v>498</v>
+      </c>
+      <c r="B156" s="0" t="s">
+        <v>503</v>
+      </c>
+      <c r="C156" s="0">
+        <v>0.15</v>
+      </c>
+      <c r="D156" s="0"/>
+      <c r="E156" s="0"/>
+      <c r="F156" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G156" s="0"/>
+      <c r="H156" s="0"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="0" t="s">
+        <v>499</v>
+      </c>
+      <c r="B157" s="0" t="s">
+        <v>503</v>
+      </c>
+      <c r="C157" s="0">
+        <v>-0.79111105164197637</v>
+      </c>
+      <c r="D157" s="0"/>
+      <c r="E157" s="0"/>
+      <c r="F157" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G157" s="0"/>
+      <c r="H157" s="0"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="0" t="s">
+        <v>500</v>
+      </c>
+      <c r="B158" s="0" t="s">
+        <v>503</v>
+      </c>
+      <c r="C158" s="0">
         <v>0.12602616170797043</v>
       </c>
-      <c r="F22" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>327</v>
-      </c>
-      <c r="B23" t="s">
-        <v>56</v>
-      </c>
-      <c r="C23">
-        <v>0.49722452282391244</v>
-      </c>
-      <c r="D23" t="s">
-        <v>66</v>
-      </c>
-      <c r="E23" t="s">
-        <v>359</v>
-      </c>
-      <c r="F23" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>328</v>
-      </c>
-      <c r="B24" t="s">
-        <v>56</v>
-      </c>
-      <c r="C24">
-        <v>0.34410001579509508</v>
-      </c>
-      <c r="D24" t="s">
-        <v>59</v>
-      </c>
-      <c r="E24" t="s">
-        <v>360</v>
-      </c>
-      <c r="F24" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>329</v>
-      </c>
-      <c r="B25" t="s">
-        <v>56</v>
-      </c>
-      <c r="C25">
-        <v>4.3591977074863637</v>
-      </c>
-      <c r="D25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" t="s">
-        <v>361</v>
-      </c>
-      <c r="F25" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>330</v>
-      </c>
-      <c r="B26" t="s">
-        <v>56</v>
-      </c>
-      <c r="C26">
-        <v>8.4528168880065119E-2</v>
-      </c>
-      <c r="D26" t="s">
-        <v>66</v>
-      </c>
-      <c r="E26" t="s">
-        <v>362</v>
-      </c>
-      <c r="F26" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>331</v>
-      </c>
-      <c r="B27" t="s">
-        <v>56</v>
-      </c>
-      <c r="C27">
-        <v>0.45969601064199239</v>
-      </c>
-      <c r="D27" t="s">
-        <v>59</v>
-      </c>
-      <c r="E27" t="s">
-        <v>363</v>
-      </c>
-      <c r="F27" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>332</v>
-      </c>
-      <c r="B28" t="s">
-        <v>56</v>
-      </c>
-      <c r="C28">
-        <v>0.18387840425679697</v>
-      </c>
-      <c r="D28" t="s">
-        <v>59</v>
-      </c>
-      <c r="E28" t="s">
-        <v>364</v>
-      </c>
-      <c r="F28" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>333</v>
-      </c>
-      <c r="B29" t="s">
-        <v>56</v>
-      </c>
-      <c r="C29">
-        <v>0.39523392547876368</v>
-      </c>
-      <c r="D29" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" t="s">
-        <v>365</v>
-      </c>
-      <c r="F29" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>334</v>
-      </c>
-      <c r="B30" t="s">
-        <v>56</v>
-      </c>
-      <c r="C30">
-        <v>7.4583678423586861E-2</v>
-      </c>
-      <c r="D30" t="s">
-        <v>66</v>
-      </c>
-      <c r="E30" t="s">
-        <v>366</v>
-      </c>
-      <c r="F30" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>335</v>
-      </c>
-      <c r="B31" t="s">
-        <v>56</v>
-      </c>
-      <c r="C31">
-        <v>7.4583678423586861E-2</v>
-      </c>
-      <c r="D31" t="s">
-        <v>66</v>
-      </c>
-      <c r="E31" t="s">
-        <v>367</v>
-      </c>
-      <c r="F31" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>336</v>
-      </c>
-      <c r="B32" t="s">
-        <v>56</v>
-      </c>
-      <c r="C32">
-        <v>0.28249696620183012</v>
-      </c>
-      <c r="D32" t="s">
-        <v>59</v>
-      </c>
-      <c r="E32" t="s">
-        <v>368</v>
-      </c>
-      <c r="F32" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>337</v>
-      </c>
-      <c r="B33" t="s">
-        <v>56</v>
-      </c>
-      <c r="C33">
-        <v>0.26401585626339263</v>
-      </c>
-      <c r="D33" t="s">
-        <v>59</v>
-      </c>
-      <c r="E33" t="s">
-        <v>369</v>
-      </c>
-      <c r="F33" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>391</v>
-      </c>
-      <c r="B34" t="s">
-        <v>56</v>
-      </c>
-      <c r="C34">
-        <v>1.8046437163813135E-2</v>
-      </c>
-      <c r="F34" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>392</v>
-      </c>
-      <c r="B35" t="s">
-        <v>56</v>
-      </c>
-      <c r="C35">
-        <v>0.23885083680507355</v>
-      </c>
-      <c r="F35" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>393</v>
-      </c>
-      <c r="B36" t="s">
-        <v>56</v>
-      </c>
-      <c r="C36">
-        <v>0.3656082203404642</v>
-      </c>
-      <c r="F36" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>394</v>
-      </c>
-      <c r="B37" t="s">
-        <v>56</v>
-      </c>
-      <c r="C37">
-        <v>0.2156082203404642</v>
-      </c>
-      <c r="F37" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>167</v>
-      </c>
-      <c r="B38" t="s">
-        <v>136</v>
-      </c>
-      <c r="C38">
-        <v>4.0516000000000005</v>
-      </c>
-      <c r="F38" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>338</v>
-      </c>
-      <c r="B39" t="s">
-        <v>136</v>
-      </c>
-      <c r="C39">
-        <v>22.737783592977756</v>
-      </c>
-      <c r="D39" t="s">
-        <v>137</v>
-      </c>
-      <c r="E39" t="s">
-        <v>370</v>
-      </c>
-      <c r="F39" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>339</v>
-      </c>
-      <c r="B40" t="s">
-        <v>136</v>
-      </c>
-      <c r="C40">
-        <v>11</v>
-      </c>
-      <c r="D40" t="s">
-        <v>137</v>
-      </c>
-      <c r="E40" t="s">
-        <v>371</v>
-      </c>
-      <c r="F40" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>340</v>
-      </c>
-      <c r="B41" t="s">
-        <v>136</v>
-      </c>
-      <c r="C41">
-        <v>14.810748414335091</v>
-      </c>
-      <c r="D41" t="s">
-        <v>137</v>
-      </c>
-      <c r="E41" t="s">
-        <v>372</v>
-      </c>
-      <c r="F41" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>341</v>
-      </c>
-      <c r="B42" t="s">
-        <v>136</v>
-      </c>
-      <c r="C42">
-        <v>12.24744871391589</v>
-      </c>
-      <c r="D42" t="s">
-        <v>137</v>
-      </c>
-      <c r="E42" t="s">
-        <v>373</v>
-      </c>
-      <c r="F42" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>342</v>
-      </c>
-      <c r="B43" t="s">
-        <v>136</v>
-      </c>
-      <c r="C43">
-        <v>48.189685104221404</v>
-      </c>
-      <c r="D43" t="s">
-        <v>23</v>
-      </c>
-      <c r="E43" t="s">
-        <v>374</v>
-      </c>
-      <c r="F43" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>343</v>
-      </c>
-      <c r="B44" t="s">
-        <v>136</v>
-      </c>
-      <c r="C44">
-        <v>16.699244233993625</v>
-      </c>
-      <c r="D44" t="s">
-        <v>23</v>
-      </c>
-      <c r="E44" t="s">
-        <v>375</v>
-      </c>
-      <c r="F44" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>344</v>
-      </c>
-      <c r="B45" t="s">
-        <v>136</v>
-      </c>
-      <c r="C45">
-        <v>39.746196000000005</v>
-      </c>
-      <c r="D45" t="s">
-        <v>348</v>
-      </c>
-      <c r="E45" t="s">
-        <v>376</v>
-      </c>
-      <c r="F45" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>345</v>
-      </c>
-      <c r="B46" t="s">
-        <v>136</v>
-      </c>
-      <c r="C46">
-        <v>0.44283295832701008</v>
-      </c>
-      <c r="F46" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>346</v>
-      </c>
-      <c r="B47" t="s">
-        <v>136</v>
-      </c>
-      <c r="C47">
-        <v>233372.96903833433</v>
-      </c>
-      <c r="F47" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>347</v>
-      </c>
-      <c r="B48" t="s">
-        <v>136</v>
-      </c>
-      <c r="C48">
-        <v>130688.86266146721</v>
-      </c>
-      <c r="F48" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>395</v>
-      </c>
-      <c r="B49" t="s">
-        <v>136</v>
-      </c>
-      <c r="C49">
-        <v>34.144135350668904</v>
-      </c>
-      <c r="F49" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>396</v>
-      </c>
-      <c r="B50" t="s">
-        <v>136</v>
-      </c>
-      <c r="C50">
-        <v>15.480365443172449</v>
-      </c>
-      <c r="F50" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>397</v>
-      </c>
-      <c r="B51" t="s">
-        <v>136</v>
-      </c>
-      <c r="C51">
-        <v>3.8</v>
-      </c>
-      <c r="F51" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>398</v>
-      </c>
-      <c r="B52" t="s">
-        <v>136</v>
-      </c>
-      <c r="C52">
-        <v>-1.52</v>
-      </c>
-      <c r="F52" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>399</v>
-      </c>
-      <c r="B53" t="s">
-        <v>136</v>
-      </c>
-      <c r="C53">
-        <v>5.6999999999999993</v>
-      </c>
-      <c r="F53" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>400</v>
-      </c>
-      <c r="B54" t="s">
-        <v>136</v>
-      </c>
-      <c r="C54">
-        <v>-2.2800000000000002</v>
-      </c>
-      <c r="F54" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>401</v>
-      </c>
-      <c r="B55" t="s">
-        <v>136</v>
-      </c>
-      <c r="C55">
-        <v>18.622682892532463</v>
-      </c>
-      <c r="F55" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>402</v>
-      </c>
-      <c r="B56" t="s">
-        <v>136</v>
-      </c>
-      <c r="C56">
-        <v>27.131986877647702</v>
-      </c>
-      <c r="F56" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>403</v>
-      </c>
-      <c r="B57" t="s">
-        <v>136</v>
-      </c>
-      <c r="C57">
-        <v>25.580006542099976</v>
-      </c>
-      <c r="F57" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>404</v>
-      </c>
-      <c r="B58" t="s">
-        <v>136</v>
-      </c>
-      <c r="C58">
-        <v>28.422229491222197</v>
-      </c>
-      <c r="F58" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>405</v>
-      </c>
-      <c r="B59" t="s">
-        <v>136</v>
-      </c>
-      <c r="C59">
-        <v>6.3586494759793881</v>
-      </c>
-      <c r="F59" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>406</v>
-      </c>
-      <c r="B60" t="s">
-        <v>136</v>
-      </c>
-      <c r="C60">
-        <v>12.884684205822825</v>
-      </c>
-      <c r="F60" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>407</v>
-      </c>
-      <c r="B61" t="s">
-        <v>136</v>
-      </c>
-      <c r="C61">
-        <v>2.2299999999999964</v>
-      </c>
-      <c r="F61" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>408</v>
-      </c>
-      <c r="B62" t="s">
-        <v>136</v>
-      </c>
-      <c r="C62">
-        <v>11.011406321896699</v>
-      </c>
-      <c r="F62" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>409</v>
-      </c>
-      <c r="B63" t="s">
-        <v>136</v>
-      </c>
-      <c r="C63" t="b">
-        <v>1</v>
-      </c>
-      <c r="F63" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>410</v>
-      </c>
-      <c r="B64" t="s">
-        <v>136</v>
-      </c>
-      <c r="C64">
-        <v>5.6667672012645314</v>
-      </c>
-      <c r="F64" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>411</v>
-      </c>
-      <c r="B65" t="s">
-        <v>136</v>
-      </c>
-      <c r="C65">
-        <v>19.023298859748962</v>
-      </c>
-      <c r="F65" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>412</v>
-      </c>
-      <c r="B66" t="s">
-        <v>136</v>
-      </c>
-      <c r="C66">
-        <v>5.2940237236683272</v>
-      </c>
-      <c r="F66" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
-        <v>413</v>
-      </c>
-      <c r="B67" t="s">
-        <v>136</v>
-      </c>
-      <c r="C67">
-        <v>22.608098531363336</v>
-      </c>
-      <c r="F67" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
-        <v>414</v>
-      </c>
-      <c r="B68" t="s">
-        <v>136</v>
-      </c>
-      <c r="C68">
-        <v>12.709922788411269</v>
-      </c>
-      <c r="F68" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>415</v>
-      </c>
-      <c r="B69" t="s">
-        <v>136</v>
-      </c>
-      <c r="C69">
-        <v>16.27392540932771</v>
-      </c>
-      <c r="F69" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
-        <v>416</v>
-      </c>
-      <c r="B70" t="s">
-        <v>136</v>
-      </c>
-      <c r="C70">
-        <v>15.956485750905872</v>
-      </c>
-      <c r="F70" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>417</v>
-      </c>
-      <c r="B71" t="s">
-        <v>136</v>
-      </c>
-      <c r="C71">
-        <v>13.695854805920606</v>
-      </c>
-      <c r="F71" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>418</v>
-      </c>
-      <c r="B72" t="s">
-        <v>136</v>
-      </c>
-      <c r="C72">
-        <v>1.0954451150103324</v>
-      </c>
-      <c r="F72" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>419</v>
-      </c>
-      <c r="B73" t="s">
-        <v>136</v>
-      </c>
-      <c r="C73">
-        <v>24.094842552110709</v>
-      </c>
-      <c r="F73" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
-        <v>420</v>
-      </c>
-      <c r="B74" t="s">
-        <v>136</v>
-      </c>
-      <c r="C74" t="b">
-        <v>1</v>
-      </c>
-      <c r="F74" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>421</v>
-      </c>
-      <c r="B75" t="s">
-        <v>136</v>
-      </c>
-      <c r="C75">
-        <v>156.52835771396133</v>
-      </c>
-      <c r="F75" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
-        <v>422</v>
-      </c>
-      <c r="B76" t="s">
-        <v>136</v>
-      </c>
-      <c r="C76">
-        <v>44593.916314433394</v>
-      </c>
-      <c r="F76" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
-        <v>423</v>
-      </c>
-      <c r="B77" t="s">
-        <v>136</v>
-      </c>
-      <c r="C77" t="b">
-        <v>1</v>
-      </c>
-      <c r="F77" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
-        <v>424</v>
-      </c>
-      <c r="B78" t="s">
-        <v>136</v>
-      </c>
-      <c r="C78" t="b">
-        <v>1</v>
-      </c>
-      <c r="F78" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
-        <v>425</v>
-      </c>
-      <c r="B79" t="s">
-        <v>136</v>
-      </c>
-      <c r="C79">
-        <v>13</v>
-      </c>
-      <c r="F79" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
-        <v>426</v>
-      </c>
-      <c r="B80" t="s">
-        <v>136</v>
-      </c>
-      <c r="C80">
-        <v>86094.946347033809</v>
-      </c>
-      <c r="F80" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
-        <v>427</v>
-      </c>
-      <c r="B81" t="s">
-        <v>136</v>
-      </c>
-      <c r="C81">
-        <v>0.16336801963384023</v>
-      </c>
-      <c r="F81" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
-        <v>428</v>
-      </c>
-      <c r="B82" t="s">
-        <v>136</v>
-      </c>
-      <c r="C82">
-        <v>2.185902626124927</v>
-      </c>
-      <c r="F82" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
-        <v>429</v>
-      </c>
-      <c r="B83" t="s">
-        <v>170</v>
-      </c>
-      <c r="C83" t="s">
-        <v>505</v>
-      </c>
-      <c r="F83" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
-        <v>430</v>
-      </c>
-      <c r="B84" t="s">
-        <v>170</v>
-      </c>
-      <c r="C84">
-        <v>-4.0973254512723323E-2</v>
-      </c>
-      <c r="F84" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
-        <v>431</v>
-      </c>
-      <c r="B85" t="s">
-        <v>170</v>
-      </c>
-      <c r="C85" t="b">
-        <v>0</v>
-      </c>
-      <c r="F85" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
-        <v>432</v>
-      </c>
-      <c r="B86" t="s">
-        <v>170</v>
-      </c>
-      <c r="C86">
-        <v>0.254</v>
-      </c>
-      <c r="F86" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
-        <v>433</v>
-      </c>
-      <c r="B87" t="s">
-        <v>170</v>
-      </c>
-      <c r="C87">
-        <v>0.127</v>
-      </c>
-      <c r="F87" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
-        <v>434</v>
-      </c>
-      <c r="B88" t="s">
-        <v>170</v>
-      </c>
-      <c r="C88">
-        <v>14500</v>
-      </c>
-      <c r="F88" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
-        <v>435</v>
-      </c>
-      <c r="B89" t="s">
-        <v>170</v>
-      </c>
-      <c r="C89" t="s">
-        <v>506</v>
-      </c>
-      <c r="F89" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
-        <v>436</v>
-      </c>
-      <c r="B90" t="s">
-        <v>170</v>
-      </c>
-      <c r="C90" t="s">
-        <v>507</v>
-      </c>
-      <c r="F90" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
-        <v>437</v>
-      </c>
-      <c r="B91" t="s">
-        <v>170</v>
-      </c>
-      <c r="C91" t="s">
-        <v>508</v>
-      </c>
-      <c r="F91" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
-        <v>438</v>
-      </c>
-      <c r="B92" t="s">
-        <v>170</v>
-      </c>
-      <c r="C92" t="s">
-        <v>508</v>
-      </c>
-      <c r="F92" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
-        <v>439</v>
-      </c>
-      <c r="B93" t="s">
-        <v>170</v>
-      </c>
-      <c r="C93" t="s">
-        <v>508</v>
-      </c>
-      <c r="F93" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
-        <v>440</v>
-      </c>
-      <c r="B94" t="s">
-        <v>170</v>
-      </c>
-      <c r="C94" t="s">
-        <v>508</v>
-      </c>
-      <c r="F94" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
-        <v>441</v>
-      </c>
-      <c r="B95" t="s">
-        <v>170</v>
-      </c>
-      <c r="C95" t="s">
-        <v>508</v>
-      </c>
-      <c r="F95" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
-        <v>442</v>
-      </c>
-      <c r="B96" t="s">
-        <v>170</v>
-      </c>
-      <c r="C96" t="s">
-        <v>508</v>
-      </c>
-      <c r="F96" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
-        <v>443</v>
-      </c>
-      <c r="B97" t="s">
-        <v>170</v>
-      </c>
-      <c r="C97" t="s">
-        <v>508</v>
-      </c>
-      <c r="F97" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
-        <v>444</v>
-      </c>
-      <c r="B98" t="s">
-        <v>170</v>
-      </c>
-      <c r="C98" t="s">
-        <v>508</v>
-      </c>
-      <c r="F98" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
-        <v>445</v>
-      </c>
-      <c r="B99" t="s">
-        <v>170</v>
-      </c>
-      <c r="C99" t="s">
-        <v>509</v>
-      </c>
-      <c r="F99" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
-        <v>446</v>
-      </c>
-      <c r="B100" t="s">
-        <v>170</v>
-      </c>
-      <c r="C100">
-        <v>700</v>
-      </c>
-      <c r="F100" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
-        <v>447</v>
-      </c>
-      <c r="B101" t="s">
-        <v>170</v>
-      </c>
-      <c r="C101">
-        <v>50</v>
-      </c>
-      <c r="F101" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
-        <v>448</v>
-      </c>
-      <c r="B102" t="s">
-        <v>170</v>
-      </c>
-      <c r="C102" t="s">
-        <v>510</v>
-      </c>
-      <c r="F102" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
-        <v>449</v>
-      </c>
-      <c r="B103" t="s">
-        <v>170</v>
-      </c>
-      <c r="C103" t="s">
-        <v>508</v>
-      </c>
-      <c r="F103" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
-        <v>450</v>
-      </c>
-      <c r="B104" t="s">
-        <v>170</v>
-      </c>
-      <c r="C104" t="s">
-        <v>511</v>
-      </c>
-      <c r="F104" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
-        <v>451</v>
-      </c>
-      <c r="B105" t="s">
-        <v>170</v>
-      </c>
-      <c r="C105" t="s">
-        <v>512</v>
-      </c>
-      <c r="F105" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
-        <v>452</v>
-      </c>
-      <c r="B106" t="s">
-        <v>170</v>
-      </c>
-      <c r="C106" t="s">
-        <v>513</v>
-      </c>
-      <c r="F106" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
-        <v>453</v>
-      </c>
-      <c r="B107" t="s">
-        <v>170</v>
-      </c>
-      <c r="C107" t="s">
-        <v>514</v>
-      </c>
-      <c r="F107" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
-        <v>454</v>
-      </c>
-      <c r="B108" t="s">
-        <v>170</v>
-      </c>
-      <c r="C108" t="s">
-        <v>515</v>
-      </c>
-      <c r="F108" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
-        <v>455</v>
-      </c>
-      <c r="B109" t="s">
-        <v>170</v>
-      </c>
-      <c r="C109" t="s">
-        <v>516</v>
-      </c>
-      <c r="F109" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
-        <v>456</v>
-      </c>
-      <c r="B110" t="s">
-        <v>170</v>
-      </c>
-      <c r="C110" t="s">
-        <v>517</v>
-      </c>
-      <c r="F110" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
-        <v>457</v>
-      </c>
-      <c r="B111" t="s">
-        <v>265</v>
-      </c>
-      <c r="C111">
-        <v>32.946133306980855</v>
-      </c>
-      <c r="F111" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
-        <v>458</v>
-      </c>
-      <c r="B112" t="s">
-        <v>265</v>
-      </c>
-      <c r="C112">
-        <v>0</v>
-      </c>
-      <c r="F112" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" t="s">
-        <v>459</v>
-      </c>
-      <c r="B113" t="s">
-        <v>265</v>
-      </c>
-      <c r="C113" t="s">
-        <v>518</v>
-      </c>
-      <c r="F113" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
-        <v>460</v>
-      </c>
-      <c r="B114" t="s">
-        <v>265</v>
-      </c>
-      <c r="C114">
-        <v>86.068285472894019</v>
-      </c>
-      <c r="F114" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
-        <v>461</v>
-      </c>
-      <c r="B115" t="s">
-        <v>265</v>
-      </c>
-      <c r="C115">
-        <v>0</v>
-      </c>
-      <c r="F115" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" t="s">
-        <v>462</v>
-      </c>
-      <c r="B116" t="s">
-        <v>265</v>
-      </c>
-      <c r="C116">
-        <v>-1.8275795392708134</v>
-      </c>
-      <c r="F116" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
-        <v>463</v>
-      </c>
-      <c r="B117" t="s">
-        <v>265</v>
-      </c>
-      <c r="C117">
-        <v>0</v>
-      </c>
-      <c r="F117" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" t="s">
-        <v>464</v>
-      </c>
-      <c r="B118" t="s">
-        <v>265</v>
-      </c>
-      <c r="C118">
-        <v>1.7526473681977495</v>
-      </c>
-      <c r="F118" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" t="s">
-        <v>465</v>
-      </c>
-      <c r="B119" t="s">
-        <v>265</v>
-      </c>
-      <c r="C119">
-        <v>0.15168253041257554</v>
-      </c>
-      <c r="F119" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" t="s">
-        <v>466</v>
-      </c>
-      <c r="B120" t="s">
-        <v>265</v>
-      </c>
-      <c r="C120">
-        <v>2.4110213483593652</v>
-      </c>
-      <c r="F120" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" t="s">
-        <v>467</v>
-      </c>
-      <c r="B121" t="s">
-        <v>265</v>
-      </c>
-      <c r="C121">
-        <v>2.7131092758196531</v>
-      </c>
-      <c r="F121" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" t="s">
-        <v>468</v>
-      </c>
-      <c r="B122" t="s">
-        <v>265</v>
-      </c>
-      <c r="C122">
-        <v>16.090147165877724</v>
-      </c>
-      <c r="F122" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" t="s">
-        <v>469</v>
-      </c>
-      <c r="B123" t="s">
-        <v>265</v>
-      </c>
-      <c r="C123">
-        <v>16.925292122478595</v>
-      </c>
-      <c r="F123" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" t="s">
-        <v>470</v>
-      </c>
-      <c r="B124" t="s">
-        <v>265</v>
-      </c>
-      <c r="C124">
-        <v>0.35178486510320511</v>
-      </c>
-      <c r="F124" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" t="s">
-        <v>471</v>
-      </c>
-      <c r="B125" t="s">
-        <v>265</v>
-      </c>
-      <c r="C125" t="s">
-        <v>519</v>
-      </c>
-      <c r="F125" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" t="s">
-        <v>472</v>
-      </c>
-      <c r="B126" t="s">
-        <v>265</v>
-      </c>
-      <c r="C126">
-        <v>233.69773788009346</v>
-      </c>
-      <c r="F126" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" t="s">
-        <v>473</v>
-      </c>
-      <c r="B127" t="s">
-        <v>265</v>
-      </c>
-      <c r="C127">
-        <v>0.35242563899228196</v>
-      </c>
-      <c r="F127" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" t="s">
-        <v>474</v>
-      </c>
-      <c r="B128" t="s">
-        <v>265</v>
-      </c>
-      <c r="C128" t="s">
-        <v>519</v>
-      </c>
-      <c r="F128" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" t="s">
-        <v>475</v>
-      </c>
-      <c r="B129" t="s">
-        <v>265</v>
-      </c>
-      <c r="C129">
-        <v>9.4744003772526408</v>
-      </c>
-      <c r="F129" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" t="s">
-        <v>476</v>
-      </c>
-      <c r="B130" t="s">
-        <v>265</v>
-      </c>
-      <c r="C130">
-        <v>341.83792795003058</v>
-      </c>
-      <c r="F130" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" t="s">
-        <v>477</v>
-      </c>
-      <c r="B131" t="s">
-        <v>265</v>
-      </c>
-      <c r="C131">
-        <v>34.733446426726843</v>
-      </c>
-      <c r="F131" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" t="s">
-        <v>478</v>
-      </c>
-      <c r="B132" t="s">
-        <v>265</v>
-      </c>
-      <c r="C132">
-        <v>0.42099254615460552</v>
-      </c>
-      <c r="F132" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" t="s">
-        <v>479</v>
-      </c>
-      <c r="B133" t="s">
-        <v>265</v>
-      </c>
-      <c r="C133">
-        <v>4.0516000000000005</v>
-      </c>
-      <c r="F133" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" t="s">
-        <v>480</v>
-      </c>
-      <c r="B134" t="s">
-        <v>265</v>
-      </c>
-      <c r="C134">
-        <v>39.746196000000005</v>
-      </c>
-      <c r="F134" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" t="s">
-        <v>481</v>
-      </c>
-      <c r="B135" t="s">
-        <v>265</v>
-      </c>
-      <c r="C135">
-        <v>18.230437113682747</v>
-      </c>
-      <c r="F135" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" t="s">
-        <v>482</v>
-      </c>
-      <c r="B136" t="s">
-        <v>265</v>
-      </c>
-      <c r="C136">
-        <v>8.0999999999999989E-2</v>
-      </c>
-      <c r="F136" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" t="s">
-        <v>483</v>
-      </c>
-      <c r="B137" t="s">
-        <v>265</v>
-      </c>
-      <c r="C137">
-        <v>64.749890848167752</v>
-      </c>
-      <c r="F137" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" t="s">
-        <v>484</v>
-      </c>
-      <c r="B138" t="s">
-        <v>504</v>
-      </c>
-      <c r="C138">
-        <v>0.3</v>
-      </c>
-      <c r="F138" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" t="s">
-        <v>485</v>
-      </c>
-      <c r="B139" t="s">
-        <v>504</v>
-      </c>
-      <c r="C139">
-        <v>26.360381758366742</v>
-      </c>
-      <c r="F139" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" t="s">
-        <v>486</v>
-      </c>
-      <c r="B140" t="s">
-        <v>504</v>
-      </c>
-      <c r="C140">
-        <v>3.6396182416332579</v>
-      </c>
-      <c r="F140" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" t="s">
-        <v>487</v>
-      </c>
-      <c r="B141" t="s">
-        <v>504</v>
-      </c>
-      <c r="C141">
-        <v>0.25</v>
-      </c>
-      <c r="F141" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" t="s">
-        <v>488</v>
-      </c>
-      <c r="B142" t="s">
-        <v>504</v>
-      </c>
-      <c r="C142">
-        <v>0.7</v>
-      </c>
-      <c r="F142" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" t="s">
-        <v>489</v>
-      </c>
-      <c r="B143" t="s">
-        <v>504</v>
-      </c>
-      <c r="C143">
-        <v>1</v>
-      </c>
-      <c r="F143" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A144" t="s">
-        <v>490</v>
-      </c>
-      <c r="B144" t="s">
-        <v>504</v>
-      </c>
-      <c r="C144">
-        <v>0.12048857500544551</v>
-      </c>
-      <c r="F144" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A145" t="s">
-        <v>491</v>
-      </c>
-      <c r="B145" t="s">
-        <v>504</v>
-      </c>
-      <c r="C145">
-        <v>119.66043834086311</v>
-      </c>
-      <c r="F145" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A146" t="s">
-        <v>492</v>
-      </c>
-      <c r="B146" t="s">
-        <v>504</v>
-      </c>
-      <c r="C146">
-        <v>7.4583678423586861E-2</v>
-      </c>
-      <c r="F146" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A147" t="s">
-        <v>493</v>
-      </c>
-      <c r="B147" t="s">
-        <v>504</v>
-      </c>
-      <c r="C147">
-        <v>1.07</v>
-      </c>
-      <c r="F147" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A148" t="s">
-        <v>494</v>
-      </c>
-      <c r="B148" t="s">
-        <v>504</v>
-      </c>
-      <c r="C148">
-        <v>0.3</v>
-      </c>
-      <c r="F148" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A149" t="s">
-        <v>495</v>
-      </c>
-      <c r="B149" t="s">
-        <v>504</v>
-      </c>
-      <c r="C149">
-        <v>29.162154556467332</v>
-      </c>
-      <c r="F149" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A150" t="s">
-        <v>496</v>
-      </c>
-      <c r="B150" t="s">
-        <v>504</v>
-      </c>
-      <c r="C150">
-        <v>0.83784544353266455</v>
-      </c>
-      <c r="F150" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A151" t="s">
-        <v>497</v>
-      </c>
-      <c r="B151" t="s">
-        <v>504</v>
-      </c>
-      <c r="C151">
-        <v>5.2740736776131758</v>
-      </c>
-      <c r="F151" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A152" t="s">
-        <v>498</v>
-      </c>
-      <c r="B152" t="s">
-        <v>504</v>
-      </c>
-      <c r="C152">
-        <v>0.3656082203404642</v>
-      </c>
-      <c r="F152" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A153" t="s">
-        <v>499</v>
-      </c>
-      <c r="B153" t="s">
-        <v>504</v>
-      </c>
-      <c r="C153">
-        <v>0.15</v>
-      </c>
-      <c r="F153" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A154" t="s">
-        <v>500</v>
-      </c>
-      <c r="B154" t="s">
-        <v>504</v>
-      </c>
-      <c r="C154">
-        <v>-0.79111105164197637</v>
-      </c>
-      <c r="F154" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A155" t="s">
+      <c r="D158" s="0"/>
+      <c r="E158" s="0"/>
+      <c r="F158" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G158" s="0"/>
+      <c r="H158" s="0"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="0" t="s">
         <v>501</v>
       </c>
-      <c r="B155" t="s">
-        <v>504</v>
-      </c>
-      <c r="C155">
-        <v>0.12602616170797043</v>
-      </c>
-      <c r="F155" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A156" t="s">
+      <c r="B159" s="0" t="s">
+        <v>503</v>
+      </c>
+      <c r="C159" s="0">
+        <v>5</v>
+      </c>
+      <c r="D159" s="0"/>
+      <c r="E159" s="0"/>
+      <c r="F159" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G159" s="0"/>
+      <c r="H159" s="0"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="0" t="s">
         <v>502</v>
       </c>
-      <c r="B156" t="s">
-        <v>504</v>
-      </c>
-      <c r="C156">
-        <v>5</v>
-      </c>
-      <c r="F156" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A157" t="s">
+      <c r="B160" s="0" t="s">
         <v>503</v>
       </c>
-      <c r="B157" t="s">
-        <v>504</v>
-      </c>
-      <c r="C157">
+      <c r="C160" s="0">
         <v>-0.18486997339978403</v>
       </c>
-      <c r="F157" t="s">
-        <v>378</v>
-      </c>
+      <c r="D160" s="0"/>
+      <c r="E160" s="0"/>
+      <c r="F160" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="G160" s="0"/>
+      <c r="H160" s="0"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6395,7 +7028,7 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="22" t="s">
         <v>277</v>
       </c>
       <c r="B3" s="21">
@@ -6437,7 +7070,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="22" t="s">
         <v>304</v>
       </c>
       <c r="B6" s="21">
@@ -6563,7 +7196,7 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="23" t="s">
+      <c r="A15" s="22" t="s">
         <v>288</v>
       </c>
       <c r="B15" s="21">
@@ -7153,20 +7786,20 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="C109:F109"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="11.5546875" customWidth="1"/>
-    <col min="6" max="6" width="142.44140625" customWidth="1"/>
+    <col min="3" max="3" width="11.5546875" customWidth="true"/>
+    <col min="6" max="6" width="142.44140625" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="109" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C109">
-        <v>12.250154543435004</v>
-      </c>
-      <c r="F109" t="s">
-        <v>380</v>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="109" x14ac:dyDescent="0.3">
+      <c r="C109" s="0">
+        <v>11.941543440928031</v>
+      </c>
+      <c r="F109" s="0" t="s">
+        <v>379</v>
       </c>
     </row>
   </sheetData>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,18 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\Fall 2026\AAE 451\451-DBF-Team01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37DAE441-3691-47BB-B387-517F08F01369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B01D57E5-C52D-43CD-AF1B-338C7A96A113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs" sheetId="1" r:id="rId1"/>
     <sheet name="Outputs" sheetId="4" r:id="rId2"/>
     <sheet name="MassBudget" sheetId="3" r:id="rId3"/>
     <sheet name="Hinge Moments" sheetId="2" r:id="rId4"/>
-    <sheet name="Sheet1" sheetId="5" r:id="rId8"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="true"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1386" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="541">
   <si>
     <t>Parameter</t>
   </si>
@@ -1179,12 +1179,6 @@
     <t>Overwritten input (Sheet1 value: 6)</t>
   </si>
   <si>
-    <t>Written by writeOutputs.m on 2026-10-06 13:51</t>
-  </si>
-  <si>
-    <t>Written by writeOutputs.m on 2026-10-06 13:54</t>
-  </si>
-  <si>
     <t>COMPUTED each run by MaxPayloadSweep.m = 1.25x the baseline self-consistent stall speed -- not read back in as an input, edit LANDING_SPEED_RATIO in that script instead.</t>
   </si>
   <si>
@@ -1606,18 +1600,78 @@
   </si>
   <si>
     <t>Written by writeOutputs.m on 2026-10-06 13:56</t>
+  </si>
+  <si>
+    <t>materials</t>
+  </si>
+  <si>
+    <t>MPa</t>
+  </si>
+  <si>
+    <t>width_spar</t>
+  </si>
+  <si>
+    <t>length_spar</t>
+  </si>
+  <si>
+    <t>fa_plywood</t>
+  </si>
+  <si>
+    <t>width_tail_boom</t>
+  </si>
+  <si>
+    <t>length_tail_boom</t>
+  </si>
+  <si>
+    <t>wall_thick_spar</t>
+  </si>
+  <si>
+    <t>wall_thick_tail_boom</t>
+  </si>
+  <si>
+    <t>fty_al_6061_t6</t>
+  </si>
+  <si>
+    <t>fbry_al_6061_t6</t>
+  </si>
+  <si>
+    <t>fsu_al_6061_t6</t>
+  </si>
+  <si>
+    <t>E_al_6061_t6</t>
+  </si>
+  <si>
+    <t>height_fuselage</t>
+  </si>
+  <si>
+    <t>wall_thick_fuselage</t>
+  </si>
+  <si>
+    <t>gear_strut_angle</t>
+  </si>
+  <si>
+    <t>gear_strut_thickness</t>
+  </si>
+  <si>
+    <t>gear_strut_length</t>
+  </si>
+  <si>
+    <t>gear_strut_width_max</t>
+  </si>
+  <si>
+    <t>gear_strut_width_min</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1713,12 +1767,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79995117038484"/>
+        <fgColor theme="5" tint="0.79995117038483843"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1726,57 +1780,64 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border/>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="true"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="true"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="true" applyFill="true"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="true"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="true"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="true"/>
-    <xf numFmtId="166" fontId="5" fillId="3" borderId="0" xfId="1" applyNumberFormat="true" applyFont="true" applyFill="true"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="1" applyNumberFormat="true" applyFont="true" applyFill="true"/>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="0" xfId="1" applyNumberFormat="true" applyFont="true" applyFill="true"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="true"/>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="0" xfId="1" applyNumberFormat="true" applyFont="true" applyFill="true"/>
-    <xf numFmtId="2" fontId="6" fillId="4" borderId="0" xfId="1" applyNumberFormat="true" applyFont="true" applyFill="true"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="1" applyFont="true" applyFill="true"/>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="1" applyNumberFormat="true" applyFill="true"/>
-    <xf numFmtId="166" fontId="5" fillId="5" borderId="0" xfId="1" applyNumberFormat="true" applyFont="true" applyFill="true"/>
-    <xf numFmtId="2" fontId="5" fillId="5" borderId="0" xfId="1" applyNumberFormat="true" applyFont="true" applyFill="true"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="6" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="5" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" justifyLastLine="false" shrinkToFit="false" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" justifyLastLine="false" shrinkToFit="false" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" justifyLastLine="false" shrinkToFit="false" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1792,40 +1853,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" id="1" name="Table1" displayName="Table1" ref="A1:F109" totalsRowShown="false">
-  <autoFilter ref="A1:F109"/>
-  <sortState ref="A2:E43">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:F141" totalsRowShown="0">
+  <autoFilter ref="A1:F141" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E43">
     <sortCondition ref="B1:B101"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" name="Parameter"/>
-    <tableColumn id="2" name="Subclass" dataDxfId="2"/>
-    <tableColumn id="3" name="Value" dataDxfId="1"/>
-    <tableColumn id="4" name="Units" dataDxfId="0"/>
-    <tableColumn id="5" name="Description"/>
-    <tableColumn id="6" name="Notes"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Parameter"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Subclass" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Value" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Units" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Description"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Notes"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium15" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" id="2" name="Table2" displayName="Table2" ref="A1:F34" totalsRowShown="false">
-  <autoFilter ref="A1:F34"/>
-  <tableColumns count="6">
-    <tableColumn id="1" name="Parameter"/>
-    <tableColumn id="2" name="Subclass"/>
-    <tableColumn id="3" name="Value"/>
-    <tableColumn id="4" name="Units"/>
-    <tableColumn id="5" name="Description"/>
-    <tableColumn id="6" name="Source"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium15" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
+  <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1942,7 +1988,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="true">
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -1966,9 +2012,9 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="false"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="true">
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -1992,7 +2038,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="false"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -2027,7 +2073,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="false">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -2045,7 +2091,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="true">
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -2070,7 +2116,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="false"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -2086,19 +2132,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F109"/>
-  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F128"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" bestFit="true" customWidth="true"/>
-    <col min="2" max="2" width="15.140625" style="20" customWidth="true"/>
-    <col min="3" max="3" width="13.7109375" style="20" customWidth="true"/>
-    <col min="4" max="4" width="16.85546875" style="20" customWidth="true"/>
-    <col min="5" max="5" width="168.140625" bestFit="true" customWidth="true"/>
-    <col min="6" max="6" width="142.42578125" bestFit="true" customWidth="true"/>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" style="20" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" style="20" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" style="20" customWidth="1"/>
+    <col min="5" max="5" width="168.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="142.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2118,7 +2164,7 @@
         <v>5</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -2135,7 +2181,7 @@
         <v>9</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -2152,7 +2198,7 @@
         <v>11</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -2169,7 +2215,7 @@
         <v>13</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -2186,7 +2232,7 @@
         <v>15</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -2203,7 +2249,7 @@
         <v>17</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -2220,7 +2266,7 @@
         <v>19</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -2237,7 +2283,7 @@
         <v>21</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>205</v>
       </c>
@@ -2251,7 +2297,7 @@
         <v>8</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -2268,7 +2314,7 @@
         <v>24</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -2285,7 +2331,7 @@
         <v>26</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -2302,7 +2348,7 @@
         <v>203</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -2319,7 +2365,7 @@
         <v>30</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -2336,7 +2382,7 @@
         <v>32</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -2353,7 +2399,7 @@
         <v>34</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>35</v>
       </c>
@@ -2370,7 +2416,7 @@
         <v>36</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>37</v>
       </c>
@@ -2387,7 +2433,7 @@
         <v>38</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>39</v>
       </c>
@@ -2404,7 +2450,7 @@
         <v>40</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="19" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>41</v>
       </c>
@@ -2421,7 +2467,7 @@
         <v>44</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>45</v>
       </c>
@@ -2438,7 +2484,7 @@
         <v>47</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="21" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -2455,7 +2501,7 @@
         <v>50</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="22" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -2472,7 +2518,7 @@
         <v>52</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="23" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -2489,7 +2535,7 @@
         <v>54</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="24" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -2506,7 +2552,7 @@
         <v>57</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>58</v>
       </c>
@@ -2523,7 +2569,7 @@
         <v>60</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="26" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>61</v>
       </c>
@@ -2531,7 +2577,7 @@
         <v>56</v>
       </c>
       <c r="C26" s="20">
-        <v>5.5E-2</v>
+        <v>0.08</v>
       </c>
       <c r="D26" s="20" t="s">
         <v>59</v>
@@ -2540,7 +2586,7 @@
         <v>62</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="27" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>63</v>
       </c>
@@ -2557,7 +2603,7 @@
         <v>64</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="28" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>65</v>
       </c>
@@ -2574,7 +2620,7 @@
         <v>67</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="29" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -2591,7 +2637,7 @@
         <v>69</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -2608,7 +2654,7 @@
         <v>71</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="31" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>72</v>
       </c>
@@ -2625,7 +2671,7 @@
         <v>73</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="32" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>74</v>
       </c>
@@ -2642,7 +2688,7 @@
         <v>75</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="33" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>76</v>
       </c>
@@ -2659,7 +2705,7 @@
         <v>77</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="34" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>78</v>
       </c>
@@ -2676,7 +2722,7 @@
         <v>79</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="35" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>80</v>
       </c>
@@ -2693,7 +2739,7 @@
         <v>81</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="36" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>82</v>
       </c>
@@ -2710,7 +2756,7 @@
         <v>83</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="37" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>84</v>
       </c>
@@ -2727,7 +2773,7 @@
         <v>85</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="38" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>86</v>
       </c>
@@ -2744,7 +2790,7 @@
         <v>87</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="39" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>88</v>
       </c>
@@ -2761,7 +2807,7 @@
         <v>89</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="40" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>90</v>
       </c>
@@ -2778,7 +2824,7 @@
         <v>91</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="41" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>92</v>
       </c>
@@ -2795,7 +2841,7 @@
         <v>93</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="42" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>94</v>
       </c>
@@ -2812,7 +2858,7 @@
         <v>95</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="43" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>96</v>
       </c>
@@ -2829,7 +2875,7 @@
         <v>97</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="44" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>98</v>
       </c>
@@ -2846,7 +2892,7 @@
         <v>99</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="45" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>100</v>
       </c>
@@ -2863,7 +2909,7 @@
         <v>102</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="46" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>103</v>
       </c>
@@ -2880,7 +2926,7 @@
         <v>104</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="47" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>105</v>
       </c>
@@ -2897,7 +2943,7 @@
         <v>106</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="48" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>107</v>
       </c>
@@ -2914,7 +2960,7 @@
         <v>108</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="49" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>109</v>
       </c>
@@ -2931,7 +2977,7 @@
         <v>110</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="50" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>111</v>
       </c>
@@ -2948,7 +2994,7 @@
         <v>112</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="51" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>113</v>
       </c>
@@ -2965,7 +3011,7 @@
         <v>114</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="52" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>115</v>
       </c>
@@ -2982,7 +3028,7 @@
         <v>116</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="53" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>117</v>
       </c>
@@ -2999,7 +3045,7 @@
         <v>118</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="54" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>119</v>
       </c>
@@ -3016,7 +3062,7 @@
         <v>120</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="55" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>121</v>
       </c>
@@ -3033,7 +3079,7 @@
         <v>122</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="56" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>123</v>
       </c>
@@ -3050,7 +3096,7 @@
         <v>124</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="57" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>125</v>
       </c>
@@ -3067,7 +3113,7 @@
         <v>126</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="58" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>127</v>
       </c>
@@ -3084,7 +3130,7 @@
         <v>128</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="59" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>129</v>
       </c>
@@ -3101,7 +3147,7 @@
         <v>130</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="60" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>131</v>
       </c>
@@ -3118,7 +3164,7 @@
         <v>132</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="61" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>133</v>
       </c>
@@ -3135,7 +3181,7 @@
         <v>134</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="62" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>135</v>
       </c>
@@ -3152,7 +3198,7 @@
         <v>138</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="63" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>139</v>
       </c>
@@ -3169,7 +3215,7 @@
         <v>140</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="64" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>141</v>
       </c>
@@ -3186,7 +3232,7 @@
         <v>142</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="65" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>143</v>
       </c>
@@ -3203,7 +3249,7 @@
         <v>144</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="66" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>145</v>
       </c>
@@ -3220,7 +3266,7 @@
         <v>200</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="67" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>201</v>
       </c>
@@ -3237,7 +3283,7 @@
         <v>202</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="68" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>146</v>
       </c>
@@ -3254,7 +3300,7 @@
         <v>147</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="69" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>148</v>
       </c>
@@ -3271,7 +3317,7 @@
         <v>149</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="70" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>150</v>
       </c>
@@ -3288,7 +3334,7 @@
         <v>151</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="71" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>152</v>
       </c>
@@ -3305,7 +3351,7 @@
         <v>153</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="72" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>154</v>
       </c>
@@ -3322,7 +3368,7 @@
         <v>156</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="73" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>157</v>
       </c>
@@ -3339,7 +3385,7 @@
         <v>159</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="74" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>160</v>
       </c>
@@ -3356,7 +3402,7 @@
         <v>161</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>162</v>
       </c>
@@ -3373,7 +3419,7 @@
         <v>164</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="76" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>165</v>
       </c>
@@ -3390,7 +3436,7 @@
         <v>166</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="77" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>167</v>
       </c>
@@ -3407,7 +3453,7 @@
         <v>168</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="78" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>169</v>
       </c>
@@ -3424,7 +3470,7 @@
         <v>171</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="79" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>172</v>
       </c>
@@ -3441,7 +3487,7 @@
         <v>173</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="80" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>174</v>
       </c>
@@ -3458,7 +3504,7 @@
         <v>175</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="81" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>176</v>
       </c>
@@ -3475,7 +3521,7 @@
         <v>177</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="82" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>178</v>
       </c>
@@ -3492,7 +3538,7 @@
         <v>179</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="83" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>180</v>
       </c>
@@ -3509,7 +3555,7 @@
         <v>182</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="84" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>183</v>
       </c>
@@ -3526,7 +3572,7 @@
         <v>185</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="85" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>186</v>
       </c>
@@ -3543,7 +3589,7 @@
         <v>188</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="86" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>189</v>
       </c>
@@ -3560,7 +3606,7 @@
         <v>206</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="87" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>191</v>
       </c>
@@ -3577,7 +3623,7 @@
         <v>192</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="88" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>193</v>
       </c>
@@ -3594,7 +3640,7 @@
         <v>195</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="89" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>196</v>
       </c>
@@ -3611,7 +3657,7 @@
         <v>197</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="90" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>198</v>
       </c>
@@ -3628,7 +3674,7 @@
         <v>199</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="91" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>248</v>
       </c>
@@ -3645,7 +3691,7 @@
         <v>250</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="92" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>251</v>
       </c>
@@ -3662,7 +3708,7 @@
         <v>252</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="93" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>253</v>
       </c>
@@ -3679,7 +3725,7 @@
         <v>254</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="94" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>255</v>
       </c>
@@ -3696,7 +3742,7 @@
         <v>256</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="95" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>261</v>
       </c>
@@ -3713,7 +3759,7 @@
         <v>262</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="96" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>263</v>
       </c>
@@ -3730,7 +3776,7 @@
         <v>295</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="97" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>264</v>
       </c>
@@ -3747,7 +3793,7 @@
         <v>296</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="98" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>266</v>
       </c>
@@ -3764,7 +3810,7 @@
         <v>297</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="99" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>267</v>
       </c>
@@ -3781,7 +3827,7 @@
         <v>298</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="100" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>268</v>
       </c>
@@ -3798,7 +3844,7 @@
         <v>299</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="101" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>269</v>
       </c>
@@ -3815,7 +3861,7 @@
         <v>300</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="102" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>270</v>
       </c>
@@ -3832,7 +3878,7 @@
         <v>301</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="103" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>271</v>
       </c>
@@ -3849,7 +3895,7 @@
         <v>302</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="104" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>272</v>
       </c>
@@ -3866,7 +3912,7 @@
         <v>314</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="105" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>305</v>
       </c>
@@ -3883,7 +3929,7 @@
         <v>306</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="106" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>307</v>
       </c>
@@ -3900,7 +3946,7 @@
         <v>313</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="107" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>308</v>
       </c>
@@ -3917,7 +3963,7 @@
         <v>311</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="108" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>309</v>
       </c>
@@ -3934,7 +3980,7 @@
         <v>311</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="109" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>310</v>
       </c>
@@ -3949,6 +3995,261 @@
       </c>
       <c r="E109" t="s">
         <v>315</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>530</v>
+      </c>
+      <c r="B110" s="20" t="s">
+        <v>521</v>
+      </c>
+      <c r="C110" s="20">
+        <v>241</v>
+      </c>
+      <c r="D110" s="20" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>532</v>
+      </c>
+      <c r="B111" s="20" t="s">
+        <v>521</v>
+      </c>
+      <c r="C111" s="23">
+        <v>186</v>
+      </c>
+      <c r="D111" s="20" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>531</v>
+      </c>
+      <c r="B112" s="20" t="s">
+        <v>521</v>
+      </c>
+      <c r="C112" s="20">
+        <v>338</v>
+      </c>
+      <c r="D112" s="20" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>525</v>
+      </c>
+      <c r="B113" s="20" t="s">
+        <v>521</v>
+      </c>
+      <c r="C113" s="20">
+        <v>30</v>
+      </c>
+      <c r="D113" s="20" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>533</v>
+      </c>
+      <c r="B114" s="20" t="s">
+        <v>521</v>
+      </c>
+      <c r="C114" s="24">
+        <v>68900</v>
+      </c>
+      <c r="D114" s="20" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C115" s="24"/>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>538</v>
+      </c>
+      <c r="B116" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="C116" s="25">
+        <v>0.14799999999999999</v>
+      </c>
+      <c r="D116" s="20" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>537</v>
+      </c>
+      <c r="B117" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="C117" s="20">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="D117" s="20" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>539</v>
+      </c>
+      <c r="B118" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="C118" s="20">
+        <v>0.04</v>
+      </c>
+      <c r="D118" s="20" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>540</v>
+      </c>
+      <c r="B119" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="C119" s="20">
+        <v>2.3E-2</v>
+      </c>
+      <c r="D119" s="20" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>536</v>
+      </c>
+      <c r="B120" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="C120" s="20">
+        <v>50</v>
+      </c>
+      <c r="D120" s="20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>534</v>
+      </c>
+      <c r="B121" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="C121" s="20">
+        <v>0.09</v>
+      </c>
+      <c r="D121" s="20" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>535</v>
+      </c>
+      <c r="B122" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="C122" s="20">
+        <v>6.3499999999999997E-3</v>
+      </c>
+      <c r="D122" s="20" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>523</v>
+      </c>
+      <c r="B123" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="C123" s="20">
+        <v>1.2699999999999999E-2</v>
+      </c>
+      <c r="D123" s="20" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>524</v>
+      </c>
+      <c r="B124" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="C124" s="20">
+        <v>0.76</v>
+      </c>
+      <c r="D124" s="20" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>528</v>
+      </c>
+      <c r="B125" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="C125" s="20">
+        <v>1.5874999999999999E-3</v>
+      </c>
+      <c r="D125" s="20" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>526</v>
+      </c>
+      <c r="B126" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="C126" s="20">
+        <v>1.2699999999999999E-2</v>
+      </c>
+      <c r="D126" s="20" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>527</v>
+      </c>
+      <c r="B127" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="C127" s="20">
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="D127" s="20" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>529</v>
+      </c>
+      <c r="B128" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="C128" s="20">
+        <v>1.5874999999999999E-3</v>
+      </c>
+      <c r="D128" s="20" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -3960,2983 +4261,2410 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H157"/>
-  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.7109375" customWidth="true"/>
-    <col min="2" max="2" width="12.5703125" customWidth="true"/>
-    <col min="3" max="3" width="64.5703125" customWidth="true"/>
-    <col min="4" max="4" width="5.7109375" customWidth="true"/>
-    <col min="5" max="5" width="46" customWidth="true"/>
-    <col min="6" max="6" width="32.42578125" customWidth="true"/>
-    <col min="8" max="8" width="42.7109375" customWidth="true"/>
-    <col min="7" max="7" width="9.140625"/>
+    <col min="1" max="1" width="40.7109375" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" customWidth="1"/>
+    <col min="3" max="3" width="64.5703125" customWidth="1"/>
+    <col min="4" max="4" width="5.7109375" customWidth="1"/>
+    <col min="5" max="5" width="46" customWidth="1"/>
+    <col min="6" max="6" width="32.42578125" customWidth="1"/>
+    <col min="8" max="8" width="42.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" t="s">
         <v>377</v>
       </c>
-      <c r="G1" s="0"/>
-      <c r="H1" s="0" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="0" t="s">
+      <c r="H1" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>316</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="0">
-        <v>0.29999999999999999</v>
-      </c>
-      <c r="D2" s="0" t="s">
+      <c r="C2">
+        <v>0.3</v>
+      </c>
+      <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" t="s">
         <v>349</v>
       </c>
-      <c r="F2" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G2" s="0"/>
-      <c r="H2" s="0"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="0" t="s">
+      <c r="F2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>317</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="0">
+      <c r="C3">
         <v>1.1818181818181817</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" t="s">
         <v>350</v>
       </c>
-      <c r="F3" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G3" s="0"/>
-      <c r="H3" s="0"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="0" t="s">
+      <c r="F3" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>318</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="0">
+      <c r="C4">
         <v>0.92201380973471758</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" t="s">
         <v>351</v>
       </c>
-      <c r="F4" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G4" s="0"/>
-      <c r="H4" s="0"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="0" t="s">
+      <c r="F4" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>319</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="0">
-        <v>0.07919652663705147</v>
-      </c>
-      <c r="D5" s="0" t="s">
+      <c r="C5">
+        <v>7.919652663705147E-2</v>
+      </c>
+      <c r="D5" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" t="s">
         <v>352</v>
       </c>
-      <c r="F5" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G5" s="0"/>
-      <c r="H5" s="0"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="0" t="s">
+      <c r="F5" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>320</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="0">
+      <c r="C6">
         <v>0.19588300688233271</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" t="s">
         <v>353</v>
       </c>
-      <c r="F6" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G6" s="0"/>
-      <c r="H6" s="0"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="0" t="s">
+      <c r="F6" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>321</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="0">
-        <v>0.029817638776781716</v>
-      </c>
-      <c r="D7" s="0"/>
-      <c r="E7" s="0"/>
-      <c r="F7" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G7" s="0"/>
-      <c r="H7" s="0"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="0" t="s">
+      <c r="C7">
+        <v>2.9817638776781716E-2</v>
+      </c>
+      <c r="F7" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>322</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="0">
-        <v>0.036945326174116347</v>
-      </c>
-      <c r="D8" s="0" t="s">
+      <c r="C8">
+        <v>3.6945326174116347E-2</v>
+      </c>
+      <c r="D8" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="E8" t="s">
         <v>354</v>
       </c>
-      <c r="F8" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G8" s="0"/>
-      <c r="H8" s="0"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="0" t="s">
+      <c r="F8" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>323</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="0">
-        <v>0.036945326174116347</v>
-      </c>
-      <c r="D9" s="0" t="s">
+      <c r="C9">
+        <v>3.6945326174116347E-2</v>
+      </c>
+      <c r="D9" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="0" t="s">
+      <c r="E9" t="s">
         <v>355</v>
       </c>
-      <c r="F9" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G9" s="0"/>
-      <c r="H9" s="0"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="0" t="s">
+      <c r="F9" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>324</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="0">
-        <v>0.021945326174116347</v>
-      </c>
-      <c r="D10" s="0" t="s">
+      <c r="C10">
+        <v>2.1945326174116347E-2</v>
+      </c>
+      <c r="D10" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="0" t="s">
+      <c r="E10" t="s">
         <v>356</v>
       </c>
-      <c r="F10" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G10" s="0"/>
-      <c r="H10" s="0"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="0" t="s">
+      <c r="F10" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>325</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="0">
+      <c r="C11">
         <v>8.120106954426566</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="0" t="s">
+      <c r="E11" t="s">
         <v>357</v>
       </c>
-      <c r="F11" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G11" s="0"/>
-      <c r="H11" s="0"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="0" t="s">
+      <c r="F11" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>326</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="0">
+      <c r="C12">
         <v>10.289169276665902</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="0" t="s">
+      <c r="E12" t="s">
         <v>358</v>
       </c>
-      <c r="F12" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G12" s="0"/>
-      <c r="H12" s="0"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="0" t="s">
+      <c r="F12" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>381</v>
+      </c>
+      <c r="B13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13">
+        <v>3.0198549799930445</v>
+      </c>
+      <c r="F13" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>382</v>
+      </c>
+      <c r="B14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14">
+        <v>4.0327458299223453</v>
+      </c>
+      <c r="F14" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>383</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B15" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="0">
-        <v>3.0198549799930445</v>
-      </c>
-      <c r="D13" s="0"/>
-      <c r="E13" s="0"/>
-      <c r="F13" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G13" s="0"/>
-      <c r="H13" s="0"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="0" t="s">
+      <c r="C15">
+        <v>0.58894455001488533</v>
+      </c>
+      <c r="F15" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>384</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B16" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="0">
-        <v>4.0327458299223453</v>
-      </c>
-      <c r="D14" s="0"/>
-      <c r="E14" s="0"/>
-      <c r="F14" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G14" s="0"/>
-      <c r="H14" s="0"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="0" t="s">
+      <c r="C16">
+        <v>5.2740736776131758</v>
+      </c>
+      <c r="F16" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>385</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B17" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="0">
-        <v>0.58894455001488533</v>
-      </c>
-      <c r="D15" s="0"/>
-      <c r="E15" s="0"/>
-      <c r="F15" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G15" s="0"/>
-      <c r="H15" s="0"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="0" t="s">
+      <c r="C17">
+        <v>-9.4788465253600393E-2</v>
+      </c>
+      <c r="F17" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>386</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B18" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="0">
+      <c r="C18">
+        <v>0.66074594914354523</v>
+      </c>
+      <c r="F18" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>387</v>
+      </c>
+      <c r="B19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19">
+        <v>0.60899778104422941</v>
+      </c>
+      <c r="F19" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>388</v>
+      </c>
+      <c r="B20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20">
+        <v>1.5753270213496304</v>
+      </c>
+      <c r="F20" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>389</v>
+      </c>
+      <c r="B21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21">
+        <v>0.66074594914354523</v>
+      </c>
+      <c r="F21" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>390</v>
+      </c>
+      <c r="B22" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22">
+        <v>0.12602616170797043</v>
+      </c>
+      <c r="F22" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>327</v>
+      </c>
+      <c r="B23" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23">
+        <v>0.49722452282391244</v>
+      </c>
+      <c r="D23" t="s">
+        <v>66</v>
+      </c>
+      <c r="E23" t="s">
+        <v>359</v>
+      </c>
+      <c r="F23" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>328</v>
+      </c>
+      <c r="B24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24">
+        <v>0.34410001579509508</v>
+      </c>
+      <c r="D24" t="s">
+        <v>59</v>
+      </c>
+      <c r="E24" t="s">
+        <v>360</v>
+      </c>
+      <c r="F24" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>329</v>
+      </c>
+      <c r="B25" t="s">
+        <v>56</v>
+      </c>
+      <c r="C25">
+        <v>4.3591977074863637</v>
+      </c>
+      <c r="D25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" t="s">
+        <v>361</v>
+      </c>
+      <c r="F25" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>330</v>
+      </c>
+      <c r="B26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26">
+        <v>8.4528168880065119E-2</v>
+      </c>
+      <c r="D26" t="s">
+        <v>66</v>
+      </c>
+      <c r="E26" t="s">
+        <v>362</v>
+      </c>
+      <c r="F26" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>331</v>
+      </c>
+      <c r="B27" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27">
+        <v>0.45969601064199239</v>
+      </c>
+      <c r="D27" t="s">
+        <v>59</v>
+      </c>
+      <c r="E27" t="s">
+        <v>363</v>
+      </c>
+      <c r="F27" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>332</v>
+      </c>
+      <c r="B28" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28">
+        <v>0.18387840425679697</v>
+      </c>
+      <c r="D28" t="s">
+        <v>59</v>
+      </c>
+      <c r="E28" t="s">
+        <v>364</v>
+      </c>
+      <c r="F28" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>333</v>
+      </c>
+      <c r="B29" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29">
+        <v>0.39523392547876368</v>
+      </c>
+      <c r="D29" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" t="s">
+        <v>365</v>
+      </c>
+      <c r="F29" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>334</v>
+      </c>
+      <c r="B30" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30">
+        <v>7.4583678423586861E-2</v>
+      </c>
+      <c r="D30" t="s">
+        <v>66</v>
+      </c>
+      <c r="E30" t="s">
+        <v>366</v>
+      </c>
+      <c r="F30" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>335</v>
+      </c>
+      <c r="B31" t="s">
+        <v>56</v>
+      </c>
+      <c r="C31">
+        <v>7.4583678423586861E-2</v>
+      </c>
+      <c r="D31" t="s">
+        <v>66</v>
+      </c>
+      <c r="E31" t="s">
+        <v>367</v>
+      </c>
+      <c r="F31" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>336</v>
+      </c>
+      <c r="B32" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32">
+        <v>0.28249696620183012</v>
+      </c>
+      <c r="D32" t="s">
+        <v>59</v>
+      </c>
+      <c r="E32" t="s">
+        <v>368</v>
+      </c>
+      <c r="F32" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>337</v>
+      </c>
+      <c r="B33" t="s">
+        <v>56</v>
+      </c>
+      <c r="C33">
+        <v>0.26401585626339263</v>
+      </c>
+      <c r="D33" t="s">
+        <v>59</v>
+      </c>
+      <c r="E33" t="s">
+        <v>369</v>
+      </c>
+      <c r="F33" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>391</v>
+      </c>
+      <c r="B34" t="s">
+        <v>56</v>
+      </c>
+      <c r="C34">
+        <v>1.8046437163813135E-2</v>
+      </c>
+      <c r="F34" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>392</v>
+      </c>
+      <c r="B35" t="s">
+        <v>56</v>
+      </c>
+      <c r="C35">
+        <v>0.23885083680507355</v>
+      </c>
+      <c r="F35" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>393</v>
+      </c>
+      <c r="B36" t="s">
+        <v>56</v>
+      </c>
+      <c r="C36">
+        <v>0.3656082203404642</v>
+      </c>
+      <c r="F36" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>394</v>
+      </c>
+      <c r="B37" t="s">
+        <v>56</v>
+      </c>
+      <c r="C37">
+        <v>0.2156082203404642</v>
+      </c>
+      <c r="F37" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>167</v>
+      </c>
+      <c r="B38" t="s">
+        <v>136</v>
+      </c>
+      <c r="C38">
+        <v>4.0516000000000005</v>
+      </c>
+      <c r="F38" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>338</v>
+      </c>
+      <c r="B39" t="s">
+        <v>136</v>
+      </c>
+      <c r="C39">
+        <v>22.737783592977756</v>
+      </c>
+      <c r="D39" t="s">
+        <v>137</v>
+      </c>
+      <c r="E39" t="s">
+        <v>370</v>
+      </c>
+      <c r="F39" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>339</v>
+      </c>
+      <c r="B40" t="s">
+        <v>136</v>
+      </c>
+      <c r="C40">
+        <v>11</v>
+      </c>
+      <c r="D40" t="s">
+        <v>137</v>
+      </c>
+      <c r="E40" t="s">
+        <v>371</v>
+      </c>
+      <c r="F40" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>340</v>
+      </c>
+      <c r="B41" t="s">
+        <v>136</v>
+      </c>
+      <c r="C41">
+        <v>14.810748414335091</v>
+      </c>
+      <c r="D41" t="s">
+        <v>137</v>
+      </c>
+      <c r="E41" t="s">
+        <v>372</v>
+      </c>
+      <c r="F41" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>341</v>
+      </c>
+      <c r="B42" t="s">
+        <v>136</v>
+      </c>
+      <c r="C42">
+        <v>12.24744871391589</v>
+      </c>
+      <c r="D42" t="s">
+        <v>137</v>
+      </c>
+      <c r="E42" t="s">
+        <v>373</v>
+      </c>
+      <c r="F42" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>342</v>
+      </c>
+      <c r="B43" t="s">
+        <v>136</v>
+      </c>
+      <c r="C43">
+        <v>48.189685104221404</v>
+      </c>
+      <c r="D43" t="s">
+        <v>23</v>
+      </c>
+      <c r="E43" t="s">
+        <v>374</v>
+      </c>
+      <c r="F43" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>343</v>
+      </c>
+      <c r="B44" t="s">
+        <v>136</v>
+      </c>
+      <c r="C44">
+        <v>16.699244233993625</v>
+      </c>
+      <c r="D44" t="s">
+        <v>23</v>
+      </c>
+      <c r="E44" t="s">
+        <v>375</v>
+      </c>
+      <c r="F44" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>344</v>
+      </c>
+      <c r="B45" t="s">
+        <v>136</v>
+      </c>
+      <c r="C45">
+        <v>39.746196000000005</v>
+      </c>
+      <c r="D45" t="s">
+        <v>348</v>
+      </c>
+      <c r="E45" t="s">
+        <v>376</v>
+      </c>
+      <c r="F45" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>345</v>
+      </c>
+      <c r="B46" t="s">
+        <v>136</v>
+      </c>
+      <c r="C46">
+        <v>0.44283295832701008</v>
+      </c>
+      <c r="F46" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>346</v>
+      </c>
+      <c r="B47" t="s">
+        <v>136</v>
+      </c>
+      <c r="C47">
+        <v>233372.96903833433</v>
+      </c>
+      <c r="F47" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>347</v>
+      </c>
+      <c r="B48" t="s">
+        <v>136</v>
+      </c>
+      <c r="C48">
+        <v>130688.86266146721</v>
+      </c>
+      <c r="F48" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>395</v>
+      </c>
+      <c r="B49" t="s">
+        <v>136</v>
+      </c>
+      <c r="C49">
+        <v>34.144135350668904</v>
+      </c>
+      <c r="F49" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>396</v>
+      </c>
+      <c r="B50" t="s">
+        <v>136</v>
+      </c>
+      <c r="C50">
+        <v>15.480365443172449</v>
+      </c>
+      <c r="F50" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>397</v>
+      </c>
+      <c r="B51" t="s">
+        <v>136</v>
+      </c>
+      <c r="C51">
+        <v>3.8</v>
+      </c>
+      <c r="F51" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>398</v>
+      </c>
+      <c r="B52" t="s">
+        <v>136</v>
+      </c>
+      <c r="C52">
+        <v>-1.52</v>
+      </c>
+      <c r="F52" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>399</v>
+      </c>
+      <c r="B53" t="s">
+        <v>136</v>
+      </c>
+      <c r="C53">
+        <v>5.6999999999999993</v>
+      </c>
+      <c r="F53" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>400</v>
+      </c>
+      <c r="B54" t="s">
+        <v>136</v>
+      </c>
+      <c r="C54">
+        <v>-2.2800000000000002</v>
+      </c>
+      <c r="F54" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>401</v>
+      </c>
+      <c r="B55" t="s">
+        <v>136</v>
+      </c>
+      <c r="C55">
+        <v>18.622682892532463</v>
+      </c>
+      <c r="F55" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>402</v>
+      </c>
+      <c r="B56" t="s">
+        <v>136</v>
+      </c>
+      <c r="C56">
+        <v>27.131986877647702</v>
+      </c>
+      <c r="F56" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>403</v>
+      </c>
+      <c r="B57" t="s">
+        <v>136</v>
+      </c>
+      <c r="C57">
+        <v>25.580006542099976</v>
+      </c>
+      <c r="F57" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>404</v>
+      </c>
+      <c r="B58" t="s">
+        <v>136</v>
+      </c>
+      <c r="C58">
+        <v>28.422229491222197</v>
+      </c>
+      <c r="F58" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>405</v>
+      </c>
+      <c r="B59" t="s">
+        <v>136</v>
+      </c>
+      <c r="C59">
+        <v>6.3586494759793881</v>
+      </c>
+      <c r="F59" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>406</v>
+      </c>
+      <c r="B60" t="s">
+        <v>136</v>
+      </c>
+      <c r="C60">
+        <v>12.884684205822825</v>
+      </c>
+      <c r="F60" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>407</v>
+      </c>
+      <c r="B61" t="s">
+        <v>136</v>
+      </c>
+      <c r="C61">
+        <v>2.2299999999999964</v>
+      </c>
+      <c r="F61" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>408</v>
+      </c>
+      <c r="B62" t="s">
+        <v>136</v>
+      </c>
+      <c r="C62">
+        <v>11.011406321896699</v>
+      </c>
+      <c r="F62" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>409</v>
+      </c>
+      <c r="B63" t="s">
+        <v>136</v>
+      </c>
+      <c r="C63" t="b">
+        <v>1</v>
+      </c>
+      <c r="F63" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>410</v>
+      </c>
+      <c r="B64" t="s">
+        <v>136</v>
+      </c>
+      <c r="C64">
+        <v>5.6667672012645314</v>
+      </c>
+      <c r="F64" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>411</v>
+      </c>
+      <c r="B65" t="s">
+        <v>136</v>
+      </c>
+      <c r="C65">
+        <v>19.023298859748962</v>
+      </c>
+      <c r="F65" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>412</v>
+      </c>
+      <c r="B66" t="s">
+        <v>136</v>
+      </c>
+      <c r="C66">
+        <v>5.2940237236683272</v>
+      </c>
+      <c r="F66" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>413</v>
+      </c>
+      <c r="B67" t="s">
+        <v>136</v>
+      </c>
+      <c r="C67">
+        <v>22.608098531363336</v>
+      </c>
+      <c r="F67" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>414</v>
+      </c>
+      <c r="B68" t="s">
+        <v>136</v>
+      </c>
+      <c r="C68">
+        <v>12.709922788411269</v>
+      </c>
+      <c r="F68" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>415</v>
+      </c>
+      <c r="B69" t="s">
+        <v>136</v>
+      </c>
+      <c r="C69">
+        <v>16.27392540932771</v>
+      </c>
+      <c r="F69" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>416</v>
+      </c>
+      <c r="B70" t="s">
+        <v>136</v>
+      </c>
+      <c r="C70">
+        <v>15.956485750905872</v>
+      </c>
+      <c r="F70" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>417</v>
+      </c>
+      <c r="B71" t="s">
+        <v>136</v>
+      </c>
+      <c r="C71">
+        <v>13.695854805920606</v>
+      </c>
+      <c r="F71" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>418</v>
+      </c>
+      <c r="B72" t="s">
+        <v>136</v>
+      </c>
+      <c r="C72">
+        <v>1.0954451150103324</v>
+      </c>
+      <c r="F72" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>419</v>
+      </c>
+      <c r="B73" t="s">
+        <v>136</v>
+      </c>
+      <c r="C73">
+        <v>24.094842552110709</v>
+      </c>
+      <c r="F73" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>420</v>
+      </c>
+      <c r="B74" t="s">
+        <v>136</v>
+      </c>
+      <c r="C74" t="b">
+        <v>1</v>
+      </c>
+      <c r="F74" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>421</v>
+      </c>
+      <c r="B75" t="s">
+        <v>136</v>
+      </c>
+      <c r="C75">
+        <v>156.52835771396133</v>
+      </c>
+      <c r="F75" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>422</v>
+      </c>
+      <c r="B76" t="s">
+        <v>136</v>
+      </c>
+      <c r="C76">
+        <v>44593.916314433394</v>
+      </c>
+      <c r="F76" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>423</v>
+      </c>
+      <c r="B77" t="s">
+        <v>136</v>
+      </c>
+      <c r="C77" t="b">
+        <v>1</v>
+      </c>
+      <c r="F77" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>424</v>
+      </c>
+      <c r="B78" t="s">
+        <v>136</v>
+      </c>
+      <c r="C78" t="b">
+        <v>1</v>
+      </c>
+      <c r="F78" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>425</v>
+      </c>
+      <c r="B79" t="s">
+        <v>136</v>
+      </c>
+      <c r="C79">
+        <v>13</v>
+      </c>
+      <c r="F79" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>426</v>
+      </c>
+      <c r="B80" t="s">
+        <v>136</v>
+      </c>
+      <c r="C80">
+        <v>86094.946347033809</v>
+      </c>
+      <c r="F80" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>427</v>
+      </c>
+      <c r="B81" t="s">
+        <v>136</v>
+      </c>
+      <c r="C81">
+        <v>0.16336801963384023</v>
+      </c>
+      <c r="F81" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>428</v>
+      </c>
+      <c r="B82" t="s">
+        <v>136</v>
+      </c>
+      <c r="C82">
+        <v>2.185902626124927</v>
+      </c>
+      <c r="F82" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>429</v>
+      </c>
+      <c r="B83" t="s">
+        <v>170</v>
+      </c>
+      <c r="C83" t="s">
+        <v>505</v>
+      </c>
+      <c r="F83" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>430</v>
+      </c>
+      <c r="B84" t="s">
+        <v>170</v>
+      </c>
+      <c r="C84">
+        <v>-4.0973254512723323E-2</v>
+      </c>
+      <c r="F84" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>431</v>
+      </c>
+      <c r="B85" t="s">
+        <v>170</v>
+      </c>
+      <c r="C85" t="b">
+        <v>0</v>
+      </c>
+      <c r="F85" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>432</v>
+      </c>
+      <c r="B86" t="s">
+        <v>170</v>
+      </c>
+      <c r="C86">
+        <v>0.254</v>
+      </c>
+      <c r="F86" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>433</v>
+      </c>
+      <c r="B87" t="s">
+        <v>170</v>
+      </c>
+      <c r="C87">
+        <v>0.127</v>
+      </c>
+      <c r="F87" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>434</v>
+      </c>
+      <c r="B88" t="s">
+        <v>170</v>
+      </c>
+      <c r="C88">
+        <v>14500</v>
+      </c>
+      <c r="F88" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>435</v>
+      </c>
+      <c r="B89" t="s">
+        <v>170</v>
+      </c>
+      <c r="C89" t="s">
+        <v>506</v>
+      </c>
+      <c r="F89" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>436</v>
+      </c>
+      <c r="B90" t="s">
+        <v>170</v>
+      </c>
+      <c r="C90" t="s">
+        <v>507</v>
+      </c>
+      <c r="F90" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>437</v>
+      </c>
+      <c r="B91" t="s">
+        <v>170</v>
+      </c>
+      <c r="C91" t="s">
+        <v>508</v>
+      </c>
+      <c r="F91" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>438</v>
+      </c>
+      <c r="B92" t="s">
+        <v>170</v>
+      </c>
+      <c r="C92" t="s">
+        <v>508</v>
+      </c>
+      <c r="F92" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>439</v>
+      </c>
+      <c r="B93" t="s">
+        <v>170</v>
+      </c>
+      <c r="C93" t="s">
+        <v>508</v>
+      </c>
+      <c r="F93" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>440</v>
+      </c>
+      <c r="B94" t="s">
+        <v>170</v>
+      </c>
+      <c r="C94" t="s">
+        <v>508</v>
+      </c>
+      <c r="F94" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>441</v>
+      </c>
+      <c r="B95" t="s">
+        <v>170</v>
+      </c>
+      <c r="C95" t="s">
+        <v>508</v>
+      </c>
+      <c r="F95" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>442</v>
+      </c>
+      <c r="B96" t="s">
+        <v>170</v>
+      </c>
+      <c r="C96" t="s">
+        <v>508</v>
+      </c>
+      <c r="F96" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>443</v>
+      </c>
+      <c r="B97" t="s">
+        <v>170</v>
+      </c>
+      <c r="C97" t="s">
+        <v>508</v>
+      </c>
+      <c r="F97" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>444</v>
+      </c>
+      <c r="B98" t="s">
+        <v>170</v>
+      </c>
+      <c r="C98" t="s">
+        <v>508</v>
+      </c>
+      <c r="F98" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>445</v>
+      </c>
+      <c r="B99" t="s">
+        <v>170</v>
+      </c>
+      <c r="C99" t="s">
+        <v>509</v>
+      </c>
+      <c r="F99" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>446</v>
+      </c>
+      <c r="B100" t="s">
+        <v>170</v>
+      </c>
+      <c r="C100">
+        <v>700</v>
+      </c>
+      <c r="F100" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>447</v>
+      </c>
+      <c r="B101" t="s">
+        <v>170</v>
+      </c>
+      <c r="C101">
+        <v>50</v>
+      </c>
+      <c r="F101" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>448</v>
+      </c>
+      <c r="B102" t="s">
+        <v>170</v>
+      </c>
+      <c r="C102" t="s">
+        <v>510</v>
+      </c>
+      <c r="F102" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>449</v>
+      </c>
+      <c r="B103" t="s">
+        <v>170</v>
+      </c>
+      <c r="C103" t="s">
+        <v>508</v>
+      </c>
+      <c r="F103" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>450</v>
+      </c>
+      <c r="B104" t="s">
+        <v>170</v>
+      </c>
+      <c r="C104" t="s">
+        <v>511</v>
+      </c>
+      <c r="F104" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>451</v>
+      </c>
+      <c r="B105" t="s">
+        <v>170</v>
+      </c>
+      <c r="C105" t="s">
+        <v>512</v>
+      </c>
+      <c r="F105" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>452</v>
+      </c>
+      <c r="B106" t="s">
+        <v>170</v>
+      </c>
+      <c r="C106" t="s">
+        <v>513</v>
+      </c>
+      <c r="F106" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>453</v>
+      </c>
+      <c r="B107" t="s">
+        <v>170</v>
+      </c>
+      <c r="C107" t="s">
+        <v>514</v>
+      </c>
+      <c r="F107" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>454</v>
+      </c>
+      <c r="B108" t="s">
+        <v>170</v>
+      </c>
+      <c r="C108" t="s">
+        <v>515</v>
+      </c>
+      <c r="F108" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>455</v>
+      </c>
+      <c r="B109" t="s">
+        <v>170</v>
+      </c>
+      <c r="C109" t="s">
+        <v>516</v>
+      </c>
+      <c r="F109" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>456</v>
+      </c>
+      <c r="B110" t="s">
+        <v>170</v>
+      </c>
+      <c r="C110" t="s">
+        <v>517</v>
+      </c>
+      <c r="F110" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>457</v>
+      </c>
+      <c r="B111" t="s">
+        <v>265</v>
+      </c>
+      <c r="C111">
+        <v>32.946133306980855</v>
+      </c>
+      <c r="F111" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>458</v>
+      </c>
+      <c r="B112" t="s">
+        <v>265</v>
+      </c>
+      <c r="C112">
+        <v>0</v>
+      </c>
+      <c r="F112" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>459</v>
+      </c>
+      <c r="B113" t="s">
+        <v>265</v>
+      </c>
+      <c r="C113" t="s">
+        <v>518</v>
+      </c>
+      <c r="F113" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>460</v>
+      </c>
+      <c r="B114" t="s">
+        <v>265</v>
+      </c>
+      <c r="C114">
+        <v>86.068285472894019</v>
+      </c>
+      <c r="F114" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>461</v>
+      </c>
+      <c r="B115" t="s">
+        <v>265</v>
+      </c>
+      <c r="C115">
+        <v>0</v>
+      </c>
+      <c r="F115" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>462</v>
+      </c>
+      <c r="B116" t="s">
+        <v>265</v>
+      </c>
+      <c r="C116">
+        <v>-1.8275795392708134</v>
+      </c>
+      <c r="F116" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>463</v>
+      </c>
+      <c r="B117" t="s">
+        <v>265</v>
+      </c>
+      <c r="C117">
+        <v>0</v>
+      </c>
+      <c r="F117" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>464</v>
+      </c>
+      <c r="B118" t="s">
+        <v>265</v>
+      </c>
+      <c r="C118">
+        <v>1.7526473681977495</v>
+      </c>
+      <c r="F118" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>465</v>
+      </c>
+      <c r="B119" t="s">
+        <v>265</v>
+      </c>
+      <c r="C119">
+        <v>0.15168253041257554</v>
+      </c>
+      <c r="F119" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>466</v>
+      </c>
+      <c r="B120" t="s">
+        <v>265</v>
+      </c>
+      <c r="C120">
+        <v>2.4110213483593652</v>
+      </c>
+      <c r="F120" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>467</v>
+      </c>
+      <c r="B121" t="s">
+        <v>265</v>
+      </c>
+      <c r="C121">
+        <v>2.7131092758196531</v>
+      </c>
+      <c r="F121" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>468</v>
+      </c>
+      <c r="B122" t="s">
+        <v>265</v>
+      </c>
+      <c r="C122">
+        <v>16.090147165877724</v>
+      </c>
+      <c r="F122" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>469</v>
+      </c>
+      <c r="B123" t="s">
+        <v>265</v>
+      </c>
+      <c r="C123">
+        <v>16.925292122478595</v>
+      </c>
+      <c r="F123" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>470</v>
+      </c>
+      <c r="B124" t="s">
+        <v>265</v>
+      </c>
+      <c r="C124">
+        <v>0.35178486510320511</v>
+      </c>
+      <c r="F124" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>471</v>
+      </c>
+      <c r="B125" t="s">
+        <v>265</v>
+      </c>
+      <c r="C125" t="s">
+        <v>519</v>
+      </c>
+      <c r="F125" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>472</v>
+      </c>
+      <c r="B126" t="s">
+        <v>265</v>
+      </c>
+      <c r="C126">
+        <v>233.69773788009346</v>
+      </c>
+      <c r="F126" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>473</v>
+      </c>
+      <c r="B127" t="s">
+        <v>265</v>
+      </c>
+      <c r="C127">
+        <v>0.35242563899228196</v>
+      </c>
+      <c r="F127" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>474</v>
+      </c>
+      <c r="B128" t="s">
+        <v>265</v>
+      </c>
+      <c r="C128" t="s">
+        <v>519</v>
+      </c>
+      <c r="F128" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>475</v>
+      </c>
+      <c r="B129" t="s">
+        <v>265</v>
+      </c>
+      <c r="C129">
+        <v>9.4744003772526408</v>
+      </c>
+      <c r="F129" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>476</v>
+      </c>
+      <c r="B130" t="s">
+        <v>265</v>
+      </c>
+      <c r="C130">
+        <v>341.83792795003058</v>
+      </c>
+      <c r="F130" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>477</v>
+      </c>
+      <c r="B131" t="s">
+        <v>265</v>
+      </c>
+      <c r="C131">
+        <v>34.733446426726843</v>
+      </c>
+      <c r="F131" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>478</v>
+      </c>
+      <c r="B132" t="s">
+        <v>265</v>
+      </c>
+      <c r="C132">
+        <v>0.42099254615460552</v>
+      </c>
+      <c r="F132" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>479</v>
+      </c>
+      <c r="B133" t="s">
+        <v>265</v>
+      </c>
+      <c r="C133">
+        <v>4.0516000000000005</v>
+      </c>
+      <c r="F133" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>480</v>
+      </c>
+      <c r="B134" t="s">
+        <v>265</v>
+      </c>
+      <c r="C134">
+        <v>39.746196000000005</v>
+      </c>
+      <c r="F134" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>481</v>
+      </c>
+      <c r="B135" t="s">
+        <v>265</v>
+      </c>
+      <c r="C135">
+        <v>18.230437113682747</v>
+      </c>
+      <c r="F135" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>482</v>
+      </c>
+      <c r="B136" t="s">
+        <v>265</v>
+      </c>
+      <c r="C136">
+        <v>8.0999999999999989E-2</v>
+      </c>
+      <c r="F136" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>483</v>
+      </c>
+      <c r="B137" t="s">
+        <v>265</v>
+      </c>
+      <c r="C137">
+        <v>64.749890848167752</v>
+      </c>
+      <c r="F137" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>484</v>
+      </c>
+      <c r="B138" t="s">
+        <v>504</v>
+      </c>
+      <c r="C138">
+        <v>0.3</v>
+      </c>
+      <c r="F138" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>485</v>
+      </c>
+      <c r="B139" t="s">
+        <v>504</v>
+      </c>
+      <c r="C139">
+        <v>26.360381758366742</v>
+      </c>
+      <c r="F139" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>486</v>
+      </c>
+      <c r="B140" t="s">
+        <v>504</v>
+      </c>
+      <c r="C140">
+        <v>3.6396182416332579</v>
+      </c>
+      <c r="F140" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>487</v>
+      </c>
+      <c r="B141" t="s">
+        <v>504</v>
+      </c>
+      <c r="C141">
+        <v>0.25</v>
+      </c>
+      <c r="F141" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>488</v>
+      </c>
+      <c r="B142" t="s">
+        <v>504</v>
+      </c>
+      <c r="C142">
+        <v>0.7</v>
+      </c>
+      <c r="F142" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>489</v>
+      </c>
+      <c r="B143" t="s">
+        <v>504</v>
+      </c>
+      <c r="C143">
+        <v>1</v>
+      </c>
+      <c r="F143" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>490</v>
+      </c>
+      <c r="B144" t="s">
+        <v>504</v>
+      </c>
+      <c r="C144">
+        <v>0.12048857500544551</v>
+      </c>
+      <c r="F144" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>491</v>
+      </c>
+      <c r="B145" t="s">
+        <v>504</v>
+      </c>
+      <c r="C145">
+        <v>119.66043834086311</v>
+      </c>
+      <c r="F145" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>492</v>
+      </c>
+      <c r="B146" t="s">
+        <v>504</v>
+      </c>
+      <c r="C146">
+        <v>7.4583678423586861E-2</v>
+      </c>
+      <c r="F146" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>493</v>
+      </c>
+      <c r="B147" t="s">
+        <v>504</v>
+      </c>
+      <c r="C147">
+        <v>1.07</v>
+      </c>
+      <c r="F147" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>494</v>
+      </c>
+      <c r="B148" t="s">
+        <v>504</v>
+      </c>
+      <c r="C148">
+        <v>0.3</v>
+      </c>
+      <c r="F148" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>495</v>
+      </c>
+      <c r="B149" t="s">
+        <v>504</v>
+      </c>
+      <c r="C149">
+        <v>29.162154556467332</v>
+      </c>
+      <c r="F149" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>496</v>
+      </c>
+      <c r="B150" t="s">
+        <v>504</v>
+      </c>
+      <c r="C150">
+        <v>0.83784544353266455</v>
+      </c>
+      <c r="F150" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>497</v>
+      </c>
+      <c r="B151" t="s">
+        <v>504</v>
+      </c>
+      <c r="C151">
         <v>5.2740736776131758</v>
       </c>
-      <c r="D16" s="0"/>
-      <c r="E16" s="0"/>
-      <c r="F16" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G16" s="0"/>
-      <c r="H16" s="0"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="0" t="s">
-        <v>387</v>
-      </c>
-      <c r="B17" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="0">
-        <v>-0.094788465253600393</v>
-      </c>
-      <c r="D17" s="0"/>
-      <c r="E17" s="0"/>
-      <c r="F17" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G17" s="0"/>
-      <c r="H17" s="0"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="0" t="s">
-        <v>388</v>
-      </c>
-      <c r="B18" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="0">
-        <v>0.66074594914354523</v>
-      </c>
-      <c r="D18" s="0"/>
-      <c r="E18" s="0"/>
-      <c r="F18" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G18" s="0"/>
-      <c r="H18" s="0"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="0" t="s">
-        <v>389</v>
-      </c>
-      <c r="B19" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="0">
-        <v>0.60899778104422941</v>
-      </c>
-      <c r="D19" s="0"/>
-      <c r="E19" s="0"/>
-      <c r="F19" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G19" s="0"/>
-      <c r="H19" s="0"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="0" t="s">
-        <v>390</v>
-      </c>
-      <c r="B20" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="0">
-        <v>1.5753270213496304</v>
-      </c>
-      <c r="D20" s="0"/>
-      <c r="E20" s="0"/>
-      <c r="F20" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G20" s="0"/>
-      <c r="H20" s="0"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="0" t="s">
-        <v>391</v>
-      </c>
-      <c r="B21" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="0">
-        <v>0.66074594914354523</v>
-      </c>
-      <c r="D21" s="0"/>
-      <c r="E21" s="0"/>
-      <c r="F21" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G21" s="0"/>
-      <c r="H21" s="0"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="0" t="s">
-        <v>392</v>
-      </c>
-      <c r="B22" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="0">
+      <c r="F151" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>498</v>
+      </c>
+      <c r="B152" t="s">
+        <v>504</v>
+      </c>
+      <c r="C152">
+        <v>0.3656082203404642</v>
+      </c>
+      <c r="F152" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>499</v>
+      </c>
+      <c r="B153" t="s">
+        <v>504</v>
+      </c>
+      <c r="C153">
+        <v>0.15</v>
+      </c>
+      <c r="F153" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>500</v>
+      </c>
+      <c r="B154" t="s">
+        <v>504</v>
+      </c>
+      <c r="C154">
+        <v>-0.79111105164197637</v>
+      </c>
+      <c r="F154" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>501</v>
+      </c>
+      <c r="B155" t="s">
+        <v>504</v>
+      </c>
+      <c r="C155">
         <v>0.12602616170797043</v>
       </c>
-      <c r="D22" s="0"/>
-      <c r="E22" s="0"/>
-      <c r="F22" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G22" s="0"/>
-      <c r="H22" s="0"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="0" t="s">
-        <v>327</v>
-      </c>
-      <c r="B23" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C23" s="0">
-        <v>0.49722452282391244</v>
-      </c>
-      <c r="D23" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="E23" s="0" t="s">
-        <v>359</v>
-      </c>
-      <c r="F23" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G23" s="0"/>
-      <c r="H23" s="0"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="0" t="s">
-        <v>328</v>
-      </c>
-      <c r="B24" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C24" s="0">
-        <v>0.34410001579509508</v>
-      </c>
-      <c r="D24" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="E24" s="0" t="s">
-        <v>360</v>
-      </c>
-      <c r="F24" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G24" s="0"/>
-      <c r="H24" s="0"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="0" t="s">
-        <v>329</v>
-      </c>
-      <c r="B25" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C25" s="0">
-        <v>4.3591977074863637</v>
-      </c>
-      <c r="D25" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="0" t="s">
-        <v>361</v>
-      </c>
-      <c r="F25" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G25" s="0"/>
-      <c r="H25" s="0"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="0" t="s">
-        <v>330</v>
-      </c>
-      <c r="B26" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C26" s="0">
-        <v>0.084528168880065119</v>
-      </c>
-      <c r="D26" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="E26" s="0" t="s">
-        <v>362</v>
-      </c>
-      <c r="F26" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G26" s="0"/>
-      <c r="H26" s="0"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="0" t="s">
-        <v>331</v>
-      </c>
-      <c r="B27" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C27" s="0">
-        <v>0.45969601064199239</v>
-      </c>
-      <c r="D27" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="E27" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="F27" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G27" s="0"/>
-      <c r="H27" s="0"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="0" t="s">
-        <v>332</v>
-      </c>
-      <c r="B28" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C28" s="0">
-        <v>0.18387840425679697</v>
-      </c>
-      <c r="D28" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="E28" s="0" t="s">
-        <v>364</v>
-      </c>
-      <c r="F28" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G28" s="0"/>
-      <c r="H28" s="0"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="0" t="s">
-        <v>333</v>
-      </c>
-      <c r="B29" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C29" s="0">
-        <v>0.39523392547876368</v>
-      </c>
-      <c r="D29" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="0" t="s">
-        <v>365</v>
-      </c>
-      <c r="F29" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G29" s="0"/>
-      <c r="H29" s="0"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="0" t="s">
-        <v>334</v>
-      </c>
-      <c r="B30" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C30" s="0">
-        <v>0.074583678423586861</v>
-      </c>
-      <c r="D30" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="E30" s="0" t="s">
-        <v>366</v>
-      </c>
-      <c r="F30" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G30" s="0"/>
-      <c r="H30" s="0"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="0" t="s">
-        <v>335</v>
-      </c>
-      <c r="B31" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C31" s="0">
-        <v>0.074583678423586861</v>
-      </c>
-      <c r="D31" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="E31" s="0" t="s">
-        <v>367</v>
-      </c>
-      <c r="F31" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G31" s="0"/>
-      <c r="H31" s="0"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="0" t="s">
-        <v>336</v>
-      </c>
-      <c r="B32" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C32" s="0">
-        <v>0.28249696620183012</v>
-      </c>
-      <c r="D32" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="E32" s="0" t="s">
-        <v>368</v>
-      </c>
-      <c r="F32" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G32" s="0"/>
-      <c r="H32" s="0"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="0" t="s">
-        <v>337</v>
-      </c>
-      <c r="B33" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C33" s="0">
-        <v>0.26401585626339263</v>
-      </c>
-      <c r="D33" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="E33" s="0" t="s">
-        <v>369</v>
-      </c>
-      <c r="F33" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G33" s="0"/>
-      <c r="H33" s="0"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="0" t="s">
-        <v>393</v>
-      </c>
-      <c r="B34" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C34" s="0">
-        <v>0.018046437163813135</v>
-      </c>
-      <c r="D34" s="0"/>
-      <c r="E34" s="0"/>
-      <c r="F34" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G34" s="0"/>
-      <c r="H34" s="0"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="0" t="s">
-        <v>394</v>
-      </c>
-      <c r="B35" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C35" s="0">
-        <v>0.23885083680507355</v>
-      </c>
-      <c r="D35" s="0"/>
-      <c r="E35" s="0"/>
-      <c r="F35" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G35" s="0"/>
-      <c r="H35" s="0"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="0" t="s">
-        <v>395</v>
-      </c>
-      <c r="B36" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C36" s="0">
-        <v>0.3656082203404642</v>
-      </c>
-      <c r="D36" s="0"/>
-      <c r="E36" s="0"/>
-      <c r="F36" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G36" s="0"/>
-      <c r="H36" s="0"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="0" t="s">
-        <v>396</v>
-      </c>
-      <c r="B37" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C37" s="0">
-        <v>0.2156082203404642</v>
-      </c>
-      <c r="D37" s="0"/>
-      <c r="E37" s="0"/>
-      <c r="F37" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G37" s="0"/>
-      <c r="H37" s="0"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="0" t="s">
-        <v>167</v>
-      </c>
-      <c r="B38" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C38" s="0">
-        <v>4.0516000000000005</v>
-      </c>
-      <c r="D38" s="0"/>
-      <c r="E38" s="0"/>
-      <c r="F38" s="0" t="s">
-        <v>379</v>
-      </c>
-      <c r="G38" s="0"/>
-      <c r="H38" s="0"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="0" t="s">
-        <v>338</v>
-      </c>
-      <c r="B39" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C39" s="0">
-        <v>22.737783592977756</v>
-      </c>
-      <c r="D39" s="0" t="s">
-        <v>137</v>
-      </c>
-      <c r="E39" s="0" t="s">
-        <v>370</v>
-      </c>
-      <c r="F39" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G39" s="0"/>
-      <c r="H39" s="0"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="0" t="s">
-        <v>339</v>
-      </c>
-      <c r="B40" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C40" s="0">
-        <v>11</v>
-      </c>
-      <c r="D40" s="0" t="s">
-        <v>137</v>
-      </c>
-      <c r="E40" s="0" t="s">
-        <v>371</v>
-      </c>
-      <c r="F40" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G40" s="0"/>
-      <c r="H40" s="0"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="0" t="s">
-        <v>340</v>
-      </c>
-      <c r="B41" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C41" s="0">
-        <v>14.810748414335091</v>
-      </c>
-      <c r="D41" s="0" t="s">
-        <v>137</v>
-      </c>
-      <c r="E41" s="0" t="s">
-        <v>372</v>
-      </c>
-      <c r="F41" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G41" s="0"/>
-      <c r="H41" s="0"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="0" t="s">
-        <v>341</v>
-      </c>
-      <c r="B42" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C42" s="0">
-        <v>12.24744871391589</v>
-      </c>
-      <c r="D42" s="0" t="s">
-        <v>137</v>
-      </c>
-      <c r="E42" s="0" t="s">
-        <v>373</v>
-      </c>
-      <c r="F42" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G42" s="0"/>
-      <c r="H42" s="0"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="0" t="s">
-        <v>342</v>
-      </c>
-      <c r="B43" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C43" s="0">
-        <v>48.189685104221404</v>
-      </c>
-      <c r="D43" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="E43" s="0" t="s">
-        <v>374</v>
-      </c>
-      <c r="F43" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G43" s="0"/>
-      <c r="H43" s="0"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="0" t="s">
-        <v>343</v>
-      </c>
-      <c r="B44" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C44" s="0">
-        <v>16.699244233993625</v>
-      </c>
-      <c r="D44" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="E44" s="0" t="s">
-        <v>375</v>
-      </c>
-      <c r="F44" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G44" s="0"/>
-      <c r="H44" s="0"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="0" t="s">
-        <v>344</v>
-      </c>
-      <c r="B45" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C45" s="0">
-        <v>39.746196000000005</v>
-      </c>
-      <c r="D45" s="0" t="s">
-        <v>348</v>
-      </c>
-      <c r="E45" s="0" t="s">
-        <v>376</v>
-      </c>
-      <c r="F45" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G45" s="0"/>
-      <c r="H45" s="0"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="0" t="s">
-        <v>345</v>
-      </c>
-      <c r="B46" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C46" s="0">
-        <v>0.44283295832701008</v>
-      </c>
-      <c r="D46" s="0"/>
-      <c r="E46" s="0"/>
-      <c r="F46" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G46" s="0"/>
-      <c r="H46" s="0"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="0" t="s">
-        <v>346</v>
-      </c>
-      <c r="B47" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C47" s="0">
-        <v>233372.96903833433</v>
-      </c>
-      <c r="D47" s="0"/>
-      <c r="E47" s="0"/>
-      <c r="F47" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G47" s="0"/>
-      <c r="H47" s="0"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="0" t="s">
-        <v>347</v>
-      </c>
-      <c r="B48" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C48" s="0">
-        <v>130688.86266146721</v>
-      </c>
-      <c r="D48" s="0"/>
-      <c r="E48" s="0"/>
-      <c r="F48" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G48" s="0"/>
-      <c r="H48" s="0"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="0" t="s">
-        <v>397</v>
-      </c>
-      <c r="B49" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C49" s="0">
-        <v>34.144135350668904</v>
-      </c>
-      <c r="D49" s="0"/>
-      <c r="E49" s="0"/>
-      <c r="F49" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G49" s="0"/>
-      <c r="H49" s="0"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="0" t="s">
-        <v>398</v>
-      </c>
-      <c r="B50" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C50" s="0">
-        <v>15.480365443172449</v>
-      </c>
-      <c r="D50" s="0"/>
-      <c r="E50" s="0"/>
-      <c r="F50" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G50" s="0"/>
-      <c r="H50" s="0"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="0" t="s">
-        <v>399</v>
-      </c>
-      <c r="B51" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C51" s="0">
-        <v>3.7999999999999998</v>
-      </c>
-      <c r="D51" s="0"/>
-      <c r="E51" s="0"/>
-      <c r="F51" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G51" s="0"/>
-      <c r="H51" s="0"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="0" t="s">
-        <v>400</v>
-      </c>
-      <c r="B52" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C52" s="0">
-        <v>-1.52</v>
-      </c>
-      <c r="D52" s="0"/>
-      <c r="E52" s="0"/>
-      <c r="F52" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G52" s="0"/>
-      <c r="H52" s="0"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="0" t="s">
-        <v>401</v>
-      </c>
-      <c r="B53" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C53" s="0">
-        <v>5.6999999999999993</v>
-      </c>
-      <c r="D53" s="0"/>
-      <c r="E53" s="0"/>
-      <c r="F53" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G53" s="0"/>
-      <c r="H53" s="0"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="0" t="s">
-        <v>402</v>
-      </c>
-      <c r="B54" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C54" s="0">
-        <v>-2.2800000000000002</v>
-      </c>
-      <c r="D54" s="0"/>
-      <c r="E54" s="0"/>
-      <c r="F54" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G54" s="0"/>
-      <c r="H54" s="0"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="0" t="s">
-        <v>403</v>
-      </c>
-      <c r="B55" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C55" s="0">
-        <v>18.622682892532463</v>
-      </c>
-      <c r="D55" s="0"/>
-      <c r="E55" s="0"/>
-      <c r="F55" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G55" s="0"/>
-      <c r="H55" s="0"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="0" t="s">
-        <v>404</v>
-      </c>
-      <c r="B56" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C56" s="0">
-        <v>27.131986877647702</v>
-      </c>
-      <c r="D56" s="0"/>
-      <c r="E56" s="0"/>
-      <c r="F56" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G56" s="0"/>
-      <c r="H56" s="0"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="0" t="s">
-        <v>405</v>
-      </c>
-      <c r="B57" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C57" s="0">
-        <v>25.580006542099976</v>
-      </c>
-      <c r="D57" s="0"/>
-      <c r="E57" s="0"/>
-      <c r="F57" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G57" s="0"/>
-      <c r="H57" s="0"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="0" t="s">
-        <v>406</v>
-      </c>
-      <c r="B58" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C58" s="0">
-        <v>28.422229491222197</v>
-      </c>
-      <c r="D58" s="0"/>
-      <c r="E58" s="0"/>
-      <c r="F58" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G58" s="0"/>
-      <c r="H58" s="0"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="0" t="s">
-        <v>407</v>
-      </c>
-      <c r="B59" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C59" s="0">
-        <v>6.3586494759793881</v>
-      </c>
-      <c r="D59" s="0"/>
-      <c r="E59" s="0"/>
-      <c r="F59" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G59" s="0"/>
-      <c r="H59" s="0"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="0" t="s">
-        <v>408</v>
-      </c>
-      <c r="B60" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C60" s="0">
-        <v>12.884684205822825</v>
-      </c>
-      <c r="D60" s="0"/>
-      <c r="E60" s="0"/>
-      <c r="F60" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G60" s="0"/>
-      <c r="H60" s="0"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="0" t="s">
-        <v>409</v>
-      </c>
-      <c r="B61" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C61" s="0">
-        <v>2.2299999999999964</v>
-      </c>
-      <c r="D61" s="0"/>
-      <c r="E61" s="0"/>
-      <c r="F61" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G61" s="0"/>
-      <c r="H61" s="0"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="0" t="s">
-        <v>410</v>
-      </c>
-      <c r="B62" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C62" s="0">
-        <v>11.011406321896699</v>
-      </c>
-      <c r="D62" s="0"/>
-      <c r="E62" s="0"/>
-      <c r="F62" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G62" s="0"/>
-      <c r="H62" s="0"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="0" t="s">
-        <v>411</v>
-      </c>
-      <c r="B63" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C63" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="D63" s="0"/>
-      <c r="E63" s="0"/>
-      <c r="F63" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G63" s="0"/>
-      <c r="H63" s="0"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="0" t="s">
-        <v>412</v>
-      </c>
-      <c r="B64" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C64" s="0">
-        <v>5.6667672012645314</v>
-      </c>
-      <c r="D64" s="0"/>
-      <c r="E64" s="0"/>
-      <c r="F64" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G64" s="0"/>
-      <c r="H64" s="0"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="0" t="s">
-        <v>413</v>
-      </c>
-      <c r="B65" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C65" s="0">
-        <v>19.023298859748962</v>
-      </c>
-      <c r="D65" s="0"/>
-      <c r="E65" s="0"/>
-      <c r="F65" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G65" s="0"/>
-      <c r="H65" s="0"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="0" t="s">
-        <v>414</v>
-      </c>
-      <c r="B66" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C66" s="0">
-        <v>5.2940237236683272</v>
-      </c>
-      <c r="D66" s="0"/>
-      <c r="E66" s="0"/>
-      <c r="F66" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G66" s="0"/>
-      <c r="H66" s="0"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="0" t="s">
-        <v>415</v>
-      </c>
-      <c r="B67" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C67" s="0">
-        <v>22.608098531363336</v>
-      </c>
-      <c r="D67" s="0"/>
-      <c r="E67" s="0"/>
-      <c r="F67" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G67" s="0"/>
-      <c r="H67" s="0"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="0" t="s">
-        <v>416</v>
-      </c>
-      <c r="B68" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C68" s="0">
-        <v>12.709922788411269</v>
-      </c>
-      <c r="D68" s="0"/>
-      <c r="E68" s="0"/>
-      <c r="F68" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G68" s="0"/>
-      <c r="H68" s="0"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="0" t="s">
-        <v>417</v>
-      </c>
-      <c r="B69" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C69" s="0">
-        <v>16.27392540932771</v>
-      </c>
-      <c r="D69" s="0"/>
-      <c r="E69" s="0"/>
-      <c r="F69" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G69" s="0"/>
-      <c r="H69" s="0"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="0" t="s">
-        <v>418</v>
-      </c>
-      <c r="B70" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C70" s="0">
-        <v>15.956485750905872</v>
-      </c>
-      <c r="D70" s="0"/>
-      <c r="E70" s="0"/>
-      <c r="F70" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G70" s="0"/>
-      <c r="H70" s="0"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="0" t="s">
-        <v>419</v>
-      </c>
-      <c r="B71" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C71" s="0">
-        <v>13.695854805920606</v>
-      </c>
-      <c r="D71" s="0"/>
-      <c r="E71" s="0"/>
-      <c r="F71" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G71" s="0"/>
-      <c r="H71" s="0"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="0" t="s">
-        <v>420</v>
-      </c>
-      <c r="B72" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C72" s="0">
-        <v>1.0954451150103324</v>
-      </c>
-      <c r="D72" s="0"/>
-      <c r="E72" s="0"/>
-      <c r="F72" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G72" s="0"/>
-      <c r="H72" s="0"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="0" t="s">
-        <v>421</v>
-      </c>
-      <c r="B73" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C73" s="0">
-        <v>24.094842552110709</v>
-      </c>
-      <c r="D73" s="0"/>
-      <c r="E73" s="0"/>
-      <c r="F73" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G73" s="0"/>
-      <c r="H73" s="0"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="0" t="s">
-        <v>422</v>
-      </c>
-      <c r="B74" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C74" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="D74" s="0"/>
-      <c r="E74" s="0"/>
-      <c r="F74" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G74" s="0"/>
-      <c r="H74" s="0"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="0" t="s">
-        <v>423</v>
-      </c>
-      <c r="B75" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C75" s="0">
-        <v>156.52835771396133</v>
-      </c>
-      <c r="D75" s="0"/>
-      <c r="E75" s="0"/>
-      <c r="F75" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G75" s="0"/>
-      <c r="H75" s="0"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="0" t="s">
-        <v>424</v>
-      </c>
-      <c r="B76" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C76" s="0">
-        <v>44593.916314433394</v>
-      </c>
-      <c r="D76" s="0"/>
-      <c r="E76" s="0"/>
-      <c r="F76" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G76" s="0"/>
-      <c r="H76" s="0"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="0" t="s">
-        <v>425</v>
-      </c>
-      <c r="B77" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C77" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="D77" s="0"/>
-      <c r="E77" s="0"/>
-      <c r="F77" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G77" s="0"/>
-      <c r="H77" s="0"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="0" t="s">
-        <v>426</v>
-      </c>
-      <c r="B78" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C78" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="D78" s="0"/>
-      <c r="E78" s="0"/>
-      <c r="F78" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G78" s="0"/>
-      <c r="H78" s="0"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="0" t="s">
-        <v>427</v>
-      </c>
-      <c r="B79" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C79" s="0">
-        <v>13</v>
-      </c>
-      <c r="D79" s="0"/>
-      <c r="E79" s="0"/>
-      <c r="F79" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G79" s="0"/>
-      <c r="H79" s="0"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="0" t="s">
-        <v>428</v>
-      </c>
-      <c r="B80" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C80" s="0">
-        <v>86094.946347033809</v>
-      </c>
-      <c r="D80" s="0"/>
-      <c r="E80" s="0"/>
-      <c r="F80" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G80" s="0"/>
-      <c r="H80" s="0"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="0" t="s">
-        <v>429</v>
-      </c>
-      <c r="B81" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C81" s="0">
-        <v>0.16336801963384023</v>
-      </c>
-      <c r="D81" s="0"/>
-      <c r="E81" s="0"/>
-      <c r="F81" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G81" s="0"/>
-      <c r="H81" s="0"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="0" t="s">
-        <v>430</v>
-      </c>
-      <c r="B82" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C82" s="0">
-        <v>2.185902626124927</v>
-      </c>
-      <c r="D82" s="0"/>
-      <c r="E82" s="0"/>
-      <c r="F82" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G82" s="0"/>
-      <c r="H82" s="0"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="0" t="s">
-        <v>431</v>
-      </c>
-      <c r="B83" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C83" s="0" t="s">
-        <v>507</v>
-      </c>
-      <c r="D83" s="0"/>
-      <c r="E83" s="0"/>
-      <c r="F83" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G83" s="0"/>
-      <c r="H83" s="0"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="0" t="s">
-        <v>432</v>
-      </c>
-      <c r="B84" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C84" s="0">
-        <v>-0.040973254512723323</v>
-      </c>
-      <c r="D84" s="0"/>
-      <c r="E84" s="0"/>
-      <c r="F84" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G84" s="0"/>
-      <c r="H84" s="0"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="0" t="s">
-        <v>433</v>
-      </c>
-      <c r="B85" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C85" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="D85" s="0"/>
-      <c r="E85" s="0"/>
-      <c r="F85" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G85" s="0"/>
-      <c r="H85" s="0"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="0" t="s">
-        <v>434</v>
-      </c>
-      <c r="B86" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C86" s="0">
-        <v>0.254</v>
-      </c>
-      <c r="D86" s="0"/>
-      <c r="E86" s="0"/>
-      <c r="F86" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G86" s="0"/>
-      <c r="H86" s="0"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="0" t="s">
-        <v>435</v>
-      </c>
-      <c r="B87" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C87" s="0">
-        <v>0.127</v>
-      </c>
-      <c r="D87" s="0"/>
-      <c r="E87" s="0"/>
-      <c r="F87" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G87" s="0"/>
-      <c r="H87" s="0"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="0" t="s">
-        <v>436</v>
-      </c>
-      <c r="B88" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C88" s="0">
-        <v>14500</v>
-      </c>
-      <c r="D88" s="0"/>
-      <c r="E88" s="0"/>
-      <c r="F88" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G88" s="0"/>
-      <c r="H88" s="0"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="0" t="s">
-        <v>437</v>
-      </c>
-      <c r="B89" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C89" s="0" t="s">
-        <v>508</v>
-      </c>
-      <c r="D89" s="0"/>
-      <c r="E89" s="0"/>
-      <c r="F89" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G89" s="0"/>
-      <c r="H89" s="0"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="0" t="s">
-        <v>438</v>
-      </c>
-      <c r="B90" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C90" s="0" t="s">
-        <v>509</v>
-      </c>
-      <c r="D90" s="0"/>
-      <c r="E90" s="0"/>
-      <c r="F90" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G90" s="0"/>
-      <c r="H90" s="0"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="0" t="s">
-        <v>439</v>
-      </c>
-      <c r="B91" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C91" s="0" t="s">
-        <v>510</v>
-      </c>
-      <c r="D91" s="0"/>
-      <c r="E91" s="0"/>
-      <c r="F91" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G91" s="0"/>
-      <c r="H91" s="0"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="0" t="s">
-        <v>440</v>
-      </c>
-      <c r="B92" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C92" s="0" t="s">
-        <v>510</v>
-      </c>
-      <c r="D92" s="0"/>
-      <c r="E92" s="0"/>
-      <c r="F92" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G92" s="0"/>
-      <c r="H92" s="0"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="0" t="s">
-        <v>441</v>
-      </c>
-      <c r="B93" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C93" s="0" t="s">
-        <v>510</v>
-      </c>
-      <c r="D93" s="0"/>
-      <c r="E93" s="0"/>
-      <c r="F93" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G93" s="0"/>
-      <c r="H93" s="0"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="0" t="s">
-        <v>442</v>
-      </c>
-      <c r="B94" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C94" s="0" t="s">
-        <v>510</v>
-      </c>
-      <c r="D94" s="0"/>
-      <c r="E94" s="0"/>
-      <c r="F94" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G94" s="0"/>
-      <c r="H94" s="0"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="0" t="s">
-        <v>443</v>
-      </c>
-      <c r="B95" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C95" s="0" t="s">
-        <v>510</v>
-      </c>
-      <c r="D95" s="0"/>
-      <c r="E95" s="0"/>
-      <c r="F95" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G95" s="0"/>
-      <c r="H95" s="0"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="0" t="s">
-        <v>444</v>
-      </c>
-      <c r="B96" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C96" s="0" t="s">
-        <v>510</v>
-      </c>
-      <c r="D96" s="0"/>
-      <c r="E96" s="0"/>
-      <c r="F96" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G96" s="0"/>
-      <c r="H96" s="0"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="0" t="s">
-        <v>445</v>
-      </c>
-      <c r="B97" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C97" s="0" t="s">
-        <v>510</v>
-      </c>
-      <c r="D97" s="0"/>
-      <c r="E97" s="0"/>
-      <c r="F97" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G97" s="0"/>
-      <c r="H97" s="0"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="0" t="s">
-        <v>446</v>
-      </c>
-      <c r="B98" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C98" s="0" t="s">
-        <v>510</v>
-      </c>
-      <c r="D98" s="0"/>
-      <c r="E98" s="0"/>
-      <c r="F98" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G98" s="0"/>
-      <c r="H98" s="0"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="0" t="s">
-        <v>447</v>
-      </c>
-      <c r="B99" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C99" s="0" t="s">
-        <v>511</v>
-      </c>
-      <c r="D99" s="0"/>
-      <c r="E99" s="0"/>
-      <c r="F99" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G99" s="0"/>
-      <c r="H99" s="0"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="0" t="s">
-        <v>448</v>
-      </c>
-      <c r="B100" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C100" s="0">
-        <v>700</v>
-      </c>
-      <c r="D100" s="0"/>
-      <c r="E100" s="0"/>
-      <c r="F100" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G100" s="0"/>
-      <c r="H100" s="0"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="0" t="s">
-        <v>449</v>
-      </c>
-      <c r="B101" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C101" s="0">
-        <v>50</v>
-      </c>
-      <c r="D101" s="0"/>
-      <c r="E101" s="0"/>
-      <c r="F101" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G101" s="0"/>
-      <c r="H101" s="0"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="0" t="s">
-        <v>450</v>
-      </c>
-      <c r="B102" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C102" s="0" t="s">
-        <v>512</v>
-      </c>
-      <c r="D102" s="0"/>
-      <c r="E102" s="0"/>
-      <c r="F102" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G102" s="0"/>
-      <c r="H102" s="0"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="0" t="s">
-        <v>451</v>
-      </c>
-      <c r="B103" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C103" s="0" t="s">
-        <v>510</v>
-      </c>
-      <c r="D103" s="0"/>
-      <c r="E103" s="0"/>
-      <c r="F103" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G103" s="0"/>
-      <c r="H103" s="0"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="0" t="s">
-        <v>452</v>
-      </c>
-      <c r="B104" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C104" s="0" t="s">
-        <v>513</v>
-      </c>
-      <c r="D104" s="0"/>
-      <c r="E104" s="0"/>
-      <c r="F104" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G104" s="0"/>
-      <c r="H104" s="0"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="0" t="s">
-        <v>453</v>
-      </c>
-      <c r="B105" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C105" s="0" t="s">
-        <v>514</v>
-      </c>
-      <c r="D105" s="0"/>
-      <c r="E105" s="0"/>
-      <c r="F105" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G105" s="0"/>
-      <c r="H105" s="0"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="0" t="s">
-        <v>454</v>
-      </c>
-      <c r="B106" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C106" s="0" t="s">
-        <v>515</v>
-      </c>
-      <c r="D106" s="0"/>
-      <c r="E106" s="0"/>
-      <c r="F106" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G106" s="0"/>
-      <c r="H106" s="0"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="0" t="s">
-        <v>455</v>
-      </c>
-      <c r="B107" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C107" s="0" t="s">
-        <v>516</v>
-      </c>
-      <c r="D107" s="0"/>
-      <c r="E107" s="0"/>
-      <c r="F107" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G107" s="0"/>
-      <c r="H107" s="0"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="0" t="s">
-        <v>456</v>
-      </c>
-      <c r="B108" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C108" s="0" t="s">
-        <v>517</v>
-      </c>
-      <c r="D108" s="0"/>
-      <c r="E108" s="0"/>
-      <c r="F108" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G108" s="0"/>
-      <c r="H108" s="0"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="0" t="s">
-        <v>457</v>
-      </c>
-      <c r="B109" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C109" s="0" t="s">
-        <v>518</v>
-      </c>
-      <c r="D109" s="0"/>
-      <c r="E109" s="0"/>
-      <c r="F109" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G109" s="0"/>
-      <c r="H109" s="0"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="0" t="s">
-        <v>458</v>
-      </c>
-      <c r="B110" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C110" s="0" t="s">
-        <v>519</v>
-      </c>
-      <c r="D110" s="0"/>
-      <c r="E110" s="0"/>
-      <c r="F110" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G110" s="0"/>
-      <c r="H110" s="0"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="0" t="s">
-        <v>459</v>
-      </c>
-      <c r="B111" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C111" s="0">
-        <v>32.946133306980855</v>
-      </c>
-      <c r="D111" s="0"/>
-      <c r="E111" s="0"/>
-      <c r="F111" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G111" s="0"/>
-      <c r="H111" s="0"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="0" t="s">
-        <v>460</v>
-      </c>
-      <c r="B112" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C112" s="0">
-        <v>0</v>
-      </c>
-      <c r="D112" s="0"/>
-      <c r="E112" s="0"/>
-      <c r="F112" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G112" s="0"/>
-      <c r="H112" s="0"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="0" t="s">
-        <v>461</v>
-      </c>
-      <c r="B113" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C113" s="0" t="s">
-        <v>520</v>
-      </c>
-      <c r="D113" s="0"/>
-      <c r="E113" s="0"/>
-      <c r="F113" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G113" s="0"/>
-      <c r="H113" s="0"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="0" t="s">
-        <v>462</v>
-      </c>
-      <c r="B114" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C114" s="0">
-        <v>86.068285472894019</v>
-      </c>
-      <c r="D114" s="0"/>
-      <c r="E114" s="0"/>
-      <c r="F114" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G114" s="0"/>
-      <c r="H114" s="0"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="0" t="s">
-        <v>463</v>
-      </c>
-      <c r="B115" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C115" s="0">
-        <v>0</v>
-      </c>
-      <c r="D115" s="0"/>
-      <c r="E115" s="0"/>
-      <c r="F115" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G115" s="0"/>
-      <c r="H115" s="0"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="0" t="s">
-        <v>464</v>
-      </c>
-      <c r="B116" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C116" s="0">
-        <v>-1.8275795392708134</v>
-      </c>
-      <c r="D116" s="0"/>
-      <c r="E116" s="0"/>
-      <c r="F116" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G116" s="0"/>
-      <c r="H116" s="0"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="0" t="s">
-        <v>465</v>
-      </c>
-      <c r="B117" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C117" s="0">
-        <v>0</v>
-      </c>
-      <c r="D117" s="0"/>
-      <c r="E117" s="0"/>
-      <c r="F117" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G117" s="0"/>
-      <c r="H117" s="0"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="0" t="s">
-        <v>466</v>
-      </c>
-      <c r="B118" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C118" s="0">
-        <v>1.7526473681977495</v>
-      </c>
-      <c r="D118" s="0"/>
-      <c r="E118" s="0"/>
-      <c r="F118" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G118" s="0"/>
-      <c r="H118" s="0"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="0" t="s">
-        <v>467</v>
-      </c>
-      <c r="B119" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C119" s="0">
-        <v>0.15168253041257554</v>
-      </c>
-      <c r="D119" s="0"/>
-      <c r="E119" s="0"/>
-      <c r="F119" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G119" s="0"/>
-      <c r="H119" s="0"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="0" t="s">
-        <v>468</v>
-      </c>
-      <c r="B120" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C120" s="0">
-        <v>2.4110213483593652</v>
-      </c>
-      <c r="D120" s="0"/>
-      <c r="E120" s="0"/>
-      <c r="F120" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G120" s="0"/>
-      <c r="H120" s="0"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="0" t="s">
-        <v>469</v>
-      </c>
-      <c r="B121" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C121" s="0">
-        <v>2.7131092758196531</v>
-      </c>
-      <c r="D121" s="0"/>
-      <c r="E121" s="0"/>
-      <c r="F121" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G121" s="0"/>
-      <c r="H121" s="0"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="0" t="s">
-        <v>470</v>
-      </c>
-      <c r="B122" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C122" s="0">
-        <v>16.090147165877724</v>
-      </c>
-      <c r="D122" s="0"/>
-      <c r="E122" s="0"/>
-      <c r="F122" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G122" s="0"/>
-      <c r="H122" s="0"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="0" t="s">
-        <v>471</v>
-      </c>
-      <c r="B123" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C123" s="0">
-        <v>16.925292122478595</v>
-      </c>
-      <c r="D123" s="0"/>
-      <c r="E123" s="0"/>
-      <c r="F123" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G123" s="0"/>
-      <c r="H123" s="0"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="0" t="s">
-        <v>472</v>
-      </c>
-      <c r="B124" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C124" s="0">
-        <v>0.35178486510320511</v>
-      </c>
-      <c r="D124" s="0"/>
-      <c r="E124" s="0"/>
-      <c r="F124" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G124" s="0"/>
-      <c r="H124" s="0"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="0" t="s">
-        <v>473</v>
-      </c>
-      <c r="B125" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C125" s="0" t="s">
-        <v>521</v>
-      </c>
-      <c r="D125" s="0"/>
-      <c r="E125" s="0"/>
-      <c r="F125" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G125" s="0"/>
-      <c r="H125" s="0"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="0" t="s">
-        <v>474</v>
-      </c>
-      <c r="B126" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C126" s="0">
-        <v>233.69773788009346</v>
-      </c>
-      <c r="D126" s="0"/>
-      <c r="E126" s="0"/>
-      <c r="F126" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G126" s="0"/>
-      <c r="H126" s="0"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="0" t="s">
-        <v>475</v>
-      </c>
-      <c r="B127" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C127" s="0">
-        <v>0.35242563899228196</v>
-      </c>
-      <c r="D127" s="0"/>
-      <c r="E127" s="0"/>
-      <c r="F127" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G127" s="0"/>
-      <c r="H127" s="0"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="0" t="s">
-        <v>476</v>
-      </c>
-      <c r="B128" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C128" s="0" t="s">
-        <v>521</v>
-      </c>
-      <c r="D128" s="0"/>
-      <c r="E128" s="0"/>
-      <c r="F128" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G128" s="0"/>
-      <c r="H128" s="0"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="0" t="s">
-        <v>477</v>
-      </c>
-      <c r="B129" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C129" s="0">
-        <v>9.4744003772526408</v>
-      </c>
-      <c r="D129" s="0"/>
-      <c r="E129" s="0"/>
-      <c r="F129" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G129" s="0"/>
-      <c r="H129" s="0"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="0" t="s">
-        <v>478</v>
-      </c>
-      <c r="B130" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C130" s="0">
-        <v>341.83792795003058</v>
-      </c>
-      <c r="D130" s="0"/>
-      <c r="E130" s="0"/>
-      <c r="F130" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G130" s="0"/>
-      <c r="H130" s="0"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="0" t="s">
-        <v>479</v>
-      </c>
-      <c r="B131" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C131" s="0">
-        <v>34.733446426726843</v>
-      </c>
-      <c r="D131" s="0"/>
-      <c r="E131" s="0"/>
-      <c r="F131" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G131" s="0"/>
-      <c r="H131" s="0"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="0" t="s">
-        <v>480</v>
-      </c>
-      <c r="B132" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C132" s="0">
-        <v>0.42099254615460552</v>
-      </c>
-      <c r="D132" s="0"/>
-      <c r="E132" s="0"/>
-      <c r="F132" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G132" s="0"/>
-      <c r="H132" s="0"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="0" t="s">
-        <v>481</v>
-      </c>
-      <c r="B133" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C133" s="0">
-        <v>4.0516000000000005</v>
-      </c>
-      <c r="D133" s="0"/>
-      <c r="E133" s="0"/>
-      <c r="F133" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G133" s="0"/>
-      <c r="H133" s="0"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="0" t="s">
-        <v>482</v>
-      </c>
-      <c r="B134" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C134" s="0">
-        <v>39.746196000000005</v>
-      </c>
-      <c r="D134" s="0"/>
-      <c r="E134" s="0"/>
-      <c r="F134" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G134" s="0"/>
-      <c r="H134" s="0"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="0" t="s">
-        <v>483</v>
-      </c>
-      <c r="B135" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C135" s="0">
-        <v>18.230437113682747</v>
-      </c>
-      <c r="D135" s="0"/>
-      <c r="E135" s="0"/>
-      <c r="F135" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G135" s="0"/>
-      <c r="H135" s="0"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="0" t="s">
-        <v>484</v>
-      </c>
-      <c r="B136" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C136" s="0">
-        <v>0.080999999999999989</v>
-      </c>
-      <c r="D136" s="0"/>
-      <c r="E136" s="0"/>
-      <c r="F136" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G136" s="0"/>
-      <c r="H136" s="0"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="0" t="s">
-        <v>485</v>
-      </c>
-      <c r="B137" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C137" s="0">
-        <v>64.749890848167752</v>
-      </c>
-      <c r="D137" s="0"/>
-      <c r="E137" s="0"/>
-      <c r="F137" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G137" s="0"/>
-      <c r="H137" s="0"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="0" t="s">
-        <v>486</v>
-      </c>
-      <c r="B138" s="0" t="s">
-        <v>506</v>
-      </c>
-      <c r="C138" s="0">
-        <v>0.29999999999999999</v>
-      </c>
-      <c r="D138" s="0"/>
-      <c r="E138" s="0"/>
-      <c r="F138" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G138" s="0"/>
-      <c r="H138" s="0"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="0" t="s">
-        <v>487</v>
-      </c>
-      <c r="B139" s="0" t="s">
-        <v>506</v>
-      </c>
-      <c r="C139" s="0">
-        <v>26.360381758366742</v>
-      </c>
-      <c r="D139" s="0"/>
-      <c r="E139" s="0"/>
-      <c r="F139" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G139" s="0"/>
-      <c r="H139" s="0"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="0" t="s">
-        <v>488</v>
-      </c>
-      <c r="B140" s="0" t="s">
-        <v>506</v>
-      </c>
-      <c r="C140" s="0">
-        <v>3.6396182416332579</v>
-      </c>
-      <c r="D140" s="0"/>
-      <c r="E140" s="0"/>
-      <c r="F140" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G140" s="0"/>
-      <c r="H140" s="0"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="0" t="s">
-        <v>489</v>
-      </c>
-      <c r="B141" s="0" t="s">
-        <v>506</v>
-      </c>
-      <c r="C141" s="0">
-        <v>0.25</v>
-      </c>
-      <c r="D141" s="0"/>
-      <c r="E141" s="0"/>
-      <c r="F141" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G141" s="0"/>
-      <c r="H141" s="0"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="0" t="s">
-        <v>490</v>
-      </c>
-      <c r="B142" s="0" t="s">
-        <v>506</v>
-      </c>
-      <c r="C142" s="0">
-        <v>0.69999999999999996</v>
-      </c>
-      <c r="D142" s="0"/>
-      <c r="E142" s="0"/>
-      <c r="F142" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G142" s="0"/>
-      <c r="H142" s="0"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="0" t="s">
-        <v>491</v>
-      </c>
-      <c r="B143" s="0" t="s">
-        <v>506</v>
-      </c>
-      <c r="C143" s="0">
-        <v>1</v>
-      </c>
-      <c r="D143" s="0"/>
-      <c r="E143" s="0"/>
-      <c r="F143" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G143" s="0"/>
-      <c r="H143" s="0"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="0" t="s">
-        <v>492</v>
-      </c>
-      <c r="B144" s="0" t="s">
-        <v>506</v>
-      </c>
-      <c r="C144" s="0">
-        <v>0.12048857500544551</v>
-      </c>
-      <c r="D144" s="0"/>
-      <c r="E144" s="0"/>
-      <c r="F144" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G144" s="0"/>
-      <c r="H144" s="0"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="0" t="s">
-        <v>493</v>
-      </c>
-      <c r="B145" s="0" t="s">
-        <v>506</v>
-      </c>
-      <c r="C145" s="0">
-        <v>119.66043834086311</v>
-      </c>
-      <c r="D145" s="0"/>
-      <c r="E145" s="0"/>
-      <c r="F145" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G145" s="0"/>
-      <c r="H145" s="0"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="0" t="s">
-        <v>494</v>
-      </c>
-      <c r="B146" s="0" t="s">
-        <v>506</v>
-      </c>
-      <c r="C146" s="0">
-        <v>0.074583678423586861</v>
-      </c>
-      <c r="D146" s="0"/>
-      <c r="E146" s="0"/>
-      <c r="F146" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G146" s="0"/>
-      <c r="H146" s="0"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="0" t="s">
-        <v>495</v>
-      </c>
-      <c r="B147" s="0" t="s">
-        <v>506</v>
-      </c>
-      <c r="C147" s="0">
-        <v>1.0700000000000001</v>
-      </c>
-      <c r="D147" s="0"/>
-      <c r="E147" s="0"/>
-      <c r="F147" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G147" s="0"/>
-      <c r="H147" s="0"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="0" t="s">
-        <v>496</v>
-      </c>
-      <c r="B148" s="0" t="s">
-        <v>506</v>
-      </c>
-      <c r="C148" s="0">
-        <v>0.29999999999999999</v>
-      </c>
-      <c r="D148" s="0"/>
-      <c r="E148" s="0"/>
-      <c r="F148" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G148" s="0"/>
-      <c r="H148" s="0"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="0" t="s">
-        <v>497</v>
-      </c>
-      <c r="B149" s="0" t="s">
-        <v>506</v>
-      </c>
-      <c r="C149" s="0">
-        <v>29.162154556467332</v>
-      </c>
-      <c r="D149" s="0"/>
-      <c r="E149" s="0"/>
-      <c r="F149" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G149" s="0"/>
-      <c r="H149" s="0"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="0" t="s">
-        <v>498</v>
-      </c>
-      <c r="B150" s="0" t="s">
-        <v>506</v>
-      </c>
-      <c r="C150" s="0">
-        <v>0.83784544353266455</v>
-      </c>
-      <c r="D150" s="0"/>
-      <c r="E150" s="0"/>
-      <c r="F150" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G150" s="0"/>
-      <c r="H150" s="0"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="0" t="s">
-        <v>499</v>
-      </c>
-      <c r="B151" s="0" t="s">
-        <v>506</v>
-      </c>
-      <c r="C151" s="0">
-        <v>5.2740736776131758</v>
-      </c>
-      <c r="D151" s="0"/>
-      <c r="E151" s="0"/>
-      <c r="F151" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G151" s="0"/>
-      <c r="H151" s="0"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="0" t="s">
-        <v>500</v>
-      </c>
-      <c r="B152" s="0" t="s">
-        <v>506</v>
-      </c>
-      <c r="C152" s="0">
-        <v>0.3656082203404642</v>
-      </c>
-      <c r="D152" s="0"/>
-      <c r="E152" s="0"/>
-      <c r="F152" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G152" s="0"/>
-      <c r="H152" s="0"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="0" t="s">
-        <v>501</v>
-      </c>
-      <c r="B153" s="0" t="s">
-        <v>506</v>
-      </c>
-      <c r="C153" s="0">
-        <v>0.14999999999999999</v>
-      </c>
-      <c r="D153" s="0"/>
-      <c r="E153" s="0"/>
-      <c r="F153" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G153" s="0"/>
-      <c r="H153" s="0"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="0" t="s">
+      <c r="F155" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
         <v>502</v>
       </c>
-      <c r="B154" s="0" t="s">
-        <v>506</v>
-      </c>
-      <c r="C154" s="0">
-        <v>-0.79111105164197637</v>
-      </c>
-      <c r="D154" s="0"/>
-      <c r="E154" s="0"/>
-      <c r="F154" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G154" s="0"/>
-      <c r="H154" s="0"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="0" t="s">
+      <c r="B156" t="s">
+        <v>504</v>
+      </c>
+      <c r="C156">
+        <v>5</v>
+      </c>
+      <c r="F156" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
         <v>503</v>
       </c>
-      <c r="B155" s="0" t="s">
-        <v>506</v>
-      </c>
-      <c r="C155" s="0">
-        <v>0.12602616170797043</v>
-      </c>
-      <c r="D155" s="0"/>
-      <c r="E155" s="0"/>
-      <c r="F155" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G155" s="0"/>
-      <c r="H155" s="0"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="0" t="s">
+      <c r="B157" t="s">
         <v>504</v>
       </c>
-      <c r="B156" s="0" t="s">
-        <v>506</v>
-      </c>
-      <c r="C156" s="0">
-        <v>5</v>
-      </c>
-      <c r="D156" s="0"/>
-      <c r="E156" s="0"/>
-      <c r="F156" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G156" s="0"/>
-      <c r="H156" s="0"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="0" t="s">
-        <v>505</v>
-      </c>
-      <c r="B157" s="0" t="s">
-        <v>506</v>
-      </c>
-      <c r="C157" s="0">
+      <c r="C157">
         <v>-0.18486997339978403</v>
       </c>
-      <c r="D157" s="0"/>
-      <c r="E157" s="0"/>
-      <c r="F157" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G157" s="0"/>
-      <c r="H157" s="0"/>
+      <c r="F157" t="s">
+        <v>378</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFCC8514-E0AF-4C67-BF86-8649FC702924}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFCC8514-E0AF-4C67-BF86-8649FC702924}">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.42578125" customWidth="true"/>
-    <col min="2" max="3" width="32.42578125" style="20" customWidth="true"/>
-    <col min="4" max="4" width="13.28515625" style="20" customWidth="true"/>
+    <col min="1" max="1" width="32.42578125" customWidth="1"/>
+    <col min="2" max="3" width="32.42578125" style="20" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" style="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>274</v>
       </c>
@@ -6950,7 +6678,7 @@
         <v>303</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>276</v>
       </c>
@@ -6964,7 +6692,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>277</v>
       </c>
@@ -6978,7 +6706,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>278</v>
       </c>
@@ -6992,7 +6720,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>279</v>
       </c>
@@ -7006,7 +6734,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>304</v>
       </c>
@@ -7020,7 +6748,7 @@
         <v>-4.4999999999999998E-2</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>280</v>
       </c>
@@ -7034,7 +6762,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>281</v>
       </c>
@@ -7048,7 +6776,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>282</v>
       </c>
@@ -7062,7 +6790,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>283</v>
       </c>
@@ -7076,7 +6804,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>284</v>
       </c>
@@ -7090,7 +6818,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>285</v>
       </c>
@@ -7104,7 +6832,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>286</v>
       </c>
@@ -7118,7 +6846,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>287</v>
       </c>
@@ -7132,7 +6860,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>288</v>
       </c>
@@ -7146,7 +6874,7 @@
         <v>-7.8E-2</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>289</v>
       </c>
@@ -7160,7 +6888,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>290</v>
       </c>
@@ -7174,7 +6902,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>291</v>
       </c>
@@ -7188,7 +6916,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="19" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>293</v>
       </c>
@@ -7202,7 +6930,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>292</v>
       </c>
@@ -7222,28 +6950,28 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{118BE621-EF6B-4648-868E-9937B9C5B685}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{118BE621-EF6B-4648-868E-9937B9C5B685}">
   <dimension ref="A1:F32"/>
-  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="48.140625" style="2" customWidth="true"/>
-    <col min="2" max="4" width="15.7109375" style="2" customWidth="true"/>
-    <col min="5" max="5" width="3.7109375" style="2" customWidth="true"/>
-    <col min="6" max="6" width="46.7109375" style="2" customWidth="true"/>
+    <col min="1" max="1" width="48.140625" style="2" customWidth="1"/>
+    <col min="2" max="4" width="15.7109375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="3.7109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="46.7109375" style="2" customWidth="1"/>
     <col min="7" max="16384" width="8.7109375" style="2"/>
   </cols>
   <sheetData>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>207</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>244</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>208</v>
       </c>
@@ -7257,13 +6985,13 @@
         <v>211</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>212</v>
       </c>
       <c r="B5" s="5">
         <f>(Inputs!C19*Inputs!C77/Inputs!C72)/(Inputs!C25-Inputs!C26)</f>
-        <v>0.42877435804042974</v>
+        <v>0.43632320237212752</v>
       </c>
       <c r="C5" s="15">
         <v>0.19600000000000001</v>
@@ -7275,7 +7003,7 @@
         <v>213</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>214</v>
       </c>
@@ -7295,13 +7023,13 @@
         <v>215</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>216</v>
       </c>
       <c r="B7" s="5">
         <f>B6*B5</f>
-        <v>0.10719358951010743</v>
+        <v>0.10908080059303188</v>
       </c>
       <c r="C7" s="5">
         <f>C6*C5</f>
@@ -7315,7 +7043,7 @@
         <v>245</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>217</v>
       </c>
@@ -7333,7 +7061,7 @@
         <v>246</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>218</v>
       </c>
@@ -7353,7 +7081,7 @@
         <v>219</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>220</v>
       </c>
@@ -7370,7 +7098,7 @@
         <v>221</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>222</v>
       </c>
@@ -7387,7 +7115,7 @@
         <v>247</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>223</v>
       </c>
@@ -7407,7 +7135,7 @@
         <v>224</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>225</v>
       </c>
@@ -7424,7 +7152,7 @@
         <v>226</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>257</v>
       </c>
@@ -7444,7 +7172,7 @@
         <v>259</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>258</v>
       </c>
@@ -7464,7 +7192,7 @@
         <v>260</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>227</v>
       </c>
@@ -7472,7 +7200,7 @@
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>228</v>
       </c>
@@ -7489,7 +7217,7 @@
         <v>1.9823131728623846</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>229</v>
       </c>
@@ -7506,7 +7234,7 @@
         <v>1.1592794807274085</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="19" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>230</v>
       </c>
@@ -7523,7 +7251,7 @@
         <v>-0.62740704594148844</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>231</v>
       </c>
@@ -7540,7 +7268,7 @@
         <v>-0.96540266006846076</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="21" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>232</v>
       </c>
@@ -7548,7 +7276,7 @@
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="22" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>233</v>
       </c>
@@ -7565,7 +7293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="23" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>234</v>
       </c>
@@ -7582,7 +7310,7 @@
         <v>0.52359877559829882</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="24" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>235</v>
       </c>
@@ -7599,7 +7327,7 @@
         <v>-0.50548365077118673</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>236</v>
       </c>
@@ -7616,13 +7344,13 @@
         <v>324.01250000000005</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="26" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>237</v>
       </c>
       <c r="B26" s="5">
         <f>B7*B8</f>
-        <v>2.4118557639774177E-2</v>
+        <v>2.4543180133432176E-2</v>
       </c>
       <c r="C26" s="5">
         <f>C7*C8</f>
@@ -7633,13 +7361,13 @@
         <v>1.42884E-2</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="27" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>238</v>
       </c>
       <c r="B27" s="12">
         <f>B24*B25*B26*B7</f>
-        <v>-0.2069388778157791</v>
+        <v>-0.21428960045194023</v>
       </c>
       <c r="C27" s="12">
         <f>C24*C25*C26*C7</f>
@@ -7650,13 +7378,13 @@
         <v>-0.13760360258695806</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="28" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>239</v>
       </c>
       <c r="B28" s="6">
         <f>ABS(B27)*B13</f>
-        <v>0.2069388778157791</v>
+        <v>0.21428960045194023</v>
       </c>
       <c r="C28" s="6">
         <f>ABS(C27)*C13</f>
@@ -7667,13 +7395,13 @@
         <v>0.13760360258695806</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="29" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>240</v>
       </c>
       <c r="B29" s="13">
         <f>B28*B14/B15*141.612</f>
-        <v>34.476503959115426</v>
+        <v>35.701151646117836</v>
       </c>
       <c r="C29" s="13">
         <f>C28*C14/C15*141.612</f>
@@ -7684,7 +7412,7 @@
         <v>22.925083964169769</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>241</v>
       </c>
@@ -7692,7 +7420,7 @@
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="31" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>242</v>
       </c>
@@ -7700,7 +7428,7 @@
       <c r="C31" s="14"/>
       <c r="D31" s="14"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="32" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>243</v>
       </c>
@@ -7723,22 +7451,23 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="C109:F109"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="11.7109375" customWidth="true"/>
-    <col min="6" max="6" width="153.85546875" customWidth="true"/>
+    <col min="3" max="3" width="11.7109375" customWidth="1"/>
+    <col min="6" max="6" width="153.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="109">
-      <c r="C109" s="0">
+    <row r="109" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C109">
         <v>11.941543440928031</v>
       </c>
-      <c r="F109" s="0" t="s">
-        <v>382</v>
+      <c r="F109" t="s">
+        <v>380</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ceaa8977d2236823/Documents/GitHub/451-DBF-Team01/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2a1ac608aa9918f7/Documents/GitHub/451-DBF-Team01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{37DAE441-3691-47BB-B387-517F08F01369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84407836-4197-495E-8968-99AA3ACC1078}"/>
+  <xr:revisionPtr revIDLastSave="78" documentId="13_ncr:1_{37DAE441-3691-47BB-B387-517F08F01369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0C8D41D-CB4D-4A5B-B008-BE7BD96D2718}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="9930" yWindow="4845" windowWidth="28500" windowHeight="13770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Hinge Moments" sheetId="2" r:id="rId4"/>
     <sheet name="Sheet1" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="true"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2192" uniqueCount="526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="524">
   <si>
     <t>Parameter</t>
   </si>
@@ -1596,9 +1596,6 @@
     <t>hard landing</t>
   </si>
   <si>
-    <t>Written by writeOutputs.m on 2026-10-06 13:56</t>
-  </si>
-  <si>
     <t>Motor Spec per Jackson</t>
   </si>
   <si>
@@ -1609,9 +1606,6 @@
   </si>
   <si>
     <t>mission_P_peak</t>
-  </si>
-  <si>
-    <t>Written by writeOutputs.m on 2026-10-06 17:23</t>
   </si>
   <si>
     <t>Written by writeOutputs.m on 2026-10-06 17:29</t>
@@ -1620,13 +1614,13 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1727,7 +1721,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1735,57 +1729,55 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border/>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="true"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="true"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="true" applyFill="true"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="true"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="true"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="true"/>
-    <xf numFmtId="166" fontId="5" fillId="3" borderId="0" xfId="1" applyNumberFormat="true" applyFont="true" applyFill="true"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="1" applyNumberFormat="true" applyFont="true" applyFill="true"/>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="0" xfId="1" applyNumberFormat="true" applyFont="true" applyFill="true"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="true"/>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="0" xfId="1" applyNumberFormat="true" applyFont="true" applyFill="true"/>
-    <xf numFmtId="2" fontId="6" fillId="4" borderId="0" xfId="1" applyNumberFormat="true" applyFont="true" applyFill="true"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="1" applyFont="true" applyFill="true"/>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="1" applyNumberFormat="true" applyFill="true"/>
-    <xf numFmtId="166" fontId="5" fillId="5" borderId="0" xfId="1" applyNumberFormat="true" applyFont="true" applyFill="true"/>
-    <xf numFmtId="2" fontId="5" fillId="5" borderId="0" xfId="1" applyNumberFormat="true" applyFont="true" applyFill="true"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="6" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="5" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" justifyLastLine="false" shrinkToFit="false" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" justifyLastLine="false" shrinkToFit="false" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" justifyLastLine="false" shrinkToFit="false" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1801,40 +1793,40 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" id="1" name="Table1" displayName="Table1" ref="A1:F109" totalsRowShown="false">
-  <autoFilter ref="A1:F109"/>
-  <sortState ref="A2:E43">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:F109" totalsRowShown="0">
+  <autoFilter ref="A1:F109" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E43">
     <sortCondition ref="B1:B101"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" name="Parameter"/>
-    <tableColumn id="2" name="Subclass" dataDxfId="2"/>
-    <tableColumn id="3" name="Value" dataDxfId="1"/>
-    <tableColumn id="4" name="Units" dataDxfId="0"/>
-    <tableColumn id="5" name="Description"/>
-    <tableColumn id="6" name="Notes"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Parameter"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Subclass" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Value" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Units" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Description"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Notes"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium15" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
+  <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" id="2" name="Table2" displayName="Table2" ref="A1:F34" totalsRowShown="false">
-  <autoFilter ref="A1:F34"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="A1:F34" totalsRowShown="0">
+  <autoFilter ref="A1:F34" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="Parameter"/>
-    <tableColumn id="2" name="Subclass"/>
-    <tableColumn id="3" name="Value"/>
-    <tableColumn id="4" name="Units"/>
-    <tableColumn id="5" name="Description"/>
-    <tableColumn id="6" name="Source"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Parameter"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Subclass"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Value"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Units"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Description"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Source"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium15" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
+  <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1951,7 +1943,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="true">
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -1975,9 +1967,9 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="false"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="true">
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -2001,7 +1993,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="false"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -2036,7 +2028,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="false">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -2054,7 +2046,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="true">
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -2079,7 +2071,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="false"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -2097,17 +2089,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F109"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.109375" style="20" customWidth="1"/>
-    <col min="3" max="3" width="13.6640625" style="20" customWidth="1"/>
-    <col min="4" max="4" width="16.88671875" style="20" customWidth="1"/>
-    <col min="5" max="5" width="168.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="142.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" style="20" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" style="20" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" style="20" customWidth="1"/>
+    <col min="5" max="5" width="168.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="142.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2127,7 +2119,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -2144,7 +2136,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -2161,7 +2153,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -2178,7 +2170,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -2195,7 +2187,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -2212,7 +2204,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -2229,7 +2221,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -2246,7 +2238,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>205</v>
       </c>
@@ -2260,7 +2252,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -2277,7 +2269,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -2294,7 +2286,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -2311,7 +2303,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -2328,7 +2320,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -2345,7 +2337,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -2362,7 +2354,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>35</v>
       </c>
@@ -2379,7 +2371,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>37</v>
       </c>
@@ -2396,7 +2388,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>39</v>
       </c>
@@ -2413,7 +2405,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>41</v>
       </c>
@@ -2430,7 +2422,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>45</v>
       </c>
@@ -2447,7 +2439,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -2464,7 +2456,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -2481,7 +2473,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -2498,7 +2490,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -2515,7 +2507,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>58</v>
       </c>
@@ -2532,7 +2524,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>61</v>
       </c>
@@ -2549,7 +2541,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>63</v>
       </c>
@@ -2566,7 +2558,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>65</v>
       </c>
@@ -2583,7 +2575,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -2600,7 +2592,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -2617,7 +2609,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>72</v>
       </c>
@@ -2634,7 +2626,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>74</v>
       </c>
@@ -2651,7 +2643,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>76</v>
       </c>
@@ -2668,7 +2660,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>78</v>
       </c>
@@ -2685,7 +2677,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>80</v>
       </c>
@@ -2702,7 +2694,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>82</v>
       </c>
@@ -2719,7 +2711,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>84</v>
       </c>
@@ -2736,7 +2728,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>86</v>
       </c>
@@ -2753,7 +2745,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>88</v>
       </c>
@@ -2770,7 +2762,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>90</v>
       </c>
@@ -2787,7 +2779,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>92</v>
       </c>
@@ -2804,7 +2796,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>94</v>
       </c>
@@ -2821,7 +2813,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>96</v>
       </c>
@@ -2838,7 +2830,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>98</v>
       </c>
@@ -2855,7 +2847,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>100</v>
       </c>
@@ -2872,7 +2864,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>103</v>
       </c>
@@ -2889,7 +2881,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>105</v>
       </c>
@@ -2906,7 +2898,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>107</v>
       </c>
@@ -2923,7 +2915,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>109</v>
       </c>
@@ -2940,7 +2932,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>111</v>
       </c>
@@ -2957,7 +2949,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>113</v>
       </c>
@@ -2974,7 +2966,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>115</v>
       </c>
@@ -2991,7 +2983,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>117</v>
       </c>
@@ -3008,7 +3000,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>119</v>
       </c>
@@ -3025,7 +3017,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>121</v>
       </c>
@@ -3042,7 +3034,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>123</v>
       </c>
@@ -3059,7 +3051,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>125</v>
       </c>
@@ -3076,7 +3068,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>127</v>
       </c>
@@ -3093,7 +3085,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>129</v>
       </c>
@@ -3110,7 +3102,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>131</v>
       </c>
@@ -3127,7 +3119,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>133</v>
       </c>
@@ -3144,7 +3136,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>135</v>
       </c>
@@ -3161,7 +3153,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>139</v>
       </c>
@@ -3178,7 +3170,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>141</v>
       </c>
@@ -3195,7 +3187,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>143</v>
       </c>
@@ -3212,7 +3204,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>145</v>
       </c>
@@ -3229,7 +3221,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>201</v>
       </c>
@@ -3246,7 +3238,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>146</v>
       </c>
@@ -3263,7 +3255,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>148</v>
       </c>
@@ -3280,7 +3272,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>150</v>
       </c>
@@ -3297,7 +3289,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>152</v>
       </c>
@@ -3314,7 +3306,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>154</v>
       </c>
@@ -3331,7 +3323,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>157</v>
       </c>
@@ -3348,7 +3340,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>160</v>
       </c>
@@ -3365,7 +3357,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>162</v>
       </c>
@@ -3382,7 +3374,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>165</v>
       </c>
@@ -3399,7 +3391,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>167</v>
       </c>
@@ -3416,7 +3408,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>169</v>
       </c>
@@ -3433,7 +3425,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>172</v>
       </c>
@@ -3450,7 +3442,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>174</v>
       </c>
@@ -3467,7 +3459,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>176</v>
       </c>
@@ -3484,7 +3476,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>178</v>
       </c>
@@ -3501,7 +3493,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>180</v>
       </c>
@@ -3518,7 +3510,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>183</v>
       </c>
@@ -3535,7 +3527,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>186</v>
       </c>
@@ -3552,7 +3544,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>189</v>
       </c>
@@ -3569,7 +3561,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>191</v>
       </c>
@@ -3586,7 +3578,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>193</v>
       </c>
@@ -3603,7 +3595,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>196</v>
       </c>
@@ -3620,7 +3612,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>198</v>
       </c>
@@ -3637,7 +3629,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>248</v>
       </c>
@@ -3654,7 +3646,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>251</v>
       </c>
@@ -3671,7 +3663,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>253</v>
       </c>
@@ -3688,7 +3680,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>255</v>
       </c>
@@ -3705,7 +3697,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>261</v>
       </c>
@@ -3722,7 +3714,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>263</v>
       </c>
@@ -3739,7 +3731,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>264</v>
       </c>
@@ -3756,7 +3748,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>266</v>
       </c>
@@ -3773,7 +3765,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>267</v>
       </c>
@@ -3790,7 +3782,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>268</v>
       </c>
@@ -3807,7 +3799,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>269</v>
       </c>
@@ -3824,7 +3816,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>270</v>
       </c>
@@ -3832,7 +3824,7 @@
         <v>265</v>
       </c>
       <c r="C102" s="21">
-        <v>0.3</v>
+        <v>0.29499999999999998</v>
       </c>
       <c r="D102" s="20" t="s">
         <v>59</v>
@@ -3841,7 +3833,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>271</v>
       </c>
@@ -3858,7 +3850,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>272</v>
       </c>
@@ -3875,7 +3867,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>305</v>
       </c>
@@ -3892,7 +3884,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>307</v>
       </c>
@@ -3909,7 +3901,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>308</v>
       </c>
@@ -3923,10 +3915,10 @@
         <v>311</v>
       </c>
       <c r="E107" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>309</v>
       </c>
@@ -3940,10 +3932,10 @@
         <v>184</v>
       </c>
       <c r="E108" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>310</v>
       </c>
@@ -3969,3017 +3961,2435 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H160"/>
-  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="true"/>
-    <col min="2" max="2" width="11.5546875" customWidth="true"/>
-    <col min="3" max="3" width="58.5546875" customWidth="true"/>
-    <col min="4" max="4" width="5.21875" customWidth="true"/>
-    <col min="5" max="5" width="42.77734375" customWidth="true"/>
-    <col min="6" max="6" width="29.21875" customWidth="true"/>
-    <col min="7" max="7" width="9.109375"/>
-    <col min="8" max="8" width="40.109375" customWidth="true"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" customWidth="1"/>
+    <col min="3" max="3" width="58.5703125" customWidth="1"/>
+    <col min="4" max="4" width="5.28515625" customWidth="1"/>
+    <col min="5" max="5" width="42.7109375" customWidth="1"/>
+    <col min="6" max="6" width="29.28515625" customWidth="1"/>
+    <col min="8" max="8" width="40.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" t="s">
         <v>376</v>
       </c>
-      <c r="G1" s="0"/>
-      <c r="H1" s="0" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="0" t="s">
+      <c r="H1" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>315</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="0">
-        <v>0.29999999999999999</v>
-      </c>
-      <c r="D2" s="0" t="s">
+      <c r="C2">
+        <v>0.3</v>
+      </c>
+      <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" t="s">
         <v>348</v>
       </c>
-      <c r="F2" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G2" s="0"/>
-      <c r="H2" s="0"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="0" t="s">
+      <c r="F2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>316</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="0">
+      <c r="C3">
         <v>1.1818181818181817</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" t="s">
         <v>349</v>
       </c>
-      <c r="F3" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G3" s="0"/>
-      <c r="H3" s="0"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="0" t="s">
+      <c r="F3" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>317</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="0">
+      <c r="C4">
         <v>0.92201380973471758</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" t="s">
         <v>350</v>
       </c>
-      <c r="F4" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G4" s="0"/>
-      <c r="H4" s="0"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="0" t="s">
+      <c r="F4" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>318</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="0">
-        <v>0.07919652663705147</v>
-      </c>
-      <c r="D5" s="0" t="s">
+      <c r="C5">
+        <v>7.919652663705147E-2</v>
+      </c>
+      <c r="D5" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" t="s">
         <v>351</v>
       </c>
-      <c r="F5" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G5" s="0"/>
-      <c r="H5" s="0"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="0" t="s">
+      <c r="F5" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>319</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="0">
+      <c r="C6">
         <v>0.19588300688233271</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" t="s">
         <v>352</v>
       </c>
-      <c r="F6" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G6" s="0"/>
-      <c r="H6" s="0"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="0" t="s">
+      <c r="F6" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>320</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="0">
-        <v>0.029817638776781716</v>
-      </c>
-      <c r="D7" s="0"/>
-      <c r="E7" s="0"/>
-      <c r="F7" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G7" s="0"/>
-      <c r="H7" s="0"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="0" t="s">
+      <c r="C7">
+        <v>2.9817638776781716E-2</v>
+      </c>
+      <c r="F7" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>321</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="0">
-        <v>0.036945326174116347</v>
-      </c>
-      <c r="D8" s="0" t="s">
+      <c r="C8">
+        <v>3.6945326174116347E-2</v>
+      </c>
+      <c r="D8" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="E8" t="s">
         <v>353</v>
       </c>
-      <c r="F8" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G8" s="0"/>
-      <c r="H8" s="0"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="0" t="s">
+      <c r="F8" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>322</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="0">
-        <v>0.036945326174116347</v>
-      </c>
-      <c r="D9" s="0" t="s">
+      <c r="C9">
+        <v>3.6945326174116347E-2</v>
+      </c>
+      <c r="D9" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="0" t="s">
+      <c r="E9" t="s">
         <v>354</v>
       </c>
-      <c r="F9" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G9" s="0"/>
-      <c r="H9" s="0"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="0" t="s">
+      <c r="F9" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>323</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="0">
-        <v>0.021945326174116348</v>
-      </c>
-      <c r="D10" s="0" t="s">
+      <c r="C10">
+        <v>2.1945326174116347E-2</v>
+      </c>
+      <c r="D10" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="0" t="s">
+      <c r="E10" t="s">
         <v>355</v>
       </c>
-      <c r="F10" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G10" s="0"/>
-      <c r="H10" s="0"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="0" t="s">
+      <c r="F10" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>324</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="0">
-        <v>8.1201069544265661</v>
-      </c>
-      <c r="D11" s="0" t="s">
+      <c r="C11">
+        <v>8.120106954426566</v>
+      </c>
+      <c r="D11" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="0" t="s">
+      <c r="E11" t="s">
         <v>356</v>
       </c>
-      <c r="F11" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G11" s="0"/>
-      <c r="H11" s="0"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="0" t="s">
+      <c r="F11" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>325</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="0">
+      <c r="C12">
         <v>10.289169276665902</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="0" t="s">
+      <c r="E12" t="s">
         <v>357</v>
       </c>
-      <c r="F12" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G12" s="0"/>
-      <c r="H12" s="0"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="0" t="s">
+      <c r="F12" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>380</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="0">
+      <c r="C13">
         <v>3.0198549799930445</v>
       </c>
-      <c r="D13" s="0"/>
-      <c r="E13" s="0"/>
-      <c r="F13" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G13" s="0"/>
-      <c r="H13" s="0"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="0" t="s">
+      <c r="F13" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>381</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="0">
+      <c r="C14">
         <v>4.0327458299223453</v>
       </c>
-      <c r="D14" s="0"/>
-      <c r="E14" s="0"/>
-      <c r="F14" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G14" s="0"/>
-      <c r="H14" s="0"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="0" t="s">
+      <c r="F14" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>382</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="0">
+      <c r="C15">
         <v>0.58894455001488533</v>
       </c>
-      <c r="D15" s="0"/>
-      <c r="E15" s="0"/>
-      <c r="F15" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G15" s="0"/>
-      <c r="H15" s="0"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="0" t="s">
+      <c r="F15" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>383</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="0">
+      <c r="C16">
         <v>5.2740736776131758</v>
       </c>
-      <c r="D16" s="0"/>
-      <c r="E16" s="0"/>
-      <c r="F16" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G16" s="0"/>
-      <c r="H16" s="0"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="0" t="s">
+      <c r="F16" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>384</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="0">
-        <v>-0.094788465253600393</v>
-      </c>
-      <c r="D17" s="0"/>
-      <c r="E17" s="0"/>
-      <c r="F17" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G17" s="0"/>
-      <c r="H17" s="0"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="0" t="s">
+      <c r="C17">
+        <v>-9.4788465253600393E-2</v>
+      </c>
+      <c r="F17" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>385</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="0">
+      <c r="C18">
         <v>0.66074594914354523</v>
       </c>
-      <c r="D18" s="0"/>
-      <c r="E18" s="0"/>
-      <c r="F18" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G18" s="0"/>
-      <c r="H18" s="0"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="0" t="s">
+      <c r="F18" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>386</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="0">
+      <c r="C19">
         <v>0.60899778104422941</v>
       </c>
-      <c r="D19" s="0"/>
-      <c r="E19" s="0"/>
-      <c r="F19" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G19" s="0"/>
-      <c r="H19" s="0"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="0" t="s">
+      <c r="F19" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>387</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="0">
+      <c r="C20">
         <v>1.5753270213496304</v>
       </c>
-      <c r="D20" s="0"/>
-      <c r="E20" s="0"/>
-      <c r="F20" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G20" s="0"/>
-      <c r="H20" s="0"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="0" t="s">
+      <c r="F20" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>388</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="0">
+      <c r="C21">
         <v>0.66074594914354523</v>
       </c>
-      <c r="D21" s="0"/>
-      <c r="E21" s="0"/>
-      <c r="F21" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G21" s="0"/>
-      <c r="H21" s="0"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="0" t="s">
+      <c r="F21" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>389</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="0">
+      <c r="C22">
         <v>0.12602616170797043</v>
       </c>
-      <c r="D22" s="0"/>
-      <c r="E22" s="0"/>
-      <c r="F22" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G22" s="0"/>
-      <c r="H22" s="0"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="0" t="s">
+      <c r="F22" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>520</v>
+      </c>
+      <c r="B23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23">
+        <v>0.8871601270722228</v>
+      </c>
+      <c r="F23" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>326</v>
+      </c>
+      <c r="B24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24">
+        <v>0.49722452282391244</v>
+      </c>
+      <c r="D24" t="s">
+        <v>66</v>
+      </c>
+      <c r="E24" t="s">
+        <v>358</v>
+      </c>
+      <c r="F24" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>327</v>
+      </c>
+      <c r="B25" t="s">
+        <v>56</v>
+      </c>
+      <c r="C25">
+        <v>0.34410001579509508</v>
+      </c>
+      <c r="D25" t="s">
+        <v>59</v>
+      </c>
+      <c r="E25" t="s">
+        <v>359</v>
+      </c>
+      <c r="F25" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>328</v>
+      </c>
+      <c r="B26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26">
+        <v>4.3591977074863637</v>
+      </c>
+      <c r="D26" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" t="s">
+        <v>360</v>
+      </c>
+      <c r="F26" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>329</v>
+      </c>
+      <c r="B27" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27">
+        <v>8.4528168880065119E-2</v>
+      </c>
+      <c r="D27" t="s">
+        <v>66</v>
+      </c>
+      <c r="E27" t="s">
+        <v>361</v>
+      </c>
+      <c r="F27" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>330</v>
+      </c>
+      <c r="B28" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28">
+        <v>0.45969601064199239</v>
+      </c>
+      <c r="D28" t="s">
+        <v>59</v>
+      </c>
+      <c r="E28" t="s">
+        <v>362</v>
+      </c>
+      <c r="F28" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>331</v>
+      </c>
+      <c r="B29" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29">
+        <v>0.18387840425679697</v>
+      </c>
+      <c r="D29" t="s">
+        <v>59</v>
+      </c>
+      <c r="E29" t="s">
+        <v>363</v>
+      </c>
+      <c r="F29" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>332</v>
+      </c>
+      <c r="B30" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30">
+        <v>0.39523392547876368</v>
+      </c>
+      <c r="D30" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" t="s">
+        <v>364</v>
+      </c>
+      <c r="F30" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>333</v>
+      </c>
+      <c r="B31" t="s">
+        <v>56</v>
+      </c>
+      <c r="C31">
+        <v>7.4583678423586861E-2</v>
+      </c>
+      <c r="D31" t="s">
+        <v>66</v>
+      </c>
+      <c r="E31" t="s">
+        <v>365</v>
+      </c>
+      <c r="F31" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>334</v>
+      </c>
+      <c r="B32" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32">
+        <v>7.4583678423586861E-2</v>
+      </c>
+      <c r="D32" t="s">
+        <v>66</v>
+      </c>
+      <c r="E32" t="s">
+        <v>366</v>
+      </c>
+      <c r="F32" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>335</v>
+      </c>
+      <c r="B33" t="s">
+        <v>56</v>
+      </c>
+      <c r="C33">
+        <v>0.28249696620183012</v>
+      </c>
+      <c r="D33" t="s">
+        <v>59</v>
+      </c>
+      <c r="E33" t="s">
+        <v>367</v>
+      </c>
+      <c r="F33" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>336</v>
+      </c>
+      <c r="B34" t="s">
+        <v>56</v>
+      </c>
+      <c r="C34">
+        <v>0.26401585626339263</v>
+      </c>
+      <c r="D34" t="s">
+        <v>59</v>
+      </c>
+      <c r="E34" t="s">
+        <v>368</v>
+      </c>
+      <c r="F34" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>390</v>
+      </c>
+      <c r="B35" t="s">
+        <v>56</v>
+      </c>
+      <c r="C35">
+        <v>1.8046437163813135E-2</v>
+      </c>
+      <c r="F35" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>391</v>
+      </c>
+      <c r="B36" t="s">
+        <v>56</v>
+      </c>
+      <c r="C36">
+        <v>0.23885083680507355</v>
+      </c>
+      <c r="F36" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>392</v>
+      </c>
+      <c r="B37" t="s">
+        <v>56</v>
+      </c>
+      <c r="C37">
+        <v>0.3656082203404642</v>
+      </c>
+      <c r="F37" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>393</v>
+      </c>
+      <c r="B38" t="s">
+        <v>56</v>
+      </c>
+      <c r="C38">
+        <v>0.2156082203404642</v>
+      </c>
+      <c r="F38" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>167</v>
+      </c>
+      <c r="B39" t="s">
+        <v>136</v>
+      </c>
+      <c r="C39">
+        <v>4.0516000000000005</v>
+      </c>
+      <c r="F39" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>337</v>
+      </c>
+      <c r="B40" t="s">
+        <v>136</v>
+      </c>
+      <c r="C40">
+        <v>22.737783592977756</v>
+      </c>
+      <c r="D40" t="s">
+        <v>137</v>
+      </c>
+      <c r="E40" t="s">
+        <v>369</v>
+      </c>
+      <c r="F40" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>338</v>
+      </c>
+      <c r="B41" t="s">
+        <v>136</v>
+      </c>
+      <c r="C41">
+        <v>11</v>
+      </c>
+      <c r="D41" t="s">
+        <v>137</v>
+      </c>
+      <c r="E41" t="s">
+        <v>370</v>
+      </c>
+      <c r="F41" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>339</v>
+      </c>
+      <c r="B42" t="s">
+        <v>136</v>
+      </c>
+      <c r="C42">
+        <v>14.810748414335091</v>
+      </c>
+      <c r="D42" t="s">
+        <v>137</v>
+      </c>
+      <c r="E42" t="s">
+        <v>371</v>
+      </c>
+      <c r="F42" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>340</v>
+      </c>
+      <c r="B43" t="s">
+        <v>136</v>
+      </c>
+      <c r="C43">
+        <v>12.24744871391589</v>
+      </c>
+      <c r="D43" t="s">
+        <v>137</v>
+      </c>
+      <c r="E43" t="s">
+        <v>372</v>
+      </c>
+      <c r="F43" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>341</v>
+      </c>
+      <c r="B44" t="s">
+        <v>136</v>
+      </c>
+      <c r="C44">
+        <v>48.189685104221404</v>
+      </c>
+      <c r="D44" t="s">
+        <v>23</v>
+      </c>
+      <c r="E44" t="s">
+        <v>373</v>
+      </c>
+      <c r="F44" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>342</v>
+      </c>
+      <c r="B45" t="s">
+        <v>136</v>
+      </c>
+      <c r="C45">
+        <v>16.699244233993625</v>
+      </c>
+      <c r="D45" t="s">
+        <v>23</v>
+      </c>
+      <c r="E45" t="s">
+        <v>374</v>
+      </c>
+      <c r="F45" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>343</v>
+      </c>
+      <c r="B46" t="s">
+        <v>136</v>
+      </c>
+      <c r="C46">
+        <v>39.746196000000005</v>
+      </c>
+      <c r="D46" t="s">
+        <v>347</v>
+      </c>
+      <c r="E46" t="s">
+        <v>375</v>
+      </c>
+      <c r="F46" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>344</v>
+      </c>
+      <c r="B47" t="s">
+        <v>136</v>
+      </c>
+      <c r="C47">
+        <v>0.44283295832701008</v>
+      </c>
+      <c r="F47" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>345</v>
+      </c>
+      <c r="B48" t="s">
+        <v>136</v>
+      </c>
+      <c r="C48">
+        <v>233372.96903833433</v>
+      </c>
+      <c r="F48" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>346</v>
+      </c>
+      <c r="B49" t="s">
+        <v>136</v>
+      </c>
+      <c r="C49">
+        <v>130688.86266146721</v>
+      </c>
+      <c r="F49" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>394</v>
+      </c>
+      <c r="B50" t="s">
+        <v>136</v>
+      </c>
+      <c r="C50">
+        <v>34.194077618408031</v>
+      </c>
+      <c r="F50" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>395</v>
+      </c>
+      <c r="B51" t="s">
+        <v>136</v>
+      </c>
+      <c r="C51">
+        <v>15.480365443172449</v>
+      </c>
+      <c r="F51" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>396</v>
+      </c>
+      <c r="B52" t="s">
+        <v>136</v>
+      </c>
+      <c r="C52">
+        <v>3.8</v>
+      </c>
+      <c r="F52" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>397</v>
+      </c>
+      <c r="B53" t="s">
+        <v>136</v>
+      </c>
+      <c r="C53">
+        <v>-1.52</v>
+      </c>
+      <c r="F53" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>398</v>
+      </c>
+      <c r="B54" t="s">
+        <v>136</v>
+      </c>
+      <c r="C54">
+        <v>5.6999999999999993</v>
+      </c>
+      <c r="F54" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>399</v>
+      </c>
+      <c r="B55" t="s">
+        <v>136</v>
+      </c>
+      <c r="C55">
+        <v>-2.2800000000000002</v>
+      </c>
+      <c r="F55" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>400</v>
+      </c>
+      <c r="B56" t="s">
+        <v>136</v>
+      </c>
+      <c r="C56">
+        <v>18.622682892532463</v>
+      </c>
+      <c r="F56" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>401</v>
+      </c>
+      <c r="B57" t="s">
+        <v>136</v>
+      </c>
+      <c r="C57">
+        <v>27.131986877647702</v>
+      </c>
+      <c r="F57" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>402</v>
+      </c>
+      <c r="B58" t="s">
+        <v>136</v>
+      </c>
+      <c r="C58">
+        <v>25.580006542099976</v>
+      </c>
+      <c r="F58" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>403</v>
+      </c>
+      <c r="B59" t="s">
+        <v>136</v>
+      </c>
+      <c r="C59">
+        <v>28.422229491222197</v>
+      </c>
+      <c r="F59" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>404</v>
+      </c>
+      <c r="B60" t="s">
+        <v>136</v>
+      </c>
+      <c r="C60">
+        <v>6.3586494759793881</v>
+      </c>
+      <c r="F60" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>405</v>
+      </c>
+      <c r="B61" t="s">
+        <v>136</v>
+      </c>
+      <c r="C61">
+        <v>11.113261724726186</v>
+      </c>
+      <c r="F61" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>406</v>
+      </c>
+      <c r="B62" t="s">
+        <v>136</v>
+      </c>
+      <c r="C62">
+        <v>1.9300000000000015</v>
+      </c>
+      <c r="F62" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>407</v>
+      </c>
+      <c r="B63" t="s">
+        <v>136</v>
+      </c>
+      <c r="C63">
+        <v>11.008581406383897</v>
+      </c>
+      <c r="F63" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>408</v>
+      </c>
+      <c r="B64" t="s">
+        <v>136</v>
+      </c>
+      <c r="C64" t="b">
+        <v>1</v>
+      </c>
+      <c r="F64" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>409</v>
+      </c>
+      <c r="B65" t="s">
+        <v>136</v>
+      </c>
+      <c r="C65">
+        <v>7.4507370536077033</v>
+      </c>
+      <c r="F65" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>410</v>
+      </c>
+      <c r="B66" t="s">
+        <v>136</v>
+      </c>
+      <c r="C66">
+        <v>20.550728554427437</v>
+      </c>
+      <c r="F66" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>411</v>
+      </c>
+      <c r="B67" t="s">
+        <v>136</v>
+      </c>
+      <c r="C67">
+        <v>4.0264472875839541</v>
+      </c>
+      <c r="F67" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
         <v>521</v>
       </c>
-      <c r="B23" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="0">
-        <v>0.8871601270722228</v>
-      </c>
-      <c r="D23" s="0"/>
-      <c r="E23" s="0"/>
-      <c r="F23" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G23" s="0"/>
-      <c r="H23" s="0"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="0" t="s">
-        <v>326</v>
-      </c>
-      <c r="B24" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C24" s="0">
-        <v>0.49722452282391244</v>
-      </c>
-      <c r="D24" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="E24" s="0" t="s">
-        <v>358</v>
-      </c>
-      <c r="F24" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G24" s="0"/>
-      <c r="H24" s="0"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="0" t="s">
-        <v>327</v>
-      </c>
-      <c r="B25" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C25" s="0">
-        <v>0.34410001579509508</v>
-      </c>
-      <c r="D25" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="E25" s="0" t="s">
-        <v>359</v>
-      </c>
-      <c r="F25" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G25" s="0"/>
-      <c r="H25" s="0"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="0" t="s">
-        <v>328</v>
-      </c>
-      <c r="B26" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C26" s="0">
-        <v>4.3591977074863637</v>
-      </c>
-      <c r="D26" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E26" s="0" t="s">
-        <v>360</v>
-      </c>
-      <c r="F26" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G26" s="0"/>
-      <c r="H26" s="0"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="0" t="s">
-        <v>329</v>
-      </c>
-      <c r="B27" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C27" s="0">
-        <v>0.084528168880065119</v>
-      </c>
-      <c r="D27" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="E27" s="0" t="s">
-        <v>361</v>
-      </c>
-      <c r="F27" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G27" s="0"/>
-      <c r="H27" s="0"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="0" t="s">
-        <v>330</v>
-      </c>
-      <c r="B28" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C28" s="0">
-        <v>0.45969601064199239</v>
-      </c>
-      <c r="D28" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="E28" s="0" t="s">
-        <v>362</v>
-      </c>
-      <c r="F28" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G28" s="0"/>
-      <c r="H28" s="0"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="0" t="s">
-        <v>331</v>
-      </c>
-      <c r="B29" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C29" s="0">
-        <v>0.18387840425679697</v>
-      </c>
-      <c r="D29" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="E29" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="F29" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G29" s="0"/>
-      <c r="H29" s="0"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="0" t="s">
-        <v>332</v>
-      </c>
-      <c r="B30" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C30" s="0">
-        <v>0.39523392547876368</v>
-      </c>
-      <c r="D30" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E30" s="0" t="s">
-        <v>364</v>
-      </c>
-      <c r="F30" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G30" s="0"/>
-      <c r="H30" s="0"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="0" t="s">
-        <v>333</v>
-      </c>
-      <c r="B31" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C31" s="0">
-        <v>0.074583678423586861</v>
-      </c>
-      <c r="D31" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="E31" s="0" t="s">
-        <v>365</v>
-      </c>
-      <c r="F31" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G31" s="0"/>
-      <c r="H31" s="0"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="0" t="s">
-        <v>334</v>
-      </c>
-      <c r="B32" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C32" s="0">
-        <v>0.074583678423586861</v>
-      </c>
-      <c r="D32" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="E32" s="0" t="s">
-        <v>366</v>
-      </c>
-      <c r="F32" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G32" s="0"/>
-      <c r="H32" s="0"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="0" t="s">
-        <v>335</v>
-      </c>
-      <c r="B33" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C33" s="0">
-        <v>0.28249696620183012</v>
-      </c>
-      <c r="D33" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="E33" s="0" t="s">
-        <v>367</v>
-      </c>
-      <c r="F33" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G33" s="0"/>
-      <c r="H33" s="0"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="0" t="s">
-        <v>336</v>
-      </c>
-      <c r="B34" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C34" s="0">
-        <v>0.26401585626339264</v>
-      </c>
-      <c r="D34" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="E34" s="0" t="s">
-        <v>368</v>
-      </c>
-      <c r="F34" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G34" s="0"/>
-      <c r="H34" s="0"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="0" t="s">
-        <v>390</v>
-      </c>
-      <c r="B35" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C35" s="0">
-        <v>0.018046437163813135</v>
-      </c>
-      <c r="D35" s="0"/>
-      <c r="E35" s="0"/>
-      <c r="F35" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G35" s="0"/>
-      <c r="H35" s="0"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="0" t="s">
-        <v>391</v>
-      </c>
-      <c r="B36" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C36" s="0">
-        <v>0.23885083680507355</v>
-      </c>
-      <c r="D36" s="0"/>
-      <c r="E36" s="0"/>
-      <c r="F36" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G36" s="0"/>
-      <c r="H36" s="0"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="0" t="s">
-        <v>392</v>
-      </c>
-      <c r="B37" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C37" s="0">
+      <c r="B68" t="s">
+        <v>136</v>
+      </c>
+      <c r="C68">
+        <v>77.116605805538327</v>
+      </c>
+      <c r="F68" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>412</v>
+      </c>
+      <c r="B69" t="s">
+        <v>136</v>
+      </c>
+      <c r="C69">
+        <v>22.608098531363336</v>
+      </c>
+      <c r="F69" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>413</v>
+      </c>
+      <c r="B70" t="s">
+        <v>136</v>
+      </c>
+      <c r="C70">
+        <v>12.709922788411269</v>
+      </c>
+      <c r="F70" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>414</v>
+      </c>
+      <c r="B71" t="s">
+        <v>136</v>
+      </c>
+      <c r="C71">
+        <v>16.27392540932771</v>
+      </c>
+      <c r="F71" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>415</v>
+      </c>
+      <c r="B72" t="s">
+        <v>136</v>
+      </c>
+      <c r="C72">
+        <v>15.956485750905872</v>
+      </c>
+      <c r="F72" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>416</v>
+      </c>
+      <c r="B73" t="s">
+        <v>136</v>
+      </c>
+      <c r="C73">
+        <v>13.695854805920606</v>
+      </c>
+      <c r="F73" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>417</v>
+      </c>
+      <c r="B74" t="s">
+        <v>136</v>
+      </c>
+      <c r="C74">
+        <v>1.0954451150103324</v>
+      </c>
+      <c r="F74" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>418</v>
+      </c>
+      <c r="B75" t="s">
+        <v>136</v>
+      </c>
+      <c r="C75">
+        <v>24.094842552110709</v>
+      </c>
+      <c r="F75" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>419</v>
+      </c>
+      <c r="B76" t="s">
+        <v>136</v>
+      </c>
+      <c r="C76" t="b">
+        <v>1</v>
+      </c>
+      <c r="F76" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>420</v>
+      </c>
+      <c r="B77" t="s">
+        <v>136</v>
+      </c>
+      <c r="C77">
+        <v>150.69320484179264</v>
+      </c>
+      <c r="F77" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>421</v>
+      </c>
+      <c r="B78" t="s">
+        <v>136</v>
+      </c>
+      <c r="C78">
+        <v>46195.337793815328</v>
+      </c>
+      <c r="F78" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>422</v>
+      </c>
+      <c r="B79" t="s">
+        <v>136</v>
+      </c>
+      <c r="C79" t="b">
+        <v>1</v>
+      </c>
+      <c r="F79" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>423</v>
+      </c>
+      <c r="B80" t="s">
+        <v>136</v>
+      </c>
+      <c r="C80" t="b">
+        <v>1</v>
+      </c>
+      <c r="F80" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>522</v>
+      </c>
+      <c r="B81" t="s">
+        <v>136</v>
+      </c>
+      <c r="C81">
+        <v>890</v>
+      </c>
+      <c r="F81" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>424</v>
+      </c>
+      <c r="B82" t="s">
+        <v>136</v>
+      </c>
+      <c r="C82">
+        <v>13</v>
+      </c>
+      <c r="F82" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>425</v>
+      </c>
+      <c r="B83" t="s">
+        <v>136</v>
+      </c>
+      <c r="C83">
+        <v>84493.524867651882</v>
+      </c>
+      <c r="F83" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>426</v>
+      </c>
+      <c r="B84" t="s">
+        <v>136</v>
+      </c>
+      <c r="C84">
+        <v>0.16032926919858043</v>
+      </c>
+      <c r="F84" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>427</v>
+      </c>
+      <c r="B85" t="s">
+        <v>136</v>
+      </c>
+      <c r="C85">
+        <v>2.4683999999999995</v>
+      </c>
+      <c r="F85" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>428</v>
+      </c>
+      <c r="B86" t="s">
+        <v>170</v>
+      </c>
+      <c r="C86" t="s">
+        <v>504</v>
+      </c>
+      <c r="F86" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>429</v>
+      </c>
+      <c r="B87" t="s">
+        <v>170</v>
+      </c>
+      <c r="C87">
+        <v>-4.0973254512723323E-2</v>
+      </c>
+      <c r="F87" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>430</v>
+      </c>
+      <c r="B88" t="s">
+        <v>170</v>
+      </c>
+      <c r="C88" t="b">
+        <v>0</v>
+      </c>
+      <c r="F88" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>431</v>
+      </c>
+      <c r="B89" t="s">
+        <v>170</v>
+      </c>
+      <c r="C89">
+        <v>0.254</v>
+      </c>
+      <c r="F89" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>432</v>
+      </c>
+      <c r="B90" t="s">
+        <v>170</v>
+      </c>
+      <c r="C90">
+        <v>0.127</v>
+      </c>
+      <c r="F90" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>433</v>
+      </c>
+      <c r="B91" t="s">
+        <v>170</v>
+      </c>
+      <c r="C91">
+        <v>14500</v>
+      </c>
+      <c r="F91" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>434</v>
+      </c>
+      <c r="B92" t="s">
+        <v>170</v>
+      </c>
+      <c r="C92" t="s">
+        <v>505</v>
+      </c>
+      <c r="F92" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>435</v>
+      </c>
+      <c r="B93" t="s">
+        <v>170</v>
+      </c>
+      <c r="C93" t="s">
+        <v>506</v>
+      </c>
+      <c r="F93" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>436</v>
+      </c>
+      <c r="B94" t="s">
+        <v>170</v>
+      </c>
+      <c r="C94" t="s">
+        <v>507</v>
+      </c>
+      <c r="F94" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>437</v>
+      </c>
+      <c r="B95" t="s">
+        <v>170</v>
+      </c>
+      <c r="C95" t="s">
+        <v>507</v>
+      </c>
+      <c r="F95" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>438</v>
+      </c>
+      <c r="B96" t="s">
+        <v>170</v>
+      </c>
+      <c r="C96" t="s">
+        <v>507</v>
+      </c>
+      <c r="F96" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>439</v>
+      </c>
+      <c r="B97" t="s">
+        <v>170</v>
+      </c>
+      <c r="C97" t="s">
+        <v>507</v>
+      </c>
+      <c r="F97" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>440</v>
+      </c>
+      <c r="B98" t="s">
+        <v>170</v>
+      </c>
+      <c r="C98" t="s">
+        <v>507</v>
+      </c>
+      <c r="F98" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>441</v>
+      </c>
+      <c r="B99" t="s">
+        <v>170</v>
+      </c>
+      <c r="C99" t="s">
+        <v>507</v>
+      </c>
+      <c r="F99" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>442</v>
+      </c>
+      <c r="B100" t="s">
+        <v>170</v>
+      </c>
+      <c r="C100" t="s">
+        <v>507</v>
+      </c>
+      <c r="F100" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>443</v>
+      </c>
+      <c r="B101" t="s">
+        <v>170</v>
+      </c>
+      <c r="C101" t="s">
+        <v>507</v>
+      </c>
+      <c r="F101" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>444</v>
+      </c>
+      <c r="B102" t="s">
+        <v>170</v>
+      </c>
+      <c r="C102" t="s">
+        <v>508</v>
+      </c>
+      <c r="F102" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>445</v>
+      </c>
+      <c r="B103" t="s">
+        <v>170</v>
+      </c>
+      <c r="C103">
+        <v>890</v>
+      </c>
+      <c r="F103" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>446</v>
+      </c>
+      <c r="B104" t="s">
+        <v>170</v>
+      </c>
+      <c r="C104">
+        <v>60</v>
+      </c>
+      <c r="F104" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>447</v>
+      </c>
+      <c r="B105" t="s">
+        <v>170</v>
+      </c>
+      <c r="C105" t="s">
+        <v>509</v>
+      </c>
+      <c r="F105" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>448</v>
+      </c>
+      <c r="B106" t="s">
+        <v>170</v>
+      </c>
+      <c r="C106" t="s">
+        <v>507</v>
+      </c>
+      <c r="F106" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>449</v>
+      </c>
+      <c r="B107" t="s">
+        <v>170</v>
+      </c>
+      <c r="C107" t="s">
+        <v>510</v>
+      </c>
+      <c r="F107" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>450</v>
+      </c>
+      <c r="B108" t="s">
+        <v>170</v>
+      </c>
+      <c r="C108" t="s">
+        <v>511</v>
+      </c>
+      <c r="F108" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>451</v>
+      </c>
+      <c r="B109" t="s">
+        <v>170</v>
+      </c>
+      <c r="C109" t="s">
+        <v>512</v>
+      </c>
+      <c r="F109" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>452</v>
+      </c>
+      <c r="B110" t="s">
+        <v>170</v>
+      </c>
+      <c r="C110" t="s">
+        <v>513</v>
+      </c>
+      <c r="F110" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>453</v>
+      </c>
+      <c r="B111" t="s">
+        <v>170</v>
+      </c>
+      <c r="C111" t="s">
+        <v>514</v>
+      </c>
+      <c r="F111" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>454</v>
+      </c>
+      <c r="B112" t="s">
+        <v>170</v>
+      </c>
+      <c r="C112" t="s">
+        <v>515</v>
+      </c>
+      <c r="F112" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>455</v>
+      </c>
+      <c r="B113" t="s">
+        <v>170</v>
+      </c>
+      <c r="C113" t="s">
+        <v>516</v>
+      </c>
+      <c r="F113" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>456</v>
+      </c>
+      <c r="B114" t="s">
+        <v>265</v>
+      </c>
+      <c r="C114">
+        <v>32.946133306980855</v>
+      </c>
+      <c r="F114" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>457</v>
+      </c>
+      <c r="B115" t="s">
+        <v>265</v>
+      </c>
+      <c r="C115">
+        <v>0</v>
+      </c>
+      <c r="F115" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>458</v>
+      </c>
+      <c r="B116" t="s">
+        <v>265</v>
+      </c>
+      <c r="C116" t="s">
+        <v>517</v>
+      </c>
+      <c r="F116" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>459</v>
+      </c>
+      <c r="B117" t="s">
+        <v>265</v>
+      </c>
+      <c r="C117">
+        <v>86.068285472894019</v>
+      </c>
+      <c r="F117" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>460</v>
+      </c>
+      <c r="B118" t="s">
+        <v>265</v>
+      </c>
+      <c r="C118">
+        <v>0</v>
+      </c>
+      <c r="F118" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>461</v>
+      </c>
+      <c r="B119" t="s">
+        <v>265</v>
+      </c>
+      <c r="C119">
+        <v>-1.8275795392708134</v>
+      </c>
+      <c r="F119" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>462</v>
+      </c>
+      <c r="B120" t="s">
+        <v>265</v>
+      </c>
+      <c r="C120">
+        <v>0</v>
+      </c>
+      <c r="F120" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>463</v>
+      </c>
+      <c r="B121" t="s">
+        <v>265</v>
+      </c>
+      <c r="C121">
+        <v>1.7526473681977495</v>
+      </c>
+      <c r="F121" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>464</v>
+      </c>
+      <c r="B122" t="s">
+        <v>265</v>
+      </c>
+      <c r="C122">
+        <v>0.15168253041257554</v>
+      </c>
+      <c r="F122" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>465</v>
+      </c>
+      <c r="B123" t="s">
+        <v>265</v>
+      </c>
+      <c r="C123">
+        <v>2.4110213483593652</v>
+      </c>
+      <c r="F123" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>466</v>
+      </c>
+      <c r="B124" t="s">
+        <v>265</v>
+      </c>
+      <c r="C124">
+        <v>2.7131092758196531</v>
+      </c>
+      <c r="F124" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>467</v>
+      </c>
+      <c r="B125" t="s">
+        <v>265</v>
+      </c>
+      <c r="C125">
+        <v>16.090147165877724</v>
+      </c>
+      <c r="F125" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>468</v>
+      </c>
+      <c r="B126" t="s">
+        <v>265</v>
+      </c>
+      <c r="C126">
+        <v>16.925292122478595</v>
+      </c>
+      <c r="F126" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>469</v>
+      </c>
+      <c r="B127" t="s">
+        <v>265</v>
+      </c>
+      <c r="C127">
+        <v>0.35178486510320511</v>
+      </c>
+      <c r="F127" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>470</v>
+      </c>
+      <c r="B128" t="s">
+        <v>265</v>
+      </c>
+      <c r="C128" t="s">
+        <v>518</v>
+      </c>
+      <c r="F128" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>471</v>
+      </c>
+      <c r="B129" t="s">
+        <v>265</v>
+      </c>
+      <c r="C129">
+        <v>233.69773788009346</v>
+      </c>
+      <c r="F129" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>472</v>
+      </c>
+      <c r="B130" t="s">
+        <v>265</v>
+      </c>
+      <c r="C130">
+        <v>0.35242563899228196</v>
+      </c>
+      <c r="F130" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>473</v>
+      </c>
+      <c r="B131" t="s">
+        <v>265</v>
+      </c>
+      <c r="C131" t="s">
+        <v>518</v>
+      </c>
+      <c r="F131" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>474</v>
+      </c>
+      <c r="B132" t="s">
+        <v>265</v>
+      </c>
+      <c r="C132">
+        <v>9.4744003772526408</v>
+      </c>
+      <c r="F132" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>475</v>
+      </c>
+      <c r="B133" t="s">
+        <v>265</v>
+      </c>
+      <c r="C133">
+        <v>341.83792795003058</v>
+      </c>
+      <c r="F133" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>476</v>
+      </c>
+      <c r="B134" t="s">
+        <v>265</v>
+      </c>
+      <c r="C134">
+        <v>34.733446426726843</v>
+      </c>
+      <c r="F134" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>477</v>
+      </c>
+      <c r="B135" t="s">
+        <v>265</v>
+      </c>
+      <c r="C135">
+        <v>0.42099254615460552</v>
+      </c>
+      <c r="F135" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>478</v>
+      </c>
+      <c r="B136" t="s">
+        <v>265</v>
+      </c>
+      <c r="C136">
+        <v>4.0516000000000005</v>
+      </c>
+      <c r="F136" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>479</v>
+      </c>
+      <c r="B137" t="s">
+        <v>265</v>
+      </c>
+      <c r="C137">
+        <v>39.746196000000005</v>
+      </c>
+      <c r="F137" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>480</v>
+      </c>
+      <c r="B138" t="s">
+        <v>265</v>
+      </c>
+      <c r="C138">
+        <v>18.230437113682747</v>
+      </c>
+      <c r="F138" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>481</v>
+      </c>
+      <c r="B139" t="s">
+        <v>265</v>
+      </c>
+      <c r="C139">
+        <v>8.0999999999999989E-2</v>
+      </c>
+      <c r="F139" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>482</v>
+      </c>
+      <c r="B140" t="s">
+        <v>265</v>
+      </c>
+      <c r="C140">
+        <v>64.749890848167752</v>
+      </c>
+      <c r="F140" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>483</v>
+      </c>
+      <c r="B141" t="s">
+        <v>503</v>
+      </c>
+      <c r="C141">
+        <v>0.3</v>
+      </c>
+      <c r="F141" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>484</v>
+      </c>
+      <c r="B142" t="s">
+        <v>503</v>
+      </c>
+      <c r="C142">
+        <v>26.360381758366742</v>
+      </c>
+      <c r="F142" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>485</v>
+      </c>
+      <c r="B143" t="s">
+        <v>503</v>
+      </c>
+      <c r="C143">
+        <v>3.6396182416332579</v>
+      </c>
+      <c r="F143" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>486</v>
+      </c>
+      <c r="B144" t="s">
+        <v>503</v>
+      </c>
+      <c r="C144">
+        <v>0.25</v>
+      </c>
+      <c r="F144" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>487</v>
+      </c>
+      <c r="B145" t="s">
+        <v>503</v>
+      </c>
+      <c r="C145">
+        <v>0.7</v>
+      </c>
+      <c r="F145" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>488</v>
+      </c>
+      <c r="B146" t="s">
+        <v>503</v>
+      </c>
+      <c r="C146">
+        <v>1</v>
+      </c>
+      <c r="F146" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>489</v>
+      </c>
+      <c r="B147" t="s">
+        <v>503</v>
+      </c>
+      <c r="C147">
+        <v>0.12048857500544551</v>
+      </c>
+      <c r="F147" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>490</v>
+      </c>
+      <c r="B148" t="s">
+        <v>503</v>
+      </c>
+      <c r="C148">
+        <v>119.66043834086311</v>
+      </c>
+      <c r="F148" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>491</v>
+      </c>
+      <c r="B149" t="s">
+        <v>503</v>
+      </c>
+      <c r="C149">
+        <v>7.4583678423586861E-2</v>
+      </c>
+      <c r="F149" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>492</v>
+      </c>
+      <c r="B150" t="s">
+        <v>503</v>
+      </c>
+      <c r="C150">
+        <v>1.07</v>
+      </c>
+      <c r="F150" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>493</v>
+      </c>
+      <c r="B151" t="s">
+        <v>503</v>
+      </c>
+      <c r="C151">
+        <v>0.3</v>
+      </c>
+      <c r="F151" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>494</v>
+      </c>
+      <c r="B152" t="s">
+        <v>503</v>
+      </c>
+      <c r="C152">
+        <v>29.162154556467332</v>
+      </c>
+      <c r="F152" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>495</v>
+      </c>
+      <c r="B153" t="s">
+        <v>503</v>
+      </c>
+      <c r="C153">
+        <v>0.83784544353266455</v>
+      </c>
+      <c r="F153" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>496</v>
+      </c>
+      <c r="B154" t="s">
+        <v>503</v>
+      </c>
+      <c r="C154">
+        <v>5.2740736776131758</v>
+      </c>
+      <c r="F154" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>497</v>
+      </c>
+      <c r="B155" t="s">
+        <v>503</v>
+      </c>
+      <c r="C155">
         <v>0.3656082203404642</v>
       </c>
-      <c r="D37" s="0"/>
-      <c r="E37" s="0"/>
-      <c r="F37" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G37" s="0"/>
-      <c r="H37" s="0"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="0" t="s">
-        <v>393</v>
-      </c>
-      <c r="B38" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C38" s="0">
-        <v>0.2156082203404642</v>
-      </c>
-      <c r="D38" s="0"/>
-      <c r="E38" s="0"/>
-      <c r="F38" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G38" s="0"/>
-      <c r="H38" s="0"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="0" t="s">
-        <v>167</v>
-      </c>
-      <c r="B39" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C39" s="0">
-        <v>4.0516000000000005</v>
-      </c>
-      <c r="D39" s="0"/>
-      <c r="E39" s="0"/>
-      <c r="F39" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G39" s="0"/>
-      <c r="H39" s="0"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="0" t="s">
-        <v>337</v>
-      </c>
-      <c r="B40" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C40" s="0">
-        <v>22.737783592977756</v>
-      </c>
-      <c r="D40" s="0" t="s">
-        <v>137</v>
-      </c>
-      <c r="E40" s="0" t="s">
-        <v>369</v>
-      </c>
-      <c r="F40" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G40" s="0"/>
-      <c r="H40" s="0"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="0" t="s">
-        <v>338</v>
-      </c>
-      <c r="B41" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C41" s="0">
-        <v>11</v>
-      </c>
-      <c r="D41" s="0" t="s">
-        <v>137</v>
-      </c>
-      <c r="E41" s="0" t="s">
-        <v>370</v>
-      </c>
-      <c r="F41" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G41" s="0"/>
-      <c r="H41" s="0"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="0" t="s">
-        <v>339</v>
-      </c>
-      <c r="B42" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C42" s="0">
-        <v>14.810748414335091</v>
-      </c>
-      <c r="D42" s="0" t="s">
-        <v>137</v>
-      </c>
-      <c r="E42" s="0" t="s">
-        <v>371</v>
-      </c>
-      <c r="F42" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G42" s="0"/>
-      <c r="H42" s="0"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="0" t="s">
-        <v>340</v>
-      </c>
-      <c r="B43" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C43" s="0">
-        <v>12.24744871391589</v>
-      </c>
-      <c r="D43" s="0" t="s">
-        <v>137</v>
-      </c>
-      <c r="E43" s="0" t="s">
-        <v>372</v>
-      </c>
-      <c r="F43" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G43" s="0"/>
-      <c r="H43" s="0"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="0" t="s">
-        <v>341</v>
-      </c>
-      <c r="B44" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C44" s="0">
-        <v>48.189685104221404</v>
-      </c>
-      <c r="D44" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="E44" s="0" t="s">
-        <v>373</v>
-      </c>
-      <c r="F44" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G44" s="0"/>
-      <c r="H44" s="0"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="0" t="s">
-        <v>342</v>
-      </c>
-      <c r="B45" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C45" s="0">
-        <v>16.699244233993625</v>
-      </c>
-      <c r="D45" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="E45" s="0" t="s">
-        <v>374</v>
-      </c>
-      <c r="F45" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G45" s="0"/>
-      <c r="H45" s="0"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="0" t="s">
-        <v>343</v>
-      </c>
-      <c r="B46" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C46" s="0">
-        <v>39.746196000000005</v>
-      </c>
-      <c r="D46" s="0" t="s">
-        <v>347</v>
-      </c>
-      <c r="E46" s="0" t="s">
-        <v>375</v>
-      </c>
-      <c r="F46" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G46" s="0"/>
-      <c r="H46" s="0"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="0" t="s">
-        <v>344</v>
-      </c>
-      <c r="B47" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C47" s="0">
-        <v>0.44283295832701009</v>
-      </c>
-      <c r="D47" s="0"/>
-      <c r="E47" s="0"/>
-      <c r="F47" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G47" s="0"/>
-      <c r="H47" s="0"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="0" t="s">
-        <v>345</v>
-      </c>
-      <c r="B48" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C48" s="0">
-        <v>233372.96903833433</v>
-      </c>
-      <c r="D48" s="0"/>
-      <c r="E48" s="0"/>
-      <c r="F48" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G48" s="0"/>
-      <c r="H48" s="0"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="0" t="s">
-        <v>346</v>
-      </c>
-      <c r="B49" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C49" s="0">
-        <v>130688.86266146721</v>
-      </c>
-      <c r="D49" s="0"/>
-      <c r="E49" s="0"/>
-      <c r="F49" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G49" s="0"/>
-      <c r="H49" s="0"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="0" t="s">
-        <v>394</v>
-      </c>
-      <c r="B50" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C50" s="0">
-        <v>34.194077618408031</v>
-      </c>
-      <c r="D50" s="0"/>
-      <c r="E50" s="0"/>
-      <c r="F50" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G50" s="0"/>
-      <c r="H50" s="0"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="0" t="s">
-        <v>395</v>
-      </c>
-      <c r="B51" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C51" s="0">
-        <v>15.480365443172449</v>
-      </c>
-      <c r="D51" s="0"/>
-      <c r="E51" s="0"/>
-      <c r="F51" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G51" s="0"/>
-      <c r="H51" s="0"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="0" t="s">
-        <v>396</v>
-      </c>
-      <c r="B52" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C52" s="0">
-        <v>3.7999999999999998</v>
-      </c>
-      <c r="D52" s="0"/>
-      <c r="E52" s="0"/>
-      <c r="F52" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G52" s="0"/>
-      <c r="H52" s="0"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="0" t="s">
-        <v>397</v>
-      </c>
-      <c r="B53" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C53" s="0">
-        <v>-1.52</v>
-      </c>
-      <c r="D53" s="0"/>
-      <c r="E53" s="0"/>
-      <c r="F53" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G53" s="0"/>
-      <c r="H53" s="0"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="0" t="s">
-        <v>398</v>
-      </c>
-      <c r="B54" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C54" s="0">
-        <v>5.6999999999999993</v>
-      </c>
-      <c r="D54" s="0"/>
-      <c r="E54" s="0"/>
-      <c r="F54" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G54" s="0"/>
-      <c r="H54" s="0"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="0" t="s">
-        <v>399</v>
-      </c>
-      <c r="B55" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C55" s="0">
-        <v>-2.2800000000000003</v>
-      </c>
-      <c r="D55" s="0"/>
-      <c r="E55" s="0"/>
-      <c r="F55" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G55" s="0"/>
-      <c r="H55" s="0"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="0" t="s">
-        <v>400</v>
-      </c>
-      <c r="B56" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C56" s="0">
-        <v>18.622682892532463</v>
-      </c>
-      <c r="D56" s="0"/>
-      <c r="E56" s="0"/>
-      <c r="F56" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G56" s="0"/>
-      <c r="H56" s="0"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="0" t="s">
-        <v>401</v>
-      </c>
-      <c r="B57" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C57" s="0">
-        <v>27.131986877647702</v>
-      </c>
-      <c r="D57" s="0"/>
-      <c r="E57" s="0"/>
-      <c r="F57" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G57" s="0"/>
-      <c r="H57" s="0"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="0" t="s">
-        <v>402</v>
-      </c>
-      <c r="B58" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C58" s="0">
-        <v>25.580006542099977</v>
-      </c>
-      <c r="D58" s="0"/>
-      <c r="E58" s="0"/>
-      <c r="F58" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G58" s="0"/>
-      <c r="H58" s="0"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="0" t="s">
-        <v>403</v>
-      </c>
-      <c r="B59" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C59" s="0">
-        <v>28.422229491222197</v>
-      </c>
-      <c r="D59" s="0"/>
-      <c r="E59" s="0"/>
-      <c r="F59" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G59" s="0"/>
-      <c r="H59" s="0"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="0" t="s">
-        <v>404</v>
-      </c>
-      <c r="B60" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C60" s="0">
-        <v>6.3586494759793881</v>
-      </c>
-      <c r="D60" s="0"/>
-      <c r="E60" s="0"/>
-      <c r="F60" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G60" s="0"/>
-      <c r="H60" s="0"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="0" t="s">
-        <v>405</v>
-      </c>
-      <c r="B61" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C61" s="0">
-        <v>11.113261724726186</v>
-      </c>
-      <c r="D61" s="0"/>
-      <c r="E61" s="0"/>
-      <c r="F61" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G61" s="0"/>
-      <c r="H61" s="0"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="0" t="s">
-        <v>406</v>
-      </c>
-      <c r="B62" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C62" s="0">
-        <v>1.9300000000000015</v>
-      </c>
-      <c r="D62" s="0"/>
-      <c r="E62" s="0"/>
-      <c r="F62" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G62" s="0"/>
-      <c r="H62" s="0"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="0" t="s">
-        <v>407</v>
-      </c>
-      <c r="B63" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C63" s="0">
-        <v>11.008581406383897</v>
-      </c>
-      <c r="D63" s="0"/>
-      <c r="E63" s="0"/>
-      <c r="F63" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G63" s="0"/>
-      <c r="H63" s="0"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="0" t="s">
-        <v>408</v>
-      </c>
-      <c r="B64" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C64" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="D64" s="0"/>
-      <c r="E64" s="0"/>
-      <c r="F64" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G64" s="0"/>
-      <c r="H64" s="0"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="0" t="s">
-        <v>409</v>
-      </c>
-      <c r="B65" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C65" s="0">
-        <v>7.4507370536077033</v>
-      </c>
-      <c r="D65" s="0"/>
-      <c r="E65" s="0"/>
-      <c r="F65" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G65" s="0"/>
-      <c r="H65" s="0"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="0" t="s">
-        <v>410</v>
-      </c>
-      <c r="B66" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C66" s="0">
-        <v>20.550728554427437</v>
-      </c>
-      <c r="D66" s="0"/>
-      <c r="E66" s="0"/>
-      <c r="F66" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G66" s="0"/>
-      <c r="H66" s="0"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="0" t="s">
-        <v>411</v>
-      </c>
-      <c r="B67" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C67" s="0">
-        <v>4.0264472875839541</v>
-      </c>
-      <c r="D67" s="0"/>
-      <c r="E67" s="0"/>
-      <c r="F67" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G67" s="0"/>
-      <c r="H67" s="0"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="0" t="s">
-        <v>522</v>
-      </c>
-      <c r="B68" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C68" s="0">
-        <v>77.116605805538328</v>
-      </c>
-      <c r="D68" s="0"/>
-      <c r="E68" s="0"/>
-      <c r="F68" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G68" s="0"/>
-      <c r="H68" s="0"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="0" t="s">
-        <v>412</v>
-      </c>
-      <c r="B69" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C69" s="0">
-        <v>22.608098531363336</v>
-      </c>
-      <c r="D69" s="0"/>
-      <c r="E69" s="0"/>
-      <c r="F69" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G69" s="0"/>
-      <c r="H69" s="0"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="0" t="s">
-        <v>413</v>
-      </c>
-      <c r="B70" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C70" s="0">
-        <v>12.709922788411269</v>
-      </c>
-      <c r="D70" s="0"/>
-      <c r="E70" s="0"/>
-      <c r="F70" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G70" s="0"/>
-      <c r="H70" s="0"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="0" t="s">
-        <v>414</v>
-      </c>
-      <c r="B71" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C71" s="0">
-        <v>16.27392540932771</v>
-      </c>
-      <c r="D71" s="0"/>
-      <c r="E71" s="0"/>
-      <c r="F71" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G71" s="0"/>
-      <c r="H71" s="0"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="0" t="s">
-        <v>415</v>
-      </c>
-      <c r="B72" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C72" s="0">
-        <v>15.956485750905872</v>
-      </c>
-      <c r="D72" s="0"/>
-      <c r="E72" s="0"/>
-      <c r="F72" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G72" s="0"/>
-      <c r="H72" s="0"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="0" t="s">
-        <v>416</v>
-      </c>
-      <c r="B73" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C73" s="0">
-        <v>13.695854805920606</v>
-      </c>
-      <c r="D73" s="0"/>
-      <c r="E73" s="0"/>
-      <c r="F73" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G73" s="0"/>
-      <c r="H73" s="0"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="0" t="s">
-        <v>417</v>
-      </c>
-      <c r="B74" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C74" s="0">
-        <v>1.0954451150103324</v>
-      </c>
-      <c r="D74" s="0"/>
-      <c r="E74" s="0"/>
-      <c r="F74" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G74" s="0"/>
-      <c r="H74" s="0"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="0" t="s">
-        <v>418</v>
-      </c>
-      <c r="B75" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C75" s="0">
-        <v>24.094842552110709</v>
-      </c>
-      <c r="D75" s="0"/>
-      <c r="E75" s="0"/>
-      <c r="F75" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G75" s="0"/>
-      <c r="H75" s="0"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="0" t="s">
-        <v>419</v>
-      </c>
-      <c r="B76" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C76" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="D76" s="0"/>
-      <c r="E76" s="0"/>
-      <c r="F76" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G76" s="0"/>
-      <c r="H76" s="0"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="0" t="s">
-        <v>420</v>
-      </c>
-      <c r="B77" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C77" s="0">
-        <v>150.69320484179264</v>
-      </c>
-      <c r="D77" s="0"/>
-      <c r="E77" s="0"/>
-      <c r="F77" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G77" s="0"/>
-      <c r="H77" s="0"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="0" t="s">
-        <v>421</v>
-      </c>
-      <c r="B78" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C78" s="0">
-        <v>46195.337793815328</v>
-      </c>
-      <c r="D78" s="0"/>
-      <c r="E78" s="0"/>
-      <c r="F78" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G78" s="0"/>
-      <c r="H78" s="0"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="0" t="s">
-        <v>422</v>
-      </c>
-      <c r="B79" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C79" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="D79" s="0"/>
-      <c r="E79" s="0"/>
-      <c r="F79" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G79" s="0"/>
-      <c r="H79" s="0"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="0" t="s">
-        <v>423</v>
-      </c>
-      <c r="B80" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C80" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="D80" s="0"/>
-      <c r="E80" s="0"/>
-      <c r="F80" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G80" s="0"/>
-      <c r="H80" s="0"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="0" t="s">
-        <v>523</v>
-      </c>
-      <c r="B81" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C81" s="0">
-        <v>890</v>
-      </c>
-      <c r="D81" s="0"/>
-      <c r="E81" s="0"/>
-      <c r="F81" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G81" s="0"/>
-      <c r="H81" s="0"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="0" t="s">
-        <v>424</v>
-      </c>
-      <c r="B82" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C82" s="0">
-        <v>13</v>
-      </c>
-      <c r="D82" s="0"/>
-      <c r="E82" s="0"/>
-      <c r="F82" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G82" s="0"/>
-      <c r="H82" s="0"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="0" t="s">
-        <v>425</v>
-      </c>
-      <c r="B83" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C83" s="0">
-        <v>84493.524867651882</v>
-      </c>
-      <c r="D83" s="0"/>
-      <c r="E83" s="0"/>
-      <c r="F83" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G83" s="0"/>
-      <c r="H83" s="0"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="0" t="s">
-        <v>426</v>
-      </c>
-      <c r="B84" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C84" s="0">
-        <v>0.16032926919858043</v>
-      </c>
-      <c r="D84" s="0"/>
-      <c r="E84" s="0"/>
-      <c r="F84" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G84" s="0"/>
-      <c r="H84" s="0"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="0" t="s">
-        <v>427</v>
-      </c>
-      <c r="B85" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C85" s="0">
-        <v>2.4683999999999995</v>
-      </c>
-      <c r="D85" s="0"/>
-      <c r="E85" s="0"/>
-      <c r="F85" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G85" s="0"/>
-      <c r="H85" s="0"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="0" t="s">
-        <v>428</v>
-      </c>
-      <c r="B86" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C86" s="0" t="s">
-        <v>504</v>
-      </c>
-      <c r="D86" s="0"/>
-      <c r="E86" s="0"/>
-      <c r="F86" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G86" s="0"/>
-      <c r="H86" s="0"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="0" t="s">
-        <v>429</v>
-      </c>
-      <c r="B87" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C87" s="0">
-        <v>-0.040973254512723323</v>
-      </c>
-      <c r="D87" s="0"/>
-      <c r="E87" s="0"/>
-      <c r="F87" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G87" s="0"/>
-      <c r="H87" s="0"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="0" t="s">
-        <v>430</v>
-      </c>
-      <c r="B88" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C88" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="D88" s="0"/>
-      <c r="E88" s="0"/>
-      <c r="F88" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G88" s="0"/>
-      <c r="H88" s="0"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="0" t="s">
-        <v>431</v>
-      </c>
-      <c r="B89" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C89" s="0">
-        <v>0.254</v>
-      </c>
-      <c r="D89" s="0"/>
-      <c r="E89" s="0"/>
-      <c r="F89" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G89" s="0"/>
-      <c r="H89" s="0"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="0" t="s">
-        <v>432</v>
-      </c>
-      <c r="B90" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C90" s="0">
-        <v>0.127</v>
-      </c>
-      <c r="D90" s="0"/>
-      <c r="E90" s="0"/>
-      <c r="F90" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G90" s="0"/>
-      <c r="H90" s="0"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="0" t="s">
-        <v>433</v>
-      </c>
-      <c r="B91" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C91" s="0">
-        <v>14500</v>
-      </c>
-      <c r="D91" s="0"/>
-      <c r="E91" s="0"/>
-      <c r="F91" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G91" s="0"/>
-      <c r="H91" s="0"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="0" t="s">
-        <v>434</v>
-      </c>
-      <c r="B92" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C92" s="0" t="s">
-        <v>505</v>
-      </c>
-      <c r="D92" s="0"/>
-      <c r="E92" s="0"/>
-      <c r="F92" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G92" s="0"/>
-      <c r="H92" s="0"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="0" t="s">
-        <v>435</v>
-      </c>
-      <c r="B93" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C93" s="0" t="s">
-        <v>506</v>
-      </c>
-      <c r="D93" s="0"/>
-      <c r="E93" s="0"/>
-      <c r="F93" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G93" s="0"/>
-      <c r="H93" s="0"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="0" t="s">
-        <v>436</v>
-      </c>
-      <c r="B94" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C94" s="0" t="s">
-        <v>507</v>
-      </c>
-      <c r="D94" s="0"/>
-      <c r="E94" s="0"/>
-      <c r="F94" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G94" s="0"/>
-      <c r="H94" s="0"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="0" t="s">
-        <v>437</v>
-      </c>
-      <c r="B95" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C95" s="0" t="s">
-        <v>507</v>
-      </c>
-      <c r="D95" s="0"/>
-      <c r="E95" s="0"/>
-      <c r="F95" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G95" s="0"/>
-      <c r="H95" s="0"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="0" t="s">
-        <v>438</v>
-      </c>
-      <c r="B96" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C96" s="0" t="s">
-        <v>507</v>
-      </c>
-      <c r="D96" s="0"/>
-      <c r="E96" s="0"/>
-      <c r="F96" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G96" s="0"/>
-      <c r="H96" s="0"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="0" t="s">
-        <v>439</v>
-      </c>
-      <c r="B97" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C97" s="0" t="s">
-        <v>507</v>
-      </c>
-      <c r="D97" s="0"/>
-      <c r="E97" s="0"/>
-      <c r="F97" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G97" s="0"/>
-      <c r="H97" s="0"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="0" t="s">
-        <v>440</v>
-      </c>
-      <c r="B98" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C98" s="0" t="s">
-        <v>507</v>
-      </c>
-      <c r="D98" s="0"/>
-      <c r="E98" s="0"/>
-      <c r="F98" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G98" s="0"/>
-      <c r="H98" s="0"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="0" t="s">
-        <v>441</v>
-      </c>
-      <c r="B99" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C99" s="0" t="s">
-        <v>507</v>
-      </c>
-      <c r="D99" s="0"/>
-      <c r="E99" s="0"/>
-      <c r="F99" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G99" s="0"/>
-      <c r="H99" s="0"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="0" t="s">
-        <v>442</v>
-      </c>
-      <c r="B100" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C100" s="0" t="s">
-        <v>507</v>
-      </c>
-      <c r="D100" s="0"/>
-      <c r="E100" s="0"/>
-      <c r="F100" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G100" s="0"/>
-      <c r="H100" s="0"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="0" t="s">
-        <v>443</v>
-      </c>
-      <c r="B101" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C101" s="0" t="s">
-        <v>507</v>
-      </c>
-      <c r="D101" s="0"/>
-      <c r="E101" s="0"/>
-      <c r="F101" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G101" s="0"/>
-      <c r="H101" s="0"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="0" t="s">
-        <v>444</v>
-      </c>
-      <c r="B102" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C102" s="0" t="s">
-        <v>508</v>
-      </c>
-      <c r="D102" s="0"/>
-      <c r="E102" s="0"/>
-      <c r="F102" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G102" s="0"/>
-      <c r="H102" s="0"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="0" t="s">
-        <v>445</v>
-      </c>
-      <c r="B103" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C103" s="0">
-        <v>890</v>
-      </c>
-      <c r="D103" s="0"/>
-      <c r="E103" s="0"/>
-      <c r="F103" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G103" s="0"/>
-      <c r="H103" s="0"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="0" t="s">
-        <v>446</v>
-      </c>
-      <c r="B104" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C104" s="0">
-        <v>60</v>
-      </c>
-      <c r="D104" s="0"/>
-      <c r="E104" s="0"/>
-      <c r="F104" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G104" s="0"/>
-      <c r="H104" s="0"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="0" t="s">
-        <v>447</v>
-      </c>
-      <c r="B105" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C105" s="0" t="s">
-        <v>509</v>
-      </c>
-      <c r="D105" s="0"/>
-      <c r="E105" s="0"/>
-      <c r="F105" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G105" s="0"/>
-      <c r="H105" s="0"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="0" t="s">
-        <v>448</v>
-      </c>
-      <c r="B106" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C106" s="0" t="s">
-        <v>507</v>
-      </c>
-      <c r="D106" s="0"/>
-      <c r="E106" s="0"/>
-      <c r="F106" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G106" s="0"/>
-      <c r="H106" s="0"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="0" t="s">
-        <v>449</v>
-      </c>
-      <c r="B107" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C107" s="0" t="s">
-        <v>510</v>
-      </c>
-      <c r="D107" s="0"/>
-      <c r="E107" s="0"/>
-      <c r="F107" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G107" s="0"/>
-      <c r="H107" s="0"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="0" t="s">
-        <v>450</v>
-      </c>
-      <c r="B108" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C108" s="0" t="s">
-        <v>511</v>
-      </c>
-      <c r="D108" s="0"/>
-      <c r="E108" s="0"/>
-      <c r="F108" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G108" s="0"/>
-      <c r="H108" s="0"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="0" t="s">
-        <v>451</v>
-      </c>
-      <c r="B109" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C109" s="0" t="s">
-        <v>512</v>
-      </c>
-      <c r="D109" s="0"/>
-      <c r="E109" s="0"/>
-      <c r="F109" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G109" s="0"/>
-      <c r="H109" s="0"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="0" t="s">
-        <v>452</v>
-      </c>
-      <c r="B110" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C110" s="0" t="s">
-        <v>513</v>
-      </c>
-      <c r="D110" s="0"/>
-      <c r="E110" s="0"/>
-      <c r="F110" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G110" s="0"/>
-      <c r="H110" s="0"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="0" t="s">
-        <v>453</v>
-      </c>
-      <c r="B111" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C111" s="0" t="s">
-        <v>514</v>
-      </c>
-      <c r="D111" s="0"/>
-      <c r="E111" s="0"/>
-      <c r="F111" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G111" s="0"/>
-      <c r="H111" s="0"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="0" t="s">
-        <v>454</v>
-      </c>
-      <c r="B112" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C112" s="0" t="s">
-        <v>515</v>
-      </c>
-      <c r="D112" s="0"/>
-      <c r="E112" s="0"/>
-      <c r="F112" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G112" s="0"/>
-      <c r="H112" s="0"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="0" t="s">
-        <v>455</v>
-      </c>
-      <c r="B113" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C113" s="0" t="s">
-        <v>516</v>
-      </c>
-      <c r="D113" s="0"/>
-      <c r="E113" s="0"/>
-      <c r="F113" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G113" s="0"/>
-      <c r="H113" s="0"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="0" t="s">
-        <v>456</v>
-      </c>
-      <c r="B114" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C114" s="0">
-        <v>32.946133306980855</v>
-      </c>
-      <c r="D114" s="0"/>
-      <c r="E114" s="0"/>
-      <c r="F114" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G114" s="0"/>
-      <c r="H114" s="0"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="0" t="s">
-        <v>457</v>
-      </c>
-      <c r="B115" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C115" s="0">
-        <v>0</v>
-      </c>
-      <c r="D115" s="0"/>
-      <c r="E115" s="0"/>
-      <c r="F115" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G115" s="0"/>
-      <c r="H115" s="0"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="0" t="s">
-        <v>458</v>
-      </c>
-      <c r="B116" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C116" s="0" t="s">
-        <v>517</v>
-      </c>
-      <c r="D116" s="0"/>
-      <c r="E116" s="0"/>
-      <c r="F116" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G116" s="0"/>
-      <c r="H116" s="0"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="0" t="s">
-        <v>459</v>
-      </c>
-      <c r="B117" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C117" s="0">
-        <v>86.068285472894019</v>
-      </c>
-      <c r="D117" s="0"/>
-      <c r="E117" s="0"/>
-      <c r="F117" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G117" s="0"/>
-      <c r="H117" s="0"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="0" t="s">
-        <v>460</v>
-      </c>
-      <c r="B118" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C118" s="0">
-        <v>0</v>
-      </c>
-      <c r="D118" s="0"/>
-      <c r="E118" s="0"/>
-      <c r="F118" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G118" s="0"/>
-      <c r="H118" s="0"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="0" t="s">
-        <v>461</v>
-      </c>
-      <c r="B119" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C119" s="0">
-        <v>-1.8275795392708134</v>
-      </c>
-      <c r="D119" s="0"/>
-      <c r="E119" s="0"/>
-      <c r="F119" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G119" s="0"/>
-      <c r="H119" s="0"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="0" t="s">
-        <v>462</v>
-      </c>
-      <c r="B120" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C120" s="0">
-        <v>0</v>
-      </c>
-      <c r="D120" s="0"/>
-      <c r="E120" s="0"/>
-      <c r="F120" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G120" s="0"/>
-      <c r="H120" s="0"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="0" t="s">
-        <v>463</v>
-      </c>
-      <c r="B121" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C121" s="0">
-        <v>1.7526473681977495</v>
-      </c>
-      <c r="D121" s="0"/>
-      <c r="E121" s="0"/>
-      <c r="F121" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G121" s="0"/>
-      <c r="H121" s="0"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="0" t="s">
-        <v>464</v>
-      </c>
-      <c r="B122" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C122" s="0">
-        <v>0.15168253041257554</v>
-      </c>
-      <c r="D122" s="0"/>
-      <c r="E122" s="0"/>
-      <c r="F122" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G122" s="0"/>
-      <c r="H122" s="0"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="0" t="s">
-        <v>465</v>
-      </c>
-      <c r="B123" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C123" s="0">
-        <v>2.4110213483593652</v>
-      </c>
-      <c r="D123" s="0"/>
-      <c r="E123" s="0"/>
-      <c r="F123" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G123" s="0"/>
-      <c r="H123" s="0"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="0" t="s">
-        <v>466</v>
-      </c>
-      <c r="B124" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C124" s="0">
-        <v>2.7131092758196531</v>
-      </c>
-      <c r="D124" s="0"/>
-      <c r="E124" s="0"/>
-      <c r="F124" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G124" s="0"/>
-      <c r="H124" s="0"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="0" t="s">
-        <v>467</v>
-      </c>
-      <c r="B125" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C125" s="0">
-        <v>16.090147165877724</v>
-      </c>
-      <c r="D125" s="0"/>
-      <c r="E125" s="0"/>
-      <c r="F125" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G125" s="0"/>
-      <c r="H125" s="0"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="0" t="s">
-        <v>468</v>
-      </c>
-      <c r="B126" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C126" s="0">
-        <v>16.925292122478595</v>
-      </c>
-      <c r="D126" s="0"/>
-      <c r="E126" s="0"/>
-      <c r="F126" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G126" s="0"/>
-      <c r="H126" s="0"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="0" t="s">
-        <v>469</v>
-      </c>
-      <c r="B127" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C127" s="0">
-        <v>0.35178486510320511</v>
-      </c>
-      <c r="D127" s="0"/>
-      <c r="E127" s="0"/>
-      <c r="F127" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G127" s="0"/>
-      <c r="H127" s="0"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="0" t="s">
-        <v>470</v>
-      </c>
-      <c r="B128" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C128" s="0" t="s">
-        <v>518</v>
-      </c>
-      <c r="D128" s="0"/>
-      <c r="E128" s="0"/>
-      <c r="F128" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G128" s="0"/>
-      <c r="H128" s="0"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="0" t="s">
-        <v>471</v>
-      </c>
-      <c r="B129" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C129" s="0">
-        <v>233.69773788009346</v>
-      </c>
-      <c r="D129" s="0"/>
-      <c r="E129" s="0"/>
-      <c r="F129" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G129" s="0"/>
-      <c r="H129" s="0"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="0" t="s">
-        <v>472</v>
-      </c>
-      <c r="B130" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C130" s="0">
-        <v>0.35242563899228197</v>
-      </c>
-      <c r="D130" s="0"/>
-      <c r="E130" s="0"/>
-      <c r="F130" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G130" s="0"/>
-      <c r="H130" s="0"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="0" t="s">
-        <v>473</v>
-      </c>
-      <c r="B131" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C131" s="0" t="s">
-        <v>518</v>
-      </c>
-      <c r="D131" s="0"/>
-      <c r="E131" s="0"/>
-      <c r="F131" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G131" s="0"/>
-      <c r="H131" s="0"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="0" t="s">
-        <v>474</v>
-      </c>
-      <c r="B132" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C132" s="0">
-        <v>9.4744003772526408</v>
-      </c>
-      <c r="D132" s="0"/>
-      <c r="E132" s="0"/>
-      <c r="F132" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G132" s="0"/>
-      <c r="H132" s="0"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="0" t="s">
-        <v>475</v>
-      </c>
-      <c r="B133" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C133" s="0">
-        <v>341.83792795003058</v>
-      </c>
-      <c r="D133" s="0"/>
-      <c r="E133" s="0"/>
-      <c r="F133" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G133" s="0"/>
-      <c r="H133" s="0"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="0" t="s">
-        <v>476</v>
-      </c>
-      <c r="B134" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C134" s="0">
-        <v>34.733446426726843</v>
-      </c>
-      <c r="D134" s="0"/>
-      <c r="E134" s="0"/>
-      <c r="F134" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G134" s="0"/>
-      <c r="H134" s="0"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="0" t="s">
-        <v>477</v>
-      </c>
-      <c r="B135" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C135" s="0">
-        <v>0.42099254615460552</v>
-      </c>
-      <c r="D135" s="0"/>
-      <c r="E135" s="0"/>
-      <c r="F135" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G135" s="0"/>
-      <c r="H135" s="0"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="0" t="s">
-        <v>478</v>
-      </c>
-      <c r="B136" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C136" s="0">
-        <v>4.0516000000000005</v>
-      </c>
-      <c r="D136" s="0"/>
-      <c r="E136" s="0"/>
-      <c r="F136" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G136" s="0"/>
-      <c r="H136" s="0"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="0" t="s">
-        <v>479</v>
-      </c>
-      <c r="B137" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C137" s="0">
-        <v>39.746196000000005</v>
-      </c>
-      <c r="D137" s="0"/>
-      <c r="E137" s="0"/>
-      <c r="F137" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G137" s="0"/>
-      <c r="H137" s="0"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="0" t="s">
-        <v>480</v>
-      </c>
-      <c r="B138" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C138" s="0">
-        <v>18.230437113682747</v>
-      </c>
-      <c r="D138" s="0"/>
-      <c r="E138" s="0"/>
-      <c r="F138" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G138" s="0"/>
-      <c r="H138" s="0"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="0" t="s">
-        <v>481</v>
-      </c>
-      <c r="B139" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C139" s="0">
-        <v>0.080999999999999989</v>
-      </c>
-      <c r="D139" s="0"/>
-      <c r="E139" s="0"/>
-      <c r="F139" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G139" s="0"/>
-      <c r="H139" s="0"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="0" t="s">
-        <v>482</v>
-      </c>
-      <c r="B140" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C140" s="0">
-        <v>64.749890848167752</v>
-      </c>
-      <c r="D140" s="0"/>
-      <c r="E140" s="0"/>
-      <c r="F140" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G140" s="0"/>
-      <c r="H140" s="0"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="0" t="s">
-        <v>483</v>
-      </c>
-      <c r="B141" s="0" t="s">
+      <c r="F155" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>498</v>
+      </c>
+      <c r="B156" t="s">
         <v>503</v>
       </c>
-      <c r="C141" s="0">
-        <v>0.29999999999999999</v>
-      </c>
-      <c r="D141" s="0"/>
-      <c r="E141" s="0"/>
-      <c r="F141" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G141" s="0"/>
-      <c r="H141" s="0"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="0" t="s">
-        <v>484</v>
-      </c>
-      <c r="B142" s="0" t="s">
+      <c r="C156">
+        <v>0.15</v>
+      </c>
+      <c r="F156" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>499</v>
+      </c>
+      <c r="B157" t="s">
         <v>503</v>
       </c>
-      <c r="C142" s="0">
-        <v>26.360381758366742</v>
-      </c>
-      <c r="D142" s="0"/>
-      <c r="E142" s="0"/>
-      <c r="F142" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G142" s="0"/>
-      <c r="H142" s="0"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="0" t="s">
-        <v>485</v>
-      </c>
-      <c r="B143" s="0" t="s">
+      <c r="C157">
+        <v>-0.79111105164197637</v>
+      </c>
+      <c r="F157" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>500</v>
+      </c>
+      <c r="B158" t="s">
         <v>503</v>
       </c>
-      <c r="C143" s="0">
-        <v>3.6396182416332579</v>
-      </c>
-      <c r="D143" s="0"/>
-      <c r="E143" s="0"/>
-      <c r="F143" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G143" s="0"/>
-      <c r="H143" s="0"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="0" t="s">
-        <v>486</v>
-      </c>
-      <c r="B144" s="0" t="s">
+      <c r="C158">
+        <v>0.12602616170797043</v>
+      </c>
+      <c r="F158" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>501</v>
+      </c>
+      <c r="B159" t="s">
         <v>503</v>
       </c>
-      <c r="C144" s="0">
-        <v>0.25</v>
-      </c>
-      <c r="D144" s="0"/>
-      <c r="E144" s="0"/>
-      <c r="F144" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G144" s="0"/>
-      <c r="H144" s="0"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="0" t="s">
-        <v>487</v>
-      </c>
-      <c r="B145" s="0" t="s">
+      <c r="C159">
+        <v>5</v>
+      </c>
+      <c r="F159" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>502</v>
+      </c>
+      <c r="B160" t="s">
         <v>503</v>
       </c>
-      <c r="C145" s="0">
-        <v>0.69999999999999996</v>
-      </c>
-      <c r="D145" s="0"/>
-      <c r="E145" s="0"/>
-      <c r="F145" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G145" s="0"/>
-      <c r="H145" s="0"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="0" t="s">
-        <v>488</v>
-      </c>
-      <c r="B146" s="0" t="s">
-        <v>503</v>
-      </c>
-      <c r="C146" s="0">
-        <v>1</v>
-      </c>
-      <c r="D146" s="0"/>
-      <c r="E146" s="0"/>
-      <c r="F146" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G146" s="0"/>
-      <c r="H146" s="0"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="0" t="s">
-        <v>489</v>
-      </c>
-      <c r="B147" s="0" t="s">
-        <v>503</v>
-      </c>
-      <c r="C147" s="0">
-        <v>0.12048857500544551</v>
-      </c>
-      <c r="D147" s="0"/>
-      <c r="E147" s="0"/>
-      <c r="F147" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G147" s="0"/>
-      <c r="H147" s="0"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="0" t="s">
-        <v>490</v>
-      </c>
-      <c r="B148" s="0" t="s">
-        <v>503</v>
-      </c>
-      <c r="C148" s="0">
-        <v>119.66043834086311</v>
-      </c>
-      <c r="D148" s="0"/>
-      <c r="E148" s="0"/>
-      <c r="F148" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G148" s="0"/>
-      <c r="H148" s="0"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="0" t="s">
-        <v>491</v>
-      </c>
-      <c r="B149" s="0" t="s">
-        <v>503</v>
-      </c>
-      <c r="C149" s="0">
-        <v>0.074583678423586861</v>
-      </c>
-      <c r="D149" s="0"/>
-      <c r="E149" s="0"/>
-      <c r="F149" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G149" s="0"/>
-      <c r="H149" s="0"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="0" t="s">
-        <v>492</v>
-      </c>
-      <c r="B150" s="0" t="s">
-        <v>503</v>
-      </c>
-      <c r="C150" s="0">
-        <v>1.0700000000000001</v>
-      </c>
-      <c r="D150" s="0"/>
-      <c r="E150" s="0"/>
-      <c r="F150" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G150" s="0"/>
-      <c r="H150" s="0"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="0" t="s">
-        <v>493</v>
-      </c>
-      <c r="B151" s="0" t="s">
-        <v>503</v>
-      </c>
-      <c r="C151" s="0">
-        <v>0.29999999999999999</v>
-      </c>
-      <c r="D151" s="0"/>
-      <c r="E151" s="0"/>
-      <c r="F151" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G151" s="0"/>
-      <c r="H151" s="0"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="0" t="s">
-        <v>494</v>
-      </c>
-      <c r="B152" s="0" t="s">
-        <v>503</v>
-      </c>
-      <c r="C152" s="0">
-        <v>29.162154556467332</v>
-      </c>
-      <c r="D152" s="0"/>
-      <c r="E152" s="0"/>
-      <c r="F152" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G152" s="0"/>
-      <c r="H152" s="0"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="0" t="s">
-        <v>495</v>
-      </c>
-      <c r="B153" s="0" t="s">
-        <v>503</v>
-      </c>
-      <c r="C153" s="0">
-        <v>0.83784544353266455</v>
-      </c>
-      <c r="D153" s="0"/>
-      <c r="E153" s="0"/>
-      <c r="F153" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G153" s="0"/>
-      <c r="H153" s="0"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="0" t="s">
-        <v>496</v>
-      </c>
-      <c r="B154" s="0" t="s">
-        <v>503</v>
-      </c>
-      <c r="C154" s="0">
-        <v>5.2740736776131758</v>
-      </c>
-      <c r="D154" s="0"/>
-      <c r="E154" s="0"/>
-      <c r="F154" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G154" s="0"/>
-      <c r="H154" s="0"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="0" t="s">
-        <v>497</v>
-      </c>
-      <c r="B155" s="0" t="s">
-        <v>503</v>
-      </c>
-      <c r="C155" s="0">
-        <v>0.3656082203404642</v>
-      </c>
-      <c r="D155" s="0"/>
-      <c r="E155" s="0"/>
-      <c r="F155" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G155" s="0"/>
-      <c r="H155" s="0"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="0" t="s">
-        <v>498</v>
-      </c>
-      <c r="B156" s="0" t="s">
-        <v>503</v>
-      </c>
-      <c r="C156" s="0">
-        <v>0.15</v>
-      </c>
-      <c r="D156" s="0"/>
-      <c r="E156" s="0"/>
-      <c r="F156" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G156" s="0"/>
-      <c r="H156" s="0"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="0" t="s">
-        <v>499</v>
-      </c>
-      <c r="B157" s="0" t="s">
-        <v>503</v>
-      </c>
-      <c r="C157" s="0">
-        <v>-0.79111105164197637</v>
-      </c>
-      <c r="D157" s="0"/>
-      <c r="E157" s="0"/>
-      <c r="F157" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G157" s="0"/>
-      <c r="H157" s="0"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="0" t="s">
-        <v>500</v>
-      </c>
-      <c r="B158" s="0" t="s">
-        <v>503</v>
-      </c>
-      <c r="C158" s="0">
-        <v>0.12602616170797043</v>
-      </c>
-      <c r="D158" s="0"/>
-      <c r="E158" s="0"/>
-      <c r="F158" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G158" s="0"/>
-      <c r="H158" s="0"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="0" t="s">
-        <v>501</v>
-      </c>
-      <c r="B159" s="0" t="s">
-        <v>503</v>
-      </c>
-      <c r="C159" s="0">
-        <v>5</v>
-      </c>
-      <c r="D159" s="0"/>
-      <c r="E159" s="0"/>
-      <c r="F159" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G159" s="0"/>
-      <c r="H159" s="0"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="0" t="s">
-        <v>502</v>
-      </c>
-      <c r="B160" s="0" t="s">
-        <v>503</v>
-      </c>
-      <c r="C160" s="0">
+      <c r="C160">
         <v>-0.18486997339978403</v>
       </c>
-      <c r="D160" s="0"/>
-      <c r="E160" s="0"/>
-      <c r="F160" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G160" s="0"/>
-      <c r="H160" s="0"/>
+      <c r="F160" t="s">
+        <v>377</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6992,14 +6402,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFCC8514-E0AF-4C67-BF86-8649FC702924}">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.44140625" customWidth="1"/>
-    <col min="2" max="3" width="32.44140625" style="20" customWidth="1"/>
-    <col min="4" max="4" width="13.33203125" style="20" customWidth="1"/>
+    <col min="1" max="1" width="32.42578125" customWidth="1"/>
+    <col min="2" max="3" width="32.42578125" style="20" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" style="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>274</v>
       </c>
@@ -7013,7 +6423,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>276</v>
       </c>
@@ -7024,150 +6434,150 @@
         <v>0</v>
       </c>
       <c r="D2" s="21">
-        <v>2.8000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
         <v>277</v>
       </c>
       <c r="B3" s="21">
-        <v>116.7</v>
+        <v>210</v>
       </c>
       <c r="C3" s="21">
-        <v>3.5000000000000003E-2</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="D3" s="21">
-        <v>2.8000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>278</v>
       </c>
       <c r="B4" s="21">
-        <v>22.7</v>
+        <v>74.599999999999994</v>
       </c>
       <c r="C4" s="21">
-        <v>5.5E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="D4" s="21">
-        <v>2.8000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+        <v>5.6000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>279</v>
       </c>
       <c r="B5" s="21">
-        <v>32.4</v>
+        <v>96.2</v>
       </c>
       <c r="C5" s="21">
-        <v>0.09</v>
+        <v>0.13600000000000001</v>
       </c>
       <c r="D5" s="21">
-        <v>2.5000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1.7999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
         <v>304</v>
       </c>
       <c r="B6" s="21">
-        <v>45.4</v>
+        <v>9</v>
       </c>
       <c r="C6" s="21">
-        <v>1.1000000000000001</v>
+        <v>1.254</v>
       </c>
       <c r="D6" s="21">
-        <v>-4.4999999999999998E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+        <v>-2.1999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>280</v>
       </c>
       <c r="B7" s="21">
-        <v>440.8</v>
+        <v>451</v>
       </c>
       <c r="C7" s="21">
-        <v>0.12</v>
+        <v>0.17199999999999999</v>
       </c>
       <c r="D7" s="21">
-        <v>1.4999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+        <v>4.9000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>281</v>
       </c>
       <c r="B8" s="21">
-        <v>58.3</v>
+        <v>119.9</v>
       </c>
       <c r="C8" s="21">
-        <v>0.23</v>
+        <v>0.437</v>
       </c>
       <c r="D8" s="21">
-        <v>2.8000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+        <v>5.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>282</v>
       </c>
       <c r="B9" s="21">
-        <v>64.8</v>
+        <v>44.7</v>
       </c>
       <c r="C9" s="21">
-        <v>0.3</v>
+        <v>0.56499999999999995</v>
       </c>
       <c r="D9" s="21">
-        <v>2.8000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+        <v>8.6999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>283</v>
       </c>
       <c r="B10" s="21">
-        <v>259.3</v>
+        <v>0.05</v>
       </c>
       <c r="C10" s="21">
-        <v>0.32</v>
+        <v>0.33200000000000002</v>
       </c>
       <c r="D10" s="21">
-        <v>2.8000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>284</v>
       </c>
       <c r="B11" s="21">
-        <v>13.4</v>
+        <v>20.7</v>
       </c>
       <c r="C11" s="21">
-        <v>0.4</v>
+        <v>0.46200000000000002</v>
       </c>
       <c r="D11" s="21">
-        <v>5.5E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+        <v>0.14599999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>285</v>
       </c>
       <c r="B12" s="21">
-        <v>13.4</v>
+        <v>20.7</v>
       </c>
       <c r="C12" s="21">
-        <v>0.4</v>
+        <v>0.46200000000000002</v>
       </c>
       <c r="D12" s="21">
-        <v>5.5E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+        <v>0.14599999999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>286</v>
       </c>
@@ -7175,108 +6585,108 @@
         <v>520</v>
       </c>
       <c r="C13" s="21">
-        <v>0.4</v>
+        <v>0.32700000000000001</v>
       </c>
       <c r="D13" s="21">
-        <v>2.8000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+        <v>3.2000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>287</v>
       </c>
       <c r="B14" s="21">
-        <v>907.6</v>
+        <v>688.5</v>
       </c>
       <c r="C14" s="21">
-        <v>0.40699999999999997</v>
+        <v>0.39500000000000002</v>
       </c>
       <c r="D14" s="21">
-        <v>5.5E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+        <v>0.126</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
         <v>288</v>
       </c>
       <c r="B15" s="21">
-        <v>142.6</v>
+        <v>256</v>
       </c>
       <c r="C15" s="21">
-        <v>0.35199999999999998</v>
+        <v>0.249</v>
       </c>
       <c r="D15" s="21">
-        <v>-7.8E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+        <v>-4.3999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>289</v>
       </c>
       <c r="B16" s="21">
-        <v>1231.8</v>
+        <v>763.7</v>
       </c>
       <c r="C16" s="21">
-        <v>0.55000000000000004</v>
+        <v>0.29799999999999999</v>
       </c>
       <c r="D16" s="21">
-        <v>2.8000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+        <v>4.5999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>290</v>
       </c>
       <c r="B17" s="21">
-        <v>13.4</v>
+        <v>22</v>
       </c>
       <c r="C17" s="21">
-        <v>1</v>
+        <v>1.1879999999999999</v>
       </c>
       <c r="D17" s="21">
-        <v>1.4999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+        <v>0.11700000000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>291</v>
       </c>
       <c r="B18" s="21">
-        <v>13.4</v>
+        <v>23.3</v>
       </c>
       <c r="C18" s="21">
-        <v>1</v>
+        <v>1.1850000000000001</v>
       </c>
       <c r="D18" s="21">
-        <v>1.4999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+        <v>7.2999999999999995E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>293</v>
       </c>
       <c r="B19" s="21">
-        <v>77.8</v>
+        <v>31.3</v>
       </c>
       <c r="C19" s="21">
-        <v>1.05</v>
+        <v>1.2070000000000001</v>
       </c>
       <c r="D19" s="21">
-        <v>1.4999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+        <v>7.6999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>292</v>
       </c>
       <c r="B20" s="21">
-        <v>51.9</v>
+        <v>13.9</v>
       </c>
       <c r="C20" s="21">
-        <v>1.05</v>
+        <v>1.2050000000000001</v>
       </c>
       <c r="D20" s="21">
-        <v>0.15</v>
+        <v>0.188</v>
       </c>
     </row>
   </sheetData>
@@ -7287,26 +6697,26 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{118BE621-EF6B-4648-868E-9937B9C5B685}">
   <dimension ref="A1:F32"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="48.109375" style="2" customWidth="1"/>
-    <col min="2" max="4" width="15.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="3.6640625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="46.6640625" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="8.6640625" style="2"/>
+    <col min="1" max="1" width="48.140625" style="2" customWidth="1"/>
+    <col min="2" max="4" width="15.7109375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="3.7109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="46.7109375" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="8.7109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>208</v>
       </c>
@@ -7320,7 +6730,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>212</v>
       </c>
@@ -7338,7 +6748,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>214</v>
       </c>
@@ -7358,7 +6768,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>216</v>
       </c>
@@ -7378,7 +6788,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>217</v>
       </c>
@@ -7396,7 +6806,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>218</v>
       </c>
@@ -7416,7 +6826,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>220</v>
       </c>
@@ -7433,7 +6843,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>222</v>
       </c>
@@ -7450,7 +6860,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>223</v>
       </c>
@@ -7470,7 +6880,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>225</v>
       </c>
@@ -7487,7 +6897,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>257</v>
       </c>
@@ -7507,7 +6917,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>258</v>
       </c>
@@ -7527,7 +6937,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>227</v>
       </c>
@@ -7535,7 +6945,7 @@
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>228</v>
       </c>
@@ -7552,7 +6962,7 @@
         <v>1.9823131728623846</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>229</v>
       </c>
@@ -7569,7 +6979,7 @@
         <v>1.1592794807274085</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>230</v>
       </c>
@@ -7586,7 +6996,7 @@
         <v>-0.62740704594148844</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>231</v>
       </c>
@@ -7603,7 +7013,7 @@
         <v>-0.96540266006846076</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>232</v>
       </c>
@@ -7611,7 +7021,7 @@
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>233</v>
       </c>
@@ -7628,7 +7038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>234</v>
       </c>
@@ -7645,7 +7055,7 @@
         <v>0.52359877559829882</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>235</v>
       </c>
@@ -7662,7 +7072,7 @@
         <v>-0.50548365077118673</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>236</v>
       </c>
@@ -7679,7 +7089,7 @@
         <v>324.01250000000005</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>237</v>
       </c>
@@ -7696,7 +7106,7 @@
         <v>1.42884E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>238</v>
       </c>
@@ -7713,7 +7123,7 @@
         <v>-0.13760360258695806</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>239</v>
       </c>
@@ -7730,7 +7140,7 @@
         <v>0.13760360258695806</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>240</v>
       </c>
@@ -7747,7 +7157,7 @@
         <v>22.925083964169769</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>241</v>
       </c>
@@ -7755,7 +7165,7 @@
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>242</v>
       </c>
@@ -7763,7 +7173,7 @@
       <c r="C31" s="14"/>
       <c r="D31" s="14"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>243</v>
       </c>
@@ -7786,19 +7196,19 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="C109:F109"/>
-  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="11.5546875" customWidth="true"/>
-    <col min="6" max="6" width="142.44140625" customWidth="true"/>
+    <col min="3" max="3" width="11.5703125" customWidth="1"/>
+    <col min="6" max="6" width="142.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="109" x14ac:dyDescent="0.3">
-      <c r="C109" s="0">
+    <row r="109" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C109">
         <v>11.941543440928031</v>
       </c>
-      <c r="F109" s="0" t="s">
+      <c r="F109" t="s">
         <v>379</v>
       </c>
     </row>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ceaa8977d2236823/Documents/GitHub/451-DBF-Team01/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\Fall 2026\AAE 451\451-DBF-Team01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{37DAE441-3691-47BB-B387-517F08F01369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84407836-4197-495E-8968-99AA3ACC1078}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B82BD59C-93A3-4A69-81EC-79832B9DA956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,8 @@
     <sheet name="Hinge Moments" sheetId="2" r:id="rId4"/>
     <sheet name="Sheet1" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="true"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2192" uniqueCount="526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="485">
   <si>
     <t>Parameter</t>
   </si>
@@ -1254,159 +1255,6 @@
     <t>V_tailUp</t>
   </si>
   <si>
-    <t>groundRoll_x</t>
-  </si>
-  <si>
-    <t>groundRoll_t</t>
-  </si>
-  <si>
-    <t>groundRoll_V_LO</t>
-  </si>
-  <si>
-    <t>groundRoll_ok</t>
-  </si>
-  <si>
-    <t>ROC_max</t>
-  </si>
-  <si>
-    <t>V_ROC_max</t>
-  </si>
-  <si>
-    <t>t_climb</t>
-  </si>
-  <si>
-    <t>V_max_level_A8</t>
-  </si>
-  <si>
-    <t>V_endurance</t>
-  </si>
-  <si>
-    <t>V_range</t>
-  </si>
-  <si>
-    <t>endurance_min</t>
-  </si>
-  <si>
-    <t>range_km</t>
-  </si>
-  <si>
-    <t>n_turn</t>
-  </si>
-  <si>
-    <t>bank_turn_deg</t>
-  </si>
-  <si>
-    <t>turn_ok</t>
-  </si>
-  <si>
-    <t>mission_t</t>
-  </si>
-  <si>
-    <t>mission_E</t>
-  </si>
-  <si>
-    <t>mission_ok_energy</t>
-  </si>
-  <si>
-    <t>mission_ok_power</t>
-  </si>
-  <si>
-    <t>mission_laps_possible</t>
-  </si>
-  <si>
-    <t>mission_E_left</t>
-  </si>
-  <si>
-    <t>mission_battery_mass_left_kg</t>
-  </si>
-  <si>
-    <t>W_pay_max</t>
-  </si>
-  <si>
-    <t>model.CD_trim_fn</t>
-  </si>
-  <si>
-    <t>model.CL_minDrag</t>
-  </si>
-  <si>
-    <t>model.CD_trim_is_parabolic_at_zero</t>
-  </si>
-  <si>
-    <t>model.D_prop</t>
-  </si>
-  <si>
-    <t>model.R_prop</t>
-  </si>
-  <si>
-    <t>model.RPM_lim</t>
-  </si>
-  <si>
-    <t>model.V_grid</t>
-  </si>
-  <si>
-    <t>model.throttle_grid</t>
-  </si>
-  <si>
-    <t>model.T_avail_fn</t>
-  </si>
-  <si>
-    <t>model.Pelec_avail_fn</t>
-  </si>
-  <si>
-    <t>model.I_avail_fn</t>
-  </si>
-  <si>
-    <t>model.throttle_cap_fn</t>
-  </si>
-  <si>
-    <t>model.RPM_avail_fn</t>
-  </si>
-  <si>
-    <t>model.T_grid_fn</t>
-  </si>
-  <si>
-    <t>model.Pelec_grid_fn</t>
-  </si>
-  <si>
-    <t>model.I_grid_fn</t>
-  </si>
-  <si>
-    <t>model.find_throttle_for_thrust</t>
-  </si>
-  <si>
-    <t>model.P_cap</t>
-  </si>
-  <si>
-    <t>model.I_cap</t>
-  </si>
-  <si>
-    <t>model.throttle_bound</t>
-  </si>
-  <si>
-    <t>model.Ct_corr_fn</t>
-  </si>
-  <si>
-    <t>model.labCal.RPM</t>
-  </si>
-  <si>
-    <t>model.labCal.Ct_meas</t>
-  </si>
-  <si>
-    <t>model.labCal.Ct_apc</t>
-  </si>
-  <si>
-    <t>model.labCal.Ct_pctDiff</t>
-  </si>
-  <si>
-    <t>model.labCal.Cp_meas</t>
-  </si>
-  <si>
-    <t>model.labCal.Cp_apc</t>
-  </si>
-  <si>
-    <t>model.labCal.Cp_pctDiff</t>
-  </si>
-  <si>
     <t>wing_M_driving</t>
   </si>
   <si>
@@ -1551,82 +1399,112 @@
     <t>stability</t>
   </si>
   <si>
-    <t>@(CL)local_CD_trim(CL,params)</t>
-  </si>
-  <si>
-    <t>[1x81 double] min 0, max 40</t>
-  </si>
-  <si>
-    <t>[19x1 double] min 0.1, max 1</t>
-  </si>
-  <si>
-    <t>[1x1 griddedInterpolant]</t>
-  </si>
-  <si>
-    <t>@(V,T_req)local_findThrottleForThrust(V,T_req,throttle_grid,T_grid_fn)</t>
-  </si>
-  <si>
-    <t>[1x81 logical]</t>
-  </si>
-  <si>
-    <t>[5186.73 7068.46 9016.72 11006.5]</t>
-  </si>
-  <si>
-    <t>[0.0921493 0.0960023 0.103712 0.108459]</t>
-  </si>
-  <si>
-    <t>[0.120956 0.121521 0.122105 0.122803]</t>
-  </si>
-  <si>
-    <t>[-23.8159 -20.9991 -15.0632 -11.6807]</t>
-  </si>
-  <si>
-    <t>[0.0523414 0.0494839 0.0510573 0.0535032]</t>
-  </si>
-  <si>
-    <t>[0.0514693 0.0504726 0.0498983 0.0498]</t>
-  </si>
-  <si>
-    <t>[1.69451 -1.95884 2.32259 7.43611]</t>
-  </si>
-  <si>
     <t>rolling maneuver (down-going wing)</t>
   </si>
   <si>
     <t>hard landing</t>
   </si>
   <si>
-    <t>Written by writeOutputs.m on 2026-10-06 13:56</t>
-  </si>
-  <si>
     <t>Motor Spec per Jackson</t>
   </si>
   <si>
     <t>CL_ground_attitude</t>
   </si>
   <si>
-    <t>x_climb</t>
-  </si>
-  <si>
-    <t>mission_P_peak</t>
-  </si>
-  <si>
-    <t>Written by writeOutputs.m on 2026-10-06 17:23</t>
-  </si>
-  <si>
-    <t>Written by writeOutputs.m on 2026-10-06 17:29</t>
+    <t>fty_al_6061_t6</t>
+  </si>
+  <si>
+    <t>materials</t>
+  </si>
+  <si>
+    <t>MPa</t>
+  </si>
+  <si>
+    <t>fsu_al_6061_t6</t>
+  </si>
+  <si>
+    <t>fbry_al_6061_t6</t>
+  </si>
+  <si>
+    <t>fa_plywood</t>
+  </si>
+  <si>
+    <t>E_al_6061_t6</t>
+  </si>
+  <si>
+    <t>gear_strut_length</t>
+  </si>
+  <si>
+    <t>gear_strut_thickness</t>
+  </si>
+  <si>
+    <t>gear_strut_width_max</t>
+  </si>
+  <si>
+    <t>gear_strut_width_min</t>
+  </si>
+  <si>
+    <t>gear_strut_angle</t>
+  </si>
+  <si>
+    <t>height_fuselage</t>
+  </si>
+  <si>
+    <t>wall_thick_fuselage</t>
+  </si>
+  <si>
+    <t>width_spar</t>
+  </si>
+  <si>
+    <t>length_spar</t>
+  </si>
+  <si>
+    <t>wall_thick_spar</t>
+  </si>
+  <si>
+    <t>width_tail_boom</t>
+  </si>
+  <si>
+    <t>length_tail_boom</t>
+  </si>
+  <si>
+    <t>wall_thick_tail_boom</t>
+  </si>
+  <si>
+    <t>washer_OD</t>
+  </si>
+  <si>
+    <t>washer_ID</t>
+  </si>
+  <si>
+    <t>MoS_spar_vm</t>
+  </si>
+  <si>
+    <t>MoS_tail_boom_vm</t>
+  </si>
+  <si>
+    <t>MoS_fuselage_bend</t>
+  </si>
+  <si>
+    <t>MoS_fuselage_shear</t>
+  </si>
+  <si>
+    <t>MoS_gear_vm</t>
+  </si>
+  <si>
+    <t>Written by writeOutputs.m on 2026-10-07 01:37</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1683,7 +1561,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1726,6 +1604,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor theme="0" tint="-0.14999847407452621"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1735,57 +1619,84 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border/>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="true"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="true"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="true" applyFill="true"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="true"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="true"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="true"/>
-    <xf numFmtId="166" fontId="5" fillId="3" borderId="0" xfId="1" applyNumberFormat="true" applyFont="true" applyFill="true"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="1" applyNumberFormat="true" applyFont="true" applyFill="true"/>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="0" xfId="1" applyNumberFormat="true" applyFont="true" applyFill="true"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="true"/>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="0" xfId="1" applyNumberFormat="true" applyFont="true" applyFill="true"/>
-    <xf numFmtId="2" fontId="6" fillId="4" borderId="0" xfId="1" applyNumberFormat="true" applyFont="true" applyFill="true"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="1" applyFont="true" applyFill="true"/>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="1" applyNumberFormat="true" applyFill="true"/>
-    <xf numFmtId="166" fontId="5" fillId="5" borderId="0" xfId="1" applyNumberFormat="true" applyFont="true" applyFill="true"/>
-    <xf numFmtId="2" fontId="5" fillId="5" borderId="0" xfId="1" applyNumberFormat="true" applyFont="true" applyFill="true"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="6" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="5" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" justifyLastLine="false" shrinkToFit="false" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" justifyLastLine="false" shrinkToFit="false" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" justifyLastLine="false" shrinkToFit="false" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1801,40 +1712,40 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" id="1" name="Table1" displayName="Table1" ref="A1:F109" totalsRowShown="false">
-  <autoFilter ref="A1:F109"/>
-  <sortState ref="A2:E43">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:F132" totalsRowShown="0">
+  <autoFilter ref="A1:F132" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E43">
     <sortCondition ref="B1:B101"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" name="Parameter"/>
-    <tableColumn id="2" name="Subclass" dataDxfId="2"/>
-    <tableColumn id="3" name="Value" dataDxfId="1"/>
-    <tableColumn id="4" name="Units" dataDxfId="0"/>
-    <tableColumn id="5" name="Description"/>
-    <tableColumn id="6" name="Notes"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Parameter"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Subclass" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Value" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Units" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Description"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Notes"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium15" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
+  <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" id="2" name="Table2" displayName="Table2" ref="A1:F34" totalsRowShown="false">
-  <autoFilter ref="A1:F34"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="A1:F34" totalsRowShown="0">
+  <autoFilter ref="A1:F34" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="Parameter"/>
-    <tableColumn id="2" name="Subclass"/>
-    <tableColumn id="3" name="Value"/>
-    <tableColumn id="4" name="Units"/>
-    <tableColumn id="5" name="Description"/>
-    <tableColumn id="6" name="Source"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Parameter"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Subclass"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Value"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Units"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Description"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Source"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium15" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
+  <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1951,7 +1862,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="true">
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -1975,9 +1886,9 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="false"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="true">
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -2001,7 +1912,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="false"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -2036,7 +1947,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="false">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -2054,7 +1965,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="true">
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -2079,7 +1990,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="false"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -2096,18 +2007,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F109"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F129"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.109375" style="20" customWidth="1"/>
-    <col min="3" max="3" width="13.6640625" style="20" customWidth="1"/>
-    <col min="4" max="4" width="16.88671875" style="20" customWidth="1"/>
-    <col min="5" max="5" width="168.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="142.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" style="20" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" style="20" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" style="20" customWidth="1"/>
+    <col min="5" max="5" width="168.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="142.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2127,7 +2038,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -2144,7 +2055,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -2161,7 +2072,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -2178,7 +2089,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -2195,7 +2106,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -2212,7 +2123,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -2229,7 +2140,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -2246,7 +2157,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>205</v>
       </c>
@@ -2260,7 +2171,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -2277,7 +2188,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -2294,7 +2205,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -2311,7 +2222,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -2328,7 +2239,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -2345,7 +2256,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -2362,7 +2273,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>35</v>
       </c>
@@ -2379,7 +2290,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>37</v>
       </c>
@@ -2396,7 +2307,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>39</v>
       </c>
@@ -2413,7 +2324,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>41</v>
       </c>
@@ -2430,7 +2341,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>45</v>
       </c>
@@ -2447,7 +2358,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -2464,7 +2375,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -2481,7 +2392,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -2498,7 +2409,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -2515,7 +2426,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>58</v>
       </c>
@@ -2532,7 +2443,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>61</v>
       </c>
@@ -2549,7 +2460,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>63</v>
       </c>
@@ -2566,7 +2477,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>65</v>
       </c>
@@ -2583,7 +2494,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -2600,7 +2511,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -2617,7 +2528,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>72</v>
       </c>
@@ -2634,7 +2545,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>74</v>
       </c>
@@ -2651,7 +2562,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>76</v>
       </c>
@@ -2668,7 +2579,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>78</v>
       </c>
@@ -2685,7 +2596,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>80</v>
       </c>
@@ -2702,7 +2613,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>82</v>
       </c>
@@ -2719,7 +2630,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>84</v>
       </c>
@@ -2736,7 +2647,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>86</v>
       </c>
@@ -2753,7 +2664,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>88</v>
       </c>
@@ -2770,7 +2681,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>90</v>
       </c>
@@ -2787,7 +2698,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>92</v>
       </c>
@@ -2804,7 +2715,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>94</v>
       </c>
@@ -2821,7 +2732,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>96</v>
       </c>
@@ -2838,7 +2749,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>98</v>
       </c>
@@ -2855,7 +2766,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>100</v>
       </c>
@@ -2872,7 +2783,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>103</v>
       </c>
@@ -2889,7 +2800,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>105</v>
       </c>
@@ -2906,7 +2817,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>107</v>
       </c>
@@ -2923,7 +2834,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>109</v>
       </c>
@@ -2940,7 +2851,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>111</v>
       </c>
@@ -2957,7 +2868,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>113</v>
       </c>
@@ -2974,7 +2885,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>115</v>
       </c>
@@ -2991,7 +2902,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>117</v>
       </c>
@@ -3008,7 +2919,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>119</v>
       </c>
@@ -3025,7 +2936,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>121</v>
       </c>
@@ -3042,7 +2953,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>123</v>
       </c>
@@ -3059,7 +2970,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>125</v>
       </c>
@@ -3076,7 +2987,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>127</v>
       </c>
@@ -3093,7 +3004,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>129</v>
       </c>
@@ -3110,7 +3021,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>131</v>
       </c>
@@ -3127,7 +3038,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>133</v>
       </c>
@@ -3144,7 +3055,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>135</v>
       </c>
@@ -3161,7 +3072,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>139</v>
       </c>
@@ -3178,7 +3089,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>141</v>
       </c>
@@ -3195,7 +3106,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>143</v>
       </c>
@@ -3212,7 +3123,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>145</v>
       </c>
@@ -3229,7 +3140,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>201</v>
       </c>
@@ -3246,7 +3157,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>146</v>
       </c>
@@ -3263,7 +3174,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>148</v>
       </c>
@@ -3280,7 +3191,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>150</v>
       </c>
@@ -3297,7 +3208,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>152</v>
       </c>
@@ -3314,7 +3225,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>154</v>
       </c>
@@ -3331,7 +3242,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>157</v>
       </c>
@@ -3348,7 +3259,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>160</v>
       </c>
@@ -3365,7 +3276,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>162</v>
       </c>
@@ -3382,7 +3293,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>165</v>
       </c>
@@ -3399,7 +3310,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>167</v>
       </c>
@@ -3416,7 +3327,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>169</v>
       </c>
@@ -3433,7 +3344,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>172</v>
       </c>
@@ -3450,7 +3361,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>174</v>
       </c>
@@ -3467,7 +3378,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>176</v>
       </c>
@@ -3484,7 +3395,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>178</v>
       </c>
@@ -3501,7 +3412,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>180</v>
       </c>
@@ -3518,7 +3429,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>183</v>
       </c>
@@ -3535,7 +3446,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>186</v>
       </c>
@@ -3552,7 +3463,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>189</v>
       </c>
@@ -3569,7 +3480,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>191</v>
       </c>
@@ -3586,7 +3497,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>193</v>
       </c>
@@ -3603,7 +3514,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>196</v>
       </c>
@@ -3620,7 +3531,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>198</v>
       </c>
@@ -3637,7 +3548,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>248</v>
       </c>
@@ -3654,7 +3565,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>251</v>
       </c>
@@ -3671,7 +3582,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>253</v>
       </c>
@@ -3688,7 +3599,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>255</v>
       </c>
@@ -3705,7 +3616,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>261</v>
       </c>
@@ -3722,7 +3633,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>263</v>
       </c>
@@ -3739,7 +3650,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>264</v>
       </c>
@@ -3756,7 +3667,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>266</v>
       </c>
@@ -3773,7 +3684,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>267</v>
       </c>
@@ -3790,7 +3701,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>268</v>
       </c>
@@ -3807,7 +3718,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>269</v>
       </c>
@@ -3824,7 +3735,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>270</v>
       </c>
@@ -3841,7 +3752,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>271</v>
       </c>
@@ -3858,7 +3769,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>272</v>
       </c>
@@ -3875,7 +3786,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>305</v>
       </c>
@@ -3892,7 +3803,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>307</v>
       </c>
@@ -3909,7 +3820,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>308</v>
       </c>
@@ -3923,10 +3834,10 @@
         <v>311</v>
       </c>
       <c r="E107" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>309</v>
       </c>
@@ -3940,10 +3851,10 @@
         <v>184</v>
       </c>
       <c r="E108" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>310</v>
       </c>
@@ -3958,6 +3869,286 @@
       </c>
       <c r="E109" t="s">
         <v>314</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" s="23" t="s">
+        <v>457</v>
+      </c>
+      <c r="B110" s="24" t="s">
+        <v>458</v>
+      </c>
+      <c r="C110" s="24">
+        <v>241</v>
+      </c>
+      <c r="D110" s="24" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" s="25" t="s">
+        <v>460</v>
+      </c>
+      <c r="B111" s="26" t="s">
+        <v>458</v>
+      </c>
+      <c r="C111" s="27">
+        <v>186</v>
+      </c>
+      <c r="D111" s="26" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" s="23" t="s">
+        <v>461</v>
+      </c>
+      <c r="B112" s="24" t="s">
+        <v>458</v>
+      </c>
+      <c r="C112" s="24">
+        <v>338</v>
+      </c>
+      <c r="D112" s="24" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" s="25" t="s">
+        <v>462</v>
+      </c>
+      <c r="B113" s="26" t="s">
+        <v>458</v>
+      </c>
+      <c r="C113" s="26">
+        <v>30</v>
+      </c>
+      <c r="D113" s="26" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114" s="23" t="s">
+        <v>463</v>
+      </c>
+      <c r="B114" s="24" t="s">
+        <v>458</v>
+      </c>
+      <c r="C114" s="28">
+        <v>68900</v>
+      </c>
+      <c r="D114" s="24" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115" s="23" t="s">
+        <v>464</v>
+      </c>
+      <c r="B115" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C115" s="24">
+        <v>0.14799999999999999</v>
+      </c>
+      <c r="D115" s="24" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116" s="25" t="s">
+        <v>465</v>
+      </c>
+      <c r="B116" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C116" s="26">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="D116" s="26" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" s="23" t="s">
+        <v>466</v>
+      </c>
+      <c r="B117" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C117" s="24">
+        <v>0.04</v>
+      </c>
+      <c r="D117" s="24" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118" s="25" t="s">
+        <v>467</v>
+      </c>
+      <c r="B118" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C118" s="26">
+        <v>2.3E-2</v>
+      </c>
+      <c r="D118" s="26" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119" s="23" t="s">
+        <v>468</v>
+      </c>
+      <c r="B119" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C119" s="24">
+        <v>50</v>
+      </c>
+      <c r="D119" s="24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120" s="25" t="s">
+        <v>469</v>
+      </c>
+      <c r="B120" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C120" s="26">
+        <v>0.09</v>
+      </c>
+      <c r="D120" s="26" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121" s="23" t="s">
+        <v>470</v>
+      </c>
+      <c r="B121" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C121" s="24">
+        <v>6.3499999999999997E-3</v>
+      </c>
+      <c r="D121" s="24" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122" s="25" t="s">
+        <v>471</v>
+      </c>
+      <c r="B122" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C122" s="26">
+        <v>1.2699999999999999E-2</v>
+      </c>
+      <c r="D122" s="26" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123" s="23" t="s">
+        <v>472</v>
+      </c>
+      <c r="B123" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C123" s="24">
+        <v>0.76</v>
+      </c>
+      <c r="D123" s="24" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124" s="25" t="s">
+        <v>473</v>
+      </c>
+      <c r="B124" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C124" s="26">
+        <v>1.5874999999999999E-3</v>
+      </c>
+      <c r="D124" s="26" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125" s="23" t="s">
+        <v>474</v>
+      </c>
+      <c r="B125" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C125" s="24">
+        <v>1.2699999999999999E-2</v>
+      </c>
+      <c r="D125" s="24" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126" s="25" t="s">
+        <v>475</v>
+      </c>
+      <c r="B126" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C126" s="26">
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="D126" s="26" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127" s="23" t="s">
+        <v>476</v>
+      </c>
+      <c r="B127" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C127" s="24">
+        <v>1.5874999999999999E-3</v>
+      </c>
+      <c r="D127" s="24" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>477</v>
+      </c>
+      <c r="B128" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="C128" s="20">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="D128" s="20" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>478</v>
+      </c>
+      <c r="B129" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="C129" s="20">
+        <v>4.3E-3</v>
+      </c>
+      <c r="D129" s="20" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -3969,3017 +4160,1763 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:H160"/>
-  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:H112"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="true"/>
-    <col min="2" max="2" width="11.5546875" customWidth="true"/>
-    <col min="3" max="3" width="58.5546875" customWidth="true"/>
-    <col min="4" max="4" width="5.21875" customWidth="true"/>
-    <col min="5" max="5" width="42.77734375" customWidth="true"/>
-    <col min="6" max="6" width="29.21875" customWidth="true"/>
-    <col min="7" max="7" width="9.109375"/>
-    <col min="8" max="8" width="40.109375" customWidth="true"/>
+    <col min="1" max="1" width="40.7109375" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" customWidth="1"/>
+    <col min="3" max="3" width="33.42578125" customWidth="1"/>
+    <col min="4" max="4" width="5.7109375" customWidth="1"/>
+    <col min="5" max="5" width="46" customWidth="1"/>
+    <col min="6" max="6" width="32.42578125" customWidth="1"/>
+    <col min="8" max="8" width="42.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" t="s">
         <v>376</v>
       </c>
-      <c r="G1" s="0"/>
-      <c r="H1" s="0" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="0" t="s">
+      <c r="H1" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>315</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="0">
-        <v>0.29999999999999999</v>
-      </c>
-      <c r="D2" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="0" t="s">
+      <c r="C2">
+        <v>0.3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
         <v>348</v>
       </c>
-      <c r="F2" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G2" s="0"/>
-      <c r="H2" s="0"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="0" t="s">
+      <c r="F2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>316</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="0">
+      <c r="C3">
         <v>1.1818181818181817</v>
       </c>
-      <c r="D3" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="0" t="s">
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s">
         <v>349</v>
       </c>
-      <c r="F3" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G3" s="0"/>
-      <c r="H3" s="0"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="0" t="s">
+      <c r="F3" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>317</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="0">
+      <c r="C4">
         <v>0.92201380973471758</v>
       </c>
-      <c r="D4" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="0" t="s">
+      <c r="D4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
         <v>350</v>
       </c>
-      <c r="F4" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G4" s="0"/>
-      <c r="H4" s="0"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="0" t="s">
+      <c r="F4" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>318</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="0">
-        <v>0.07919652663705147</v>
-      </c>
-      <c r="D5" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="0" t="s">
+      <c r="C5">
+        <v>7.919652663705147E-2</v>
+      </c>
+      <c r="D5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" t="s">
         <v>351</v>
       </c>
-      <c r="F5" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G5" s="0"/>
-      <c r="H5" s="0"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="0" t="s">
+      <c r="F5" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>319</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="0">
+      <c r="C6">
         <v>0.19588300688233271</v>
       </c>
-      <c r="D6" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="0" t="s">
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" t="s">
         <v>352</v>
       </c>
-      <c r="F6" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G6" s="0"/>
-      <c r="H6" s="0"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="0" t="s">
+      <c r="F6" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>320</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="0">
-        <v>0.029817638776781716</v>
-      </c>
-      <c r="D7" s="0"/>
-      <c r="E7" s="0"/>
-      <c r="F7" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G7" s="0"/>
-      <c r="H7" s="0"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="0" t="s">
+      <c r="C7">
+        <v>2.9817638776781716E-2</v>
+      </c>
+      <c r="F7" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>321</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="0">
-        <v>0.036945326174116347</v>
-      </c>
-      <c r="D8" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="0" t="s">
+      <c r="C8">
+        <v>3.6945326174116347E-2</v>
+      </c>
+      <c r="D8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" t="s">
         <v>353</v>
       </c>
-      <c r="F8" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G8" s="0"/>
-      <c r="H8" s="0"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="0" t="s">
+      <c r="F8" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>322</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="0">
-        <v>0.036945326174116347</v>
-      </c>
-      <c r="D9" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="0" t="s">
+      <c r="C9">
+        <v>3.6945326174116347E-2</v>
+      </c>
+      <c r="D9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" t="s">
         <v>354</v>
       </c>
-      <c r="F9" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G9" s="0"/>
-      <c r="H9" s="0"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="0" t="s">
+      <c r="F9" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>323</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="0">
-        <v>0.021945326174116348</v>
-      </c>
-      <c r="D10" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="0" t="s">
+      <c r="C10">
+        <v>2.1945326174116347E-2</v>
+      </c>
+      <c r="D10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" t="s">
         <v>355</v>
       </c>
-      <c r="F10" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G10" s="0"/>
-      <c r="H10" s="0"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="0" t="s">
+      <c r="F10" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>324</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="0">
-        <v>8.1201069544265661</v>
-      </c>
-      <c r="D11" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="0" t="s">
+      <c r="C11">
+        <v>8.120106954426566</v>
+      </c>
+      <c r="D11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" t="s">
         <v>356</v>
       </c>
-      <c r="F11" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G11" s="0"/>
-      <c r="H11" s="0"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="0" t="s">
+      <c r="F11" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>325</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="0">
+      <c r="C12">
         <v>10.289169276665902</v>
       </c>
-      <c r="D12" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="0" t="s">
+      <c r="D12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" t="s">
         <v>357</v>
       </c>
-      <c r="F12" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G12" s="0"/>
-      <c r="H12" s="0"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="0" t="s">
+      <c r="F12" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>380</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="0">
+      <c r="C13">
         <v>3.0198549799930445</v>
       </c>
-      <c r="D13" s="0"/>
-      <c r="E13" s="0"/>
-      <c r="F13" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G13" s="0"/>
-      <c r="H13" s="0"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="0" t="s">
+      <c r="F13" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>381</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="0">
+      <c r="C14">
         <v>4.0327458299223453</v>
       </c>
-      <c r="D14" s="0"/>
-      <c r="E14" s="0"/>
-      <c r="F14" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G14" s="0"/>
-      <c r="H14" s="0"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="0" t="s">
+      <c r="F14" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>382</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="0">
+      <c r="C15">
         <v>0.58894455001488533</v>
       </c>
-      <c r="D15" s="0"/>
-      <c r="E15" s="0"/>
-      <c r="F15" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G15" s="0"/>
-      <c r="H15" s="0"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="0" t="s">
+      <c r="F15" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>383</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="0">
+      <c r="C16">
         <v>5.2740736776131758</v>
       </c>
-      <c r="D16" s="0"/>
-      <c r="E16" s="0"/>
-      <c r="F16" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G16" s="0"/>
-      <c r="H16" s="0"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="0" t="s">
+      <c r="F16" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>384</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="0">
-        <v>-0.094788465253600393</v>
-      </c>
-      <c r="D17" s="0"/>
-      <c r="E17" s="0"/>
-      <c r="F17" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G17" s="0"/>
-      <c r="H17" s="0"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="0" t="s">
+      <c r="C17">
+        <v>-9.4788465253600393E-2</v>
+      </c>
+      <c r="F17" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>385</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="0">
+      <c r="C18">
         <v>0.66074594914354523</v>
       </c>
-      <c r="D18" s="0"/>
-      <c r="E18" s="0"/>
-      <c r="F18" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G18" s="0"/>
-      <c r="H18" s="0"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="0" t="s">
+      <c r="F18" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>386</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="0">
+      <c r="C19">
         <v>0.60899778104422941</v>
       </c>
-      <c r="D19" s="0"/>
-      <c r="E19" s="0"/>
-      <c r="F19" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G19" s="0"/>
-      <c r="H19" s="0"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="0" t="s">
+      <c r="F19" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>387</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="0">
+      <c r="C20">
         <v>1.5753270213496304</v>
       </c>
-      <c r="D20" s="0"/>
-      <c r="E20" s="0"/>
-      <c r="F20" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G20" s="0"/>
-      <c r="H20" s="0"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="0" t="s">
+      <c r="F20" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>388</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="0">
+      <c r="C21">
         <v>0.66074594914354523</v>
       </c>
-      <c r="D21" s="0"/>
-      <c r="E21" s="0"/>
-      <c r="F21" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G21" s="0"/>
-      <c r="H21" s="0"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="0" t="s">
+      <c r="F21" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>389</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="0">
+      <c r="C22">
         <v>0.12602616170797043</v>
       </c>
-      <c r="D22" s="0"/>
-      <c r="E22" s="0"/>
-      <c r="F22" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G22" s="0"/>
-      <c r="H22" s="0"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="0" t="s">
-        <v>521</v>
-      </c>
-      <c r="B23" s="0" t="s">
+      <c r="F22" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>456</v>
+      </c>
+      <c r="B23" t="s">
         <v>7</v>
       </c>
-      <c r="C23" s="0">
+      <c r="C23">
         <v>0.8871601270722228</v>
       </c>
-      <c r="D23" s="0"/>
-      <c r="E23" s="0"/>
-      <c r="F23" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G23" s="0"/>
-      <c r="H23" s="0"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="0" t="s">
+      <c r="F23" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>326</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="0">
+      <c r="C24">
         <v>0.49722452282391244</v>
       </c>
-      <c r="D24" s="0" t="s">
+      <c r="D24" t="s">
         <v>66</v>
       </c>
-      <c r="E24" s="0" t="s">
+      <c r="E24" t="s">
         <v>358</v>
       </c>
-      <c r="F24" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G24" s="0"/>
-      <c r="H24" s="0"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="0" t="s">
+      <c r="F24" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>327</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" t="s">
         <v>56</v>
       </c>
-      <c r="C25" s="0">
+      <c r="C25">
         <v>0.34410001579509508</v>
       </c>
-      <c r="D25" s="0" t="s">
+      <c r="D25" t="s">
         <v>59</v>
       </c>
-      <c r="E25" s="0" t="s">
+      <c r="E25" t="s">
         <v>359</v>
       </c>
-      <c r="F25" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G25" s="0"/>
-      <c r="H25" s="0"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="0" t="s">
+      <c r="F25" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>328</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" t="s">
         <v>56</v>
       </c>
-      <c r="C26" s="0">
+      <c r="C26">
         <v>4.3591977074863637</v>
       </c>
-      <c r="D26" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E26" s="0" t="s">
+      <c r="D26" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" t="s">
         <v>360</v>
       </c>
-      <c r="F26" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G26" s="0"/>
-      <c r="H26" s="0"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="0" t="s">
+      <c r="F26" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>329</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="B27" t="s">
         <v>56</v>
       </c>
-      <c r="C27" s="0">
-        <v>0.084528168880065119</v>
-      </c>
-      <c r="D27" s="0" t="s">
+      <c r="C27">
+        <v>8.4528168880065119E-2</v>
+      </c>
+      <c r="D27" t="s">
         <v>66</v>
       </c>
-      <c r="E27" s="0" t="s">
+      <c r="E27" t="s">
         <v>361</v>
       </c>
-      <c r="F27" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G27" s="0"/>
-      <c r="H27" s="0"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="0" t="s">
+      <c r="F27" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>330</v>
       </c>
-      <c r="B28" s="0" t="s">
+      <c r="B28" t="s">
         <v>56</v>
       </c>
-      <c r="C28" s="0">
+      <c r="C28">
         <v>0.45969601064199239</v>
       </c>
-      <c r="D28" s="0" t="s">
+      <c r="D28" t="s">
         <v>59</v>
       </c>
-      <c r="E28" s="0" t="s">
+      <c r="E28" t="s">
         <v>362</v>
       </c>
-      <c r="F28" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G28" s="0"/>
-      <c r="H28" s="0"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="0" t="s">
+      <c r="F28" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>331</v>
       </c>
-      <c r="B29" s="0" t="s">
+      <c r="B29" t="s">
         <v>56</v>
       </c>
-      <c r="C29" s="0">
+      <c r="C29">
         <v>0.18387840425679697</v>
       </c>
-      <c r="D29" s="0" t="s">
+      <c r="D29" t="s">
         <v>59</v>
       </c>
-      <c r="E29" s="0" t="s">
+      <c r="E29" t="s">
         <v>363</v>
       </c>
-      <c r="F29" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G29" s="0"/>
-      <c r="H29" s="0"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="0" t="s">
+      <c r="F29" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>332</v>
       </c>
-      <c r="B30" s="0" t="s">
+      <c r="B30" t="s">
         <v>56</v>
       </c>
-      <c r="C30" s="0">
+      <c r="C30">
         <v>0.39523392547876368</v>
       </c>
-      <c r="D30" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E30" s="0" t="s">
+      <c r="D30" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" t="s">
         <v>364</v>
       </c>
-      <c r="F30" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G30" s="0"/>
-      <c r="H30" s="0"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="0" t="s">
+      <c r="F30" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>333</v>
       </c>
-      <c r="B31" s="0" t="s">
+      <c r="B31" t="s">
         <v>56</v>
       </c>
-      <c r="C31" s="0">
-        <v>0.074583678423586861</v>
-      </c>
-      <c r="D31" s="0" t="s">
+      <c r="C31">
+        <v>7.4583678423586861E-2</v>
+      </c>
+      <c r="D31" t="s">
         <v>66</v>
       </c>
-      <c r="E31" s="0" t="s">
+      <c r="E31" t="s">
         <v>365</v>
       </c>
-      <c r="F31" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G31" s="0"/>
-      <c r="H31" s="0"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="0" t="s">
+      <c r="F31" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>334</v>
       </c>
-      <c r="B32" s="0" t="s">
+      <c r="B32" t="s">
         <v>56</v>
       </c>
-      <c r="C32" s="0">
-        <v>0.074583678423586861</v>
-      </c>
-      <c r="D32" s="0" t="s">
+      <c r="C32">
+        <v>7.4583678423586861E-2</v>
+      </c>
+      <c r="D32" t="s">
         <v>66</v>
       </c>
-      <c r="E32" s="0" t="s">
+      <c r="E32" t="s">
         <v>366</v>
       </c>
-      <c r="F32" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G32" s="0"/>
-      <c r="H32" s="0"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="0" t="s">
+      <c r="F32" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>335</v>
       </c>
-      <c r="B33" s="0" t="s">
+      <c r="B33" t="s">
         <v>56</v>
       </c>
-      <c r="C33" s="0">
+      <c r="C33">
         <v>0.28249696620183012</v>
       </c>
-      <c r="D33" s="0" t="s">
+      <c r="D33" t="s">
         <v>59</v>
       </c>
-      <c r="E33" s="0" t="s">
+      <c r="E33" t="s">
         <v>367</v>
       </c>
-      <c r="F33" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G33" s="0"/>
-      <c r="H33" s="0"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="0" t="s">
+      <c r="F33" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>336</v>
       </c>
-      <c r="B34" s="0" t="s">
+      <c r="B34" t="s">
         <v>56</v>
       </c>
-      <c r="C34" s="0">
-        <v>0.26401585626339264</v>
-      </c>
-      <c r="D34" s="0" t="s">
+      <c r="C34">
+        <v>0.26401585626339263</v>
+      </c>
+      <c r="D34" t="s">
         <v>59</v>
       </c>
-      <c r="E34" s="0" t="s">
+      <c r="E34" t="s">
         <v>368</v>
       </c>
-      <c r="F34" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G34" s="0"/>
-      <c r="H34" s="0"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="0" t="s">
+      <c r="F34" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>390</v>
       </c>
-      <c r="B35" s="0" t="s">
+      <c r="B35" t="s">
         <v>56</v>
       </c>
-      <c r="C35" s="0">
-        <v>0.018046437163813135</v>
-      </c>
-      <c r="D35" s="0"/>
-      <c r="E35" s="0"/>
-      <c r="F35" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G35" s="0"/>
-      <c r="H35" s="0"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="0" t="s">
+      <c r="C35">
+        <v>1.8046437163813135E-2</v>
+      </c>
+      <c r="F35" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>391</v>
       </c>
-      <c r="B36" s="0" t="s">
+      <c r="B36" t="s">
         <v>56</v>
       </c>
-      <c r="C36" s="0">
+      <c r="C36">
         <v>0.23885083680507355</v>
       </c>
-      <c r="D36" s="0"/>
-      <c r="E36" s="0"/>
-      <c r="F36" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G36" s="0"/>
-      <c r="H36" s="0"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="0" t="s">
+      <c r="F36" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>392</v>
       </c>
-      <c r="B37" s="0" t="s">
+      <c r="B37" t="s">
         <v>56</v>
       </c>
-      <c r="C37" s="0">
+      <c r="C37">
         <v>0.3656082203404642</v>
       </c>
-      <c r="D37" s="0"/>
-      <c r="E37" s="0"/>
-      <c r="F37" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G37" s="0"/>
-      <c r="H37" s="0"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="0" t="s">
+      <c r="F37" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>393</v>
       </c>
-      <c r="B38" s="0" t="s">
+      <c r="B38" t="s">
         <v>56</v>
       </c>
-      <c r="C38" s="0">
+      <c r="C38">
         <v>0.2156082203404642</v>
       </c>
-      <c r="D38" s="0"/>
-      <c r="E38" s="0"/>
-      <c r="F38" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G38" s="0"/>
-      <c r="H38" s="0"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="0" t="s">
+      <c r="F38" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>167</v>
       </c>
-      <c r="B39" s="0" t="s">
+      <c r="B39" t="s">
         <v>136</v>
       </c>
-      <c r="C39" s="0">
+      <c r="C39">
+        <v>4.8141647916350516</v>
+      </c>
+      <c r="F39" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>337</v>
+      </c>
+      <c r="B40" t="s">
+        <v>136</v>
+      </c>
+      <c r="C40">
+        <v>22.737783592977756</v>
+      </c>
+      <c r="D40" t="s">
+        <v>137</v>
+      </c>
+      <c r="E40" t="s">
+        <v>369</v>
+      </c>
+      <c r="F40" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>338</v>
+      </c>
+      <c r="B41" t="s">
+        <v>136</v>
+      </c>
+      <c r="C41">
+        <v>11</v>
+      </c>
+      <c r="D41" t="s">
+        <v>137</v>
+      </c>
+      <c r="E41" t="s">
+        <v>370</v>
+      </c>
+      <c r="F41" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>339</v>
+      </c>
+      <c r="B42" t="s">
+        <v>136</v>
+      </c>
+      <c r="C42">
+        <v>14.810748414335091</v>
+      </c>
+      <c r="D42" t="s">
+        <v>137</v>
+      </c>
+      <c r="E42" t="s">
+        <v>371</v>
+      </c>
+      <c r="F42" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>340</v>
+      </c>
+      <c r="B43" t="s">
+        <v>136</v>
+      </c>
+      <c r="C43">
+        <v>12.24744871391589</v>
+      </c>
+      <c r="D43" t="s">
+        <v>137</v>
+      </c>
+      <c r="E43" t="s">
+        <v>372</v>
+      </c>
+      <c r="F43" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>341</v>
+      </c>
+      <c r="B44" t="s">
+        <v>136</v>
+      </c>
+      <c r="C44">
+        <v>48.189685104221404</v>
+      </c>
+      <c r="D44" t="s">
+        <v>23</v>
+      </c>
+      <c r="E44" t="s">
+        <v>373</v>
+      </c>
+      <c r="F44" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>342</v>
+      </c>
+      <c r="B45" t="s">
+        <v>136</v>
+      </c>
+      <c r="C45">
+        <v>16.699244233993625</v>
+      </c>
+      <c r="D45" t="s">
+        <v>23</v>
+      </c>
+      <c r="E45" t="s">
+        <v>374</v>
+      </c>
+      <c r="F45" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>343</v>
+      </c>
+      <c r="B46" t="s">
+        <v>136</v>
+      </c>
+      <c r="C46">
+        <v>47.226956605939861</v>
+      </c>
+      <c r="D46" t="s">
+        <v>347</v>
+      </c>
+      <c r="E46" t="s">
+        <v>375</v>
+      </c>
+      <c r="F46" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>344</v>
+      </c>
+      <c r="B47" t="s">
+        <v>136</v>
+      </c>
+      <c r="C47">
+        <v>0.44283295832701008</v>
+      </c>
+      <c r="F47" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>345</v>
+      </c>
+      <c r="B48" t="s">
+        <v>136</v>
+      </c>
+      <c r="C48">
+        <v>233372.96903833433</v>
+      </c>
+      <c r="F48" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>346</v>
+      </c>
+      <c r="B49" t="s">
+        <v>136</v>
+      </c>
+      <c r="C49">
+        <v>130688.86266146721</v>
+      </c>
+      <c r="F49" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>394</v>
+      </c>
+      <c r="B50" t="s">
+        <v>136</v>
+      </c>
+      <c r="C50">
+        <v>22.608098531363336</v>
+      </c>
+      <c r="F50" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>395</v>
+      </c>
+      <c r="B51" t="s">
+        <v>136</v>
+      </c>
+      <c r="C51">
+        <v>15.480365443172449</v>
+      </c>
+      <c r="F51" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>396</v>
+      </c>
+      <c r="B52" t="s">
+        <v>136</v>
+      </c>
+      <c r="C52">
+        <v>3.8</v>
+      </c>
+      <c r="F52" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>397</v>
+      </c>
+      <c r="B53" t="s">
+        <v>136</v>
+      </c>
+      <c r="C53">
+        <v>-1.52</v>
+      </c>
+      <c r="F53" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>398</v>
+      </c>
+      <c r="B54" t="s">
+        <v>136</v>
+      </c>
+      <c r="C54">
+        <v>5.6999999999999993</v>
+      </c>
+      <c r="F54" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>399</v>
+      </c>
+      <c r="B55" t="s">
+        <v>136</v>
+      </c>
+      <c r="C55">
+        <v>-2.2800000000000002</v>
+      </c>
+      <c r="F55" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>400</v>
+      </c>
+      <c r="B56" t="s">
+        <v>136</v>
+      </c>
+      <c r="C56">
+        <v>18.622682892532463</v>
+      </c>
+      <c r="F56" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>401</v>
+      </c>
+      <c r="B57" t="s">
+        <v>136</v>
+      </c>
+      <c r="C57">
+        <v>27.131986877647702</v>
+      </c>
+      <c r="F57" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>402</v>
+      </c>
+      <c r="B58" t="s">
+        <v>136</v>
+      </c>
+      <c r="C58">
+        <v>25.580006542099976</v>
+      </c>
+      <c r="F58" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>403</v>
+      </c>
+      <c r="B59" t="s">
+        <v>136</v>
+      </c>
+      <c r="C59">
+        <v>28.422229491222197</v>
+      </c>
+      <c r="F59" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>404</v>
+      </c>
+      <c r="B60" t="s">
+        <v>136</v>
+      </c>
+      <c r="C60">
+        <v>6.3586494759793881</v>
+      </c>
+      <c r="F60" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>405</v>
+      </c>
+      <c r="B61" t="s">
+        <v>265</v>
+      </c>
+      <c r="C61">
+        <v>32.946133306980855</v>
+      </c>
+      <c r="F61" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>406</v>
+      </c>
+      <c r="B62" t="s">
+        <v>265</v>
+      </c>
+      <c r="C62">
+        <v>0</v>
+      </c>
+      <c r="F62" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>407</v>
+      </c>
+      <c r="B63" t="s">
+        <v>265</v>
+      </c>
+      <c r="C63" t="s">
+        <v>453</v>
+      </c>
+      <c r="F63" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>408</v>
+      </c>
+      <c r="B64" t="s">
+        <v>265</v>
+      </c>
+      <c r="C64">
+        <v>86.068285472894019</v>
+      </c>
+      <c r="F64" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>409</v>
+      </c>
+      <c r="B65" t="s">
+        <v>265</v>
+      </c>
+      <c r="C65">
+        <v>0</v>
+      </c>
+      <c r="F65" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>410</v>
+      </c>
+      <c r="B66" t="s">
+        <v>265</v>
+      </c>
+      <c r="C66">
+        <v>-1.8275795392708134</v>
+      </c>
+      <c r="F66" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>411</v>
+      </c>
+      <c r="B67" t="s">
+        <v>265</v>
+      </c>
+      <c r="C67">
+        <v>0</v>
+      </c>
+      <c r="F67" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>412</v>
+      </c>
+      <c r="B68" t="s">
+        <v>265</v>
+      </c>
+      <c r="C68">
+        <v>1.7526473681977495</v>
+      </c>
+      <c r="F68" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>413</v>
+      </c>
+      <c r="B69" t="s">
+        <v>265</v>
+      </c>
+      <c r="C69">
+        <v>0.15168253041257554</v>
+      </c>
+      <c r="F69" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>414</v>
+      </c>
+      <c r="B70" t="s">
+        <v>265</v>
+      </c>
+      <c r="C70">
+        <v>2.4110213483593652</v>
+      </c>
+      <c r="F70" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>415</v>
+      </c>
+      <c r="B71" t="s">
+        <v>265</v>
+      </c>
+      <c r="C71">
+        <v>2.7131092758196531</v>
+      </c>
+      <c r="F71" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>416</v>
+      </c>
+      <c r="B72" t="s">
+        <v>265</v>
+      </c>
+      <c r="C72">
+        <v>16.090147165877724</v>
+      </c>
+      <c r="F72" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>417</v>
+      </c>
+      <c r="B73" t="s">
+        <v>265</v>
+      </c>
+      <c r="C73">
+        <v>16.925292122478595</v>
+      </c>
+      <c r="F73" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>418</v>
+      </c>
+      <c r="B74" t="s">
+        <v>265</v>
+      </c>
+      <c r="C74">
+        <v>0.35178486510320511</v>
+      </c>
+      <c r="F74" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>419</v>
+      </c>
+      <c r="B75" t="s">
+        <v>265</v>
+      </c>
+      <c r="C75" t="s">
+        <v>454</v>
+      </c>
+      <c r="F75" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>420</v>
+      </c>
+      <c r="B76" t="s">
+        <v>265</v>
+      </c>
+      <c r="C76">
+        <v>233.69773788009346</v>
+      </c>
+      <c r="F76" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>421</v>
+      </c>
+      <c r="B77" t="s">
+        <v>265</v>
+      </c>
+      <c r="C77">
+        <v>0.35242563899228196</v>
+      </c>
+      <c r="F77" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>422</v>
+      </c>
+      <c r="B78" t="s">
+        <v>265</v>
+      </c>
+      <c r="C78" t="s">
+        <v>454</v>
+      </c>
+      <c r="F78" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>423</v>
+      </c>
+      <c r="B79" t="s">
+        <v>265</v>
+      </c>
+      <c r="C79">
+        <v>9.4744003772526408</v>
+      </c>
+      <c r="F79" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>424</v>
+      </c>
+      <c r="B80" t="s">
+        <v>265</v>
+      </c>
+      <c r="C80">
+        <v>341.83792795003058</v>
+      </c>
+      <c r="F80" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>425</v>
+      </c>
+      <c r="B81" t="s">
+        <v>265</v>
+      </c>
+      <c r="C81">
+        <v>34.733446426726843</v>
+      </c>
+      <c r="F81" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>426</v>
+      </c>
+      <c r="B82" t="s">
+        <v>265</v>
+      </c>
+      <c r="C82">
+        <v>0.42099254615460552</v>
+      </c>
+      <c r="F82" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>427</v>
+      </c>
+      <c r="B83" t="s">
+        <v>265</v>
+      </c>
+      <c r="C83">
         <v>4.0516000000000005</v>
       </c>
-      <c r="D39" s="0"/>
-      <c r="E39" s="0"/>
-      <c r="F39" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="G39" s="0"/>
-      <c r="H39" s="0"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="0" t="s">
-        <v>337</v>
-      </c>
-      <c r="B40" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C40" s="0">
-        <v>22.737783592977756</v>
-      </c>
-      <c r="D40" s="0" t="s">
-        <v>137</v>
-      </c>
-      <c r="E40" s="0" t="s">
-        <v>369</v>
-      </c>
-      <c r="F40" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G40" s="0"/>
-      <c r="H40" s="0"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="0" t="s">
-        <v>338</v>
-      </c>
-      <c r="B41" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C41" s="0">
-        <v>11</v>
-      </c>
-      <c r="D41" s="0" t="s">
-        <v>137</v>
-      </c>
-      <c r="E41" s="0" t="s">
-        <v>370</v>
-      </c>
-      <c r="F41" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G41" s="0"/>
-      <c r="H41" s="0"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="0" t="s">
-        <v>339</v>
-      </c>
-      <c r="B42" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C42" s="0">
-        <v>14.810748414335091</v>
-      </c>
-      <c r="D42" s="0" t="s">
-        <v>137</v>
-      </c>
-      <c r="E42" s="0" t="s">
-        <v>371</v>
-      </c>
-      <c r="F42" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G42" s="0"/>
-      <c r="H42" s="0"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="0" t="s">
-        <v>340</v>
-      </c>
-      <c r="B43" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C43" s="0">
-        <v>12.24744871391589</v>
-      </c>
-      <c r="D43" s="0" t="s">
-        <v>137</v>
-      </c>
-      <c r="E43" s="0" t="s">
-        <v>372</v>
-      </c>
-      <c r="F43" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G43" s="0"/>
-      <c r="H43" s="0"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="0" t="s">
-        <v>341</v>
-      </c>
-      <c r="B44" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C44" s="0">
-        <v>48.189685104221404</v>
-      </c>
-      <c r="D44" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="E44" s="0" t="s">
-        <v>373</v>
-      </c>
-      <c r="F44" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G44" s="0"/>
-      <c r="H44" s="0"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="0" t="s">
-        <v>342</v>
-      </c>
-      <c r="B45" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C45" s="0">
-        <v>16.699244233993625</v>
-      </c>
-      <c r="D45" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="E45" s="0" t="s">
-        <v>374</v>
-      </c>
-      <c r="F45" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G45" s="0"/>
-      <c r="H45" s="0"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="0" t="s">
-        <v>343</v>
-      </c>
-      <c r="B46" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C46" s="0">
+      <c r="F83" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>428</v>
+      </c>
+      <c r="B84" t="s">
+        <v>265</v>
+      </c>
+      <c r="C84">
         <v>39.746196000000005</v>
       </c>
-      <c r="D46" s="0" t="s">
-        <v>347</v>
-      </c>
-      <c r="E46" s="0" t="s">
-        <v>375</v>
-      </c>
-      <c r="F46" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G46" s="0"/>
-      <c r="H46" s="0"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="0" t="s">
-        <v>344</v>
-      </c>
-      <c r="B47" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C47" s="0">
-        <v>0.44283295832701009</v>
-      </c>
-      <c r="D47" s="0"/>
-      <c r="E47" s="0"/>
-      <c r="F47" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G47" s="0"/>
-      <c r="H47" s="0"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="0" t="s">
-        <v>345</v>
-      </c>
-      <c r="B48" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C48" s="0">
-        <v>233372.96903833433</v>
-      </c>
-      <c r="D48" s="0"/>
-      <c r="E48" s="0"/>
-      <c r="F48" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G48" s="0"/>
-      <c r="H48" s="0"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="0" t="s">
-        <v>346</v>
-      </c>
-      <c r="B49" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C49" s="0">
-        <v>130688.86266146721</v>
-      </c>
-      <c r="D49" s="0"/>
-      <c r="E49" s="0"/>
-      <c r="F49" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G49" s="0"/>
-      <c r="H49" s="0"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="0" t="s">
-        <v>394</v>
-      </c>
-      <c r="B50" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C50" s="0">
-        <v>34.194077618408031</v>
-      </c>
-      <c r="D50" s="0"/>
-      <c r="E50" s="0"/>
-      <c r="F50" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G50" s="0"/>
-      <c r="H50" s="0"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="0" t="s">
-        <v>395</v>
-      </c>
-      <c r="B51" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C51" s="0">
-        <v>15.480365443172449</v>
-      </c>
-      <c r="D51" s="0"/>
-      <c r="E51" s="0"/>
-      <c r="F51" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G51" s="0"/>
-      <c r="H51" s="0"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="0" t="s">
-        <v>396</v>
-      </c>
-      <c r="B52" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C52" s="0">
-        <v>3.7999999999999998</v>
-      </c>
-      <c r="D52" s="0"/>
-      <c r="E52" s="0"/>
-      <c r="F52" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G52" s="0"/>
-      <c r="H52" s="0"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="0" t="s">
-        <v>397</v>
-      </c>
-      <c r="B53" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C53" s="0">
-        <v>-1.52</v>
-      </c>
-      <c r="D53" s="0"/>
-      <c r="E53" s="0"/>
-      <c r="F53" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G53" s="0"/>
-      <c r="H53" s="0"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="0" t="s">
-        <v>398</v>
-      </c>
-      <c r="B54" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C54" s="0">
-        <v>5.6999999999999993</v>
-      </c>
-      <c r="D54" s="0"/>
-      <c r="E54" s="0"/>
-      <c r="F54" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G54" s="0"/>
-      <c r="H54" s="0"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="0" t="s">
-        <v>399</v>
-      </c>
-      <c r="B55" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C55" s="0">
-        <v>-2.2800000000000003</v>
-      </c>
-      <c r="D55" s="0"/>
-      <c r="E55" s="0"/>
-      <c r="F55" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G55" s="0"/>
-      <c r="H55" s="0"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="0" t="s">
-        <v>400</v>
-      </c>
-      <c r="B56" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C56" s="0">
-        <v>18.622682892532463</v>
-      </c>
-      <c r="D56" s="0"/>
-      <c r="E56" s="0"/>
-      <c r="F56" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G56" s="0"/>
-      <c r="H56" s="0"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="0" t="s">
-        <v>401</v>
-      </c>
-      <c r="B57" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C57" s="0">
-        <v>27.131986877647702</v>
-      </c>
-      <c r="D57" s="0"/>
-      <c r="E57" s="0"/>
-      <c r="F57" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G57" s="0"/>
-      <c r="H57" s="0"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="0" t="s">
-        <v>402</v>
-      </c>
-      <c r="B58" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C58" s="0">
-        <v>25.580006542099977</v>
-      </c>
-      <c r="D58" s="0"/>
-      <c r="E58" s="0"/>
-      <c r="F58" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G58" s="0"/>
-      <c r="H58" s="0"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="0" t="s">
-        <v>403</v>
-      </c>
-      <c r="B59" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C59" s="0">
-        <v>28.422229491222197</v>
-      </c>
-      <c r="D59" s="0"/>
-      <c r="E59" s="0"/>
-      <c r="F59" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G59" s="0"/>
-      <c r="H59" s="0"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="0" t="s">
-        <v>404</v>
-      </c>
-      <c r="B60" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C60" s="0">
-        <v>6.3586494759793881</v>
-      </c>
-      <c r="D60" s="0"/>
-      <c r="E60" s="0"/>
-      <c r="F60" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G60" s="0"/>
-      <c r="H60" s="0"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="0" t="s">
-        <v>405</v>
-      </c>
-      <c r="B61" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C61" s="0">
-        <v>11.113261724726186</v>
-      </c>
-      <c r="D61" s="0"/>
-      <c r="E61" s="0"/>
-      <c r="F61" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G61" s="0"/>
-      <c r="H61" s="0"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="0" t="s">
-        <v>406</v>
-      </c>
-      <c r="B62" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C62" s="0">
-        <v>1.9300000000000015</v>
-      </c>
-      <c r="D62" s="0"/>
-      <c r="E62" s="0"/>
-      <c r="F62" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G62" s="0"/>
-      <c r="H62" s="0"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="0" t="s">
-        <v>407</v>
-      </c>
-      <c r="B63" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C63" s="0">
-        <v>11.008581406383897</v>
-      </c>
-      <c r="D63" s="0"/>
-      <c r="E63" s="0"/>
-      <c r="F63" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G63" s="0"/>
-      <c r="H63" s="0"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="0" t="s">
-        <v>408</v>
-      </c>
-      <c r="B64" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C64" s="0" t="b">
+      <c r="F84" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>429</v>
+      </c>
+      <c r="B85" t="s">
+        <v>265</v>
+      </c>
+      <c r="C85">
+        <v>18.230437113682747</v>
+      </c>
+      <c r="F85" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>430</v>
+      </c>
+      <c r="B86" t="s">
+        <v>265</v>
+      </c>
+      <c r="C86">
+        <v>8.0999999999999989E-2</v>
+      </c>
+      <c r="F86" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>431</v>
+      </c>
+      <c r="B87" t="s">
+        <v>265</v>
+      </c>
+      <c r="C87">
+        <v>64.749890848167752</v>
+      </c>
+      <c r="F87" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>479</v>
+      </c>
+      <c r="B88" t="s">
+        <v>265</v>
+      </c>
+      <c r="C88">
+        <v>0.13624047155608898</v>
+      </c>
+      <c r="F88" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>480</v>
+      </c>
+      <c r="B89" t="s">
+        <v>265</v>
+      </c>
+      <c r="C89">
+        <v>1.2959289314238291</v>
+      </c>
+      <c r="F89" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>481</v>
+      </c>
+      <c r="B90" t="s">
+        <v>265</v>
+      </c>
+      <c r="C90">
+        <v>43.98430265528372</v>
+      </c>
+      <c r="F90" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>482</v>
+      </c>
+      <c r="B91" t="s">
+        <v>265</v>
+      </c>
+      <c r="C91">
+        <v>72.401108111255283</v>
+      </c>
+      <c r="F91" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>483</v>
+      </c>
+      <c r="B92" t="s">
+        <v>265</v>
+      </c>
+      <c r="C92">
+        <v>5.8894690270286931E-2</v>
+      </c>
+      <c r="F92" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>432</v>
+      </c>
+      <c r="B93" t="s">
+        <v>452</v>
+      </c>
+      <c r="C93">
+        <v>0.3</v>
+      </c>
+      <c r="F93" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>433</v>
+      </c>
+      <c r="B94" t="s">
+        <v>452</v>
+      </c>
+      <c r="C94">
+        <v>26.360381758366742</v>
+      </c>
+      <c r="F94" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>434</v>
+      </c>
+      <c r="B95" t="s">
+        <v>452</v>
+      </c>
+      <c r="C95">
+        <v>3.6396182416332579</v>
+      </c>
+      <c r="F95" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>435</v>
+      </c>
+      <c r="B96" t="s">
+        <v>452</v>
+      </c>
+      <c r="C96">
+        <v>0.25</v>
+      </c>
+      <c r="F96" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>436</v>
+      </c>
+      <c r="B97" t="s">
+        <v>452</v>
+      </c>
+      <c r="C97">
+        <v>0.7</v>
+      </c>
+      <c r="F97" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>437</v>
+      </c>
+      <c r="B98" t="s">
+        <v>452</v>
+      </c>
+      <c r="C98">
         <v>1</v>
       </c>
-      <c r="D64" s="0"/>
-      <c r="E64" s="0"/>
-      <c r="F64" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G64" s="0"/>
-      <c r="H64" s="0"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="0" t="s">
-        <v>409</v>
-      </c>
-      <c r="B65" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C65" s="0">
-        <v>7.4507370536077033</v>
-      </c>
-      <c r="D65" s="0"/>
-      <c r="E65" s="0"/>
-      <c r="F65" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G65" s="0"/>
-      <c r="H65" s="0"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="0" t="s">
-        <v>410</v>
-      </c>
-      <c r="B66" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C66" s="0">
-        <v>20.550728554427437</v>
-      </c>
-      <c r="D66" s="0"/>
-      <c r="E66" s="0"/>
-      <c r="F66" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G66" s="0"/>
-      <c r="H66" s="0"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="0" t="s">
-        <v>411</v>
-      </c>
-      <c r="B67" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C67" s="0">
-        <v>4.0264472875839541</v>
-      </c>
-      <c r="D67" s="0"/>
-      <c r="E67" s="0"/>
-      <c r="F67" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G67" s="0"/>
-      <c r="H67" s="0"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="0" t="s">
-        <v>522</v>
-      </c>
-      <c r="B68" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C68" s="0">
-        <v>77.116605805538328</v>
-      </c>
-      <c r="D68" s="0"/>
-      <c r="E68" s="0"/>
-      <c r="F68" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G68" s="0"/>
-      <c r="H68" s="0"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="0" t="s">
-        <v>412</v>
-      </c>
-      <c r="B69" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C69" s="0">
-        <v>22.608098531363336</v>
-      </c>
-      <c r="D69" s="0"/>
-      <c r="E69" s="0"/>
-      <c r="F69" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G69" s="0"/>
-      <c r="H69" s="0"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="0" t="s">
-        <v>413</v>
-      </c>
-      <c r="B70" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C70" s="0">
-        <v>12.709922788411269</v>
-      </c>
-      <c r="D70" s="0"/>
-      <c r="E70" s="0"/>
-      <c r="F70" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G70" s="0"/>
-      <c r="H70" s="0"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="0" t="s">
-        <v>414</v>
-      </c>
-      <c r="B71" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C71" s="0">
-        <v>16.27392540932771</v>
-      </c>
-      <c r="D71" s="0"/>
-      <c r="E71" s="0"/>
-      <c r="F71" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G71" s="0"/>
-      <c r="H71" s="0"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="0" t="s">
-        <v>415</v>
-      </c>
-      <c r="B72" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C72" s="0">
-        <v>15.956485750905872</v>
-      </c>
-      <c r="D72" s="0"/>
-      <c r="E72" s="0"/>
-      <c r="F72" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G72" s="0"/>
-      <c r="H72" s="0"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="0" t="s">
-        <v>416</v>
-      </c>
-      <c r="B73" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C73" s="0">
-        <v>13.695854805920606</v>
-      </c>
-      <c r="D73" s="0"/>
-      <c r="E73" s="0"/>
-      <c r="F73" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G73" s="0"/>
-      <c r="H73" s="0"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="0" t="s">
-        <v>417</v>
-      </c>
-      <c r="B74" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C74" s="0">
-        <v>1.0954451150103324</v>
-      </c>
-      <c r="D74" s="0"/>
-      <c r="E74" s="0"/>
-      <c r="F74" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G74" s="0"/>
-      <c r="H74" s="0"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="0" t="s">
-        <v>418</v>
-      </c>
-      <c r="B75" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C75" s="0">
-        <v>24.094842552110709</v>
-      </c>
-      <c r="D75" s="0"/>
-      <c r="E75" s="0"/>
-      <c r="F75" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G75" s="0"/>
-      <c r="H75" s="0"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="0" t="s">
-        <v>419</v>
-      </c>
-      <c r="B76" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C76" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="D76" s="0"/>
-      <c r="E76" s="0"/>
-      <c r="F76" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G76" s="0"/>
-      <c r="H76" s="0"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="0" t="s">
-        <v>420</v>
-      </c>
-      <c r="B77" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C77" s="0">
-        <v>150.69320484179264</v>
-      </c>
-      <c r="D77" s="0"/>
-      <c r="E77" s="0"/>
-      <c r="F77" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G77" s="0"/>
-      <c r="H77" s="0"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="0" t="s">
-        <v>421</v>
-      </c>
-      <c r="B78" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C78" s="0">
-        <v>46195.337793815328</v>
-      </c>
-      <c r="D78" s="0"/>
-      <c r="E78" s="0"/>
-      <c r="F78" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G78" s="0"/>
-      <c r="H78" s="0"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="0" t="s">
-        <v>422</v>
-      </c>
-      <c r="B79" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C79" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="D79" s="0"/>
-      <c r="E79" s="0"/>
-      <c r="F79" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G79" s="0"/>
-      <c r="H79" s="0"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="0" t="s">
-        <v>423</v>
-      </c>
-      <c r="B80" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C80" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="D80" s="0"/>
-      <c r="E80" s="0"/>
-      <c r="F80" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G80" s="0"/>
-      <c r="H80" s="0"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="0" t="s">
-        <v>523</v>
-      </c>
-      <c r="B81" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C81" s="0">
-        <v>890</v>
-      </c>
-      <c r="D81" s="0"/>
-      <c r="E81" s="0"/>
-      <c r="F81" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G81" s="0"/>
-      <c r="H81" s="0"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="0" t="s">
-        <v>424</v>
-      </c>
-      <c r="B82" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C82" s="0">
-        <v>13</v>
-      </c>
-      <c r="D82" s="0"/>
-      <c r="E82" s="0"/>
-      <c r="F82" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G82" s="0"/>
-      <c r="H82" s="0"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="0" t="s">
-        <v>425</v>
-      </c>
-      <c r="B83" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C83" s="0">
-        <v>84493.524867651882</v>
-      </c>
-      <c r="D83" s="0"/>
-      <c r="E83" s="0"/>
-      <c r="F83" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G83" s="0"/>
-      <c r="H83" s="0"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="0" t="s">
-        <v>426</v>
-      </c>
-      <c r="B84" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C84" s="0">
-        <v>0.16032926919858043</v>
-      </c>
-      <c r="D84" s="0"/>
-      <c r="E84" s="0"/>
-      <c r="F84" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G84" s="0"/>
-      <c r="H84" s="0"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="0" t="s">
-        <v>427</v>
-      </c>
-      <c r="B85" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C85" s="0">
-        <v>2.4683999999999995</v>
-      </c>
-      <c r="D85" s="0"/>
-      <c r="E85" s="0"/>
-      <c r="F85" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G85" s="0"/>
-      <c r="H85" s="0"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="0" t="s">
-        <v>428</v>
-      </c>
-      <c r="B86" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C86" s="0" t="s">
-        <v>504</v>
-      </c>
-      <c r="D86" s="0"/>
-      <c r="E86" s="0"/>
-      <c r="F86" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G86" s="0"/>
-      <c r="H86" s="0"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="0" t="s">
-        <v>429</v>
-      </c>
-      <c r="B87" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C87" s="0">
-        <v>-0.040973254512723323</v>
-      </c>
-      <c r="D87" s="0"/>
-      <c r="E87" s="0"/>
-      <c r="F87" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G87" s="0"/>
-      <c r="H87" s="0"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="0" t="s">
-        <v>430</v>
-      </c>
-      <c r="B88" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C88" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="D88" s="0"/>
-      <c r="E88" s="0"/>
-      <c r="F88" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G88" s="0"/>
-      <c r="H88" s="0"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="0" t="s">
-        <v>431</v>
-      </c>
-      <c r="B89" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C89" s="0">
-        <v>0.254</v>
-      </c>
-      <c r="D89" s="0"/>
-      <c r="E89" s="0"/>
-      <c r="F89" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G89" s="0"/>
-      <c r="H89" s="0"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="0" t="s">
-        <v>432</v>
-      </c>
-      <c r="B90" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C90" s="0">
-        <v>0.127</v>
-      </c>
-      <c r="D90" s="0"/>
-      <c r="E90" s="0"/>
-      <c r="F90" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G90" s="0"/>
-      <c r="H90" s="0"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="0" t="s">
-        <v>433</v>
-      </c>
-      <c r="B91" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C91" s="0">
-        <v>14500</v>
-      </c>
-      <c r="D91" s="0"/>
-      <c r="E91" s="0"/>
-      <c r="F91" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G91" s="0"/>
-      <c r="H91" s="0"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="0" t="s">
-        <v>434</v>
-      </c>
-      <c r="B92" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C92" s="0" t="s">
-        <v>505</v>
-      </c>
-      <c r="D92" s="0"/>
-      <c r="E92" s="0"/>
-      <c r="F92" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G92" s="0"/>
-      <c r="H92" s="0"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="0" t="s">
-        <v>435</v>
-      </c>
-      <c r="B93" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C93" s="0" t="s">
-        <v>506</v>
-      </c>
-      <c r="D93" s="0"/>
-      <c r="E93" s="0"/>
-      <c r="F93" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G93" s="0"/>
-      <c r="H93" s="0"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="0" t="s">
-        <v>436</v>
-      </c>
-      <c r="B94" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C94" s="0" t="s">
-        <v>507</v>
-      </c>
-      <c r="D94" s="0"/>
-      <c r="E94" s="0"/>
-      <c r="F94" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G94" s="0"/>
-      <c r="H94" s="0"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="0" t="s">
-        <v>437</v>
-      </c>
-      <c r="B95" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C95" s="0" t="s">
-        <v>507</v>
-      </c>
-      <c r="D95" s="0"/>
-      <c r="E95" s="0"/>
-      <c r="F95" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G95" s="0"/>
-      <c r="H95" s="0"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="0" t="s">
+      <c r="F98" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
         <v>438</v>
       </c>
-      <c r="B96" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C96" s="0" t="s">
-        <v>507</v>
-      </c>
-      <c r="D96" s="0"/>
-      <c r="E96" s="0"/>
-      <c r="F96" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G96" s="0"/>
-      <c r="H96" s="0"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="0" t="s">
+      <c r="B99" t="s">
+        <v>452</v>
+      </c>
+      <c r="C99">
+        <v>0.12048857500544551</v>
+      </c>
+      <c r="F99" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
         <v>439</v>
       </c>
-      <c r="B97" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C97" s="0" t="s">
-        <v>507</v>
-      </c>
-      <c r="D97" s="0"/>
-      <c r="E97" s="0"/>
-      <c r="F97" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G97" s="0"/>
-      <c r="H97" s="0"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="0" t="s">
+      <c r="B100" t="s">
+        <v>452</v>
+      </c>
+      <c r="C100">
+        <v>119.66043834086311</v>
+      </c>
+      <c r="F100" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
         <v>440</v>
       </c>
-      <c r="B98" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C98" s="0" t="s">
-        <v>507</v>
-      </c>
-      <c r="D98" s="0"/>
-      <c r="E98" s="0"/>
-      <c r="F98" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G98" s="0"/>
-      <c r="H98" s="0"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="0" t="s">
+      <c r="B101" t="s">
+        <v>452</v>
+      </c>
+      <c r="C101">
+        <v>7.4583678423586861E-2</v>
+      </c>
+      <c r="F101" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
         <v>441</v>
       </c>
-      <c r="B99" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C99" s="0" t="s">
-        <v>507</v>
-      </c>
-      <c r="D99" s="0"/>
-      <c r="E99" s="0"/>
-      <c r="F99" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G99" s="0"/>
-      <c r="H99" s="0"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="0" t="s">
+      <c r="B102" t="s">
+        <v>452</v>
+      </c>
+      <c r="C102">
+        <v>1.07</v>
+      </c>
+      <c r="F102" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
         <v>442</v>
       </c>
-      <c r="B100" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C100" s="0" t="s">
-        <v>507</v>
-      </c>
-      <c r="D100" s="0"/>
-      <c r="E100" s="0"/>
-      <c r="F100" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G100" s="0"/>
-      <c r="H100" s="0"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="0" t="s">
+      <c r="B103" t="s">
+        <v>452</v>
+      </c>
+      <c r="C103">
+        <v>0.3</v>
+      </c>
+      <c r="F103" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
         <v>443</v>
       </c>
-      <c r="B101" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C101" s="0" t="s">
-        <v>507</v>
-      </c>
-      <c r="D101" s="0"/>
-      <c r="E101" s="0"/>
-      <c r="F101" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G101" s="0"/>
-      <c r="H101" s="0"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="0" t="s">
+      <c r="B104" t="s">
+        <v>452</v>
+      </c>
+      <c r="C104">
+        <v>29.162154556467332</v>
+      </c>
+      <c r="F104" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
         <v>444</v>
       </c>
-      <c r="B102" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C102" s="0" t="s">
-        <v>508</v>
-      </c>
-      <c r="D102" s="0"/>
-      <c r="E102" s="0"/>
-      <c r="F102" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G102" s="0"/>
-      <c r="H102" s="0"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="0" t="s">
+      <c r="B105" t="s">
+        <v>452</v>
+      </c>
+      <c r="C105">
+        <v>0.83784544353266455</v>
+      </c>
+      <c r="F105" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
         <v>445</v>
       </c>
-      <c r="B103" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C103" s="0">
-        <v>890</v>
-      </c>
-      <c r="D103" s="0"/>
-      <c r="E103" s="0"/>
-      <c r="F103" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G103" s="0"/>
-      <c r="H103" s="0"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="0" t="s">
+      <c r="B106" t="s">
+        <v>452</v>
+      </c>
+      <c r="C106">
+        <v>5.2740736776131758</v>
+      </c>
+      <c r="F106" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
         <v>446</v>
       </c>
-      <c r="B104" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C104" s="0">
-        <v>60</v>
-      </c>
-      <c r="D104" s="0"/>
-      <c r="E104" s="0"/>
-      <c r="F104" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G104" s="0"/>
-      <c r="H104" s="0"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="0" t="s">
+      <c r="B107" t="s">
+        <v>452</v>
+      </c>
+      <c r="C107">
+        <v>0.3656082203404642</v>
+      </c>
+      <c r="F107" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
         <v>447</v>
       </c>
-      <c r="B105" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C105" s="0" t="s">
-        <v>509</v>
-      </c>
-      <c r="D105" s="0"/>
-      <c r="E105" s="0"/>
-      <c r="F105" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G105" s="0"/>
-      <c r="H105" s="0"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="0" t="s">
+      <c r="B108" t="s">
+        <v>452</v>
+      </c>
+      <c r="C108">
+        <v>0.15</v>
+      </c>
+      <c r="F108" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
         <v>448</v>
       </c>
-      <c r="B106" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C106" s="0" t="s">
-        <v>507</v>
-      </c>
-      <c r="D106" s="0"/>
-      <c r="E106" s="0"/>
-      <c r="F106" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G106" s="0"/>
-      <c r="H106" s="0"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="0" t="s">
+      <c r="B109" t="s">
+        <v>452</v>
+      </c>
+      <c r="C109">
+        <v>-0.79111105164197637</v>
+      </c>
+      <c r="F109" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
         <v>449</v>
       </c>
-      <c r="B107" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C107" s="0" t="s">
-        <v>510</v>
-      </c>
-      <c r="D107" s="0"/>
-      <c r="E107" s="0"/>
-      <c r="F107" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G107" s="0"/>
-      <c r="H107" s="0"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="0" t="s">
+      <c r="B110" t="s">
+        <v>452</v>
+      </c>
+      <c r="C110">
+        <v>0.12602616170797043</v>
+      </c>
+      <c r="F110" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
         <v>450</v>
       </c>
-      <c r="B108" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C108" s="0" t="s">
-        <v>511</v>
-      </c>
-      <c r="D108" s="0"/>
-      <c r="E108" s="0"/>
-      <c r="F108" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G108" s="0"/>
-      <c r="H108" s="0"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="0" t="s">
+      <c r="B111" t="s">
+        <v>452</v>
+      </c>
+      <c r="C111">
+        <v>5</v>
+      </c>
+      <c r="F111" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
         <v>451</v>
       </c>
-      <c r="B109" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C109" s="0" t="s">
-        <v>512</v>
-      </c>
-      <c r="D109" s="0"/>
-      <c r="E109" s="0"/>
-      <c r="F109" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G109" s="0"/>
-      <c r="H109" s="0"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="0" t="s">
+      <c r="B112" t="s">
         <v>452</v>
       </c>
-      <c r="B110" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C110" s="0" t="s">
-        <v>513</v>
-      </c>
-      <c r="D110" s="0"/>
-      <c r="E110" s="0"/>
-      <c r="F110" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G110" s="0"/>
-      <c r="H110" s="0"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="0" t="s">
-        <v>453</v>
-      </c>
-      <c r="B111" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C111" s="0" t="s">
-        <v>514</v>
-      </c>
-      <c r="D111" s="0"/>
-      <c r="E111" s="0"/>
-      <c r="F111" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G111" s="0"/>
-      <c r="H111" s="0"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="0" t="s">
-        <v>454</v>
-      </c>
-      <c r="B112" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C112" s="0" t="s">
-        <v>515</v>
-      </c>
-      <c r="D112" s="0"/>
-      <c r="E112" s="0"/>
-      <c r="F112" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G112" s="0"/>
-      <c r="H112" s="0"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="0" t="s">
-        <v>455</v>
-      </c>
-      <c r="B113" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C113" s="0" t="s">
-        <v>516</v>
-      </c>
-      <c r="D113" s="0"/>
-      <c r="E113" s="0"/>
-      <c r="F113" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G113" s="0"/>
-      <c r="H113" s="0"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="0" t="s">
-        <v>456</v>
-      </c>
-      <c r="B114" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C114" s="0">
-        <v>32.946133306980855</v>
-      </c>
-      <c r="D114" s="0"/>
-      <c r="E114" s="0"/>
-      <c r="F114" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G114" s="0"/>
-      <c r="H114" s="0"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="0" t="s">
-        <v>457</v>
-      </c>
-      <c r="B115" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C115" s="0">
-        <v>0</v>
-      </c>
-      <c r="D115" s="0"/>
-      <c r="E115" s="0"/>
-      <c r="F115" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G115" s="0"/>
-      <c r="H115" s="0"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="0" t="s">
-        <v>458</v>
-      </c>
-      <c r="B116" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C116" s="0" t="s">
-        <v>517</v>
-      </c>
-      <c r="D116" s="0"/>
-      <c r="E116" s="0"/>
-      <c r="F116" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G116" s="0"/>
-      <c r="H116" s="0"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="0" t="s">
-        <v>459</v>
-      </c>
-      <c r="B117" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C117" s="0">
-        <v>86.068285472894019</v>
-      </c>
-      <c r="D117" s="0"/>
-      <c r="E117" s="0"/>
-      <c r="F117" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G117" s="0"/>
-      <c r="H117" s="0"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="0" t="s">
-        <v>460</v>
-      </c>
-      <c r="B118" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C118" s="0">
-        <v>0</v>
-      </c>
-      <c r="D118" s="0"/>
-      <c r="E118" s="0"/>
-      <c r="F118" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G118" s="0"/>
-      <c r="H118" s="0"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="0" t="s">
-        <v>461</v>
-      </c>
-      <c r="B119" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C119" s="0">
-        <v>-1.8275795392708134</v>
-      </c>
-      <c r="D119" s="0"/>
-      <c r="E119" s="0"/>
-      <c r="F119" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G119" s="0"/>
-      <c r="H119" s="0"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="0" t="s">
-        <v>462</v>
-      </c>
-      <c r="B120" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C120" s="0">
-        <v>0</v>
-      </c>
-      <c r="D120" s="0"/>
-      <c r="E120" s="0"/>
-      <c r="F120" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G120" s="0"/>
-      <c r="H120" s="0"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="0" t="s">
-        <v>463</v>
-      </c>
-      <c r="B121" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C121" s="0">
-        <v>1.7526473681977495</v>
-      </c>
-      <c r="D121" s="0"/>
-      <c r="E121" s="0"/>
-      <c r="F121" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G121" s="0"/>
-      <c r="H121" s="0"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="0" t="s">
-        <v>464</v>
-      </c>
-      <c r="B122" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C122" s="0">
-        <v>0.15168253041257554</v>
-      </c>
-      <c r="D122" s="0"/>
-      <c r="E122" s="0"/>
-      <c r="F122" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G122" s="0"/>
-      <c r="H122" s="0"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="0" t="s">
-        <v>465</v>
-      </c>
-      <c r="B123" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C123" s="0">
-        <v>2.4110213483593652</v>
-      </c>
-      <c r="D123" s="0"/>
-      <c r="E123" s="0"/>
-      <c r="F123" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G123" s="0"/>
-      <c r="H123" s="0"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="0" t="s">
-        <v>466</v>
-      </c>
-      <c r="B124" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C124" s="0">
-        <v>2.7131092758196531</v>
-      </c>
-      <c r="D124" s="0"/>
-      <c r="E124" s="0"/>
-      <c r="F124" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G124" s="0"/>
-      <c r="H124" s="0"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="0" t="s">
-        <v>467</v>
-      </c>
-      <c r="B125" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C125" s="0">
-        <v>16.090147165877724</v>
-      </c>
-      <c r="D125" s="0"/>
-      <c r="E125" s="0"/>
-      <c r="F125" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G125" s="0"/>
-      <c r="H125" s="0"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="0" t="s">
-        <v>468</v>
-      </c>
-      <c r="B126" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C126" s="0">
-        <v>16.925292122478595</v>
-      </c>
-      <c r="D126" s="0"/>
-      <c r="E126" s="0"/>
-      <c r="F126" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G126" s="0"/>
-      <c r="H126" s="0"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="0" t="s">
-        <v>469</v>
-      </c>
-      <c r="B127" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C127" s="0">
-        <v>0.35178486510320511</v>
-      </c>
-      <c r="D127" s="0"/>
-      <c r="E127" s="0"/>
-      <c r="F127" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G127" s="0"/>
-      <c r="H127" s="0"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="0" t="s">
-        <v>470</v>
-      </c>
-      <c r="B128" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C128" s="0" t="s">
-        <v>518</v>
-      </c>
-      <c r="D128" s="0"/>
-      <c r="E128" s="0"/>
-      <c r="F128" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G128" s="0"/>
-      <c r="H128" s="0"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="0" t="s">
-        <v>471</v>
-      </c>
-      <c r="B129" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C129" s="0">
-        <v>233.69773788009346</v>
-      </c>
-      <c r="D129" s="0"/>
-      <c r="E129" s="0"/>
-      <c r="F129" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G129" s="0"/>
-      <c r="H129" s="0"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="0" t="s">
-        <v>472</v>
-      </c>
-      <c r="B130" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C130" s="0">
-        <v>0.35242563899228197</v>
-      </c>
-      <c r="D130" s="0"/>
-      <c r="E130" s="0"/>
-      <c r="F130" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G130" s="0"/>
-      <c r="H130" s="0"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="0" t="s">
-        <v>473</v>
-      </c>
-      <c r="B131" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C131" s="0" t="s">
-        <v>518</v>
-      </c>
-      <c r="D131" s="0"/>
-      <c r="E131" s="0"/>
-      <c r="F131" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G131" s="0"/>
-      <c r="H131" s="0"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="0" t="s">
-        <v>474</v>
-      </c>
-      <c r="B132" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C132" s="0">
-        <v>9.4744003772526408</v>
-      </c>
-      <c r="D132" s="0"/>
-      <c r="E132" s="0"/>
-      <c r="F132" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G132" s="0"/>
-      <c r="H132" s="0"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="0" t="s">
-        <v>475</v>
-      </c>
-      <c r="B133" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C133" s="0">
-        <v>341.83792795003058</v>
-      </c>
-      <c r="D133" s="0"/>
-      <c r="E133" s="0"/>
-      <c r="F133" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G133" s="0"/>
-      <c r="H133" s="0"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="0" t="s">
-        <v>476</v>
-      </c>
-      <c r="B134" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C134" s="0">
-        <v>34.733446426726843</v>
-      </c>
-      <c r="D134" s="0"/>
-      <c r="E134" s="0"/>
-      <c r="F134" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G134" s="0"/>
-      <c r="H134" s="0"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="0" t="s">
-        <v>477</v>
-      </c>
-      <c r="B135" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C135" s="0">
-        <v>0.42099254615460552</v>
-      </c>
-      <c r="D135" s="0"/>
-      <c r="E135" s="0"/>
-      <c r="F135" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G135" s="0"/>
-      <c r="H135" s="0"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="0" t="s">
-        <v>478</v>
-      </c>
-      <c r="B136" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C136" s="0">
-        <v>4.0516000000000005</v>
-      </c>
-      <c r="D136" s="0"/>
-      <c r="E136" s="0"/>
-      <c r="F136" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G136" s="0"/>
-      <c r="H136" s="0"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="0" t="s">
-        <v>479</v>
-      </c>
-      <c r="B137" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C137" s="0">
-        <v>39.746196000000005</v>
-      </c>
-      <c r="D137" s="0"/>
-      <c r="E137" s="0"/>
-      <c r="F137" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G137" s="0"/>
-      <c r="H137" s="0"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="0" t="s">
-        <v>480</v>
-      </c>
-      <c r="B138" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C138" s="0">
-        <v>18.230437113682747</v>
-      </c>
-      <c r="D138" s="0"/>
-      <c r="E138" s="0"/>
-      <c r="F138" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G138" s="0"/>
-      <c r="H138" s="0"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="0" t="s">
-        <v>481</v>
-      </c>
-      <c r="B139" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C139" s="0">
-        <v>0.080999999999999989</v>
-      </c>
-      <c r="D139" s="0"/>
-      <c r="E139" s="0"/>
-      <c r="F139" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G139" s="0"/>
-      <c r="H139" s="0"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="0" t="s">
-        <v>482</v>
-      </c>
-      <c r="B140" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="C140" s="0">
-        <v>64.749890848167752</v>
-      </c>
-      <c r="D140" s="0"/>
-      <c r="E140" s="0"/>
-      <c r="F140" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G140" s="0"/>
-      <c r="H140" s="0"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="0" t="s">
-        <v>483</v>
-      </c>
-      <c r="B141" s="0" t="s">
-        <v>503</v>
-      </c>
-      <c r="C141" s="0">
-        <v>0.29999999999999999</v>
-      </c>
-      <c r="D141" s="0"/>
-      <c r="E141" s="0"/>
-      <c r="F141" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G141" s="0"/>
-      <c r="H141" s="0"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="0" t="s">
-        <v>484</v>
-      </c>
-      <c r="B142" s="0" t="s">
-        <v>503</v>
-      </c>
-      <c r="C142" s="0">
-        <v>26.360381758366742</v>
-      </c>
-      <c r="D142" s="0"/>
-      <c r="E142" s="0"/>
-      <c r="F142" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G142" s="0"/>
-      <c r="H142" s="0"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="0" t="s">
-        <v>485</v>
-      </c>
-      <c r="B143" s="0" t="s">
-        <v>503</v>
-      </c>
-      <c r="C143" s="0">
-        <v>3.6396182416332579</v>
-      </c>
-      <c r="D143" s="0"/>
-      <c r="E143" s="0"/>
-      <c r="F143" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G143" s="0"/>
-      <c r="H143" s="0"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="0" t="s">
-        <v>486</v>
-      </c>
-      <c r="B144" s="0" t="s">
-        <v>503</v>
-      </c>
-      <c r="C144" s="0">
-        <v>0.25</v>
-      </c>
-      <c r="D144" s="0"/>
-      <c r="E144" s="0"/>
-      <c r="F144" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G144" s="0"/>
-      <c r="H144" s="0"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="0" t="s">
-        <v>487</v>
-      </c>
-      <c r="B145" s="0" t="s">
-        <v>503</v>
-      </c>
-      <c r="C145" s="0">
-        <v>0.69999999999999996</v>
-      </c>
-      <c r="D145" s="0"/>
-      <c r="E145" s="0"/>
-      <c r="F145" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G145" s="0"/>
-      <c r="H145" s="0"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="0" t="s">
-        <v>488</v>
-      </c>
-      <c r="B146" s="0" t="s">
-        <v>503</v>
-      </c>
-      <c r="C146" s="0">
-        <v>1</v>
-      </c>
-      <c r="D146" s="0"/>
-      <c r="E146" s="0"/>
-      <c r="F146" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G146" s="0"/>
-      <c r="H146" s="0"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="0" t="s">
-        <v>489</v>
-      </c>
-      <c r="B147" s="0" t="s">
-        <v>503</v>
-      </c>
-      <c r="C147" s="0">
-        <v>0.12048857500544551</v>
-      </c>
-      <c r="D147" s="0"/>
-      <c r="E147" s="0"/>
-      <c r="F147" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G147" s="0"/>
-      <c r="H147" s="0"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="0" t="s">
-        <v>490</v>
-      </c>
-      <c r="B148" s="0" t="s">
-        <v>503</v>
-      </c>
-      <c r="C148" s="0">
-        <v>119.66043834086311</v>
-      </c>
-      <c r="D148" s="0"/>
-      <c r="E148" s="0"/>
-      <c r="F148" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G148" s="0"/>
-      <c r="H148" s="0"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="0" t="s">
-        <v>491</v>
-      </c>
-      <c r="B149" s="0" t="s">
-        <v>503</v>
-      </c>
-      <c r="C149" s="0">
-        <v>0.074583678423586861</v>
-      </c>
-      <c r="D149" s="0"/>
-      <c r="E149" s="0"/>
-      <c r="F149" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G149" s="0"/>
-      <c r="H149" s="0"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="0" t="s">
-        <v>492</v>
-      </c>
-      <c r="B150" s="0" t="s">
-        <v>503</v>
-      </c>
-      <c r="C150" s="0">
-        <v>1.0700000000000001</v>
-      </c>
-      <c r="D150" s="0"/>
-      <c r="E150" s="0"/>
-      <c r="F150" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G150" s="0"/>
-      <c r="H150" s="0"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="0" t="s">
-        <v>493</v>
-      </c>
-      <c r="B151" s="0" t="s">
-        <v>503</v>
-      </c>
-      <c r="C151" s="0">
-        <v>0.29999999999999999</v>
-      </c>
-      <c r="D151" s="0"/>
-      <c r="E151" s="0"/>
-      <c r="F151" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G151" s="0"/>
-      <c r="H151" s="0"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="0" t="s">
-        <v>494</v>
-      </c>
-      <c r="B152" s="0" t="s">
-        <v>503</v>
-      </c>
-      <c r="C152" s="0">
-        <v>29.162154556467332</v>
-      </c>
-      <c r="D152" s="0"/>
-      <c r="E152" s="0"/>
-      <c r="F152" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G152" s="0"/>
-      <c r="H152" s="0"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="0" t="s">
-        <v>495</v>
-      </c>
-      <c r="B153" s="0" t="s">
-        <v>503</v>
-      </c>
-      <c r="C153" s="0">
-        <v>0.83784544353266455</v>
-      </c>
-      <c r="D153" s="0"/>
-      <c r="E153" s="0"/>
-      <c r="F153" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G153" s="0"/>
-      <c r="H153" s="0"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="0" t="s">
-        <v>496</v>
-      </c>
-      <c r="B154" s="0" t="s">
-        <v>503</v>
-      </c>
-      <c r="C154" s="0">
-        <v>5.2740736776131758</v>
-      </c>
-      <c r="D154" s="0"/>
-      <c r="E154" s="0"/>
-      <c r="F154" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G154" s="0"/>
-      <c r="H154" s="0"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="0" t="s">
-        <v>497</v>
-      </c>
-      <c r="B155" s="0" t="s">
-        <v>503</v>
-      </c>
-      <c r="C155" s="0">
-        <v>0.3656082203404642</v>
-      </c>
-      <c r="D155" s="0"/>
-      <c r="E155" s="0"/>
-      <c r="F155" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G155" s="0"/>
-      <c r="H155" s="0"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="0" t="s">
-        <v>498</v>
-      </c>
-      <c r="B156" s="0" t="s">
-        <v>503</v>
-      </c>
-      <c r="C156" s="0">
-        <v>0.15</v>
-      </c>
-      <c r="D156" s="0"/>
-      <c r="E156" s="0"/>
-      <c r="F156" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G156" s="0"/>
-      <c r="H156" s="0"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="0" t="s">
-        <v>499</v>
-      </c>
-      <c r="B157" s="0" t="s">
-        <v>503</v>
-      </c>
-      <c r="C157" s="0">
-        <v>-0.79111105164197637</v>
-      </c>
-      <c r="D157" s="0"/>
-      <c r="E157" s="0"/>
-      <c r="F157" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G157" s="0"/>
-      <c r="H157" s="0"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="0" t="s">
-        <v>500</v>
-      </c>
-      <c r="B158" s="0" t="s">
-        <v>503</v>
-      </c>
-      <c r="C158" s="0">
-        <v>0.12602616170797043</v>
-      </c>
-      <c r="D158" s="0"/>
-      <c r="E158" s="0"/>
-      <c r="F158" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G158" s="0"/>
-      <c r="H158" s="0"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="0" t="s">
-        <v>501</v>
-      </c>
-      <c r="B159" s="0" t="s">
-        <v>503</v>
-      </c>
-      <c r="C159" s="0">
-        <v>5</v>
-      </c>
-      <c r="D159" s="0"/>
-      <c r="E159" s="0"/>
-      <c r="F159" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G159" s="0"/>
-      <c r="H159" s="0"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="0" t="s">
-        <v>502</v>
-      </c>
-      <c r="B160" s="0" t="s">
-        <v>503</v>
-      </c>
-      <c r="C160" s="0">
+      <c r="C112">
         <v>-0.18486997339978403</v>
       </c>
-      <c r="D160" s="0"/>
-      <c r="E160" s="0"/>
-      <c r="F160" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="G160" s="0"/>
-      <c r="H160" s="0"/>
+      <c r="F112" t="s">
+        <v>377</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6992,14 +5929,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFCC8514-E0AF-4C67-BF86-8649FC702924}">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.44140625" customWidth="1"/>
-    <col min="2" max="3" width="32.44140625" style="20" customWidth="1"/>
-    <col min="4" max="4" width="13.33203125" style="20" customWidth="1"/>
+    <col min="1" max="1" width="32.42578125" customWidth="1"/>
+    <col min="2" max="3" width="32.42578125" style="20" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" style="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>274</v>
       </c>
@@ -7013,7 +5950,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>276</v>
       </c>
@@ -7027,7 +5964,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
         <v>277</v>
       </c>
@@ -7041,7 +5978,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>278</v>
       </c>
@@ -7055,7 +5992,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>279</v>
       </c>
@@ -7069,7 +6006,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
         <v>304</v>
       </c>
@@ -7083,7 +6020,7 @@
         <v>-4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>280</v>
       </c>
@@ -7097,7 +6034,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>281</v>
       </c>
@@ -7111,7 +6048,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>282</v>
       </c>
@@ -7125,7 +6062,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>283</v>
       </c>
@@ -7139,7 +6076,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>284</v>
       </c>
@@ -7153,7 +6090,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>285</v>
       </c>
@@ -7167,7 +6104,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>286</v>
       </c>
@@ -7181,7 +6118,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>287</v>
       </c>
@@ -7195,7 +6132,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
         <v>288</v>
       </c>
@@ -7209,7 +6146,7 @@
         <v>-7.8E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>289</v>
       </c>
@@ -7223,7 +6160,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>290</v>
       </c>
@@ -7237,7 +6174,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>291</v>
       </c>
@@ -7251,7 +6188,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>293</v>
       </c>
@@ -7265,7 +6202,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>292</v>
       </c>
@@ -7287,26 +6224,26 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{118BE621-EF6B-4648-868E-9937B9C5B685}">
   <dimension ref="A1:F32"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="48.109375" style="2" customWidth="1"/>
-    <col min="2" max="4" width="15.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="3.6640625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="46.6640625" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="8.6640625" style="2"/>
+    <col min="1" max="1" width="48.140625" style="2" customWidth="1"/>
+    <col min="2" max="4" width="15.7109375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="3.7109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="46.7109375" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="8.7109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>208</v>
       </c>
@@ -7320,7 +6257,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>212</v>
       </c>
@@ -7338,7 +6275,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>214</v>
       </c>
@@ -7358,7 +6295,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>216</v>
       </c>
@@ -7378,7 +6315,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>217</v>
       </c>
@@ -7396,7 +6333,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>218</v>
       </c>
@@ -7416,7 +6353,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>220</v>
       </c>
@@ -7433,7 +6370,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>222</v>
       </c>
@@ -7450,7 +6387,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>223</v>
       </c>
@@ -7470,7 +6407,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>225</v>
       </c>
@@ -7487,7 +6424,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>257</v>
       </c>
@@ -7507,7 +6444,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>258</v>
       </c>
@@ -7527,7 +6464,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>227</v>
       </c>
@@ -7535,7 +6472,7 @@
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>228</v>
       </c>
@@ -7552,7 +6489,7 @@
         <v>1.9823131728623846</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>229</v>
       </c>
@@ -7569,7 +6506,7 @@
         <v>1.1592794807274085</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>230</v>
       </c>
@@ -7586,7 +6523,7 @@
         <v>-0.62740704594148844</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>231</v>
       </c>
@@ -7603,7 +6540,7 @@
         <v>-0.96540266006846076</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>232</v>
       </c>
@@ -7611,7 +6548,7 @@
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>233</v>
       </c>
@@ -7628,7 +6565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>234</v>
       </c>
@@ -7645,7 +6582,7 @@
         <v>0.52359877559829882</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>235</v>
       </c>
@@ -7662,7 +6599,7 @@
         <v>-0.50548365077118673</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>236</v>
       </c>
@@ -7679,7 +6616,7 @@
         <v>324.01250000000005</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>237</v>
       </c>
@@ -7696,7 +6633,7 @@
         <v>1.42884E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>238</v>
       </c>
@@ -7713,7 +6650,7 @@
         <v>-0.13760360258695806</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>239</v>
       </c>
@@ -7730,7 +6667,7 @@
         <v>0.13760360258695806</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>240</v>
       </c>
@@ -7747,7 +6684,7 @@
         <v>22.925083964169769</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>241</v>
       </c>
@@ -7755,7 +6692,7 @@
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>242</v>
       </c>
@@ -7763,7 +6700,7 @@
       <c r="C31" s="14"/>
       <c r="D31" s="14"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>243</v>
       </c>
@@ -7786,19 +6723,19 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="C109:F109"/>
-  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="11.5546875" customWidth="true"/>
-    <col min="6" max="6" width="142.44140625" customWidth="true"/>
+    <col min="3" max="3" width="11.5703125" customWidth="1"/>
+    <col min="6" max="6" width="142.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="109" x14ac:dyDescent="0.3">
-      <c r="C109" s="0">
+    <row r="109" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C109">
         <v>11.941543440928031</v>
       </c>
-      <c r="F109" s="0" t="s">
+      <c r="F109" t="s">
         <v>379</v>
       </c>
     </row>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2a1ac608aa9918f7/Documents/GitHub/451-DBF-Team01/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\Fall 2026\AAE 451\451-DBF-Team01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="78" documentId="13_ncr:1_{37DAE441-3691-47BB-B387-517F08F01369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0C8D41D-CB4D-4A5B-B008-BE7BD96D2718}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64E19CEC-8588-49E3-B36E-18DDBFB481A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9930" yWindow="4845" windowWidth="28500" windowHeight="13770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="545">
   <si>
     <t>Parameter</t>
   </si>
@@ -306,9 +306,6 @@
     <t>main_gear_len</t>
   </si>
   <si>
-    <t>Main gear strut length</t>
-  </si>
-  <si>
     <t>main_strut_dia</t>
   </si>
   <si>
@@ -1609,6 +1606,72 @@
   </si>
   <si>
     <t>Written by writeOutputs.m on 2026-10-06 17:29</t>
+  </si>
+  <si>
+    <t>fty_al_6061_t6</t>
+  </si>
+  <si>
+    <t>materials</t>
+  </si>
+  <si>
+    <t>MPa</t>
+  </si>
+  <si>
+    <t>fsu_al_6061_t6</t>
+  </si>
+  <si>
+    <t>fbry_al_6061_t6</t>
+  </si>
+  <si>
+    <t>fa_plywood</t>
+  </si>
+  <si>
+    <t>E_al_6061_t6</t>
+  </si>
+  <si>
+    <t>gear_strut_thickness</t>
+  </si>
+  <si>
+    <t>gear_strut_width_max</t>
+  </si>
+  <si>
+    <t>gear_strut_width_min</t>
+  </si>
+  <si>
+    <t>gear_strut_angle</t>
+  </si>
+  <si>
+    <t>height_fuselage</t>
+  </si>
+  <si>
+    <t>wall_thick_fuselage</t>
+  </si>
+  <si>
+    <t>width_spar</t>
+  </si>
+  <si>
+    <t>length_spar</t>
+  </si>
+  <si>
+    <t>wall_thick_spar</t>
+  </si>
+  <si>
+    <t>width_tail_boom</t>
+  </si>
+  <si>
+    <t>length_tail_boom</t>
+  </si>
+  <si>
+    <t>wall_thick_tail_boom</t>
+  </si>
+  <si>
+    <t>washer_OD</t>
+  </si>
+  <si>
+    <t>washer_ID</t>
+  </si>
+  <si>
+    <t>Main gear strut vertical height</t>
   </si>
 </sst>
 </file>
@@ -1677,7 +1740,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1720,8 +1783,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor theme="0" tint="-0.14999847407452621"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1729,12 +1798,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -1764,6 +1848,20 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1793,8 +1891,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:F109" totalsRowShown="0">
-  <autoFilter ref="A1:F109" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:F144" totalsRowShown="0">
+  <autoFilter ref="A1:F144" xr:uid="{00000000-0009-0000-0100-000001000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="geometry"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E43">
     <sortCondition ref="B1:B101"/>
   </sortState>
@@ -2088,7 +2192,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F109"/>
+  <dimension ref="A1:F144"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
@@ -2119,7 +2223,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -2136,7 +2240,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -2153,7 +2257,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -2170,7 +2274,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -2187,7 +2291,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -2204,7 +2308,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -2221,7 +2325,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -2238,9 +2342,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B9" s="20" t="s">
         <v>7</v>
@@ -2252,7 +2356,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -2269,7 +2373,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -2286,7 +2390,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -2300,10 +2404,10 @@
         <v>8</v>
       </c>
       <c r="E12" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -2320,7 +2424,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -2337,7 +2441,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -2354,7 +2458,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>35</v>
       </c>
@@ -2371,7 +2475,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>37</v>
       </c>
@@ -2388,7 +2492,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>39</v>
       </c>
@@ -2405,7 +2509,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>41</v>
       </c>
@@ -2422,7 +2526,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>45</v>
       </c>
@@ -2439,7 +2543,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -2456,7 +2560,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -2473,7 +2577,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -2719,7 +2823,7 @@
         <v>56</v>
       </c>
       <c r="C37" s="20">
-        <v>0.05</v>
+        <v>8.3000000000000004E-2</v>
       </c>
       <c r="D37" s="20" t="s">
         <v>59</v>
@@ -2736,7 +2840,7 @@
         <v>56</v>
       </c>
       <c r="C38" s="20">
-        <v>1.4999999999999999E-2</v>
+        <v>4.7E-2</v>
       </c>
       <c r="D38" s="20" t="s">
         <v>59</v>
@@ -2753,18 +2857,18 @@
         <v>56</v>
       </c>
       <c r="C39" s="20">
-        <v>0.155</v>
+        <v>0.1043</v>
       </c>
       <c r="D39" s="20" t="s">
         <v>59</v>
       </c>
       <c r="E39" t="s">
-        <v>89</v>
+        <v>544</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B40" s="20" t="s">
         <v>56</v>
@@ -2776,80 +2880,80 @@
         <v>59</v>
       </c>
       <c r="E40" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B41" s="20" t="s">
         <v>56</v>
       </c>
       <c r="C41" s="20">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="D41" s="20" t="s">
         <v>59</v>
       </c>
       <c r="E41" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B42" s="20" t="s">
         <v>56</v>
       </c>
       <c r="C42" s="20">
-        <v>1.4999999999999999E-2</v>
+        <v>0.01</v>
       </c>
       <c r="D42" s="20" t="s">
         <v>59</v>
       </c>
       <c r="E42" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B43" s="20" t="s">
         <v>56</v>
       </c>
       <c r="C43" s="20">
-        <v>0.09</v>
+        <v>6.3E-2</v>
       </c>
       <c r="D43" s="20" t="s">
         <v>59</v>
       </c>
       <c r="E43" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B44" s="20" t="s">
         <v>56</v>
       </c>
       <c r="C44" s="20">
-        <v>0.01</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="D44" s="20" t="s">
         <v>59</v>
       </c>
       <c r="E44" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B45" s="20" t="s">
         <v>56</v>
@@ -2858,15 +2962,15 @@
         <v>0.08</v>
       </c>
       <c r="D45" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="E45" t="s">
         <v>101</v>
-      </c>
-      <c r="E45" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B46" s="20" t="s">
         <v>56</v>
@@ -2878,12 +2982,12 @@
         <v>59</v>
       </c>
       <c r="E46" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B47" s="20" t="s">
         <v>56</v>
@@ -2895,12 +2999,12 @@
         <v>59</v>
       </c>
       <c r="E47" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B48" s="20" t="s">
         <v>56</v>
@@ -2912,12 +3016,12 @@
         <v>8</v>
       </c>
       <c r="E48" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B49" s="20" t="s">
         <v>56</v>
@@ -2929,12 +3033,12 @@
         <v>59</v>
       </c>
       <c r="E49" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B50" s="20" t="s">
         <v>56</v>
@@ -2946,12 +3050,12 @@
         <v>8</v>
       </c>
       <c r="E50" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B51" s="20" t="s">
         <v>56</v>
@@ -2963,12 +3067,12 @@
         <v>8</v>
       </c>
       <c r="E51" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B52" s="20" t="s">
         <v>56</v>
@@ -2980,12 +3084,12 @@
         <v>8</v>
       </c>
       <c r="E52" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B53" s="20" t="s">
         <v>56</v>
@@ -2997,12 +3101,12 @@
         <v>8</v>
       </c>
       <c r="E53" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B54" s="20" t="s">
         <v>56</v>
@@ -3014,12 +3118,12 @@
         <v>23</v>
       </c>
       <c r="E54" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B55" s="20" t="s">
         <v>56</v>
@@ -3031,12 +3135,12 @@
         <v>8</v>
       </c>
       <c r="E55" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B56" s="20" t="s">
         <v>56</v>
@@ -3048,12 +3152,12 @@
         <v>23</v>
       </c>
       <c r="E56" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B57" s="20" t="s">
         <v>56</v>
@@ -3065,12 +3169,12 @@
         <v>8</v>
       </c>
       <c r="E57" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B58" s="20" t="s">
         <v>56</v>
@@ -3082,12 +3186,12 @@
         <v>8</v>
       </c>
       <c r="E58" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B59" s="20" t="s">
         <v>56</v>
@@ -3099,12 +3203,12 @@
         <v>8</v>
       </c>
       <c r="E59" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B60" s="20" t="s">
         <v>56</v>
@@ -3116,12 +3220,12 @@
         <v>23</v>
       </c>
       <c r="E60" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B61" s="20" t="s">
         <v>56</v>
@@ -3133,32 +3237,32 @@
         <v>23</v>
       </c>
       <c r="E61" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+      <c r="B62" s="20" t="s">
         <v>135</v>
-      </c>
-      <c r="B62" s="20" t="s">
-        <v>136</v>
       </c>
       <c r="C62" s="20">
         <v>10</v>
       </c>
       <c r="D62" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="E62" t="s">
         <v>137</v>
       </c>
-      <c r="E62" t="s">
+    </row>
+    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>139</v>
-      </c>
       <c r="B63" s="20" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C63" s="20">
         <v>1.1000000000000001</v>
@@ -3167,15 +3271,15 @@
         <v>8</v>
       </c>
       <c r="E63" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>141</v>
-      </c>
       <c r="B64" s="20" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C64" s="20">
         <v>0.75</v>
@@ -3184,15 +3288,15 @@
         <v>8</v>
       </c>
       <c r="E64" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>143</v>
-      </c>
       <c r="B65" s="20" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C65" s="20">
         <v>1.5</v>
@@ -3201,15 +3305,15 @@
         <v>8</v>
       </c>
       <c r="E65" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>145</v>
-      </c>
       <c r="B66" s="20" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C66" s="20">
         <v>20</v>
@@ -3218,15 +3322,15 @@
         <v>59</v>
       </c>
       <c r="E66" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>201</v>
-      </c>
       <c r="B67" s="20" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C67" s="20">
         <v>50</v>
@@ -3235,15 +3339,15 @@
         <v>59</v>
       </c>
       <c r="E67" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B68" s="20" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C68" s="20">
         <v>30</v>
@@ -3252,15 +3356,15 @@
         <v>59</v>
       </c>
       <c r="E68" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>148</v>
-      </c>
       <c r="B69" s="20" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C69" s="20">
         <v>100</v>
@@ -3269,15 +3373,15 @@
         <v>59</v>
       </c>
       <c r="E69" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>150</v>
-      </c>
       <c r="B70" s="20" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C70" s="20">
         <v>25</v>
@@ -3286,15 +3390,15 @@
         <v>59</v>
       </c>
       <c r="E70" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>152</v>
-      </c>
       <c r="B71" s="20" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C71" s="20">
         <v>200</v>
@@ -3303,49 +3407,49 @@
         <v>59</v>
       </c>
       <c r="E71" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>154</v>
-      </c>
       <c r="B72" s="20" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C72" s="20">
         <v>95</v>
       </c>
       <c r="D72" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="E72" t="s">
         <v>155</v>
       </c>
-      <c r="E72" t="s">
+    </row>
+    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>157</v>
-      </c>
       <c r="B73" s="20" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C73" s="20">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="D73" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="E73" t="s">
         <v>158</v>
       </c>
-      <c r="E73" t="s">
+    </row>
+    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>160</v>
-      </c>
       <c r="B74" s="20" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C74" s="20">
         <v>0.8</v>
@@ -3354,32 +3458,32 @@
         <v>8</v>
       </c>
       <c r="E74" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>162</v>
-      </c>
       <c r="B75" s="20" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C75" s="20">
         <v>0.52</v>
       </c>
       <c r="D75" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="E75" t="s">
         <v>163</v>
       </c>
-      <c r="E75" t="s">
+    </row>
+    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>165</v>
-      </c>
       <c r="B76" s="20" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C76" s="20">
         <v>10</v>
@@ -3388,32 +3492,32 @@
         <v>8</v>
       </c>
       <c r="E76" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>167</v>
-      </c>
       <c r="B77" s="20" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C77" s="20">
         <v>6</v>
       </c>
       <c r="D77" s="20" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E77" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
+      <c r="B78" s="20" t="s">
         <v>169</v>
-      </c>
-      <c r="B78" s="20" t="s">
-        <v>170</v>
       </c>
       <c r="C78" s="20">
         <v>0.75</v>
@@ -3422,15 +3526,15 @@
         <v>8</v>
       </c>
       <c r="E78" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>172</v>
-      </c>
       <c r="B79" s="20" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C79" s="20">
         <v>0.45</v>
@@ -3439,15 +3543,15 @@
         <v>8</v>
       </c>
       <c r="E79" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>174</v>
-      </c>
       <c r="B80" s="20" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C80" s="20">
         <v>1</v>
@@ -3456,15 +3560,15 @@
         <v>8</v>
       </c>
       <c r="E80" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>176</v>
-      </c>
       <c r="B81" s="20" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C81" s="20">
         <v>0.75</v>
@@ -3473,15 +3577,15 @@
         <v>8</v>
       </c>
       <c r="E81" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>178</v>
-      </c>
       <c r="B82" s="20" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C82" s="20">
         <v>0.95</v>
@@ -3490,117 +3594,117 @@
         <v>8</v>
       </c>
       <c r="E82" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>180</v>
-      </c>
       <c r="B83" s="20" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C83" s="20">
         <v>980</v>
       </c>
       <c r="D83" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="E83" t="s">
         <v>181</v>
       </c>
-      <c r="E83" t="s">
+    </row>
+    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>183</v>
-      </c>
       <c r="B84" s="20" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C84" s="20">
         <v>1.84</v>
       </c>
       <c r="D84" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="E84" t="s">
         <v>184</v>
       </c>
-      <c r="E84" t="s">
+    </row>
+    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>186</v>
-      </c>
       <c r="B85" s="20" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C85" s="20">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="D85" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="E85" t="s">
         <v>187</v>
       </c>
-      <c r="E85" t="s">
+    </row>
+    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>189</v>
-      </c>
       <c r="B86" s="20" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C86" s="20">
         <v>14.8</v>
       </c>
       <c r="D86" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="E86" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
         <v>190</v>
       </c>
-      <c r="E86" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>191</v>
-      </c>
       <c r="B87" s="20" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C87" s="20" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D87" s="20" t="s">
         <v>8</v>
       </c>
       <c r="E87" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>193</v>
-      </c>
       <c r="B88" s="20" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C88" s="20">
         <v>527000</v>
       </c>
       <c r="D88" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="E88" t="s">
         <v>194</v>
       </c>
-      <c r="E88" t="s">
+    </row>
+    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>196</v>
-      </c>
       <c r="B89" s="20" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C89" s="20">
         <v>0.8</v>
@@ -3609,15 +3713,15 @@
         <v>8</v>
       </c>
       <c r="E89" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>198</v>
-      </c>
       <c r="B90" s="20" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C90" s="20">
         <v>0.7</v>
@@ -3626,15 +3730,15 @@
         <v>8</v>
       </c>
       <c r="E90" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>247</v>
+      </c>
+      <c r="B91" s="20" t="s">
         <v>248</v>
-      </c>
-      <c r="B91" s="20" t="s">
-        <v>249</v>
       </c>
       <c r="C91" s="20">
         <v>1</v>
@@ -3643,15 +3747,15 @@
         <v>8</v>
       </c>
       <c r="E91" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>251</v>
-      </c>
       <c r="B92" s="20" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C92" s="20">
         <v>1.2</v>
@@ -3660,15 +3764,15 @@
         <v>8</v>
       </c>
       <c r="E92" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>253</v>
-      </c>
       <c r="B93" s="20" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C93" s="20">
         <v>1</v>
@@ -3677,15 +3781,15 @@
         <v>8</v>
       </c>
       <c r="E93" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>255</v>
-      </c>
       <c r="B94" s="20" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C94" s="20">
         <v>0.85</v>
@@ -3694,29 +3798,29 @@
         <v>8</v>
       </c>
       <c r="E94" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B95" s="20" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C95" s="20">
         <v>5.5</v>
       </c>
       <c r="D95" s="20" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E95" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
         <v>262</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>263</v>
       </c>
       <c r="B96" s="20" t="s">
         <v>7</v>
@@ -3728,15 +3832,15 @@
         <v>8</v>
       </c>
       <c r="E96" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>263</v>
+      </c>
+      <c r="B97" s="21" t="s">
         <v>264</v>
-      </c>
-      <c r="B97" s="21" t="s">
-        <v>265</v>
       </c>
       <c r="C97" s="21">
         <v>0.3</v>
@@ -3745,15 +3849,15 @@
         <v>8</v>
       </c>
       <c r="E97" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B98" s="21" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C98" s="21">
         <v>1</v>
@@ -3762,15 +3866,15 @@
         <v>8</v>
       </c>
       <c r="E98" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B99" s="21" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C99" s="21">
         <v>1</v>
@@ -3779,15 +3883,15 @@
         <v>8</v>
       </c>
       <c r="E99" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B100" s="20" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C100" s="20">
         <v>1</v>
@@ -3796,15 +3900,15 @@
         <v>8</v>
       </c>
       <c r="E100" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B101" s="21" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C101" s="21">
         <v>0.03</v>
@@ -3813,15 +3917,15 @@
         <v>59</v>
       </c>
       <c r="E101" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B102" s="21" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C102" s="21">
         <v>0.29499999999999998</v>
@@ -3830,49 +3934,49 @@
         <v>59</v>
       </c>
       <c r="E102" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B103" s="20" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C103" s="20">
         <v>1</v>
       </c>
       <c r="D103" s="20" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E103" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B104" s="21" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C104" s="21">
         <v>35000</v>
       </c>
       <c r="D104" s="20" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E104" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B105" s="21" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C105" s="21">
         <v>0.22</v>
@@ -3881,77 +3985,358 @@
         <v>59</v>
       </c>
       <c r="E105" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>307</v>
-      </c>
       <c r="B106" s="20" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C106" s="20">
         <v>1000</v>
       </c>
       <c r="D106" s="20" t="s">
+        <v>310</v>
+      </c>
+      <c r="E106" t="s">
         <v>311</v>
       </c>
-      <c r="E106" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B107" s="20" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C107" s="20">
         <v>890</v>
       </c>
       <c r="D107" s="20" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E107" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B108" s="20" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C108" s="20">
         <v>60</v>
       </c>
       <c r="D108" s="20" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E108" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B109" s="20" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C109" s="20">
         <v>11.941543440928031</v>
       </c>
       <c r="D109" s="20" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E109" t="s">
-        <v>314</v>
-      </c>
-    </row>
+        <v>313</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="23" t="s">
+        <v>523</v>
+      </c>
+      <c r="B110" s="24" t="s">
+        <v>524</v>
+      </c>
+      <c r="C110" s="24">
+        <v>241</v>
+      </c>
+      <c r="D110" s="24" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="25" t="s">
+        <v>526</v>
+      </c>
+      <c r="B111" s="26" t="s">
+        <v>524</v>
+      </c>
+      <c r="C111" s="27">
+        <v>186</v>
+      </c>
+      <c r="D111" s="26" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="23" t="s">
+        <v>527</v>
+      </c>
+      <c r="B112" s="24" t="s">
+        <v>524</v>
+      </c>
+      <c r="C112" s="24">
+        <v>338</v>
+      </c>
+      <c r="D112" s="24" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="25" t="s">
+        <v>528</v>
+      </c>
+      <c r="B113" s="26" t="s">
+        <v>524</v>
+      </c>
+      <c r="C113" s="26">
+        <v>30</v>
+      </c>
+      <c r="D113" s="26" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="23" t="s">
+        <v>529</v>
+      </c>
+      <c r="B114" s="24" t="s">
+        <v>524</v>
+      </c>
+      <c r="C114" s="28">
+        <v>68900</v>
+      </c>
+      <c r="D114" s="24" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115" s="23" t="s">
+        <v>530</v>
+      </c>
+      <c r="B115" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C115" s="24">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="D115" s="24" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116" s="23" t="s">
+        <v>531</v>
+      </c>
+      <c r="B116" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C116" s="24">
+        <v>0.04</v>
+      </c>
+      <c r="D116" s="24" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" s="23" t="s">
+        <v>532</v>
+      </c>
+      <c r="B117" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C117" s="24">
+        <v>2.3E-2</v>
+      </c>
+      <c r="D117" s="24" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118" s="23" t="s">
+        <v>533</v>
+      </c>
+      <c r="B118" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C118" s="24">
+        <v>50</v>
+      </c>
+      <c r="D118" s="24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119" s="23" t="s">
+        <v>534</v>
+      </c>
+      <c r="B119" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C119" s="24">
+        <v>0.09</v>
+      </c>
+      <c r="D119" s="24" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120" s="23" t="s">
+        <v>535</v>
+      </c>
+      <c r="B120" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C120" s="24">
+        <v>6.3499999999999997E-3</v>
+      </c>
+      <c r="D120" s="24" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121" s="23" t="s">
+        <v>536</v>
+      </c>
+      <c r="B121" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C121" s="24">
+        <v>1.2699999999999999E-2</v>
+      </c>
+      <c r="D121" s="24" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122" s="23" t="s">
+        <v>537</v>
+      </c>
+      <c r="B122" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C122" s="24">
+        <v>0.76</v>
+      </c>
+      <c r="D122" s="24" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123" s="23" t="s">
+        <v>538</v>
+      </c>
+      <c r="B123" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C123" s="24">
+        <v>1.5874999999999999E-3</v>
+      </c>
+      <c r="D123" s="24" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124" s="23" t="s">
+        <v>539</v>
+      </c>
+      <c r="B124" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C124" s="24">
+        <v>1.2699999999999999E-2</v>
+      </c>
+      <c r="D124" s="24" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125" s="23" t="s">
+        <v>540</v>
+      </c>
+      <c r="B125" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C125" s="24">
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="D125" s="24" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126" s="23" t="s">
+        <v>541</v>
+      </c>
+      <c r="B126" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C126" s="24">
+        <v>1.5874999999999999E-3</v>
+      </c>
+      <c r="D126" s="24" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127" s="23" t="s">
+        <v>542</v>
+      </c>
+      <c r="B127" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C127" s="24">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="D127" s="24" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128" s="25" t="s">
+        <v>543</v>
+      </c>
+      <c r="B128" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C128" s="26">
+        <v>4.3E-3</v>
+      </c>
+      <c r="D128" s="26" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="130" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="131" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="132" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="133" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="134" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="135" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="136" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="137" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="138" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="139" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="140" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="141" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="142" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="143" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="144" hidden="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -3991,15 +4376,15 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -4011,15 +4396,15 @@
         <v>8</v>
       </c>
       <c r="E2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
@@ -4031,15 +4416,15 @@
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
@@ -4051,15 +4436,15 @@
         <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B5" t="s">
         <v>7</v>
@@ -4071,15 +4456,15 @@
         <v>8</v>
       </c>
       <c r="E5" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F5" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
@@ -4091,15 +4476,15 @@
         <v>8</v>
       </c>
       <c r="E6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B7" t="s">
         <v>7</v>
@@ -4108,12 +4493,12 @@
         <v>2.9817638776781716E-2</v>
       </c>
       <c r="F7" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B8" t="s">
         <v>7</v>
@@ -4125,15 +4510,15 @@
         <v>8</v>
       </c>
       <c r="E8" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F8" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B9" t="s">
         <v>7</v>
@@ -4145,15 +4530,15 @@
         <v>8</v>
       </c>
       <c r="E9" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F9" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B10" t="s">
         <v>7</v>
@@ -4165,15 +4550,15 @@
         <v>8</v>
       </c>
       <c r="E10" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B11" t="s">
         <v>7</v>
@@ -4185,15 +4570,15 @@
         <v>8</v>
       </c>
       <c r="E11" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B12" t="s">
         <v>7</v>
@@ -4205,15 +4590,15 @@
         <v>8</v>
       </c>
       <c r="E12" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F12" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B13" t="s">
         <v>7</v>
@@ -4222,12 +4607,12 @@
         <v>3.0198549799930445</v>
       </c>
       <c r="F13" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B14" t="s">
         <v>7</v>
@@ -4236,12 +4621,12 @@
         <v>4.0327458299223453</v>
       </c>
       <c r="F14" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B15" t="s">
         <v>7</v>
@@ -4250,12 +4635,12 @@
         <v>0.58894455001488533</v>
       </c>
       <c r="F15" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B16" t="s">
         <v>7</v>
@@ -4264,12 +4649,12 @@
         <v>5.2740736776131758</v>
       </c>
       <c r="F16" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B17" t="s">
         <v>7</v>
@@ -4278,12 +4663,12 @@
         <v>-9.4788465253600393E-2</v>
       </c>
       <c r="F17" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B18" t="s">
         <v>7</v>
@@ -4292,12 +4677,12 @@
         <v>0.66074594914354523</v>
       </c>
       <c r="F18" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B19" t="s">
         <v>7</v>
@@ -4306,12 +4691,12 @@
         <v>0.60899778104422941</v>
       </c>
       <c r="F19" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B20" t="s">
         <v>7</v>
@@ -4320,12 +4705,12 @@
         <v>1.5753270213496304</v>
       </c>
       <c r="F20" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B21" t="s">
         <v>7</v>
@@ -4334,12 +4719,12 @@
         <v>0.66074594914354523</v>
       </c>
       <c r="F21" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B22" t="s">
         <v>7</v>
@@ -4348,12 +4733,12 @@
         <v>0.12602616170797043</v>
       </c>
       <c r="F22" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B23" t="s">
         <v>7</v>
@@ -4362,12 +4747,12 @@
         <v>0.8871601270722228</v>
       </c>
       <c r="F23" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B24" t="s">
         <v>56</v>
@@ -4379,15 +4764,15 @@
         <v>66</v>
       </c>
       <c r="E24" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F24" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B25" t="s">
         <v>56</v>
@@ -4399,15 +4784,15 @@
         <v>59</v>
       </c>
       <c r="E25" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F25" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B26" t="s">
         <v>56</v>
@@ -4419,15 +4804,15 @@
         <v>8</v>
       </c>
       <c r="E26" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F26" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B27" t="s">
         <v>56</v>
@@ -4439,15 +4824,15 @@
         <v>66</v>
       </c>
       <c r="E27" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F27" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B28" t="s">
         <v>56</v>
@@ -4459,15 +4844,15 @@
         <v>59</v>
       </c>
       <c r="E28" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F28" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B29" t="s">
         <v>56</v>
@@ -4479,15 +4864,15 @@
         <v>59</v>
       </c>
       <c r="E29" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F29" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B30" t="s">
         <v>56</v>
@@ -4499,15 +4884,15 @@
         <v>8</v>
       </c>
       <c r="E30" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F30" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B31" t="s">
         <v>56</v>
@@ -4519,15 +4904,15 @@
         <v>66</v>
       </c>
       <c r="E31" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F31" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B32" t="s">
         <v>56</v>
@@ -4539,15 +4924,15 @@
         <v>66</v>
       </c>
       <c r="E32" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F32" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B33" t="s">
         <v>56</v>
@@ -4559,15 +4944,15 @@
         <v>59</v>
       </c>
       <c r="E33" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F33" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B34" t="s">
         <v>56</v>
@@ -4579,15 +4964,15 @@
         <v>59</v>
       </c>
       <c r="E34" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F34" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B35" t="s">
         <v>56</v>
@@ -4596,12 +4981,12 @@
         <v>1.8046437163813135E-2</v>
       </c>
       <c r="F35" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B36" t="s">
         <v>56</v>
@@ -4610,12 +4995,12 @@
         <v>0.23885083680507355</v>
       </c>
       <c r="F36" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B37" t="s">
         <v>56</v>
@@ -4624,12 +5009,12 @@
         <v>0.3656082203404642</v>
       </c>
       <c r="F37" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B38" t="s">
         <v>56</v>
@@ -4638,109 +5023,109 @@
         <v>0.2156082203404642</v>
       </c>
       <c r="F38" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B39" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C39">
         <v>4.0516000000000005</v>
       </c>
       <c r="F39" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B40" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C40">
         <v>22.737783592977756</v>
       </c>
       <c r="D40" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E40" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F40" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B41" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C41">
         <v>11</v>
       </c>
       <c r="D41" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E41" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F41" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B42" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C42">
         <v>14.810748414335091</v>
       </c>
       <c r="D42" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E42" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F42" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B43" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C43">
         <v>12.24744871391589</v>
       </c>
       <c r="D43" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E43" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F43" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C44">
         <v>48.189685104221404</v>
@@ -4749,18 +5134,18 @@
         <v>23</v>
       </c>
       <c r="E44" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F44" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B45" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C45">
         <v>16.699244233993625</v>
@@ -4769,1626 +5154,1626 @@
         <v>23</v>
       </c>
       <c r="E45" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F45" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B46" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C46">
         <v>39.746196000000005</v>
       </c>
       <c r="D46" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E46" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F46" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B47" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C47">
         <v>0.44283295832701008</v>
       </c>
       <c r="F47" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B48" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C48">
         <v>233372.96903833433</v>
       </c>
       <c r="F48" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B49" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C49">
         <v>130688.86266146721</v>
       </c>
       <c r="F49" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B50" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C50">
         <v>34.194077618408031</v>
       </c>
       <c r="F50" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B51" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C51">
         <v>15.480365443172449</v>
       </c>
       <c r="F51" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B52" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C52">
         <v>3.8</v>
       </c>
       <c r="F52" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B53" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C53">
         <v>-1.52</v>
       </c>
       <c r="F53" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B54" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C54">
         <v>5.6999999999999993</v>
       </c>
       <c r="F54" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B55" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C55">
         <v>-2.2800000000000002</v>
       </c>
       <c r="F55" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B56" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C56">
         <v>18.622682892532463</v>
       </c>
       <c r="F56" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B57" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C57">
         <v>27.131986877647702</v>
       </c>
       <c r="F57" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B58" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C58">
         <v>25.580006542099976</v>
       </c>
       <c r="F58" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B59" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C59">
         <v>28.422229491222197</v>
       </c>
       <c r="F59" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B60" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C60">
         <v>6.3586494759793881</v>
       </c>
       <c r="F60" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B61" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C61">
         <v>11.113261724726186</v>
       </c>
       <c r="F61" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B62" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C62">
         <v>1.9300000000000015</v>
       </c>
       <c r="F62" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B63" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C63">
         <v>11.008581406383897</v>
       </c>
       <c r="F63" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B64" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C64" t="b">
         <v>1</v>
       </c>
       <c r="F64" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B65" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C65">
         <v>7.4507370536077033</v>
       </c>
       <c r="F65" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B66" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C66">
         <v>20.550728554427437</v>
       </c>
       <c r="F66" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B67" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C67">
         <v>4.0264472875839541</v>
       </c>
       <c r="F67" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B68" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C68">
         <v>77.116605805538327</v>
       </c>
       <c r="F68" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B69" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C69">
         <v>22.608098531363336</v>
       </c>
       <c r="F69" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B70" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C70">
         <v>12.709922788411269</v>
       </c>
       <c r="F70" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B71" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C71">
         <v>16.27392540932771</v>
       </c>
       <c r="F71" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B72" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C72">
         <v>15.956485750905872</v>
       </c>
       <c r="F72" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B73" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C73">
         <v>13.695854805920606</v>
       </c>
       <c r="F73" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B74" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C74">
         <v>1.0954451150103324</v>
       </c>
       <c r="F74" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B75" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C75">
         <v>24.094842552110709</v>
       </c>
       <c r="F75" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B76" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C76" t="b">
         <v>1</v>
       </c>
       <c r="F76" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B77" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C77">
         <v>150.69320484179264</v>
       </c>
       <c r="F77" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B78" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C78">
         <v>46195.337793815328</v>
       </c>
       <c r="F78" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B79" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C79" t="b">
         <v>1</v>
       </c>
       <c r="F79" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B80" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C80" t="b">
         <v>1</v>
       </c>
       <c r="F80" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B81" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C81">
         <v>890</v>
       </c>
       <c r="F81" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B82" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C82">
         <v>13</v>
       </c>
       <c r="F82" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B83" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C83">
         <v>84493.524867651882</v>
       </c>
       <c r="F83" t="s">
-        <v>377</v>
+ 